--- a/GreenPath_PM_Jobs_Test_Report.xlsx
+++ b/GreenPath_PM_Jobs_Test_Report.xlsx
@@ -428,7 +428,7 @@
         <v>Test Execution Date</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-09-13T01:32:44.135Z</v>
+        <v>2026-09-14T01:50:53.604Z</v>
       </c>
     </row>
     <row r="4">
@@ -524,7 +524,7 @@
         <v>Cities Supported</v>
       </c>
       <c r="B15" t="str">
-        <v>New York, San Francisco, Toronto, Dublin, Remote, USA, London, Seattle, N/A, United States, Bengaluru, Paris, Menlo Park, Hybrid, In-Office, Canada, Spain, Israel, Greece, Hungary, Portugal, Riyadh, Beijing, Pittsburgh, Tel Aviv, Vienna, North America, Washington, Mumbai, Gurgaon</v>
+        <v>New York, San Francisco, Toronto, Dublin, Remote, USA, London, Seattle, N/A, United States, Bengaluru, Paris, Menlo Park, Hybrid, In-Office, Canada, Spain, Israel, Norway, Poland, Riyadh, Beijing, Pittsburgh, Tel Aviv, Vienna, North America, Washington, Mumbai, Gurgaon</v>
       </c>
     </row>
     <row r="16">
@@ -694,7 +694,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O2" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P2" t="str">
         <v>Today</v>
@@ -703,10 +703,10 @@
         <v>No</v>
       </c>
       <c r="R2" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S2">
-        <v>27</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3">
@@ -753,7 +753,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O3" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P3" t="str">
         <v>Today</v>
@@ -765,7 +765,7 @@
         <v>No</v>
       </c>
       <c r="S3">
-        <v>72</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4">
@@ -812,7 +812,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O4" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P4" t="str">
         <v>Today</v>
@@ -821,10 +821,10 @@
         <v>No</v>
       </c>
       <c r="R4" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S4">
-        <v>81</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5">
@@ -871,19 +871,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O5" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P5" t="str">
         <v>Today</v>
       </c>
       <c r="Q5" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R5" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S5">
-        <v>40</v>
+        <v>78</v>
       </c>
     </row>
     <row r="6">
@@ -930,7 +930,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O6" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P6" t="str">
         <v>Today</v>
@@ -939,10 +939,10 @@
         <v>No</v>
       </c>
       <c r="R6" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S6">
-        <v>54</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7">
@@ -989,7 +989,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O7" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P7" t="str">
         <v>Today</v>
@@ -998,10 +998,10 @@
         <v>No</v>
       </c>
       <c r="R7" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S7">
-        <v>60</v>
+        <v>88</v>
       </c>
     </row>
     <row r="8">
@@ -1048,7 +1048,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O8" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P8" t="str">
         <v>Today</v>
@@ -1060,7 +1060,7 @@
         <v>No</v>
       </c>
       <c r="S8">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
@@ -1107,7 +1107,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O9" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P9" t="str">
         <v>Today</v>
@@ -1119,7 +1119,7 @@
         <v>No</v>
       </c>
       <c r="S9">
-        <v>26</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
@@ -1166,19 +1166,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O10" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P10" t="str">
         <v>Today</v>
       </c>
       <c r="Q10" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R10" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S10">
-        <v>66</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
@@ -1225,19 +1225,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O11" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P11" t="str">
         <v>Today</v>
       </c>
       <c r="Q11" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R11" t="str">
         <v>No</v>
       </c>
       <c r="S11">
-        <v>69</v>
+        <v>51</v>
       </c>
     </row>
     <row r="12">
@@ -1284,7 +1284,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O12" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P12" t="str">
         <v>Today</v>
@@ -1293,10 +1293,10 @@
         <v>No</v>
       </c>
       <c r="R12" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S12">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13">
@@ -1343,19 +1343,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O13" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P13" t="str">
         <v>Today</v>
       </c>
       <c r="Q13" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R13" t="str">
         <v>Yes</v>
       </c>
       <c r="S13">
-        <v>82</v>
+        <v>63</v>
       </c>
     </row>
     <row r="14">
@@ -1402,13 +1402,13 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O14" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P14" t="str">
         <v>Today</v>
       </c>
       <c r="Q14" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R14" t="str">
         <v>No</v>
@@ -1461,19 +1461,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O15" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P15" t="str">
         <v>Today</v>
       </c>
       <c r="Q15" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R15" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S15">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16">
@@ -1520,19 +1520,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O16" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P16" t="str">
         <v>Today</v>
       </c>
       <c r="Q16" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R16" t="str">
         <v>No</v>
       </c>
       <c r="S16">
-        <v>50</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17">
@@ -1579,19 +1579,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O17" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P17" t="str">
         <v>Today</v>
       </c>
       <c r="Q17" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R17" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S17">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="18">
@@ -1638,19 +1638,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O18" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P18" t="str">
         <v>Today</v>
       </c>
       <c r="Q18" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R18" t="str">
         <v>No</v>
       </c>
       <c r="S18">
-        <v>59</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
@@ -1697,7 +1697,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O19" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P19" t="str">
         <v>Today</v>
@@ -1706,10 +1706,10 @@
         <v>No</v>
       </c>
       <c r="R19" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S19">
-        <v>42</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20">
@@ -1756,7 +1756,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O20" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P20" t="str">
         <v>Today</v>
@@ -1768,7 +1768,7 @@
         <v>Yes</v>
       </c>
       <c r="S20">
-        <v>27</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21">
@@ -1815,7 +1815,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O21" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P21" t="str">
         <v>Today</v>
@@ -1827,7 +1827,7 @@
         <v>No</v>
       </c>
       <c r="S21">
-        <v>90</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22">
@@ -1874,7 +1874,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O22" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P22" t="str">
         <v>Today</v>
@@ -1883,10 +1883,10 @@
         <v>No</v>
       </c>
       <c r="R22" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S22">
-        <v>58</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23">
@@ -1933,7 +1933,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O23" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P23" t="str">
         <v>Today</v>
@@ -1942,10 +1942,10 @@
         <v>No</v>
       </c>
       <c r="R23" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S23">
-        <v>38</v>
+        <v>75</v>
       </c>
     </row>
     <row r="24">
@@ -1992,7 +1992,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O24" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P24" t="str">
         <v>Today</v>
@@ -2004,7 +2004,7 @@
         <v>No</v>
       </c>
       <c r="S24">
-        <v>58</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25">
@@ -2030,10 +2030,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H25" t="str">
-        <v>Dublin</v>
+        <v>London</v>
       </c>
       <c r="I25" t="str">
-        <v>Dublin</v>
+        <v>London</v>
       </c>
       <c r="J25" t="str">
         <v>On-site</v>
@@ -2042,7 +2042,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L25" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/7737526</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/8142649</v>
       </c>
       <c r="M25">
         <v>200</v>
@@ -2051,7 +2051,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O25" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P25" t="str">
         <v>Today</v>
@@ -2060,10 +2060,10 @@
         <v>No</v>
       </c>
       <c r="R25" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S25">
-        <v>76</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26">
@@ -2110,7 +2110,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O26" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P26" t="str">
         <v>Today</v>
@@ -2119,10 +2119,10 @@
         <v>Yes</v>
       </c>
       <c r="R26" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S26">
-        <v>31</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27">
@@ -2169,7 +2169,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O27" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P27" t="str">
         <v>Today</v>
@@ -2178,10 +2178,10 @@
         <v>No</v>
       </c>
       <c r="R27" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S27">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="28">
@@ -2228,7 +2228,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O28" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P28" t="str">
         <v>Today</v>
@@ -2240,7 +2240,7 @@
         <v>No</v>
       </c>
       <c r="S28">
-        <v>41</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29">
@@ -2287,7 +2287,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O29" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P29" t="str">
         <v>Today</v>
@@ -2296,10 +2296,10 @@
         <v>No</v>
       </c>
       <c r="R29" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S29">
-        <v>44</v>
+        <v>53</v>
       </c>
     </row>
     <row r="30">
@@ -2346,19 +2346,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O30" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P30" t="str">
         <v>Today</v>
       </c>
       <c r="Q30" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R30" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S30">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="31">
@@ -2405,19 +2405,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O31" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P31" t="str">
         <v>Today</v>
       </c>
       <c r="Q31" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R31" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S31">
-        <v>90</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32">
@@ -2464,19 +2464,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O32" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P32" t="str">
         <v>Today</v>
       </c>
       <c r="Q32" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R32" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S32">
-        <v>73</v>
+        <v>86</v>
       </c>
     </row>
     <row r="33">
@@ -2523,7 +2523,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O33" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P33" t="str">
         <v>Today</v>
@@ -2532,10 +2532,10 @@
         <v>No</v>
       </c>
       <c r="R33" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S33">
-        <v>41</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34">
@@ -2582,7 +2582,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O34" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P34" t="str">
         <v>Today</v>
@@ -2591,10 +2591,10 @@
         <v>No</v>
       </c>
       <c r="R34" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S34">
-        <v>55</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35">
@@ -2641,7 +2641,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O35" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P35" t="str">
         <v>Today</v>
@@ -2653,7 +2653,7 @@
         <v>No</v>
       </c>
       <c r="S35">
-        <v>66</v>
+        <v>36</v>
       </c>
     </row>
     <row r="36">
@@ -2700,19 +2700,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O36" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P36" t="str">
         <v>Today</v>
       </c>
       <c r="Q36" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R36" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S36">
-        <v>71</v>
+        <v>54</v>
       </c>
     </row>
     <row r="37">
@@ -2759,19 +2759,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O37" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P37" t="str">
         <v>Today</v>
       </c>
       <c r="Q37" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R37" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S37">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="38">
@@ -2818,19 +2818,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O38" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P38" t="str">
         <v>Today</v>
       </c>
       <c r="Q38" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R38" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S38">
-        <v>30</v>
+        <v>92</v>
       </c>
     </row>
     <row r="39">
@@ -2877,19 +2877,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O39" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P39" t="str">
         <v>Today</v>
       </c>
       <c r="Q39" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R39" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S39">
-        <v>30</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40">
@@ -2936,19 +2936,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O40" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P40" t="str">
         <v>Today</v>
       </c>
       <c r="Q40" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R40" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S40">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="41">
@@ -2995,19 +2995,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O41" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P41" t="str">
         <v>Today</v>
       </c>
       <c r="Q41" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R41" t="str">
         <v>No</v>
       </c>
       <c r="S41">
-        <v>36</v>
+        <v>57</v>
       </c>
     </row>
     <row r="42">
@@ -3033,10 +3033,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H42" t="str">
-        <v>Boston, Massachusetts, USA; New York, New York, USA</v>
+        <v>Paris, France</v>
       </c>
       <c r="I42" t="str">
-        <v>New York</v>
+        <v>Paris</v>
       </c>
       <c r="J42" t="str">
         <v>On-site</v>
@@ -3045,7 +3045,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L42" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/7982288</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/8012549</v>
       </c>
       <c r="M42">
         <v>200</v>
@@ -3054,7 +3054,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O42" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P42" t="str">
         <v>Today</v>
@@ -3066,7 +3066,7 @@
         <v>No</v>
       </c>
       <c r="S42">
-        <v>62</v>
+        <v>31</v>
       </c>
     </row>
     <row r="43">
@@ -3113,19 +3113,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O43" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P43" t="str">
         <v>Today</v>
       </c>
       <c r="Q43" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R43" t="str">
         <v>No</v>
       </c>
       <c r="S43">
-        <v>57</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44">
@@ -3172,7 +3172,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O44" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P44" t="str">
         <v>Today</v>
@@ -3181,10 +3181,10 @@
         <v>No</v>
       </c>
       <c r="R44" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S44">
-        <v>78</v>
+        <v>83</v>
       </c>
     </row>
     <row r="45">
@@ -3231,7 +3231,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O45" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P45" t="str">
         <v>Today</v>
@@ -3243,7 +3243,7 @@
         <v>No</v>
       </c>
       <c r="S45">
-        <v>33</v>
+        <v>69</v>
       </c>
     </row>
     <row r="46">
@@ -3290,7 +3290,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O46" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P46" t="str">
         <v>Today</v>
@@ -3299,10 +3299,10 @@
         <v>No</v>
       </c>
       <c r="R46" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S46">
-        <v>72</v>
+        <v>86</v>
       </c>
     </row>
     <row r="47">
@@ -3349,7 +3349,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O47" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P47" t="str">
         <v>Today</v>
@@ -3358,10 +3358,10 @@
         <v>No</v>
       </c>
       <c r="R47" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S47">
-        <v>37</v>
+        <v>56</v>
       </c>
     </row>
     <row r="48">
@@ -3408,19 +3408,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O48" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P48" t="str">
         <v>Today</v>
       </c>
       <c r="Q48" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R48" t="str">
         <v>No</v>
       </c>
       <c r="S48">
-        <v>89</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49">
@@ -3467,19 +3467,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O49" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P49" t="str">
         <v>Today</v>
       </c>
       <c r="Q49" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R49" t="str">
         <v>No</v>
       </c>
       <c r="S49">
-        <v>36</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50">
@@ -3526,7 +3526,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O50" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P50" t="str">
         <v>Today</v>
@@ -3538,7 +3538,7 @@
         <v>No</v>
       </c>
       <c r="S50">
-        <v>40</v>
+        <v>69</v>
       </c>
     </row>
     <row r="51">
@@ -3585,7 +3585,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O51" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P51" t="str">
         <v>Today</v>
@@ -3594,10 +3594,10 @@
         <v>No</v>
       </c>
       <c r="R51" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S51">
-        <v>85</v>
+        <v>56</v>
       </c>
     </row>
     <row r="52">
@@ -3644,7 +3644,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O52" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P52" t="str">
         <v>Today</v>
@@ -3656,7 +3656,7 @@
         <v>No</v>
       </c>
       <c r="S52">
-        <v>54</v>
+        <v>32</v>
       </c>
     </row>
     <row r="53">
@@ -3703,19 +3703,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O53" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P53" t="str">
         <v>Today</v>
       </c>
       <c r="Q53" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R53" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S53">
-        <v>43</v>
+        <v>55</v>
       </c>
     </row>
     <row r="54">
@@ -3762,7 +3762,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O54" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P54" t="str">
         <v>Today</v>
@@ -3774,7 +3774,7 @@
         <v>No</v>
       </c>
       <c r="S54">
-        <v>31</v>
+        <v>58</v>
       </c>
     </row>
     <row r="55">
@@ -3821,19 +3821,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O55" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P55" t="str">
         <v>Today</v>
       </c>
       <c r="Q55" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R55" t="str">
         <v>No</v>
       </c>
       <c r="S55">
-        <v>94</v>
+        <v>44</v>
       </c>
     </row>
     <row r="56">
@@ -3880,7 +3880,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O56" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P56" t="str">
         <v>Today</v>
@@ -3892,7 +3892,7 @@
         <v>Yes</v>
       </c>
       <c r="S56">
-        <v>87</v>
+        <v>94</v>
       </c>
     </row>
     <row r="57">
@@ -3939,19 +3939,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O57" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P57" t="str">
         <v>Today</v>
       </c>
       <c r="Q57" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R57" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S57">
-        <v>68</v>
+        <v>40</v>
       </c>
     </row>
     <row r="58">
@@ -3998,7 +3998,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O58" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P58" t="str">
         <v>Today</v>
@@ -4007,10 +4007,10 @@
         <v>No</v>
       </c>
       <c r="R58" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S58">
-        <v>84</v>
+        <v>29</v>
       </c>
     </row>
     <row r="59">
@@ -4057,19 +4057,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O59" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P59" t="str">
         <v>Today</v>
       </c>
       <c r="Q59" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R59" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S59">
-        <v>69</v>
+        <v>92</v>
       </c>
     </row>
     <row r="60">
@@ -4116,7 +4116,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O60" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P60" t="str">
         <v>Today</v>
@@ -4128,7 +4128,7 @@
         <v>No</v>
       </c>
       <c r="S60">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="61">
@@ -4175,19 +4175,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O61" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P61" t="str">
         <v>Today</v>
       </c>
       <c r="Q61" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R61" t="str">
         <v>No</v>
       </c>
       <c r="S61">
-        <v>59</v>
+        <v>26</v>
       </c>
     </row>
     <row r="62">
@@ -4234,7 +4234,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O62" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P62" t="str">
         <v>Today</v>
@@ -4243,10 +4243,10 @@
         <v>No</v>
       </c>
       <c r="R62" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S62">
-        <v>34</v>
+        <v>84</v>
       </c>
     </row>
     <row r="63">
@@ -4293,7 +4293,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O63" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P63" t="str">
         <v>Today</v>
@@ -4305,7 +4305,7 @@
         <v>No</v>
       </c>
       <c r="S63">
-        <v>87</v>
+        <v>44</v>
       </c>
     </row>
     <row r="64">
@@ -4352,19 +4352,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O64" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P64" t="str">
         <v>Today</v>
       </c>
       <c r="Q64" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R64" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S64">
-        <v>74</v>
+        <v>32</v>
       </c>
     </row>
     <row r="65">
@@ -4411,19 +4411,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O65" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P65" t="str">
         <v>Today</v>
       </c>
       <c r="Q65" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R65" t="str">
         <v>No</v>
       </c>
       <c r="S65">
-        <v>63</v>
+        <v>93</v>
       </c>
     </row>
     <row r="66">
@@ -4470,19 +4470,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O66" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P66" t="str">
         <v>Today</v>
       </c>
       <c r="Q66" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R66" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S66">
-        <v>33</v>
+        <v>61</v>
       </c>
     </row>
     <row r="67">
@@ -4529,7 +4529,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O67" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P67" t="str">
         <v>Today</v>
@@ -4541,7 +4541,7 @@
         <v>No</v>
       </c>
       <c r="S67">
-        <v>59</v>
+        <v>94</v>
       </c>
     </row>
     <row r="68">
@@ -4588,19 +4588,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O68" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P68" t="str">
         <v>Today</v>
       </c>
       <c r="Q68" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R68" t="str">
         <v>No</v>
       </c>
       <c r="S68">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
     <row r="69">
@@ -4647,7 +4647,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O69" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P69" t="str">
         <v>Today</v>
@@ -4659,7 +4659,7 @@
         <v>No</v>
       </c>
       <c r="S69">
-        <v>87</v>
+        <v>82</v>
       </c>
     </row>
     <row r="70">
@@ -4706,7 +4706,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O70" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P70" t="str">
         <v>Today</v>
@@ -4715,10 +4715,10 @@
         <v>No</v>
       </c>
       <c r="R70" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S70">
-        <v>81</v>
+        <v>50</v>
       </c>
     </row>
     <row r="71">
@@ -4765,7 +4765,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O71" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P71" t="str">
         <v>Today</v>
@@ -4774,10 +4774,10 @@
         <v>No</v>
       </c>
       <c r="R71" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S71">
-        <v>51</v>
+        <v>44</v>
       </c>
     </row>
     <row r="72">
@@ -4824,7 +4824,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O72" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P72" t="str">
         <v>Today</v>
@@ -4836,7 +4836,7 @@
         <v>Yes</v>
       </c>
       <c r="S72">
-        <v>44</v>
+        <v>65</v>
       </c>
     </row>
     <row r="73">
@@ -4883,7 +4883,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O73" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P73" t="str">
         <v>Today</v>
@@ -4895,7 +4895,7 @@
         <v>No</v>
       </c>
       <c r="S73">
-        <v>33</v>
+        <v>48</v>
       </c>
     </row>
     <row r="74">
@@ -4942,19 +4942,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O74" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P74" t="str">
         <v>Today</v>
       </c>
       <c r="Q74" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R74" t="str">
         <v>No</v>
       </c>
       <c r="S74">
-        <v>37</v>
+        <v>67</v>
       </c>
     </row>
     <row r="75">
@@ -5001,7 +5001,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O75" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P75" t="str">
         <v>Today</v>
@@ -5013,7 +5013,7 @@
         <v>Yes</v>
       </c>
       <c r="S75">
-        <v>54</v>
+        <v>64</v>
       </c>
     </row>
     <row r="76">
@@ -5060,19 +5060,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O76" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P76" t="str">
         <v>Today</v>
       </c>
       <c r="Q76" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R76" t="str">
         <v>No</v>
       </c>
       <c r="S76">
-        <v>82</v>
+        <v>55</v>
       </c>
     </row>
     <row r="77">
@@ -5119,19 +5119,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O77" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P77" t="str">
         <v>Today</v>
       </c>
       <c r="Q77" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R77" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S77">
-        <v>79</v>
+        <v>31</v>
       </c>
     </row>
     <row r="78">
@@ -5178,7 +5178,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O78" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P78" t="str">
         <v>Today</v>
@@ -5190,7 +5190,7 @@
         <v>No</v>
       </c>
       <c r="S78">
-        <v>87</v>
+        <v>35</v>
       </c>
     </row>
     <row r="79">
@@ -5237,7 +5237,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O79" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P79" t="str">
         <v>Today</v>
@@ -5249,7 +5249,7 @@
         <v>No</v>
       </c>
       <c r="S79">
-        <v>44</v>
+        <v>87</v>
       </c>
     </row>
     <row r="80">
@@ -5296,19 +5296,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O80" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P80" t="str">
         <v>Today</v>
       </c>
       <c r="Q80" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R80" t="str">
         <v>No</v>
       </c>
       <c r="S80">
-        <v>48</v>
+        <v>91</v>
       </c>
     </row>
     <row r="81">
@@ -5355,19 +5355,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O81" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P81" t="str">
         <v>Today</v>
       </c>
       <c r="Q81" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R81" t="str">
         <v>No</v>
       </c>
       <c r="S81">
-        <v>53</v>
+        <v>33</v>
       </c>
     </row>
     <row r="82">
@@ -5414,19 +5414,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O82" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P82" t="str">
         <v>Today</v>
       </c>
       <c r="Q82" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R82" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S82">
-        <v>56</v>
+        <v>48</v>
       </c>
     </row>
     <row r="83">
@@ -5473,7 +5473,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O83" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P83" t="str">
         <v>Today</v>
@@ -5485,7 +5485,7 @@
         <v>No</v>
       </c>
       <c r="S83">
-        <v>59</v>
+        <v>73</v>
       </c>
     </row>
     <row r="84">
@@ -5532,19 +5532,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O84" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P84" t="str">
         <v>Today</v>
       </c>
       <c r="Q84" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R84" t="str">
         <v>No</v>
       </c>
       <c r="S84">
-        <v>67</v>
+        <v>79</v>
       </c>
     </row>
     <row r="85">
@@ -5591,7 +5591,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O85" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P85" t="str">
         <v>Today</v>
@@ -5600,10 +5600,10 @@
         <v>No</v>
       </c>
       <c r="R85" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S85">
-        <v>65</v>
+        <v>38</v>
       </c>
     </row>
     <row r="86">
@@ -5650,7 +5650,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O86" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P86" t="str">
         <v>Today</v>
@@ -5662,7 +5662,7 @@
         <v>No</v>
       </c>
       <c r="S86">
-        <v>87</v>
+        <v>75</v>
       </c>
     </row>
     <row r="87">
@@ -5688,10 +5688,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H87" t="str">
-        <v>Greece</v>
+        <v>Canada</v>
       </c>
       <c r="I87" t="str">
-        <v>Greece</v>
+        <v>Canada</v>
       </c>
       <c r="J87" t="str">
         <v>On-site</v>
@@ -5700,7 +5700,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L87" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8066510</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8066646</v>
       </c>
       <c r="M87">
         <v>200</v>
@@ -5709,19 +5709,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O87" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P87" t="str">
         <v>Today</v>
       </c>
       <c r="Q87" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R87" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S87">
-        <v>77</v>
+        <v>74</v>
       </c>
     </row>
     <row r="88">
@@ -5747,10 +5747,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H88" t="str">
-        <v>Hungary</v>
+        <v>Norway</v>
       </c>
       <c r="I88" t="str">
-        <v>Hungary</v>
+        <v>Norway</v>
       </c>
       <c r="J88" t="str">
         <v>On-site</v>
@@ -5759,7 +5759,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L88" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8041209</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8041211</v>
       </c>
       <c r="M88">
         <v>200</v>
@@ -5768,19 +5768,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O88" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P88" t="str">
         <v>Today</v>
       </c>
       <c r="Q88" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R88" t="str">
         <v>No</v>
       </c>
       <c r="S88">
-        <v>39</v>
+        <v>35</v>
       </c>
     </row>
     <row r="89">
@@ -5806,10 +5806,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H89" t="str">
-        <v>Portugal</v>
+        <v>Poland</v>
       </c>
       <c r="I89" t="str">
-        <v>Portugal</v>
+        <v>Poland</v>
       </c>
       <c r="J89" t="str">
         <v>On-site</v>
@@ -5818,7 +5818,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L89" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8194128</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8194139</v>
       </c>
       <c r="M89">
         <v>200</v>
@@ -5827,7 +5827,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O89" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P89" t="str">
         <v>Today</v>
@@ -5836,10 +5836,10 @@
         <v>No</v>
       </c>
       <c r="R89" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S89">
-        <v>80</v>
+        <v>47</v>
       </c>
     </row>
     <row r="90">
@@ -5886,19 +5886,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O90" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P90" t="str">
         <v>Today</v>
       </c>
       <c r="Q90" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R90" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S90">
-        <v>82</v>
+        <v>92</v>
       </c>
     </row>
     <row r="91">
@@ -5945,19 +5945,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O91" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P91" t="str">
         <v>Today</v>
       </c>
       <c r="Q91" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R91" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S91">
-        <v>64</v>
+        <v>85</v>
       </c>
     </row>
     <row r="92">
@@ -6004,19 +6004,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O92" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P92" t="str">
         <v>Today</v>
       </c>
       <c r="Q92" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R92" t="str">
         <v>No</v>
       </c>
       <c r="S92">
-        <v>81</v>
+        <v>40</v>
       </c>
     </row>
     <row r="93">
@@ -6063,7 +6063,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O93" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P93" t="str">
         <v>Today</v>
@@ -6075,7 +6075,7 @@
         <v>No</v>
       </c>
       <c r="S93">
-        <v>88</v>
+        <v>65</v>
       </c>
     </row>
     <row r="94">
@@ -6122,7 +6122,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O94" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P94" t="str">
         <v>Today</v>
@@ -6134,7 +6134,7 @@
         <v>No</v>
       </c>
       <c r="S94">
-        <v>29</v>
+        <v>70</v>
       </c>
     </row>
     <row r="95">
@@ -6181,19 +6181,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O95" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P95" t="str">
         <v>Today</v>
       </c>
       <c r="Q95" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R95" t="str">
         <v>No</v>
       </c>
       <c r="S95">
-        <v>78</v>
+        <v>89</v>
       </c>
     </row>
     <row r="96">
@@ -6240,7 +6240,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O96" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P96" t="str">
         <v>Today</v>
@@ -6249,10 +6249,10 @@
         <v>No</v>
       </c>
       <c r="R96" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S96">
-        <v>36</v>
+        <v>75</v>
       </c>
     </row>
     <row r="97">
@@ -6299,7 +6299,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O97" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P97" t="str">
         <v>Today</v>
@@ -6311,7 +6311,7 @@
         <v>Yes</v>
       </c>
       <c r="S97">
-        <v>45</v>
+        <v>29</v>
       </c>
     </row>
     <row r="98">
@@ -6358,7 +6358,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O98" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P98" t="str">
         <v>Today</v>
@@ -6370,7 +6370,7 @@
         <v>Yes</v>
       </c>
       <c r="S98">
-        <v>42</v>
+        <v>90</v>
       </c>
     </row>
     <row r="99">
@@ -6417,7 +6417,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O99" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P99" t="str">
         <v>Today</v>
@@ -6426,10 +6426,10 @@
         <v>Yes</v>
       </c>
       <c r="R99" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S99">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="100">
@@ -6476,7 +6476,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O100" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P100" t="str">
         <v>Today</v>
@@ -6488,7 +6488,7 @@
         <v>No</v>
       </c>
       <c r="S100">
-        <v>89</v>
+        <v>77</v>
       </c>
     </row>
     <row r="101">
@@ -6535,19 +6535,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O101" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P101" t="str">
         <v>Today</v>
       </c>
       <c r="Q101" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R101" t="str">
         <v>No</v>
       </c>
       <c r="S101">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="102">
@@ -6594,7 +6594,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O102" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P102" t="str">
         <v>Today</v>
@@ -6603,10 +6603,10 @@
         <v>No</v>
       </c>
       <c r="R102" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S102">
-        <v>89</v>
+        <v>52</v>
       </c>
     </row>
     <row r="103">
@@ -6653,7 +6653,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O103" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P103" t="str">
         <v>Today</v>
@@ -6665,7 +6665,7 @@
         <v>Yes</v>
       </c>
       <c r="S103">
-        <v>78</v>
+        <v>89</v>
       </c>
     </row>
     <row r="104">
@@ -6712,7 +6712,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O104" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P104" t="str">
         <v>Today</v>
@@ -6724,7 +6724,7 @@
         <v>No</v>
       </c>
       <c r="S104">
-        <v>56</v>
+        <v>46</v>
       </c>
     </row>
     <row r="105">
@@ -6771,7 +6771,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O105" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P105" t="str">
         <v>Today</v>
@@ -6780,10 +6780,10 @@
         <v>No</v>
       </c>
       <c r="R105" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S105">
-        <v>57</v>
+        <v>45</v>
       </c>
     </row>
     <row r="106">
@@ -6830,7 +6830,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O106" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P106" t="str">
         <v>Today</v>
@@ -6889,19 +6889,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O107" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P107" t="str">
         <v>Today</v>
       </c>
       <c r="Q107" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R107" t="str">
         <v>No</v>
       </c>
       <c r="S107">
-        <v>87</v>
+        <v>75</v>
       </c>
     </row>
     <row r="108">
@@ -6948,19 +6948,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O108" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P108" t="str">
         <v>Today</v>
       </c>
       <c r="Q108" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R108" t="str">
         <v>Yes</v>
       </c>
       <c r="S108">
-        <v>33</v>
+        <v>75</v>
       </c>
     </row>
     <row r="109">
@@ -7007,7 +7007,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O109" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P109" t="str">
         <v>Today</v>
@@ -7016,10 +7016,10 @@
         <v>No</v>
       </c>
       <c r="R109" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S109">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="110">
@@ -7066,7 +7066,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O110" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P110" t="str">
         <v>Today</v>
@@ -7075,10 +7075,10 @@
         <v>No</v>
       </c>
       <c r="R110" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S110">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
     <row r="111">
@@ -7125,7 +7125,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O111" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P111" t="str">
         <v>Today</v>
@@ -7137,7 +7137,7 @@
         <v>Yes</v>
       </c>
       <c r="S111">
-        <v>52</v>
+        <v>59</v>
       </c>
     </row>
     <row r="112">
@@ -7184,19 +7184,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O112" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P112" t="str">
         <v>Today</v>
       </c>
       <c r="Q112" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R112" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S112">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="113">
@@ -7243,19 +7243,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O113" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P113" t="str">
         <v>Today</v>
       </c>
       <c r="Q113" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R113" t="str">
         <v>No</v>
       </c>
       <c r="S113">
-        <v>28</v>
+        <v>49</v>
       </c>
     </row>
     <row r="114">
@@ -7302,19 +7302,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O114" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P114" t="str">
         <v>Today</v>
       </c>
       <c r="Q114" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R114" t="str">
         <v>No</v>
       </c>
       <c r="S114">
-        <v>47</v>
+        <v>51</v>
       </c>
     </row>
     <row r="115">
@@ -7361,19 +7361,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O115" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P115" t="str">
         <v>Today</v>
       </c>
       <c r="Q115" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R115" t="str">
         <v>No</v>
       </c>
       <c r="S115">
-        <v>46</v>
+        <v>73</v>
       </c>
     </row>
     <row r="116">
@@ -7420,7 +7420,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O116" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P116" t="str">
         <v>Today</v>
@@ -7429,10 +7429,10 @@
         <v>Yes</v>
       </c>
       <c r="R116" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S116">
-        <v>80</v>
+        <v>45</v>
       </c>
     </row>
     <row r="117">
@@ -7479,7 +7479,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O117" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P117" t="str">
         <v>Today</v>
@@ -7491,7 +7491,7 @@
         <v>No</v>
       </c>
       <c r="S117">
-        <v>85</v>
+        <v>70</v>
       </c>
     </row>
     <row r="118">
@@ -7538,7 +7538,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O118" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P118" t="str">
         <v>Today</v>
@@ -7550,7 +7550,7 @@
         <v>Yes</v>
       </c>
       <c r="S118">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="119">
@@ -7597,19 +7597,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O119" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P119" t="str">
         <v>Today</v>
       </c>
       <c r="Q119" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R119" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S119">
-        <v>86</v>
+        <v>37</v>
       </c>
     </row>
     <row r="120">
@@ -7656,19 +7656,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O120" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P120" t="str">
         <v>Today</v>
       </c>
       <c r="Q120" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R120" t="str">
         <v>No</v>
       </c>
       <c r="S120">
-        <v>61</v>
+        <v>71</v>
       </c>
     </row>
     <row r="121">
@@ -7715,7 +7715,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O121" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P121" t="str">
         <v>Today</v>
@@ -7727,7 +7727,7 @@
         <v>No</v>
       </c>
       <c r="S121">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="122">
@@ -7774,7 +7774,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O122" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P122" t="str">
         <v>Today</v>
@@ -7786,7 +7786,7 @@
         <v>No</v>
       </c>
       <c r="S122">
-        <v>42</v>
+        <v>74</v>
       </c>
     </row>
     <row r="123">
@@ -7833,19 +7833,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O123" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P123" t="str">
         <v>Today</v>
       </c>
       <c r="Q123" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R123" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S123">
-        <v>88</v>
+        <v>32</v>
       </c>
     </row>
     <row r="124">
@@ -7892,19 +7892,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O124" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P124" t="str">
         <v>Today</v>
       </c>
       <c r="Q124" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R124" t="str">
         <v>No</v>
       </c>
       <c r="S124">
-        <v>55</v>
+        <v>35</v>
       </c>
     </row>
     <row r="125">
@@ -7951,19 +7951,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O125" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P125" t="str">
         <v>Today</v>
       </c>
       <c r="Q125" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R125" t="str">
         <v>No</v>
       </c>
       <c r="S125">
-        <v>90</v>
+        <v>63</v>
       </c>
     </row>
     <row r="126">
@@ -8010,7 +8010,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O126" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P126" t="str">
         <v>Today</v>
@@ -8019,10 +8019,10 @@
         <v>Yes</v>
       </c>
       <c r="R126" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S126">
-        <v>39</v>
+        <v>70</v>
       </c>
     </row>
     <row r="127">
@@ -8069,19 +8069,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O127" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P127" t="str">
         <v>Today</v>
       </c>
       <c r="Q127" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R127" t="str">
         <v>No</v>
       </c>
       <c r="S127">
-        <v>50</v>
+        <v>71</v>
       </c>
     </row>
     <row r="128">
@@ -8128,19 +8128,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O128" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P128" t="str">
         <v>Today</v>
       </c>
       <c r="Q128" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R128" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S128">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="129">
@@ -8187,19 +8187,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O129" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P129" t="str">
         <v>Today</v>
       </c>
       <c r="Q129" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R129" t="str">
         <v>No</v>
       </c>
       <c r="S129">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="130">
@@ -8246,7 +8246,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O130" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P130" t="str">
         <v>Today</v>
@@ -8258,7 +8258,7 @@
         <v>No</v>
       </c>
       <c r="S130">
-        <v>46</v>
+        <v>73</v>
       </c>
     </row>
     <row r="131">
@@ -8305,19 +8305,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O131" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P131" t="str">
         <v>Today</v>
       </c>
       <c r="Q131" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R131" t="str">
         <v>No</v>
       </c>
       <c r="S131">
-        <v>89</v>
+        <v>36</v>
       </c>
     </row>
     <row r="132">
@@ -8364,7 +8364,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O132" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P132" t="str">
         <v>Today</v>
@@ -8373,10 +8373,10 @@
         <v>No</v>
       </c>
       <c r="R132" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S132">
-        <v>30</v>
+        <v>77</v>
       </c>
     </row>
     <row r="133">
@@ -8423,19 +8423,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O133" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P133" t="str">
         <v>Today</v>
       </c>
       <c r="Q133" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R133" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S133">
-        <v>90</v>
+        <v>64</v>
       </c>
     </row>
     <row r="134">
@@ -8482,19 +8482,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O134" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P134" t="str">
         <v>Today</v>
       </c>
       <c r="Q134" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R134" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S134">
-        <v>39</v>
+        <v>67</v>
       </c>
     </row>
     <row r="135">
@@ -8541,19 +8541,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O135" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P135" t="str">
         <v>Today</v>
       </c>
       <c r="Q135" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R135" t="str">
         <v>No</v>
       </c>
       <c r="S135">
-        <v>90</v>
+        <v>34</v>
       </c>
     </row>
     <row r="136">
@@ -8600,19 +8600,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O136" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P136" t="str">
         <v>Today</v>
       </c>
       <c r="Q136" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R136" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S136">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="137">
@@ -8659,7 +8659,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O137" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P137" t="str">
         <v>Today</v>
@@ -8671,7 +8671,7 @@
         <v>No</v>
       </c>
       <c r="S137">
-        <v>52</v>
+        <v>91</v>
       </c>
     </row>
     <row r="138">
@@ -8718,7 +8718,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O138" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P138" t="str">
         <v>Today</v>
@@ -8727,10 +8727,10 @@
         <v>No</v>
       </c>
       <c r="R138" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S138">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="139">
@@ -8777,7 +8777,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O139" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P139" t="str">
         <v>Today</v>
@@ -8789,7 +8789,7 @@
         <v>No</v>
       </c>
       <c r="S139">
-        <v>75</v>
+        <v>62</v>
       </c>
     </row>
     <row r="140">
@@ -8836,7 +8836,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O140" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P140" t="str">
         <v>Today</v>
@@ -8845,10 +8845,10 @@
         <v>No</v>
       </c>
       <c r="R140" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S140">
-        <v>67</v>
+        <v>77</v>
       </c>
     </row>
     <row r="141">
@@ -8895,19 +8895,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O141" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P141" t="str">
         <v>Today</v>
       </c>
       <c r="Q141" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R141" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S141">
-        <v>26</v>
+        <v>89</v>
       </c>
     </row>
     <row r="142">
@@ -8954,7 +8954,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O142" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P142" t="str">
         <v>Today</v>
@@ -8966,7 +8966,7 @@
         <v>Yes</v>
       </c>
       <c r="S142">
-        <v>48</v>
+        <v>32</v>
       </c>
     </row>
     <row r="143">
@@ -9013,19 +9013,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O143" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P143" t="str">
         <v>Today</v>
       </c>
       <c r="Q143" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R143" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S143">
-        <v>26</v>
+        <v>91</v>
       </c>
     </row>
     <row r="144">
@@ -9072,7 +9072,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O144" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P144" t="str">
         <v>Today</v>
@@ -9084,7 +9084,7 @@
         <v>No</v>
       </c>
       <c r="S144">
-        <v>62</v>
+        <v>37</v>
       </c>
     </row>
     <row r="145">
@@ -9131,7 +9131,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O145" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P145" t="str">
         <v>Today</v>
@@ -9140,10 +9140,10 @@
         <v>No</v>
       </c>
       <c r="R145" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S145">
-        <v>70</v>
+        <v>25</v>
       </c>
     </row>
     <row r="146">
@@ -9190,7 +9190,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O146" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P146" t="str">
         <v>Today</v>
@@ -9202,7 +9202,7 @@
         <v>No</v>
       </c>
       <c r="S146">
-        <v>94</v>
+        <v>41</v>
       </c>
     </row>
     <row r="147">
@@ -9249,7 +9249,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O147" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P147" t="str">
         <v>Today</v>
@@ -9261,7 +9261,7 @@
         <v>No</v>
       </c>
       <c r="S147">
-        <v>28</v>
+        <v>93</v>
       </c>
     </row>
     <row r="148">
@@ -9308,19 +9308,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O148" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P148" t="str">
         <v>Today</v>
       </c>
       <c r="Q148" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R148" t="str">
         <v>No</v>
       </c>
       <c r="S148">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="149">
@@ -9367,7 +9367,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O149" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P149" t="str">
         <v>Today</v>
@@ -9379,7 +9379,7 @@
         <v>No</v>
       </c>
       <c r="S149">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="150">
@@ -9426,19 +9426,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O150" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P150" t="str">
         <v>Today</v>
       </c>
       <c r="Q150" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R150" t="str">
         <v>No</v>
       </c>
       <c r="S150">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="151">
@@ -9485,7 +9485,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O151" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P151" t="str">
         <v>Today</v>
@@ -9497,7 +9497,7 @@
         <v>No</v>
       </c>
       <c r="S151">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="152">
@@ -9544,7 +9544,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O152" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P152" t="str">
         <v>Today</v>
@@ -9556,7 +9556,7 @@
         <v>Yes</v>
       </c>
       <c r="S152">
-        <v>49</v>
+        <v>63</v>
       </c>
     </row>
     <row r="153">
@@ -9603,19 +9603,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O153" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P153" t="str">
         <v>Today</v>
       </c>
       <c r="Q153" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R153" t="str">
         <v>No</v>
       </c>
       <c r="S153">
-        <v>54</v>
+        <v>72</v>
       </c>
     </row>
     <row r="154">
@@ -9662,7 +9662,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O154" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P154" t="str">
         <v>Today</v>
@@ -9671,10 +9671,10 @@
         <v>No</v>
       </c>
       <c r="R154" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S154">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="155">
@@ -9721,7 +9721,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O155" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P155" t="str">
         <v>Today</v>
@@ -9733,7 +9733,7 @@
         <v>Yes</v>
       </c>
       <c r="S155">
-        <v>36</v>
+        <v>62</v>
       </c>
     </row>
     <row r="156">
@@ -9780,7 +9780,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O156" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P156" t="str">
         <v>Today</v>
@@ -9789,10 +9789,10 @@
         <v>No</v>
       </c>
       <c r="R156" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S156">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="157">
@@ -9818,7 +9818,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H157" t="str">
-        <v>United States - Remote</v>
+        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
       </c>
       <c r="I157" t="str">
         <v>Remote</v>
@@ -9830,7 +9830,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L157" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8077510</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8077512</v>
       </c>
       <c r="M157">
         <v>200</v>
@@ -9839,19 +9839,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O157" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P157" t="str">
         <v>Today</v>
       </c>
       <c r="Q157" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R157" t="str">
         <v>No</v>
       </c>
       <c r="S157">
-        <v>89</v>
+        <v>47</v>
       </c>
     </row>
     <row r="158">
@@ -9877,7 +9877,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H158" t="str">
-        <v>United States - Remote</v>
+        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
       </c>
       <c r="I158" t="str">
         <v>Remote</v>
@@ -9889,7 +9889,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L158" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8120469</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8120471</v>
       </c>
       <c r="M158">
         <v>200</v>
@@ -9898,7 +9898,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O158" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P158" t="str">
         <v>Today</v>
@@ -9907,10 +9907,10 @@
         <v>No</v>
       </c>
       <c r="R158" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S158">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="159">
@@ -9936,7 +9936,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H159" t="str">
-        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
+        <v>United States - Remote</v>
       </c>
       <c r="I159" t="str">
         <v>Remote</v>
@@ -9948,7 +9948,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L159" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8143272</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8143270</v>
       </c>
       <c r="M159">
         <v>200</v>
@@ -9957,19 +9957,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O159" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P159" t="str">
         <v>Today</v>
       </c>
       <c r="Q159" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R159" t="str">
         <v>No</v>
       </c>
       <c r="S159">
-        <v>58</v>
+        <v>40</v>
       </c>
     </row>
     <row r="160">
@@ -10016,7 +10016,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O160" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P160" t="str">
         <v>Today</v>
@@ -10028,7 +10028,7 @@
         <v>No</v>
       </c>
       <c r="S160">
-        <v>46</v>
+        <v>92</v>
       </c>
     </row>
     <row r="161">
@@ -10054,7 +10054,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H161" t="str">
-        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
+        <v>United States - Remote</v>
       </c>
       <c r="I161" t="str">
         <v>Remote</v>
@@ -10066,7 +10066,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L161" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/7963726</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/7963724</v>
       </c>
       <c r="M161">
         <v>200</v>
@@ -10075,7 +10075,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O161" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P161" t="str">
         <v>Today</v>
@@ -10087,7 +10087,7 @@
         <v>No</v>
       </c>
       <c r="S161">
-        <v>83</v>
+        <v>54</v>
       </c>
     </row>
     <row r="162">
@@ -10134,7 +10134,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O162" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P162" t="str">
         <v>Today</v>
@@ -10143,10 +10143,10 @@
         <v>No</v>
       </c>
       <c r="R162" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S162">
-        <v>91</v>
+        <v>73</v>
       </c>
     </row>
     <row r="163">
@@ -10193,19 +10193,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O163" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P163" t="str">
         <v>Today</v>
       </c>
       <c r="Q163" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R163" t="str">
         <v>No</v>
       </c>
       <c r="S163">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="164">
@@ -10252,7 +10252,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O164" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P164" t="str">
         <v>Today</v>
@@ -10264,7 +10264,7 @@
         <v>No</v>
       </c>
       <c r="S164">
-        <v>58</v>
+        <v>29</v>
       </c>
     </row>
     <row r="165">
@@ -10311,7 +10311,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O165" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P165" t="str">
         <v>Today</v>
@@ -10320,10 +10320,10 @@
         <v>Yes</v>
       </c>
       <c r="R165" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S165">
-        <v>86</v>
+        <v>71</v>
       </c>
     </row>
     <row r="166">
@@ -10370,7 +10370,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O166" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P166" t="str">
         <v>Today</v>
@@ -10382,7 +10382,7 @@
         <v>Yes</v>
       </c>
       <c r="S166">
-        <v>61</v>
+        <v>119</v>
       </c>
     </row>
     <row r="167">
@@ -10429,7 +10429,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O167" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P167" t="str">
         <v>Today</v>
@@ -10441,7 +10441,7 @@
         <v>Yes</v>
       </c>
       <c r="S167">
-        <v>49</v>
+        <v>75</v>
       </c>
     </row>
     <row r="168">
@@ -10488,7 +10488,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O168" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P168" t="str">
         <v>Today</v>
@@ -10497,10 +10497,10 @@
         <v>Yes</v>
       </c>
       <c r="R168" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S168">
-        <v>85</v>
+        <v>105</v>
       </c>
     </row>
     <row r="169">
@@ -10547,7 +10547,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O169" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P169" t="str">
         <v>Today</v>
@@ -10556,10 +10556,10 @@
         <v>Yes</v>
       </c>
       <c r="R169" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S169">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="170">
@@ -10606,7 +10606,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O170" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P170" t="str">
         <v>Today</v>
@@ -10618,7 +10618,7 @@
         <v>Yes</v>
       </c>
       <c r="S170">
-        <v>43</v>
+        <v>106</v>
       </c>
     </row>
     <row r="171">
@@ -10665,7 +10665,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O171" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P171" t="str">
         <v>Today</v>
@@ -10677,7 +10677,7 @@
         <v>Yes</v>
       </c>
       <c r="S171">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="172">
@@ -10724,7 +10724,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O172" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P172" t="str">
         <v>Today</v>
@@ -10733,10 +10733,10 @@
         <v>Yes</v>
       </c>
       <c r="R172" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S172">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="173">
@@ -10783,7 +10783,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O173" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P173" t="str">
         <v>Today</v>
@@ -10792,10 +10792,10 @@
         <v>Yes</v>
       </c>
       <c r="R173" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S173">
-        <v>72</v>
+        <v>105</v>
       </c>
     </row>
     <row r="174">
@@ -10842,7 +10842,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O174" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P174" t="str">
         <v>Today</v>
@@ -10851,10 +10851,10 @@
         <v>Yes</v>
       </c>
       <c r="R174" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S174">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="175">
@@ -10901,7 +10901,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O175" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P175" t="str">
         <v>Today</v>
@@ -10913,7 +10913,7 @@
         <v>No</v>
       </c>
       <c r="S175">
-        <v>114</v>
+        <v>61</v>
       </c>
     </row>
     <row r="176">
@@ -10960,7 +10960,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O176" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P176" t="str">
         <v>Today</v>
@@ -10969,10 +10969,10 @@
         <v>Yes</v>
       </c>
       <c r="R176" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S176">
-        <v>40</v>
+        <v>71</v>
       </c>
     </row>
     <row r="177">
@@ -11019,7 +11019,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O177" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P177" t="str">
         <v>Today</v>
@@ -11028,10 +11028,10 @@
         <v>Yes</v>
       </c>
       <c r="R177" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S177">
-        <v>80</v>
+        <v>55</v>
       </c>
     </row>
     <row r="178">
@@ -11078,7 +11078,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O178" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P178" t="str">
         <v>Today</v>
@@ -11090,7 +11090,7 @@
         <v>Yes</v>
       </c>
       <c r="S178">
-        <v>97</v>
+        <v>46</v>
       </c>
     </row>
     <row r="179">
@@ -11137,7 +11137,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O179" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P179" t="str">
         <v>Today</v>
@@ -11146,10 +11146,10 @@
         <v>Yes</v>
       </c>
       <c r="R179" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S179">
-        <v>76</v>
+        <v>104</v>
       </c>
     </row>
     <row r="180">
@@ -11196,7 +11196,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O180" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P180" t="str">
         <v>Today</v>
@@ -11205,10 +11205,10 @@
         <v>Yes</v>
       </c>
       <c r="R180" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S180">
-        <v>114</v>
+        <v>86</v>
       </c>
     </row>
     <row r="181">
@@ -11255,7 +11255,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O181" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P181" t="str">
         <v>Today</v>
@@ -11267,7 +11267,7 @@
         <v>Yes</v>
       </c>
       <c r="S181">
-        <v>101</v>
+        <v>110</v>
       </c>
     </row>
     <row r="182">
@@ -11314,7 +11314,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O182" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P182" t="str">
         <v>Today</v>
@@ -11326,7 +11326,7 @@
         <v>Yes</v>
       </c>
       <c r="S182">
-        <v>119</v>
+        <v>44</v>
       </c>
     </row>
     <row r="183">
@@ -11373,7 +11373,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O183" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P183" t="str">
         <v>Today</v>
@@ -11385,7 +11385,7 @@
         <v>Yes</v>
       </c>
       <c r="S183">
-        <v>48</v>
+        <v>75</v>
       </c>
     </row>
     <row r="184">
@@ -11432,7 +11432,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O184" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P184" t="str">
         <v>Today</v>
@@ -11441,10 +11441,10 @@
         <v>Yes</v>
       </c>
       <c r="R184" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S184">
-        <v>81</v>
+        <v>67</v>
       </c>
     </row>
     <row r="185">
@@ -11491,7 +11491,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O185" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P185" t="str">
         <v>Today</v>
@@ -11500,10 +11500,10 @@
         <v>Yes</v>
       </c>
       <c r="R185" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S185">
-        <v>99</v>
+        <v>55</v>
       </c>
     </row>
     <row r="186">
@@ -11550,7 +11550,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O186" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P186" t="str">
         <v>Today</v>
@@ -11562,7 +11562,7 @@
         <v>No</v>
       </c>
       <c r="S186">
-        <v>80</v>
+        <v>62</v>
       </c>
     </row>
     <row r="187">
@@ -11609,7 +11609,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O187" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P187" t="str">
         <v>Today</v>
@@ -11621,7 +11621,7 @@
         <v>Yes</v>
       </c>
       <c r="S187">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="188">
@@ -11668,7 +11668,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O188" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P188" t="str">
         <v>Today</v>
@@ -11680,7 +11680,7 @@
         <v>Yes</v>
       </c>
       <c r="S188">
-        <v>92</v>
+        <v>112</v>
       </c>
     </row>
     <row r="189">
@@ -11727,7 +11727,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O189" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P189" t="str">
         <v>Today</v>
@@ -11739,7 +11739,7 @@
         <v>Yes</v>
       </c>
       <c r="S189">
-        <v>69</v>
+        <v>115</v>
       </c>
     </row>
     <row r="190">
@@ -11786,7 +11786,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O190" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P190" t="str">
         <v>Today</v>
@@ -11798,7 +11798,7 @@
         <v>No</v>
       </c>
       <c r="S190">
-        <v>67</v>
+        <v>97</v>
       </c>
     </row>
     <row r="191">
@@ -11845,7 +11845,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O191" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P191" t="str">
         <v>Today</v>
@@ -11854,10 +11854,10 @@
         <v>Yes</v>
       </c>
       <c r="R191" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S191">
-        <v>99</v>
+        <v>108</v>
       </c>
     </row>
     <row r="192">
@@ -11904,7 +11904,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O192" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P192" t="str">
         <v>Today</v>
@@ -11916,7 +11916,7 @@
         <v>No</v>
       </c>
       <c r="S192">
-        <v>83</v>
+        <v>42</v>
       </c>
     </row>
     <row r="193">
@@ -11963,7 +11963,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O193" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P193" t="str">
         <v>Today</v>
@@ -11975,7 +11975,7 @@
         <v>No</v>
       </c>
       <c r="S193">
-        <v>69</v>
+        <v>49</v>
       </c>
     </row>
     <row r="194">
@@ -12022,7 +12022,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O194" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P194" t="str">
         <v>Today</v>
@@ -12034,7 +12034,7 @@
         <v>No</v>
       </c>
       <c r="S194">
-        <v>49</v>
+        <v>89</v>
       </c>
     </row>
     <row r="195">
@@ -12081,7 +12081,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O195" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P195" t="str">
         <v>Today</v>
@@ -12093,7 +12093,7 @@
         <v>No</v>
       </c>
       <c r="S195">
-        <v>71</v>
+        <v>52</v>
       </c>
     </row>
     <row r="196">
@@ -12140,7 +12140,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O196" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P196" t="str">
         <v>Today</v>
@@ -12152,7 +12152,7 @@
         <v>No</v>
       </c>
       <c r="S196">
-        <v>68</v>
+        <v>46</v>
       </c>
     </row>
     <row r="197">
@@ -12199,7 +12199,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O197" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P197" t="str">
         <v>Today</v>
@@ -12211,7 +12211,7 @@
         <v>No</v>
       </c>
       <c r="S197">
-        <v>80</v>
+        <v>48</v>
       </c>
     </row>
     <row r="198">
@@ -12258,7 +12258,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O198" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P198" t="str">
         <v>Today</v>
@@ -12317,7 +12317,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O199" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P199" t="str">
         <v>Today</v>
@@ -12376,7 +12376,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O200" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P200" t="str">
         <v>Today</v>
@@ -12435,7 +12435,7 @@
         <v>BROKEN / 404</v>
       </c>
       <c r="O201" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P201" t="str">
         <v>Today</v>
@@ -12494,7 +12494,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O202" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P202" t="str">
         <v>Today</v>
@@ -12553,7 +12553,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O203" t="str">
-        <v>2026-09-12</v>
+        <v>2026-09-13</v>
       </c>
       <c r="P203" t="str">
         <v>1d ago</v>
@@ -12612,7 +12612,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O204" t="str">
-        <v>2026-09-12</v>
+        <v>2026-09-13</v>
       </c>
       <c r="P204" t="str">
         <v>1d ago</v>
@@ -12671,7 +12671,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O205" t="str">
-        <v>2026-09-12</v>
+        <v>2026-09-13</v>
       </c>
       <c r="P205" t="str">
         <v>1d ago</v>

--- a/GreenPath_PM_Jobs_Test_Report.xlsx
+++ b/GreenPath_PM_Jobs_Test_Report.xlsx
@@ -428,7 +428,7 @@
         <v>Test Execution Date</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-09-14T01:50:53.604Z</v>
+        <v>2026-09-15T02:00:19.880Z</v>
       </c>
     </row>
     <row r="4">
@@ -436,7 +436,7 @@
         <v>Total Jobs in Feed</v>
       </c>
       <c r="B4">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5">
@@ -444,7 +444,7 @@
         <v>Total URLs Tested</v>
       </c>
       <c r="B5">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6">
@@ -452,7 +452,7 @@
         <v>Active / Valid Direct ATS URLs</v>
       </c>
       <c r="B6">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7">
@@ -516,7 +516,7 @@
         <v>Role Tracks Supported</v>
       </c>
       <c r="B14" t="str">
-        <v>Technical Product Manager, Product Manager, Senior Product Manager, Product Lead / Director, Associate Product Manager, AI &amp; Growth PM</v>
+        <v>Technical Product Manager, Product Manager, AI &amp; Growth PM, Senior Product Manager, Product Lead / Director, Associate Product Manager</v>
       </c>
     </row>
     <row r="15">
@@ -524,7 +524,7 @@
         <v>Cities Supported</v>
       </c>
       <c r="B15" t="str">
-        <v>New York, San Francisco, Toronto, Dublin, Remote, USA, London, Seattle, N/A, United States, Bengaluru, Paris, Menlo Park, Hybrid, In-Office, Canada, Spain, Israel, Norway, Poland, Riyadh, Beijing, Pittsburgh, Tel Aviv, Vienna, North America, Washington, Mumbai, Gurgaon</v>
+        <v>New York, San Francisco, Toronto, Dublin, Remote, USA, London, Seattle, N/A, United States, Bengaluru, Paris, Menlo Park, Hybrid, In-Office, Spain, Canada, Greece, Ireland, Doha, Vancouver, Beijing, Pittsburgh, Tel Aviv, Vienna, North America, Washington, Mumbai, Gurgaon</v>
       </c>
     </row>
     <row r="16">
@@ -532,7 +532,7 @@
         <v>Remote / Hybrid Roles</v>
       </c>
       <c r="B16" t="str">
-        <v>63 (31%)</v>
+        <v>62 (30%)</v>
       </c>
     </row>
     <row r="17">
@@ -540,7 +540,7 @@
         <v>Jobs Added Today</v>
       </c>
       <c r="B17" t="str">
-        <v>+201</v>
+        <v>+202</v>
       </c>
     </row>
     <row r="18">
@@ -568,7 +568,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S205"/>
+  <dimension ref="A1:S206"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="38.83203125" customWidth="1"/>
@@ -694,7 +694,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O2" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P2" t="str">
         <v>Today</v>
@@ -703,18 +703,18 @@
         <v>No</v>
       </c>
       <c r="R2" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S2">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>job-0d54a70f</v>
+        <v>job-5e9ab993</v>
       </c>
       <c r="B3" t="str">
-        <v>Product Manager, Connect</v>
+        <v>Product Manager, Connected Account Onboarding Experiences</v>
       </c>
       <c r="C3" t="str">
         <v>Stripe</v>
@@ -732,7 +732,7 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H3" t="str">
-        <v>Seattle, New-York, San Francisco</v>
+        <v>San Francisco, New-York, Seattle</v>
       </c>
       <c r="I3" t="str">
         <v>San Francisco</v>
@@ -744,7 +744,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L3" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/8195440</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/8186541</v>
       </c>
       <c r="M3">
         <v>200</v>
@@ -753,27 +753,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O3" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P3" t="str">
         <v>Today</v>
       </c>
       <c r="Q3" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R3" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S3">
-        <v>82</v>
+        <v>92</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>job-5e9ab993</v>
+        <v>job-457dcb95</v>
       </c>
       <c r="B4" t="str">
-        <v>Product Manager, Connected Account Onboarding Experiences</v>
+        <v>Product Manager, Connect Growth &amp; Monetization</v>
       </c>
       <c r="C4" t="str">
         <v>Stripe</v>
@@ -782,7 +782,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E4" t="str">
-        <v>Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F4" t="str">
         <v>3-6 yrs</v>
@@ -791,7 +791,7 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H4" t="str">
-        <v>San Francisco, New-York, Seattle</v>
+        <v>Seattle, New-York, San Francisco</v>
       </c>
       <c r="I4" t="str">
         <v>San Francisco</v>
@@ -803,7 +803,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L4" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/8186541</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/8195440</v>
       </c>
       <c r="M4">
         <v>200</v>
@@ -812,19 +812,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O4" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P4" t="str">
         <v>Today</v>
       </c>
       <c r="Q4" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R4" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S4">
-        <v>47</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
@@ -871,7 +871,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O5" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P5" t="str">
         <v>Today</v>
@@ -883,7 +883,7 @@
         <v>No</v>
       </c>
       <c r="S5">
-        <v>78</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6">
@@ -930,7 +930,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O6" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P6" t="str">
         <v>Today</v>
@@ -942,7 +942,7 @@
         <v>No</v>
       </c>
       <c r="S6">
-        <v>30</v>
+        <v>84</v>
       </c>
     </row>
     <row r="7">
@@ -989,19 +989,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O7" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P7" t="str">
         <v>Today</v>
       </c>
       <c r="Q7" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R7" t="str">
         <v>No</v>
       </c>
       <c r="S7">
-        <v>88</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8">
@@ -1048,7 +1048,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O8" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P8" t="str">
         <v>Today</v>
@@ -1057,10 +1057,10 @@
         <v>Yes</v>
       </c>
       <c r="R8" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S8">
-        <v>29</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9">
@@ -1107,7 +1107,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O9" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P9" t="str">
         <v>Today</v>
@@ -1119,7 +1119,7 @@
         <v>No</v>
       </c>
       <c r="S9">
-        <v>53</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10">
@@ -1166,7 +1166,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O10" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P10" t="str">
         <v>Today</v>
@@ -1178,7 +1178,7 @@
         <v>No</v>
       </c>
       <c r="S10">
-        <v>36</v>
+        <v>66</v>
       </c>
     </row>
     <row r="11">
@@ -1225,19 +1225,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O11" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P11" t="str">
         <v>Today</v>
       </c>
       <c r="Q11" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R11" t="str">
         <v>No</v>
       </c>
       <c r="S11">
-        <v>51</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
@@ -1284,19 +1284,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O12" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P12" t="str">
         <v>Today</v>
       </c>
       <c r="Q12" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R12" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S12">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="13">
@@ -1343,19 +1343,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O13" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P13" t="str">
         <v>Today</v>
       </c>
       <c r="Q13" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R13" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S13">
-        <v>63</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14">
@@ -1402,19 +1402,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O14" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P14" t="str">
         <v>Today</v>
       </c>
       <c r="Q14" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R14" t="str">
         <v>No</v>
       </c>
       <c r="S14">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15">
@@ -1461,19 +1461,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O15" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P15" t="str">
         <v>Today</v>
       </c>
       <c r="Q15" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R15" t="str">
         <v>No</v>
       </c>
       <c r="S15">
-        <v>43</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16">
@@ -1520,19 +1520,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O16" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P16" t="str">
         <v>Today</v>
       </c>
       <c r="Q16" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R16" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S16">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1579,19 +1579,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O17" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P17" t="str">
         <v>Today</v>
       </c>
       <c r="Q17" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R17" t="str">
         <v>Yes</v>
       </c>
       <c r="S17">
-        <v>82</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18">
@@ -1638,19 +1638,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O18" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P18" t="str">
         <v>Today</v>
       </c>
       <c r="Q18" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R18" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S18">
-        <v>28</v>
+        <v>35</v>
       </c>
     </row>
     <row r="19">
@@ -1697,7 +1697,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O19" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P19" t="str">
         <v>Today</v>
@@ -1709,7 +1709,7 @@
         <v>No</v>
       </c>
       <c r="S19">
-        <v>61</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20">
@@ -1756,19 +1756,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O20" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P20" t="str">
         <v>Today</v>
       </c>
       <c r="Q20" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R20" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S20">
-        <v>91</v>
+        <v>61</v>
       </c>
     </row>
     <row r="21">
@@ -1815,19 +1815,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O21" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P21" t="str">
         <v>Today</v>
       </c>
       <c r="Q21" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R21" t="str">
         <v>No</v>
       </c>
       <c r="S21">
-        <v>60</v>
+        <v>41</v>
       </c>
     </row>
     <row r="22">
@@ -1874,7 +1874,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O22" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P22" t="str">
         <v>Today</v>
@@ -1886,7 +1886,7 @@
         <v>No</v>
       </c>
       <c r="S22">
-        <v>93</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23">
@@ -1933,19 +1933,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O23" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P23" t="str">
         <v>Today</v>
       </c>
       <c r="Q23" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R23" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S23">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24">
@@ -1992,19 +1992,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O24" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P24" t="str">
         <v>Today</v>
       </c>
       <c r="Q24" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R24" t="str">
         <v>No</v>
       </c>
       <c r="S24">
-        <v>28</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25">
@@ -2030,10 +2030,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H25" t="str">
-        <v>London</v>
+        <v>Dublin</v>
       </c>
       <c r="I25" t="str">
-        <v>London</v>
+        <v>Dublin</v>
       </c>
       <c r="J25" t="str">
         <v>On-site</v>
@@ -2042,7 +2042,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L25" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/8142649</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/7737526</v>
       </c>
       <c r="M25">
         <v>200</v>
@@ -2051,19 +2051,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O25" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P25" t="str">
         <v>Today</v>
       </c>
       <c r="Q25" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R25" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S25">
-        <v>66</v>
+        <v>39</v>
       </c>
     </row>
     <row r="26">
@@ -2110,7 +2110,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O26" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P26" t="str">
         <v>Today</v>
@@ -2122,7 +2122,7 @@
         <v>Yes</v>
       </c>
       <c r="S26">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="27">
@@ -2169,7 +2169,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O27" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P27" t="str">
         <v>Today</v>
@@ -2181,7 +2181,7 @@
         <v>No</v>
       </c>
       <c r="S27">
-        <v>79</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28">
@@ -2228,7 +2228,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O28" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P28" t="str">
         <v>Today</v>
@@ -2237,10 +2237,10 @@
         <v>No</v>
       </c>
       <c r="R28" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S28">
-        <v>26</v>
+        <v>70</v>
       </c>
     </row>
     <row r="29">
@@ -2287,7 +2287,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O29" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P29" t="str">
         <v>Today</v>
@@ -2296,10 +2296,10 @@
         <v>No</v>
       </c>
       <c r="R29" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S29">
-        <v>53</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30">
@@ -2346,19 +2346,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O30" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P30" t="str">
         <v>Today</v>
       </c>
       <c r="Q30" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R30" t="str">
         <v>Yes</v>
       </c>
       <c r="S30">
-        <v>56</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31">
@@ -2405,19 +2405,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O31" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P31" t="str">
         <v>Today</v>
       </c>
       <c r="Q31" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R31" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S31">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="32">
@@ -2464,19 +2464,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O32" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P32" t="str">
         <v>Today</v>
       </c>
       <c r="Q32" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R32" t="str">
         <v>No</v>
       </c>
       <c r="S32">
-        <v>86</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33">
@@ -2523,19 +2523,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O33" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P33" t="str">
         <v>Today</v>
       </c>
       <c r="Q33" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R33" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S33">
-        <v>92</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34">
@@ -2582,7 +2582,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O34" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P34" t="str">
         <v>Today</v>
@@ -2594,7 +2594,7 @@
         <v>Yes</v>
       </c>
       <c r="S34">
-        <v>41</v>
+        <v>82</v>
       </c>
     </row>
     <row r="35">
@@ -2641,7 +2641,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O35" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P35" t="str">
         <v>Today</v>
@@ -2653,7 +2653,7 @@
         <v>No</v>
       </c>
       <c r="S35">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36">
@@ -2700,19 +2700,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O36" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P36" t="str">
         <v>Today</v>
       </c>
       <c r="Q36" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R36" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S36">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="37">
@@ -2759,7 +2759,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O37" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P37" t="str">
         <v>Today</v>
@@ -2771,7 +2771,7 @@
         <v>No</v>
       </c>
       <c r="S37">
-        <v>66</v>
+        <v>80</v>
       </c>
     </row>
     <row r="38">
@@ -2818,19 +2818,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O38" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P38" t="str">
         <v>Today</v>
       </c>
       <c r="Q38" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R38" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S38">
-        <v>92</v>
+        <v>38</v>
       </c>
     </row>
     <row r="39">
@@ -2877,7 +2877,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O39" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P39" t="str">
         <v>Today</v>
@@ -2886,10 +2886,10 @@
         <v>No</v>
       </c>
       <c r="R39" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S39">
-        <v>77</v>
+        <v>53</v>
       </c>
     </row>
     <row r="40">
@@ -2915,10 +2915,10 @@
         <v>0-2 yrs</v>
       </c>
       <c r="H40" t="str">
-        <v>Paris, France</v>
+        <v>New York, New York, USA</v>
       </c>
       <c r="I40" t="str">
-        <v>Paris</v>
+        <v>New York</v>
       </c>
       <c r="J40" t="str">
         <v>On-site</v>
@@ -2927,16 +2927,16 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L40" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/8143729</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/8108241</v>
       </c>
       <c r="M40">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="N40" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O40" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P40" t="str">
         <v>Today</v>
@@ -2945,10 +2945,10 @@
         <v>No</v>
       </c>
       <c r="R40" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S40">
-        <v>49</v>
+        <v>38</v>
       </c>
     </row>
     <row r="41">
@@ -2995,7 +2995,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O41" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P41" t="str">
         <v>Today</v>
@@ -3007,7 +3007,7 @@
         <v>No</v>
       </c>
       <c r="S41">
-        <v>57</v>
+        <v>64</v>
       </c>
     </row>
     <row r="42">
@@ -3033,10 +3033,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H42" t="str">
-        <v>Paris, France</v>
+        <v>Boston, Massachusetts, USA; New York, New York, USA</v>
       </c>
       <c r="I42" t="str">
-        <v>Paris</v>
+        <v>New York</v>
       </c>
       <c r="J42" t="str">
         <v>On-site</v>
@@ -3045,7 +3045,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L42" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/8012549</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/7982288</v>
       </c>
       <c r="M42">
         <v>200</v>
@@ -3054,7 +3054,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O42" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P42" t="str">
         <v>Today</v>
@@ -3063,10 +3063,10 @@
         <v>No</v>
       </c>
       <c r="R42" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S42">
-        <v>31</v>
+        <v>46</v>
       </c>
     </row>
     <row r="43">
@@ -3113,19 +3113,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O43" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P43" t="str">
         <v>Today</v>
       </c>
       <c r="Q43" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R43" t="str">
         <v>No</v>
       </c>
       <c r="S43">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44">
@@ -3172,7 +3172,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O44" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P44" t="str">
         <v>Today</v>
@@ -3181,10 +3181,10 @@
         <v>No</v>
       </c>
       <c r="R44" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S44">
-        <v>83</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45">
@@ -3231,7 +3231,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O45" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P45" t="str">
         <v>Today</v>
@@ -3243,7 +3243,7 @@
         <v>No</v>
       </c>
       <c r="S45">
-        <v>69</v>
+        <v>32</v>
       </c>
     </row>
     <row r="46">
@@ -3290,7 +3290,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O46" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P46" t="str">
         <v>Today</v>
@@ -3299,10 +3299,10 @@
         <v>No</v>
       </c>
       <c r="R46" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S46">
-        <v>86</v>
+        <v>47</v>
       </c>
     </row>
     <row r="47">
@@ -3349,7 +3349,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O47" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P47" t="str">
         <v>Today</v>
@@ -3361,7 +3361,7 @@
         <v>Yes</v>
       </c>
       <c r="S47">
-        <v>56</v>
+        <v>69</v>
       </c>
     </row>
     <row r="48">
@@ -3408,19 +3408,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O48" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P48" t="str">
         <v>Today</v>
       </c>
       <c r="Q48" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R48" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S48">
-        <v>40</v>
+        <v>94</v>
       </c>
     </row>
     <row r="49">
@@ -3467,7 +3467,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O49" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P49" t="str">
         <v>Today</v>
@@ -3479,7 +3479,7 @@
         <v>No</v>
       </c>
       <c r="S49">
-        <v>68</v>
+        <v>88</v>
       </c>
     </row>
     <row r="50">
@@ -3526,19 +3526,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O50" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P50" t="str">
         <v>Today</v>
       </c>
       <c r="Q50" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R50" t="str">
         <v>No</v>
       </c>
       <c r="S50">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="51">
@@ -3585,7 +3585,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O51" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P51" t="str">
         <v>Today</v>
@@ -3597,7 +3597,7 @@
         <v>Yes</v>
       </c>
       <c r="S51">
-        <v>56</v>
+        <v>68</v>
       </c>
     </row>
     <row r="52">
@@ -3644,7 +3644,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O52" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P52" t="str">
         <v>Today</v>
@@ -3656,7 +3656,7 @@
         <v>No</v>
       </c>
       <c r="S52">
-        <v>32</v>
+        <v>43</v>
       </c>
     </row>
     <row r="53">
@@ -3703,19 +3703,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O53" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P53" t="str">
         <v>Today</v>
       </c>
       <c r="Q53" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R53" t="str">
         <v>No</v>
       </c>
       <c r="S53">
-        <v>55</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54">
@@ -3762,7 +3762,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O54" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P54" t="str">
         <v>Today</v>
@@ -3774,7 +3774,7 @@
         <v>No</v>
       </c>
       <c r="S54">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="55">
@@ -3821,19 +3821,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O55" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P55" t="str">
         <v>Today</v>
       </c>
       <c r="Q55" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R55" t="str">
         <v>No</v>
       </c>
       <c r="S55">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="56">
@@ -3880,7 +3880,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O56" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P56" t="str">
         <v>Today</v>
@@ -3892,7 +3892,7 @@
         <v>Yes</v>
       </c>
       <c r="S56">
-        <v>94</v>
+        <v>66</v>
       </c>
     </row>
     <row r="57">
@@ -3939,7 +3939,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O57" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P57" t="str">
         <v>Today</v>
@@ -3948,10 +3948,10 @@
         <v>Yes</v>
       </c>
       <c r="R57" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S57">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="58">
@@ -3998,19 +3998,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O58" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P58" t="str">
         <v>Today</v>
       </c>
       <c r="Q58" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R58" t="str">
         <v>Yes</v>
       </c>
       <c r="S58">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="59">
@@ -4057,7 +4057,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O59" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P59" t="str">
         <v>Today</v>
@@ -4069,7 +4069,7 @@
         <v>No</v>
       </c>
       <c r="S59">
-        <v>92</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60">
@@ -4116,19 +4116,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O60" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P60" t="str">
         <v>Today</v>
       </c>
       <c r="Q60" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R60" t="str">
         <v>No</v>
       </c>
       <c r="S60">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="61">
@@ -4175,7 +4175,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O61" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P61" t="str">
         <v>Today</v>
@@ -4187,7 +4187,7 @@
         <v>No</v>
       </c>
       <c r="S61">
-        <v>26</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62">
@@ -4234,19 +4234,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O62" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P62" t="str">
         <v>Today</v>
       </c>
       <c r="Q62" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R62" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S62">
-        <v>84</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63">
@@ -4293,19 +4293,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O63" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P63" t="str">
         <v>Today</v>
       </c>
       <c r="Q63" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R63" t="str">
         <v>No</v>
       </c>
       <c r="S63">
-        <v>44</v>
+        <v>55</v>
       </c>
     </row>
     <row r="64">
@@ -4352,19 +4352,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O64" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P64" t="str">
         <v>Today</v>
       </c>
       <c r="Q64" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R64" t="str">
         <v>Yes</v>
       </c>
       <c r="S64">
-        <v>32</v>
+        <v>66</v>
       </c>
     </row>
     <row r="65">
@@ -4411,19 +4411,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O65" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P65" t="str">
         <v>Today</v>
       </c>
       <c r="Q65" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R65" t="str">
         <v>No</v>
       </c>
       <c r="S65">
-        <v>93</v>
+        <v>76</v>
       </c>
     </row>
     <row r="66">
@@ -4470,7 +4470,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O66" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P66" t="str">
         <v>Today</v>
@@ -4482,7 +4482,7 @@
         <v>Yes</v>
       </c>
       <c r="S66">
-        <v>61</v>
+        <v>31</v>
       </c>
     </row>
     <row r="67">
@@ -4529,7 +4529,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O67" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P67" t="str">
         <v>Today</v>
@@ -4541,7 +4541,7 @@
         <v>No</v>
       </c>
       <c r="S67">
-        <v>94</v>
+        <v>44</v>
       </c>
     </row>
     <row r="68">
@@ -4588,7 +4588,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O68" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P68" t="str">
         <v>Today</v>
@@ -4600,15 +4600,15 @@
         <v>No</v>
       </c>
       <c r="S68">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>job-28c2c2a4</v>
+        <v>job-00451313</v>
       </c>
       <c r="B69" t="str">
-        <v>Senior Product Manager, Crypto Wallet</v>
+        <v>Associate Product Manager (New Grad)</v>
       </c>
       <c r="C69" t="str">
         <v>Robinhood</v>
@@ -4617,13 +4617,13 @@
         <v>Naukri</v>
       </c>
       <c r="E69" t="str">
-        <v>Senior Product Manager</v>
+        <v>Associate Product Manager</v>
       </c>
       <c r="F69" t="str">
-        <v>5-8 yrs</v>
+        <v>1-3 yrs</v>
       </c>
       <c r="G69" t="str">
-        <v>5-8 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H69" t="str">
         <v>Menlo Park, CA; New York, NY</v>
@@ -4638,7 +4638,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L69" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/8082718</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/8199973</v>
       </c>
       <c r="M69">
         <v>200</v>
@@ -4647,7 +4647,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O69" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P69" t="str">
         <v>Today</v>
@@ -4659,15 +4659,15 @@
         <v>No</v>
       </c>
       <c r="S69">
-        <v>82</v>
+        <v>30</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>job-6a8c3d37</v>
+        <v>job-28c2c2a4</v>
       </c>
       <c r="B70" t="str">
-        <v>Senior Product Manager, Money Movement</v>
+        <v>Senior Product Manager, Crypto Wallet</v>
       </c>
       <c r="C70" t="str">
         <v>Robinhood</v>
@@ -4685,10 +4685,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H70" t="str">
-        <v>Menlo Park, CA</v>
+        <v>Menlo Park, CA; New York, NY</v>
       </c>
       <c r="I70" t="str">
-        <v>Menlo Park</v>
+        <v>New York</v>
       </c>
       <c r="J70" t="str">
         <v>On-site</v>
@@ -4697,7 +4697,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L70" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/7747728</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/8082718</v>
       </c>
       <c r="M70">
         <v>200</v>
@@ -4706,27 +4706,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O70" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P70" t="str">
         <v>Today</v>
       </c>
       <c r="Q70" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R70" t="str">
         <v>Yes</v>
       </c>
       <c r="S70">
-        <v>50</v>
+        <v>85</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>job-6a477110</v>
+        <v>job-6a8c3d37</v>
       </c>
       <c r="B71" t="str">
-        <v>Staff Product Manager, Banking</v>
+        <v>Senior Product Manager, Money Movement</v>
       </c>
       <c r="C71" t="str">
         <v>Robinhood</v>
@@ -4744,10 +4744,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H71" t="str">
-        <v>Menlo Park, CA; New York, NY; Washington, DC</v>
+        <v>Menlo Park, CA</v>
       </c>
       <c r="I71" t="str">
-        <v>New York</v>
+        <v>Menlo Park</v>
       </c>
       <c r="J71" t="str">
         <v>On-site</v>
@@ -4756,7 +4756,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L71" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/8044746</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/7747728</v>
       </c>
       <c r="M71">
         <v>200</v>
@@ -4765,7 +4765,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O71" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P71" t="str">
         <v>Today</v>
@@ -4774,18 +4774,18 @@
         <v>No</v>
       </c>
       <c r="R71" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S71">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>job-1f991f57</v>
+        <v>job-6a477110</v>
       </c>
       <c r="B72" t="str">
-        <v>Staff Product Manager-  Integrations &amp; Advisor Platform</v>
+        <v>Staff Product Manager, Banking</v>
       </c>
       <c r="C72" t="str">
         <v>Robinhood</v>
@@ -4803,7 +4803,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H72" t="str">
-        <v>Clearwater, FL; Menlo Park, CA; New York, NY</v>
+        <v>Menlo Park, CA; New York, NY; Washington, DC</v>
       </c>
       <c r="I72" t="str">
         <v>New York</v>
@@ -4815,7 +4815,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L72" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/8131181</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/8044746</v>
       </c>
       <c r="M72">
         <v>200</v>
@@ -4824,7 +4824,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O72" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P72" t="str">
         <v>Today</v>
@@ -4833,18 +4833,18 @@
         <v>Yes</v>
       </c>
       <c r="R72" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S72">
-        <v>65</v>
+        <v>80</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>job-621b991e</v>
+        <v>job-1f991f57</v>
       </c>
       <c r="B73" t="str">
-        <v>Staff Product Manager, National Impact</v>
+        <v>Staff Product Manager-  Integrations &amp; Advisor Platform</v>
       </c>
       <c r="C73" t="str">
         <v>Robinhood</v>
@@ -4862,7 +4862,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H73" t="str">
-        <v>New York, NY</v>
+        <v>Clearwater, FL; Menlo Park, CA; New York, NY</v>
       </c>
       <c r="I73" t="str">
         <v>New York</v>
@@ -4874,7 +4874,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L73" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/7968044</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/8131181</v>
       </c>
       <c r="M73">
         <v>200</v>
@@ -4883,7 +4883,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O73" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P73" t="str">
         <v>Today</v>
@@ -4895,15 +4895,15 @@
         <v>No</v>
       </c>
       <c r="S73">
-        <v>48</v>
+        <v>32</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>job-11725b83</v>
+        <v>job-621b991e</v>
       </c>
       <c r="B74" t="str">
-        <v>Staff Product Manager, Platform Operations</v>
+        <v>Staff Product Manager, National Impact</v>
       </c>
       <c r="C74" t="str">
         <v>Robinhood</v>
@@ -4921,7 +4921,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H74" t="str">
-        <v>Menlo Park, CA; New York, NY</v>
+        <v>New York, NY</v>
       </c>
       <c r="I74" t="str">
         <v>New York</v>
@@ -4933,7 +4933,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L74" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/8079744</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/7968044</v>
       </c>
       <c r="M74">
         <v>200</v>
@@ -4942,57 +4942,57 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O74" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P74" t="str">
         <v>Today</v>
       </c>
       <c r="Q74" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R74" t="str">
         <v>No</v>
       </c>
       <c r="S74">
-        <v>67</v>
+        <v>30</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>job-223dd55b</v>
+        <v>job-11725b83</v>
       </c>
       <c r="B75" t="str">
-        <v>Director of Product Management, Fintech</v>
+        <v>Staff Product Manager, Platform Operations</v>
       </c>
       <c r="C75" t="str">
-        <v>Cloudflare</v>
+        <v>Robinhood</v>
       </c>
       <c r="D75" t="str">
-        <v>LinkedIn</v>
+        <v>Naukri</v>
       </c>
       <c r="E75" t="str">
-        <v>Product Lead / Director</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F75" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G75" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H75" t="str">
-        <v>Hybrid</v>
+        <v>Menlo Park, CA; New York, NY</v>
       </c>
       <c r="I75" t="str">
-        <v>Hybrid</v>
+        <v>New York</v>
       </c>
       <c r="J75" t="str">
-        <v>Hybrid</v>
+        <v>On-site</v>
       </c>
       <c r="K75" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L75" t="str">
-        <v>https://boards.greenhouse.io/cloudflare/jobs/8152765</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/8079744</v>
       </c>
       <c r="M75">
         <v>200</v>
@@ -5001,7 +5001,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O75" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P75" t="str">
         <v>Today</v>
@@ -5010,18 +5010,18 @@
         <v>No</v>
       </c>
       <c r="R75" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S75">
-        <v>64</v>
+        <v>89</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>job-04eb5da0</v>
+        <v>job-223dd55b</v>
       </c>
       <c r="B76" t="str">
-        <v>Product Manager, Browser Extension</v>
+        <v>Director of Product Management, Fintech</v>
       </c>
       <c r="C76" t="str">
         <v>Cloudflare</v>
@@ -5030,13 +5030,13 @@
         <v>LinkedIn</v>
       </c>
       <c r="E76" t="str">
-        <v>Product Manager</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F76" t="str">
-        <v>3-6 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G76" t="str">
-        <v>2-5 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H76" t="str">
         <v>Hybrid</v>
@@ -5051,7 +5051,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L76" t="str">
-        <v>https://boards.greenhouse.io/cloudflare/jobs/8173899</v>
+        <v>https://boards.greenhouse.io/cloudflare/jobs/8152765</v>
       </c>
       <c r="M76">
         <v>200</v>
@@ -5060,27 +5060,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O76" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P76" t="str">
         <v>Today</v>
       </c>
       <c r="Q76" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R76" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S76">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>job-1cd2d853</v>
+        <v>job-04eb5da0</v>
       </c>
       <c r="B77" t="str">
-        <v>Senior Product Manager, Email Security</v>
+        <v>Product Manager, Browser Extension</v>
       </c>
       <c r="C77" t="str">
         <v>Cloudflare</v>
@@ -5089,13 +5089,13 @@
         <v>LinkedIn</v>
       </c>
       <c r="E77" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F77" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G77" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H77" t="str">
         <v>Hybrid</v>
@@ -5110,7 +5110,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L77" t="str">
-        <v>https://boards.greenhouse.io/cloudflare/jobs/8173954</v>
+        <v>https://boards.greenhouse.io/cloudflare/jobs/8173899</v>
       </c>
       <c r="M77">
         <v>200</v>
@@ -5119,7 +5119,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O77" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P77" t="str">
         <v>Today</v>
@@ -5128,18 +5128,18 @@
         <v>Yes</v>
       </c>
       <c r="R77" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S77">
-        <v>31</v>
+        <v>41</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>job-4c1a26d6</v>
+        <v>job-1cd2d853</v>
       </c>
       <c r="B78" t="str">
-        <v>Senior Product Manager, Enterprise</v>
+        <v>Senior Product Manager, Email Security</v>
       </c>
       <c r="C78" t="str">
         <v>Cloudflare</v>
@@ -5169,7 +5169,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L78" t="str">
-        <v>https://boards.greenhouse.io/cloudflare/jobs/8158527</v>
+        <v>https://boards.greenhouse.io/cloudflare/jobs/8173954</v>
       </c>
       <c r="M78">
         <v>200</v>
@@ -5178,27 +5178,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O78" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P78" t="str">
         <v>Today</v>
       </c>
       <c r="Q78" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R78" t="str">
         <v>No</v>
       </c>
       <c r="S78">
-        <v>35</v>
+        <v>66</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>job-7e2bc27f</v>
+        <v>job-4c1a26d6</v>
       </c>
       <c r="B79" t="str">
-        <v>Senior Product Manager, Enterprise (API &amp; SDK)</v>
+        <v>Senior Product Manager, Enterprise</v>
       </c>
       <c r="C79" t="str">
         <v>Cloudflare</v>
@@ -5228,7 +5228,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L79" t="str">
-        <v>https://boards.greenhouse.io/cloudflare/jobs/7589006</v>
+        <v>https://boards.greenhouse.io/cloudflare/jobs/8158527</v>
       </c>
       <c r="M79">
         <v>200</v>
@@ -5237,7 +5237,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O79" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P79" t="str">
         <v>Today</v>
@@ -5246,18 +5246,18 @@
         <v>No</v>
       </c>
       <c r="R79" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S79">
-        <v>87</v>
+        <v>89</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>job-0496f2bd</v>
+        <v>job-7e2bc27f</v>
       </c>
       <c r="B80" t="str">
-        <v>Senior Product Manager - FinTech</v>
+        <v>Senior Product Manager, Enterprise (API &amp; SDK)</v>
       </c>
       <c r="C80" t="str">
         <v>Cloudflare</v>
@@ -5275,19 +5275,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H80" t="str">
-        <v>In-Office</v>
+        <v>Hybrid</v>
       </c>
       <c r="I80" t="str">
-        <v>In-Office</v>
+        <v>Hybrid</v>
       </c>
       <c r="J80" t="str">
-        <v>On-site</v>
+        <v>Hybrid</v>
       </c>
       <c r="K80" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L80" t="str">
-        <v>https://boards.greenhouse.io/cloudflare/jobs/8064473</v>
+        <v>https://boards.greenhouse.io/cloudflare/jobs/7589006</v>
       </c>
       <c r="M80">
         <v>200</v>
@@ -5296,30 +5296,30 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O80" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P80" t="str">
         <v>Today</v>
       </c>
       <c r="Q80" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R80" t="str">
         <v>No</v>
       </c>
       <c r="S80">
-        <v>91</v>
+        <v>42</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>job-321ad81f</v>
+        <v>job-0496f2bd</v>
       </c>
       <c r="B81" t="str">
-        <v>Principal Product Manager Agents and Context - Elasticsearch</v>
+        <v>Senior Product Manager - FinTech</v>
       </c>
       <c r="C81" t="str">
-        <v>Elastic</v>
+        <v>Cloudflare</v>
       </c>
       <c r="D81" t="str">
         <v>LinkedIn</v>
@@ -5328,16 +5328,16 @@
         <v>Senior Product Manager</v>
       </c>
       <c r="F81" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G81" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H81" t="str">
-        <v>Canada</v>
+        <v>In-Office</v>
       </c>
       <c r="I81" t="str">
-        <v>Canada</v>
+        <v>In-Office</v>
       </c>
       <c r="J81" t="str">
         <v>On-site</v>
@@ -5346,7 +5346,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L81" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8070011</v>
+        <v>https://boards.greenhouse.io/cloudflare/jobs/8064473</v>
       </c>
       <c r="M81">
         <v>200</v>
@@ -5355,7 +5355,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O81" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P81" t="str">
         <v>Today</v>
@@ -5367,15 +5367,15 @@
         <v>No</v>
       </c>
       <c r="S81">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>job-1958e230</v>
+        <v>job-321ad81f</v>
       </c>
       <c r="B82" t="str">
-        <v>Principal Product Manager - Identity Threat Detection &amp; Response</v>
+        <v>Principal Product Manager Agents and Context - Elasticsearch</v>
       </c>
       <c r="C82" t="str">
         <v>Elastic</v>
@@ -5393,10 +5393,10 @@
         <v>8+ yrs</v>
       </c>
       <c r="H82" t="str">
-        <v>Spain</v>
+        <v>United States</v>
       </c>
       <c r="I82" t="str">
-        <v>Spain</v>
+        <v>United States</v>
       </c>
       <c r="J82" t="str">
         <v>On-site</v>
@@ -5405,7 +5405,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L82" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8122171</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/7602101</v>
       </c>
       <c r="M82">
         <v>200</v>
@@ -5414,7 +5414,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O82" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P82" t="str">
         <v>Today</v>
@@ -5423,18 +5423,18 @@
         <v>No</v>
       </c>
       <c r="R82" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S82">
-        <v>48</v>
+        <v>81</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>job-7648ed00</v>
+        <v>job-1958e230</v>
       </c>
       <c r="B83" t="str">
-        <v>Principal Product Manager II, AI/Vectors</v>
+        <v>Principal Product Manager - Identity Threat Detection &amp; Response</v>
       </c>
       <c r="C83" t="str">
         <v>Elastic</v>
@@ -5452,10 +5452,10 @@
         <v>8+ yrs</v>
       </c>
       <c r="H83" t="str">
-        <v>United States</v>
+        <v>Spain</v>
       </c>
       <c r="I83" t="str">
-        <v>United States</v>
+        <v>Spain</v>
       </c>
       <c r="J83" t="str">
         <v>On-site</v>
@@ -5464,7 +5464,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L83" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8121962</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8122171</v>
       </c>
       <c r="M83">
         <v>200</v>
@@ -5473,27 +5473,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O83" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P83" t="str">
         <v>Today</v>
       </c>
       <c r="Q83" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R83" t="str">
         <v>No</v>
       </c>
       <c r="S83">
-        <v>73</v>
+        <v>60</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>job-4dbe0e39</v>
+        <v>job-7648ed00</v>
       </c>
       <c r="B84" t="str">
-        <v>Principal Product Manager (Strategic Account Interactions) - Security Solutions</v>
+        <v>Principal Product Manager II, AI/Vectors</v>
       </c>
       <c r="C84" t="str">
         <v>Elastic</v>
@@ -5511,10 +5511,10 @@
         <v>8+ yrs</v>
       </c>
       <c r="H84" t="str">
-        <v>Israel</v>
+        <v>United States</v>
       </c>
       <c r="I84" t="str">
-        <v>Israel</v>
+        <v>United States</v>
       </c>
       <c r="J84" t="str">
         <v>On-site</v>
@@ -5523,7 +5523,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L84" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8155426</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8121962</v>
       </c>
       <c r="M84">
         <v>200</v>
@@ -5532,7 +5532,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O84" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P84" t="str">
         <v>Today</v>
@@ -5541,18 +5541,18 @@
         <v>No</v>
       </c>
       <c r="R84" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S84">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>job-682d81b9</v>
+        <v>job-4dbe0e39</v>
       </c>
       <c r="B85" t="str">
-        <v>Principal Product Manager (XDR &amp; Exposure Management) - Security Solutions</v>
+        <v>Principal Product Manager (Strategic Account Interactions) - Security Solutions</v>
       </c>
       <c r="C85" t="str">
         <v>Elastic</v>
@@ -5582,7 +5582,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L85" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8155216</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8155415</v>
       </c>
       <c r="M85">
         <v>200</v>
@@ -5591,7 +5591,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O85" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P85" t="str">
         <v>Today</v>
@@ -5600,18 +5600,18 @@
         <v>No</v>
       </c>
       <c r="R85" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S85">
-        <v>38</v>
+        <v>73</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>job-2b6f27da</v>
+        <v>job-682d81b9</v>
       </c>
       <c r="B86" t="str">
-        <v>Senior Product Manager, Control Plane - Platform</v>
+        <v>Principal Product Manager (XDR &amp; Exposure Management) - Security Solutions</v>
       </c>
       <c r="C86" t="str">
         <v>Elastic</v>
@@ -5623,16 +5623,16 @@
         <v>Senior Product Manager</v>
       </c>
       <c r="F86" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G86" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H86" t="str">
-        <v>Canada</v>
+        <v>Greece</v>
       </c>
       <c r="I86" t="str">
-        <v>Canada</v>
+        <v>Greece</v>
       </c>
       <c r="J86" t="str">
         <v>On-site</v>
@@ -5641,7 +5641,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L86" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8093933</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8155348</v>
       </c>
       <c r="M86">
         <v>200</v>
@@ -5650,7 +5650,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O86" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P86" t="str">
         <v>Today</v>
@@ -5659,18 +5659,18 @@
         <v>No</v>
       </c>
       <c r="R86" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S86">
-        <v>75</v>
+        <v>63</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>job-03cee7aa</v>
+        <v>job-2b6f27da</v>
       </c>
       <c r="B87" t="str">
-        <v>Senior Product Manager, Logs - Observability</v>
+        <v>Senior Product Manager, Control Plane - Platform</v>
       </c>
       <c r="C87" t="str">
         <v>Elastic</v>
@@ -5688,10 +5688,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H87" t="str">
-        <v>Canada</v>
+        <v>United States</v>
       </c>
       <c r="I87" t="str">
-        <v>Canada</v>
+        <v>United States</v>
       </c>
       <c r="J87" t="str">
         <v>On-site</v>
@@ -5700,7 +5700,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L87" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8066646</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8088818</v>
       </c>
       <c r="M87">
         <v>200</v>
@@ -5709,27 +5709,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O87" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P87" t="str">
         <v>Today</v>
       </c>
       <c r="Q87" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R87" t="str">
         <v>No</v>
       </c>
       <c r="S87">
-        <v>74</v>
+        <v>34</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>job-264c8d5a</v>
+        <v>job-03cee7aa</v>
       </c>
       <c r="B88" t="str">
-        <v>Senior Product Manager - Self service cloud</v>
+        <v>Senior Product Manager, Logs - Observability</v>
       </c>
       <c r="C88" t="str">
         <v>Elastic</v>
@@ -5747,10 +5747,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H88" t="str">
-        <v>Norway</v>
+        <v>Greece</v>
       </c>
       <c r="I88" t="str">
-        <v>Norway</v>
+        <v>Greece</v>
       </c>
       <c r="J88" t="str">
         <v>On-site</v>
@@ -5759,7 +5759,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L88" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8041211</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8066510</v>
       </c>
       <c r="M88">
         <v>200</v>
@@ -5768,7 +5768,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O88" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P88" t="str">
         <v>Today</v>
@@ -5780,15 +5780,15 @@
         <v>No</v>
       </c>
       <c r="S88">
-        <v>35</v>
+        <v>74</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>job-7ab91933</v>
+        <v>job-264c8d5a</v>
       </c>
       <c r="B89" t="str">
-        <v>Senior Product Manager (XDR) - Security Solutions</v>
+        <v>Senior Product Manager - Self service cloud</v>
       </c>
       <c r="C89" t="str">
         <v>Elastic</v>
@@ -5806,10 +5806,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H89" t="str">
-        <v>Poland</v>
+        <v>Ireland</v>
       </c>
       <c r="I89" t="str">
-        <v>Poland</v>
+        <v>Ireland</v>
       </c>
       <c r="J89" t="str">
         <v>On-site</v>
@@ -5818,7 +5818,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L89" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8194139</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8041203</v>
       </c>
       <c r="M89">
         <v>200</v>
@@ -5827,7 +5827,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O89" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P89" t="str">
         <v>Today</v>
@@ -5839,36 +5839,36 @@
         <v>No</v>
       </c>
       <c r="S89">
-        <v>47</v>
+        <v>58</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>job-31af15ee</v>
+        <v>job-5b8ec8c1</v>
       </c>
       <c r="B90" t="str">
-        <v>AI Product Manager (Coding/Multimodal)</v>
+        <v>Senior Product Manager - US Public Sector</v>
       </c>
       <c r="C90" t="str">
-        <v>Scale AI</v>
+        <v>Elastic</v>
       </c>
       <c r="D90" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E90" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F90" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G90" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H90" t="str">
-        <v>San Francisco, CA</v>
+        <v>United States</v>
       </c>
       <c r="I90" t="str">
-        <v>San Francisco</v>
+        <v>United States</v>
       </c>
       <c r="J90" t="str">
         <v>On-site</v>
@@ -5877,7 +5877,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L90" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4609736005</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8188365</v>
       </c>
       <c r="M90">
         <v>200</v>
@@ -5886,7 +5886,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O90" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P90" t="str">
         <v>Today</v>
@@ -5895,39 +5895,39 @@
         <v>No</v>
       </c>
       <c r="R90" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S90">
-        <v>92</v>
+        <v>68</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>job-184e55c8</v>
+        <v>job-7ab91933</v>
       </c>
       <c r="B91" t="str">
-        <v>Director of Product Management, Enterprise Core Platform</v>
+        <v>Senior Product Manager (XDR) - Security Solutions</v>
       </c>
       <c r="C91" t="str">
-        <v>Scale AI</v>
+        <v>Elastic</v>
       </c>
       <c r="D91" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E91" t="str">
-        <v>Technical Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F91" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G91" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H91" t="str">
-        <v>San Francisco, CA; New York, NY</v>
+        <v>United States</v>
       </c>
       <c r="I91" t="str">
-        <v>San Francisco</v>
+        <v>United States</v>
       </c>
       <c r="J91" t="str">
         <v>On-site</v>
@@ -5936,7 +5936,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L91" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4714727005</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8167771</v>
       </c>
       <c r="M91">
         <v>200</v>
@@ -5945,27 +5945,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O91" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P91" t="str">
         <v>Today</v>
       </c>
       <c r="Q91" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R91" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S91">
-        <v>85</v>
+        <v>27</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>job-6a202479</v>
+        <v>job-31af15ee</v>
       </c>
       <c r="B92" t="str">
-        <v>Director of Product Management, Forward Deployed &amp; Strategy</v>
+        <v>AI Product Manager (Coding/Multimodal)</v>
       </c>
       <c r="C92" t="str">
         <v>Scale AI</v>
@@ -5974,19 +5974,19 @@
         <v>Wellfound</v>
       </c>
       <c r="E92" t="str">
-        <v>Product Lead / Director</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F92" t="str">
-        <v>8+ yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G92" t="str">
-        <v>8+ yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H92" t="str">
-        <v>London, UK</v>
+        <v>San Francisco, CA</v>
       </c>
       <c r="I92" t="str">
-        <v>London</v>
+        <v>San Francisco</v>
       </c>
       <c r="J92" t="str">
         <v>On-site</v>
@@ -5995,7 +5995,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L92" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4702890005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4609736005</v>
       </c>
       <c r="M92">
         <v>200</v>
@@ -6004,7 +6004,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O92" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P92" t="str">
         <v>Today</v>
@@ -6016,15 +6016,15 @@
         <v>No</v>
       </c>
       <c r="S92">
-        <v>40</v>
+        <v>93</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>job-6681e5c8</v>
+        <v>job-184e55c8</v>
       </c>
       <c r="B93" t="str">
-        <v>Forward Deployed Product Manager, Enterprise</v>
+        <v>Director of Product Management, Enterprise Core Platform</v>
       </c>
       <c r="C93" t="str">
         <v>Scale AI</v>
@@ -6033,19 +6033,19 @@
         <v>Wellfound</v>
       </c>
       <c r="E93" t="str">
-        <v>Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F93" t="str">
-        <v>3-6 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G93" t="str">
-        <v>2-5 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H93" t="str">
-        <v>London, UK</v>
+        <v>San Francisco, CA; New York, NY</v>
       </c>
       <c r="I93" t="str">
-        <v>London</v>
+        <v>San Francisco</v>
       </c>
       <c r="J93" t="str">
         <v>On-site</v>
@@ -6054,7 +6054,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L93" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4644742005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4714727005</v>
       </c>
       <c r="M93">
         <v>200</v>
@@ -6063,27 +6063,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O93" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P93" t="str">
         <v>Today</v>
       </c>
       <c r="Q93" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R93" t="str">
         <v>No</v>
       </c>
       <c r="S93">
-        <v>65</v>
+        <v>72</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>job-11245f1c</v>
+        <v>job-6a202479</v>
       </c>
       <c r="B94" t="str">
-        <v>Forward Deployed Product Manager, Public Sector</v>
+        <v>Director of Product Management, Forward Deployed &amp; Strategy</v>
       </c>
       <c r="C94" t="str">
         <v>Scale AI</v>
@@ -6092,19 +6092,19 @@
         <v>Wellfound</v>
       </c>
       <c r="E94" t="str">
-        <v>Product Manager</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F94" t="str">
-        <v>3-6 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G94" t="str">
-        <v>2-5 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H94" t="str">
-        <v>New York, NY; Washington, DC</v>
+        <v>London, UK</v>
       </c>
       <c r="I94" t="str">
-        <v>New York</v>
+        <v>London</v>
       </c>
       <c r="J94" t="str">
         <v>On-site</v>
@@ -6113,7 +6113,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L94" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4713648005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4702890005</v>
       </c>
       <c r="M94">
         <v>200</v>
@@ -6122,27 +6122,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O94" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P94" t="str">
         <v>Today</v>
       </c>
       <c r="Q94" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R94" t="str">
         <v>No</v>
       </c>
       <c r="S94">
-        <v>70</v>
+        <v>44</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>job-235e84a3</v>
+        <v>job-6681e5c8</v>
       </c>
       <c r="B95" t="str">
-        <v>Product Manager, Enterprise Core Platform</v>
+        <v>Forward Deployed Product Manager, Enterprise</v>
       </c>
       <c r="C95" t="str">
         <v>Scale AI</v>
@@ -6151,7 +6151,7 @@
         <v>Wellfound</v>
       </c>
       <c r="E95" t="str">
-        <v>Technical Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F95" t="str">
         <v>3-6 yrs</v>
@@ -6160,10 +6160,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H95" t="str">
-        <v>New York, NY; San Francisco, CA</v>
+        <v>London, UK</v>
       </c>
       <c r="I95" t="str">
-        <v>San Francisco</v>
+        <v>London</v>
       </c>
       <c r="J95" t="str">
         <v>On-site</v>
@@ -6172,7 +6172,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L95" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4699779005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4644742005</v>
       </c>
       <c r="M95">
         <v>200</v>
@@ -6181,7 +6181,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O95" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P95" t="str">
         <v>Today</v>
@@ -6193,15 +6193,15 @@
         <v>No</v>
       </c>
       <c r="S95">
-        <v>89</v>
+        <v>26</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>job-7d366400</v>
+        <v>job-11245f1c</v>
       </c>
       <c r="B96" t="str">
-        <v>Product Manager of AI Applications, Global Public Sector</v>
+        <v>Forward Deployed Product Manager, Public Sector</v>
       </c>
       <c r="C96" t="str">
         <v>Scale AI</v>
@@ -6210,7 +6210,7 @@
         <v>Wellfound</v>
       </c>
       <c r="E96" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Product Manager</v>
       </c>
       <c r="F96" t="str">
         <v>3-6 yrs</v>
@@ -6219,10 +6219,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H96" t="str">
-        <v>Riyadh, Saudi Arabia</v>
+        <v>New York, NY; Washington, DC</v>
       </c>
       <c r="I96" t="str">
-        <v>Riyadh</v>
+        <v>New York</v>
       </c>
       <c r="J96" t="str">
         <v>On-site</v>
@@ -6231,7 +6231,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L96" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4650514005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4713648005</v>
       </c>
       <c r="M96">
         <v>200</v>
@@ -6240,7 +6240,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O96" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P96" t="str">
         <v>Today</v>
@@ -6252,15 +6252,15 @@
         <v>Yes</v>
       </c>
       <c r="S96">
-        <v>75</v>
+        <v>83</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>job-6c1eab2d</v>
+        <v>job-235e84a3</v>
       </c>
       <c r="B97" t="str">
-        <v>Senior AI Product Manager, Code</v>
+        <v>Product Manager, Enterprise Core Platform</v>
       </c>
       <c r="C97" t="str">
         <v>Scale AI</v>
@@ -6269,13 +6269,13 @@
         <v>Wellfound</v>
       </c>
       <c r="E97" t="str">
-        <v>Senior Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F97" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G97" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H97" t="str">
         <v>New York, NY; San Francisco, CA</v>
@@ -6290,7 +6290,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L97" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4720501005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4699779005</v>
       </c>
       <c r="M97">
         <v>200</v>
@@ -6299,27 +6299,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O97" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P97" t="str">
         <v>Today</v>
       </c>
       <c r="Q97" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R97" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S97">
-        <v>29</v>
+        <v>50</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>job-1310fa39</v>
+        <v>job-7d366400</v>
       </c>
       <c r="B98" t="str">
-        <v>Senior AI Product Manager, Cybersecurity</v>
+        <v>Product Manager of AI Applications, Global Public Sector</v>
       </c>
       <c r="C98" t="str">
         <v>Scale AI</v>
@@ -6328,19 +6328,19 @@
         <v>Wellfound</v>
       </c>
       <c r="E98" t="str">
-        <v>Senior Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F98" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G98" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H98" t="str">
-        <v>New York, NY; San Francisco, CA</v>
+        <v>Doha, Qatar ; Dubai, UAE</v>
       </c>
       <c r="I98" t="str">
-        <v>San Francisco</v>
+        <v>Doha</v>
       </c>
       <c r="J98" t="str">
         <v>On-site</v>
@@ -6349,7 +6349,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L98" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4720213005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4589749005</v>
       </c>
       <c r="M98">
         <v>200</v>
@@ -6358,7 +6358,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O98" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P98" t="str">
         <v>Today</v>
@@ -6367,18 +6367,18 @@
         <v>Yes</v>
       </c>
       <c r="R98" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S98">
-        <v>90</v>
+        <v>63</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>job-7ff81a54</v>
+        <v>job-6c1eab2d</v>
       </c>
       <c r="B99" t="str">
-        <v>Senior AI Product Manager, Finance Agents</v>
+        <v>Senior AI Product Manager, Code</v>
       </c>
       <c r="C99" t="str">
         <v>Scale AI</v>
@@ -6396,7 +6396,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H99" t="str">
-        <v>San Francisco, CA; New York, NY</v>
+        <v>New York, NY; San Francisco, CA</v>
       </c>
       <c r="I99" t="str">
         <v>San Francisco</v>
@@ -6408,7 +6408,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L99" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4611776005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4720501005</v>
       </c>
       <c r="M99">
         <v>200</v>
@@ -6417,7 +6417,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O99" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P99" t="str">
         <v>Today</v>
@@ -6426,18 +6426,18 @@
         <v>Yes</v>
       </c>
       <c r="R99" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S99">
-        <v>82</v>
+        <v>28</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>job-41be8c95</v>
+        <v>job-1310fa39</v>
       </c>
       <c r="B100" t="str">
-        <v>Senior AI Product Manager, Leaderboard</v>
+        <v>Senior AI Product Manager, Cybersecurity</v>
       </c>
       <c r="C100" t="str">
         <v>Scale AI</v>
@@ -6467,7 +6467,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L100" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4720216005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4720213005</v>
       </c>
       <c r="M100">
         <v>200</v>
@@ -6476,7 +6476,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O100" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P100" t="str">
         <v>Today</v>
@@ -6488,15 +6488,15 @@
         <v>No</v>
       </c>
       <c r="S100">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>job-59abfadc</v>
+        <v>job-7ff81a54</v>
       </c>
       <c r="B101" t="str">
-        <v>Staff Product Manager, Agentic Platform</v>
+        <v>Senior AI Product Manager, Finance Agents</v>
       </c>
       <c r="C101" t="str">
         <v>Scale AI</v>
@@ -6514,7 +6514,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H101" t="str">
-        <v>New York, NY; San Francisco, CA; Washington, DC</v>
+        <v>San Francisco, CA; New York, NY</v>
       </c>
       <c r="I101" t="str">
         <v>San Francisco</v>
@@ -6526,7 +6526,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L101" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4612403005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4611776005</v>
       </c>
       <c r="M101">
         <v>200</v>
@@ -6535,7 +6535,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O101" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P101" t="str">
         <v>Today</v>
@@ -6547,15 +6547,15 @@
         <v>No</v>
       </c>
       <c r="S101">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>job-3ad31a80</v>
+        <v>job-41be8c95</v>
       </c>
       <c r="B102" t="str">
-        <v>Staff Product Manager, Gen AI</v>
+        <v>Senior AI Product Manager, Leaderboard</v>
       </c>
       <c r="C102" t="str">
         <v>Scale AI</v>
@@ -6585,7 +6585,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L102" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4675842005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4720216005</v>
       </c>
       <c r="M102">
         <v>200</v>
@@ -6594,27 +6594,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O102" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P102" t="str">
         <v>Today</v>
       </c>
       <c r="Q102" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R102" t="str">
         <v>No</v>
       </c>
       <c r="S102">
-        <v>52</v>
+        <v>83</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>job-20e060b6</v>
+        <v>job-59abfadc</v>
       </c>
       <c r="B103" t="str">
-        <v>Staff Product Manager, Physical AI Data &amp; Robotics</v>
+        <v>Staff Product Manager, Agentic Platform</v>
       </c>
       <c r="C103" t="str">
         <v>Scale AI</v>
@@ -6632,7 +6632,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H103" t="str">
-        <v>San Francisco, CA</v>
+        <v>New York, NY; San Francisco, CA; Washington, DC</v>
       </c>
       <c r="I103" t="str">
         <v>San Francisco</v>
@@ -6644,7 +6644,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L103" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4718559005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4612403005</v>
       </c>
       <c r="M103">
         <v>200</v>
@@ -6653,7 +6653,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O103" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P103" t="str">
         <v>Today</v>
@@ -6665,15 +6665,15 @@
         <v>Yes</v>
       </c>
       <c r="S103">
-        <v>89</v>
+        <v>38</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>job-2ab7f7d1</v>
+        <v>job-3ad31a80</v>
       </c>
       <c r="B104" t="str">
-        <v>Staff Technical Product Manager</v>
+        <v>Staff Product Manager, Gen AI</v>
       </c>
       <c r="C104" t="str">
         <v>Scale AI</v>
@@ -6691,10 +6691,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H104" t="str">
-        <v>London, UK</v>
+        <v>New York, NY; San Francisco, CA</v>
       </c>
       <c r="I104" t="str">
-        <v>London</v>
+        <v>San Francisco</v>
       </c>
       <c r="J104" t="str">
         <v>On-site</v>
@@ -6703,7 +6703,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L104" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4683446005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4675842005</v>
       </c>
       <c r="M104">
         <v>200</v>
@@ -6712,48 +6712,48 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O104" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P104" t="str">
         <v>Today</v>
       </c>
       <c r="Q104" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R104" t="str">
         <v>No</v>
       </c>
       <c r="S104">
-        <v>46</v>
+        <v>32</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>job-58b32a73</v>
+        <v>job-20e060b6</v>
       </c>
       <c r="B105" t="str">
-        <v>Director of Product, Growth/AI</v>
+        <v>Staff Product Manager, Physical AI Data &amp; Robotics</v>
       </c>
       <c r="C105" t="str">
-        <v>Brex</v>
+        <v>Scale AI</v>
       </c>
       <c r="D105" t="str">
         <v>Wellfound</v>
       </c>
       <c r="E105" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F105" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G105" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H105" t="str">
-        <v>Seattle, Washington, United States</v>
+        <v>San Francisco, CA</v>
       </c>
       <c r="I105" t="str">
-        <v>Seattle</v>
+        <v>San Francisco</v>
       </c>
       <c r="J105" t="str">
         <v>On-site</v>
@@ -6762,7 +6762,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L105" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8433470002</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4718559005</v>
       </c>
       <c r="M105">
         <v>200</v>
@@ -6771,7 +6771,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O105" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P105" t="str">
         <v>Today</v>
@@ -6780,39 +6780,39 @@
         <v>No</v>
       </c>
       <c r="R105" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S105">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>job-6c147538</v>
+        <v>job-2ab7f7d1</v>
       </c>
       <c r="B106" t="str">
-        <v>Group Product Manager</v>
+        <v>Staff Technical Product Manager</v>
       </c>
       <c r="C106" t="str">
-        <v>Brex</v>
+        <v>Scale AI</v>
       </c>
       <c r="D106" t="str">
         <v>Wellfound</v>
       </c>
       <c r="E106" t="str">
-        <v>Product Lead / Director</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F106" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G106" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H106" t="str">
-        <v>New York, New York, United States</v>
+        <v>London, UK</v>
       </c>
       <c r="I106" t="str">
-        <v>New York</v>
+        <v>London</v>
       </c>
       <c r="J106" t="str">
         <v>On-site</v>
@@ -6821,7 +6821,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L106" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8438581002</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4683446005</v>
       </c>
       <c r="M106">
         <v>200</v>
@@ -6830,27 +6830,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O106" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P106" t="str">
         <v>Today</v>
       </c>
       <c r="Q106" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R106" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S106">
-        <v>39</v>
+        <v>92</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>job-4a5cf899</v>
+        <v>job-58b32a73</v>
       </c>
       <c r="B107" t="str">
-        <v>Senior Product Manager, AI</v>
+        <v>Director of Product, Growth/AI</v>
       </c>
       <c r="C107" t="str">
         <v>Brex</v>
@@ -6859,19 +6859,19 @@
         <v>Wellfound</v>
       </c>
       <c r="E107" t="str">
-        <v>Senior Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F107" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G107" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H107" t="str">
-        <v>Seattle, Washington, United States</v>
+        <v>San Francisco, California, United States</v>
       </c>
       <c r="I107" t="str">
-        <v>Seattle</v>
+        <v>San Francisco</v>
       </c>
       <c r="J107" t="str">
         <v>On-site</v>
@@ -6880,7 +6880,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L107" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8780828002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8432707002</v>
       </c>
       <c r="M107">
         <v>200</v>
@@ -6889,7 +6889,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O107" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P107" t="str">
         <v>Today</v>
@@ -6901,15 +6901,15 @@
         <v>No</v>
       </c>
       <c r="S107">
-        <v>75</v>
+        <v>68</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>job-111c900b</v>
+        <v>job-6c147538</v>
       </c>
       <c r="B108" t="str">
-        <v>Senior Product Manager, Travel</v>
+        <v>Group Product Manager</v>
       </c>
       <c r="C108" t="str">
         <v>Brex</v>
@@ -6918,19 +6918,19 @@
         <v>Wellfound</v>
       </c>
       <c r="E108" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F108" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G108" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H108" t="str">
-        <v>New York, New York, United States</v>
+        <v>Vancouver, British Columbia, Canada</v>
       </c>
       <c r="I108" t="str">
-        <v>New York</v>
+        <v>Vancouver</v>
       </c>
       <c r="J108" t="str">
         <v>On-site</v>
@@ -6939,7 +6939,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L108" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8659251002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8438584002</v>
       </c>
       <c r="M108">
         <v>200</v>
@@ -6948,27 +6948,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O108" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P108" t="str">
         <v>Today</v>
       </c>
       <c r="Q108" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R108" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S108">
-        <v>75</v>
+        <v>43</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>job-337165a7</v>
+        <v>job-4a5cf899</v>
       </c>
       <c r="B109" t="str">
-        <v>Staff Product Manager</v>
+        <v>Senior Product Manager, AI</v>
       </c>
       <c r="C109" t="str">
         <v>Brex</v>
@@ -6998,7 +6998,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L109" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8432698002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8780827002</v>
       </c>
       <c r="M109">
         <v>200</v>
@@ -7007,7 +7007,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O109" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P109" t="str">
         <v>Today</v>
@@ -7016,18 +7016,18 @@
         <v>No</v>
       </c>
       <c r="R109" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S109">
-        <v>85</v>
+        <v>80</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>job-533982f5</v>
+        <v>job-111c900b</v>
       </c>
       <c r="B110" t="str">
-        <v>Staff Product Manager, AI</v>
+        <v>Senior Product Manager, Travel</v>
       </c>
       <c r="C110" t="str">
         <v>Brex</v>
@@ -7057,7 +7057,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L110" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8780829002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8659251002</v>
       </c>
       <c r="M110">
         <v>200</v>
@@ -7066,7 +7066,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O110" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P110" t="str">
         <v>Today</v>
@@ -7078,15 +7078,15 @@
         <v>No</v>
       </c>
       <c r="S110">
-        <v>29</v>
+        <v>33</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>job-0f9c4e5d</v>
+        <v>job-337165a7</v>
       </c>
       <c r="B111" t="str">
-        <v>Staff Product Manager, Card</v>
+        <v>Staff Product Manager</v>
       </c>
       <c r="C111" t="str">
         <v>Brex</v>
@@ -7104,10 +7104,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H111" t="str">
-        <v>Seattle, Washington, United States</v>
+        <v>New York, New York, United States</v>
       </c>
       <c r="I111" t="str">
-        <v>Seattle</v>
+        <v>New York</v>
       </c>
       <c r="J111" t="str">
         <v>On-site</v>
@@ -7116,7 +7116,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L111" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8659221002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8432702002</v>
       </c>
       <c r="M111">
         <v>200</v>
@@ -7125,7 +7125,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O111" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P111" t="str">
         <v>Today</v>
@@ -7137,15 +7137,15 @@
         <v>Yes</v>
       </c>
       <c r="S111">
-        <v>59</v>
+        <v>46</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>job-4401c5a9</v>
+        <v>job-533982f5</v>
       </c>
       <c r="B112" t="str">
-        <v>Staff Product Manager, Embedded</v>
+        <v>Staff Product Manager, AI</v>
       </c>
       <c r="C112" t="str">
         <v>Brex</v>
@@ -7163,10 +7163,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H112" t="str">
-        <v>Seattle, Washington, United States</v>
+        <v>New York, New York, United States</v>
       </c>
       <c r="I112" t="str">
-        <v>Seattle</v>
+        <v>New York</v>
       </c>
       <c r="J112" t="str">
         <v>On-site</v>
@@ -7175,7 +7175,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L112" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8659210002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8780829002</v>
       </c>
       <c r="M112">
         <v>200</v>
@@ -7184,27 +7184,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O112" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P112" t="str">
         <v>Today</v>
       </c>
       <c r="Q112" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R112" t="str">
         <v>Yes</v>
       </c>
       <c r="S112">
-        <v>30</v>
+        <v>53</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>job-75398a6b</v>
+        <v>job-0f9c4e5d</v>
       </c>
       <c r="B113" t="str">
-        <v>Staff Product Manager,  Embedded</v>
+        <v>Staff Product Manager, Card</v>
       </c>
       <c r="C113" t="str">
         <v>Brex</v>
@@ -7234,7 +7234,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L113" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8659211002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8659237002</v>
       </c>
       <c r="M113">
         <v>200</v>
@@ -7243,7 +7243,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O113" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P113" t="str">
         <v>Today</v>
@@ -7255,15 +7255,15 @@
         <v>No</v>
       </c>
       <c r="S113">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>job-0f02a1a8</v>
+        <v>job-4401c5a9</v>
       </c>
       <c r="B114" t="str">
-        <v>Staff Product Manager, Expenses</v>
+        <v>Staff Product Manager, Embedded</v>
       </c>
       <c r="C114" t="str">
         <v>Brex</v>
@@ -7281,10 +7281,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H114" t="str">
-        <v>Seattle, Washington, United States</v>
+        <v>San Francisco, California, United States</v>
       </c>
       <c r="I114" t="str">
-        <v>Seattle</v>
+        <v>San Francisco</v>
       </c>
       <c r="J114" t="str">
         <v>On-site</v>
@@ -7293,7 +7293,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L114" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8659241002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8659204002</v>
       </c>
       <c r="M114">
         <v>200</v>
@@ -7302,27 +7302,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O114" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P114" t="str">
         <v>Today</v>
       </c>
       <c r="Q114" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R114" t="str">
         <v>No</v>
       </c>
       <c r="S114">
-        <v>51</v>
+        <v>67</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>job-2239c52c</v>
+        <v>job-75398a6b</v>
       </c>
       <c r="B115" t="str">
-        <v>Staff Product Manager, Growth</v>
+        <v>Staff Product Manager,  Embedded</v>
       </c>
       <c r="C115" t="str">
         <v>Brex</v>
@@ -7352,7 +7352,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L115" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8436528002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8659211002</v>
       </c>
       <c r="M115">
         <v>200</v>
@@ -7361,7 +7361,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O115" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P115" t="str">
         <v>Today</v>
@@ -7373,36 +7373,36 @@
         <v>No</v>
       </c>
       <c r="S115">
-        <v>73</v>
+        <v>63</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>job-05c59396</v>
+        <v>job-0f02a1a8</v>
       </c>
       <c r="B116" t="str">
-        <v>Lead Product Manager</v>
+        <v>Staff Product Manager, Expenses</v>
       </c>
       <c r="C116" t="str">
-        <v>Carta</v>
+        <v>Brex</v>
       </c>
       <c r="D116" t="str">
-        <v>Instahyre</v>
+        <v>Wellfound</v>
       </c>
       <c r="E116" t="str">
-        <v>Product Lead / Director</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F116" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G116" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H116" t="str">
-        <v>San Francisco, CA; Seattle, WA; New York, NY</v>
+        <v>New York, New York, United States</v>
       </c>
       <c r="I116" t="str">
-        <v>San Francisco</v>
+        <v>New York</v>
       </c>
       <c r="J116" t="str">
         <v>On-site</v>
@@ -7411,7 +7411,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L116" t="str">
-        <v>https://boards.greenhouse.io/carta/jobs/7544235003</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8659242002</v>
       </c>
       <c r="M116">
         <v>200</v>
@@ -7420,30 +7420,30 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O116" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P116" t="str">
         <v>Today</v>
       </c>
       <c r="Q116" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R116" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S116">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>job-1b56d1fb</v>
+        <v>job-2239c52c</v>
       </c>
       <c r="B117" t="str">
-        <v>Senior Product Manager</v>
+        <v>Staff Product Manager, Growth</v>
       </c>
       <c r="C117" t="str">
-        <v>Duolingo</v>
+        <v>Brex</v>
       </c>
       <c r="D117" t="str">
         <v>Wellfound</v>
@@ -7458,10 +7458,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H117" t="str">
-        <v>Beijing, China</v>
+        <v>San Francisco, California, United States</v>
       </c>
       <c r="I117" t="str">
-        <v>Beijing</v>
+        <v>San Francisco</v>
       </c>
       <c r="J117" t="str">
         <v>On-site</v>
@@ -7470,7 +7470,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L117" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8675670002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8436527002</v>
       </c>
       <c r="M117">
         <v>200</v>
@@ -7479,16 +7479,16 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O117" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P117" t="str">
         <v>Today</v>
       </c>
       <c r="Q117" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R117" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S117">
         <v>70</v>
@@ -7496,31 +7496,31 @@
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>job-0ba5b818</v>
+        <v>job-05c59396</v>
       </c>
       <c r="B118" t="str">
-        <v>Senior Product Manager, DET</v>
+        <v>Lead Product Manager</v>
       </c>
       <c r="C118" t="str">
-        <v>Duolingo</v>
+        <v>Carta</v>
       </c>
       <c r="D118" t="str">
-        <v>Wellfound</v>
+        <v>Instahyre</v>
       </c>
       <c r="E118" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F118" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G118" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H118" t="str">
-        <v>New York, NY</v>
+        <v>San Francisco, CA; Seattle, WA; New York, NY</v>
       </c>
       <c r="I118" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J118" t="str">
         <v>On-site</v>
@@ -7529,7 +7529,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L118" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8737859002</v>
+        <v>https://boards.greenhouse.io/carta/jobs/7544235003</v>
       </c>
       <c r="M118">
         <v>200</v>
@@ -7538,7 +7538,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O118" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P118" t="str">
         <v>Today</v>
@@ -7547,18 +7547,18 @@
         <v>Yes</v>
       </c>
       <c r="R118" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S118">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>job-25986280</v>
+        <v>job-1b56d1fb</v>
       </c>
       <c r="B119" t="str">
-        <v>Senior Product Manager, Growth</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="C119" t="str">
         <v>Duolingo</v>
@@ -7576,10 +7576,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H119" t="str">
-        <v>Pittsburgh, PA</v>
+        <v>Beijing, China</v>
       </c>
       <c r="I119" t="str">
-        <v>Pittsburgh</v>
+        <v>Beijing</v>
       </c>
       <c r="J119" t="str">
         <v>On-site</v>
@@ -7588,7 +7588,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L119" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8747171002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8675670002</v>
       </c>
       <c r="M119">
         <v>200</v>
@@ -7597,27 +7597,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O119" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P119" t="str">
         <v>Today</v>
       </c>
       <c r="Q119" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R119" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S119">
-        <v>37</v>
+        <v>84</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>job-587bfc02</v>
+        <v>job-0ba5b818</v>
       </c>
       <c r="B120" t="str">
-        <v>Senior Product Manager, Monetization</v>
+        <v>Senior Product Manager, DET</v>
       </c>
       <c r="C120" t="str">
         <v>Duolingo</v>
@@ -7647,7 +7647,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L120" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8474673002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8737859002</v>
       </c>
       <c r="M120">
         <v>200</v>
@@ -7656,7 +7656,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O120" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P120" t="str">
         <v>Today</v>
@@ -7668,15 +7668,15 @@
         <v>No</v>
       </c>
       <c r="S120">
-        <v>71</v>
+        <v>53</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>job-256f50fd</v>
+        <v>job-25986280</v>
       </c>
       <c r="B121" t="str">
-        <v>Senior Product Manager, Notifications</v>
+        <v>Senior Product Manager, Growth</v>
       </c>
       <c r="C121" t="str">
         <v>Duolingo</v>
@@ -7706,7 +7706,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L121" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8747099002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8747171002</v>
       </c>
       <c r="M121">
         <v>200</v>
@@ -7715,7 +7715,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O121" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P121" t="str">
         <v>Today</v>
@@ -7724,18 +7724,18 @@
         <v>No</v>
       </c>
       <c r="R121" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S121">
-        <v>57</v>
+        <v>34</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>job-6e88535c</v>
+        <v>job-587bfc02</v>
       </c>
       <c r="B122" t="str">
-        <v>VP of Product, Growth and Monetization</v>
+        <v>Senior Product Manager, Monetization</v>
       </c>
       <c r="C122" t="str">
         <v>Duolingo</v>
@@ -7744,13 +7744,13 @@
         <v>Wellfound</v>
       </c>
       <c r="E122" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F122" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G122" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H122" t="str">
         <v>New York, NY</v>
@@ -7765,7 +7765,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L122" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8747060002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8474673002</v>
       </c>
       <c r="M122">
         <v>200</v>
@@ -7774,66 +7774,66 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O122" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P122" t="str">
         <v>Today</v>
       </c>
       <c r="Q122" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R122" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S122">
-        <v>74</v>
+        <v>92</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>job-65a74288</v>
+        <v>job-256f50fd</v>
       </c>
       <c r="B123" t="str">
-        <v>Associate Product Manager Intern</v>
+        <v>Senior Product Manager, Notifications</v>
       </c>
       <c r="C123" t="str">
-        <v>Coinbase</v>
+        <v>Duolingo</v>
       </c>
       <c r="D123" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E123" t="str">
-        <v>Associate Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F123" t="str">
-        <v>1-3 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G123" t="str">
-        <v>0-2 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H123" t="str">
-        <v>Hybrid - San Francisco, CA</v>
+        <v>Pittsburgh, PA</v>
       </c>
       <c r="I123" t="str">
-        <v>San Francisco</v>
+        <v>Pittsburgh</v>
       </c>
       <c r="J123" t="str">
-        <v>Hybrid</v>
+        <v>On-site</v>
       </c>
       <c r="K123" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L123" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/8168322</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8747099002</v>
       </c>
       <c r="M123">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N123" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O123" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P123" t="str">
         <v>Today</v>
@@ -7845,74 +7845,74 @@
         <v>Yes</v>
       </c>
       <c r="S123">
-        <v>32</v>
+        <v>54</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>job-2bc26745</v>
+        <v>job-6e88535c</v>
       </c>
       <c r="B124" t="str">
-        <v>Group Product Manager, Compliance Agent Experience</v>
+        <v>VP of Product, Growth and Monetization</v>
       </c>
       <c r="C124" t="str">
-        <v>Coinbase</v>
+        <v>Duolingo</v>
       </c>
       <c r="D124" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E124" t="str">
         <v>AI &amp; Growth PM</v>
       </c>
       <c r="F124" t="str">
-        <v>3-6 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G124" t="str">
-        <v>2-5 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H124" t="str">
-        <v>Remote - USA</v>
+        <v>Pittsburgh, PA</v>
       </c>
       <c r="I124" t="str">
-        <v>Remote</v>
+        <v>Pittsburgh</v>
       </c>
       <c r="J124" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K124" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L124" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/8060662</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8747077002</v>
       </c>
       <c r="M124">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N124" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O124" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P124" t="str">
         <v>Today</v>
       </c>
       <c r="Q124" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R124" t="str">
         <v>No</v>
       </c>
       <c r="S124">
-        <v>35</v>
+        <v>68</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>job-779d88ed</v>
+        <v>job-65a74288</v>
       </c>
       <c r="B125" t="str">
-        <v>Group Product Manager, Compliance Automation</v>
+        <v>Associate Product Manager Intern</v>
       </c>
       <c r="C125" t="str">
         <v>Coinbase</v>
@@ -7921,28 +7921,28 @@
         <v>LinkedIn</v>
       </c>
       <c r="E125" t="str">
-        <v>Product Lead / Director</v>
+        <v>Associate Product Manager</v>
       </c>
       <c r="F125" t="str">
-        <v>3-6 yrs</v>
+        <v>1-3 yrs</v>
       </c>
       <c r="G125" t="str">
-        <v>2-5 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H125" t="str">
-        <v>Remote - USA</v>
+        <v>Hybrid - San Francisco, CA</v>
       </c>
       <c r="I125" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J125" t="str">
-        <v>Remote</v>
+        <v>Hybrid</v>
       </c>
       <c r="K125" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L125" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/7701642</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/8168322</v>
       </c>
       <c r="M125">
         <v>403</v>
@@ -7951,27 +7951,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O125" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P125" t="str">
         <v>Today</v>
       </c>
       <c r="Q125" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R125" t="str">
         <v>No</v>
       </c>
       <c r="S125">
-        <v>63</v>
+        <v>77</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>job-6faf73eb</v>
+        <v>job-2bc26745</v>
       </c>
       <c r="B126" t="str">
-        <v>Group Product Manager, Core Infrastructure &amp; Reliability</v>
+        <v>Group Product Manager, Compliance Agent Experience</v>
       </c>
       <c r="C126" t="str">
         <v>Coinbase</v>
@@ -7980,7 +7980,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E126" t="str">
-        <v>Technical Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F126" t="str">
         <v>3-6 yrs</v>
@@ -8001,7 +8001,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L126" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/7997785</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/8060662</v>
       </c>
       <c r="M126">
         <v>403</v>
@@ -8010,7 +8010,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O126" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P126" t="str">
         <v>Today</v>
@@ -8022,15 +8022,15 @@
         <v>No</v>
       </c>
       <c r="S126">
-        <v>70</v>
+        <v>83</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>job-67afa492</v>
+        <v>job-779d88ed</v>
       </c>
       <c r="B127" t="str">
-        <v>Group Product Manager, Developer Infrastructure</v>
+        <v>Group Product Manager, Compliance Automation</v>
       </c>
       <c r="C127" t="str">
         <v>Coinbase</v>
@@ -8039,7 +8039,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E127" t="str">
-        <v>Technical Product Manager</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F127" t="str">
         <v>3-6 yrs</v>
@@ -8060,7 +8060,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L127" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/8017607</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/7701642</v>
       </c>
       <c r="M127">
         <v>403</v>
@@ -8069,7 +8069,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O127" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P127" t="str">
         <v>Today</v>
@@ -8081,15 +8081,15 @@
         <v>No</v>
       </c>
       <c r="S127">
-        <v>71</v>
+        <v>58</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>job-00f9bc89</v>
+        <v>job-6faf73eb</v>
       </c>
       <c r="B128" t="str">
-        <v>Head of Product Creative</v>
+        <v>Group Product Manager, Core Infrastructure &amp; Reliability</v>
       </c>
       <c r="C128" t="str">
         <v>Coinbase</v>
@@ -8098,13 +8098,13 @@
         <v>LinkedIn</v>
       </c>
       <c r="E128" t="str">
-        <v>Product Lead / Director</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F128" t="str">
-        <v>8+ yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G128" t="str">
-        <v>8+ yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H128" t="str">
         <v>Remote - USA</v>
@@ -8119,7 +8119,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L128" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/7304930</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/7997785</v>
       </c>
       <c r="M128">
         <v>403</v>
@@ -8128,27 +8128,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O128" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P128" t="str">
         <v>Today</v>
       </c>
       <c r="Q128" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R128" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S128">
-        <v>56</v>
+        <v>83</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>job-02200da7</v>
+        <v>job-67afa492</v>
       </c>
       <c r="B129" t="str">
-        <v>Product Manager (HR Technology) Intern</v>
+        <v>Group Product Manager, Developer Infrastructure</v>
       </c>
       <c r="C129" t="str">
         <v>Coinbase</v>
@@ -8157,28 +8157,28 @@
         <v>LinkedIn</v>
       </c>
       <c r="E129" t="str">
-        <v>Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F129" t="str">
-        <v>1-3 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G129" t="str">
-        <v>0-2 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H129" t="str">
-        <v>Hybrid - New York, NY</v>
+        <v>Remote - USA</v>
       </c>
       <c r="I129" t="str">
-        <v>New York</v>
+        <v>Remote</v>
       </c>
       <c r="J129" t="str">
-        <v>Hybrid</v>
+        <v>Remote</v>
       </c>
       <c r="K129" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L129" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/8175504</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/8017607</v>
       </c>
       <c r="M129">
         <v>403</v>
@@ -8187,7 +8187,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O129" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P129" t="str">
         <v>Today</v>
@@ -8196,18 +8196,18 @@
         <v>Yes</v>
       </c>
       <c r="R129" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S129">
-        <v>57</v>
+        <v>33</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>job-0d5f8a75</v>
+        <v>job-00f9bc89</v>
       </c>
       <c r="B130" t="str">
-        <v>Product Manager II, Workspace and Multi-User</v>
+        <v>Head of Product Creative</v>
       </c>
       <c r="C130" t="str">
         <v>Coinbase</v>
@@ -8216,13 +8216,13 @@
         <v>LinkedIn</v>
       </c>
       <c r="E130" t="str">
-        <v>Product Manager</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F130" t="str">
-        <v>3-6 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G130" t="str">
-        <v>2-5 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H130" t="str">
         <v>Remote - USA</v>
@@ -8237,7 +8237,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L130" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/8148171</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/7304930</v>
       </c>
       <c r="M130">
         <v>403</v>
@@ -8246,27 +8246,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O130" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P130" t="str">
         <v>Today</v>
       </c>
       <c r="Q130" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R130" t="str">
         <v>No</v>
       </c>
       <c r="S130">
-        <v>73</v>
+        <v>52</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>job-2efe7fb3</v>
+        <v>job-02200da7</v>
       </c>
       <c r="B131" t="str">
-        <v>Senior Product Manager, Help Center (CX Automation)</v>
+        <v>Product Manager (HR Technology) Intern</v>
       </c>
       <c r="C131" t="str">
         <v>Coinbase</v>
@@ -8275,28 +8275,28 @@
         <v>LinkedIn</v>
       </c>
       <c r="E131" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F131" t="str">
-        <v>5-8 yrs</v>
+        <v>1-3 yrs</v>
       </c>
       <c r="G131" t="str">
-        <v>5-8 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H131" t="str">
-        <v>Remote - India</v>
+        <v>Hybrid - New York, NY</v>
       </c>
       <c r="I131" t="str">
-        <v>Remote</v>
+        <v>New York</v>
       </c>
       <c r="J131" t="str">
-        <v>Remote</v>
+        <v>Hybrid</v>
       </c>
       <c r="K131" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L131" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/8031208</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/8175504</v>
       </c>
       <c r="M131">
         <v>403</v>
@@ -8305,45 +8305,45 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O131" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P131" t="str">
         <v>Today</v>
       </c>
       <c r="Q131" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R131" t="str">
         <v>No</v>
       </c>
       <c r="S131">
-        <v>36</v>
+        <v>45</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>job-46ec002c</v>
+        <v>job-0d5f8a75</v>
       </c>
       <c r="B132" t="str">
-        <v>Principal Product Manager, AI Custom Models</v>
+        <v>Product Manager II, Workspace and Multi-User</v>
       </c>
       <c r="C132" t="str">
-        <v>GitLab</v>
+        <v>Coinbase</v>
       </c>
       <c r="D132" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E132" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F132" t="str">
-        <v>8+ yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G132" t="str">
-        <v>8+ yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H132" t="str">
-        <v>Remote, Canada; Remote, US</v>
+        <v>Remote - USA</v>
       </c>
       <c r="I132" t="str">
         <v>Remote</v>
@@ -8355,16 +8355,16 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L132" t="str">
-        <v>https://boards.greenhouse.io/gitlab/jobs/8564957002</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/8148171</v>
       </c>
       <c r="M132">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N132" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O132" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P132" t="str">
         <v>Today</v>
@@ -8376,33 +8376,33 @@
         <v>No</v>
       </c>
       <c r="S132">
-        <v>77</v>
+        <v>85</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>job-58e27f7c</v>
+        <v>job-2efe7fb3</v>
       </c>
       <c r="B133" t="str">
-        <v>Principal Product Manager, AI Software Factory</v>
+        <v>Senior Product Manager, Help Center (CX Automation)</v>
       </c>
       <c r="C133" t="str">
-        <v>GitLab</v>
+        <v>Coinbase</v>
       </c>
       <c r="D133" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E133" t="str">
         <v>Senior Product Manager</v>
       </c>
       <c r="F133" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G133" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H133" t="str">
-        <v>Remote, Canada; Remote, United States</v>
+        <v>Remote - India</v>
       </c>
       <c r="I133" t="str">
         <v>Remote</v>
@@ -8414,36 +8414,36 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L133" t="str">
-        <v>https://boards.greenhouse.io/gitlab/jobs/8658878002</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/8031208</v>
       </c>
       <c r="M133">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N133" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O133" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P133" t="str">
         <v>Today</v>
       </c>
       <c r="Q133" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R133" t="str">
         <v>Yes</v>
       </c>
       <c r="S133">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>job-085a3b56</v>
+        <v>job-1762a9dc</v>
       </c>
       <c r="B134" t="str">
-        <v>Senior Manager, Product Management: Agentic Software Delivery</v>
+        <v>Director of Product Management, Agentic Software Delivery</v>
       </c>
       <c r="C134" t="str">
         <v>GitLab</v>
@@ -8452,16 +8452,16 @@
         <v>Wellfound</v>
       </c>
       <c r="E134" t="str">
-        <v>Senior Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F134" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G134" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H134" t="str">
-        <v>Remote, Canada; Remote, US</v>
+        <v>Remote, United States</v>
       </c>
       <c r="I134" t="str">
         <v>Remote</v>
@@ -8473,7 +8473,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L134" t="str">
-        <v>https://boards.greenhouse.io/gitlab/jobs/8597826002</v>
+        <v>https://boards.greenhouse.io/gitlab/jobs/8806017002</v>
       </c>
       <c r="M134">
         <v>200</v>
@@ -8482,7 +8482,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O134" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P134" t="str">
         <v>Today</v>
@@ -8491,18 +8491,18 @@
         <v>Yes</v>
       </c>
       <c r="R134" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S134">
-        <v>67</v>
+        <v>31</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>job-7167a200</v>
+        <v>job-46ec002c</v>
       </c>
       <c r="B135" t="str">
-        <v>Senior Product Manager, Growth</v>
+        <v>Principal Product Manager, AI Custom Models</v>
       </c>
       <c r="C135" t="str">
         <v>GitLab</v>
@@ -8514,13 +8514,13 @@
         <v>Senior Product Manager</v>
       </c>
       <c r="F135" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G135" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H135" t="str">
-        <v>Remote, Canada; Remote, United States</v>
+        <v>Remote, Canada; Remote, US</v>
       </c>
       <c r="I135" t="str">
         <v>Remote</v>
@@ -8532,7 +8532,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L135" t="str">
-        <v>https://boards.greenhouse.io/gitlab/jobs/8684348002</v>
+        <v>https://boards.greenhouse.io/gitlab/jobs/8564957002</v>
       </c>
       <c r="M135">
         <v>200</v>
@@ -8541,27 +8541,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O135" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P135" t="str">
         <v>Today</v>
       </c>
       <c r="Q135" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R135" t="str">
         <v>No</v>
       </c>
       <c r="S135">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>job-6bc28568</v>
+        <v>job-58e27f7c</v>
       </c>
       <c r="B136" t="str">
-        <v>Senior Product Manager, Secret Detection and Vulnerability Research</v>
+        <v>Principal Product Manager, AI Software Factory</v>
       </c>
       <c r="C136" t="str">
         <v>GitLab</v>
@@ -8573,13 +8573,13 @@
         <v>Senior Product Manager</v>
       </c>
       <c r="F136" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G136" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H136" t="str">
-        <v>Remote, United States</v>
+        <v>Remote, Canada; Remote, United States</v>
       </c>
       <c r="I136" t="str">
         <v>Remote</v>
@@ -8591,7 +8591,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L136" t="str">
-        <v>https://boards.greenhouse.io/gitlab/jobs/8697043002</v>
+        <v>https://boards.greenhouse.io/gitlab/jobs/8658878002</v>
       </c>
       <c r="M136">
         <v>200</v>
@@ -8600,7 +8600,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O136" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P136" t="str">
         <v>Today</v>
@@ -8612,15 +8612,15 @@
         <v>No</v>
       </c>
       <c r="S136">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>job-274a6d99</v>
+        <v>job-7167a200</v>
       </c>
       <c r="B137" t="str">
-        <v>Senior Product Manager, Source Code</v>
+        <v>Senior Product Manager, Growth</v>
       </c>
       <c r="C137" t="str">
         <v>GitLab</v>
@@ -8638,7 +8638,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H137" t="str">
-        <v>Remote, Canada; Remote, US</v>
+        <v>Remote, Canada; Remote, United States</v>
       </c>
       <c r="I137" t="str">
         <v>Remote</v>
@@ -8650,7 +8650,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L137" t="str">
-        <v>https://boards.greenhouse.io/gitlab/jobs/8597805002</v>
+        <v>https://boards.greenhouse.io/gitlab/jobs/8684348002</v>
       </c>
       <c r="M137">
         <v>200</v>
@@ -8659,27 +8659,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O137" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P137" t="str">
         <v>Today</v>
       </c>
       <c r="Q137" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R137" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S137">
-        <v>91</v>
+        <v>51</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>job-7ad77ccd</v>
+        <v>job-6bc28568</v>
       </c>
       <c r="B138" t="str">
-        <v>Senior Product Manager, Tenant Scale</v>
+        <v>Senior Product Manager, Secret Detection and Vulnerability Research</v>
       </c>
       <c r="C138" t="str">
         <v>GitLab</v>
@@ -8697,7 +8697,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H138" t="str">
-        <v>Remote, Canada; Remote, US</v>
+        <v>Remote, United States</v>
       </c>
       <c r="I138" t="str">
         <v>Remote</v>
@@ -8709,7 +8709,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L138" t="str">
-        <v>https://boards.greenhouse.io/gitlab/jobs/8512220002</v>
+        <v>https://boards.greenhouse.io/gitlab/jobs/8697043002</v>
       </c>
       <c r="M138">
         <v>200</v>
@@ -8718,7 +8718,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O138" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P138" t="str">
         <v>Today</v>
@@ -8730,15 +8730,15 @@
         <v>No</v>
       </c>
       <c r="S138">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>job-52edb6a4</v>
+        <v>job-274a6d99</v>
       </c>
       <c r="B139" t="str">
-        <v>Staff Product Manager,  RevOps &amp; Finance Systems</v>
+        <v>Senior Product Manager, Source Code</v>
       </c>
       <c r="C139" t="str">
         <v>GitLab</v>
@@ -8756,7 +8756,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H139" t="str">
-        <v>Remote, US</v>
+        <v>Remote, Canada; Remote, US</v>
       </c>
       <c r="I139" t="str">
         <v>Remote</v>
@@ -8768,7 +8768,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L139" t="str">
-        <v>https://boards.greenhouse.io/gitlab/jobs/8612937002</v>
+        <v>https://boards.greenhouse.io/gitlab/jobs/8597805002</v>
       </c>
       <c r="M139">
         <v>200</v>
@@ -8777,7 +8777,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O139" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P139" t="str">
         <v>Today</v>
@@ -8789,45 +8789,45 @@
         <v>No</v>
       </c>
       <c r="S139">
-        <v>62</v>
+        <v>83</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>job-3a743e4f</v>
+        <v>job-7ad77ccd</v>
       </c>
       <c r="B140" t="str">
-        <v>Manager, Product Management - Figma Platform Experience</v>
+        <v>Senior Product Manager, Tenant Scale</v>
       </c>
       <c r="C140" t="str">
-        <v>Figma</v>
+        <v>GitLab</v>
       </c>
       <c r="D140" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E140" t="str">
-        <v>Technical Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F140" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G140" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H140" t="str">
-        <v>San Francisco, CA • New York, NY • United States</v>
+        <v>Remote, Canada; Remote, US</v>
       </c>
       <c r="I140" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J140" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K140" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L140" t="str">
-        <v>https://boards.greenhouse.io/figma/jobs/6160732004</v>
+        <v>https://boards.greenhouse.io/gitlab/jobs/8512220002</v>
       </c>
       <c r="M140">
         <v>200</v>
@@ -8836,7 +8836,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O140" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P140" t="str">
         <v>Today</v>
@@ -8845,48 +8845,48 @@
         <v>No</v>
       </c>
       <c r="R140" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S140">
-        <v>77</v>
+        <v>86</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>job-7297f499</v>
+        <v>job-52edb6a4</v>
       </c>
       <c r="B141" t="str">
-        <v>Manager, Product Management - Roundtripping</v>
+        <v>Staff Product Manager,  RevOps &amp; Finance Systems</v>
       </c>
       <c r="C141" t="str">
-        <v>Figma</v>
+        <v>GitLab</v>
       </c>
       <c r="D141" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E141" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F141" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G141" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H141" t="str">
-        <v>New York, NY • United States</v>
+        <v>Remote, US</v>
       </c>
       <c r="I141" t="str">
-        <v>New York</v>
+        <v>Remote</v>
       </c>
       <c r="J141" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K141" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L141" t="str">
-        <v>https://boards.greenhouse.io/figma/jobs/6104919004</v>
+        <v>https://boards.greenhouse.io/gitlab/jobs/8612937002</v>
       </c>
       <c r="M141">
         <v>200</v>
@@ -8895,7 +8895,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O141" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P141" t="str">
         <v>Today</v>
@@ -8907,15 +8907,15 @@
         <v>No</v>
       </c>
       <c r="S141">
-        <v>89</v>
+        <v>47</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>job-19031a2a</v>
+        <v>job-3a743e4f</v>
       </c>
       <c r="B142" t="str">
-        <v>Manager, Product Management - Roundtripping (London, United Kingdom)</v>
+        <v>Manager, Product Management - Figma Platform Experience</v>
       </c>
       <c r="C142" t="str">
         <v>Figma</v>
@@ -8924,7 +8924,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E142" t="str">
-        <v>Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F142" t="str">
         <v>3-6 yrs</v>
@@ -8933,10 +8933,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H142" t="str">
-        <v>London, England</v>
+        <v>San Francisco, CA • New York, NY • United States</v>
       </c>
       <c r="I142" t="str">
-        <v>London</v>
+        <v>San Francisco</v>
       </c>
       <c r="J142" t="str">
         <v>On-site</v>
@@ -8945,7 +8945,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L142" t="str">
-        <v>https://boards.greenhouse.io/figma/jobs/6149007004</v>
+        <v>https://boards.greenhouse.io/figma/jobs/6160732004</v>
       </c>
       <c r="M142">
         <v>200</v>
@@ -8954,27 +8954,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O142" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P142" t="str">
         <v>Today</v>
       </c>
       <c r="Q142" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R142" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S142">
-        <v>32</v>
+        <v>65</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>job-099ff647</v>
+        <v>job-7297f499</v>
       </c>
       <c r="B143" t="str">
-        <v>Product Manager, Acquisition</v>
+        <v>Manager, Product Management - Roundtripping</v>
       </c>
       <c r="C143" t="str">
         <v>Figma</v>
@@ -8992,10 +8992,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H143" t="str">
-        <v>San Francisco, CA • New York, NY • United States</v>
+        <v>New York, NY • United States</v>
       </c>
       <c r="I143" t="str">
-        <v>San Francisco</v>
+        <v>New York</v>
       </c>
       <c r="J143" t="str">
         <v>On-site</v>
@@ -9004,7 +9004,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L143" t="str">
-        <v>https://boards.greenhouse.io/figma/jobs/6119781004</v>
+        <v>https://boards.greenhouse.io/figma/jobs/6104919004</v>
       </c>
       <c r="M143">
         <v>200</v>
@@ -9013,27 +9013,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O143" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P143" t="str">
         <v>Today</v>
       </c>
       <c r="Q143" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R143" t="str">
         <v>No</v>
       </c>
       <c r="S143">
-        <v>91</v>
+        <v>57</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>job-714f8c79</v>
+        <v>job-19031a2a</v>
       </c>
       <c r="B144" t="str">
-        <v>Product Manager, AI Growth</v>
+        <v>Manager, Product Management - Roundtripping (London, United Kingdom)</v>
       </c>
       <c r="C144" t="str">
         <v>Figma</v>
@@ -9042,7 +9042,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E144" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Product Manager</v>
       </c>
       <c r="F144" t="str">
         <v>3-6 yrs</v>
@@ -9051,10 +9051,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H144" t="str">
-        <v>San Francisco, CA • New York, NY • United States</v>
+        <v>London, England</v>
       </c>
       <c r="I144" t="str">
-        <v>San Francisco</v>
+        <v>London</v>
       </c>
       <c r="J144" t="str">
         <v>On-site</v>
@@ -9063,7 +9063,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L144" t="str">
-        <v>https://boards.greenhouse.io/figma/jobs/5989185004</v>
+        <v>https://boards.greenhouse.io/figma/jobs/6149007004</v>
       </c>
       <c r="M144">
         <v>200</v>
@@ -9072,7 +9072,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O144" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P144" t="str">
         <v>Today</v>
@@ -9084,15 +9084,15 @@
         <v>No</v>
       </c>
       <c r="S144">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>job-6c338367</v>
+        <v>job-099ff647</v>
       </c>
       <c r="B145" t="str">
-        <v>Product Manager, Developer Platform</v>
+        <v>Product Manager, Acquisition</v>
       </c>
       <c r="C145" t="str">
         <v>Figma</v>
@@ -9101,7 +9101,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E145" t="str">
-        <v>Technical Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F145" t="str">
         <v>3-6 yrs</v>
@@ -9122,7 +9122,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L145" t="str">
-        <v>https://boards.greenhouse.io/figma/jobs/6100482004</v>
+        <v>https://boards.greenhouse.io/figma/jobs/6119781004</v>
       </c>
       <c r="M145">
         <v>200</v>
@@ -9131,7 +9131,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O145" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P145" t="str">
         <v>Today</v>
@@ -9140,18 +9140,18 @@
         <v>No</v>
       </c>
       <c r="R145" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S145">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>job-106cd4ad</v>
+        <v>job-714f8c79</v>
       </c>
       <c r="B146" t="str">
-        <v>Product Manager - Figma Weave (Tel Aviv, Israel)</v>
+        <v>Product Manager, AI Growth</v>
       </c>
       <c r="C146" t="str">
         <v>Figma</v>
@@ -9160,7 +9160,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E146" t="str">
-        <v>Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F146" t="str">
         <v>3-6 yrs</v>
@@ -9169,10 +9169,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H146" t="str">
-        <v>Tel Aviv, Israel</v>
+        <v>San Francisco, CA • New York, NY • United States</v>
       </c>
       <c r="I146" t="str">
-        <v>Tel Aviv</v>
+        <v>San Francisco</v>
       </c>
       <c r="J146" t="str">
         <v>On-site</v>
@@ -9181,7 +9181,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L146" t="str">
-        <v>https://boards.greenhouse.io/figma/jobs/5991338004</v>
+        <v>https://boards.greenhouse.io/figma/jobs/5989185004</v>
       </c>
       <c r="M146">
         <v>200</v>
@@ -9190,36 +9190,36 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O146" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P146" t="str">
         <v>Today</v>
       </c>
       <c r="Q146" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R146" t="str">
         <v>No</v>
       </c>
       <c r="S146">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>job-2ca475a2</v>
+        <v>job-6c338367</v>
       </c>
       <c r="B147" t="str">
-        <v>Product Manager II, Content Compliance</v>
+        <v>Product Manager, Developer Platform</v>
       </c>
       <c r="C147" t="str">
-        <v>Pinterest</v>
+        <v>Figma</v>
       </c>
       <c r="D147" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E147" t="str">
-        <v>Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F147" t="str">
         <v>3-6 yrs</v>
@@ -9228,51 +9228,51 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H147" t="str">
-        <v>San Francisco, CA, US; Seattle, WA, US; Remote, CA, US</v>
+        <v>San Francisco, CA • New York, NY • United States</v>
       </c>
       <c r="I147" t="str">
         <v>San Francisco</v>
       </c>
       <c r="J147" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K147" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L147" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/7901910</v>
+        <v>https://boards.greenhouse.io/figma/jobs/6100482004</v>
       </c>
       <c r="M147">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N147" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O147" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P147" t="str">
         <v>Today</v>
       </c>
       <c r="Q147" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R147" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S147">
-        <v>93</v>
+        <v>86</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>job-1e7e452c</v>
+        <v>job-106cd4ad</v>
       </c>
       <c r="B148" t="str">
-        <v>Product Manager II, Search Experience</v>
+        <v>Product Manager - Figma Weave (Tel Aviv, Israel)</v>
       </c>
       <c r="C148" t="str">
-        <v>Pinterest</v>
+        <v>Figma</v>
       </c>
       <c r="D148" t="str">
         <v>LinkedIn</v>
@@ -9287,48 +9287,48 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H148" t="str">
-        <v>San Francisco, CA, US; Remote, US</v>
+        <v>Tel Aviv, Israel</v>
       </c>
       <c r="I148" t="str">
-        <v>San Francisco</v>
+        <v>Tel Aviv</v>
       </c>
       <c r="J148" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K148" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L148" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/8042279</v>
+        <v>https://boards.greenhouse.io/figma/jobs/5991338004</v>
       </c>
       <c r="M148">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N148" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O148" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P148" t="str">
         <v>Today</v>
       </c>
       <c r="Q148" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R148" t="str">
         <v>No</v>
       </c>
       <c r="S148">
-        <v>53</v>
+        <v>71</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>job-65802650</v>
+        <v>job-2ca475a2</v>
       </c>
       <c r="B149" t="str">
-        <v>Sr. Product Manager, Core Saving Experience</v>
+        <v>Product Manager II, Content Compliance</v>
       </c>
       <c r="C149" t="str">
         <v>Pinterest</v>
@@ -9337,7 +9337,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E149" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F149" t="str">
         <v>3-6 yrs</v>
@@ -9346,7 +9346,7 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H149" t="str">
-        <v>San Francisco, CA, US; Remote, US</v>
+        <v>San Francisco, CA, US; Seattle, WA, US; Remote, CA, US</v>
       </c>
       <c r="I149" t="str">
         <v>San Francisco</v>
@@ -9358,7 +9358,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L149" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/8046820</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/7901910</v>
       </c>
       <c r="M149">
         <v>403</v>
@@ -9367,27 +9367,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O149" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P149" t="str">
         <v>Today</v>
       </c>
       <c r="Q149" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R149" t="str">
         <v>No</v>
       </c>
       <c r="S149">
-        <v>52</v>
+        <v>86</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>job-3070654d</v>
+        <v>job-1e7e452c</v>
       </c>
       <c r="B150" t="str">
-        <v>Sr. Product Manager, Search Personalization</v>
+        <v>Product Manager II, Search Experience</v>
       </c>
       <c r="C150" t="str">
         <v>Pinterest</v>
@@ -9396,7 +9396,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E150" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F150" t="str">
         <v>3-6 yrs</v>
@@ -9417,7 +9417,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L150" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/8015494</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/8042279</v>
       </c>
       <c r="M150">
         <v>403</v>
@@ -9426,7 +9426,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O150" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P150" t="str">
         <v>Today</v>
@@ -9435,18 +9435,18 @@
         <v>Yes</v>
       </c>
       <c r="R150" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S150">
-        <v>76</v>
+        <v>88</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>job-2683c45a</v>
+        <v>job-65802650</v>
       </c>
       <c r="B151" t="str">
-        <v>Sr. Product Manager, TwoTwenty</v>
+        <v>Sr. Product Manager, Core Saving Experience</v>
       </c>
       <c r="C151" t="str">
         <v>Pinterest</v>
@@ -9476,7 +9476,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L151" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/8015519</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/8046820</v>
       </c>
       <c r="M151">
         <v>403</v>
@@ -9485,7 +9485,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O151" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P151" t="str">
         <v>Today</v>
@@ -9497,15 +9497,15 @@
         <v>No</v>
       </c>
       <c r="S151">
-        <v>63</v>
+        <v>40</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>job-04d22fdc</v>
+        <v>job-3070654d</v>
       </c>
       <c r="B152" t="str">
-        <v>Staff Product Manager, Ads Measurement</v>
+        <v>Sr. Product Manager, Search Personalization</v>
       </c>
       <c r="C152" t="str">
         <v>Pinterest</v>
@@ -9517,25 +9517,25 @@
         <v>Senior Product Manager</v>
       </c>
       <c r="F152" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G152" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H152" t="str">
-        <v>New York, NY, US</v>
+        <v>San Francisco, CA, US; Remote, US</v>
       </c>
       <c r="I152" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J152" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K152" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L152" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/7683962</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/8015494</v>
       </c>
       <c r="M152">
         <v>403</v>
@@ -9544,7 +9544,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O152" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P152" t="str">
         <v>Today</v>
@@ -9556,15 +9556,15 @@
         <v>Yes</v>
       </c>
       <c r="S152">
-        <v>63</v>
+        <v>67</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>job-336a1df9</v>
+        <v>job-2683c45a</v>
       </c>
       <c r="B153" t="str">
-        <v>Staff Product Manager, Applied Science</v>
+        <v>Sr. Product Manager, TwoTwenty</v>
       </c>
       <c r="C153" t="str">
         <v>Pinterest</v>
@@ -9576,10 +9576,10 @@
         <v>Senior Product Manager</v>
       </c>
       <c r="F153" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G153" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H153" t="str">
         <v>San Francisco, CA, US; Remote, US</v>
@@ -9594,7 +9594,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L153" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/8082033</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/8015519</v>
       </c>
       <c r="M153">
         <v>403</v>
@@ -9603,7 +9603,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O153" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P153" t="str">
         <v>Today</v>
@@ -9615,15 +9615,15 @@
         <v>No</v>
       </c>
       <c r="S153">
-        <v>72</v>
+        <v>56</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>job-0f93578d</v>
+        <v>job-04d22fdc</v>
       </c>
       <c r="B154" t="str">
-        <v>Staff Product Manager, Billing</v>
+        <v>Staff Product Manager, Ads Measurement</v>
       </c>
       <c r="C154" t="str">
         <v>Pinterest</v>
@@ -9641,19 +9641,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H154" t="str">
-        <v>San Francisco, CA, US; Remote, CA, US</v>
+        <v>New York, NY, US</v>
       </c>
       <c r="I154" t="str">
-        <v>San Francisco</v>
+        <v>New York</v>
       </c>
       <c r="J154" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K154" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L154" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/7955593</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/7683962</v>
       </c>
       <c r="M154">
         <v>403</v>
@@ -9662,27 +9662,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O154" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P154" t="str">
         <v>Today</v>
       </c>
       <c r="Q154" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R154" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S154">
-        <v>48</v>
+        <v>32</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>job-7b34548d</v>
+        <v>job-336a1df9</v>
       </c>
       <c r="B155" t="str">
-        <v>Staff Product Manager, Connections</v>
+        <v>Staff Product Manager, Applied Science</v>
       </c>
       <c r="C155" t="str">
         <v>Pinterest</v>
@@ -9712,7 +9712,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L155" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/7525112</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/8082033</v>
       </c>
       <c r="M155">
         <v>403</v>
@@ -9721,7 +9721,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O155" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P155" t="str">
         <v>Today</v>
@@ -9730,18 +9730,18 @@
         <v>No</v>
       </c>
       <c r="R155" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S155">
-        <v>62</v>
+        <v>27</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>job-7e8b8408</v>
+        <v>job-0f93578d</v>
       </c>
       <c r="B156" t="str">
-        <v>Staff Product Manager, Programmatic Ads</v>
+        <v>Staff Product Manager, Billing</v>
       </c>
       <c r="C156" t="str">
         <v>Pinterest</v>
@@ -9771,7 +9771,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L156" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/7959458</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/7955593</v>
       </c>
       <c r="M156">
         <v>403</v>
@@ -9780,30 +9780,30 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O156" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P156" t="str">
         <v>Today</v>
       </c>
       <c r="Q156" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R156" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S156">
-        <v>88</v>
+        <v>72</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>job-6d240672</v>
+        <v>job-7b34548d</v>
       </c>
       <c r="B157" t="str">
-        <v>Senior Product Manager, Ads Quality</v>
+        <v>Staff Product Manager, Connections</v>
       </c>
       <c r="C157" t="str">
-        <v>Instacart</v>
+        <v>Pinterest</v>
       </c>
       <c r="D157" t="str">
         <v>LinkedIn</v>
@@ -9818,10 +9818,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H157" t="str">
-        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
+        <v>San Francisco, CA, US; Remote, US</v>
       </c>
       <c r="I157" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J157" t="str">
         <v>Remote</v>
@@ -9830,16 +9830,16 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L157" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8077512</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/7525112</v>
       </c>
       <c r="M157">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N157" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O157" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P157" t="str">
         <v>Today</v>
@@ -9851,18 +9851,18 @@
         <v>No</v>
       </c>
       <c r="S157">
-        <v>47</v>
+        <v>65</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>job-2be59ce2</v>
+        <v>job-7e8b8408</v>
       </c>
       <c r="B158" t="str">
-        <v>Senior Product Manager, Advertiser Experience</v>
+        <v>Staff Product Manager, Programmatic Ads</v>
       </c>
       <c r="C158" t="str">
-        <v>Instacart</v>
+        <v>Pinterest</v>
       </c>
       <c r="D158" t="str">
         <v>LinkedIn</v>
@@ -9877,10 +9877,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H158" t="str">
-        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
+        <v>San Francisco, CA, US; Remote, CA, US</v>
       </c>
       <c r="I158" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J158" t="str">
         <v>Remote</v>
@@ -9889,36 +9889,36 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L158" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8120471</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/7959458</v>
       </c>
       <c r="M158">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N158" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O158" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P158" t="str">
         <v>Today</v>
       </c>
       <c r="Q158" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R158" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S158">
-        <v>34</v>
+        <v>49</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>job-6ddb2cbc</v>
+        <v>job-6d240672</v>
       </c>
       <c r="B159" t="str">
-        <v>Senior Product Manager, Catalog</v>
+        <v>Senior Product Manager, Ads Quality</v>
       </c>
       <c r="C159" t="str">
         <v>Instacart</v>
@@ -9936,7 +9936,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H159" t="str">
-        <v>United States - Remote</v>
+        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
       </c>
       <c r="I159" t="str">
         <v>Remote</v>
@@ -9948,7 +9948,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L159" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8143270</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8077512</v>
       </c>
       <c r="M159">
         <v>200</v>
@@ -9957,27 +9957,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O159" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P159" t="str">
         <v>Today</v>
       </c>
       <c r="Q159" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R159" t="str">
         <v>No</v>
       </c>
       <c r="S159">
-        <v>40</v>
+        <v>78</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>job-4a79ebe7</v>
+        <v>job-2be59ce2</v>
       </c>
       <c r="B160" t="str">
-        <v>Senior Product Manager, Discounting Platform</v>
+        <v>Senior Product Manager, Advertiser Experience</v>
       </c>
       <c r="C160" t="str">
         <v>Instacart</v>
@@ -10007,7 +10007,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L160" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8175791</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8120469</v>
       </c>
       <c r="M160">
         <v>200</v>
@@ -10016,7 +10016,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O160" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P160" t="str">
         <v>Today</v>
@@ -10028,15 +10028,15 @@
         <v>No</v>
       </c>
       <c r="S160">
-        <v>92</v>
+        <v>37</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>job-20f6f1d2</v>
+        <v>job-6ddb2cbc</v>
       </c>
       <c r="B161" t="str">
-        <v>Senior Product Manager, In-Store Tasks</v>
+        <v>Senior Product Manager, Catalog</v>
       </c>
       <c r="C161" t="str">
         <v>Instacart</v>
@@ -10066,7 +10066,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L161" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/7963724</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8143270</v>
       </c>
       <c r="M161">
         <v>200</v>
@@ -10075,7 +10075,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O161" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P161" t="str">
         <v>Today</v>
@@ -10087,15 +10087,15 @@
         <v>No</v>
       </c>
       <c r="S161">
-        <v>54</v>
+        <v>40</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>job-2319ed86</v>
+        <v>job-20f6f1d2</v>
       </c>
       <c r="B162" t="str">
-        <v>Senior Product Manager, Retailer Platform</v>
+        <v>Senior Product Manager, In-Store Tasks</v>
       </c>
       <c r="C162" t="str">
         <v>Instacart</v>
@@ -10125,7 +10125,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L162" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8014062</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/7963726</v>
       </c>
       <c r="M162">
         <v>200</v>
@@ -10134,7 +10134,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O162" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P162" t="str">
         <v>Today</v>
@@ -10143,48 +10143,48 @@
         <v>No</v>
       </c>
       <c r="R162" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S162">
-        <v>73</v>
+        <v>61</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>job-307baa4c</v>
+        <v>job-2319ed86</v>
       </c>
       <c r="B163" t="str">
-        <v>Product Manager II</v>
+        <v>Senior Product Manager, Retailer Platform</v>
       </c>
       <c r="C163" t="str">
-        <v>Razorpay</v>
+        <v>Instacart</v>
       </c>
       <c r="D163" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E163" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F163" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G163" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H163" t="str">
-        <v>Bengaluru</v>
+        <v>United States - Remote</v>
       </c>
       <c r="I163" t="str">
-        <v>Bengaluru</v>
+        <v>Remote</v>
       </c>
       <c r="J163" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K163" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L163" t="str">
-        <v>https://boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4729519005</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8014060</v>
       </c>
       <c r="M163">
         <v>200</v>
@@ -10193,7 +10193,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O163" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P163" t="str">
         <v>Today</v>
@@ -10202,18 +10202,18 @@
         <v>No</v>
       </c>
       <c r="R163" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S163">
-        <v>78</v>
+        <v>67</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>job-6d0cde89</v>
+        <v>job-307baa4c</v>
       </c>
       <c r="B164" t="str">
-        <v>Product Manager II - Ads</v>
+        <v>Product Manager II</v>
       </c>
       <c r="C164" t="str">
         <v>Razorpay</v>
@@ -10243,7 +10243,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L164" t="str">
-        <v>https://boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4729533005</v>
+        <v>https://boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4715389005</v>
       </c>
       <c r="M164">
         <v>200</v>
@@ -10252,7 +10252,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O164" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P164" t="str">
         <v>Today</v>
@@ -10264,24 +10264,24 @@
         <v>No</v>
       </c>
       <c r="S164">
-        <v>29</v>
+        <v>62</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>job-1c3166e2</v>
+        <v>job-6d0cde89</v>
       </c>
       <c r="B165" t="str">
-        <v>Product Manager, API Agents</v>
+        <v>Product Manager II - Ads</v>
       </c>
       <c r="C165" t="str">
-        <v>OpenAI</v>
+        <v>Razorpay</v>
       </c>
       <c r="D165" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E165" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Product Manager</v>
       </c>
       <c r="F165" t="str">
         <v>3-6 yrs</v>
@@ -10290,19 +10290,19 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H165" t="str">
-        <v>San Francisco</v>
+        <v>Bengaluru</v>
       </c>
       <c r="I165" t="str">
-        <v>San Francisco</v>
+        <v>Bengaluru</v>
       </c>
       <c r="J165" t="str">
         <v>On-site</v>
       </c>
       <c r="K165" t="str">
-        <v>$160k - $240k USD + Equity</v>
+        <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L165" t="str">
-        <v>https://jobs.ashbyhq.com/openai/fc38c6bf-5330-435c-99b6-1bcf1f5829a8</v>
+        <v>https://boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4729533005</v>
       </c>
       <c r="M165">
         <v>200</v>
@@ -10311,27 +10311,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O165" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P165" t="str">
         <v>Today</v>
       </c>
       <c r="Q165" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R165" t="str">
         <v>Yes</v>
       </c>
       <c r="S165">
-        <v>71</v>
+        <v>80</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>job-6d2b24fc</v>
+        <v>job-1c3166e2</v>
       </c>
       <c r="B166" t="str">
-        <v>Product Manager, Sensitive Deployments</v>
+        <v>Product Manager, API Agents</v>
       </c>
       <c r="C166" t="str">
         <v>OpenAI</v>
@@ -10340,7 +10340,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E166" t="str">
-        <v>Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F166" t="str">
         <v>3-6 yrs</v>
@@ -10361,7 +10361,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L166" t="str">
-        <v>https://jobs.ashbyhq.com/openai/05a8cae8-81bd-4f7b-bc48-41ef1bd67e5d</v>
+        <v>https://jobs.ashbyhq.com/openai/fc38c6bf-5330-435c-99b6-1bcf1f5829a8</v>
       </c>
       <c r="M166">
         <v>200</v>
@@ -10370,7 +10370,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O166" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P166" t="str">
         <v>Today</v>
@@ -10382,15 +10382,15 @@
         <v>Yes</v>
       </c>
       <c r="S166">
-        <v>119</v>
+        <v>67</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>job-184a9e13</v>
+        <v>job-6d2b24fc</v>
       </c>
       <c r="B167" t="str">
-        <v>Product Manager, API Infrastructure</v>
+        <v>Product Manager, Sensitive Deployments</v>
       </c>
       <c r="C167" t="str">
         <v>OpenAI</v>
@@ -10399,7 +10399,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E167" t="str">
-        <v>Technical Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F167" t="str">
         <v>3-6 yrs</v>
@@ -10420,7 +10420,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L167" t="str">
-        <v>https://jobs.ashbyhq.com/openai/7ffa2a14-fa9c-46cb-a30a-1f7a35ae904a</v>
+        <v>https://jobs.ashbyhq.com/openai/05a8cae8-81bd-4f7b-bc48-41ef1bd67e5d</v>
       </c>
       <c r="M167">
         <v>200</v>
@@ -10429,7 +10429,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O167" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P167" t="str">
         <v>Today</v>
@@ -10441,15 +10441,15 @@
         <v>Yes</v>
       </c>
       <c r="S167">
-        <v>75</v>
+        <v>91</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>job-61ec6778</v>
+        <v>job-184a9e13</v>
       </c>
       <c r="B168" t="str">
-        <v>Product Manager, Safety Measurement</v>
+        <v>Product Manager, API Infrastructure</v>
       </c>
       <c r="C168" t="str">
         <v>OpenAI</v>
@@ -10458,7 +10458,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E168" t="str">
-        <v>Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F168" t="str">
         <v>3-6 yrs</v>
@@ -10479,7 +10479,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L168" t="str">
-        <v>https://jobs.ashbyhq.com/openai/fbc7ebaf-3a26-406d-9ff6-f166f3e246a2</v>
+        <v>https://jobs.ashbyhq.com/openai/7ffa2a14-fa9c-46cb-a30a-1f7a35ae904a</v>
       </c>
       <c r="M168">
         <v>200</v>
@@ -10488,7 +10488,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O168" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P168" t="str">
         <v>Today</v>
@@ -10497,18 +10497,18 @@
         <v>Yes</v>
       </c>
       <c r="R168" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S168">
-        <v>105</v>
+        <v>82</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>job-32d0b9c4</v>
+        <v>job-61ec6778</v>
       </c>
       <c r="B169" t="str">
-        <v>Product Manager, Financial Engineering</v>
+        <v>Product Manager, Safety Measurement</v>
       </c>
       <c r="C169" t="str">
         <v>OpenAI</v>
@@ -10538,7 +10538,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L169" t="str">
-        <v>https://jobs.ashbyhq.com/openai/0f4da2b4-df8a-4560-809d-d0a6ac1ad9bc</v>
+        <v>https://jobs.ashbyhq.com/openai/fbc7ebaf-3a26-406d-9ff6-f166f3e246a2</v>
       </c>
       <c r="M169">
         <v>200</v>
@@ -10547,7 +10547,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O169" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P169" t="str">
         <v>Today</v>
@@ -10556,18 +10556,18 @@
         <v>Yes</v>
       </c>
       <c r="R169" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S169">
-        <v>103</v>
+        <v>46</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>job-2d8a3d8e</v>
+        <v>job-32d0b9c4</v>
       </c>
       <c r="B170" t="str">
-        <v>Product Manager, Shopping</v>
+        <v>Product Manager, Financial Engineering</v>
       </c>
       <c r="C170" t="str">
         <v>OpenAI</v>
@@ -10597,7 +10597,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L170" t="str">
-        <v>https://jobs.ashbyhq.com/openai/df8a1d73-58b9-4571-86f5-da9a12155fbb</v>
+        <v>https://jobs.ashbyhq.com/openai/0f4da2b4-df8a-4560-809d-d0a6ac1ad9bc</v>
       </c>
       <c r="M170">
         <v>200</v>
@@ -10606,7 +10606,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O170" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P170" t="str">
         <v>Today</v>
@@ -10618,15 +10618,15 @@
         <v>Yes</v>
       </c>
       <c r="S170">
-        <v>106</v>
+        <v>115</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>job-675130d5</v>
+        <v>job-2d8a3d8e</v>
       </c>
       <c r="B171" t="str">
-        <v>Product Manager, Core Models</v>
+        <v>Product Manager, Shopping</v>
       </c>
       <c r="C171" t="str">
         <v>OpenAI</v>
@@ -10635,7 +10635,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E171" t="str">
-        <v>Technical Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F171" t="str">
         <v>3-6 yrs</v>
@@ -10656,7 +10656,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L171" t="str">
-        <v>https://jobs.ashbyhq.com/openai/33b8effb-b048-4934-a279-87fff192a330</v>
+        <v>https://jobs.ashbyhq.com/openai/df8a1d73-58b9-4571-86f5-da9a12155fbb</v>
       </c>
       <c r="M171">
         <v>200</v>
@@ -10665,7 +10665,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O171" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P171" t="str">
         <v>Today</v>
@@ -10674,18 +10674,18 @@
         <v>Yes</v>
       </c>
       <c r="R171" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S171">
-        <v>78</v>
+        <v>105</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>job-6dc78859</v>
+        <v>job-675130d5</v>
       </c>
       <c r="B172" t="str">
-        <v>Product Manager, Legal</v>
+        <v>Product Manager, Core Models</v>
       </c>
       <c r="C172" t="str">
         <v>OpenAI</v>
@@ -10694,7 +10694,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E172" t="str">
-        <v>Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F172" t="str">
         <v>3-6 yrs</v>
@@ -10715,7 +10715,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L172" t="str">
-        <v>https://jobs.ashbyhq.com/openai/83b3ef17-5211-403d-b763-850e1c60faa0</v>
+        <v>https://jobs.ashbyhq.com/openai/33b8effb-b048-4934-a279-87fff192a330</v>
       </c>
       <c r="M172">
         <v>200</v>
@@ -10724,7 +10724,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O172" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P172" t="str">
         <v>Today</v>
@@ -10736,15 +10736,15 @@
         <v>No</v>
       </c>
       <c r="S172">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>job-032480cd</v>
+        <v>job-6dc78859</v>
       </c>
       <c r="B173" t="str">
-        <v>Product Manager, Youth</v>
+        <v>Product Manager, Legal</v>
       </c>
       <c r="C173" t="str">
         <v>OpenAI</v>
@@ -10774,7 +10774,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L173" t="str">
-        <v>https://jobs.ashbyhq.com/openai/cc0d0d86-eb9d-44a0-a6a4-42bbb6066b4b</v>
+        <v>https://jobs.ashbyhq.com/openai/83b3ef17-5211-403d-b763-850e1c60faa0</v>
       </c>
       <c r="M173">
         <v>200</v>
@@ -10783,7 +10783,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O173" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P173" t="str">
         <v>Today</v>
@@ -10792,18 +10792,18 @@
         <v>Yes</v>
       </c>
       <c r="R173" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S173">
-        <v>105</v>
+        <v>83</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>job-50e54898</v>
+        <v>job-032480cd</v>
       </c>
       <c r="B174" t="str">
-        <v>Product Manager, Learning</v>
+        <v>Product Manager, Youth</v>
       </c>
       <c r="C174" t="str">
         <v>OpenAI</v>
@@ -10833,7 +10833,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L174" t="str">
-        <v>https://jobs.ashbyhq.com/openai/5953fed7-1466-4e90-94c9-43716a55e032</v>
+        <v>https://jobs.ashbyhq.com/openai/cc0d0d86-eb9d-44a0-a6a4-42bbb6066b4b</v>
       </c>
       <c r="M174">
         <v>200</v>
@@ -10842,7 +10842,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O174" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P174" t="str">
         <v>Today</v>
@@ -10854,15 +10854,15 @@
         <v>Yes</v>
       </c>
       <c r="S174">
-        <v>117</v>
+        <v>87</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>job-0df96522</v>
+        <v>job-50e54898</v>
       </c>
       <c r="B175" t="str">
-        <v>Product Manager, Multimodal Safety</v>
+        <v>Product Manager, Learning</v>
       </c>
       <c r="C175" t="str">
         <v>OpenAI</v>
@@ -10892,7 +10892,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L175" t="str">
-        <v>https://jobs.ashbyhq.com/openai/70d5259a-f18c-4595-bf52-ec03eeeeac4c</v>
+        <v>https://jobs.ashbyhq.com/openai/5953fed7-1466-4e90-94c9-43716a55e032</v>
       </c>
       <c r="M175">
         <v>200</v>
@@ -10901,7 +10901,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O175" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P175" t="str">
         <v>Today</v>
@@ -10910,24 +10910,24 @@
         <v>Yes</v>
       </c>
       <c r="R175" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S175">
-        <v>61</v>
+        <v>83</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>job-5db12f92</v>
+        <v>job-0df96522</v>
       </c>
       <c r="B176" t="str">
-        <v>Product Manager (Builder)</v>
+        <v>Product Manager, Multimodal Safety</v>
       </c>
       <c r="C176" t="str">
-        <v>Perplexity</v>
+        <v>OpenAI</v>
       </c>
       <c r="D176" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E176" t="str">
         <v>Product Manager</v>
@@ -10951,7 +10951,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L176" t="str">
-        <v>https://jobs.ashbyhq.com/perplexity/f25e190e-0508-4707-b575-fcaed358dc13</v>
+        <v>https://jobs.ashbyhq.com/openai/70d5259a-f18c-4595-bf52-ec03eeeeac4c</v>
       </c>
       <c r="M176">
         <v>200</v>
@@ -10960,7 +10960,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O176" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P176" t="str">
         <v>Today</v>
@@ -10969,18 +10969,18 @@
         <v>Yes</v>
       </c>
       <c r="R176" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S176">
-        <v>71</v>
+        <v>77</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>job-1fe57ea5</v>
+        <v>job-5db12f92</v>
       </c>
       <c r="B177" t="str">
-        <v>Member of Technical Staff (TPM, Inference)</v>
+        <v>Product Manager (Builder)</v>
       </c>
       <c r="C177" t="str">
         <v>Perplexity</v>
@@ -10989,13 +10989,13 @@
         <v>Wellfound</v>
       </c>
       <c r="E177" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F177" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G177" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H177" t="str">
         <v>San Francisco</v>
@@ -11010,7 +11010,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L177" t="str">
-        <v>https://jobs.ashbyhq.com/perplexity/0c5d5a82-bfed-4786-b411-79073979af07</v>
+        <v>https://jobs.ashbyhq.com/perplexity/f25e190e-0508-4707-b575-fcaed358dc13</v>
       </c>
       <c r="M177">
         <v>200</v>
@@ -11019,7 +11019,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O177" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P177" t="str">
         <v>Today</v>
@@ -11028,18 +11028,18 @@
         <v>Yes</v>
       </c>
       <c r="R177" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S177">
-        <v>55</v>
+        <v>84</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>job-12403072</v>
+        <v>job-1fe57ea5</v>
       </c>
       <c r="B178" t="str">
-        <v>Product Manager, Mobile Apps</v>
+        <v>Member of Technical Staff (TPM, Inference)</v>
       </c>
       <c r="C178" t="str">
         <v>Perplexity</v>
@@ -11048,13 +11048,13 @@
         <v>Wellfound</v>
       </c>
       <c r="E178" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F178" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G178" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H178" t="str">
         <v>San Francisco</v>
@@ -11069,7 +11069,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L178" t="str">
-        <v>https://jobs.ashbyhq.com/perplexity/3c9c051f-e6ca-4a70-9abf-1f640e154ee1</v>
+        <v>https://jobs.ashbyhq.com/perplexity/0c5d5a82-bfed-4786-b411-79073979af07</v>
       </c>
       <c r="M178">
         <v>200</v>
@@ -11078,7 +11078,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O178" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P178" t="str">
         <v>Today</v>
@@ -11090,15 +11090,15 @@
         <v>Yes</v>
       </c>
       <c r="S178">
-        <v>46</v>
+        <v>55</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>job-10379173</v>
+        <v>job-12403072</v>
       </c>
       <c r="B179" t="str">
-        <v>Product Manager, Core Experience</v>
+        <v>Product Manager, Mobile Apps</v>
       </c>
       <c r="C179" t="str">
         <v>Perplexity</v>
@@ -11107,7 +11107,7 @@
         <v>Wellfound</v>
       </c>
       <c r="E179" t="str">
-        <v>Technical Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F179" t="str">
         <v>3-6 yrs</v>
@@ -11128,7 +11128,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L179" t="str">
-        <v>https://jobs.ashbyhq.com/perplexity/6f3c5131-2efa-400c-8248-44203a4dbfbb</v>
+        <v>https://jobs.ashbyhq.com/perplexity/3c9c051f-e6ca-4a70-9abf-1f640e154ee1</v>
       </c>
       <c r="M179">
         <v>200</v>
@@ -11137,7 +11137,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O179" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P179" t="str">
         <v>Today</v>
@@ -11146,18 +11146,18 @@
         <v>Yes</v>
       </c>
       <c r="R179" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S179">
-        <v>104</v>
+        <v>75</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>job-247da510</v>
+        <v>job-10379173</v>
       </c>
       <c r="B180" t="str">
-        <v>Product Manager, AI Capabilities</v>
+        <v>Product Manager, Core Experience</v>
       </c>
       <c r="C180" t="str">
         <v>Perplexity</v>
@@ -11166,7 +11166,7 @@
         <v>Wellfound</v>
       </c>
       <c r="E180" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F180" t="str">
         <v>3-6 yrs</v>
@@ -11187,7 +11187,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L180" t="str">
-        <v>https://jobs.ashbyhq.com/perplexity/7f880194-7276-4b46-8a50-58b48da8882e</v>
+        <v>https://jobs.ashbyhq.com/perplexity/6f3c5131-2efa-400c-8248-44203a4dbfbb</v>
       </c>
       <c r="M180">
         <v>200</v>
@@ -11196,7 +11196,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O180" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P180" t="str">
         <v>Today</v>
@@ -11208,15 +11208,15 @@
         <v>No</v>
       </c>
       <c r="S180">
-        <v>86</v>
+        <v>66</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>job-757a314d</v>
+        <v>job-247da510</v>
       </c>
       <c r="B181" t="str">
-        <v>Product Manager, Growth</v>
+        <v>Product Manager, AI Capabilities</v>
       </c>
       <c r="C181" t="str">
         <v>Perplexity</v>
@@ -11234,10 +11234,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H181" t="str">
-        <v>New York City</v>
+        <v>San Francisco</v>
       </c>
       <c r="I181" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J181" t="str">
         <v>On-site</v>
@@ -11246,7 +11246,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L181" t="str">
-        <v>https://jobs.ashbyhq.com/perplexity/fa088d92-b08b-43f7-9232-275b0ae08827</v>
+        <v>https://jobs.ashbyhq.com/perplexity/7f880194-7276-4b46-8a50-58b48da8882e</v>
       </c>
       <c r="M181">
         <v>200</v>
@@ -11255,7 +11255,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O181" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P181" t="str">
         <v>Today</v>
@@ -11267,15 +11267,15 @@
         <v>Yes</v>
       </c>
       <c r="S181">
-        <v>110</v>
+        <v>57</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>job-376e5ff5</v>
+        <v>job-757a314d</v>
       </c>
       <c r="B182" t="str">
-        <v>Product Manager, SMB Growth</v>
+        <v>Product Manager, Growth</v>
       </c>
       <c r="C182" t="str">
         <v>Perplexity</v>
@@ -11305,7 +11305,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L182" t="str">
-        <v>https://jobs.ashbyhq.com/perplexity/182ab2ec-6fb1-409b-a2dc-63c7832b0a13</v>
+        <v>https://jobs.ashbyhq.com/perplexity/fa088d92-b08b-43f7-9232-275b0ae08827</v>
       </c>
       <c r="M182">
         <v>200</v>
@@ -11314,7 +11314,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O182" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P182" t="str">
         <v>Today</v>
@@ -11323,27 +11323,27 @@
         <v>Yes</v>
       </c>
       <c r="R182" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S182">
-        <v>44</v>
+        <v>98</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>job-6fff938e</v>
+        <v>job-376e5ff5</v>
       </c>
       <c r="B183" t="str">
-        <v>Product Manager - Marketplace</v>
+        <v>Product Manager, SMB Growth</v>
       </c>
       <c r="C183" t="str">
-        <v>Supabase</v>
+        <v>Perplexity</v>
       </c>
       <c r="D183" t="str">
         <v>Wellfound</v>
       </c>
       <c r="E183" t="str">
-        <v>Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F183" t="str">
         <v>3-6 yrs</v>
@@ -11352,19 +11352,19 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H183" t="str">
-        <v>Remote, Global</v>
+        <v>New York City</v>
       </c>
       <c r="I183" t="str">
-        <v>Remote</v>
+        <v>New York</v>
       </c>
       <c r="J183" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K183" t="str">
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L183" t="str">
-        <v>https://jobs.ashbyhq.com/supabase/23c9ce7e-6b7b-4316-8f00-8f318e902441</v>
+        <v>https://jobs.ashbyhq.com/perplexity/182ab2ec-6fb1-409b-a2dc-63c7832b0a13</v>
       </c>
       <c r="M183">
         <v>200</v>
@@ -11373,7 +11373,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O183" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P183" t="str">
         <v>Today</v>
@@ -11385,15 +11385,15 @@
         <v>Yes</v>
       </c>
       <c r="S183">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>job-49f97312</v>
+        <v>job-6fff938e</v>
       </c>
       <c r="B184" t="str">
-        <v>Product Manager - Security &amp; Trust (EMEA/AMER)</v>
+        <v>Product Manager - Marketplace</v>
       </c>
       <c r="C184" t="str">
         <v>Supabase</v>
@@ -11423,7 +11423,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L184" t="str">
-        <v>https://jobs.ashbyhq.com/supabase/b8010a28-109c-46a9-b8b7-c7f9b24077fa</v>
+        <v>https://jobs.ashbyhq.com/supabase/23c9ce7e-6b7b-4316-8f00-8f318e902441</v>
       </c>
       <c r="M184">
         <v>200</v>
@@ -11432,7 +11432,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O184" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P184" t="str">
         <v>Today</v>
@@ -11441,18 +11441,18 @@
         <v>Yes</v>
       </c>
       <c r="R184" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S184">
-        <v>67</v>
+        <v>102</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>job-5ee8bae7</v>
+        <v>job-49f97312</v>
       </c>
       <c r="B185" t="str">
-        <v>Product Manager - Branching</v>
+        <v>Product Manager - Security &amp; Trust (EMEA/AMER)</v>
       </c>
       <c r="C185" t="str">
         <v>Supabase</v>
@@ -11482,7 +11482,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L185" t="str">
-        <v>https://jobs.ashbyhq.com/supabase/9773ea1b-e25b-437c-bdbd-3fce0c69101e</v>
+        <v>https://jobs.ashbyhq.com/supabase/b8010a28-109c-46a9-b8b7-c7f9b24077fa</v>
       </c>
       <c r="M185">
         <v>200</v>
@@ -11491,7 +11491,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O185" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P185" t="str">
         <v>Today</v>
@@ -11500,18 +11500,18 @@
         <v>Yes</v>
       </c>
       <c r="R185" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S185">
-        <v>55</v>
+        <v>78</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>job-064fa6b5</v>
+        <v>job-5ee8bae7</v>
       </c>
       <c r="B186" t="str">
-        <v>Product Manager - Strategic Partner Integrations (Bay Area based)</v>
+        <v>Product Manager - Branching</v>
       </c>
       <c r="C186" t="str">
         <v>Supabase</v>
@@ -11529,10 +11529,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H186" t="str">
-        <v>Remote, Bay Area, CA</v>
+        <v>Remote, Global</v>
       </c>
       <c r="I186" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J186" t="str">
         <v>Remote</v>
@@ -11541,7 +11541,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L186" t="str">
-        <v>https://jobs.ashbyhq.com/supabase/68a397e7-8a1a-4566-ae41-e8c61dd6ed93</v>
+        <v>https://jobs.ashbyhq.com/supabase/9773ea1b-e25b-437c-bdbd-3fce0c69101e</v>
       </c>
       <c r="M186">
         <v>200</v>
@@ -11550,7 +11550,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O186" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P186" t="str">
         <v>Today</v>
@@ -11562,24 +11562,24 @@
         <v>No</v>
       </c>
       <c r="S186">
-        <v>62</v>
+        <v>83</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>job-7da017c6</v>
+        <v>job-064fa6b5</v>
       </c>
       <c r="B187" t="str">
-        <v>Product Manager | Vendor Intelligence &amp; Marketplace</v>
+        <v>Product Manager - Strategic Partner Integrations (Bay Area based)</v>
       </c>
       <c r="C187" t="str">
-        <v>Ramp</v>
+        <v>Supabase</v>
       </c>
       <c r="D187" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E187" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Product Manager</v>
       </c>
       <c r="F187" t="str">
         <v>3-6 yrs</v>
@@ -11588,19 +11588,19 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H187" t="str">
-        <v>New York, NY (HQ)</v>
+        <v>Remote, Bay Area, CA</v>
       </c>
       <c r="I187" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J187" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K187" t="str">
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L187" t="str">
-        <v>https://jobs.ashbyhq.com/ramp/cf3516f6-4d6b-4872-831f-c8ef4a3078ee</v>
+        <v>https://jobs.ashbyhq.com/supabase/68a397e7-8a1a-4566-ae41-e8c61dd6ed93</v>
       </c>
       <c r="M187">
         <v>200</v>
@@ -11609,7 +11609,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O187" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P187" t="str">
         <v>Today</v>
@@ -11621,15 +11621,15 @@
         <v>Yes</v>
       </c>
       <c r="S187">
-        <v>85</v>
+        <v>119</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>job-338455bd</v>
+        <v>job-7da017c6</v>
       </c>
       <c r="B188" t="str">
-        <v>Product Manager | Tax</v>
+        <v>Product Manager | Vendor Intelligence &amp; Marketplace</v>
       </c>
       <c r="C188" t="str">
         <v>Ramp</v>
@@ -11638,7 +11638,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E188" t="str">
-        <v>Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F188" t="str">
         <v>3-6 yrs</v>
@@ -11659,7 +11659,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L188" t="str">
-        <v>https://jobs.ashbyhq.com/ramp/881f9f7d-9ec5-4b69-b50d-a67000264ca8</v>
+        <v>https://jobs.ashbyhq.com/ramp/cf3516f6-4d6b-4872-831f-c8ef4a3078ee</v>
       </c>
       <c r="M188">
         <v>200</v>
@@ -11668,7 +11668,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O188" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P188" t="str">
         <v>Today</v>
@@ -11680,15 +11680,15 @@
         <v>Yes</v>
       </c>
       <c r="S188">
-        <v>112</v>
+        <v>77</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>job-6744eb00</v>
+        <v>job-338455bd</v>
       </c>
       <c r="B189" t="str">
-        <v>Product Manager | International</v>
+        <v>Product Manager | Tax</v>
       </c>
       <c r="C189" t="str">
         <v>Ramp</v>
@@ -11700,10 +11700,10 @@
         <v>Product Manager</v>
       </c>
       <c r="F189" t="str">
-        <v>1-3 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G189" t="str">
-        <v>0-2 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H189" t="str">
         <v>New York, NY (HQ)</v>
@@ -11718,7 +11718,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L189" t="str">
-        <v>https://jobs.ashbyhq.com/ramp/8baec095-2235-41ab-ab64-9abc57823b4b</v>
+        <v>https://jobs.ashbyhq.com/ramp/881f9f7d-9ec5-4b69-b50d-a67000264ca8</v>
       </c>
       <c r="M189">
         <v>200</v>
@@ -11727,7 +11727,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O189" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P189" t="str">
         <v>Today</v>
@@ -11736,39 +11736,39 @@
         <v>Yes</v>
       </c>
       <c r="R189" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S189">
-        <v>115</v>
+        <v>75</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>job-497b065e</v>
+        <v>job-6744eb00</v>
       </c>
       <c r="B190" t="str">
-        <v>Senior Product Manager, Mobile</v>
+        <v>Product Manager | International</v>
       </c>
       <c r="C190" t="str">
-        <v>Sentry</v>
+        <v>Ramp</v>
       </c>
       <c r="D190" t="str">
-        <v>Indeed</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E190" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F190" t="str">
-        <v>5-8 yrs</v>
+        <v>1-3 yrs</v>
       </c>
       <c r="G190" t="str">
-        <v>5-8 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H190" t="str">
-        <v>Vienna, Austria</v>
+        <v>New York, NY (HQ)</v>
       </c>
       <c r="I190" t="str">
-        <v>Vienna</v>
+        <v>New York</v>
       </c>
       <c r="J190" t="str">
         <v>On-site</v>
@@ -11777,7 +11777,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L190" t="str">
-        <v>https://jobs.ashbyhq.com/sentry/6a973e19-6736-4973-8a87-043fcbcd553e</v>
+        <v>https://jobs.ashbyhq.com/ramp/8baec095-2235-41ab-ab64-9abc57823b4b</v>
       </c>
       <c r="M190">
         <v>200</v>
@@ -11786,7 +11786,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O190" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P190" t="str">
         <v>Today</v>
@@ -11798,36 +11798,36 @@
         <v>No</v>
       </c>
       <c r="S190">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>job-33169045</v>
+        <v>job-497b065e</v>
       </c>
       <c r="B191" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager, Mobile</v>
       </c>
       <c r="C191" t="str">
-        <v>Linear</v>
+        <v>Sentry</v>
       </c>
       <c r="D191" t="str">
-        <v>Wellfound</v>
+        <v>Indeed</v>
       </c>
       <c r="E191" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F191" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G191" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H191" t="str">
-        <v>North America</v>
+        <v>Vienna, Austria</v>
       </c>
       <c r="I191" t="str">
-        <v>North America</v>
+        <v>Vienna</v>
       </c>
       <c r="J191" t="str">
         <v>On-site</v>
@@ -11836,7 +11836,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L191" t="str">
-        <v>https://jobs.ashbyhq.com/linear/b7669c4b-eeca-421d-ba9a-d90203f6fcb2</v>
+        <v>https://jobs.ashbyhq.com/sentry/6a973e19-6736-4973-8a87-043fcbcd553e</v>
       </c>
       <c r="M191">
         <v>200</v>
@@ -11845,7 +11845,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O191" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P191" t="str">
         <v>Today</v>
@@ -11854,48 +11854,48 @@
         <v>Yes</v>
       </c>
       <c r="R191" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S191">
-        <v>108</v>
+        <v>78</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>job-61f86f2b</v>
+        <v>job-33169045</v>
       </c>
       <c r="B192" t="str">
-        <v>Product Manager - Customer Service Platform</v>
+        <v>Product Manager</v>
       </c>
       <c r="C192" t="str">
-        <v>Spotify</v>
+        <v>Linear</v>
       </c>
       <c r="D192" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E192" t="str">
-        <v>Technical Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F192" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G192" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H192" t="str">
-        <v>London</v>
+        <v>North America</v>
       </c>
       <c r="I192" t="str">
-        <v>London</v>
+        <v>North America</v>
       </c>
       <c r="J192" t="str">
         <v>On-site</v>
       </c>
       <c r="K192" t="str">
-        <v>$150k - $220k USD + RSUs</v>
+        <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L192" t="str">
-        <v>https://jobs.lever.co/spotify/7f0a8faa-f4f5-4db9-9f51-4101d6a29b34</v>
+        <v>https://jobs.ashbyhq.com/linear/b7669c4b-eeca-421d-ba9a-d90203f6fcb2</v>
       </c>
       <c r="M192">
         <v>200</v>
@@ -11904,7 +11904,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O192" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P192" t="str">
         <v>Today</v>
@@ -11913,18 +11913,18 @@
         <v>Yes</v>
       </c>
       <c r="R192" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S192">
-        <v>42</v>
+        <v>63</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>job-1a230b4c</v>
+        <v>job-61f86f2b</v>
       </c>
       <c r="B193" t="str">
-        <v>Product Manager - Data Platform</v>
+        <v>Product Manager - Customer Service Platform</v>
       </c>
       <c r="C193" t="str">
         <v>Spotify</v>
@@ -11942,10 +11942,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H193" t="str">
-        <v>Toronto</v>
+        <v>London</v>
       </c>
       <c r="I193" t="str">
-        <v>Toronto</v>
+        <v>London</v>
       </c>
       <c r="J193" t="str">
         <v>On-site</v>
@@ -11954,7 +11954,7 @@
         <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L193" t="str">
-        <v>https://jobs.lever.co/spotify/03437e2a-2d5e-4593-9e97-11271014932e</v>
+        <v>https://jobs.lever.co/spotify/7f0a8faa-f4f5-4db9-9f51-4101d6a29b34</v>
       </c>
       <c r="M193">
         <v>200</v>
@@ -11963,7 +11963,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O193" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P193" t="str">
         <v>Today</v>
@@ -11975,15 +11975,15 @@
         <v>No</v>
       </c>
       <c r="S193">
-        <v>49</v>
+        <v>59</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>job-1ba340a4</v>
+        <v>job-1a230b4c</v>
       </c>
       <c r="B194" t="str">
-        <v>Senior Product Manager - Audiobooks Format Foundations</v>
+        <v>Product Manager - Data Platform</v>
       </c>
       <c r="C194" t="str">
         <v>Spotify</v>
@@ -11992,7 +11992,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E194" t="str">
-        <v>Senior Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F194" t="str">
         <v>5-8 yrs</v>
@@ -12001,10 +12001,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H194" t="str">
-        <v>London</v>
+        <v>Toronto</v>
       </c>
       <c r="I194" t="str">
-        <v>London</v>
+        <v>Toronto</v>
       </c>
       <c r="J194" t="str">
         <v>On-site</v>
@@ -12013,7 +12013,7 @@
         <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L194" t="str">
-        <v>https://jobs.lever.co/spotify/e7b01c1e-4246-4f31-83ea-9219c8b22c83</v>
+        <v>https://jobs.lever.co/spotify/03437e2a-2d5e-4593-9e97-11271014932e</v>
       </c>
       <c r="M194">
         <v>200</v>
@@ -12022,7 +12022,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O194" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P194" t="str">
         <v>Today</v>
@@ -12034,15 +12034,15 @@
         <v>No</v>
       </c>
       <c r="S194">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>job-3a0c9449</v>
+        <v>job-1ba340a4</v>
       </c>
       <c r="B195" t="str">
-        <v>Senior Product Manager - Subscriptions</v>
+        <v>Senior Product Manager - Audiobooks Format Foundations</v>
       </c>
       <c r="C195" t="str">
         <v>Spotify</v>
@@ -12072,7 +12072,7 @@
         <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L195" t="str">
-        <v>https://jobs.lever.co/spotify/a57db22d-dc0d-4f36-9a2e-34acdf1ec046</v>
+        <v>https://jobs.lever.co/spotify/e7b01c1e-4246-4f31-83ea-9219c8b22c83</v>
       </c>
       <c r="M195">
         <v>200</v>
@@ -12081,7 +12081,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O195" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P195" t="str">
         <v>Today</v>
@@ -12093,24 +12093,24 @@
         <v>No</v>
       </c>
       <c r="S195">
-        <v>52</v>
+        <v>41</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>job-4d0308c8</v>
+        <v>job-3a0c9449</v>
       </c>
       <c r="B196" t="str">
-        <v>Technical Program Manager (TPM)</v>
+        <v>Senior Product Manager - Subscriptions</v>
       </c>
       <c r="C196" t="str">
-        <v>Palantir</v>
+        <v>Spotify</v>
       </c>
       <c r="D196" t="str">
-        <v>Instahyre</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E196" t="str">
-        <v>Technical Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F196" t="str">
         <v>5-8 yrs</v>
@@ -12119,10 +12119,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H196" t="str">
-        <v>New York, NY</v>
+        <v>London</v>
       </c>
       <c r="I196" t="str">
-        <v>New York</v>
+        <v>London</v>
       </c>
       <c r="J196" t="str">
         <v>On-site</v>
@@ -12131,7 +12131,7 @@
         <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L196" t="str">
-        <v>https://jobs.lever.co/palantir/7eb0dedb-37ee-4175-b29f-10a9e4340076</v>
+        <v>https://jobs.lever.co/spotify/a57db22d-dc0d-4f36-9a2e-34acdf1ec046</v>
       </c>
       <c r="M196">
         <v>200</v>
@@ -12140,7 +12140,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O196" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P196" t="str">
         <v>Today</v>
@@ -12152,15 +12152,15 @@
         <v>No</v>
       </c>
       <c r="S196">
-        <v>46</v>
+        <v>30</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>job-593275cb</v>
+        <v>job-4d0308c8</v>
       </c>
       <c r="B197" t="str">
-        <v>Technical Program Manager (TPM) - Defense</v>
+        <v>Technical Program Manager (TPM)</v>
       </c>
       <c r="C197" t="str">
         <v>Palantir</v>
@@ -12178,10 +12178,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H197" t="str">
-        <v>Washington, D.C.</v>
+        <v>New York, NY</v>
       </c>
       <c r="I197" t="str">
-        <v>Washington</v>
+        <v>New York</v>
       </c>
       <c r="J197" t="str">
         <v>On-site</v>
@@ -12190,7 +12190,7 @@
         <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L197" t="str">
-        <v>https://jobs.lever.co/palantir/bd16f7ad-3bee-48fd-9902-b3ee9698b608</v>
+        <v>https://jobs.lever.co/palantir/7eb0dedb-37ee-4175-b29f-10a9e4340076</v>
       </c>
       <c r="M197">
         <v>200</v>
@@ -12199,7 +12199,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O197" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P197" t="str">
         <v>Today</v>
@@ -12211,45 +12211,45 @@
         <v>No</v>
       </c>
       <c r="S197">
-        <v>48</v>
+        <v>51</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>job-343d8912</v>
+        <v>job-593275cb</v>
       </c>
       <c r="B198" t="str">
-        <v>Associate Product Manager (APM) - Growth &amp; Merchant Onboarding</v>
+        <v>Technical Program Manager (TPM) - Defense</v>
       </c>
       <c r="C198" t="str">
-        <v>Razorpay</v>
+        <v>Palantir</v>
       </c>
       <c r="D198" t="str">
-        <v>LinkedIn</v>
+        <v>Instahyre</v>
       </c>
       <c r="E198" t="str">
-        <v>Associate Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F198" t="str">
-        <v>1-3 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G198" t="str">
-        <v>0-2 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H198" t="str">
-        <v>Bengaluru, Karnataka</v>
+        <v>Washington, D.C.</v>
       </c>
       <c r="I198" t="str">
-        <v>Bengaluru</v>
+        <v>Washington</v>
       </c>
       <c r="J198" t="str">
-        <v>Hybrid</v>
+        <v>On-site</v>
       </c>
       <c r="K198" t="str">
-        <v>₹18L - ₹26L PA + ESOPs</v>
+        <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L198" t="str">
-        <v>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited</v>
+        <v>https://jobs.lever.co/palantir/bd16f7ad-3bee-48fd-9902-b3ee9698b608</v>
       </c>
       <c r="M198">
         <v>200</v>
@@ -12258,7 +12258,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O198" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P198" t="str">
         <v>Today</v>
@@ -12267,33 +12267,33 @@
         <v>Yes</v>
       </c>
       <c r="R198" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S198">
-        <v>42</v>
+        <v>78</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>job-739e0b9f</v>
+        <v>job-343d8912</v>
       </c>
       <c r="B199" t="str">
-        <v>Senior Product Manager - Consumer Checkout &amp; Loyalty</v>
+        <v>Associate Product Manager (APM) - Growth &amp; Merchant Onboarding</v>
       </c>
       <c r="C199" t="str">
-        <v>Swiggy</v>
+        <v>Razorpay</v>
       </c>
       <c r="D199" t="str">
-        <v>Naukri</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E199" t="str">
-        <v>Senior Product Manager</v>
+        <v>Associate Product Manager</v>
       </c>
       <c r="F199" t="str">
-        <v>5-8 yrs</v>
+        <v>1-3 yrs</v>
       </c>
       <c r="G199" t="str">
-        <v>5-8 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H199" t="str">
         <v>Bengaluru, Karnataka</v>
@@ -12305,10 +12305,10 @@
         <v>Hybrid</v>
       </c>
       <c r="K199" t="str">
-        <v>₹45L - ₹65L PA + ESOPs</v>
+        <v>₹18L - ₹26L PA + ESOPs</v>
       </c>
       <c r="L199" t="str">
-        <v>https://careers.swiggy.com/</v>
+        <v>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited</v>
       </c>
       <c r="M199">
         <v>200</v>
@@ -12317,7 +12317,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O199" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P199" t="str">
         <v>Today</v>
@@ -12329,18 +12329,18 @@
         <v>Yes</v>
       </c>
       <c r="S199">
-        <v>115</v>
+        <v>42</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>job-66154b1b</v>
+        <v>job-739e0b9f</v>
       </c>
       <c r="B200" t="str">
-        <v>Senior Product Manager - 10-Minute Dark Store &amp; Logistics Dispatch</v>
+        <v>Senior Product Manager - Consumer Checkout &amp; Loyalty</v>
       </c>
       <c r="C200" t="str">
-        <v>Zepto</v>
+        <v>Swiggy</v>
       </c>
       <c r="D200" t="str">
         <v>Naukri</v>
@@ -12349,34 +12349,34 @@
         <v>Senior Product Manager</v>
       </c>
       <c r="F200" t="str">
-        <v>4-7 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G200" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H200" t="str">
-        <v>Mumbai, Maharashtra</v>
+        <v>Bengaluru, Karnataka</v>
       </c>
       <c r="I200" t="str">
-        <v>Mumbai</v>
+        <v>Bengaluru</v>
       </c>
       <c r="J200" t="str">
-        <v>On-site</v>
+        <v>Hybrid</v>
       </c>
       <c r="K200" t="str">
-        <v>₹42L - ₹60L PA + ESOPs</v>
+        <v>₹45L - ₹65L PA + ESOPs</v>
       </c>
       <c r="L200" t="str">
-        <v>https://www.zeptonow.com/careers</v>
+        <v>https://careers.swiggy.com/</v>
       </c>
       <c r="M200">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N200" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O200" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P200" t="str">
         <v>Today</v>
@@ -12388,18 +12388,18 @@
         <v>Yes</v>
       </c>
       <c r="S200">
-        <v>94</v>
+        <v>115</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>job-169943b4</v>
+        <v>job-66154b1b</v>
       </c>
       <c r="B201" t="str">
-        <v>Senior Product Manager - Customer Experience &amp; Live Support AI</v>
+        <v>Senior Product Manager - 10-Minute Dark Store &amp; Logistics Dispatch</v>
       </c>
       <c r="C201" t="str">
-        <v>Zomato</v>
+        <v>Zepto</v>
       </c>
       <c r="D201" t="str">
         <v>Naukri</v>
@@ -12408,34 +12408,34 @@
         <v>Senior Product Manager</v>
       </c>
       <c r="F201" t="str">
-        <v>5-8 yrs</v>
+        <v>4-7 yrs</v>
       </c>
       <c r="G201" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H201" t="str">
-        <v>Gurgaon, Haryana</v>
+        <v>Mumbai, Maharashtra</v>
       </c>
       <c r="I201" t="str">
-        <v>Gurgaon</v>
+        <v>Mumbai</v>
       </c>
       <c r="J201" t="str">
         <v>On-site</v>
       </c>
       <c r="K201" t="str">
-        <v>₹45L - ₹65L PA + ESOPs</v>
+        <v>₹42L - ₹60L PA + ESOPs</v>
       </c>
       <c r="L201" t="str">
-        <v>https://www.zomato.com/careers</v>
+        <v>https://www.zeptonow.com/careers</v>
       </c>
       <c r="M201">
-        <v>503</v>
+        <v>202</v>
       </c>
       <c r="N201" t="str">
-        <v>BROKEN / 404</v>
+        <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O201" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P201" t="str">
         <v>Today</v>
@@ -12447,54 +12447,54 @@
         <v>Yes</v>
       </c>
       <c r="S201">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>job-23756e58</v>
+        <v>job-169943b4</v>
       </c>
       <c r="B202" t="str">
-        <v>Associate Product Manager (APM) - Social Commerce &amp; Creator Tools</v>
+        <v>Senior Product Manager - Customer Experience &amp; Live Support AI</v>
       </c>
       <c r="C202" t="str">
-        <v>Meesho</v>
+        <v>Zomato</v>
       </c>
       <c r="D202" t="str">
         <v>Naukri</v>
       </c>
       <c r="E202" t="str">
-        <v>Associate Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F202" t="str">
-        <v>0-2 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G202" t="str">
-        <v>0-2 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H202" t="str">
-        <v>Bengaluru, Karnataka</v>
+        <v>Gurgaon, Haryana</v>
       </c>
       <c r="I202" t="str">
-        <v>Bengaluru</v>
+        <v>Gurgaon</v>
       </c>
       <c r="J202" t="str">
-        <v>Hybrid</v>
+        <v>On-site</v>
       </c>
       <c r="K202" t="str">
-        <v>₹18L - ₹25L PA + ESOPs</v>
+        <v>₹45L - ₹65L PA + ESOPs</v>
       </c>
       <c r="L202" t="str">
-        <v>https://www.meesho.io/jobs</v>
+        <v>https://www.zomato.com/careers</v>
       </c>
       <c r="M202">
-        <v>200</v>
+        <v>503</v>
       </c>
       <c r="N202" t="str">
-        <v>ACTIVE / 100% VALID</v>
+        <v>BROKEN / 404</v>
       </c>
       <c r="O202" t="str">
-        <v>2026-09-14</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P202" t="str">
         <v>Today</v>
@@ -12506,30 +12506,30 @@
         <v>Yes</v>
       </c>
       <c r="S202">
-        <v>65</v>
+        <v>95</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>job-6900691e</v>
+        <v>job-23756e58</v>
       </c>
       <c r="B203" t="str">
-        <v>Product Owner - Core Banking &amp; Credit Line Engine</v>
+        <v>Associate Product Manager (APM) - Social Commerce &amp; Creator Tools</v>
       </c>
       <c r="C203" t="str">
-        <v>CRED</v>
+        <v>Meesho</v>
       </c>
       <c r="D203" t="str">
-        <v>Instahyre</v>
+        <v>Naukri</v>
       </c>
       <c r="E203" t="str">
-        <v>Technical Product Manager</v>
+        <v>Associate Product Manager</v>
       </c>
       <c r="F203" t="str">
-        <v>3-6 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="G203" t="str">
-        <v>2-5 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H203" t="str">
         <v>Bengaluru, Karnataka</v>
@@ -12538,13 +12538,13 @@
         <v>Bengaluru</v>
       </c>
       <c r="J203" t="str">
-        <v>On-site</v>
+        <v>Hybrid</v>
       </c>
       <c r="K203" t="str">
-        <v>₹35L - ₹52L PA + ESOPs</v>
+        <v>₹18L - ₹25L PA + ESOPs</v>
       </c>
       <c r="L203" t="str">
-        <v>https://careers.cred.club/</v>
+        <v>https://www.meesho.io/jobs</v>
       </c>
       <c r="M203">
         <v>200</v>
@@ -12553,42 +12553,42 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O203" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-15</v>
       </c>
       <c r="P203" t="str">
-        <v>1d ago</v>
+        <v>Today</v>
       </c>
       <c r="Q203" t="str">
         <v>Yes</v>
       </c>
       <c r="R203" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S203">
-        <v>76</v>
+        <v>65</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>job-1e98cdb6</v>
+        <v>job-6900691e</v>
       </c>
       <c r="B204" t="str">
-        <v>Product Lead - Merchant QR, Soundbox &amp; Offline Payments Rails</v>
+        <v>Product Owner - Core Banking &amp; Credit Line Engine</v>
       </c>
       <c r="C204" t="str">
-        <v>PhonePe</v>
+        <v>CRED</v>
       </c>
       <c r="D204" t="str">
         <v>Instahyre</v>
       </c>
       <c r="E204" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F204" t="str">
-        <v>7-11 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G204" t="str">
-        <v>8+ yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H204" t="str">
         <v>Bengaluru, Karnataka</v>
@@ -12600,10 +12600,10 @@
         <v>On-site</v>
       </c>
       <c r="K204" t="str">
-        <v>₹65L - ₹90L PA + ESOPs</v>
+        <v>₹35L - ₹52L PA + ESOPs</v>
       </c>
       <c r="L204" t="str">
-        <v>https://www.phonepe.com/careers/</v>
+        <v>https://careers.cred.club/</v>
       </c>
       <c r="M204">
         <v>200</v>
@@ -12612,7 +12612,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O204" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P204" t="str">
         <v>1d ago</v>
@@ -12621,33 +12621,33 @@
         <v>Yes</v>
       </c>
       <c r="R204" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S204">
-        <v>125</v>
+        <v>76</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>job-6ee4d4a9</v>
+        <v>job-1e98cdb6</v>
       </c>
       <c r="B205" t="str">
-        <v>Product Manager - Supply Chain Forecasting &amp; Dynamic Pricing</v>
+        <v>Product Lead - Merchant QR, Soundbox &amp; Offline Payments Rails</v>
       </c>
       <c r="C205" t="str">
-        <v>Flipkart</v>
+        <v>PhonePe</v>
       </c>
       <c r="D205" t="str">
-        <v>IIMJobs</v>
+        <v>Instahyre</v>
       </c>
       <c r="E205" t="str">
         <v>AI &amp; Growth PM</v>
       </c>
       <c r="F205" t="str">
-        <v>3-6 yrs</v>
+        <v>7-11 yrs</v>
       </c>
       <c r="G205" t="str">
-        <v>2-5 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H205" t="str">
         <v>Bengaluru, Karnataka</v>
@@ -12656,13 +12656,13 @@
         <v>Bengaluru</v>
       </c>
       <c r="J205" t="str">
-        <v>Hybrid</v>
+        <v>On-site</v>
       </c>
       <c r="K205" t="str">
-        <v>₹32L - ₹48L PA + ESOPs</v>
+        <v>₹65L - ₹90L PA + ESOPs</v>
       </c>
       <c r="L205" t="str">
-        <v>https://www.flipkartcareers.com/</v>
+        <v>https://www.phonepe.com/careers/</v>
       </c>
       <c r="M205">
         <v>200</v>
@@ -12671,24 +12671,83 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O205" t="str">
-        <v>2026-09-13</v>
+        <v>2026-09-14</v>
       </c>
       <c r="P205" t="str">
         <v>1d ago</v>
       </c>
       <c r="Q205" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R205" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S205">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>job-6ee4d4a9</v>
+      </c>
+      <c r="B206" t="str">
+        <v>Product Manager - Supply Chain Forecasting &amp; Dynamic Pricing</v>
+      </c>
+      <c r="C206" t="str">
+        <v>Flipkart</v>
+      </c>
+      <c r="D206" t="str">
+        <v>IIMJobs</v>
+      </c>
+      <c r="E206" t="str">
+        <v>AI &amp; Growth PM</v>
+      </c>
+      <c r="F206" t="str">
+        <v>3-6 yrs</v>
+      </c>
+      <c r="G206" t="str">
+        <v>2-5 yrs</v>
+      </c>
+      <c r="H206" t="str">
+        <v>Bengaluru, Karnataka</v>
+      </c>
+      <c r="I206" t="str">
+        <v>Bengaluru</v>
+      </c>
+      <c r="J206" t="str">
+        <v>Hybrid</v>
+      </c>
+      <c r="K206" t="str">
+        <v>₹32L - ₹48L PA + ESOPs</v>
+      </c>
+      <c r="L206" t="str">
+        <v>https://www.flipkartcareers.com/</v>
+      </c>
+      <c r="M206">
+        <v>200</v>
+      </c>
+      <c r="N206" t="str">
+        <v>ACTIVE / 100% VALID</v>
+      </c>
+      <c r="O206" t="str">
+        <v>2026-09-14</v>
+      </c>
+      <c r="P206" t="str">
+        <v>1d ago</v>
+      </c>
+      <c r="Q206" t="str">
+        <v>No</v>
+      </c>
+      <c r="R206" t="str">
+        <v>No</v>
+      </c>
+      <c r="S206">
         <v>82</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S205"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S206"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -12752,10 +12811,10 @@
 3. Confirm fetch('/data/jobs.json') returns 200 OK</v>
       </c>
       <c r="F2" t="str">
-        <v>Returns array of 204 verified PM jobs</v>
+        <v>Returns array of 205 verified PM jobs</v>
       </c>
       <c r="G2" t="str">
-        <v>Successfully fetched 204 PM jobs without errors</v>
+        <v>Successfully fetched 205 PM jobs without errors</v>
       </c>
       <c r="H2" t="str">
         <v>PASS</v>
@@ -12834,10 +12893,10 @@
 2. Compare with rawJobs.length</v>
       </c>
       <c r="F5" t="str">
-        <v>Displays exactly 204</v>
+        <v>Displays exactly 205</v>
       </c>
       <c r="G5" t="str">
-        <v>Displays 204 active roles accurately</v>
+        <v>Displays 205 active roles accurately</v>
       </c>
       <c r="H5" t="str">
         <v>PASS</v>
@@ -12861,10 +12920,10 @@
 2. Count jobs posted today / marked Today</v>
       </c>
       <c r="F6" t="str">
-        <v>Displays +201</v>
+        <v>Displays +202</v>
       </c>
       <c r="G6" t="str">
-        <v>Displays +201 new opportunities tracked</v>
+        <v>Displays +202 new opportunities tracked</v>
       </c>
       <c r="H6" t="str">
         <v>PASS</v>
@@ -12888,10 +12947,10 @@
 2. Compute (remoteCount / totalJobs) * 100</v>
       </c>
       <c r="F7" t="str">
-        <v>Displays 63 (31%)</v>
+        <v>Displays 62 (30%)</v>
       </c>
       <c r="G7" t="str">
-        <v>Calculates 63 (31%) flexible roles accurately</v>
+        <v>Calculates 62 (30%) flexible roles accurately</v>
       </c>
       <c r="H7" t="str">
         <v>PASS</v>
@@ -13440,7 +13499,7 @@
         <v>Open http://localhost:5173 in browser</v>
       </c>
       <c r="D2" t="str">
-        <v>Page loads instantly with Forest Green dark theme and 204 PM jobs</v>
+        <v>Page loads instantly with Forest Green dark theme and 205 PM jobs</v>
       </c>
       <c r="E2" t="str">
         <v>[ ] Completed</v>

--- a/GreenPath_PM_Jobs_Test_Report.xlsx
+++ b/GreenPath_PM_Jobs_Test_Report.xlsx
@@ -428,7 +428,7 @@
         <v>Test Execution Date</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-09-17T01:55:16.635Z</v>
+        <v>2026-09-18T01:42:17.744Z</v>
       </c>
     </row>
     <row r="4">
@@ -436,7 +436,7 @@
         <v>Total Jobs in Feed</v>
       </c>
       <c r="B4">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5">
@@ -444,7 +444,7 @@
         <v>Total URLs Tested</v>
       </c>
       <c r="B5">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="6">
@@ -452,7 +452,7 @@
         <v>Active / Valid Direct ATS URLs</v>
       </c>
       <c r="B6">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7">
@@ -524,7 +524,7 @@
         <v>Cities Supported</v>
       </c>
       <c r="B15" t="str">
-        <v>San Francisco, Toronto, Dublin, N/A, New York, Remote, USA, London, Seattle, United States, Bengaluru, Paris, Menlo Park, Hybrid, In-Office, Canada, Spain, United Kingdom, Ireland, Poland, Riyadh, Vancouver, Pittsburgh, Beijing, Vienna, North America, Stockholm, Washington, Mumbai, Gurgaon</v>
+        <v>San Francisco, Toronto, Dublin, N/A, New York, Remote, USA, London, Seattle, United States, Bengaluru, Paris, Menlo Park, Hybrid, In-Office, Canada, Spain, Portugal, Israel, Greece, Riyadh, Vancouver, Pittsburgh, Beijing, Vienna, North America, Stockholm, Washington, Mumbai, Gurgaon</v>
       </c>
     </row>
     <row r="16">
@@ -532,7 +532,7 @@
         <v>Remote / Hybrid Roles</v>
       </c>
       <c r="B16" t="str">
-        <v>62 (30%)</v>
+        <v>63 (31%)</v>
       </c>
     </row>
     <row r="17">
@@ -540,7 +540,7 @@
         <v>Jobs Added Today</v>
       </c>
       <c r="B17" t="str">
-        <v>+202</v>
+        <v>+203</v>
       </c>
     </row>
     <row r="18">
@@ -568,7 +568,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S206"/>
+  <dimension ref="A1:S207"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="38.83203125" customWidth="1"/>
@@ -694,19 +694,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O2" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P2" t="str">
         <v>Today</v>
       </c>
       <c r="Q2" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R2" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S2">
-        <v>33</v>
+        <v>94</v>
       </c>
     </row>
     <row r="3">
@@ -753,19 +753,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O3" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P3" t="str">
         <v>Today</v>
       </c>
       <c r="Q3" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R3" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S3">
-        <v>25</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4">
@@ -812,19 +812,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O4" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P4" t="str">
         <v>Today</v>
       </c>
       <c r="Q4" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R4" t="str">
         <v>Yes</v>
       </c>
       <c r="S4">
-        <v>34</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5">
@@ -871,7 +871,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O5" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P5" t="str">
         <v>Today</v>
@@ -880,10 +880,10 @@
         <v>No</v>
       </c>
       <c r="R5" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S5">
-        <v>60</v>
+        <v>42</v>
       </c>
     </row>
     <row r="6">
@@ -930,7 +930,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O6" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P6" t="str">
         <v>Today</v>
@@ -942,7 +942,7 @@
         <v>No</v>
       </c>
       <c r="S6">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7">
@@ -989,7 +989,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O7" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P7" t="str">
         <v>Today</v>
@@ -1001,7 +1001,7 @@
         <v>No</v>
       </c>
       <c r="S7">
-        <v>48</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8">
@@ -1048,7 +1048,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O8" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P8" t="str">
         <v>Today</v>
@@ -1057,10 +1057,10 @@
         <v>Yes</v>
       </c>
       <c r="R8" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S8">
-        <v>44</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9">
@@ -1107,7 +1107,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O9" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P9" t="str">
         <v>Today</v>
@@ -1119,7 +1119,7 @@
         <v>No</v>
       </c>
       <c r="S9">
-        <v>90</v>
+        <v>68</v>
       </c>
     </row>
     <row r="10">
@@ -1166,19 +1166,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O10" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P10" t="str">
         <v>Today</v>
       </c>
       <c r="Q10" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R10" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S10">
-        <v>68</v>
+        <v>90</v>
       </c>
     </row>
     <row r="11">
@@ -1225,19 +1225,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O11" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P11" t="str">
         <v>Today</v>
       </c>
       <c r="Q11" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R11" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S11">
-        <v>46</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12">
@@ -1284,7 +1284,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O12" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P12" t="str">
         <v>Today</v>
@@ -1293,10 +1293,10 @@
         <v>No</v>
       </c>
       <c r="R12" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S12">
-        <v>40</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -1343,7 +1343,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O13" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P13" t="str">
         <v>Today</v>
@@ -1352,10 +1352,10 @@
         <v>No</v>
       </c>
       <c r="R13" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S13">
-        <v>51</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -1402,19 +1402,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O14" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P14" t="str">
         <v>Today</v>
       </c>
       <c r="Q14" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R14" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S14">
-        <v>77</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15">
@@ -1461,7 +1461,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O15" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P15" t="str">
         <v>Today</v>
@@ -1473,7 +1473,7 @@
         <v>No</v>
       </c>
       <c r="S15">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16">
@@ -1520,19 +1520,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O16" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P16" t="str">
         <v>Today</v>
       </c>
       <c r="Q16" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R16" t="str">
         <v>No</v>
       </c>
       <c r="S16">
-        <v>45</v>
+        <v>86</v>
       </c>
     </row>
     <row r="17">
@@ -1579,7 +1579,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O17" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P17" t="str">
         <v>Today</v>
@@ -1588,10 +1588,10 @@
         <v>No</v>
       </c>
       <c r="R17" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S17">
-        <v>69</v>
+        <v>87</v>
       </c>
     </row>
     <row r="18">
@@ -1638,7 +1638,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O18" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P18" t="str">
         <v>Today</v>
@@ -1647,10 +1647,10 @@
         <v>Yes</v>
       </c>
       <c r="R18" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S18">
-        <v>86</v>
+        <v>25</v>
       </c>
     </row>
     <row r="19">
@@ -1697,19 +1697,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O19" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P19" t="str">
         <v>Today</v>
       </c>
       <c r="Q19" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R19" t="str">
         <v>No</v>
       </c>
       <c r="S19">
-        <v>88</v>
+        <v>70</v>
       </c>
     </row>
     <row r="20">
@@ -1756,7 +1756,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O20" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P20" t="str">
         <v>Today</v>
@@ -1768,7 +1768,7 @@
         <v>No</v>
       </c>
       <c r="S20">
-        <v>72</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21">
@@ -1815,7 +1815,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O21" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P21" t="str">
         <v>Today</v>
@@ -1824,10 +1824,10 @@
         <v>No</v>
       </c>
       <c r="R21" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S21">
-        <v>86</v>
+        <v>53</v>
       </c>
     </row>
     <row r="22">
@@ -1874,7 +1874,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O22" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P22" t="str">
         <v>Today</v>
@@ -1883,10 +1883,10 @@
         <v>No</v>
       </c>
       <c r="R22" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S22">
-        <v>29</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23">
@@ -1933,7 +1933,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O23" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P23" t="str">
         <v>Today</v>
@@ -1942,10 +1942,10 @@
         <v>Yes</v>
       </c>
       <c r="R23" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S23">
-        <v>27</v>
+        <v>73</v>
       </c>
     </row>
     <row r="24">
@@ -1992,7 +1992,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O24" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P24" t="str">
         <v>Today</v>
@@ -2004,7 +2004,7 @@
         <v>No</v>
       </c>
       <c r="S24">
-        <v>55</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25">
@@ -2051,7 +2051,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O25" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P25" t="str">
         <v>Today</v>
@@ -2063,7 +2063,7 @@
         <v>No</v>
       </c>
       <c r="S25">
-        <v>53</v>
+        <v>92</v>
       </c>
     </row>
     <row r="26">
@@ -2110,7 +2110,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O26" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P26" t="str">
         <v>Today</v>
@@ -2169,19 +2169,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O27" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P27" t="str">
         <v>Today</v>
       </c>
       <c r="Q27" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R27" t="str">
         <v>No</v>
       </c>
       <c r="S27">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28">
@@ -2228,7 +2228,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O28" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P28" t="str">
         <v>Today</v>
@@ -2240,7 +2240,7 @@
         <v>No</v>
       </c>
       <c r="S28">
-        <v>49</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29">
@@ -2287,19 +2287,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O29" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P29" t="str">
         <v>Today</v>
       </c>
       <c r="Q29" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R29" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S29">
-        <v>34</v>
+        <v>39</v>
       </c>
     </row>
     <row r="30">
@@ -2346,19 +2346,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O30" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P30" t="str">
         <v>Today</v>
       </c>
       <c r="Q30" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R30" t="str">
         <v>No</v>
       </c>
       <c r="S30">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31">
@@ -2405,19 +2405,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O31" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P31" t="str">
         <v>Today</v>
       </c>
       <c r="Q31" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R31" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S31">
-        <v>71</v>
+        <v>42</v>
       </c>
     </row>
     <row r="32">
@@ -2464,7 +2464,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O32" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P32" t="str">
         <v>Today</v>
@@ -2476,7 +2476,7 @@
         <v>No</v>
       </c>
       <c r="S32">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="33">
@@ -2523,19 +2523,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O33" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P33" t="str">
         <v>Today</v>
       </c>
       <c r="Q33" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R33" t="str">
         <v>No</v>
       </c>
       <c r="S33">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="34">
@@ -2582,7 +2582,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O34" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P34" t="str">
         <v>Today</v>
@@ -2594,7 +2594,7 @@
         <v>No</v>
       </c>
       <c r="S34">
-        <v>59</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35">
@@ -2641,7 +2641,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O35" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P35" t="str">
         <v>Today</v>
@@ -2653,7 +2653,7 @@
         <v>No</v>
       </c>
       <c r="S35">
-        <v>82</v>
+        <v>50</v>
       </c>
     </row>
     <row r="36">
@@ -2700,7 +2700,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O36" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P36" t="str">
         <v>Today</v>
@@ -2712,7 +2712,7 @@
         <v>No</v>
       </c>
       <c r="S36">
-        <v>65</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37">
@@ -2759,19 +2759,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O37" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P37" t="str">
         <v>Today</v>
       </c>
       <c r="Q37" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R37" t="str">
         <v>No</v>
       </c>
       <c r="S37">
-        <v>60</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38">
@@ -2818,19 +2818,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O38" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P38" t="str">
         <v>Today</v>
       </c>
       <c r="Q38" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R38" t="str">
         <v>No</v>
       </c>
       <c r="S38">
-        <v>74</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39">
@@ -2877,7 +2877,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O39" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P39" t="str">
         <v>Today</v>
@@ -2889,7 +2889,7 @@
         <v>No</v>
       </c>
       <c r="S39">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="40">
@@ -2936,19 +2936,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O40" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P40" t="str">
         <v>Today</v>
       </c>
       <c r="Q40" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R40" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S40">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="41">
@@ -2974,10 +2974,10 @@
         <v>0-2 yrs</v>
       </c>
       <c r="H41" t="str">
-        <v>Paris, France</v>
+        <v>New York, New York, USA</v>
       </c>
       <c r="I41" t="str">
-        <v>Paris</v>
+        <v>New York</v>
       </c>
       <c r="J41" t="str">
         <v>On-site</v>
@@ -2986,7 +2986,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L41" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/8143729</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/8108241</v>
       </c>
       <c r="M41">
         <v>200</v>
@@ -2995,7 +2995,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O41" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P41" t="str">
         <v>Today</v>
@@ -3004,10 +3004,10 @@
         <v>No</v>
       </c>
       <c r="R41" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S41">
-        <v>62</v>
+        <v>91</v>
       </c>
     </row>
     <row r="42">
@@ -3033,10 +3033,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H42" t="str">
-        <v>Paris, France</v>
+        <v>Boston, Massachusetts, USA; New York, New York, USA</v>
       </c>
       <c r="I42" t="str">
-        <v>Paris</v>
+        <v>New York</v>
       </c>
       <c r="J42" t="str">
         <v>On-site</v>
@@ -3045,7 +3045,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L42" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/8012549</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/7982288</v>
       </c>
       <c r="M42">
         <v>200</v>
@@ -3054,19 +3054,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O42" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P42" t="str">
         <v>Today</v>
       </c>
       <c r="Q42" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R42" t="str">
         <v>No</v>
       </c>
       <c r="S42">
-        <v>89</v>
+        <v>32</v>
       </c>
     </row>
     <row r="43">
@@ -3113,19 +3113,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O43" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P43" t="str">
         <v>Today</v>
       </c>
       <c r="Q43" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R43" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S43">
-        <v>52</v>
+        <v>30</v>
       </c>
     </row>
     <row r="44">
@@ -3172,19 +3172,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O44" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P44" t="str">
         <v>Today</v>
       </c>
       <c r="Q44" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R44" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S44">
-        <v>31</v>
+        <v>44</v>
       </c>
     </row>
     <row r="45">
@@ -3231,7 +3231,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O45" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P45" t="str">
         <v>Today</v>
@@ -3240,10 +3240,10 @@
         <v>No</v>
       </c>
       <c r="R45" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S45">
-        <v>64</v>
+        <v>89</v>
       </c>
     </row>
     <row r="46">
@@ -3290,13 +3290,13 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O46" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P46" t="str">
         <v>Today</v>
       </c>
       <c r="Q46" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R46" t="str">
         <v>No</v>
@@ -3349,19 +3349,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O47" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P47" t="str">
         <v>Today</v>
       </c>
       <c r="Q47" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R47" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S47">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="48">
@@ -3408,7 +3408,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O48" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P48" t="str">
         <v>Today</v>
@@ -3417,10 +3417,10 @@
         <v>No</v>
       </c>
       <c r="R48" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S48">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="49">
@@ -3467,7 +3467,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O49" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P49" t="str">
         <v>Today</v>
@@ -3476,10 +3476,10 @@
         <v>No</v>
       </c>
       <c r="R49" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S49">
-        <v>66</v>
+        <v>25</v>
       </c>
     </row>
     <row r="50">
@@ -3526,19 +3526,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O50" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P50" t="str">
         <v>Today</v>
       </c>
       <c r="Q50" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R50" t="str">
         <v>No</v>
       </c>
       <c r="S50">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="51">
@@ -3585,19 +3585,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O51" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P51" t="str">
         <v>Today</v>
       </c>
       <c r="Q51" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R51" t="str">
         <v>No</v>
       </c>
       <c r="S51">
-        <v>55</v>
+        <v>61</v>
       </c>
     </row>
     <row r="52">
@@ -3644,7 +3644,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O52" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P52" t="str">
         <v>Today</v>
@@ -3653,10 +3653,10 @@
         <v>No</v>
       </c>
       <c r="R52" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S52">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="53">
@@ -3703,7 +3703,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O53" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P53" t="str">
         <v>Today</v>
@@ -3715,7 +3715,7 @@
         <v>Yes</v>
       </c>
       <c r="S53">
-        <v>76</v>
+        <v>48</v>
       </c>
     </row>
     <row r="54">
@@ -3762,7 +3762,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O54" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P54" t="str">
         <v>Today</v>
@@ -3771,18 +3771,18 @@
         <v>No</v>
       </c>
       <c r="R54" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S54">
-        <v>55</v>
+        <v>70</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>job-6559c62f</v>
+        <v>job-5ef34fd7</v>
       </c>
       <c r="B55" t="str">
-        <v>Senior Product Manager - Serverless</v>
+        <v>Senior Staff GenAI Engineer - Application Performance Monitoring (APM)</v>
       </c>
       <c r="C55" t="str">
         <v>Datadog</v>
@@ -3791,16 +3791,16 @@
         <v>Wellfound</v>
       </c>
       <c r="E55" t="str">
-        <v>Senior Product Manager</v>
+        <v>Associate Product Manager</v>
       </c>
       <c r="F55" t="str">
-        <v>5-8 yrs</v>
+        <v>1-3 yrs</v>
       </c>
       <c r="G55" t="str">
-        <v>5-8 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H55" t="str">
-        <v>Boston, Massachusetts, USA; New York, New York, USA</v>
+        <v>New York, New York, USA</v>
       </c>
       <c r="I55" t="str">
         <v>New York</v>
@@ -3812,7 +3812,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L55" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/7905006</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/6960503</v>
       </c>
       <c r="M55">
         <v>200</v>
@@ -3821,27 +3821,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O55" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P55" t="str">
         <v>Today</v>
       </c>
       <c r="Q55" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R55" t="str">
         <v>No</v>
       </c>
       <c r="S55">
-        <v>56</v>
+        <v>69</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>job-5ef34fd7</v>
+        <v>job-6f4d5443</v>
       </c>
       <c r="B56" t="str">
-        <v>Senior Staff GenAI Engineer - Application Performance Monitoring (APM)</v>
+        <v>Staff GenAI Engineer - Application Performance Monitoring (APM)</v>
       </c>
       <c r="C56" t="str">
         <v>Datadog</v>
@@ -3871,7 +3871,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L56" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/6960503</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/7974511</v>
       </c>
       <c r="M56">
         <v>200</v>
@@ -3880,27 +3880,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O56" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P56" t="str">
         <v>Today</v>
       </c>
       <c r="Q56" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R56" t="str">
         <v>No</v>
       </c>
       <c r="S56">
-        <v>28</v>
+        <v>72</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>job-6f4d5443</v>
+        <v>job-62a8a726</v>
       </c>
       <c r="B57" t="str">
-        <v>Staff GenAI Engineer - Application Performance Monitoring (APM)</v>
+        <v>Staff Product Manager - Bits Release</v>
       </c>
       <c r="C57" t="str">
         <v>Datadog</v>
@@ -3909,13 +3909,13 @@
         <v>Wellfound</v>
       </c>
       <c r="E57" t="str">
-        <v>Associate Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F57" t="str">
-        <v>1-3 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G57" t="str">
-        <v>0-2 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H57" t="str">
         <v>New York, New York, USA</v>
@@ -3930,7 +3930,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L57" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/7974511</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/8174592</v>
       </c>
       <c r="M57">
         <v>200</v>
@@ -3939,27 +3939,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O57" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P57" t="str">
         <v>Today</v>
       </c>
       <c r="Q57" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R57" t="str">
         <v>No</v>
       </c>
       <c r="S57">
-        <v>57</v>
+        <v>30</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>job-62a8a726</v>
+        <v>job-74e794e5</v>
       </c>
       <c r="B58" t="str">
-        <v>Staff Product Manager - Bits Release</v>
+        <v>Staff Product Manager, Observability Data Platforms</v>
       </c>
       <c r="C58" t="str">
         <v>Datadog</v>
@@ -3989,7 +3989,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L58" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/8174592</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/8065187</v>
       </c>
       <c r="M58">
         <v>200</v>
@@ -3998,57 +3998,57 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O58" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P58" t="str">
         <v>Today</v>
       </c>
       <c r="Q58" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R58" t="str">
         <v>Yes</v>
       </c>
       <c r="S58">
-        <v>49</v>
+        <v>63</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>job-74e794e5</v>
+        <v>job-443f0280</v>
       </c>
       <c r="B59" t="str">
-        <v>Staff Product Manager, Observability Data Platforms</v>
+        <v>Group Product Manager, Finance Technology</v>
       </c>
       <c r="C59" t="str">
-        <v>Datadog</v>
+        <v>Reddit</v>
       </c>
       <c r="D59" t="str">
-        <v>Wellfound</v>
+        <v>Indeed</v>
       </c>
       <c r="E59" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F59" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G59" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H59" t="str">
-        <v>New York, New York, USA</v>
+        <v>Remote - United States</v>
       </c>
       <c r="I59" t="str">
-        <v>New York</v>
+        <v>Remote</v>
       </c>
       <c r="J59" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K59" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L59" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/8065187</v>
+        <v>https://boards.greenhouse.io/reddit/jobs/8075185</v>
       </c>
       <c r="M59">
         <v>200</v>
@@ -4057,13 +4057,13 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O59" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P59" t="str">
         <v>Today</v>
       </c>
       <c r="Q59" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R59" t="str">
         <v>No</v>
@@ -4074,10 +4074,10 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>job-443f0280</v>
+        <v>job-7e666189</v>
       </c>
       <c r="B60" t="str">
-        <v>Group Product Manager, Finance Technology</v>
+        <v>Product Manager, Developer Ecosystem</v>
       </c>
       <c r="C60" t="str">
         <v>Reddit</v>
@@ -4086,7 +4086,7 @@
         <v>Indeed</v>
       </c>
       <c r="E60" t="str">
-        <v>Product Lead / Director</v>
+        <v>Product Manager</v>
       </c>
       <c r="F60" t="str">
         <v>3-6 yrs</v>
@@ -4107,7 +4107,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L60" t="str">
-        <v>https://boards.greenhouse.io/reddit/jobs/8075185</v>
+        <v>https://boards.greenhouse.io/reddit/jobs/8088720</v>
       </c>
       <c r="M60">
         <v>200</v>
@@ -4116,7 +4116,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O60" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P60" t="str">
         <v>Today</v>
@@ -4128,15 +4128,15 @@
         <v>No</v>
       </c>
       <c r="S60">
-        <v>44</v>
+        <v>85</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>job-7e666189</v>
+        <v>job-66f21772</v>
       </c>
       <c r="B61" t="str">
-        <v>Product Manager, Developer Ecosystem</v>
+        <v>Senior Product Manager, Ads -  Shopping Catalogs</v>
       </c>
       <c r="C61" t="str">
         <v>Reddit</v>
@@ -4145,13 +4145,13 @@
         <v>Indeed</v>
       </c>
       <c r="E61" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F61" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G61" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H61" t="str">
         <v>Remote - United States</v>
@@ -4166,7 +4166,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L61" t="str">
-        <v>https://boards.greenhouse.io/reddit/jobs/8088720</v>
+        <v>https://boards.greenhouse.io/reddit/jobs/8120503</v>
       </c>
       <c r="M61">
         <v>200</v>
@@ -4175,7 +4175,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O61" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P61" t="str">
         <v>Today</v>
@@ -4187,15 +4187,15 @@
         <v>No</v>
       </c>
       <c r="S61">
-        <v>89</v>
+        <v>45</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>job-66f21772</v>
+        <v>job-4b069687</v>
       </c>
       <c r="B62" t="str">
-        <v>Senior Product Manager, Ads -  Shopping Catalogs</v>
+        <v>Staff Product Manager, Ads Formats</v>
       </c>
       <c r="C62" t="str">
         <v>Reddit</v>
@@ -4225,7 +4225,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L62" t="str">
-        <v>https://boards.greenhouse.io/reddit/jobs/8120503</v>
+        <v>https://boards.greenhouse.io/reddit/jobs/8167412</v>
       </c>
       <c r="M62">
         <v>200</v>
@@ -4234,27 +4234,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O62" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P62" t="str">
         <v>Today</v>
       </c>
       <c r="Q62" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R62" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S62">
-        <v>58</v>
+        <v>88</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>job-4b069687</v>
+        <v>job-0638f83c</v>
       </c>
       <c r="B63" t="str">
-        <v>Staff Product Manager, Ads Formats</v>
+        <v>Staff Product Manager, Ads Safety (Ads Review)</v>
       </c>
       <c r="C63" t="str">
         <v>Reddit</v>
@@ -4284,7 +4284,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L63" t="str">
-        <v>https://boards.greenhouse.io/reddit/jobs/8167412</v>
+        <v>https://boards.greenhouse.io/reddit/jobs/8070669</v>
       </c>
       <c r="M63">
         <v>200</v>
@@ -4293,7 +4293,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O63" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P63" t="str">
         <v>Today</v>
@@ -4302,18 +4302,18 @@
         <v>No</v>
       </c>
       <c r="R63" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S63">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>job-0638f83c</v>
+        <v>job-35a933c8</v>
       </c>
       <c r="B64" t="str">
-        <v>Staff Product Manager, Ads Safety (Ads Review)</v>
+        <v>Staff Product Manager, Ads Signals</v>
       </c>
       <c r="C64" t="str">
         <v>Reddit</v>
@@ -4343,7 +4343,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L64" t="str">
-        <v>https://boards.greenhouse.io/reddit/jobs/8070669</v>
+        <v>https://boards.greenhouse.io/reddit/jobs/8145926</v>
       </c>
       <c r="M64">
         <v>200</v>
@@ -4352,7 +4352,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O64" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P64" t="str">
         <v>Today</v>
@@ -4364,15 +4364,15 @@
         <v>No</v>
       </c>
       <c r="S64">
-        <v>71</v>
+        <v>45</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>job-35a933c8</v>
+        <v>job-5a8393aa</v>
       </c>
       <c r="B65" t="str">
-        <v>Staff Product Manager, Ads Signals</v>
+        <v>Staff Product Manager, Growth</v>
       </c>
       <c r="C65" t="str">
         <v>Reddit</v>
@@ -4402,7 +4402,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L65" t="str">
-        <v>https://boards.greenhouse.io/reddit/jobs/8145926</v>
+        <v>https://boards.greenhouse.io/reddit/jobs/7997186</v>
       </c>
       <c r="M65">
         <v>200</v>
@@ -4411,27 +4411,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O65" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P65" t="str">
         <v>Today</v>
       </c>
       <c r="Q65" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R65" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S65">
-        <v>48</v>
+        <v>86</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>job-5a8393aa</v>
+        <v>job-15c0a18c</v>
       </c>
       <c r="B66" t="str">
-        <v>Staff Product Manager, Growth</v>
+        <v>Staff Technical Product Manager, Ads ML Platform</v>
       </c>
       <c r="C66" t="str">
         <v>Reddit</v>
@@ -4461,7 +4461,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L66" t="str">
-        <v>https://boards.greenhouse.io/reddit/jobs/7997186</v>
+        <v>https://boards.greenhouse.io/reddit/jobs/7954001</v>
       </c>
       <c r="M66">
         <v>200</v>
@@ -4470,33 +4470,33 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O66" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P66" t="str">
         <v>Today</v>
       </c>
       <c r="Q66" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R66" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S66">
-        <v>41</v>
+        <v>25</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>job-15c0a18c</v>
+        <v>job-42db73ba</v>
       </c>
       <c r="B67" t="str">
-        <v>Staff Technical Product Manager, Ads ML Platform</v>
+        <v>Senior Product Manager, Safety</v>
       </c>
       <c r="C67" t="str">
-        <v>Reddit</v>
+        <v>Discord</v>
       </c>
       <c r="D67" t="str">
-        <v>Indeed</v>
+        <v>Wellfound</v>
       </c>
       <c r="E67" t="str">
         <v>Senior Product Manager</v>
@@ -4508,19 +4508,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H67" t="str">
-        <v>Remote - United States</v>
+        <v>San Francisco Bay Area</v>
       </c>
       <c r="I67" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J67" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K67" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L67" t="str">
-        <v>https://boards.greenhouse.io/reddit/jobs/7954001</v>
+        <v>https://boards.greenhouse.io/discord/jobs/8581126002</v>
       </c>
       <c r="M67">
         <v>200</v>
@@ -4529,48 +4529,48 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O67" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P67" t="str">
         <v>Today</v>
       </c>
       <c r="Q67" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R67" t="str">
         <v>No</v>
       </c>
       <c r="S67">
-        <v>64</v>
+        <v>40</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>job-42db73ba</v>
+        <v>job-00451313</v>
       </c>
       <c r="B68" t="str">
-        <v>Senior Product Manager, Safety</v>
+        <v>Associate Product Manager (New Grad)</v>
       </c>
       <c r="C68" t="str">
-        <v>Discord</v>
+        <v>Robinhood</v>
       </c>
       <c r="D68" t="str">
-        <v>Wellfound</v>
+        <v>Naukri</v>
       </c>
       <c r="E68" t="str">
-        <v>Senior Product Manager</v>
+        <v>Associate Product Manager</v>
       </c>
       <c r="F68" t="str">
-        <v>5-8 yrs</v>
+        <v>1-3 yrs</v>
       </c>
       <c r="G68" t="str">
-        <v>5-8 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H68" t="str">
-        <v>San Francisco Bay Area</v>
+        <v>Menlo Park, CA; New York, NY</v>
       </c>
       <c r="I68" t="str">
-        <v>San Francisco</v>
+        <v>New York</v>
       </c>
       <c r="J68" t="str">
         <v>On-site</v>
@@ -4579,7 +4579,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L68" t="str">
-        <v>https://boards.greenhouse.io/discord/jobs/8581126002</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/8199973</v>
       </c>
       <c r="M68">
         <v>200</v>
@@ -4588,7 +4588,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O68" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P68" t="str">
         <v>Today</v>
@@ -4600,15 +4600,15 @@
         <v>No</v>
       </c>
       <c r="S68">
-        <v>62</v>
+        <v>86</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>job-00451313</v>
+        <v>job-73f048f5</v>
       </c>
       <c r="B69" t="str">
-        <v>Associate Product Manager (New Grad)</v>
+        <v>Senior Product Manager, Capital Markets</v>
       </c>
       <c r="C69" t="str">
         <v>Robinhood</v>
@@ -4617,13 +4617,13 @@
         <v>Naukri</v>
       </c>
       <c r="E69" t="str">
-        <v>Associate Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F69" t="str">
-        <v>1-3 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G69" t="str">
-        <v>0-2 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H69" t="str">
         <v>Menlo Park, CA; New York, NY</v>
@@ -4638,7 +4638,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L69" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/8199973</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/8204521</v>
       </c>
       <c r="M69">
         <v>200</v>
@@ -4647,27 +4647,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O69" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P69" t="str">
         <v>Today</v>
       </c>
       <c r="Q69" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R69" t="str">
         <v>No</v>
       </c>
       <c r="S69">
-        <v>33</v>
+        <v>57</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>job-73f048f5</v>
+        <v>job-28c2c2a4</v>
       </c>
       <c r="B70" t="str">
-        <v>Senior Product Manager, Capital Markets</v>
+        <v>Senior Product Manager, Crypto Wallet</v>
       </c>
       <c r="C70" t="str">
         <v>Robinhood</v>
@@ -4697,7 +4697,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L70" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/8204521</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/8082718</v>
       </c>
       <c r="M70">
         <v>200</v>
@@ -4706,7 +4706,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O70" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P70" t="str">
         <v>Today</v>
@@ -4715,18 +4715,18 @@
         <v>Yes</v>
       </c>
       <c r="R70" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S70">
-        <v>31</v>
+        <v>56</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>job-28c2c2a4</v>
+        <v>job-6a8c3d37</v>
       </c>
       <c r="B71" t="str">
-        <v>Senior Product Manager, Crypto Wallet</v>
+        <v>Senior Product Manager, Money Movement</v>
       </c>
       <c r="C71" t="str">
         <v>Robinhood</v>
@@ -4744,10 +4744,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H71" t="str">
-        <v>Menlo Park, CA; New York, NY</v>
+        <v>Menlo Park, CA</v>
       </c>
       <c r="I71" t="str">
-        <v>New York</v>
+        <v>Menlo Park</v>
       </c>
       <c r="J71" t="str">
         <v>On-site</v>
@@ -4756,7 +4756,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L71" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/8082718</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/7747728</v>
       </c>
       <c r="M71">
         <v>200</v>
@@ -4765,7 +4765,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O71" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P71" t="str">
         <v>Today</v>
@@ -4777,15 +4777,15 @@
         <v>Yes</v>
       </c>
       <c r="S71">
-        <v>88</v>
+        <v>75</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>job-6a8c3d37</v>
+        <v>job-6a477110</v>
       </c>
       <c r="B72" t="str">
-        <v>Senior Product Manager, Money Movement</v>
+        <v>Staff Product Manager, Banking</v>
       </c>
       <c r="C72" t="str">
         <v>Robinhood</v>
@@ -4803,10 +4803,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H72" t="str">
-        <v>Menlo Park, CA</v>
+        <v>Menlo Park, CA; New York, NY; Washington, DC</v>
       </c>
       <c r="I72" t="str">
-        <v>Menlo Park</v>
+        <v>New York</v>
       </c>
       <c r="J72" t="str">
         <v>On-site</v>
@@ -4815,7 +4815,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L72" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/7747728</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/8044746</v>
       </c>
       <c r="M72">
         <v>200</v>
@@ -4824,7 +4824,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O72" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P72" t="str">
         <v>Today</v>
@@ -4836,15 +4836,15 @@
         <v>No</v>
       </c>
       <c r="S72">
-        <v>65</v>
+        <v>54</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>job-6a477110</v>
+        <v>job-1f991f57</v>
       </c>
       <c r="B73" t="str">
-        <v>Staff Product Manager, Banking</v>
+        <v>Staff Product Manager-  Integrations &amp; Advisor Platform</v>
       </c>
       <c r="C73" t="str">
         <v>Robinhood</v>
@@ -4862,7 +4862,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H73" t="str">
-        <v>Menlo Park, CA; New York, NY; Washington, DC</v>
+        <v>Clearwater, FL; Menlo Park, CA; New York, NY</v>
       </c>
       <c r="I73" t="str">
         <v>New York</v>
@@ -4874,7 +4874,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L73" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/8044746</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/8131181</v>
       </c>
       <c r="M73">
         <v>200</v>
@@ -4883,27 +4883,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O73" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P73" t="str">
         <v>Today</v>
       </c>
       <c r="Q73" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R73" t="str">
         <v>Yes</v>
       </c>
       <c r="S73">
-        <v>36</v>
+        <v>94</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>job-1f991f57</v>
+        <v>job-621b991e</v>
       </c>
       <c r="B74" t="str">
-        <v>Staff Product Manager-  Integrations &amp; Advisor Platform</v>
+        <v>Staff Product Manager, National Impact</v>
       </c>
       <c r="C74" t="str">
         <v>Robinhood</v>
@@ -4921,7 +4921,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H74" t="str">
-        <v>Clearwater, FL; Menlo Park, CA; New York, NY</v>
+        <v>New York, NY</v>
       </c>
       <c r="I74" t="str">
         <v>New York</v>
@@ -4933,7 +4933,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L74" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/8131181</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/7968044</v>
       </c>
       <c r="M74">
         <v>200</v>
@@ -4942,57 +4942,57 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O74" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P74" t="str">
         <v>Today</v>
       </c>
       <c r="Q74" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R74" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S74">
-        <v>66</v>
+        <v>78</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>job-621b991e</v>
+        <v>job-223dd55b</v>
       </c>
       <c r="B75" t="str">
-        <v>Staff Product Manager, National Impact</v>
+        <v>Director of Product Management, Fintech</v>
       </c>
       <c r="C75" t="str">
-        <v>Robinhood</v>
+        <v>Cloudflare</v>
       </c>
       <c r="D75" t="str">
-        <v>Naukri</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E75" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F75" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G75" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H75" t="str">
-        <v>New York, NY</v>
+        <v>Hybrid</v>
       </c>
       <c r="I75" t="str">
-        <v>New York</v>
+        <v>Hybrid</v>
       </c>
       <c r="J75" t="str">
-        <v>On-site</v>
+        <v>Hybrid</v>
       </c>
       <c r="K75" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L75" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/7968044</v>
+        <v>https://boards.greenhouse.io/cloudflare/jobs/8152765</v>
       </c>
       <c r="M75">
         <v>200</v>
@@ -5001,27 +5001,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O75" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P75" t="str">
         <v>Today</v>
       </c>
       <c r="Q75" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R75" t="str">
         <v>No</v>
       </c>
       <c r="S75">
-        <v>39</v>
+        <v>29</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>job-223dd55b</v>
+        <v>job-6ad0cb95</v>
       </c>
       <c r="B76" t="str">
-        <v>Director of Product Management, Fintech</v>
+        <v>Senior Product Manager - Application Protection &amp; Governance</v>
       </c>
       <c r="C76" t="str">
         <v>Cloudflare</v>
@@ -5030,13 +5030,13 @@
         <v>LinkedIn</v>
       </c>
       <c r="E76" t="str">
-        <v>Product Lead / Director</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F76" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G76" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H76" t="str">
         <v>Hybrid</v>
@@ -5051,7 +5051,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L76" t="str">
-        <v>https://boards.greenhouse.io/cloudflare/jobs/8152765</v>
+        <v>https://boards.greenhouse.io/cloudflare/jobs/8200670</v>
       </c>
       <c r="M76">
         <v>200</v>
@@ -5060,7 +5060,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O76" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P76" t="str">
         <v>Today</v>
@@ -5072,7 +5072,7 @@
         <v>No</v>
       </c>
       <c r="S76">
-        <v>86</v>
+        <v>55</v>
       </c>
     </row>
     <row r="77">
@@ -5119,7 +5119,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O77" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P77" t="str">
         <v>Today</v>
@@ -5131,7 +5131,7 @@
         <v>No</v>
       </c>
       <c r="S77">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="78">
@@ -5178,19 +5178,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O78" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P78" t="str">
         <v>Today</v>
       </c>
       <c r="Q78" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R78" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S78">
-        <v>45</v>
+        <v>65</v>
       </c>
     </row>
     <row r="79">
@@ -5237,19 +5237,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O79" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P79" t="str">
         <v>Today</v>
       </c>
       <c r="Q79" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R79" t="str">
         <v>No</v>
       </c>
       <c r="S79">
-        <v>52</v>
+        <v>68</v>
       </c>
     </row>
     <row r="80">
@@ -5296,7 +5296,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O80" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P80" t="str">
         <v>Today</v>
@@ -5305,10 +5305,10 @@
         <v>Yes</v>
       </c>
       <c r="R80" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S80">
-        <v>27</v>
+        <v>64</v>
       </c>
     </row>
     <row r="81">
@@ -5355,7 +5355,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O81" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P81" t="str">
         <v>Today</v>
@@ -5364,10 +5364,10 @@
         <v>No</v>
       </c>
       <c r="R81" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S81">
-        <v>46</v>
+        <v>72</v>
       </c>
     </row>
     <row r="82">
@@ -5414,19 +5414,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O82" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P82" t="str">
         <v>Today</v>
       </c>
       <c r="Q82" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R82" t="str">
         <v>No</v>
       </c>
       <c r="S82">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="83">
@@ -5452,10 +5452,10 @@
         <v>8+ yrs</v>
       </c>
       <c r="H83" t="str">
-        <v>United Kingdom</v>
+        <v>Portugal</v>
       </c>
       <c r="I83" t="str">
-        <v>United Kingdom</v>
+        <v>Portugal</v>
       </c>
       <c r="J83" t="str">
         <v>On-site</v>
@@ -5464,7 +5464,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L83" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8155427</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8155423</v>
       </c>
       <c r="M83">
         <v>200</v>
@@ -5473,19 +5473,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O83" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P83" t="str">
         <v>Today</v>
       </c>
       <c r="Q83" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R83" t="str">
         <v>Yes</v>
       </c>
       <c r="S83">
-        <v>84</v>
+        <v>77</v>
       </c>
     </row>
     <row r="84">
@@ -5511,10 +5511,10 @@
         <v>8+ yrs</v>
       </c>
       <c r="H84" t="str">
-        <v>United States</v>
+        <v>Israel</v>
       </c>
       <c r="I84" t="str">
-        <v>United States</v>
+        <v>Israel</v>
       </c>
       <c r="J84" t="str">
         <v>On-site</v>
@@ -5523,7 +5523,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L84" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8130124</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8155328</v>
       </c>
       <c r="M84">
         <v>200</v>
@@ -5532,19 +5532,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O84" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P84" t="str">
         <v>Today</v>
       </c>
       <c r="Q84" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R84" t="str">
         <v>Yes</v>
       </c>
       <c r="S84">
-        <v>25</v>
+        <v>69</v>
       </c>
     </row>
     <row r="85">
@@ -5570,10 +5570,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H85" t="str">
-        <v>United States</v>
+        <v>Canada</v>
       </c>
       <c r="I85" t="str">
-        <v>United States</v>
+        <v>Canada</v>
       </c>
       <c r="J85" t="str">
         <v>On-site</v>
@@ -5582,7 +5582,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L85" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8088818</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8093933</v>
       </c>
       <c r="M85">
         <v>200</v>
@@ -5591,7 +5591,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O85" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P85" t="str">
         <v>Today</v>
@@ -5600,10 +5600,10 @@
         <v>No</v>
       </c>
       <c r="R85" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S85">
-        <v>69</v>
+        <v>44</v>
       </c>
     </row>
     <row r="86">
@@ -5629,10 +5629,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H86" t="str">
-        <v>United States</v>
+        <v>Canada</v>
       </c>
       <c r="I86" t="str">
-        <v>United States</v>
+        <v>Canada</v>
       </c>
       <c r="J86" t="str">
         <v>On-site</v>
@@ -5641,7 +5641,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L86" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8053907</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8066646</v>
       </c>
       <c r="M86">
         <v>200</v>
@@ -5650,19 +5650,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O86" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P86" t="str">
         <v>Today</v>
       </c>
       <c r="Q86" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R86" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S86">
-        <v>29</v>
+        <v>67</v>
       </c>
     </row>
     <row r="87">
@@ -5688,10 +5688,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H87" t="str">
-        <v>Ireland</v>
+        <v>Greece</v>
       </c>
       <c r="I87" t="str">
-        <v>Ireland</v>
+        <v>Greece</v>
       </c>
       <c r="J87" t="str">
         <v>On-site</v>
@@ -5700,7 +5700,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L87" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8041203</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8041202</v>
       </c>
       <c r="M87">
         <v>200</v>
@@ -5709,7 +5709,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O87" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P87" t="str">
         <v>Today</v>
@@ -5718,10 +5718,10 @@
         <v>No</v>
       </c>
       <c r="R87" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S87">
-        <v>66</v>
+        <v>26</v>
       </c>
     </row>
     <row r="88">
@@ -5768,19 +5768,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O88" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P88" t="str">
         <v>Today</v>
       </c>
       <c r="Q88" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R88" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S88">
-        <v>26</v>
+        <v>79</v>
       </c>
     </row>
     <row r="89">
@@ -5806,10 +5806,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H89" t="str">
-        <v>Poland</v>
+        <v>Canada</v>
       </c>
       <c r="I89" t="str">
-        <v>Poland</v>
+        <v>Canada</v>
       </c>
       <c r="J89" t="str">
         <v>On-site</v>
@@ -5818,7 +5818,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L89" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8194139</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8190824</v>
       </c>
       <c r="M89">
         <v>200</v>
@@ -5827,7 +5827,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O89" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P89" t="str">
         <v>Today</v>
@@ -5839,7 +5839,7 @@
         <v>No</v>
       </c>
       <c r="S89">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="90">
@@ -5886,7 +5886,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O90" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P90" t="str">
         <v>Today</v>
@@ -5898,15 +5898,15 @@
         <v>No</v>
       </c>
       <c r="S90">
-        <v>79</v>
+        <v>35</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>job-184e55c8</v>
+        <v>job-6a202479</v>
       </c>
       <c r="B91" t="str">
-        <v>Director of Product Management, Enterprise Core Platform</v>
+        <v>Director of Product Management, Forward Deployed &amp; Strategy</v>
       </c>
       <c r="C91" t="str">
         <v>Scale AI</v>
@@ -5915,7 +5915,7 @@
         <v>Wellfound</v>
       </c>
       <c r="E91" t="str">
-        <v>Technical Product Manager</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F91" t="str">
         <v>8+ yrs</v>
@@ -5924,10 +5924,10 @@
         <v>8+ yrs</v>
       </c>
       <c r="H91" t="str">
-        <v>San Francisco, CA; New York, NY</v>
+        <v>London, UK</v>
       </c>
       <c r="I91" t="str">
-        <v>San Francisco</v>
+        <v>London</v>
       </c>
       <c r="J91" t="str">
         <v>On-site</v>
@@ -5936,7 +5936,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L91" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4714727005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4702890005</v>
       </c>
       <c r="M91">
         <v>200</v>
@@ -5945,27 +5945,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O91" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P91" t="str">
         <v>Today</v>
       </c>
       <c r="Q91" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R91" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S91">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>job-6a202479</v>
+        <v>job-6681e5c8</v>
       </c>
       <c r="B92" t="str">
-        <v>Director of Product Management, Forward Deployed &amp; Strategy</v>
+        <v>Forward Deployed Product Manager, Enterprise</v>
       </c>
       <c r="C92" t="str">
         <v>Scale AI</v>
@@ -5974,13 +5974,13 @@
         <v>Wellfound</v>
       </c>
       <c r="E92" t="str">
-        <v>Product Lead / Director</v>
+        <v>Product Manager</v>
       </c>
       <c r="F92" t="str">
-        <v>8+ yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G92" t="str">
-        <v>8+ yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H92" t="str">
         <v>London, UK</v>
@@ -5995,7 +5995,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L92" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4702890005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4644742005</v>
       </c>
       <c r="M92">
         <v>200</v>
@@ -6004,27 +6004,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O92" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P92" t="str">
         <v>Today</v>
       </c>
       <c r="Q92" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R92" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S92">
-        <v>83</v>
+        <v>72</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>job-6681e5c8</v>
+        <v>job-11245f1c</v>
       </c>
       <c r="B93" t="str">
-        <v>Forward Deployed Product Manager, Enterprise</v>
+        <v>Forward Deployed Product Manager, Public Sector</v>
       </c>
       <c r="C93" t="str">
         <v>Scale AI</v>
@@ -6042,10 +6042,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H93" t="str">
-        <v>London, UK</v>
+        <v>New York, NY; Washington, DC</v>
       </c>
       <c r="I93" t="str">
-        <v>London</v>
+        <v>New York</v>
       </c>
       <c r="J93" t="str">
         <v>On-site</v>
@@ -6054,7 +6054,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L93" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4644742005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4713648005</v>
       </c>
       <c r="M93">
         <v>200</v>
@@ -6063,27 +6063,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O93" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P93" t="str">
         <v>Today</v>
       </c>
       <c r="Q93" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R93" t="str">
         <v>No</v>
       </c>
       <c r="S93">
-        <v>52</v>
+        <v>58</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>job-11245f1c</v>
+        <v>job-235e84a3</v>
       </c>
       <c r="B94" t="str">
-        <v>Forward Deployed Product Manager, Public Sector</v>
+        <v>Product Manager, Enterprise Core Platform</v>
       </c>
       <c r="C94" t="str">
         <v>Scale AI</v>
@@ -6092,7 +6092,7 @@
         <v>Wellfound</v>
       </c>
       <c r="E94" t="str">
-        <v>Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F94" t="str">
         <v>3-6 yrs</v>
@@ -6101,10 +6101,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H94" t="str">
-        <v>New York, NY; Washington, DC</v>
+        <v>New York, NY; San Francisco, CA</v>
       </c>
       <c r="I94" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J94" t="str">
         <v>On-site</v>
@@ -6113,7 +6113,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L94" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4713648005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4699779005</v>
       </c>
       <c r="M94">
         <v>200</v>
@@ -6122,27 +6122,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O94" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P94" t="str">
         <v>Today</v>
       </c>
       <c r="Q94" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R94" t="str">
         <v>No</v>
       </c>
       <c r="S94">
-        <v>84</v>
+        <v>70</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>job-235e84a3</v>
+        <v>job-7d366400</v>
       </c>
       <c r="B95" t="str">
-        <v>Product Manager, Enterprise Core Platform</v>
+        <v>Product Manager of AI Applications, Global Public Sector</v>
       </c>
       <c r="C95" t="str">
         <v>Scale AI</v>
@@ -6151,7 +6151,7 @@
         <v>Wellfound</v>
       </c>
       <c r="E95" t="str">
-        <v>Technical Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F95" t="str">
         <v>3-6 yrs</v>
@@ -6160,10 +6160,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H95" t="str">
-        <v>New York, NY; San Francisco, CA</v>
+        <v>Riyadh, Saudi Arabia</v>
       </c>
       <c r="I95" t="str">
-        <v>San Francisco</v>
+        <v>Riyadh</v>
       </c>
       <c r="J95" t="str">
         <v>On-site</v>
@@ -6172,7 +6172,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L95" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4699779005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4650514005</v>
       </c>
       <c r="M95">
         <v>200</v>
@@ -6181,27 +6181,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O95" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P95" t="str">
         <v>Today</v>
       </c>
       <c r="Q95" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R95" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S95">
-        <v>53</v>
+        <v>43</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>job-7d366400</v>
+        <v>job-6c1eab2d</v>
       </c>
       <c r="B96" t="str">
-        <v>Product Manager of AI Applications, Global Public Sector</v>
+        <v>Senior AI Product Manager, Code</v>
       </c>
       <c r="C96" t="str">
         <v>Scale AI</v>
@@ -6210,19 +6210,19 @@
         <v>Wellfound</v>
       </c>
       <c r="E96" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F96" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G96" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H96" t="str">
-        <v>Riyadh, Saudi Arabia</v>
+        <v>New York, NY; San Francisco, CA</v>
       </c>
       <c r="I96" t="str">
-        <v>Riyadh</v>
+        <v>San Francisco</v>
       </c>
       <c r="J96" t="str">
         <v>On-site</v>
@@ -6231,7 +6231,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L96" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4650514005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4720501005</v>
       </c>
       <c r="M96">
         <v>200</v>
@@ -6240,27 +6240,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O96" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P96" t="str">
         <v>Today</v>
       </c>
       <c r="Q96" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R96" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S96">
-        <v>41</v>
+        <v>86</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>job-6c1eab2d</v>
+        <v>job-1310fa39</v>
       </c>
       <c r="B97" t="str">
-        <v>Senior AI Product Manager, Code</v>
+        <v>Senior AI Product Manager, Cybersecurity</v>
       </c>
       <c r="C97" t="str">
         <v>Scale AI</v>
@@ -6290,7 +6290,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L97" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4720501005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4720213005</v>
       </c>
       <c r="M97">
         <v>200</v>
@@ -6299,27 +6299,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O97" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P97" t="str">
         <v>Today</v>
       </c>
       <c r="Q97" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R97" t="str">
         <v>No</v>
       </c>
       <c r="S97">
-        <v>94</v>
+        <v>44</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>job-1310fa39</v>
+        <v>job-7ff81a54</v>
       </c>
       <c r="B98" t="str">
-        <v>Senior AI Product Manager, Cybersecurity</v>
+        <v>Senior AI Product Manager, Finance Agents</v>
       </c>
       <c r="C98" t="str">
         <v>Scale AI</v>
@@ -6337,7 +6337,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H98" t="str">
-        <v>New York, NY; San Francisco, CA</v>
+        <v>San Francisco, CA; New York, NY</v>
       </c>
       <c r="I98" t="str">
         <v>San Francisco</v>
@@ -6349,7 +6349,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L98" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4720213005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4611776005</v>
       </c>
       <c r="M98">
         <v>200</v>
@@ -6358,27 +6358,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O98" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P98" t="str">
         <v>Today</v>
       </c>
       <c r="Q98" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R98" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S98">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>job-7ff81a54</v>
+        <v>job-41be8c95</v>
       </c>
       <c r="B99" t="str">
-        <v>Senior AI Product Manager, Finance Agents</v>
+        <v>Senior AI Product Manager, Leaderboard</v>
       </c>
       <c r="C99" t="str">
         <v>Scale AI</v>
@@ -6396,7 +6396,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H99" t="str">
-        <v>San Francisco, CA; New York, NY</v>
+        <v>New York, NY; San Francisco, CA</v>
       </c>
       <c r="I99" t="str">
         <v>San Francisco</v>
@@ -6408,7 +6408,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L99" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4611776005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4720216005</v>
       </c>
       <c r="M99">
         <v>200</v>
@@ -6417,27 +6417,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O99" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P99" t="str">
         <v>Today</v>
       </c>
       <c r="Q99" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R99" t="str">
         <v>Yes</v>
       </c>
       <c r="S99">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>job-41be8c95</v>
+        <v>job-59abfadc</v>
       </c>
       <c r="B100" t="str">
-        <v>Senior AI Product Manager, Leaderboard</v>
+        <v>Staff Product Manager, Agentic Platform</v>
       </c>
       <c r="C100" t="str">
         <v>Scale AI</v>
@@ -6455,7 +6455,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H100" t="str">
-        <v>New York, NY; San Francisco, CA</v>
+        <v>New York, NY; San Francisco, CA; Washington, DC</v>
       </c>
       <c r="I100" t="str">
         <v>San Francisco</v>
@@ -6467,7 +6467,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L100" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4720216005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4612403005</v>
       </c>
       <c r="M100">
         <v>200</v>
@@ -6476,7 +6476,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O100" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P100" t="str">
         <v>Today</v>
@@ -6488,15 +6488,15 @@
         <v>No</v>
       </c>
       <c r="S100">
-        <v>88</v>
+        <v>94</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>job-59abfadc</v>
+        <v>job-3ad31a80</v>
       </c>
       <c r="B101" t="str">
-        <v>Staff Product Manager, Agentic Platform</v>
+        <v>Staff Product Manager, Gen AI</v>
       </c>
       <c r="C101" t="str">
         <v>Scale AI</v>
@@ -6514,7 +6514,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H101" t="str">
-        <v>New York, NY; San Francisco, CA; Washington, DC</v>
+        <v>New York, NY; San Francisco, CA</v>
       </c>
       <c r="I101" t="str">
         <v>San Francisco</v>
@@ -6526,7 +6526,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L101" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4612403005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4675842005</v>
       </c>
       <c r="M101">
         <v>200</v>
@@ -6535,7 +6535,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O101" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P101" t="str">
         <v>Today</v>
@@ -6547,15 +6547,15 @@
         <v>No</v>
       </c>
       <c r="S101">
-        <v>31</v>
+        <v>81</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>job-3ad31a80</v>
+        <v>job-20e060b6</v>
       </c>
       <c r="B102" t="str">
-        <v>Staff Product Manager, Gen AI</v>
+        <v>Staff Product Manager, Physical AI Data &amp; Robotics</v>
       </c>
       <c r="C102" t="str">
         <v>Scale AI</v>
@@ -6573,7 +6573,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H102" t="str">
-        <v>New York, NY; San Francisco, CA</v>
+        <v>San Francisco, CA</v>
       </c>
       <c r="I102" t="str">
         <v>San Francisco</v>
@@ -6585,7 +6585,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L102" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4675842005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4718559005</v>
       </c>
       <c r="M102">
         <v>200</v>
@@ -6594,7 +6594,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O102" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P102" t="str">
         <v>Today</v>
@@ -6603,18 +6603,18 @@
         <v>No</v>
       </c>
       <c r="R102" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S102">
-        <v>53</v>
+        <v>35</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>job-20e060b6</v>
+        <v>job-2ab7f7d1</v>
       </c>
       <c r="B103" t="str">
-        <v>Staff Product Manager, Physical AI Data &amp; Robotics</v>
+        <v>Staff Technical Product Manager</v>
       </c>
       <c r="C103" t="str">
         <v>Scale AI</v>
@@ -6632,10 +6632,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H103" t="str">
-        <v>San Francisco, CA</v>
+        <v>London, UK</v>
       </c>
       <c r="I103" t="str">
-        <v>San Francisco</v>
+        <v>London</v>
       </c>
       <c r="J103" t="str">
         <v>On-site</v>
@@ -6644,7 +6644,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L103" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4718559005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4683446005</v>
       </c>
       <c r="M103">
         <v>200</v>
@@ -6653,48 +6653,48 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O103" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P103" t="str">
         <v>Today</v>
       </c>
       <c r="Q103" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R103" t="str">
         <v>No</v>
       </c>
       <c r="S103">
-        <v>29</v>
+        <v>56</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>job-2ab7f7d1</v>
+        <v>job-58b32a73</v>
       </c>
       <c r="B104" t="str">
-        <v>Staff Technical Product Manager</v>
+        <v>Director of Product, Growth/AI</v>
       </c>
       <c r="C104" t="str">
-        <v>Scale AI</v>
+        <v>Brex</v>
       </c>
       <c r="D104" t="str">
         <v>Wellfound</v>
       </c>
       <c r="E104" t="str">
-        <v>Senior Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F104" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G104" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H104" t="str">
-        <v>London, UK</v>
+        <v>Vancouver, British Columbia, Canada</v>
       </c>
       <c r="I104" t="str">
-        <v>London</v>
+        <v>Vancouver</v>
       </c>
       <c r="J104" t="str">
         <v>On-site</v>
@@ -6703,7 +6703,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L104" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4683446005</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8433546002</v>
       </c>
       <c r="M104">
         <v>200</v>
@@ -6712,7 +6712,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O104" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P104" t="str">
         <v>Today</v>
@@ -6721,18 +6721,18 @@
         <v>Yes</v>
       </c>
       <c r="R104" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S104">
-        <v>59</v>
+        <v>39</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>job-58b32a73</v>
+        <v>job-6c147538</v>
       </c>
       <c r="B105" t="str">
-        <v>Director of Product, Growth/AI</v>
+        <v>Group Product Manager</v>
       </c>
       <c r="C105" t="str">
         <v>Brex</v>
@@ -6741,19 +6741,19 @@
         <v>Wellfound</v>
       </c>
       <c r="E105" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F105" t="str">
-        <v>8+ yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G105" t="str">
-        <v>8+ yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H105" t="str">
-        <v>New York, New York, United States</v>
+        <v>Seattle, Washington, United States</v>
       </c>
       <c r="I105" t="str">
-        <v>New York</v>
+        <v>Seattle</v>
       </c>
       <c r="J105" t="str">
         <v>On-site</v>
@@ -6762,7 +6762,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L105" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8433461002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8438582002</v>
       </c>
       <c r="M105">
         <v>200</v>
@@ -6771,7 +6771,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O105" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P105" t="str">
         <v>Today</v>
@@ -6783,15 +6783,15 @@
         <v>No</v>
       </c>
       <c r="S105">
-        <v>84</v>
+        <v>63</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>job-6c147538</v>
+        <v>job-4a5cf899</v>
       </c>
       <c r="B106" t="str">
-        <v>Group Product Manager</v>
+        <v>Senior Product Manager, AI</v>
       </c>
       <c r="C106" t="str">
         <v>Brex</v>
@@ -6800,19 +6800,19 @@
         <v>Wellfound</v>
       </c>
       <c r="E106" t="str">
-        <v>Product Lead / Director</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F106" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G106" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H106" t="str">
-        <v>Vancouver, British Columbia, Canada</v>
+        <v>Seattle, Washington, United States</v>
       </c>
       <c r="I106" t="str">
-        <v>Vancouver</v>
+        <v>Seattle</v>
       </c>
       <c r="J106" t="str">
         <v>On-site</v>
@@ -6821,7 +6821,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L106" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8438584002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8780828002</v>
       </c>
       <c r="M106">
         <v>200</v>
@@ -6830,27 +6830,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O106" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P106" t="str">
         <v>Today</v>
       </c>
       <c r="Q106" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R106" t="str">
         <v>No</v>
       </c>
       <c r="S106">
-        <v>81</v>
+        <v>50</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>job-4a5cf899</v>
+        <v>job-111c900b</v>
       </c>
       <c r="B107" t="str">
-        <v>Senior Product Manager, AI</v>
+        <v>Senior Product Manager, Travel</v>
       </c>
       <c r="C107" t="str">
         <v>Brex</v>
@@ -6880,7 +6880,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L107" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8780827002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8659249002</v>
       </c>
       <c r="M107">
         <v>200</v>
@@ -6889,27 +6889,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O107" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P107" t="str">
         <v>Today</v>
       </c>
       <c r="Q107" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R107" t="str">
         <v>No</v>
       </c>
       <c r="S107">
-        <v>25</v>
+        <v>85</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>job-111c900b</v>
+        <v>job-337165a7</v>
       </c>
       <c r="B108" t="str">
-        <v>Senior Product Manager, Travel</v>
+        <v>Staff Product Manager</v>
       </c>
       <c r="C108" t="str">
         <v>Brex</v>
@@ -6927,10 +6927,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H108" t="str">
-        <v>New York, New York, United States</v>
+        <v>Seattle, Washington, United States</v>
       </c>
       <c r="I108" t="str">
-        <v>New York</v>
+        <v>Seattle</v>
       </c>
       <c r="J108" t="str">
         <v>On-site</v>
@@ -6939,7 +6939,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L108" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8659251002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8432703002</v>
       </c>
       <c r="M108">
         <v>200</v>
@@ -6948,7 +6948,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O108" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P108" t="str">
         <v>Today</v>
@@ -6957,18 +6957,18 @@
         <v>No</v>
       </c>
       <c r="R108" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S108">
-        <v>30</v>
+        <v>69</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>job-337165a7</v>
+        <v>job-533982f5</v>
       </c>
       <c r="B109" t="str">
-        <v>Staff Product Manager</v>
+        <v>Staff Product Manager, AI</v>
       </c>
       <c r="C109" t="str">
         <v>Brex</v>
@@ -6986,10 +6986,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H109" t="str">
-        <v>Vancouver, British Columbia, Canada</v>
+        <v>New York, New York, United States</v>
       </c>
       <c r="I109" t="str">
-        <v>Vancouver</v>
+        <v>New York</v>
       </c>
       <c r="J109" t="str">
         <v>On-site</v>
@@ -6998,7 +6998,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L109" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8433764002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8780829002</v>
       </c>
       <c r="M109">
         <v>200</v>
@@ -7007,7 +7007,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O109" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P109" t="str">
         <v>Today</v>
@@ -7019,15 +7019,15 @@
         <v>No</v>
       </c>
       <c r="S109">
-        <v>50</v>
+        <v>33</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>job-533982f5</v>
+        <v>job-0f9c4e5d</v>
       </c>
       <c r="B110" t="str">
-        <v>Staff Product Manager, AI</v>
+        <v>Staff Product Manager, Card</v>
       </c>
       <c r="C110" t="str">
         <v>Brex</v>
@@ -7057,7 +7057,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L110" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8780829002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8659237002</v>
       </c>
       <c r="M110">
         <v>200</v>
@@ -7066,27 +7066,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O110" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P110" t="str">
         <v>Today</v>
       </c>
       <c r="Q110" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R110" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S110">
-        <v>74</v>
+        <v>28</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>job-0f9c4e5d</v>
+        <v>job-4401c5a9</v>
       </c>
       <c r="B111" t="str">
-        <v>Staff Product Manager, Card</v>
+        <v>Staff Product Manager, Embedded</v>
       </c>
       <c r="C111" t="str">
         <v>Brex</v>
@@ -7116,7 +7116,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L111" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8659221002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8659210002</v>
       </c>
       <c r="M111">
         <v>200</v>
@@ -7125,27 +7125,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O111" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P111" t="str">
         <v>Today</v>
       </c>
       <c r="Q111" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R111" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S111">
-        <v>25</v>
+        <v>46</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>job-4401c5a9</v>
+        <v>job-75398a6b</v>
       </c>
       <c r="B112" t="str">
-        <v>Staff Product Manager, Embedded</v>
+        <v>Staff Product Manager,  Embedded</v>
       </c>
       <c r="C112" t="str">
         <v>Brex</v>
@@ -7163,10 +7163,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H112" t="str">
-        <v>San Francisco, California, United States</v>
+        <v>New York, New York, United States</v>
       </c>
       <c r="I112" t="str">
-        <v>San Francisco</v>
+        <v>New York</v>
       </c>
       <c r="J112" t="str">
         <v>On-site</v>
@@ -7175,7 +7175,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L112" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8659204002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8659211002</v>
       </c>
       <c r="M112">
         <v>200</v>
@@ -7184,7 +7184,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O112" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P112" t="str">
         <v>Today</v>
@@ -7196,15 +7196,15 @@
         <v>No</v>
       </c>
       <c r="S112">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>job-75398a6b</v>
+        <v>job-0f02a1a8</v>
       </c>
       <c r="B113" t="str">
-        <v>Staff Product Manager,  Embedded</v>
+        <v>Staff Product Manager, Expenses</v>
       </c>
       <c r="C113" t="str">
         <v>Brex</v>
@@ -7234,7 +7234,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L113" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8659211002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8659242002</v>
       </c>
       <c r="M113">
         <v>200</v>
@@ -7243,27 +7243,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O113" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P113" t="str">
         <v>Today</v>
       </c>
       <c r="Q113" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R113" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S113">
-        <v>45</v>
+        <v>75</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>job-0f02a1a8</v>
+        <v>job-2239c52c</v>
       </c>
       <c r="B114" t="str">
-        <v>Staff Product Manager, Expenses</v>
+        <v>Staff Product Manager, Growth</v>
       </c>
       <c r="C114" t="str">
         <v>Brex</v>
@@ -7281,10 +7281,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H114" t="str">
-        <v>Seattle, Washington, United States</v>
+        <v>San Francisco, California, United States</v>
       </c>
       <c r="I114" t="str">
-        <v>Seattle</v>
+        <v>San Francisco</v>
       </c>
       <c r="J114" t="str">
         <v>On-site</v>
@@ -7293,7 +7293,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L114" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8659241002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8436527002</v>
       </c>
       <c r="M114">
         <v>200</v>
@@ -7302,7 +7302,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O114" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P114" t="str">
         <v>Today</v>
@@ -7311,39 +7311,39 @@
         <v>No</v>
       </c>
       <c r="R114" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S114">
-        <v>67</v>
+        <v>76</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>job-2239c52c</v>
+        <v>job-429ddf15</v>
       </c>
       <c r="B115" t="str">
-        <v>Staff Product Manager, Growth</v>
+        <v>Associate Product Manager, Intern</v>
       </c>
       <c r="C115" t="str">
-        <v>Brex</v>
+        <v>Duolingo</v>
       </c>
       <c r="D115" t="str">
         <v>Wellfound</v>
       </c>
       <c r="E115" t="str">
-        <v>Senior Product Manager</v>
+        <v>Associate Product Manager</v>
       </c>
       <c r="F115" t="str">
-        <v>5-8 yrs</v>
+        <v>1-3 yrs</v>
       </c>
       <c r="G115" t="str">
-        <v>5-8 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H115" t="str">
-        <v>Seattle, Washington, United States</v>
+        <v>Pittsburgh, PA</v>
       </c>
       <c r="I115" t="str">
-        <v>Seattle</v>
+        <v>Pittsburgh</v>
       </c>
       <c r="J115" t="str">
         <v>On-site</v>
@@ -7352,7 +7352,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L115" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8436530002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8806187002</v>
       </c>
       <c r="M115">
         <v>200</v>
@@ -7361,7 +7361,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O115" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P115" t="str">
         <v>Today</v>
@@ -7373,15 +7373,15 @@
         <v>No</v>
       </c>
       <c r="S115">
-        <v>86</v>
+        <v>29</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>job-429ddf15</v>
+        <v>job-1b56d1fb</v>
       </c>
       <c r="B116" t="str">
-        <v>Associate Product Manager, Intern</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="C116" t="str">
         <v>Duolingo</v>
@@ -7390,19 +7390,19 @@
         <v>Wellfound</v>
       </c>
       <c r="E116" t="str">
-        <v>Associate Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F116" t="str">
-        <v>1-3 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G116" t="str">
-        <v>0-2 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H116" t="str">
-        <v>Pittsburgh, PA</v>
+        <v>Beijing, China</v>
       </c>
       <c r="I116" t="str">
-        <v>Pittsburgh</v>
+        <v>Beijing</v>
       </c>
       <c r="J116" t="str">
         <v>On-site</v>
@@ -7411,7 +7411,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L116" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8806187002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8675670002</v>
       </c>
       <c r="M116">
         <v>200</v>
@@ -7420,7 +7420,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O116" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P116" t="str">
         <v>Today</v>
@@ -7429,18 +7429,18 @@
         <v>No</v>
       </c>
       <c r="R116" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S116">
-        <v>31</v>
+        <v>53</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>job-1b56d1fb</v>
+        <v>job-0ba5b818</v>
       </c>
       <c r="B117" t="str">
-        <v>Senior Product Manager</v>
+        <v>Senior Product Manager, DET</v>
       </c>
       <c r="C117" t="str">
         <v>Duolingo</v>
@@ -7458,10 +7458,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H117" t="str">
-        <v>Beijing, China</v>
+        <v>Pittsburgh, PA</v>
       </c>
       <c r="I117" t="str">
-        <v>Beijing</v>
+        <v>Pittsburgh</v>
       </c>
       <c r="J117" t="str">
         <v>On-site</v>
@@ -7470,7 +7470,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L117" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8675670002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8530395002</v>
       </c>
       <c r="M117">
         <v>200</v>
@@ -7479,27 +7479,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O117" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P117" t="str">
         <v>Today</v>
       </c>
       <c r="Q117" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R117" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S117">
-        <v>65</v>
+        <v>37</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>job-0ba5b818</v>
+        <v>job-25986280</v>
       </c>
       <c r="B118" t="str">
-        <v>Senior Product Manager, DET</v>
+        <v>Senior Product Manager, Growth</v>
       </c>
       <c r="C118" t="str">
         <v>Duolingo</v>
@@ -7529,7 +7529,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L118" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8530395002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8747171002</v>
       </c>
       <c r="M118">
         <v>200</v>
@@ -7538,7 +7538,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O118" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P118" t="str">
         <v>Today</v>
@@ -7550,15 +7550,15 @@
         <v>No</v>
       </c>
       <c r="S118">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>job-25986280</v>
+        <v>job-604bd697</v>
       </c>
       <c r="B119" t="str">
-        <v>Senior Product Manager, Growth</v>
+        <v>Senior Product Manager, Learning</v>
       </c>
       <c r="C119" t="str">
         <v>Duolingo</v>
@@ -7588,7 +7588,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L119" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8747275002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8816512002</v>
       </c>
       <c r="M119">
         <v>200</v>
@@ -7597,19 +7597,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O119" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P119" t="str">
         <v>Today</v>
       </c>
       <c r="Q119" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R119" t="str">
         <v>No</v>
       </c>
       <c r="S119">
-        <v>63</v>
+        <v>31</v>
       </c>
     </row>
     <row r="120">
@@ -7656,7 +7656,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O120" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P120" t="str">
         <v>Today</v>
@@ -7668,7 +7668,7 @@
         <v>No</v>
       </c>
       <c r="S120">
-        <v>70</v>
+        <v>86</v>
       </c>
     </row>
     <row r="121">
@@ -7715,19 +7715,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O121" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P121" t="str">
         <v>Today</v>
       </c>
       <c r="Q121" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R121" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S121">
-        <v>49</v>
+        <v>61</v>
       </c>
     </row>
     <row r="122">
@@ -7774,19 +7774,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O122" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P122" t="str">
         <v>Today</v>
       </c>
       <c r="Q122" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R122" t="str">
         <v>Yes</v>
       </c>
       <c r="S122">
-        <v>25</v>
+        <v>94</v>
       </c>
     </row>
     <row r="123">
@@ -7833,7 +7833,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O123" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P123" t="str">
         <v>Today</v>
@@ -7845,7 +7845,7 @@
         <v>No</v>
       </c>
       <c r="S123">
-        <v>41</v>
+        <v>93</v>
       </c>
     </row>
     <row r="124">
@@ -7892,19 +7892,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O124" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P124" t="str">
         <v>Today</v>
       </c>
       <c r="Q124" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R124" t="str">
         <v>Yes</v>
       </c>
       <c r="S124">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="125">
@@ -7951,7 +7951,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O125" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P125" t="str">
         <v>Today</v>
@@ -7960,10 +7960,10 @@
         <v>Yes</v>
       </c>
       <c r="R125" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S125">
-        <v>39</v>
+        <v>66</v>
       </c>
     </row>
     <row r="126">
@@ -8010,19 +8010,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O126" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P126" t="str">
         <v>Today</v>
       </c>
       <c r="Q126" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R126" t="str">
         <v>No</v>
       </c>
       <c r="S126">
-        <v>88</v>
+        <v>79</v>
       </c>
     </row>
     <row r="127">
@@ -8069,7 +8069,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O127" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P127" t="str">
         <v>Today</v>
@@ -8078,10 +8078,10 @@
         <v>No</v>
       </c>
       <c r="R127" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S127">
-        <v>31</v>
+        <v>72</v>
       </c>
     </row>
     <row r="128">
@@ -8128,7 +8128,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O128" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P128" t="str">
         <v>Today</v>
@@ -8140,7 +8140,7 @@
         <v>No</v>
       </c>
       <c r="S128">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="129">
@@ -8187,19 +8187,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O129" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P129" t="str">
         <v>Today</v>
       </c>
       <c r="Q129" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R129" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S129">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="130">
@@ -8246,7 +8246,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O130" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P130" t="str">
         <v>Today</v>
@@ -8255,10 +8255,10 @@
         <v>No</v>
       </c>
       <c r="R130" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S130">
-        <v>57</v>
+        <v>77</v>
       </c>
     </row>
     <row r="131">
@@ -8305,19 +8305,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O131" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P131" t="str">
         <v>Today</v>
       </c>
       <c r="Q131" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R131" t="str">
         <v>No</v>
       </c>
       <c r="S131">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="132">
@@ -8364,7 +8364,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O132" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P132" t="str">
         <v>Today</v>
@@ -8376,7 +8376,7 @@
         <v>No</v>
       </c>
       <c r="S132">
-        <v>66</v>
+        <v>38</v>
       </c>
     </row>
     <row r="133">
@@ -8423,7 +8423,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O133" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P133" t="str">
         <v>Today</v>
@@ -8435,7 +8435,7 @@
         <v>No</v>
       </c>
       <c r="S133">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="134">
@@ -8482,19 +8482,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O134" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P134" t="str">
         <v>Today</v>
       </c>
       <c r="Q134" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R134" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S134">
-        <v>94</v>
+        <v>40</v>
       </c>
     </row>
     <row r="135">
@@ -8541,19 +8541,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O135" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P135" t="str">
         <v>Today</v>
       </c>
       <c r="Q135" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R135" t="str">
         <v>No</v>
       </c>
       <c r="S135">
-        <v>57</v>
+        <v>41</v>
       </c>
     </row>
     <row r="136">
@@ -8600,7 +8600,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O136" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P136" t="str">
         <v>Today</v>
@@ -8609,10 +8609,10 @@
         <v>No</v>
       </c>
       <c r="R136" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S136">
-        <v>69</v>
+        <v>87</v>
       </c>
     </row>
     <row r="137">
@@ -8659,7 +8659,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O137" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P137" t="str">
         <v>Today</v>
@@ -8671,7 +8671,7 @@
         <v>No</v>
       </c>
       <c r="S137">
-        <v>79</v>
+        <v>31</v>
       </c>
     </row>
     <row r="138">
@@ -8718,19 +8718,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O138" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P138" t="str">
         <v>Today</v>
       </c>
       <c r="Q138" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R138" t="str">
         <v>No</v>
       </c>
       <c r="S138">
-        <v>82</v>
+        <v>44</v>
       </c>
     </row>
     <row r="139">
@@ -8777,19 +8777,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O139" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P139" t="str">
         <v>Today</v>
       </c>
       <c r="Q139" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R139" t="str">
         <v>No</v>
       </c>
       <c r="S139">
-        <v>42</v>
+        <v>78</v>
       </c>
     </row>
     <row r="140">
@@ -8836,7 +8836,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O140" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P140" t="str">
         <v>Today</v>
@@ -8848,7 +8848,7 @@
         <v>Yes</v>
       </c>
       <c r="S140">
-        <v>25</v>
+        <v>73</v>
       </c>
     </row>
     <row r="141">
@@ -8895,7 +8895,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O141" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P141" t="str">
         <v>Today</v>
@@ -8904,10 +8904,10 @@
         <v>No</v>
       </c>
       <c r="R141" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S141">
-        <v>48</v>
+        <v>32</v>
       </c>
     </row>
     <row r="142">
@@ -8954,7 +8954,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O142" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P142" t="str">
         <v>Today</v>
@@ -8963,10 +8963,10 @@
         <v>Yes</v>
       </c>
       <c r="R142" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S142">
-        <v>76</v>
+        <v>82</v>
       </c>
     </row>
     <row r="143">
@@ -9013,19 +9013,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O143" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P143" t="str">
         <v>Today</v>
       </c>
       <c r="Q143" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R143" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S143">
-        <v>63</v>
+        <v>32</v>
       </c>
     </row>
     <row r="144">
@@ -9072,19 +9072,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O144" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P144" t="str">
         <v>Today</v>
       </c>
       <c r="Q144" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R144" t="str">
         <v>No</v>
       </c>
       <c r="S144">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="145">
@@ -9131,19 +9131,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O145" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P145" t="str">
         <v>Today</v>
       </c>
       <c r="Q145" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R145" t="str">
         <v>No</v>
       </c>
       <c r="S145">
-        <v>55</v>
+        <v>40</v>
       </c>
     </row>
     <row r="146">
@@ -9190,7 +9190,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O146" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P146" t="str">
         <v>Today</v>
@@ -9199,18 +9199,18 @@
         <v>Yes</v>
       </c>
       <c r="R146" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S146">
-        <v>90</v>
+        <v>31</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>job-2ca475a2</v>
+        <v>job-3c3dabbf</v>
       </c>
       <c r="B147" t="str">
-        <v>Product Manager II, Content Compliance</v>
+        <v>Director of Product Management, Advertiser Growth</v>
       </c>
       <c r="C147" t="str">
         <v>Pinterest</v>
@@ -9219,28 +9219,28 @@
         <v>LinkedIn</v>
       </c>
       <c r="E147" t="str">
-        <v>Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F147" t="str">
-        <v>3-6 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G147" t="str">
-        <v>2-5 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H147" t="str">
-        <v>San Francisco, CA, US; Seattle, WA, US; Remote, CA, US</v>
+        <v>Palo Alto, CA, US; Seattle, WA, US; New York, NY, US</v>
       </c>
       <c r="I147" t="str">
-        <v>San Francisco</v>
+        <v>New York</v>
       </c>
       <c r="J147" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K147" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L147" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/7901910</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/8132504</v>
       </c>
       <c r="M147">
         <v>403</v>
@@ -9249,27 +9249,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O147" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P147" t="str">
         <v>Today</v>
       </c>
       <c r="Q147" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R147" t="str">
         <v>No</v>
       </c>
       <c r="S147">
-        <v>28</v>
+        <v>94</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>job-1e7e452c</v>
+        <v>job-2ca475a2</v>
       </c>
       <c r="B148" t="str">
-        <v>Product Manager II, Search Experience</v>
+        <v>Product Manager II, Content Compliance</v>
       </c>
       <c r="C148" t="str">
         <v>Pinterest</v>
@@ -9287,7 +9287,7 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H148" t="str">
-        <v>San Francisco, CA, US; Remote, US</v>
+        <v>San Francisco, CA, US; Seattle, WA, US; Remote, CA, US</v>
       </c>
       <c r="I148" t="str">
         <v>San Francisco</v>
@@ -9299,7 +9299,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L148" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/8042279</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/7901910</v>
       </c>
       <c r="M148">
         <v>403</v>
@@ -9308,27 +9308,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O148" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P148" t="str">
         <v>Today</v>
       </c>
       <c r="Q148" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R148" t="str">
         <v>No</v>
       </c>
       <c r="S148">
-        <v>80</v>
+        <v>43</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>job-65802650</v>
+        <v>job-1e7e452c</v>
       </c>
       <c r="B149" t="str">
-        <v>Sr. Product Manager, Core Saving Experience</v>
+        <v>Product Manager II, Search Experience</v>
       </c>
       <c r="C149" t="str">
         <v>Pinterest</v>
@@ -9337,7 +9337,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E149" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F149" t="str">
         <v>3-6 yrs</v>
@@ -9358,7 +9358,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L149" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/8046820</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/8042279</v>
       </c>
       <c r="M149">
         <v>403</v>
@@ -9367,7 +9367,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O149" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P149" t="str">
         <v>Today</v>
@@ -9376,18 +9376,18 @@
         <v>No</v>
       </c>
       <c r="R149" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S149">
-        <v>91</v>
+        <v>30</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>job-3070654d</v>
+        <v>job-65802650</v>
       </c>
       <c r="B150" t="str">
-        <v>Sr. Product Manager, Search Personalization</v>
+        <v>Sr. Product Manager, Core Saving Experience</v>
       </c>
       <c r="C150" t="str">
         <v>Pinterest</v>
@@ -9417,7 +9417,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L150" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/8015494</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/8046820</v>
       </c>
       <c r="M150">
         <v>403</v>
@@ -9426,27 +9426,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O150" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P150" t="str">
         <v>Today</v>
       </c>
       <c r="Q150" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R150" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S150">
-        <v>66</v>
+        <v>37</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>job-2683c45a</v>
+        <v>job-3070654d</v>
       </c>
       <c r="B151" t="str">
-        <v>Sr. Product Manager, TwoTwenty</v>
+        <v>Sr. Product Manager, Search Personalization</v>
       </c>
       <c r="C151" t="str">
         <v>Pinterest</v>
@@ -9476,7 +9476,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L151" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/8015519</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/8015494</v>
       </c>
       <c r="M151">
         <v>403</v>
@@ -9485,7 +9485,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O151" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P151" t="str">
         <v>Today</v>
@@ -9494,18 +9494,18 @@
         <v>No</v>
       </c>
       <c r="R151" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S151">
-        <v>85</v>
+        <v>64</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>job-04d22fdc</v>
+        <v>job-2683c45a</v>
       </c>
       <c r="B152" t="str">
-        <v>Staff Product Manager, Ads Measurement</v>
+        <v>Sr. Product Manager, TwoTwenty</v>
       </c>
       <c r="C152" t="str">
         <v>Pinterest</v>
@@ -9517,25 +9517,25 @@
         <v>Senior Product Manager</v>
       </c>
       <c r="F152" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G152" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H152" t="str">
-        <v>New York, NY, US</v>
+        <v>San Francisco, CA, US; Remote, US</v>
       </c>
       <c r="I152" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J152" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K152" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L152" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/7683962</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/8015519</v>
       </c>
       <c r="M152">
         <v>403</v>
@@ -9544,7 +9544,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O152" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P152" t="str">
         <v>Today</v>
@@ -9556,15 +9556,15 @@
         <v>No</v>
       </c>
       <c r="S152">
-        <v>58</v>
+        <v>87</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>job-336a1df9</v>
+        <v>job-04d22fdc</v>
       </c>
       <c r="B153" t="str">
-        <v>Staff Product Manager, Applied Science</v>
+        <v>Staff Product Manager, Ads Measurement</v>
       </c>
       <c r="C153" t="str">
         <v>Pinterest</v>
@@ -9582,19 +9582,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H153" t="str">
-        <v>San Francisco, CA, US; Remote, US</v>
+        <v>New York, NY, US</v>
       </c>
       <c r="I153" t="str">
-        <v>San Francisco</v>
+        <v>New York</v>
       </c>
       <c r="J153" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K153" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L153" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/8082033</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/7683962</v>
       </c>
       <c r="M153">
         <v>403</v>
@@ -9603,27 +9603,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O153" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P153" t="str">
         <v>Today</v>
       </c>
       <c r="Q153" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R153" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S153">
-        <v>82</v>
+        <v>69</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>job-0f93578d</v>
+        <v>job-336a1df9</v>
       </c>
       <c r="B154" t="str">
-        <v>Staff Product Manager, Billing</v>
+        <v>Staff Product Manager, Applied Science</v>
       </c>
       <c r="C154" t="str">
         <v>Pinterest</v>
@@ -9641,7 +9641,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H154" t="str">
-        <v>San Francisco, CA, US; Remote, CA, US</v>
+        <v>San Francisco, CA, US; Remote, US</v>
       </c>
       <c r="I154" t="str">
         <v>San Francisco</v>
@@ -9653,7 +9653,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L154" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/7955593</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/8082033</v>
       </c>
       <c r="M154">
         <v>403</v>
@@ -9662,7 +9662,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O154" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P154" t="str">
         <v>Today</v>
@@ -9674,15 +9674,15 @@
         <v>No</v>
       </c>
       <c r="S154">
-        <v>65</v>
+        <v>87</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>job-7b34548d</v>
+        <v>job-0f93578d</v>
       </c>
       <c r="B155" t="str">
-        <v>Staff Product Manager, Connections</v>
+        <v>Staff Product Manager, Billing</v>
       </c>
       <c r="C155" t="str">
         <v>Pinterest</v>
@@ -9700,7 +9700,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H155" t="str">
-        <v>San Francisco, CA, US; Remote, US</v>
+        <v>San Francisco, CA, US; Remote, CA, US</v>
       </c>
       <c r="I155" t="str">
         <v>San Francisco</v>
@@ -9712,7 +9712,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L155" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/7525112</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/7955593</v>
       </c>
       <c r="M155">
         <v>403</v>
@@ -9721,27 +9721,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O155" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P155" t="str">
         <v>Today</v>
       </c>
       <c r="Q155" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R155" t="str">
         <v>Yes</v>
       </c>
       <c r="S155">
-        <v>87</v>
+        <v>77</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>job-7e8b8408</v>
+        <v>job-7b34548d</v>
       </c>
       <c r="B156" t="str">
-        <v>Staff Product Manager, Programmatic Ads</v>
+        <v>Staff Product Manager, Connections</v>
       </c>
       <c r="C156" t="str">
         <v>Pinterest</v>
@@ -9759,7 +9759,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H156" t="str">
-        <v>San Francisco, CA, US; Remote, CA, US</v>
+        <v>San Francisco, CA, US; Remote, US</v>
       </c>
       <c r="I156" t="str">
         <v>San Francisco</v>
@@ -9771,7 +9771,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L156" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/7959458</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/7525112</v>
       </c>
       <c r="M156">
         <v>403</v>
@@ -9780,7 +9780,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O156" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P156" t="str">
         <v>Today</v>
@@ -9792,36 +9792,36 @@
         <v>No</v>
       </c>
       <c r="S156">
-        <v>55</v>
+        <v>38</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>job-7f4873ac</v>
+        <v>job-7e8b8408</v>
       </c>
       <c r="B157" t="str">
-        <v>Director of Product, Logistics</v>
+        <v>Staff Product Manager, Programmatic Ads</v>
       </c>
       <c r="C157" t="str">
-        <v>Instacart</v>
+        <v>Pinterest</v>
       </c>
       <c r="D157" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E157" t="str">
-        <v>Product Lead / Director</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F157" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G157" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H157" t="str">
-        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
+        <v>San Francisco, CA, US; Remote, CA, US</v>
       </c>
       <c r="I157" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J157" t="str">
         <v>Remote</v>
@@ -9830,16 +9830,16 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L157" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8198284</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/7959458</v>
       </c>
       <c r="M157">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N157" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O157" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P157" t="str">
         <v>Today</v>
@@ -9851,15 +9851,15 @@
         <v>No</v>
       </c>
       <c r="S157">
-        <v>86</v>
+        <v>44</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>job-6d240672</v>
+        <v>job-7f4873ac</v>
       </c>
       <c r="B158" t="str">
-        <v>Senior Product Manager, Ads Quality</v>
+        <v>Director of Product, Logistics</v>
       </c>
       <c r="C158" t="str">
         <v>Instacart</v>
@@ -9868,16 +9868,16 @@
         <v>LinkedIn</v>
       </c>
       <c r="E158" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F158" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G158" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H158" t="str">
-        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
+        <v>United States - Remote</v>
       </c>
       <c r="I158" t="str">
         <v>Remote</v>
@@ -9889,7 +9889,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L158" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8077512</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8198282</v>
       </c>
       <c r="M158">
         <v>200</v>
@@ -9898,27 +9898,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O158" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P158" t="str">
         <v>Today</v>
       </c>
       <c r="Q158" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R158" t="str">
         <v>No</v>
       </c>
       <c r="S158">
-        <v>44</v>
+        <v>90</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>job-2be59ce2</v>
+        <v>job-6d240672</v>
       </c>
       <c r="B159" t="str">
-        <v>Senior Product Manager, Advertiser Experience</v>
+        <v>Senior Product Manager, Ads Quality</v>
       </c>
       <c r="C159" t="str">
         <v>Instacart</v>
@@ -9948,7 +9948,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L159" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8120469</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8077510</v>
       </c>
       <c r="M159">
         <v>200</v>
@@ -9957,7 +9957,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O159" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P159" t="str">
         <v>Today</v>
@@ -9966,18 +9966,18 @@
         <v>Yes</v>
       </c>
       <c r="R159" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S159">
-        <v>78</v>
+        <v>26</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>job-6ddb2cbc</v>
+        <v>job-2be59ce2</v>
       </c>
       <c r="B160" t="str">
-        <v>Senior Product Manager, Catalog</v>
+        <v>Senior Product Manager, Advertiser Experience</v>
       </c>
       <c r="C160" t="str">
         <v>Instacart</v>
@@ -10007,7 +10007,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L160" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8143270</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8120469</v>
       </c>
       <c r="M160">
         <v>200</v>
@@ -10016,27 +10016,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O160" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P160" t="str">
         <v>Today</v>
       </c>
       <c r="Q160" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R160" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S160">
-        <v>29</v>
+        <v>61</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>job-0f329700</v>
+        <v>job-69064914</v>
       </c>
       <c r="B161" t="str">
-        <v>Senior Product Manager, Control Studio</v>
+        <v>Senior Product Manager, AI Control Studio</v>
       </c>
       <c r="C161" t="str">
         <v>Instacart</v>
@@ -10054,7 +10054,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H161" t="str">
-        <v>United States - Remote</v>
+        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
       </c>
       <c r="I161" t="str">
         <v>Remote</v>
@@ -10066,7 +10066,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L161" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8198159</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8198161</v>
       </c>
       <c r="M161">
         <v>200</v>
@@ -10075,27 +10075,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O161" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P161" t="str">
         <v>Today</v>
       </c>
       <c r="Q161" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R161" t="str">
         <v>No</v>
       </c>
       <c r="S161">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>job-3d0cfe30</v>
+        <v>job-6ddb2cbc</v>
       </c>
       <c r="B162" t="str">
-        <v>Senior Product Manager, Order Quality</v>
+        <v>Senior Product Manager, Catalog</v>
       </c>
       <c r="C162" t="str">
         <v>Instacart</v>
@@ -10113,7 +10113,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H162" t="str">
-        <v>United States - Remote</v>
+        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
       </c>
       <c r="I162" t="str">
         <v>Remote</v>
@@ -10125,7 +10125,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L162" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8203107</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8143272</v>
       </c>
       <c r="M162">
         <v>200</v>
@@ -10134,7 +10134,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O162" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P162" t="str">
         <v>Today</v>
@@ -10143,18 +10143,18 @@
         <v>No</v>
       </c>
       <c r="R162" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S162">
-        <v>54</v>
+        <v>28</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>job-2319ed86</v>
+        <v>job-3d0cfe30</v>
       </c>
       <c r="B163" t="str">
-        <v>Senior Product Manager, Retailer Platform</v>
+        <v>Senior Product Manager, Order Quality</v>
       </c>
       <c r="C163" t="str">
         <v>Instacart</v>
@@ -10172,7 +10172,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H163" t="str">
-        <v>United States - Remote</v>
+        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
       </c>
       <c r="I163" t="str">
         <v>Remote</v>
@@ -10184,7 +10184,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L163" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8014060</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8203109</v>
       </c>
       <c r="M163">
         <v>200</v>
@@ -10193,57 +10193,57 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O163" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P163" t="str">
         <v>Today</v>
       </c>
       <c r="Q163" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R163" t="str">
         <v>No</v>
       </c>
       <c r="S163">
-        <v>56</v>
+        <v>69</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>job-307baa4c</v>
+        <v>job-2319ed86</v>
       </c>
       <c r="B164" t="str">
-        <v>Product Manager II</v>
+        <v>Senior Product Manager, Retailer Platform</v>
       </c>
       <c r="C164" t="str">
-        <v>Razorpay</v>
+        <v>Instacart</v>
       </c>
       <c r="D164" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E164" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F164" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G164" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H164" t="str">
-        <v>Bengaluru</v>
+        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
       </c>
       <c r="I164" t="str">
-        <v>Bengaluru</v>
+        <v>Remote</v>
       </c>
       <c r="J164" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K164" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L164" t="str">
-        <v>https://boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4729519005</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8014062</v>
       </c>
       <c r="M164">
         <v>200</v>
@@ -10252,7 +10252,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O164" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P164" t="str">
         <v>Today</v>
@@ -10264,7 +10264,7 @@
         <v>Yes</v>
       </c>
       <c r="S164">
-        <v>48</v>
+        <v>68</v>
       </c>
     </row>
     <row r="165">
@@ -10311,7 +10311,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O165" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P165" t="str">
         <v>Today</v>
@@ -10323,7 +10323,7 @@
         <v>No</v>
       </c>
       <c r="S165">
-        <v>84</v>
+        <v>50</v>
       </c>
     </row>
     <row r="166">
@@ -10370,7 +10370,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O166" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P166" t="str">
         <v>Today</v>
@@ -10382,7 +10382,7 @@
         <v>Yes</v>
       </c>
       <c r="S166">
-        <v>74</v>
+        <v>94</v>
       </c>
     </row>
     <row r="167">
@@ -10429,7 +10429,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O167" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P167" t="str">
         <v>Today</v>
@@ -10441,7 +10441,7 @@
         <v>No</v>
       </c>
       <c r="S167">
-        <v>79</v>
+        <v>116</v>
       </c>
     </row>
     <row r="168">
@@ -10488,7 +10488,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O168" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P168" t="str">
         <v>Today</v>
@@ -10497,10 +10497,10 @@
         <v>Yes</v>
       </c>
       <c r="R168" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S168">
-        <v>88</v>
+        <v>76</v>
       </c>
     </row>
     <row r="169">
@@ -10547,7 +10547,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O169" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P169" t="str">
         <v>Today</v>
@@ -10559,7 +10559,7 @@
         <v>No</v>
       </c>
       <c r="S169">
-        <v>107</v>
+        <v>99</v>
       </c>
     </row>
     <row r="170">
@@ -10606,7 +10606,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O170" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P170" t="str">
         <v>Today</v>
@@ -10615,10 +10615,10 @@
         <v>Yes</v>
       </c>
       <c r="R170" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S170">
-        <v>59</v>
+        <v>92</v>
       </c>
     </row>
     <row r="171">
@@ -10665,7 +10665,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O171" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P171" t="str">
         <v>Today</v>
@@ -10677,7 +10677,7 @@
         <v>No</v>
       </c>
       <c r="S171">
-        <v>102</v>
+        <v>116</v>
       </c>
     </row>
     <row r="172">
@@ -10724,7 +10724,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O172" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P172" t="str">
         <v>Today</v>
@@ -10733,10 +10733,10 @@
         <v>Yes</v>
       </c>
       <c r="R172" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S172">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="173">
@@ -10783,7 +10783,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O173" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P173" t="str">
         <v>Today</v>
@@ -10795,7 +10795,7 @@
         <v>Yes</v>
       </c>
       <c r="S173">
-        <v>70</v>
+        <v>52</v>
       </c>
     </row>
     <row r="174">
@@ -10842,7 +10842,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O174" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P174" t="str">
         <v>Today</v>
@@ -10854,7 +10854,7 @@
         <v>No</v>
       </c>
       <c r="S174">
-        <v>116</v>
+        <v>85</v>
       </c>
     </row>
     <row r="175">
@@ -10901,7 +10901,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O175" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P175" t="str">
         <v>Today</v>
@@ -10913,7 +10913,7 @@
         <v>No</v>
       </c>
       <c r="S175">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="176">
@@ -10960,7 +10960,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O176" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P176" t="str">
         <v>Today</v>
@@ -10972,7 +10972,7 @@
         <v>Yes</v>
       </c>
       <c r="S176">
-        <v>65</v>
+        <v>90</v>
       </c>
     </row>
     <row r="177">
@@ -11019,7 +11019,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O177" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P177" t="str">
         <v>Today</v>
@@ -11028,10 +11028,10 @@
         <v>Yes</v>
       </c>
       <c r="R177" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S177">
-        <v>91</v>
+        <v>51</v>
       </c>
     </row>
     <row r="178">
@@ -11078,7 +11078,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O178" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P178" t="str">
         <v>Today</v>
@@ -11090,7 +11090,7 @@
         <v>Yes</v>
       </c>
       <c r="S178">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="179">
@@ -11137,7 +11137,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O179" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P179" t="str">
         <v>Today</v>
@@ -11149,7 +11149,7 @@
         <v>Yes</v>
       </c>
       <c r="S179">
-        <v>57</v>
+        <v>74</v>
       </c>
     </row>
     <row r="180">
@@ -11196,7 +11196,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O180" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P180" t="str">
         <v>Today</v>
@@ -11205,10 +11205,10 @@
         <v>Yes</v>
       </c>
       <c r="R180" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S180">
-        <v>80</v>
+        <v>92</v>
       </c>
     </row>
     <row r="181">
@@ -11255,7 +11255,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O181" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P181" t="str">
         <v>Today</v>
@@ -11267,7 +11267,7 @@
         <v>No</v>
       </c>
       <c r="S181">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="182">
@@ -11314,7 +11314,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O182" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P182" t="str">
         <v>Today</v>
@@ -11326,7 +11326,7 @@
         <v>Yes</v>
       </c>
       <c r="S182">
-        <v>75</v>
+        <v>87</v>
       </c>
     </row>
     <row r="183">
@@ -11373,7 +11373,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O183" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P183" t="str">
         <v>Today</v>
@@ -11385,7 +11385,7 @@
         <v>No</v>
       </c>
       <c r="S183">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="184">
@@ -11432,7 +11432,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O184" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P184" t="str">
         <v>Today</v>
@@ -11444,7 +11444,7 @@
         <v>No</v>
       </c>
       <c r="S184">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="185">
@@ -11491,7 +11491,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O185" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P185" t="str">
         <v>Today</v>
@@ -11500,10 +11500,10 @@
         <v>Yes</v>
       </c>
       <c r="R185" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S185">
-        <v>80</v>
+        <v>103</v>
       </c>
     </row>
     <row r="186">
@@ -11550,7 +11550,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O186" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P186" t="str">
         <v>Today</v>
@@ -11559,10 +11559,10 @@
         <v>Yes</v>
       </c>
       <c r="R186" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S186">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="187">
@@ -11609,7 +11609,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O187" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P187" t="str">
         <v>Today</v>
@@ -11618,10 +11618,10 @@
         <v>Yes</v>
       </c>
       <c r="R187" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S187">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="188">
@@ -11668,7 +11668,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O188" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P188" t="str">
         <v>Today</v>
@@ -11677,10 +11677,10 @@
         <v>Yes</v>
       </c>
       <c r="R188" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S188">
-        <v>94</v>
+        <v>59</v>
       </c>
     </row>
     <row r="189">
@@ -11727,7 +11727,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O189" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P189" t="str">
         <v>Today</v>
@@ -11736,10 +11736,10 @@
         <v>Yes</v>
       </c>
       <c r="R189" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S189">
-        <v>106</v>
+        <v>117</v>
       </c>
     </row>
     <row r="190">
@@ -11786,7 +11786,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O190" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P190" t="str">
         <v>Today</v>
@@ -11798,7 +11798,7 @@
         <v>Yes</v>
       </c>
       <c r="S190">
-        <v>118</v>
+        <v>69</v>
       </c>
     </row>
     <row r="191">
@@ -11845,7 +11845,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O191" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P191" t="str">
         <v>Today</v>
@@ -11857,15 +11857,15 @@
         <v>Yes</v>
       </c>
       <c r="S191">
-        <v>68</v>
+        <v>41</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>job-39d9f7fb</v>
+        <v>job-048a3bb1</v>
       </c>
       <c r="B192" t="str">
-        <v>Principal Product Manager - Audio and Media Playback</v>
+        <v>Head of Product Management - Artist Products</v>
       </c>
       <c r="C192" t="str">
         <v>Spotify</v>
@@ -11874,7 +11874,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E192" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F192" t="str">
         <v>5-8 yrs</v>
@@ -11883,10 +11883,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H192" t="str">
-        <v>Stockholm</v>
+        <v>New York, NY</v>
       </c>
       <c r="I192" t="str">
-        <v>Stockholm</v>
+        <v>New York</v>
       </c>
       <c r="J192" t="str">
         <v>On-site</v>
@@ -11895,7 +11895,7 @@
         <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L192" t="str">
-        <v>https://jobs.lever.co/spotify/080868dd-fc8c-4648-b6ab-6780d8ca3d63</v>
+        <v>https://jobs.lever.co/spotify/e2c7bbb8-f873-42c7-811f-0bd45bf452ae</v>
       </c>
       <c r="M192">
         <v>200</v>
@@ -11904,7 +11904,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O192" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P192" t="str">
         <v>Today</v>
@@ -11916,15 +11916,15 @@
         <v>No</v>
       </c>
       <c r="S192">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>job-61f86f2b</v>
+        <v>job-39d9f7fb</v>
       </c>
       <c r="B193" t="str">
-        <v>Product Manager - Customer Service Platform</v>
+        <v>Principal Product Manager - Audio and Media Playback</v>
       </c>
       <c r="C193" t="str">
         <v>Spotify</v>
@@ -11933,7 +11933,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E193" t="str">
-        <v>Technical Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F193" t="str">
         <v>5-8 yrs</v>
@@ -11942,10 +11942,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H193" t="str">
-        <v>London</v>
+        <v>Stockholm</v>
       </c>
       <c r="I193" t="str">
-        <v>London</v>
+        <v>Stockholm</v>
       </c>
       <c r="J193" t="str">
         <v>On-site</v>
@@ -11954,7 +11954,7 @@
         <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L193" t="str">
-        <v>https://jobs.lever.co/spotify/7f0a8faa-f4f5-4db9-9f51-4101d6a29b34</v>
+        <v>https://jobs.lever.co/spotify/080868dd-fc8c-4648-b6ab-6780d8ca3d63</v>
       </c>
       <c r="M193">
         <v>200</v>
@@ -11963,7 +11963,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O193" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P193" t="str">
         <v>Today</v>
@@ -11975,15 +11975,15 @@
         <v>No</v>
       </c>
       <c r="S193">
-        <v>81</v>
+        <v>72</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>job-1a230b4c</v>
+        <v>job-61f86f2b</v>
       </c>
       <c r="B194" t="str">
-        <v>Product Manager - Data Platform</v>
+        <v>Product Manager - Customer Service Platform</v>
       </c>
       <c r="C194" t="str">
         <v>Spotify</v>
@@ -12001,10 +12001,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H194" t="str">
-        <v>Toronto</v>
+        <v>London</v>
       </c>
       <c r="I194" t="str">
-        <v>Toronto</v>
+        <v>London</v>
       </c>
       <c r="J194" t="str">
         <v>On-site</v>
@@ -12013,7 +12013,7 @@
         <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L194" t="str">
-        <v>https://jobs.lever.co/spotify/03437e2a-2d5e-4593-9e97-11271014932e</v>
+        <v>https://jobs.lever.co/spotify/7f0a8faa-f4f5-4db9-9f51-4101d6a29b34</v>
       </c>
       <c r="M194">
         <v>200</v>
@@ -12022,7 +12022,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O194" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P194" t="str">
         <v>Today</v>
@@ -12034,15 +12034,15 @@
         <v>No</v>
       </c>
       <c r="S194">
-        <v>84</v>
+        <v>61</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>job-1ba340a4</v>
+        <v>job-1a230b4c</v>
       </c>
       <c r="B195" t="str">
-        <v>Senior Product Manager - Audiobooks Format Foundations</v>
+        <v>Product Manager - Data Platform</v>
       </c>
       <c r="C195" t="str">
         <v>Spotify</v>
@@ -12051,7 +12051,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E195" t="str">
-        <v>Senior Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F195" t="str">
         <v>5-8 yrs</v>
@@ -12060,10 +12060,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H195" t="str">
-        <v>London</v>
+        <v>Toronto</v>
       </c>
       <c r="I195" t="str">
-        <v>London</v>
+        <v>Toronto</v>
       </c>
       <c r="J195" t="str">
         <v>On-site</v>
@@ -12072,7 +12072,7 @@
         <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L195" t="str">
-        <v>https://jobs.lever.co/spotify/e7b01c1e-4246-4f31-83ea-9219c8b22c83</v>
+        <v>https://jobs.lever.co/spotify/03437e2a-2d5e-4593-9e97-11271014932e</v>
       </c>
       <c r="M195">
         <v>200</v>
@@ -12081,7 +12081,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O195" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P195" t="str">
         <v>Today</v>
@@ -12093,15 +12093,15 @@
         <v>No</v>
       </c>
       <c r="S195">
-        <v>44</v>
+        <v>56</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>job-3a0c9449</v>
+        <v>job-1ba340a4</v>
       </c>
       <c r="B196" t="str">
-        <v>Senior Product Manager - Subscriptions</v>
+        <v>Senior Product Manager - Audiobooks Format Foundations</v>
       </c>
       <c r="C196" t="str">
         <v>Spotify</v>
@@ -12131,7 +12131,7 @@
         <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L196" t="str">
-        <v>https://jobs.lever.co/spotify/a57db22d-dc0d-4f36-9a2e-34acdf1ec046</v>
+        <v>https://jobs.lever.co/spotify/e7b01c1e-4246-4f31-83ea-9219c8b22c83</v>
       </c>
       <c r="M196">
         <v>200</v>
@@ -12140,7 +12140,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O196" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P196" t="str">
         <v>Today</v>
@@ -12152,24 +12152,24 @@
         <v>No</v>
       </c>
       <c r="S196">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>job-4d0308c8</v>
+        <v>job-3a0c9449</v>
       </c>
       <c r="B197" t="str">
-        <v>Technical Program Manager (TPM)</v>
+        <v>Senior Product Manager - Subscriptions</v>
       </c>
       <c r="C197" t="str">
-        <v>Palantir</v>
+        <v>Spotify</v>
       </c>
       <c r="D197" t="str">
-        <v>Instahyre</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E197" t="str">
-        <v>Technical Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F197" t="str">
         <v>5-8 yrs</v>
@@ -12178,10 +12178,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H197" t="str">
-        <v>New York, NY</v>
+        <v>London</v>
       </c>
       <c r="I197" t="str">
-        <v>New York</v>
+        <v>London</v>
       </c>
       <c r="J197" t="str">
         <v>On-site</v>
@@ -12190,7 +12190,7 @@
         <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L197" t="str">
-        <v>https://jobs.lever.co/palantir/7eb0dedb-37ee-4175-b29f-10a9e4340076</v>
+        <v>https://jobs.lever.co/spotify/a57db22d-dc0d-4f36-9a2e-34acdf1ec046</v>
       </c>
       <c r="M197">
         <v>200</v>
@@ -12199,7 +12199,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O197" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P197" t="str">
         <v>Today</v>
@@ -12211,15 +12211,15 @@
         <v>No</v>
       </c>
       <c r="S197">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>job-593275cb</v>
+        <v>job-4d0308c8</v>
       </c>
       <c r="B198" t="str">
-        <v>Technical Program Manager (TPM) - Defense</v>
+        <v>Technical Program Manager (TPM)</v>
       </c>
       <c r="C198" t="str">
         <v>Palantir</v>
@@ -12237,10 +12237,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H198" t="str">
-        <v>Washington, D.C.</v>
+        <v>New York, NY</v>
       </c>
       <c r="I198" t="str">
-        <v>Washington</v>
+        <v>New York</v>
       </c>
       <c r="J198" t="str">
         <v>On-site</v>
@@ -12249,7 +12249,7 @@
         <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L198" t="str">
-        <v>https://jobs.lever.co/palantir/bd16f7ad-3bee-48fd-9902-b3ee9698b608</v>
+        <v>https://jobs.lever.co/palantir/7eb0dedb-37ee-4175-b29f-10a9e4340076</v>
       </c>
       <c r="M198">
         <v>200</v>
@@ -12258,7 +12258,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O198" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P198" t="str">
         <v>Today</v>
@@ -12270,45 +12270,45 @@
         <v>No</v>
       </c>
       <c r="S198">
-        <v>39</v>
+        <v>55</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>job-343d8912</v>
+        <v>job-593275cb</v>
       </c>
       <c r="B199" t="str">
-        <v>Associate Product Manager (APM) - Growth &amp; Merchant Onboarding</v>
+        <v>Technical Program Manager (TPM) - Defense</v>
       </c>
       <c r="C199" t="str">
-        <v>Razorpay</v>
+        <v>Palantir</v>
       </c>
       <c r="D199" t="str">
-        <v>LinkedIn</v>
+        <v>Instahyre</v>
       </c>
       <c r="E199" t="str">
-        <v>Associate Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F199" t="str">
-        <v>1-3 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G199" t="str">
-        <v>0-2 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H199" t="str">
-        <v>Bengaluru, Karnataka</v>
+        <v>Washington, D.C.</v>
       </c>
       <c r="I199" t="str">
-        <v>Bengaluru</v>
+        <v>Washington</v>
       </c>
       <c r="J199" t="str">
-        <v>Hybrid</v>
+        <v>On-site</v>
       </c>
       <c r="K199" t="str">
-        <v>₹18L - ₹26L PA + ESOPs</v>
+        <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L199" t="str">
-        <v>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited</v>
+        <v>https://jobs.lever.co/palantir/bd16f7ad-3bee-48fd-9902-b3ee9698b608</v>
       </c>
       <c r="M199">
         <v>200</v>
@@ -12317,7 +12317,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O199" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P199" t="str">
         <v>Today</v>
@@ -12326,33 +12326,33 @@
         <v>Yes</v>
       </c>
       <c r="R199" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S199">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>job-739e0b9f</v>
+        <v>job-343d8912</v>
       </c>
       <c r="B200" t="str">
-        <v>Senior Product Manager - Consumer Checkout &amp; Loyalty</v>
+        <v>Associate Product Manager (APM) - Growth &amp; Merchant Onboarding</v>
       </c>
       <c r="C200" t="str">
-        <v>Swiggy</v>
+        <v>Razorpay</v>
       </c>
       <c r="D200" t="str">
-        <v>Naukri</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E200" t="str">
-        <v>Senior Product Manager</v>
+        <v>Associate Product Manager</v>
       </c>
       <c r="F200" t="str">
-        <v>5-8 yrs</v>
+        <v>1-3 yrs</v>
       </c>
       <c r="G200" t="str">
-        <v>5-8 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H200" t="str">
         <v>Bengaluru, Karnataka</v>
@@ -12364,10 +12364,10 @@
         <v>Hybrid</v>
       </c>
       <c r="K200" t="str">
-        <v>₹45L - ₹65L PA + ESOPs</v>
+        <v>₹18L - ₹26L PA + ESOPs</v>
       </c>
       <c r="L200" t="str">
-        <v>https://careers.swiggy.com/</v>
+        <v>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited</v>
       </c>
       <c r="M200">
         <v>200</v>
@@ -12376,7 +12376,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O200" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P200" t="str">
         <v>Today</v>
@@ -12388,18 +12388,18 @@
         <v>Yes</v>
       </c>
       <c r="S200">
-        <v>115</v>
+        <v>42</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>job-66154b1b</v>
+        <v>job-739e0b9f</v>
       </c>
       <c r="B201" t="str">
-        <v>Senior Product Manager - 10-Minute Dark Store &amp; Logistics Dispatch</v>
+        <v>Senior Product Manager - Consumer Checkout &amp; Loyalty</v>
       </c>
       <c r="C201" t="str">
-        <v>Zepto</v>
+        <v>Swiggy</v>
       </c>
       <c r="D201" t="str">
         <v>Naukri</v>
@@ -12408,34 +12408,34 @@
         <v>Senior Product Manager</v>
       </c>
       <c r="F201" t="str">
-        <v>4-7 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G201" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H201" t="str">
-        <v>Mumbai, Maharashtra</v>
+        <v>Bengaluru, Karnataka</v>
       </c>
       <c r="I201" t="str">
-        <v>Mumbai</v>
+        <v>Bengaluru</v>
       </c>
       <c r="J201" t="str">
-        <v>On-site</v>
+        <v>Hybrid</v>
       </c>
       <c r="K201" t="str">
-        <v>₹42L - ₹60L PA + ESOPs</v>
+        <v>₹45L - ₹65L PA + ESOPs</v>
       </c>
       <c r="L201" t="str">
-        <v>https://www.zeptonow.com/careers</v>
+        <v>https://careers.swiggy.com/</v>
       </c>
       <c r="M201">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N201" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O201" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P201" t="str">
         <v>Today</v>
@@ -12447,18 +12447,18 @@
         <v>Yes</v>
       </c>
       <c r="S201">
-        <v>94</v>
+        <v>115</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>job-169943b4</v>
+        <v>job-66154b1b</v>
       </c>
       <c r="B202" t="str">
-        <v>Senior Product Manager - Customer Experience &amp; Live Support AI</v>
+        <v>Senior Product Manager - 10-Minute Dark Store &amp; Logistics Dispatch</v>
       </c>
       <c r="C202" t="str">
-        <v>Zomato</v>
+        <v>Zepto</v>
       </c>
       <c r="D202" t="str">
         <v>Naukri</v>
@@ -12467,34 +12467,34 @@
         <v>Senior Product Manager</v>
       </c>
       <c r="F202" t="str">
-        <v>5-8 yrs</v>
+        <v>4-7 yrs</v>
       </c>
       <c r="G202" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H202" t="str">
-        <v>Gurgaon, Haryana</v>
+        <v>Mumbai, Maharashtra</v>
       </c>
       <c r="I202" t="str">
-        <v>Gurgaon</v>
+        <v>Mumbai</v>
       </c>
       <c r="J202" t="str">
         <v>On-site</v>
       </c>
       <c r="K202" t="str">
-        <v>₹45L - ₹65L PA + ESOPs</v>
+        <v>₹42L - ₹60L PA + ESOPs</v>
       </c>
       <c r="L202" t="str">
-        <v>https://www.zomato.com/careers</v>
+        <v>https://www.zeptonow.com/careers</v>
       </c>
       <c r="M202">
-        <v>503</v>
+        <v>202</v>
       </c>
       <c r="N202" t="str">
-        <v>BROKEN / 404</v>
+        <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O202" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P202" t="str">
         <v>Today</v>
@@ -12506,54 +12506,54 @@
         <v>Yes</v>
       </c>
       <c r="S202">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>job-23756e58</v>
+        <v>job-169943b4</v>
       </c>
       <c r="B203" t="str">
-        <v>Associate Product Manager (APM) - Social Commerce &amp; Creator Tools</v>
+        <v>Senior Product Manager - Customer Experience &amp; Live Support AI</v>
       </c>
       <c r="C203" t="str">
-        <v>Meesho</v>
+        <v>Zomato</v>
       </c>
       <c r="D203" t="str">
         <v>Naukri</v>
       </c>
       <c r="E203" t="str">
-        <v>Associate Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F203" t="str">
-        <v>0-2 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G203" t="str">
-        <v>0-2 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H203" t="str">
-        <v>Bengaluru, Karnataka</v>
+        <v>Gurgaon, Haryana</v>
       </c>
       <c r="I203" t="str">
-        <v>Bengaluru</v>
+        <v>Gurgaon</v>
       </c>
       <c r="J203" t="str">
-        <v>Hybrid</v>
+        <v>On-site</v>
       </c>
       <c r="K203" t="str">
-        <v>₹18L - ₹25L PA + ESOPs</v>
+        <v>₹45L - ₹65L PA + ESOPs</v>
       </c>
       <c r="L203" t="str">
-        <v>https://www.meesho.io/jobs</v>
+        <v>https://www.zomato.com/careers</v>
       </c>
       <c r="M203">
-        <v>200</v>
+        <v>503</v>
       </c>
       <c r="N203" t="str">
-        <v>ACTIVE / 100% VALID</v>
+        <v>BROKEN / 404</v>
       </c>
       <c r="O203" t="str">
-        <v>2026-09-17</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P203" t="str">
         <v>Today</v>
@@ -12565,30 +12565,30 @@
         <v>Yes</v>
       </c>
       <c r="S203">
-        <v>65</v>
+        <v>95</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>job-6900691e</v>
+        <v>job-23756e58</v>
       </c>
       <c r="B204" t="str">
-        <v>Product Owner - Core Banking &amp; Credit Line Engine</v>
+        <v>Associate Product Manager (APM) - Social Commerce &amp; Creator Tools</v>
       </c>
       <c r="C204" t="str">
-        <v>CRED</v>
+        <v>Meesho</v>
       </c>
       <c r="D204" t="str">
-        <v>Instahyre</v>
+        <v>Naukri</v>
       </c>
       <c r="E204" t="str">
-        <v>Technical Product Manager</v>
+        <v>Associate Product Manager</v>
       </c>
       <c r="F204" t="str">
-        <v>3-6 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="G204" t="str">
-        <v>2-5 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H204" t="str">
         <v>Bengaluru, Karnataka</v>
@@ -12597,13 +12597,13 @@
         <v>Bengaluru</v>
       </c>
       <c r="J204" t="str">
-        <v>On-site</v>
+        <v>Hybrid</v>
       </c>
       <c r="K204" t="str">
-        <v>₹35L - ₹52L PA + ESOPs</v>
+        <v>₹18L - ₹25L PA + ESOPs</v>
       </c>
       <c r="L204" t="str">
-        <v>https://careers.cred.club/</v>
+        <v>https://www.meesho.io/jobs</v>
       </c>
       <c r="M204">
         <v>200</v>
@@ -12612,42 +12612,42 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O204" t="str">
-        <v>2026-09-16</v>
+        <v>2026-09-18</v>
       </c>
       <c r="P204" t="str">
-        <v>1d ago</v>
+        <v>Today</v>
       </c>
       <c r="Q204" t="str">
         <v>Yes</v>
       </c>
       <c r="R204" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S204">
-        <v>76</v>
+        <v>65</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>job-1e98cdb6</v>
+        <v>job-6900691e</v>
       </c>
       <c r="B205" t="str">
-        <v>Product Lead - Merchant QR, Soundbox &amp; Offline Payments Rails</v>
+        <v>Product Owner - Core Banking &amp; Credit Line Engine</v>
       </c>
       <c r="C205" t="str">
-        <v>PhonePe</v>
+        <v>CRED</v>
       </c>
       <c r="D205" t="str">
         <v>Instahyre</v>
       </c>
       <c r="E205" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F205" t="str">
-        <v>7-11 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G205" t="str">
-        <v>8+ yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H205" t="str">
         <v>Bengaluru, Karnataka</v>
@@ -12659,10 +12659,10 @@
         <v>On-site</v>
       </c>
       <c r="K205" t="str">
-        <v>₹65L - ₹90L PA + ESOPs</v>
+        <v>₹35L - ₹52L PA + ESOPs</v>
       </c>
       <c r="L205" t="str">
-        <v>https://www.phonepe.com/careers/</v>
+        <v>https://careers.cred.club/</v>
       </c>
       <c r="M205">
         <v>200</v>
@@ -12671,7 +12671,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O205" t="str">
-        <v>2026-09-16</v>
+        <v>2026-09-17</v>
       </c>
       <c r="P205" t="str">
         <v>1d ago</v>
@@ -12680,33 +12680,33 @@
         <v>Yes</v>
       </c>
       <c r="R205" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S205">
-        <v>125</v>
+        <v>76</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>job-6ee4d4a9</v>
+        <v>job-1e98cdb6</v>
       </c>
       <c r="B206" t="str">
-        <v>Product Manager - Supply Chain Forecasting &amp; Dynamic Pricing</v>
+        <v>Product Lead - Merchant QR, Soundbox &amp; Offline Payments Rails</v>
       </c>
       <c r="C206" t="str">
-        <v>Flipkart</v>
+        <v>PhonePe</v>
       </c>
       <c r="D206" t="str">
-        <v>IIMJobs</v>
+        <v>Instahyre</v>
       </c>
       <c r="E206" t="str">
         <v>AI &amp; Growth PM</v>
       </c>
       <c r="F206" t="str">
-        <v>3-6 yrs</v>
+        <v>7-11 yrs</v>
       </c>
       <c r="G206" t="str">
-        <v>2-5 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H206" t="str">
         <v>Bengaluru, Karnataka</v>
@@ -12715,13 +12715,13 @@
         <v>Bengaluru</v>
       </c>
       <c r="J206" t="str">
-        <v>Hybrid</v>
+        <v>On-site</v>
       </c>
       <c r="K206" t="str">
-        <v>₹32L - ₹48L PA + ESOPs</v>
+        <v>₹65L - ₹90L PA + ESOPs</v>
       </c>
       <c r="L206" t="str">
-        <v>https://www.flipkartcareers.com/</v>
+        <v>https://www.phonepe.com/careers/</v>
       </c>
       <c r="M206">
         <v>200</v>
@@ -12730,24 +12730,83 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O206" t="str">
-        <v>2026-09-16</v>
+        <v>2026-09-17</v>
       </c>
       <c r="P206" t="str">
         <v>1d ago</v>
       </c>
       <c r="Q206" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R206" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S206">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>job-6ee4d4a9</v>
+      </c>
+      <c r="B207" t="str">
+        <v>Product Manager - Supply Chain Forecasting &amp; Dynamic Pricing</v>
+      </c>
+      <c r="C207" t="str">
+        <v>Flipkart</v>
+      </c>
+      <c r="D207" t="str">
+        <v>IIMJobs</v>
+      </c>
+      <c r="E207" t="str">
+        <v>AI &amp; Growth PM</v>
+      </c>
+      <c r="F207" t="str">
+        <v>3-6 yrs</v>
+      </c>
+      <c r="G207" t="str">
+        <v>2-5 yrs</v>
+      </c>
+      <c r="H207" t="str">
+        <v>Bengaluru, Karnataka</v>
+      </c>
+      <c r="I207" t="str">
+        <v>Bengaluru</v>
+      </c>
+      <c r="J207" t="str">
+        <v>Hybrid</v>
+      </c>
+      <c r="K207" t="str">
+        <v>₹32L - ₹48L PA + ESOPs</v>
+      </c>
+      <c r="L207" t="str">
+        <v>https://www.flipkartcareers.com/</v>
+      </c>
+      <c r="M207">
+        <v>200</v>
+      </c>
+      <c r="N207" t="str">
+        <v>ACTIVE / 100% VALID</v>
+      </c>
+      <c r="O207" t="str">
+        <v>2026-09-17</v>
+      </c>
+      <c r="P207" t="str">
+        <v>1d ago</v>
+      </c>
+      <c r="Q207" t="str">
+        <v>No</v>
+      </c>
+      <c r="R207" t="str">
+        <v>No</v>
+      </c>
+      <c r="S207">
         <v>82</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S206"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S207"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -12811,10 +12870,10 @@
 3. Confirm fetch('/data/jobs.json') returns 200 OK</v>
       </c>
       <c r="F2" t="str">
-        <v>Returns array of 205 verified PM jobs</v>
+        <v>Returns array of 206 verified PM jobs</v>
       </c>
       <c r="G2" t="str">
-        <v>Successfully fetched 205 PM jobs without errors</v>
+        <v>Successfully fetched 206 PM jobs without errors</v>
       </c>
       <c r="H2" t="str">
         <v>PASS</v>
@@ -12893,10 +12952,10 @@
 2. Compare with rawJobs.length</v>
       </c>
       <c r="F5" t="str">
-        <v>Displays exactly 205</v>
+        <v>Displays exactly 206</v>
       </c>
       <c r="G5" t="str">
-        <v>Displays 205 active roles accurately</v>
+        <v>Displays 206 active roles accurately</v>
       </c>
       <c r="H5" t="str">
         <v>PASS</v>
@@ -12920,10 +12979,10 @@
 2. Count jobs posted today / marked Today</v>
       </c>
       <c r="F6" t="str">
-        <v>Displays +202</v>
+        <v>Displays +203</v>
       </c>
       <c r="G6" t="str">
-        <v>Displays +202 new opportunities tracked</v>
+        <v>Displays +203 new opportunities tracked</v>
       </c>
       <c r="H6" t="str">
         <v>PASS</v>
@@ -12947,10 +13006,10 @@
 2. Compute (remoteCount / totalJobs) * 100</v>
       </c>
       <c r="F7" t="str">
-        <v>Displays 62 (30%)</v>
+        <v>Displays 63 (31%)</v>
       </c>
       <c r="G7" t="str">
-        <v>Calculates 62 (30%) flexible roles accurately</v>
+        <v>Calculates 63 (31%) flexible roles accurately</v>
       </c>
       <c r="H7" t="str">
         <v>PASS</v>
@@ -12974,10 +13033,10 @@
 2. Check source counts</v>
       </c>
       <c r="F8" t="str">
-        <v>Displays LinkedIn with 102 roles</v>
+        <v>Displays LinkedIn with 104 roles</v>
       </c>
       <c r="G8" t="str">
-        <v>Displays LinkedIn (102 aggregated roles)</v>
+        <v>Displays LinkedIn (104 aggregated roles)</v>
       </c>
       <c r="H8" t="str">
         <v>PASS</v>
@@ -13499,7 +13558,7 @@
         <v>Open http://localhost:5173 in browser</v>
       </c>
       <c r="D2" t="str">
-        <v>Page loads instantly with Forest Green dark theme and 205 PM jobs</v>
+        <v>Page loads instantly with Forest Green dark theme and 206 PM jobs</v>
       </c>
       <c r="E2" t="str">
         <v>[ ] Completed</v>

--- a/GreenPath_PM_Jobs_Test_Report.xlsx
+++ b/GreenPath_PM_Jobs_Test_Report.xlsx
@@ -428,7 +428,7 @@
         <v>Test Execution Date</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-09-19T01:46:57.783Z</v>
+        <v>2026-09-20T01:49:14.497Z</v>
       </c>
     </row>
     <row r="4">
@@ -524,7 +524,7 @@
         <v>Cities Supported</v>
       </c>
       <c r="B15" t="str">
-        <v>San Francisco, Toronto, Dublin, N/A, New York, Remote, USA, London, Seattle, United States, Bengaluru, Paris, Menlo Park, Hybrid, In-Office, Spain, Switzerland, Ireland, Canada, Hungary, Greece, Riyadh, Vancouver, Pittsburgh, Beijing, Vienna, North America, Stockholm, Washington, Mumbai, Gurgaon</v>
+        <v>San Francisco, Toronto, Dublin, N/A, New York, Remote, USA, London, Seattle, United States, Bengaluru, Paris, Menlo Park, Hybrid, In-Office, Canada, Spain, Switzerland, Israel, Portugal, Greece, Doha, Vancouver, Pittsburgh, Beijing, Vienna, North America, Stockholm, Washington, Mumbai, Gurgaon</v>
       </c>
     </row>
     <row r="16">
@@ -694,7 +694,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O2" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P2" t="str">
         <v>Today</v>
@@ -703,10 +703,10 @@
         <v>No</v>
       </c>
       <c r="R2" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S2">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3">
@@ -753,19 +753,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O3" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P3" t="str">
         <v>Today</v>
       </c>
       <c r="Q3" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R3" t="str">
         <v>No</v>
       </c>
       <c r="S3">
-        <v>34</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
@@ -812,7 +812,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O4" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P4" t="str">
         <v>Today</v>
@@ -824,7 +824,7 @@
         <v>No</v>
       </c>
       <c r="S4">
-        <v>60</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
@@ -871,19 +871,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O5" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P5" t="str">
         <v>Today</v>
       </c>
       <c r="Q5" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R5" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S5">
-        <v>30</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6">
@@ -930,19 +930,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O6" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P6" t="str">
         <v>Today</v>
       </c>
       <c r="Q6" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R6" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S6">
-        <v>49</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7">
@@ -989,7 +989,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O7" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P7" t="str">
         <v>Today</v>
@@ -1001,7 +1001,7 @@
         <v>No</v>
       </c>
       <c r="S7">
-        <v>61</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8">
@@ -1048,19 +1048,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O8" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P8" t="str">
         <v>Today</v>
       </c>
       <c r="Q8" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R8" t="str">
         <v>No</v>
       </c>
       <c r="S8">
-        <v>26</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9">
@@ -1107,7 +1107,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O9" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P9" t="str">
         <v>Today</v>
@@ -1119,7 +1119,7 @@
         <v>Yes</v>
       </c>
       <c r="S9">
-        <v>35</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
@@ -1166,7 +1166,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O10" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P10" t="str">
         <v>Today</v>
@@ -1175,10 +1175,10 @@
         <v>Yes</v>
       </c>
       <c r="R10" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S10">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11">
@@ -1225,19 +1225,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O11" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P11" t="str">
         <v>Today</v>
       </c>
       <c r="Q11" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R11" t="str">
         <v>No</v>
       </c>
       <c r="S11">
-        <v>84</v>
+        <v>73</v>
       </c>
     </row>
     <row r="12">
@@ -1284,19 +1284,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O12" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P12" t="str">
         <v>Today</v>
       </c>
       <c r="Q12" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R12" t="str">
         <v>Yes</v>
       </c>
       <c r="S12">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13">
@@ -1343,7 +1343,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O13" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P13" t="str">
         <v>Today</v>
@@ -1352,10 +1352,10 @@
         <v>Yes</v>
       </c>
       <c r="R13" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S13">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14">
@@ -1402,16 +1402,16 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O14" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P14" t="str">
         <v>Today</v>
       </c>
       <c r="Q14" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R14" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S14">
         <v>62</v>
@@ -1461,7 +1461,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O15" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P15" t="str">
         <v>Today</v>
@@ -1473,7 +1473,7 @@
         <v>No</v>
       </c>
       <c r="S15">
-        <v>91</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1520,7 +1520,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O16" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P16" t="str">
         <v>Today</v>
@@ -1532,7 +1532,7 @@
         <v>No</v>
       </c>
       <c r="S16">
-        <v>69</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17">
@@ -1579,19 +1579,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O17" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P17" t="str">
         <v>Today</v>
       </c>
       <c r="Q17" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R17" t="str">
         <v>No</v>
       </c>
       <c r="S17">
-        <v>38</v>
+        <v>93</v>
       </c>
     </row>
     <row r="18">
@@ -1638,19 +1638,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O18" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P18" t="str">
         <v>Today</v>
       </c>
       <c r="Q18" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R18" t="str">
         <v>Yes</v>
       </c>
       <c r="S18">
-        <v>94</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19">
@@ -1697,7 +1697,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O19" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P19" t="str">
         <v>Today</v>
@@ -1706,10 +1706,10 @@
         <v>Yes</v>
       </c>
       <c r="R19" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S19">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="20">
@@ -1756,19 +1756,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O20" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P20" t="str">
         <v>Today</v>
       </c>
       <c r="Q20" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R20" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S20">
-        <v>31</v>
+        <v>91</v>
       </c>
     </row>
     <row r="21">
@@ -1815,19 +1815,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O21" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P21" t="str">
         <v>Today</v>
       </c>
       <c r="Q21" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R21" t="str">
         <v>No</v>
       </c>
       <c r="S21">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22">
@@ -1874,19 +1874,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O22" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P22" t="str">
         <v>Today</v>
       </c>
       <c r="Q22" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R22" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S22">
-        <v>78</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23">
@@ -1933,19 +1933,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O23" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P23" t="str">
         <v>Today</v>
       </c>
       <c r="Q23" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R23" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S23">
-        <v>50</v>
+        <v>71</v>
       </c>
     </row>
     <row r="24">
@@ -1992,19 +1992,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O24" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P24" t="str">
         <v>Today</v>
       </c>
       <c r="Q24" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R24" t="str">
         <v>No</v>
       </c>
       <c r="S24">
-        <v>91</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25">
@@ -2030,10 +2030,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H25" t="str">
-        <v>London</v>
+        <v>Dublin</v>
       </c>
       <c r="I25" t="str">
-        <v>London</v>
+        <v>Dublin</v>
       </c>
       <c r="J25" t="str">
         <v>On-site</v>
@@ -2042,7 +2042,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L25" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/8142649</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/7737526</v>
       </c>
       <c r="M25">
         <v>200</v>
@@ -2051,7 +2051,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O25" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P25" t="str">
         <v>Today</v>
@@ -2063,7 +2063,7 @@
         <v>Yes</v>
       </c>
       <c r="S25">
-        <v>62</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
@@ -2110,19 +2110,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O26" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P26" t="str">
         <v>Today</v>
       </c>
       <c r="Q26" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R26" t="str">
         <v>No</v>
       </c>
       <c r="S26">
-        <v>56</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27">
@@ -2169,7 +2169,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O27" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P27" t="str">
         <v>Today</v>
@@ -2181,7 +2181,7 @@
         <v>No</v>
       </c>
       <c r="S27">
-        <v>87</v>
+        <v>25</v>
       </c>
     </row>
     <row r="28">
@@ -2228,19 +2228,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O28" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P28" t="str">
         <v>Today</v>
       </c>
       <c r="Q28" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R28" t="str">
         <v>No</v>
       </c>
       <c r="S28">
-        <v>38</v>
+        <v>71</v>
       </c>
     </row>
     <row r="29">
@@ -2287,7 +2287,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O29" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P29" t="str">
         <v>Today</v>
@@ -2299,7 +2299,7 @@
         <v>No</v>
       </c>
       <c r="S29">
-        <v>51</v>
+        <v>43</v>
       </c>
     </row>
     <row r="30">
@@ -2346,7 +2346,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O30" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P30" t="str">
         <v>Today</v>
@@ -2355,10 +2355,10 @@
         <v>No</v>
       </c>
       <c r="R30" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S30">
-        <v>90</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31">
@@ -2405,19 +2405,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O31" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P31" t="str">
         <v>Today</v>
       </c>
       <c r="Q31" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R31" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S31">
-        <v>71</v>
+        <v>50</v>
       </c>
     </row>
     <row r="32">
@@ -2464,7 +2464,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O32" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P32" t="str">
         <v>Today</v>
@@ -2473,10 +2473,10 @@
         <v>No</v>
       </c>
       <c r="R32" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S32">
-        <v>79</v>
+        <v>37</v>
       </c>
     </row>
     <row r="33">
@@ -2523,7 +2523,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O33" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P33" t="str">
         <v>Today</v>
@@ -2535,7 +2535,7 @@
         <v>No</v>
       </c>
       <c r="S33">
-        <v>92</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34">
@@ -2582,19 +2582,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O34" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P34" t="str">
         <v>Today</v>
       </c>
       <c r="Q34" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R34" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S34">
-        <v>64</v>
+        <v>32</v>
       </c>
     </row>
     <row r="35">
@@ -2641,19 +2641,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O35" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P35" t="str">
         <v>Today</v>
       </c>
       <c r="Q35" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R35" t="str">
         <v>No</v>
       </c>
       <c r="S35">
-        <v>93</v>
+        <v>26</v>
       </c>
     </row>
     <row r="36">
@@ -2700,19 +2700,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O36" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P36" t="str">
         <v>Today</v>
       </c>
       <c r="Q36" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R36" t="str">
         <v>No</v>
       </c>
       <c r="S36">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37">
@@ -2759,19 +2759,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O37" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P37" t="str">
         <v>Today</v>
       </c>
       <c r="Q37" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R37" t="str">
         <v>No</v>
       </c>
       <c r="S37">
-        <v>73</v>
+        <v>50</v>
       </c>
     </row>
     <row r="38">
@@ -2818,7 +2818,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O38" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P38" t="str">
         <v>Today</v>
@@ -2827,10 +2827,10 @@
         <v>Yes</v>
       </c>
       <c r="R38" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S38">
-        <v>38</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39">
@@ -2877,7 +2877,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O39" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P39" t="str">
         <v>Today</v>
@@ -2889,7 +2889,7 @@
         <v>No</v>
       </c>
       <c r="S39">
-        <v>80</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40">
@@ -2936,7 +2936,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O40" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P40" t="str">
         <v>Today</v>
@@ -2945,10 +2945,10 @@
         <v>No</v>
       </c>
       <c r="R40" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S40">
-        <v>66</v>
+        <v>53</v>
       </c>
     </row>
     <row r="41">
@@ -2995,19 +2995,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O41" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P41" t="str">
         <v>Today</v>
       </c>
       <c r="Q41" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R41" t="str">
         <v>Yes</v>
       </c>
       <c r="S41">
-        <v>93</v>
+        <v>81</v>
       </c>
     </row>
     <row r="42">
@@ -3033,10 +3033,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H42" t="str">
-        <v>Boston, Massachusetts, USA; New York, New York, USA</v>
+        <v>Paris, France</v>
       </c>
       <c r="I42" t="str">
-        <v>New York</v>
+        <v>Paris</v>
       </c>
       <c r="J42" t="str">
         <v>On-site</v>
@@ -3045,7 +3045,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L42" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/7982288</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/8012549</v>
       </c>
       <c r="M42">
         <v>200</v>
@@ -3054,7 +3054,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O42" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P42" t="str">
         <v>Today</v>
@@ -3066,7 +3066,7 @@
         <v>No</v>
       </c>
       <c r="S42">
-        <v>45</v>
+        <v>57</v>
       </c>
     </row>
     <row r="43">
@@ -3113,19 +3113,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O43" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P43" t="str">
         <v>Today</v>
       </c>
       <c r="Q43" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R43" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S43">
-        <v>58</v>
+        <v>39</v>
       </c>
     </row>
     <row r="44">
@@ -3172,7 +3172,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O44" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P44" t="str">
         <v>Today</v>
@@ -3184,7 +3184,7 @@
         <v>No</v>
       </c>
       <c r="S44">
-        <v>69</v>
+        <v>43</v>
       </c>
     </row>
     <row r="45">
@@ -3231,19 +3231,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O45" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P45" t="str">
         <v>Today</v>
       </c>
       <c r="Q45" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R45" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S45">
-        <v>71</v>
+        <v>30</v>
       </c>
     </row>
     <row r="46">
@@ -3290,19 +3290,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O46" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P46" t="str">
         <v>Today</v>
       </c>
       <c r="Q46" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R46" t="str">
         <v>Yes</v>
       </c>
       <c r="S46">
-        <v>90</v>
+        <v>67</v>
       </c>
     </row>
     <row r="47">
@@ -3349,7 +3349,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O47" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P47" t="str">
         <v>Today</v>
@@ -3358,10 +3358,10 @@
         <v>No</v>
       </c>
       <c r="R47" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S47">
-        <v>52</v>
+        <v>27</v>
       </c>
     </row>
     <row r="48">
@@ -3408,7 +3408,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O48" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P48" t="str">
         <v>Today</v>
@@ -3420,7 +3420,7 @@
         <v>No</v>
       </c>
       <c r="S48">
-        <v>66</v>
+        <v>35</v>
       </c>
     </row>
     <row r="49">
@@ -3467,19 +3467,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O49" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P49" t="str">
         <v>Today</v>
       </c>
       <c r="Q49" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R49" t="str">
         <v>No</v>
       </c>
       <c r="S49">
-        <v>26</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50">
@@ -3526,19 +3526,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O50" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P50" t="str">
         <v>Today</v>
       </c>
       <c r="Q50" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R50" t="str">
         <v>No</v>
       </c>
       <c r="S50">
-        <v>84</v>
+        <v>59</v>
       </c>
     </row>
     <row r="51">
@@ -3585,19 +3585,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O51" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P51" t="str">
         <v>Today</v>
       </c>
       <c r="Q51" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R51" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S51">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52">
@@ -3644,19 +3644,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O52" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P52" t="str">
         <v>Today</v>
       </c>
       <c r="Q52" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R52" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S52">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53">
@@ -3703,7 +3703,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O53" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P53" t="str">
         <v>Today</v>
@@ -3715,7 +3715,7 @@
         <v>No</v>
       </c>
       <c r="S53">
-        <v>59</v>
+        <v>92</v>
       </c>
     </row>
     <row r="54">
@@ -3762,19 +3762,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O54" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P54" t="str">
         <v>Today</v>
       </c>
       <c r="Q54" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R54" t="str">
         <v>Yes</v>
       </c>
       <c r="S54">
-        <v>41</v>
+        <v>81</v>
       </c>
     </row>
     <row r="55">
@@ -3821,7 +3821,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O55" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P55" t="str">
         <v>Today</v>
@@ -3830,10 +3830,10 @@
         <v>No</v>
       </c>
       <c r="R55" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S55">
-        <v>68</v>
+        <v>94</v>
       </c>
     </row>
     <row r="56">
@@ -3880,19 +3880,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O56" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P56" t="str">
         <v>Today</v>
       </c>
       <c r="Q56" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R56" t="str">
         <v>No</v>
       </c>
       <c r="S56">
-        <v>54</v>
+        <v>75</v>
       </c>
     </row>
     <row r="57">
@@ -3939,7 +3939,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O57" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P57" t="str">
         <v>Today</v>
@@ -3951,7 +3951,7 @@
         <v>No</v>
       </c>
       <c r="S57">
-        <v>48</v>
+        <v>65</v>
       </c>
     </row>
     <row r="58">
@@ -3998,7 +3998,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O58" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P58" t="str">
         <v>Today</v>
@@ -4010,7 +4010,7 @@
         <v>No</v>
       </c>
       <c r="S58">
-        <v>44</v>
+        <v>66</v>
       </c>
     </row>
     <row r="59">
@@ -4057,7 +4057,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O59" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P59" t="str">
         <v>Today</v>
@@ -4066,10 +4066,10 @@
         <v>Yes</v>
       </c>
       <c r="R59" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S59">
-        <v>87</v>
+        <v>62</v>
       </c>
     </row>
     <row r="60">
@@ -4116,7 +4116,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O60" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P60" t="str">
         <v>Today</v>
@@ -4128,7 +4128,7 @@
         <v>No</v>
       </c>
       <c r="S60">
-        <v>67</v>
+        <v>29</v>
       </c>
     </row>
     <row r="61">
@@ -4175,19 +4175,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O61" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P61" t="str">
         <v>Today</v>
       </c>
       <c r="Q61" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R61" t="str">
         <v>No</v>
       </c>
       <c r="S61">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="62">
@@ -4234,19 +4234,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O62" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P62" t="str">
         <v>Today</v>
       </c>
       <c r="Q62" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R62" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S62">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="63">
@@ -4293,19 +4293,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O63" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P63" t="str">
         <v>Today</v>
       </c>
       <c r="Q63" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R63" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S63">
-        <v>80</v>
+        <v>30</v>
       </c>
     </row>
     <row r="64">
@@ -4352,19 +4352,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O64" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P64" t="str">
         <v>Today</v>
       </c>
       <c r="Q64" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R64" t="str">
         <v>No</v>
       </c>
       <c r="S64">
-        <v>81</v>
+        <v>93</v>
       </c>
     </row>
     <row r="65">
@@ -4411,19 +4411,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O65" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P65" t="str">
         <v>Today</v>
       </c>
       <c r="Q65" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R65" t="str">
         <v>No</v>
       </c>
       <c r="S65">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="66">
@@ -4470,19 +4470,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O66" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P66" t="str">
         <v>Today</v>
       </c>
       <c r="Q66" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R66" t="str">
         <v>No</v>
       </c>
       <c r="S66">
-        <v>52</v>
+        <v>76</v>
       </c>
     </row>
     <row r="67">
@@ -4529,19 +4529,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O67" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P67" t="str">
         <v>Today</v>
       </c>
       <c r="Q67" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R67" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S67">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="68">
@@ -4588,7 +4588,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O68" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P68" t="str">
         <v>Today</v>
@@ -4600,7 +4600,7 @@
         <v>No</v>
       </c>
       <c r="S68">
-        <v>72</v>
+        <v>46</v>
       </c>
     </row>
     <row r="69">
@@ -4647,7 +4647,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O69" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P69" t="str">
         <v>Today</v>
@@ -4656,10 +4656,10 @@
         <v>Yes</v>
       </c>
       <c r="R69" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S69">
-        <v>84</v>
+        <v>88</v>
       </c>
     </row>
     <row r="70">
@@ -4706,19 +4706,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O70" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P70" t="str">
         <v>Today</v>
       </c>
       <c r="Q70" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R70" t="str">
         <v>Yes</v>
       </c>
       <c r="S70">
-        <v>45</v>
+        <v>58</v>
       </c>
     </row>
     <row r="71">
@@ -4765,7 +4765,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O71" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P71" t="str">
         <v>Today</v>
@@ -4774,10 +4774,10 @@
         <v>Yes</v>
       </c>
       <c r="R71" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S71">
-        <v>85</v>
+        <v>48</v>
       </c>
     </row>
     <row r="72">
@@ -4824,7 +4824,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O72" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P72" t="str">
         <v>Today</v>
@@ -4833,10 +4833,10 @@
         <v>No</v>
       </c>
       <c r="R72" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S72">
-        <v>45</v>
+        <v>27</v>
       </c>
     </row>
     <row r="73">
@@ -4883,7 +4883,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O73" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P73" t="str">
         <v>Today</v>
@@ -4895,7 +4895,7 @@
         <v>No</v>
       </c>
       <c r="S73">
-        <v>36</v>
+        <v>92</v>
       </c>
     </row>
     <row r="74">
@@ -4942,19 +4942,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O74" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P74" t="str">
         <v>Today</v>
       </c>
       <c r="Q74" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R74" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S74">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="75">
@@ -5001,7 +5001,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O75" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P75" t="str">
         <v>Today</v>
@@ -5010,10 +5010,10 @@
         <v>No</v>
       </c>
       <c r="R75" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S75">
-        <v>68</v>
+        <v>26</v>
       </c>
     </row>
     <row r="76">
@@ -5060,7 +5060,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O76" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P76" t="str">
         <v>Today</v>
@@ -5072,7 +5072,7 @@
         <v>No</v>
       </c>
       <c r="S76">
-        <v>54</v>
+        <v>65</v>
       </c>
     </row>
     <row r="77">
@@ -5119,19 +5119,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O77" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P77" t="str">
         <v>Today</v>
       </c>
       <c r="Q77" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R77" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S77">
-        <v>68</v>
+        <v>93</v>
       </c>
     </row>
     <row r="78">
@@ -5178,19 +5178,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O78" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P78" t="str">
         <v>Today</v>
       </c>
       <c r="Q78" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R78" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S78">
-        <v>56</v>
+        <v>46</v>
       </c>
     </row>
     <row r="79">
@@ -5237,19 +5237,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O79" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P79" t="str">
         <v>Today</v>
       </c>
       <c r="Q79" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R79" t="str">
         <v>No</v>
       </c>
       <c r="S79">
-        <v>70</v>
+        <v>59</v>
       </c>
     </row>
     <row r="80">
@@ -5296,7 +5296,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O80" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P80" t="str">
         <v>Today</v>
@@ -5308,7 +5308,7 @@
         <v>Yes</v>
       </c>
       <c r="S80">
-        <v>28</v>
+        <v>45</v>
       </c>
     </row>
     <row r="81">
@@ -5334,10 +5334,10 @@
         <v>8+ yrs</v>
       </c>
       <c r="H81" t="str">
-        <v>United States</v>
+        <v>Canada</v>
       </c>
       <c r="I81" t="str">
-        <v>United States</v>
+        <v>Canada</v>
       </c>
       <c r="J81" t="str">
         <v>On-site</v>
@@ -5346,7 +5346,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L81" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/7602101</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8070011</v>
       </c>
       <c r="M81">
         <v>200</v>
@@ -5355,7 +5355,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O81" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P81" t="str">
         <v>Today</v>
@@ -5414,19 +5414,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O82" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P82" t="str">
         <v>Today</v>
       </c>
       <c r="Q82" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R82" t="str">
         <v>Yes</v>
       </c>
       <c r="S82">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="83">
@@ -5473,7 +5473,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O83" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P83" t="str">
         <v>Today</v>
@@ -5485,7 +5485,7 @@
         <v>No</v>
       </c>
       <c r="S83">
-        <v>69</v>
+        <v>51</v>
       </c>
     </row>
     <row r="84">
@@ -5532,19 +5532,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O84" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P84" t="str">
         <v>Today</v>
       </c>
       <c r="Q84" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R84" t="str">
         <v>No</v>
       </c>
       <c r="S84">
-        <v>92</v>
+        <v>54</v>
       </c>
     </row>
     <row r="85">
@@ -5570,10 +5570,10 @@
         <v>8+ yrs</v>
       </c>
       <c r="H85" t="str">
-        <v>Ireland</v>
+        <v>Israel</v>
       </c>
       <c r="I85" t="str">
-        <v>Ireland</v>
+        <v>Israel</v>
       </c>
       <c r="J85" t="str">
         <v>On-site</v>
@@ -5582,7 +5582,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L85" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8155326</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8155328</v>
       </c>
       <c r="M85">
         <v>200</v>
@@ -5591,19 +5591,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O85" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P85" t="str">
         <v>Today</v>
       </c>
       <c r="Q85" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R85" t="str">
         <v>No</v>
       </c>
       <c r="S85">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="86">
@@ -5629,10 +5629,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H86" t="str">
-        <v>United States</v>
+        <v>Canada</v>
       </c>
       <c r="I86" t="str">
-        <v>United States</v>
+        <v>Canada</v>
       </c>
       <c r="J86" t="str">
         <v>On-site</v>
@@ -5641,7 +5641,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L86" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8214106</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8214187</v>
       </c>
       <c r="M86">
         <v>200</v>
@@ -5650,7 +5650,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O86" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P86" t="str">
         <v>Today</v>
@@ -5662,7 +5662,7 @@
         <v>No</v>
       </c>
       <c r="S86">
-        <v>37</v>
+        <v>80</v>
       </c>
     </row>
     <row r="87">
@@ -5688,10 +5688,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H87" t="str">
-        <v>Canada</v>
+        <v>United States</v>
       </c>
       <c r="I87" t="str">
-        <v>Canada</v>
+        <v>United States</v>
       </c>
       <c r="J87" t="str">
         <v>On-site</v>
@@ -5700,7 +5700,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L87" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8093933</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8088818</v>
       </c>
       <c r="M87">
         <v>200</v>
@@ -5709,19 +5709,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O87" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P87" t="str">
         <v>Today</v>
       </c>
       <c r="Q87" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R87" t="str">
         <v>No</v>
       </c>
       <c r="S87">
-        <v>87</v>
+        <v>62</v>
       </c>
     </row>
     <row r="88">
@@ -5747,10 +5747,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H88" t="str">
-        <v>Canada</v>
+        <v>Spain</v>
       </c>
       <c r="I88" t="str">
-        <v>Canada</v>
+        <v>Spain</v>
       </c>
       <c r="J88" t="str">
         <v>On-site</v>
@@ -5759,7 +5759,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L88" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8066646</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8066508</v>
       </c>
       <c r="M88">
         <v>200</v>
@@ -5768,7 +5768,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O88" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P88" t="str">
         <v>Today</v>
@@ -5780,7 +5780,7 @@
         <v>No</v>
       </c>
       <c r="S88">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="89">
@@ -5806,10 +5806,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H89" t="str">
-        <v>Hungary</v>
+        <v>Portugal</v>
       </c>
       <c r="I89" t="str">
-        <v>Hungary</v>
+        <v>Portugal</v>
       </c>
       <c r="J89" t="str">
         <v>On-site</v>
@@ -5818,7 +5818,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L89" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8041209</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8041208</v>
       </c>
       <c r="M89">
         <v>200</v>
@@ -5827,19 +5827,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O89" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P89" t="str">
         <v>Today</v>
       </c>
       <c r="Q89" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R89" t="str">
         <v>No</v>
       </c>
       <c r="S89">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="90">
@@ -5886,19 +5886,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O90" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P90" t="str">
         <v>Today</v>
       </c>
       <c r="Q90" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R90" t="str">
         <v>Yes</v>
       </c>
       <c r="S90">
-        <v>78</v>
+        <v>61</v>
       </c>
     </row>
     <row r="91">
@@ -5936,7 +5936,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L91" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8194216</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8194148</v>
       </c>
       <c r="M91">
         <v>200</v>
@@ -5945,7 +5945,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O91" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P91" t="str">
         <v>Today</v>
@@ -5957,7 +5957,7 @@
         <v>No</v>
       </c>
       <c r="S91">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="92">
@@ -6004,7 +6004,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O92" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P92" t="str">
         <v>Today</v>
@@ -6013,10 +6013,10 @@
         <v>No</v>
       </c>
       <c r="R92" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S92">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="93">
@@ -6042,10 +6042,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H93" t="str">
-        <v>London, UK</v>
+        <v>New York, NY</v>
       </c>
       <c r="I93" t="str">
-        <v>London</v>
+        <v>New York</v>
       </c>
       <c r="J93" t="str">
         <v>On-site</v>
@@ -6054,7 +6054,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L93" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4644742005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4673051005</v>
       </c>
       <c r="M93">
         <v>200</v>
@@ -6063,19 +6063,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O93" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P93" t="str">
         <v>Today</v>
       </c>
       <c r="Q93" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R93" t="str">
         <v>No</v>
       </c>
       <c r="S93">
-        <v>79</v>
+        <v>68</v>
       </c>
     </row>
     <row r="94">
@@ -6122,13 +6122,13 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O94" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P94" t="str">
         <v>Today</v>
       </c>
       <c r="Q94" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R94" t="str">
         <v>No</v>
@@ -6181,7 +6181,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O95" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P95" t="str">
         <v>Today</v>
@@ -6190,10 +6190,10 @@
         <v>No</v>
       </c>
       <c r="R95" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S95">
-        <v>70</v>
+        <v>50</v>
       </c>
     </row>
     <row r="96">
@@ -6240,7 +6240,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O96" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P96" t="str">
         <v>Today</v>
@@ -6278,10 +6278,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H97" t="str">
-        <v>Riyadh, Saudi Arabia</v>
+        <v>Doha, Qatar ; Dubai, UAE</v>
       </c>
       <c r="I97" t="str">
-        <v>Riyadh</v>
+        <v>Doha</v>
       </c>
       <c r="J97" t="str">
         <v>On-site</v>
@@ -6290,7 +6290,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L97" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4650514005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4589749005</v>
       </c>
       <c r="M97">
         <v>200</v>
@@ -6299,19 +6299,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O97" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P97" t="str">
         <v>Today</v>
       </c>
       <c r="Q97" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R97" t="str">
         <v>No</v>
       </c>
       <c r="S97">
-        <v>52</v>
+        <v>60</v>
       </c>
     </row>
     <row r="98">
@@ -6358,19 +6358,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O98" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P98" t="str">
         <v>Today</v>
       </c>
       <c r="Q98" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R98" t="str">
         <v>No</v>
       </c>
       <c r="S98">
-        <v>44</v>
+        <v>37</v>
       </c>
     </row>
     <row r="99">
@@ -6417,19 +6417,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O99" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P99" t="str">
         <v>Today</v>
       </c>
       <c r="Q99" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R99" t="str">
         <v>No</v>
       </c>
       <c r="S99">
-        <v>81</v>
+        <v>36</v>
       </c>
     </row>
     <row r="100">
@@ -6476,7 +6476,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O100" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P100" t="str">
         <v>Today</v>
@@ -6485,10 +6485,10 @@
         <v>Yes</v>
       </c>
       <c r="R100" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S100">
-        <v>33</v>
+        <v>73</v>
       </c>
     </row>
     <row r="101">
@@ -6535,19 +6535,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O101" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P101" t="str">
         <v>Today</v>
       </c>
       <c r="Q101" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R101" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S101">
-        <v>75</v>
+        <v>94</v>
       </c>
     </row>
     <row r="102">
@@ -6594,19 +6594,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O102" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P102" t="str">
         <v>Today</v>
       </c>
       <c r="Q102" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R102" t="str">
         <v>No</v>
       </c>
       <c r="S102">
-        <v>83</v>
+        <v>25</v>
       </c>
     </row>
     <row r="103">
@@ -6653,19 +6653,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O103" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P103" t="str">
         <v>Today</v>
       </c>
       <c r="Q103" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R103" t="str">
         <v>No</v>
       </c>
       <c r="S103">
-        <v>34</v>
+        <v>86</v>
       </c>
     </row>
     <row r="104">
@@ -6712,19 +6712,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O104" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P104" t="str">
         <v>Today</v>
       </c>
       <c r="Q104" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R104" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S104">
-        <v>61</v>
+        <v>88</v>
       </c>
     </row>
     <row r="105">
@@ -6771,19 +6771,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O105" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P105" t="str">
         <v>Today</v>
       </c>
       <c r="Q105" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R105" t="str">
         <v>No</v>
       </c>
       <c r="S105">
-        <v>41</v>
+        <v>25</v>
       </c>
     </row>
     <row r="106">
@@ -6830,19 +6830,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O106" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P106" t="str">
         <v>Today</v>
       </c>
       <c r="Q106" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R106" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S106">
-        <v>44</v>
+        <v>71</v>
       </c>
     </row>
     <row r="107">
@@ -6889,7 +6889,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O107" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P107" t="str">
         <v>Today</v>
@@ -6901,7 +6901,7 @@
         <v>No</v>
       </c>
       <c r="S107">
-        <v>52</v>
+        <v>66</v>
       </c>
     </row>
     <row r="108">
@@ -6927,10 +6927,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H108" t="str">
-        <v>Seattle, Washington, United States</v>
+        <v>San Francisco, California, United States</v>
       </c>
       <c r="I108" t="str">
-        <v>Seattle</v>
+        <v>San Francisco</v>
       </c>
       <c r="J108" t="str">
         <v>On-site</v>
@@ -6939,7 +6939,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L108" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8780828002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8780827002</v>
       </c>
       <c r="M108">
         <v>200</v>
@@ -6948,19 +6948,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O108" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P108" t="str">
         <v>Today</v>
       </c>
       <c r="Q108" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R108" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S108">
-        <v>74</v>
+        <v>30</v>
       </c>
     </row>
     <row r="109">
@@ -6986,10 +6986,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H109" t="str">
-        <v>New York, New York, United States</v>
+        <v>San Francisco, California, United States</v>
       </c>
       <c r="I109" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J109" t="str">
         <v>On-site</v>
@@ -6998,7 +6998,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L109" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8659251002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8659249002</v>
       </c>
       <c r="M109">
         <v>200</v>
@@ -7007,7 +7007,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O109" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P109" t="str">
         <v>Today</v>
@@ -7016,10 +7016,10 @@
         <v>No</v>
       </c>
       <c r="R109" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S109">
-        <v>34</v>
+        <v>61</v>
       </c>
     </row>
     <row r="110">
@@ -7045,10 +7045,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H110" t="str">
-        <v>Seattle, Washington, United States</v>
+        <v>New York, New York, United States</v>
       </c>
       <c r="I110" t="str">
-        <v>Seattle</v>
+        <v>New York</v>
       </c>
       <c r="J110" t="str">
         <v>On-site</v>
@@ -7057,7 +7057,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L110" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8432703002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8432702002</v>
       </c>
       <c r="M110">
         <v>200</v>
@@ -7066,19 +7066,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O110" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P110" t="str">
         <v>Today</v>
       </c>
       <c r="Q110" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R110" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S110">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="111">
@@ -7125,7 +7125,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O111" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P111" t="str">
         <v>Today</v>
@@ -7137,7 +7137,7 @@
         <v>No</v>
       </c>
       <c r="S111">
-        <v>73</v>
+        <v>30</v>
       </c>
     </row>
     <row r="112">
@@ -7163,10 +7163,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H112" t="str">
-        <v>New York, New York, United States</v>
+        <v>Seattle, Washington, United States</v>
       </c>
       <c r="I112" t="str">
-        <v>New York</v>
+        <v>Seattle</v>
       </c>
       <c r="J112" t="str">
         <v>On-site</v>
@@ -7175,7 +7175,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L112" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8659237002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8659221002</v>
       </c>
       <c r="M112">
         <v>200</v>
@@ -7184,19 +7184,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O112" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P112" t="str">
         <v>Today</v>
       </c>
       <c r="Q112" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R112" t="str">
         <v>Yes</v>
       </c>
       <c r="S112">
-        <v>60</v>
+        <v>27</v>
       </c>
     </row>
     <row r="113">
@@ -7243,7 +7243,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O113" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P113" t="str">
         <v>Today</v>
@@ -7255,7 +7255,7 @@
         <v>No</v>
       </c>
       <c r="S113">
-        <v>60</v>
+        <v>25</v>
       </c>
     </row>
     <row r="114">
@@ -7302,19 +7302,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O114" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P114" t="str">
         <v>Today</v>
       </c>
       <c r="Q114" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R114" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S114">
-        <v>55</v>
+        <v>33</v>
       </c>
     </row>
     <row r="115">
@@ -7361,7 +7361,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O115" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P115" t="str">
         <v>Today</v>
@@ -7370,10 +7370,10 @@
         <v>No</v>
       </c>
       <c r="R115" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S115">
-        <v>39</v>
+        <v>79</v>
       </c>
     </row>
     <row r="116">
@@ -7399,10 +7399,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H116" t="str">
-        <v>Seattle, Washington, United States</v>
+        <v>Vancouver, British Columbia, Canada</v>
       </c>
       <c r="I116" t="str">
-        <v>Seattle</v>
+        <v>Vancouver</v>
       </c>
       <c r="J116" t="str">
         <v>On-site</v>
@@ -7411,7 +7411,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L116" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8436530002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8436531002</v>
       </c>
       <c r="M116">
         <v>200</v>
@@ -7420,7 +7420,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O116" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P116" t="str">
         <v>Today</v>
@@ -7432,7 +7432,7 @@
         <v>No</v>
       </c>
       <c r="S116">
-        <v>55</v>
+        <v>46</v>
       </c>
     </row>
     <row r="117">
@@ -7479,7 +7479,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O117" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P117" t="str">
         <v>Today</v>
@@ -7488,10 +7488,10 @@
         <v>Yes</v>
       </c>
       <c r="R117" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S117">
-        <v>90</v>
+        <v>47</v>
       </c>
     </row>
     <row r="118">
@@ -7538,19 +7538,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O118" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P118" t="str">
         <v>Today</v>
       </c>
       <c r="Q118" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R118" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S118">
-        <v>75</v>
+        <v>53</v>
       </c>
     </row>
     <row r="119">
@@ -7576,10 +7576,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H119" t="str">
-        <v>Pittsburgh, PA</v>
+        <v>New York, NY</v>
       </c>
       <c r="I119" t="str">
-        <v>Pittsburgh</v>
+        <v>New York</v>
       </c>
       <c r="J119" t="str">
         <v>On-site</v>
@@ -7588,7 +7588,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L119" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8530395002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8737859002</v>
       </c>
       <c r="M119">
         <v>200</v>
@@ -7597,19 +7597,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O119" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P119" t="str">
         <v>Today</v>
       </c>
       <c r="Q119" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R119" t="str">
         <v>Yes</v>
       </c>
       <c r="S119">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="120">
@@ -7635,10 +7635,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H120" t="str">
-        <v>Pittsburgh, PA</v>
+        <v>New York, NY</v>
       </c>
       <c r="I120" t="str">
-        <v>Pittsburgh</v>
+        <v>New York</v>
       </c>
       <c r="J120" t="str">
         <v>On-site</v>
@@ -7647,7 +7647,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L120" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8747171002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8747275002</v>
       </c>
       <c r="M120">
         <v>200</v>
@@ -7656,7 +7656,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O120" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P120" t="str">
         <v>Today</v>
@@ -7668,7 +7668,7 @@
         <v>No</v>
       </c>
       <c r="S120">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="121">
@@ -7715,7 +7715,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O121" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P121" t="str">
         <v>Today</v>
@@ -7727,7 +7727,7 @@
         <v>No</v>
       </c>
       <c r="S121">
-        <v>74</v>
+        <v>62</v>
       </c>
     </row>
     <row r="122">
@@ -7774,7 +7774,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O122" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P122" t="str">
         <v>Today</v>
@@ -7783,10 +7783,10 @@
         <v>No</v>
       </c>
       <c r="R122" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S122">
-        <v>40</v>
+        <v>46</v>
       </c>
     </row>
     <row r="123">
@@ -7833,19 +7833,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O123" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P123" t="str">
         <v>Today</v>
       </c>
       <c r="Q123" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R123" t="str">
         <v>No</v>
       </c>
       <c r="S123">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="124">
@@ -7892,19 +7892,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O124" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P124" t="str">
         <v>Today</v>
       </c>
       <c r="Q124" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R124" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S124">
-        <v>33</v>
+        <v>80</v>
       </c>
     </row>
     <row r="125">
@@ -7951,19 +7951,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O125" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P125" t="str">
         <v>Today</v>
       </c>
       <c r="Q125" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R125" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S125">
-        <v>90</v>
+        <v>33</v>
       </c>
     </row>
     <row r="126">
@@ -8010,7 +8010,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O126" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P126" t="str">
         <v>Today</v>
@@ -8019,10 +8019,10 @@
         <v>Yes</v>
       </c>
       <c r="R126" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S126">
-        <v>37</v>
+        <v>89</v>
       </c>
     </row>
     <row r="127">
@@ -8069,7 +8069,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O127" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P127" t="str">
         <v>Today</v>
@@ -8078,10 +8078,10 @@
         <v>Yes</v>
       </c>
       <c r="R127" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S127">
-        <v>83</v>
+        <v>59</v>
       </c>
     </row>
     <row r="128">
@@ -8128,7 +8128,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O128" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P128" t="str">
         <v>Today</v>
@@ -8137,10 +8137,10 @@
         <v>No</v>
       </c>
       <c r="R128" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S128">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="129">
@@ -8187,19 +8187,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O129" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P129" t="str">
         <v>Today</v>
       </c>
       <c r="Q129" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R129" t="str">
         <v>No</v>
       </c>
       <c r="S129">
-        <v>78</v>
+        <v>45</v>
       </c>
     </row>
     <row r="130">
@@ -8246,7 +8246,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O130" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P130" t="str">
         <v>Today</v>
@@ -8258,7 +8258,7 @@
         <v>Yes</v>
       </c>
       <c r="S130">
-        <v>52</v>
+        <v>76</v>
       </c>
     </row>
     <row r="131">
@@ -8305,19 +8305,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O131" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P131" t="str">
         <v>Today</v>
       </c>
       <c r="Q131" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R131" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S131">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="132">
@@ -8364,19 +8364,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O132" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P132" t="str">
         <v>Today</v>
       </c>
       <c r="Q132" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R132" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S132">
-        <v>27</v>
+        <v>94</v>
       </c>
     </row>
     <row r="133">
@@ -8423,7 +8423,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O133" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P133" t="str">
         <v>Today</v>
@@ -8435,7 +8435,7 @@
         <v>No</v>
       </c>
       <c r="S133">
-        <v>83</v>
+        <v>52</v>
       </c>
     </row>
     <row r="134">
@@ -8482,19 +8482,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O134" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P134" t="str">
         <v>Today</v>
       </c>
       <c r="Q134" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R134" t="str">
         <v>No</v>
       </c>
       <c r="S134">
-        <v>63</v>
+        <v>80</v>
       </c>
     </row>
     <row r="135">
@@ -8541,19 +8541,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O135" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P135" t="str">
         <v>Today</v>
       </c>
       <c r="Q135" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R135" t="str">
         <v>No</v>
       </c>
       <c r="S135">
-        <v>51</v>
+        <v>28</v>
       </c>
     </row>
     <row r="136">
@@ -8600,7 +8600,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O136" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P136" t="str">
         <v>Today</v>
@@ -8609,10 +8609,10 @@
         <v>No</v>
       </c>
       <c r="R136" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S136">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="137">
@@ -8659,19 +8659,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O137" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P137" t="str">
         <v>Today</v>
       </c>
       <c r="Q137" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R137" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S137">
-        <v>34</v>
+        <v>85</v>
       </c>
     </row>
     <row r="138">
@@ -8718,7 +8718,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O138" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P138" t="str">
         <v>Today</v>
@@ -8730,7 +8730,7 @@
         <v>No</v>
       </c>
       <c r="S138">
-        <v>57</v>
+        <v>69</v>
       </c>
     </row>
     <row r="139">
@@ -8777,7 +8777,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O139" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P139" t="str">
         <v>Today</v>
@@ -8789,7 +8789,7 @@
         <v>No</v>
       </c>
       <c r="S139">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="140">
@@ -8836,7 +8836,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O140" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P140" t="str">
         <v>Today</v>
@@ -8848,7 +8848,7 @@
         <v>No</v>
       </c>
       <c r="S140">
-        <v>93</v>
+        <v>77</v>
       </c>
     </row>
     <row r="141">
@@ -8895,19 +8895,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O141" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P141" t="str">
         <v>Today</v>
       </c>
       <c r="Q141" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R141" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S141">
-        <v>43</v>
+        <v>82</v>
       </c>
     </row>
     <row r="142">
@@ -8954,19 +8954,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O142" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P142" t="str">
         <v>Today</v>
       </c>
       <c r="Q142" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R142" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S142">
-        <v>44</v>
+        <v>90</v>
       </c>
     </row>
     <row r="143">
@@ -9013,13 +9013,13 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O143" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P143" t="str">
         <v>Today</v>
       </c>
       <c r="Q143" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R143" t="str">
         <v>No</v>
@@ -9072,19 +9072,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O144" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P144" t="str">
         <v>Today</v>
       </c>
       <c r="Q144" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R144" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S144">
-        <v>57</v>
+        <v>90</v>
       </c>
     </row>
     <row r="145">
@@ -9131,7 +9131,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O145" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P145" t="str">
         <v>Today</v>
@@ -9140,10 +9140,10 @@
         <v>No</v>
       </c>
       <c r="R145" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S145">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="146">
@@ -9190,19 +9190,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O146" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P146" t="str">
         <v>Today</v>
       </c>
       <c r="Q146" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R146" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S146">
-        <v>88</v>
+        <v>32</v>
       </c>
     </row>
     <row r="147">
@@ -9249,7 +9249,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O147" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P147" t="str">
         <v>Today</v>
@@ -9258,10 +9258,10 @@
         <v>No</v>
       </c>
       <c r="R147" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S147">
-        <v>81</v>
+        <v>71</v>
       </c>
     </row>
     <row r="148">
@@ -9308,19 +9308,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O148" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P148" t="str">
         <v>Today</v>
       </c>
       <c r="Q148" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R148" t="str">
         <v>No</v>
       </c>
       <c r="S148">
-        <v>31</v>
+        <v>62</v>
       </c>
     </row>
     <row r="149">
@@ -9367,7 +9367,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O149" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P149" t="str">
         <v>Today</v>
@@ -9379,7 +9379,7 @@
         <v>No</v>
       </c>
       <c r="S149">
-        <v>72</v>
+        <v>48</v>
       </c>
     </row>
     <row r="150">
@@ -9426,7 +9426,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O150" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P150" t="str">
         <v>Today</v>
@@ -9435,10 +9435,10 @@
         <v>No</v>
       </c>
       <c r="R150" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S150">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="151">
@@ -9485,19 +9485,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O151" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P151" t="str">
         <v>Today</v>
       </c>
       <c r="Q151" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R151" t="str">
         <v>No</v>
       </c>
       <c r="S151">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="152">
@@ -9544,7 +9544,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O152" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P152" t="str">
         <v>Today</v>
@@ -9556,7 +9556,7 @@
         <v>No</v>
       </c>
       <c r="S152">
-        <v>45</v>
+        <v>79</v>
       </c>
     </row>
     <row r="153">
@@ -9603,7 +9603,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O153" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P153" t="str">
         <v>Today</v>
@@ -9615,7 +9615,7 @@
         <v>No</v>
       </c>
       <c r="S153">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="154">
@@ -9662,19 +9662,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O154" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P154" t="str">
         <v>Today</v>
       </c>
       <c r="Q154" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R154" t="str">
         <v>No</v>
       </c>
       <c r="S154">
-        <v>54</v>
+        <v>82</v>
       </c>
     </row>
     <row r="155">
@@ -9721,19 +9721,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O155" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P155" t="str">
         <v>Today</v>
       </c>
       <c r="Q155" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R155" t="str">
         <v>No</v>
       </c>
       <c r="S155">
-        <v>45</v>
+        <v>69</v>
       </c>
     </row>
     <row r="156">
@@ -9780,7 +9780,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O156" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P156" t="str">
         <v>Today</v>
@@ -9792,7 +9792,7 @@
         <v>No</v>
       </c>
       <c r="S156">
-        <v>55</v>
+        <v>91</v>
       </c>
     </row>
     <row r="157">
@@ -9839,19 +9839,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O157" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P157" t="str">
         <v>Today</v>
       </c>
       <c r="Q157" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R157" t="str">
         <v>Yes</v>
       </c>
       <c r="S157">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="158">
@@ -9898,19 +9898,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O158" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P158" t="str">
         <v>Today</v>
       </c>
       <c r="Q158" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R158" t="str">
         <v>No</v>
       </c>
       <c r="S158">
-        <v>39</v>
+        <v>92</v>
       </c>
     </row>
     <row r="159">
@@ -9957,19 +9957,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O159" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P159" t="str">
         <v>Today</v>
       </c>
       <c r="Q159" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R159" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S159">
-        <v>61</v>
+        <v>46</v>
       </c>
     </row>
     <row r="160">
@@ -9995,7 +9995,7 @@
         <v>8+ yrs</v>
       </c>
       <c r="H160" t="str">
-        <v>United States - Remote</v>
+        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
       </c>
       <c r="I160" t="str">
         <v>Remote</v>
@@ -10007,7 +10007,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L160" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8198282</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8198284</v>
       </c>
       <c r="M160">
         <v>200</v>
@@ -10016,19 +10016,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O160" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P160" t="str">
         <v>Today</v>
       </c>
       <c r="Q160" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R160" t="str">
         <v>No</v>
       </c>
       <c r="S160">
-        <v>46</v>
+        <v>71</v>
       </c>
     </row>
     <row r="161">
@@ -10075,7 +10075,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O161" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P161" t="str">
         <v>Today</v>
@@ -10084,10 +10084,10 @@
         <v>Yes</v>
       </c>
       <c r="R161" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S161">
-        <v>51</v>
+        <v>63</v>
       </c>
     </row>
     <row r="162">
@@ -10134,19 +10134,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O162" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P162" t="str">
         <v>Today</v>
       </c>
       <c r="Q162" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R162" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S162">
-        <v>75</v>
+        <v>82</v>
       </c>
     </row>
     <row r="163">
@@ -10193,19 +10193,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O163" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P163" t="str">
         <v>Today</v>
       </c>
       <c r="Q163" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R163" t="str">
         <v>No</v>
       </c>
       <c r="S163">
-        <v>40</v>
+        <v>74</v>
       </c>
     </row>
     <row r="164">
@@ -10231,7 +10231,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H164" t="str">
-        <v>United States - Remote</v>
+        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
       </c>
       <c r="I164" t="str">
         <v>Remote</v>
@@ -10243,7 +10243,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L164" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8143270</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8143272</v>
       </c>
       <c r="M164">
         <v>200</v>
@@ -10252,7 +10252,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O164" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P164" t="str">
         <v>Today</v>
@@ -10261,10 +10261,10 @@
         <v>No</v>
       </c>
       <c r="R164" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S164">
-        <v>60</v>
+        <v>39</v>
       </c>
     </row>
     <row r="165">
@@ -10290,7 +10290,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H165" t="str">
-        <v>United States - Remote</v>
+        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
       </c>
       <c r="I165" t="str">
         <v>Remote</v>
@@ -10302,7 +10302,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L165" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8203107</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8203109</v>
       </c>
       <c r="M165">
         <v>200</v>
@@ -10311,7 +10311,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O165" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P165" t="str">
         <v>Today</v>
@@ -10320,10 +10320,10 @@
         <v>Yes</v>
       </c>
       <c r="R165" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S165">
-        <v>28</v>
+        <v>53</v>
       </c>
     </row>
     <row r="166">
@@ -10370,19 +10370,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O166" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P166" t="str">
         <v>Today</v>
       </c>
       <c r="Q166" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R166" t="str">
         <v>No</v>
       </c>
       <c r="S166">
-        <v>90</v>
+        <v>69</v>
       </c>
     </row>
     <row r="167">
@@ -10429,7 +10429,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O167" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P167" t="str">
         <v>Today</v>
@@ -10441,7 +10441,7 @@
         <v>No</v>
       </c>
       <c r="S167">
-        <v>57</v>
+        <v>32</v>
       </c>
     </row>
     <row r="168">
@@ -10488,7 +10488,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O168" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P168" t="str">
         <v>Today</v>
@@ -10500,7 +10500,7 @@
         <v>Yes</v>
       </c>
       <c r="S168">
-        <v>43</v>
+        <v>65</v>
       </c>
     </row>
     <row r="169">
@@ -10547,7 +10547,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O169" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P169" t="str">
         <v>Today</v>
@@ -10559,7 +10559,7 @@
         <v>Yes</v>
       </c>
       <c r="S169">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="170">
@@ -10606,7 +10606,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O170" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P170" t="str">
         <v>Today</v>
@@ -10618,7 +10618,7 @@
         <v>No</v>
       </c>
       <c r="S170">
-        <v>54</v>
+        <v>106</v>
       </c>
     </row>
     <row r="171">
@@ -10665,7 +10665,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O171" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P171" t="str">
         <v>Today</v>
@@ -10674,10 +10674,10 @@
         <v>Yes</v>
       </c>
       <c r="R171" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S171">
-        <v>46</v>
+        <v>97</v>
       </c>
     </row>
     <row r="172">
@@ -10724,7 +10724,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O172" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P172" t="str">
         <v>Today</v>
@@ -10736,7 +10736,7 @@
         <v>No</v>
       </c>
       <c r="S172">
-        <v>94</v>
+        <v>60</v>
       </c>
     </row>
     <row r="173">
@@ -10783,7 +10783,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O173" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P173" t="str">
         <v>Today</v>
@@ -10792,10 +10792,10 @@
         <v>Yes</v>
       </c>
       <c r="R173" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S173">
-        <v>60</v>
+        <v>75</v>
       </c>
     </row>
     <row r="174">
@@ -10842,7 +10842,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O174" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P174" t="str">
         <v>Today</v>
@@ -10851,10 +10851,10 @@
         <v>Yes</v>
       </c>
       <c r="R174" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S174">
-        <v>60</v>
+        <v>78</v>
       </c>
     </row>
     <row r="175">
@@ -10901,7 +10901,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O175" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P175" t="str">
         <v>Today</v>
@@ -10913,7 +10913,7 @@
         <v>No</v>
       </c>
       <c r="S175">
-        <v>102</v>
+        <v>66</v>
       </c>
     </row>
     <row r="176">
@@ -10960,7 +10960,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O176" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P176" t="str">
         <v>Today</v>
@@ -10972,7 +10972,7 @@
         <v>No</v>
       </c>
       <c r="S176">
-        <v>113</v>
+        <v>83</v>
       </c>
     </row>
     <row r="177">
@@ -11019,7 +11019,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O177" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P177" t="str">
         <v>Today</v>
@@ -11031,7 +11031,7 @@
         <v>No</v>
       </c>
       <c r="S177">
-        <v>43</v>
+        <v>108</v>
       </c>
     </row>
     <row r="178">
@@ -11078,7 +11078,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O178" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P178" t="str">
         <v>Today</v>
@@ -11087,10 +11087,10 @@
         <v>Yes</v>
       </c>
       <c r="R178" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S178">
-        <v>88</v>
+        <v>48</v>
       </c>
     </row>
     <row r="179">
@@ -11137,7 +11137,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O179" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P179" t="str">
         <v>Today</v>
@@ -11146,10 +11146,10 @@
         <v>Yes</v>
       </c>
       <c r="R179" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S179">
-        <v>118</v>
+        <v>110</v>
       </c>
     </row>
     <row r="180">
@@ -11196,7 +11196,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O180" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P180" t="str">
         <v>Today</v>
@@ -11208,7 +11208,7 @@
         <v>No</v>
       </c>
       <c r="S180">
-        <v>85</v>
+        <v>89</v>
       </c>
     </row>
     <row r="181">
@@ -11255,7 +11255,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O181" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P181" t="str">
         <v>Today</v>
@@ -11264,10 +11264,10 @@
         <v>Yes</v>
       </c>
       <c r="R181" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S181">
-        <v>94</v>
+        <v>67</v>
       </c>
     </row>
     <row r="182">
@@ -11314,7 +11314,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O182" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P182" t="str">
         <v>Today</v>
@@ -11326,7 +11326,7 @@
         <v>Yes</v>
       </c>
       <c r="S182">
-        <v>78</v>
+        <v>89</v>
       </c>
     </row>
     <row r="183">
@@ -11373,7 +11373,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O183" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P183" t="str">
         <v>Today</v>
@@ -11385,7 +11385,7 @@
         <v>No</v>
       </c>
       <c r="S183">
-        <v>112</v>
+        <v>58</v>
       </c>
     </row>
     <row r="184">
@@ -11432,7 +11432,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O184" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P184" t="str">
         <v>Today</v>
@@ -11444,7 +11444,7 @@
         <v>No</v>
       </c>
       <c r="S184">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="185">
@@ -11491,7 +11491,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O185" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P185" t="str">
         <v>Today</v>
@@ -11503,7 +11503,7 @@
         <v>Yes</v>
       </c>
       <c r="S185">
-        <v>119</v>
+        <v>58</v>
       </c>
     </row>
     <row r="186">
@@ -11550,7 +11550,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O186" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P186" t="str">
         <v>Today</v>
@@ -11559,10 +11559,10 @@
         <v>Yes</v>
       </c>
       <c r="R186" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S186">
-        <v>60</v>
+        <v>66</v>
       </c>
     </row>
     <row r="187">
@@ -11609,7 +11609,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O187" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P187" t="str">
         <v>Today</v>
@@ -11618,10 +11618,10 @@
         <v>Yes</v>
       </c>
       <c r="R187" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S187">
-        <v>83</v>
+        <v>51</v>
       </c>
     </row>
     <row r="188">
@@ -11668,7 +11668,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O188" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P188" t="str">
         <v>Today</v>
@@ -11680,7 +11680,7 @@
         <v>Yes</v>
       </c>
       <c r="S188">
-        <v>68</v>
+        <v>40</v>
       </c>
     </row>
     <row r="189">
@@ -11727,7 +11727,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O189" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P189" t="str">
         <v>Today</v>
@@ -11739,7 +11739,7 @@
         <v>Yes</v>
       </c>
       <c r="S189">
-        <v>82</v>
+        <v>51</v>
       </c>
     </row>
     <row r="190">
@@ -11786,7 +11786,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O190" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P190" t="str">
         <v>Today</v>
@@ -11798,7 +11798,7 @@
         <v>Yes</v>
       </c>
       <c r="S190">
-        <v>67</v>
+        <v>44</v>
       </c>
     </row>
     <row r="191">
@@ -11845,7 +11845,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O191" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P191" t="str">
         <v>Today</v>
@@ -11857,7 +11857,7 @@
         <v>Yes</v>
       </c>
       <c r="S191">
-        <v>118</v>
+        <v>77</v>
       </c>
     </row>
     <row r="192">
@@ -11904,7 +11904,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O192" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P192" t="str">
         <v>Today</v>
@@ -11913,10 +11913,10 @@
         <v>Yes</v>
       </c>
       <c r="R192" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S192">
-        <v>110</v>
+        <v>87</v>
       </c>
     </row>
     <row r="193">
@@ -11963,7 +11963,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O193" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P193" t="str">
         <v>Today</v>
@@ -11972,10 +11972,10 @@
         <v>Yes</v>
       </c>
       <c r="R193" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S193">
-        <v>46</v>
+        <v>114</v>
       </c>
     </row>
     <row r="194">
@@ -12022,7 +12022,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O194" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P194" t="str">
         <v>Today</v>
@@ -12034,7 +12034,7 @@
         <v>No</v>
       </c>
       <c r="S194">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="195">
@@ -12081,7 +12081,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O195" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P195" t="str">
         <v>Today</v>
@@ -12093,7 +12093,7 @@
         <v>No</v>
       </c>
       <c r="S195">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="196">
@@ -12140,7 +12140,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O196" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P196" t="str">
         <v>Today</v>
@@ -12152,7 +12152,7 @@
         <v>No</v>
       </c>
       <c r="S196">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="197">
@@ -12199,7 +12199,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O197" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P197" t="str">
         <v>Today</v>
@@ -12211,7 +12211,7 @@
         <v>No</v>
       </c>
       <c r="S197">
-        <v>44</v>
+        <v>53</v>
       </c>
     </row>
     <row r="198">
@@ -12258,7 +12258,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O198" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P198" t="str">
         <v>Today</v>
@@ -12270,7 +12270,7 @@
         <v>No</v>
       </c>
       <c r="S198">
-        <v>54</v>
+        <v>88</v>
       </c>
     </row>
     <row r="199">
@@ -12317,7 +12317,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O199" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P199" t="str">
         <v>Today</v>
@@ -12329,7 +12329,7 @@
         <v>No</v>
       </c>
       <c r="S199">
-        <v>34</v>
+        <v>60</v>
       </c>
     </row>
     <row r="200">
@@ -12376,7 +12376,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O200" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P200" t="str">
         <v>Today</v>
@@ -12388,7 +12388,7 @@
         <v>No</v>
       </c>
       <c r="S200">
-        <v>51</v>
+        <v>86</v>
       </c>
     </row>
     <row r="201">
@@ -12435,7 +12435,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O201" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P201" t="str">
         <v>Today</v>
@@ -12447,7 +12447,7 @@
         <v>No</v>
       </c>
       <c r="S201">
-        <v>78</v>
+        <v>57</v>
       </c>
     </row>
     <row r="202">
@@ -12494,7 +12494,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O202" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P202" t="str">
         <v>Today</v>
@@ -12553,7 +12553,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O203" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P203" t="str">
         <v>Today</v>
@@ -12612,7 +12612,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O204" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P204" t="str">
         <v>Today</v>
@@ -12671,7 +12671,7 @@
         <v>BROKEN / 404</v>
       </c>
       <c r="O205" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P205" t="str">
         <v>Today</v>
@@ -12730,7 +12730,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O206" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P206" t="str">
         <v>Today</v>
@@ -12789,7 +12789,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O207" t="str">
-        <v>2026-09-18</v>
+        <v>2026-09-19</v>
       </c>
       <c r="P207" t="str">
         <v>1d ago</v>
@@ -12848,7 +12848,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O208" t="str">
-        <v>2026-09-18</v>
+        <v>2026-09-19</v>
       </c>
       <c r="P208" t="str">
         <v>1d ago</v>
@@ -12907,7 +12907,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O209" t="str">
-        <v>2026-09-18</v>
+        <v>2026-09-19</v>
       </c>
       <c r="P209" t="str">
         <v>1d ago</v>

--- a/GreenPath_PM_Jobs_Test_Report.xlsx
+++ b/GreenPath_PM_Jobs_Test_Report.xlsx
@@ -428,7 +428,7 @@
         <v>Test Execution Date</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-09-20T01:49:14.497Z</v>
+        <v>2026-09-21T01:50:23.581Z</v>
       </c>
     </row>
     <row r="4">
@@ -524,7 +524,7 @@
         <v>Cities Supported</v>
       </c>
       <c r="B15" t="str">
-        <v>San Francisco, Toronto, Dublin, N/A, New York, Remote, USA, London, Seattle, United States, Bengaluru, Paris, Menlo Park, Hybrid, In-Office, Canada, Spain, Switzerland, Israel, Portugal, Greece, Doha, Vancouver, Pittsburgh, Beijing, Vienna, North America, Stockholm, Washington, Mumbai, Gurgaon</v>
+        <v>San Francisco, Toronto, Dublin, N/A, New York, Remote, USA, London, Seattle, United States, Bengaluru, Paris, Menlo Park, Hybrid, In-Office, Spain, Switzerland, Ireland, Canada, Hungary, Greece, Doha, Vancouver, Pittsburgh, Beijing, Vienna, North America, Stockholm, Washington, Mumbai, Gurgaon</v>
       </c>
     </row>
     <row r="16">
@@ -694,7 +694,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O2" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P2" t="str">
         <v>Today</v>
@@ -706,7 +706,7 @@
         <v>Yes</v>
       </c>
       <c r="S2">
-        <v>69</v>
+        <v>91</v>
       </c>
     </row>
     <row r="3">
@@ -753,7 +753,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O3" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P3" t="str">
         <v>Today</v>
@@ -765,7 +765,7 @@
         <v>No</v>
       </c>
       <c r="S3">
-        <v>55</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
@@ -812,7 +812,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O4" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P4" t="str">
         <v>Today</v>
@@ -824,7 +824,7 @@
         <v>No</v>
       </c>
       <c r="S4">
-        <v>50</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5">
@@ -871,7 +871,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O5" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P5" t="str">
         <v>Today</v>
@@ -883,7 +883,7 @@
         <v>No</v>
       </c>
       <c r="S5">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6">
@@ -930,19 +930,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O6" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P6" t="str">
         <v>Today</v>
       </c>
       <c r="Q6" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R6" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S6">
-        <v>93</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7">
@@ -989,19 +989,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O7" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P7" t="str">
         <v>Today</v>
       </c>
       <c r="Q7" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R7" t="str">
         <v>No</v>
       </c>
       <c r="S7">
-        <v>80</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8">
@@ -1048,7 +1048,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O8" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P8" t="str">
         <v>Today</v>
@@ -1060,7 +1060,7 @@
         <v>No</v>
       </c>
       <c r="S8">
-        <v>63</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9">
@@ -1107,7 +1107,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O9" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P9" t="str">
         <v>Today</v>
@@ -1119,7 +1119,7 @@
         <v>Yes</v>
       </c>
       <c r="S9">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10">
@@ -1166,19 +1166,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O10" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P10" t="str">
         <v>Today</v>
       </c>
       <c r="Q10" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R10" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S10">
-        <v>87</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
@@ -1225,19 +1225,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O11" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P11" t="str">
         <v>Today</v>
       </c>
       <c r="Q11" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R11" t="str">
         <v>No</v>
       </c>
       <c r="S11">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12">
@@ -1284,19 +1284,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O12" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P12" t="str">
         <v>Today</v>
       </c>
       <c r="Q12" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R12" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S12">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">
@@ -1343,19 +1343,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O13" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P13" t="str">
         <v>Today</v>
       </c>
       <c r="Q13" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R13" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S13">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14">
@@ -1402,19 +1402,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O14" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P14" t="str">
         <v>Today</v>
       </c>
       <c r="Q14" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R14" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S14">
-        <v>62</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -1461,7 +1461,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O15" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P15" t="str">
         <v>Today</v>
@@ -1470,10 +1470,10 @@
         <v>No</v>
       </c>
       <c r="R15" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S15">
-        <v>62</v>
+        <v>35</v>
       </c>
     </row>
     <row r="16">
@@ -1520,19 +1520,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O16" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P16" t="str">
         <v>Today</v>
       </c>
       <c r="Q16" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R16" t="str">
         <v>No</v>
       </c>
       <c r="S16">
-        <v>43</v>
+        <v>81</v>
       </c>
     </row>
     <row r="17">
@@ -1579,7 +1579,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O17" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P17" t="str">
         <v>Today</v>
@@ -1588,10 +1588,10 @@
         <v>No</v>
       </c>
       <c r="R17" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S17">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18">
@@ -1638,19 +1638,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O18" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P18" t="str">
         <v>Today</v>
       </c>
       <c r="Q18" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R18" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S18">
-        <v>31</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19">
@@ -1697,7 +1697,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O19" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P19" t="str">
         <v>Today</v>
@@ -1706,10 +1706,10 @@
         <v>Yes</v>
       </c>
       <c r="R19" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S19">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="20">
@@ -1756,19 +1756,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O20" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P20" t="str">
         <v>Today</v>
       </c>
       <c r="Q20" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R20" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S20">
-        <v>91</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21">
@@ -1815,19 +1815,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O21" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P21" t="str">
         <v>Today</v>
       </c>
       <c r="Q21" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R21" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S21">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22">
@@ -1874,7 +1874,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O22" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P22" t="str">
         <v>Today</v>
@@ -1883,10 +1883,10 @@
         <v>No</v>
       </c>
       <c r="R22" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S22">
-        <v>90</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23">
@@ -1933,19 +1933,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O23" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P23" t="str">
         <v>Today</v>
       </c>
       <c r="Q23" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R23" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S23">
-        <v>71</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24">
@@ -1992,19 +1992,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O24" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P24" t="str">
         <v>Today</v>
       </c>
       <c r="Q24" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R24" t="str">
         <v>No</v>
       </c>
       <c r="S24">
-        <v>69</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25">
@@ -2030,10 +2030,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H25" t="str">
-        <v>Dublin</v>
+        <v>London</v>
       </c>
       <c r="I25" t="str">
-        <v>Dublin</v>
+        <v>London</v>
       </c>
       <c r="J25" t="str">
         <v>On-site</v>
@@ -2042,7 +2042,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L25" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/7737526</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/8142649</v>
       </c>
       <c r="M25">
         <v>200</v>
@@ -2051,19 +2051,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O25" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P25" t="str">
         <v>Today</v>
       </c>
       <c r="Q25" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R25" t="str">
         <v>Yes</v>
       </c>
       <c r="S25">
-        <v>25</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26">
@@ -2110,7 +2110,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O26" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P26" t="str">
         <v>Today</v>
@@ -2122,7 +2122,7 @@
         <v>No</v>
       </c>
       <c r="S26">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="27">
@@ -2169,7 +2169,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O27" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P27" t="str">
         <v>Today</v>
@@ -2178,10 +2178,10 @@
         <v>No</v>
       </c>
       <c r="R27" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S27">
-        <v>25</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28">
@@ -2228,19 +2228,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O28" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P28" t="str">
         <v>Today</v>
       </c>
       <c r="Q28" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R28" t="str">
         <v>No</v>
       </c>
       <c r="S28">
-        <v>71</v>
+        <v>48</v>
       </c>
     </row>
     <row r="29">
@@ -2287,7 +2287,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O29" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P29" t="str">
         <v>Today</v>
@@ -2299,7 +2299,7 @@
         <v>No</v>
       </c>
       <c r="S29">
-        <v>43</v>
+        <v>52</v>
       </c>
     </row>
     <row r="30">
@@ -2346,7 +2346,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O30" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P30" t="str">
         <v>Today</v>
@@ -2358,7 +2358,7 @@
         <v>No</v>
       </c>
       <c r="S30">
-        <v>28</v>
+        <v>54</v>
       </c>
     </row>
     <row r="31">
@@ -2405,7 +2405,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O31" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P31" t="str">
         <v>Today</v>
@@ -2414,10 +2414,10 @@
         <v>No</v>
       </c>
       <c r="R31" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S31">
-        <v>50</v>
+        <v>64</v>
       </c>
     </row>
     <row r="32">
@@ -2464,19 +2464,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O32" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P32" t="str">
         <v>Today</v>
       </c>
       <c r="Q32" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R32" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S32">
-        <v>37</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33">
@@ -2523,7 +2523,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O33" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P33" t="str">
         <v>Today</v>
@@ -2535,7 +2535,7 @@
         <v>No</v>
       </c>
       <c r="S33">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34">
@@ -2582,7 +2582,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O34" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P34" t="str">
         <v>Today</v>
@@ -2594,7 +2594,7 @@
         <v>No</v>
       </c>
       <c r="S34">
-        <v>32</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35">
@@ -2641,19 +2641,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O35" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P35" t="str">
         <v>Today</v>
       </c>
       <c r="Q35" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R35" t="str">
         <v>No</v>
       </c>
       <c r="S35">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36">
@@ -2700,7 +2700,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O36" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P36" t="str">
         <v>Today</v>
@@ -2709,10 +2709,10 @@
         <v>Yes</v>
       </c>
       <c r="R36" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S36">
-        <v>84</v>
+        <v>39</v>
       </c>
     </row>
     <row r="37">
@@ -2759,19 +2759,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O37" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P37" t="str">
         <v>Today</v>
       </c>
       <c r="Q37" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R37" t="str">
         <v>No</v>
       </c>
       <c r="S37">
-        <v>50</v>
+        <v>56</v>
       </c>
     </row>
     <row r="38">
@@ -2812,25 +2812,25 @@
         <v>https://boards.greenhouse.io/datadog/jobs/8024863</v>
       </c>
       <c r="M38">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="N38" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O38" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P38" t="str">
         <v>Today</v>
       </c>
       <c r="Q38" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R38" t="str">
         <v>No</v>
       </c>
       <c r="S38">
-        <v>78</v>
+        <v>72</v>
       </c>
     </row>
     <row r="39">
@@ -2877,19 +2877,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O39" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P39" t="str">
         <v>Today</v>
       </c>
       <c r="Q39" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R39" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S39">
-        <v>87</v>
+        <v>51</v>
       </c>
     </row>
     <row r="40">
@@ -2936,7 +2936,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O40" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P40" t="str">
         <v>Today</v>
@@ -2945,10 +2945,10 @@
         <v>No</v>
       </c>
       <c r="R40" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S40">
-        <v>53</v>
+        <v>88</v>
       </c>
     </row>
     <row r="41">
@@ -2974,10 +2974,10 @@
         <v>0-2 yrs</v>
       </c>
       <c r="H41" t="str">
-        <v>New York, New York, USA</v>
+        <v>Paris, France</v>
       </c>
       <c r="I41" t="str">
-        <v>New York</v>
+        <v>Paris</v>
       </c>
       <c r="J41" t="str">
         <v>On-site</v>
@@ -2986,7 +2986,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L41" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/8108241</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/8143729</v>
       </c>
       <c r="M41">
         <v>200</v>
@@ -2995,7 +2995,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O41" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P41" t="str">
         <v>Today</v>
@@ -3007,7 +3007,7 @@
         <v>Yes</v>
       </c>
       <c r="S41">
-        <v>81</v>
+        <v>41</v>
       </c>
     </row>
     <row r="42">
@@ -3054,19 +3054,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O42" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P42" t="str">
         <v>Today</v>
       </c>
       <c r="Q42" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R42" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S42">
-        <v>57</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43">
@@ -3113,19 +3113,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O43" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P43" t="str">
         <v>Today</v>
       </c>
       <c r="Q43" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R43" t="str">
         <v>No</v>
       </c>
       <c r="S43">
-        <v>39</v>
+        <v>94</v>
       </c>
     </row>
     <row r="44">
@@ -3172,19 +3172,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O44" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P44" t="str">
         <v>Today</v>
       </c>
       <c r="Q44" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R44" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S44">
-        <v>43</v>
+        <v>91</v>
       </c>
     </row>
     <row r="45">
@@ -3225,25 +3225,25 @@
         <v>https://boards.greenhouse.io/datadog/jobs/7947683</v>
       </c>
       <c r="M45">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="N45" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O45" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P45" t="str">
         <v>Today</v>
       </c>
       <c r="Q45" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R45" t="str">
         <v>No</v>
       </c>
       <c r="S45">
-        <v>30</v>
+        <v>80</v>
       </c>
     </row>
     <row r="46">
@@ -3290,19 +3290,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O46" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P46" t="str">
         <v>Today</v>
       </c>
       <c r="Q46" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R46" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S46">
-        <v>67</v>
+        <v>47</v>
       </c>
     </row>
     <row r="47">
@@ -3349,7 +3349,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O47" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P47" t="str">
         <v>Today</v>
@@ -3358,10 +3358,10 @@
         <v>No</v>
       </c>
       <c r="R47" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S47">
-        <v>27</v>
+        <v>64</v>
       </c>
     </row>
     <row r="48">
@@ -3408,16 +3408,16 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O48" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P48" t="str">
         <v>Today</v>
       </c>
       <c r="Q48" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R48" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S48">
         <v>35</v>
@@ -3467,19 +3467,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O49" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P49" t="str">
         <v>Today</v>
       </c>
       <c r="Q49" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R49" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S49">
-        <v>81</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50">
@@ -3526,7 +3526,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O50" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P50" t="str">
         <v>Today</v>
@@ -3538,7 +3538,7 @@
         <v>No</v>
       </c>
       <c r="S50">
-        <v>59</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51">
@@ -3585,7 +3585,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O51" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P51" t="str">
         <v>Today</v>
@@ -3594,10 +3594,10 @@
         <v>No</v>
       </c>
       <c r="R51" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S51">
-        <v>79</v>
+        <v>94</v>
       </c>
     </row>
     <row r="52">
@@ -3644,7 +3644,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O52" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P52" t="str">
         <v>Today</v>
@@ -3653,10 +3653,10 @@
         <v>Yes</v>
       </c>
       <c r="R52" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S52">
-        <v>84</v>
+        <v>29</v>
       </c>
     </row>
     <row r="53">
@@ -3697,13 +3697,13 @@
         <v>https://boards.greenhouse.io/datadog/jobs/7974481</v>
       </c>
       <c r="M53">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="N53" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O53" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P53" t="str">
         <v>Today</v>
@@ -3715,7 +3715,7 @@
         <v>No</v>
       </c>
       <c r="S53">
-        <v>92</v>
+        <v>50</v>
       </c>
     </row>
     <row r="54">
@@ -3756,13 +3756,13 @@
         <v>https://boards.greenhouse.io/datadog/jobs/6960503</v>
       </c>
       <c r="M54">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="N54" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O54" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P54" t="str">
         <v>Today</v>
@@ -3774,7 +3774,7 @@
         <v>Yes</v>
       </c>
       <c r="S54">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="55">
@@ -3821,19 +3821,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O55" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P55" t="str">
         <v>Today</v>
       </c>
       <c r="Q55" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R55" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S55">
-        <v>94</v>
+        <v>44</v>
       </c>
     </row>
     <row r="56">
@@ -3880,19 +3880,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O56" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P56" t="str">
         <v>Today</v>
       </c>
       <c r="Q56" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R56" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S56">
-        <v>75</v>
+        <v>56</v>
       </c>
     </row>
     <row r="57">
@@ -3939,19 +3939,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O57" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P57" t="str">
         <v>Today</v>
       </c>
       <c r="Q57" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R57" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S57">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="58">
@@ -3998,7 +3998,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O58" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P58" t="str">
         <v>Today</v>
@@ -4010,7 +4010,7 @@
         <v>No</v>
       </c>
       <c r="S58">
-        <v>66</v>
+        <v>39</v>
       </c>
     </row>
     <row r="59">
@@ -4057,19 +4057,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O59" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P59" t="str">
         <v>Today</v>
       </c>
       <c r="Q59" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R59" t="str">
         <v>No</v>
       </c>
       <c r="S59">
-        <v>62</v>
+        <v>90</v>
       </c>
     </row>
     <row r="60">
@@ -4116,19 +4116,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O60" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P60" t="str">
         <v>Today</v>
       </c>
       <c r="Q60" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R60" t="str">
         <v>No</v>
       </c>
       <c r="S60">
-        <v>29</v>
+        <v>94</v>
       </c>
     </row>
     <row r="61">
@@ -4175,7 +4175,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O61" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P61" t="str">
         <v>Today</v>
@@ -4187,7 +4187,7 @@
         <v>No</v>
       </c>
       <c r="S61">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="62">
@@ -4234,7 +4234,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O62" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P62" t="str">
         <v>Today</v>
@@ -4243,10 +4243,10 @@
         <v>Yes</v>
       </c>
       <c r="R62" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S62">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="63">
@@ -4293,7 +4293,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O63" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P63" t="str">
         <v>Today</v>
@@ -4305,7 +4305,7 @@
         <v>No</v>
       </c>
       <c r="S63">
-        <v>30</v>
+        <v>62</v>
       </c>
     </row>
     <row r="64">
@@ -4352,7 +4352,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O64" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P64" t="str">
         <v>Today</v>
@@ -4364,7 +4364,7 @@
         <v>No</v>
       </c>
       <c r="S64">
-        <v>93</v>
+        <v>68</v>
       </c>
     </row>
     <row r="65">
@@ -4411,7 +4411,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O65" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P65" t="str">
         <v>Today</v>
@@ -4423,7 +4423,7 @@
         <v>No</v>
       </c>
       <c r="S65">
-        <v>61</v>
+        <v>50</v>
       </c>
     </row>
     <row r="66">
@@ -4470,7 +4470,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O66" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P66" t="str">
         <v>Today</v>
@@ -4479,10 +4479,10 @@
         <v>No</v>
       </c>
       <c r="R66" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S66">
-        <v>76</v>
+        <v>39</v>
       </c>
     </row>
     <row r="67">
@@ -4529,7 +4529,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O67" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P67" t="str">
         <v>Today</v>
@@ -4538,10 +4538,10 @@
         <v>No</v>
       </c>
       <c r="R67" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S67">
-        <v>43</v>
+        <v>51</v>
       </c>
     </row>
     <row r="68">
@@ -4588,19 +4588,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O68" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P68" t="str">
         <v>Today</v>
       </c>
       <c r="Q68" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R68" t="str">
         <v>No</v>
       </c>
       <c r="S68">
-        <v>46</v>
+        <v>85</v>
       </c>
     </row>
     <row r="69">
@@ -4647,19 +4647,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O69" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P69" t="str">
         <v>Today</v>
       </c>
       <c r="Q69" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R69" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S69">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="70">
@@ -4706,7 +4706,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O70" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P70" t="str">
         <v>Today</v>
@@ -4715,10 +4715,10 @@
         <v>Yes</v>
       </c>
       <c r="R70" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S70">
-        <v>58</v>
+        <v>30</v>
       </c>
     </row>
     <row r="71">
@@ -4765,19 +4765,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O71" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P71" t="str">
         <v>Today</v>
       </c>
       <c r="Q71" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R71" t="str">
         <v>Yes</v>
       </c>
       <c r="S71">
-        <v>48</v>
+        <v>94</v>
       </c>
     </row>
     <row r="72">
@@ -4824,7 +4824,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O72" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P72" t="str">
         <v>Today</v>
@@ -4833,10 +4833,10 @@
         <v>No</v>
       </c>
       <c r="R72" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S72">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="73">
@@ -4883,19 +4883,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O73" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P73" t="str">
         <v>Today</v>
       </c>
       <c r="Q73" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R73" t="str">
         <v>No</v>
       </c>
       <c r="S73">
-        <v>92</v>
+        <v>77</v>
       </c>
     </row>
     <row r="74">
@@ -4942,19 +4942,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O74" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P74" t="str">
         <v>Today</v>
       </c>
       <c r="Q74" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R74" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S74">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="75">
@@ -5001,7 +5001,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O75" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P75" t="str">
         <v>Today</v>
@@ -5013,7 +5013,7 @@
         <v>No</v>
       </c>
       <c r="S75">
-        <v>26</v>
+        <v>48</v>
       </c>
     </row>
     <row r="76">
@@ -5060,19 +5060,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O76" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P76" t="str">
         <v>Today</v>
       </c>
       <c r="Q76" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R76" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S76">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="77">
@@ -5119,19 +5119,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O77" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P77" t="str">
         <v>Today</v>
       </c>
       <c r="Q77" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R77" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S77">
-        <v>93</v>
+        <v>69</v>
       </c>
     </row>
     <row r="78">
@@ -5178,19 +5178,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O78" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P78" t="str">
         <v>Today</v>
       </c>
       <c r="Q78" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R78" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S78">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="79">
@@ -5237,19 +5237,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O79" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P79" t="str">
         <v>Today</v>
       </c>
       <c r="Q79" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R79" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S79">
-        <v>59</v>
+        <v>76</v>
       </c>
     </row>
     <row r="80">
@@ -5296,19 +5296,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O80" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P80" t="str">
         <v>Today</v>
       </c>
       <c r="Q80" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R80" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S80">
-        <v>45</v>
+        <v>53</v>
       </c>
     </row>
     <row r="81">
@@ -5334,10 +5334,10 @@
         <v>8+ yrs</v>
       </c>
       <c r="H81" t="str">
-        <v>Canada</v>
+        <v>United States</v>
       </c>
       <c r="I81" t="str">
-        <v>Canada</v>
+        <v>United States</v>
       </c>
       <c r="J81" t="str">
         <v>On-site</v>
@@ -5346,7 +5346,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L81" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8070011</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/7602101</v>
       </c>
       <c r="M81">
         <v>200</v>
@@ -5355,19 +5355,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O81" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P81" t="str">
         <v>Today</v>
       </c>
       <c r="Q81" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R81" t="str">
         <v>No</v>
       </c>
       <c r="S81">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="82">
@@ -5414,7 +5414,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O82" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P82" t="str">
         <v>Today</v>
@@ -5426,7 +5426,7 @@
         <v>Yes</v>
       </c>
       <c r="S82">
-        <v>42</v>
+        <v>88</v>
       </c>
     </row>
     <row r="83">
@@ -5473,7 +5473,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O83" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P83" t="str">
         <v>Today</v>
@@ -5482,10 +5482,10 @@
         <v>No</v>
       </c>
       <c r="R83" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S83">
-        <v>51</v>
+        <v>41</v>
       </c>
     </row>
     <row r="84">
@@ -5525,14 +5525,14 @@
       <c r="L84" t="str">
         <v>https://boards.greenhouse.io/elastic/jobs/8155425</v>
       </c>
-      <c r="M84">
-        <v>200</v>
+      <c r="M84" t="str">
+        <v>ACTIVE_PORTAL</v>
       </c>
       <c r="N84" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O84" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P84" t="str">
         <v>Today</v>
@@ -5541,10 +5541,10 @@
         <v>Yes</v>
       </c>
       <c r="R84" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S84">
-        <v>54</v>
+        <v>70</v>
       </c>
     </row>
     <row r="85">
@@ -5570,10 +5570,10 @@
         <v>8+ yrs</v>
       </c>
       <c r="H85" t="str">
-        <v>Israel</v>
+        <v>Ireland</v>
       </c>
       <c r="I85" t="str">
-        <v>Israel</v>
+        <v>Ireland</v>
       </c>
       <c r="J85" t="str">
         <v>On-site</v>
@@ -5582,7 +5582,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L85" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8155328</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8155326</v>
       </c>
       <c r="M85">
         <v>200</v>
@@ -5591,19 +5591,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O85" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P85" t="str">
         <v>Today</v>
       </c>
       <c r="Q85" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R85" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S85">
-        <v>45</v>
+        <v>78</v>
       </c>
     </row>
     <row r="86">
@@ -5629,10 +5629,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H86" t="str">
-        <v>Canada</v>
+        <v>United States</v>
       </c>
       <c r="I86" t="str">
-        <v>Canada</v>
+        <v>United States</v>
       </c>
       <c r="J86" t="str">
         <v>On-site</v>
@@ -5641,7 +5641,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L86" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8214187</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8214106</v>
       </c>
       <c r="M86">
         <v>200</v>
@@ -5650,19 +5650,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O86" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P86" t="str">
         <v>Today</v>
       </c>
       <c r="Q86" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R86" t="str">
         <v>No</v>
       </c>
       <c r="S86">
-        <v>80</v>
+        <v>83</v>
       </c>
     </row>
     <row r="87">
@@ -5688,10 +5688,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H87" t="str">
-        <v>United States</v>
+        <v>Canada</v>
       </c>
       <c r="I87" t="str">
-        <v>United States</v>
+        <v>Canada</v>
       </c>
       <c r="J87" t="str">
         <v>On-site</v>
@@ -5700,7 +5700,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L87" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8088818</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8093933</v>
       </c>
       <c r="M87">
         <v>200</v>
@@ -5709,19 +5709,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O87" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P87" t="str">
         <v>Today</v>
       </c>
       <c r="Q87" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R87" t="str">
         <v>No</v>
       </c>
       <c r="S87">
-        <v>62</v>
+        <v>76</v>
       </c>
     </row>
     <row r="88">
@@ -5747,10 +5747,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H88" t="str">
-        <v>Spain</v>
+        <v>Canada</v>
       </c>
       <c r="I88" t="str">
-        <v>Spain</v>
+        <v>Canada</v>
       </c>
       <c r="J88" t="str">
         <v>On-site</v>
@@ -5759,7 +5759,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L88" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8066508</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8066646</v>
       </c>
       <c r="M88">
         <v>200</v>
@@ -5768,19 +5768,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O88" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P88" t="str">
         <v>Today</v>
       </c>
       <c r="Q88" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R88" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S88">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="89">
@@ -5806,10 +5806,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H89" t="str">
-        <v>Portugal</v>
+        <v>Hungary</v>
       </c>
       <c r="I89" t="str">
-        <v>Portugal</v>
+        <v>Hungary</v>
       </c>
       <c r="J89" t="str">
         <v>On-site</v>
@@ -5818,7 +5818,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L89" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8041208</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8041209</v>
       </c>
       <c r="M89">
         <v>200</v>
@@ -5827,19 +5827,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O89" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P89" t="str">
         <v>Today</v>
       </c>
       <c r="Q89" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R89" t="str">
         <v>No</v>
       </c>
       <c r="S89">
-        <v>61</v>
+        <v>49</v>
       </c>
     </row>
     <row r="90">
@@ -5886,19 +5886,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O90" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P90" t="str">
         <v>Today</v>
       </c>
       <c r="Q90" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R90" t="str">
         <v>Yes</v>
       </c>
       <c r="S90">
-        <v>61</v>
+        <v>47</v>
       </c>
     </row>
     <row r="91">
@@ -5936,7 +5936,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L91" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8194148</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8194216</v>
       </c>
       <c r="M91">
         <v>200</v>
@@ -5945,7 +5945,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O91" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P91" t="str">
         <v>Today</v>
@@ -5954,10 +5954,10 @@
         <v>No</v>
       </c>
       <c r="R91" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S91">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="92">
@@ -6004,19 +6004,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O92" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P92" t="str">
         <v>Today</v>
       </c>
       <c r="Q92" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R92" t="str">
         <v>No</v>
       </c>
       <c r="S92">
-        <v>53</v>
+        <v>92</v>
       </c>
     </row>
     <row r="93">
@@ -6063,19 +6063,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O93" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P93" t="str">
         <v>Today</v>
       </c>
       <c r="Q93" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R93" t="str">
         <v>No</v>
       </c>
       <c r="S93">
-        <v>68</v>
+        <v>25</v>
       </c>
     </row>
     <row r="94">
@@ -6122,7 +6122,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O94" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P94" t="str">
         <v>Today</v>
@@ -6134,7 +6134,7 @@
         <v>No</v>
       </c>
       <c r="S94">
-        <v>51</v>
+        <v>62</v>
       </c>
     </row>
     <row r="95">
@@ -6181,7 +6181,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O95" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P95" t="str">
         <v>Today</v>
@@ -6193,7 +6193,7 @@
         <v>Yes</v>
       </c>
       <c r="S95">
-        <v>50</v>
+        <v>94</v>
       </c>
     </row>
     <row r="96">
@@ -6240,7 +6240,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O96" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P96" t="str">
         <v>Today</v>
@@ -6249,10 +6249,10 @@
         <v>No</v>
       </c>
       <c r="R96" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S96">
-        <v>49</v>
+        <v>83</v>
       </c>
     </row>
     <row r="97">
@@ -6299,7 +6299,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O97" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P97" t="str">
         <v>Today</v>
@@ -6311,7 +6311,7 @@
         <v>No</v>
       </c>
       <c r="S97">
-        <v>60</v>
+        <v>35</v>
       </c>
     </row>
     <row r="98">
@@ -6358,19 +6358,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O98" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P98" t="str">
         <v>Today</v>
       </c>
       <c r="Q98" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R98" t="str">
         <v>No</v>
       </c>
       <c r="S98">
-        <v>37</v>
+        <v>84</v>
       </c>
     </row>
     <row r="99">
@@ -6417,7 +6417,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O99" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P99" t="str">
         <v>Today</v>
@@ -6426,10 +6426,10 @@
         <v>Yes</v>
       </c>
       <c r="R99" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S99">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="100">
@@ -6476,7 +6476,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O100" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P100" t="str">
         <v>Today</v>
@@ -6485,10 +6485,10 @@
         <v>Yes</v>
       </c>
       <c r="R100" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S100">
-        <v>73</v>
+        <v>94</v>
       </c>
     </row>
     <row r="101">
@@ -6535,19 +6535,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O101" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P101" t="str">
         <v>Today</v>
       </c>
       <c r="Q101" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R101" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S101">
-        <v>94</v>
+        <v>81</v>
       </c>
     </row>
     <row r="102">
@@ -6594,7 +6594,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O102" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P102" t="str">
         <v>Today</v>
@@ -6606,7 +6606,7 @@
         <v>No</v>
       </c>
       <c r="S102">
-        <v>25</v>
+        <v>54</v>
       </c>
     </row>
     <row r="103">
@@ -6653,19 +6653,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O103" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P103" t="str">
         <v>Today</v>
       </c>
       <c r="Q103" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R103" t="str">
         <v>No</v>
       </c>
       <c r="S103">
-        <v>86</v>
+        <v>67</v>
       </c>
     </row>
     <row r="104">
@@ -6712,7 +6712,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O104" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P104" t="str">
         <v>Today</v>
@@ -6724,7 +6724,7 @@
         <v>No</v>
       </c>
       <c r="S104">
-        <v>88</v>
+        <v>41</v>
       </c>
     </row>
     <row r="105">
@@ -6771,7 +6771,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O105" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P105" t="str">
         <v>Today</v>
@@ -6783,7 +6783,7 @@
         <v>No</v>
       </c>
       <c r="S105">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
     <row r="106">
@@ -6830,7 +6830,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O106" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P106" t="str">
         <v>Today</v>
@@ -6839,10 +6839,10 @@
         <v>Yes</v>
       </c>
       <c r="R106" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S106">
-        <v>71</v>
+        <v>33</v>
       </c>
     </row>
     <row r="107">
@@ -6889,19 +6889,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O107" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P107" t="str">
         <v>Today</v>
       </c>
       <c r="Q107" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R107" t="str">
         <v>No</v>
       </c>
       <c r="S107">
-        <v>66</v>
+        <v>59</v>
       </c>
     </row>
     <row r="108">
@@ -6927,10 +6927,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H108" t="str">
-        <v>San Francisco, California, United States</v>
+        <v>Seattle, Washington, United States</v>
       </c>
       <c r="I108" t="str">
-        <v>San Francisco</v>
+        <v>Seattle</v>
       </c>
       <c r="J108" t="str">
         <v>On-site</v>
@@ -6939,7 +6939,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L108" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8780827002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8780828002</v>
       </c>
       <c r="M108">
         <v>200</v>
@@ -6948,7 +6948,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O108" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P108" t="str">
         <v>Today</v>
@@ -6957,10 +6957,10 @@
         <v>No</v>
       </c>
       <c r="R108" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S108">
-        <v>30</v>
+        <v>60</v>
       </c>
     </row>
     <row r="109">
@@ -6986,10 +6986,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H109" t="str">
-        <v>San Francisco, California, United States</v>
+        <v>New York, New York, United States</v>
       </c>
       <c r="I109" t="str">
-        <v>San Francisco</v>
+        <v>New York</v>
       </c>
       <c r="J109" t="str">
         <v>On-site</v>
@@ -6998,7 +6998,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L109" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8659249002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8659251002</v>
       </c>
       <c r="M109">
         <v>200</v>
@@ -7007,7 +7007,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O109" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P109" t="str">
         <v>Today</v>
@@ -7019,7 +7019,7 @@
         <v>No</v>
       </c>
       <c r="S109">
-        <v>61</v>
+        <v>35</v>
       </c>
     </row>
     <row r="110">
@@ -7045,10 +7045,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H110" t="str">
-        <v>New York, New York, United States</v>
+        <v>Seattle, Washington, United States</v>
       </c>
       <c r="I110" t="str">
-        <v>New York</v>
+        <v>Seattle</v>
       </c>
       <c r="J110" t="str">
         <v>On-site</v>
@@ -7057,7 +7057,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L110" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8432702002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8432703002</v>
       </c>
       <c r="M110">
         <v>200</v>
@@ -7066,19 +7066,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O110" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P110" t="str">
         <v>Today</v>
       </c>
       <c r="Q110" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R110" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S110">
-        <v>77</v>
+        <v>89</v>
       </c>
     </row>
     <row r="111">
@@ -7125,19 +7125,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O111" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P111" t="str">
         <v>Today</v>
       </c>
       <c r="Q111" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R111" t="str">
         <v>No</v>
       </c>
       <c r="S111">
-        <v>30</v>
+        <v>77</v>
       </c>
     </row>
     <row r="112">
@@ -7163,10 +7163,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H112" t="str">
-        <v>Seattle, Washington, United States</v>
+        <v>New York, New York, United States</v>
       </c>
       <c r="I112" t="str">
-        <v>Seattle</v>
+        <v>New York</v>
       </c>
       <c r="J112" t="str">
         <v>On-site</v>
@@ -7175,7 +7175,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L112" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8659221002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8659237002</v>
       </c>
       <c r="M112">
         <v>200</v>
@@ -7184,19 +7184,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O112" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P112" t="str">
         <v>Today</v>
       </c>
       <c r="Q112" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R112" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S112">
-        <v>27</v>
+        <v>81</v>
       </c>
     </row>
     <row r="113">
@@ -7243,19 +7243,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O113" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P113" t="str">
         <v>Today</v>
       </c>
       <c r="Q113" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R113" t="str">
         <v>No</v>
       </c>
       <c r="S113">
-        <v>25</v>
+        <v>34</v>
       </c>
     </row>
     <row r="114">
@@ -7302,7 +7302,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O114" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P114" t="str">
         <v>Today</v>
@@ -7314,7 +7314,7 @@
         <v>Yes</v>
       </c>
       <c r="S114">
-        <v>33</v>
+        <v>94</v>
       </c>
     </row>
     <row r="115">
@@ -7361,19 +7361,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O115" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P115" t="str">
         <v>Today</v>
       </c>
       <c r="Q115" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R115" t="str">
         <v>Yes</v>
       </c>
       <c r="S115">
-        <v>79</v>
+        <v>39</v>
       </c>
     </row>
     <row r="116">
@@ -7399,10 +7399,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H116" t="str">
-        <v>Vancouver, British Columbia, Canada</v>
+        <v>Seattle, Washington, United States</v>
       </c>
       <c r="I116" t="str">
-        <v>Vancouver</v>
+        <v>Seattle</v>
       </c>
       <c r="J116" t="str">
         <v>On-site</v>
@@ -7411,7 +7411,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L116" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8436531002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8436530002</v>
       </c>
       <c r="M116">
         <v>200</v>
@@ -7420,7 +7420,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O116" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P116" t="str">
         <v>Today</v>
@@ -7432,7 +7432,7 @@
         <v>No</v>
       </c>
       <c r="S116">
-        <v>46</v>
+        <v>83</v>
       </c>
     </row>
     <row r="117">
@@ -7479,7 +7479,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O117" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P117" t="str">
         <v>Today</v>
@@ -7491,7 +7491,7 @@
         <v>No</v>
       </c>
       <c r="S117">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="118">
@@ -7538,19 +7538,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O118" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P118" t="str">
         <v>Today</v>
       </c>
       <c r="Q118" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R118" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S118">
-        <v>53</v>
+        <v>83</v>
       </c>
     </row>
     <row r="119">
@@ -7576,10 +7576,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H119" t="str">
-        <v>New York, NY</v>
+        <v>Pittsburgh, PA</v>
       </c>
       <c r="I119" t="str">
-        <v>New York</v>
+        <v>Pittsburgh</v>
       </c>
       <c r="J119" t="str">
         <v>On-site</v>
@@ -7588,7 +7588,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L119" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8737859002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8530395002</v>
       </c>
       <c r="M119">
         <v>200</v>
@@ -7597,7 +7597,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O119" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P119" t="str">
         <v>Today</v>
@@ -7606,10 +7606,10 @@
         <v>No</v>
       </c>
       <c r="R119" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S119">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="120">
@@ -7635,10 +7635,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H120" t="str">
-        <v>New York, NY</v>
+        <v>Pittsburgh, PA</v>
       </c>
       <c r="I120" t="str">
-        <v>New York</v>
+        <v>Pittsburgh</v>
       </c>
       <c r="J120" t="str">
         <v>On-site</v>
@@ -7647,7 +7647,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L120" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8747275002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8747171002</v>
       </c>
       <c r="M120">
         <v>200</v>
@@ -7656,19 +7656,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O120" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P120" t="str">
         <v>Today</v>
       </c>
       <c r="Q120" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R120" t="str">
         <v>No</v>
       </c>
       <c r="S120">
-        <v>38</v>
+        <v>76</v>
       </c>
     </row>
     <row r="121">
@@ -7708,14 +7708,14 @@
       <c r="L121" t="str">
         <v>https://boards.greenhouse.io/duolingo/jobs/8816512002</v>
       </c>
-      <c r="M121">
-        <v>200</v>
+      <c r="M121" t="str">
+        <v>ACTIVE_PORTAL</v>
       </c>
       <c r="N121" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O121" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P121" t="str">
         <v>Today</v>
@@ -7727,7 +7727,7 @@
         <v>No</v>
       </c>
       <c r="S121">
-        <v>62</v>
+        <v>51</v>
       </c>
     </row>
     <row r="122">
@@ -7774,7 +7774,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O122" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P122" t="str">
         <v>Today</v>
@@ -7786,7 +7786,7 @@
         <v>No</v>
       </c>
       <c r="S122">
-        <v>46</v>
+        <v>61</v>
       </c>
     </row>
     <row r="123">
@@ -7833,7 +7833,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O123" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P123" t="str">
         <v>Today</v>
@@ -7842,10 +7842,10 @@
         <v>Yes</v>
       </c>
       <c r="R123" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S123">
-        <v>32</v>
+        <v>73</v>
       </c>
     </row>
     <row r="124">
@@ -7892,7 +7892,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O124" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P124" t="str">
         <v>Today</v>
@@ -7901,10 +7901,10 @@
         <v>No</v>
       </c>
       <c r="R124" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S124">
-        <v>80</v>
+        <v>91</v>
       </c>
     </row>
     <row r="125">
@@ -7951,7 +7951,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O125" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P125" t="str">
         <v>Today</v>
@@ -7960,10 +7960,10 @@
         <v>Yes</v>
       </c>
       <c r="R125" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S125">
-        <v>33</v>
+        <v>25</v>
       </c>
     </row>
     <row r="126">
@@ -8010,7 +8010,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O126" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P126" t="str">
         <v>Today</v>
@@ -8022,7 +8022,7 @@
         <v>No</v>
       </c>
       <c r="S126">
-        <v>89</v>
+        <v>27</v>
       </c>
     </row>
     <row r="127">
@@ -8069,7 +8069,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O127" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P127" t="str">
         <v>Today</v>
@@ -8078,10 +8078,10 @@
         <v>Yes</v>
       </c>
       <c r="R127" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S127">
-        <v>59</v>
+        <v>40</v>
       </c>
     </row>
     <row r="128">
@@ -8128,19 +8128,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O128" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P128" t="str">
         <v>Today</v>
       </c>
       <c r="Q128" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R128" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S128">
-        <v>44</v>
+        <v>79</v>
       </c>
     </row>
     <row r="129">
@@ -8187,7 +8187,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O129" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P129" t="str">
         <v>Today</v>
@@ -8199,7 +8199,7 @@
         <v>No</v>
       </c>
       <c r="S129">
-        <v>45</v>
+        <v>69</v>
       </c>
     </row>
     <row r="130">
@@ -8246,7 +8246,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O130" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P130" t="str">
         <v>Today</v>
@@ -8255,10 +8255,10 @@
         <v>No</v>
       </c>
       <c r="R130" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S130">
-        <v>76</v>
+        <v>26</v>
       </c>
     </row>
     <row r="131">
@@ -8305,19 +8305,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O131" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P131" t="str">
         <v>Today</v>
       </c>
       <c r="Q131" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R131" t="str">
         <v>Yes</v>
       </c>
       <c r="S131">
-        <v>61</v>
+        <v>66</v>
       </c>
     </row>
     <row r="132">
@@ -8364,7 +8364,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O132" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P132" t="str">
         <v>Today</v>
@@ -8376,7 +8376,7 @@
         <v>Yes</v>
       </c>
       <c r="S132">
-        <v>94</v>
+        <v>84</v>
       </c>
     </row>
     <row r="133">
@@ -8416,14 +8416,14 @@
       <c r="L133" t="str">
         <v>https://boards.greenhouse.io/coinbase/jobs/8148171</v>
       </c>
-      <c r="M133">
-        <v>403</v>
+      <c r="M133" t="str">
+        <v>ACTIVE_PORTAL</v>
       </c>
       <c r="N133" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O133" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P133" t="str">
         <v>Today</v>
@@ -8435,7 +8435,7 @@
         <v>No</v>
       </c>
       <c r="S133">
-        <v>52</v>
+        <v>56</v>
       </c>
     </row>
     <row r="134">
@@ -8482,19 +8482,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O134" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P134" t="str">
         <v>Today</v>
       </c>
       <c r="Q134" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R134" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S134">
-        <v>80</v>
+        <v>41</v>
       </c>
     </row>
     <row r="135">
@@ -8535,13 +8535,13 @@
         <v>https://boards.greenhouse.io/gitlab/jobs/8806017002</v>
       </c>
       <c r="M135">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N135" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O135" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P135" t="str">
         <v>Today</v>
@@ -8550,10 +8550,10 @@
         <v>No</v>
       </c>
       <c r="R135" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S135">
-        <v>28</v>
+        <v>91</v>
       </c>
     </row>
     <row r="136">
@@ -8600,19 +8600,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O136" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P136" t="str">
         <v>Today</v>
       </c>
       <c r="Q136" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R136" t="str">
         <v>Yes</v>
       </c>
       <c r="S136">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="137">
@@ -8659,7 +8659,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O137" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P137" t="str">
         <v>Today</v>
@@ -8671,7 +8671,7 @@
         <v>No</v>
       </c>
       <c r="S137">
-        <v>85</v>
+        <v>47</v>
       </c>
     </row>
     <row r="138">
@@ -8718,7 +8718,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O138" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P138" t="str">
         <v>Today</v>
@@ -8730,7 +8730,7 @@
         <v>No</v>
       </c>
       <c r="S138">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="139">
@@ -8777,7 +8777,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O139" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P139" t="str">
         <v>Today</v>
@@ -8786,10 +8786,10 @@
         <v>No</v>
       </c>
       <c r="R139" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S139">
-        <v>40</v>
+        <v>90</v>
       </c>
     </row>
     <row r="140">
@@ -8829,26 +8829,26 @@
       <c r="L140" t="str">
         <v>https://boards.greenhouse.io/gitlab/jobs/8597805002</v>
       </c>
-      <c r="M140">
-        <v>200</v>
+      <c r="M140" t="str">
+        <v>ACTIVE_PORTAL</v>
       </c>
       <c r="N140" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O140" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P140" t="str">
         <v>Today</v>
       </c>
       <c r="Q140" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R140" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S140">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="141">
@@ -8895,19 +8895,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O141" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P141" t="str">
         <v>Today</v>
       </c>
       <c r="Q141" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R141" t="str">
         <v>No</v>
       </c>
       <c r="S141">
-        <v>82</v>
+        <v>31</v>
       </c>
     </row>
     <row r="142">
@@ -8954,7 +8954,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O142" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P142" t="str">
         <v>Today</v>
@@ -8963,10 +8963,10 @@
         <v>No</v>
       </c>
       <c r="R142" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S142">
-        <v>90</v>
+        <v>28</v>
       </c>
     </row>
     <row r="143">
@@ -9013,19 +9013,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O143" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P143" t="str">
         <v>Today</v>
       </c>
       <c r="Q143" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R143" t="str">
         <v>No</v>
       </c>
       <c r="S143">
-        <v>40</v>
+        <v>48</v>
       </c>
     </row>
     <row r="144">
@@ -9072,7 +9072,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O144" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P144" t="str">
         <v>Today</v>
@@ -9081,10 +9081,10 @@
         <v>Yes</v>
       </c>
       <c r="R144" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S144">
-        <v>90</v>
+        <v>41</v>
       </c>
     </row>
     <row r="145">
@@ -9131,7 +9131,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O145" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P145" t="str">
         <v>Today</v>
@@ -9140,10 +9140,10 @@
         <v>No</v>
       </c>
       <c r="R145" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S145">
-        <v>42</v>
+        <v>91</v>
       </c>
     </row>
     <row r="146">
@@ -9190,7 +9190,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O146" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P146" t="str">
         <v>Today</v>
@@ -9199,10 +9199,10 @@
         <v>Yes</v>
       </c>
       <c r="R146" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S146">
-        <v>32</v>
+        <v>87</v>
       </c>
     </row>
     <row r="147">
@@ -9249,7 +9249,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O147" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P147" t="str">
         <v>Today</v>
@@ -9258,10 +9258,10 @@
         <v>No</v>
       </c>
       <c r="R147" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S147">
-        <v>71</v>
+        <v>48</v>
       </c>
     </row>
     <row r="148">
@@ -9308,19 +9308,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O148" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P148" t="str">
         <v>Today</v>
       </c>
       <c r="Q148" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R148" t="str">
         <v>No</v>
       </c>
       <c r="S148">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="149">
@@ -9367,7 +9367,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O149" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P149" t="str">
         <v>Today</v>
@@ -9376,10 +9376,10 @@
         <v>Yes</v>
       </c>
       <c r="R149" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S149">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="150">
@@ -9426,7 +9426,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O150" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P150" t="str">
         <v>Today</v>
@@ -9438,7 +9438,7 @@
         <v>Yes</v>
       </c>
       <c r="S150">
-        <v>66</v>
+        <v>38</v>
       </c>
     </row>
     <row r="151">
@@ -9485,7 +9485,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O151" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P151" t="str">
         <v>Today</v>
@@ -9494,10 +9494,10 @@
         <v>No</v>
       </c>
       <c r="R151" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S151">
-        <v>79</v>
+        <v>55</v>
       </c>
     </row>
     <row r="152">
@@ -9544,7 +9544,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O152" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P152" t="str">
         <v>Today</v>
@@ -9556,7 +9556,7 @@
         <v>No</v>
       </c>
       <c r="S152">
-        <v>79</v>
+        <v>45</v>
       </c>
     </row>
     <row r="153">
@@ -9603,7 +9603,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O153" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P153" t="str">
         <v>Today</v>
@@ -9615,7 +9615,7 @@
         <v>No</v>
       </c>
       <c r="S153">
-        <v>45</v>
+        <v>81</v>
       </c>
     </row>
     <row r="154">
@@ -9662,7 +9662,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O154" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P154" t="str">
         <v>Today</v>
@@ -9674,7 +9674,7 @@
         <v>No</v>
       </c>
       <c r="S154">
-        <v>82</v>
+        <v>38</v>
       </c>
     </row>
     <row r="155">
@@ -9721,7 +9721,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O155" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P155" t="str">
         <v>Today</v>
@@ -9733,7 +9733,7 @@
         <v>No</v>
       </c>
       <c r="S155">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="156">
@@ -9780,19 +9780,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O156" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P156" t="str">
         <v>Today</v>
       </c>
       <c r="Q156" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R156" t="str">
         <v>No</v>
       </c>
       <c r="S156">
-        <v>91</v>
+        <v>37</v>
       </c>
     </row>
     <row r="157">
@@ -9839,19 +9839,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O157" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P157" t="str">
         <v>Today</v>
       </c>
       <c r="Q157" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R157" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S157">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="158">
@@ -9898,19 +9898,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O158" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P158" t="str">
         <v>Today</v>
       </c>
       <c r="Q158" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R158" t="str">
         <v>No</v>
       </c>
       <c r="S158">
-        <v>92</v>
+        <v>72</v>
       </c>
     </row>
     <row r="159">
@@ -9957,19 +9957,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O159" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P159" t="str">
         <v>Today</v>
       </c>
       <c r="Q159" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R159" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S159">
-        <v>46</v>
+        <v>60</v>
       </c>
     </row>
     <row r="160">
@@ -9995,7 +9995,7 @@
         <v>8+ yrs</v>
       </c>
       <c r="H160" t="str">
-        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
+        <v>United States - Remote</v>
       </c>
       <c r="I160" t="str">
         <v>Remote</v>
@@ -10007,7 +10007,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L160" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8198284</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8198282</v>
       </c>
       <c r="M160">
         <v>200</v>
@@ -10016,7 +10016,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O160" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P160" t="str">
         <v>Today</v>
@@ -10028,7 +10028,7 @@
         <v>No</v>
       </c>
       <c r="S160">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="161">
@@ -10075,7 +10075,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O161" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P161" t="str">
         <v>Today</v>
@@ -10084,10 +10084,10 @@
         <v>Yes</v>
       </c>
       <c r="R161" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S161">
-        <v>63</v>
+        <v>94</v>
       </c>
     </row>
     <row r="162">
@@ -10134,19 +10134,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O162" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P162" t="str">
         <v>Today</v>
       </c>
       <c r="Q162" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R162" t="str">
         <v>No</v>
       </c>
       <c r="S162">
-        <v>82</v>
+        <v>60</v>
       </c>
     </row>
     <row r="163">
@@ -10193,7 +10193,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O163" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P163" t="str">
         <v>Today</v>
@@ -10205,7 +10205,7 @@
         <v>No</v>
       </c>
       <c r="S163">
-        <v>74</v>
+        <v>56</v>
       </c>
     </row>
     <row r="164">
@@ -10231,7 +10231,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H164" t="str">
-        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
+        <v>United States - Remote</v>
       </c>
       <c r="I164" t="str">
         <v>Remote</v>
@@ -10243,7 +10243,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L164" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8143272</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8143270</v>
       </c>
       <c r="M164">
         <v>200</v>
@@ -10252,7 +10252,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O164" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P164" t="str">
         <v>Today</v>
@@ -10264,7 +10264,7 @@
         <v>No</v>
       </c>
       <c r="S164">
-        <v>39</v>
+        <v>70</v>
       </c>
     </row>
     <row r="165">
@@ -10290,7 +10290,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H165" t="str">
-        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
+        <v>United States - Remote</v>
       </c>
       <c r="I165" t="str">
         <v>Remote</v>
@@ -10302,7 +10302,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L165" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8203109</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8203107</v>
       </c>
       <c r="M165">
         <v>200</v>
@@ -10311,19 +10311,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O165" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P165" t="str">
         <v>Today</v>
       </c>
       <c r="Q165" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R165" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S165">
-        <v>53</v>
+        <v>80</v>
       </c>
     </row>
     <row r="166">
@@ -10370,19 +10370,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O166" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P166" t="str">
         <v>Today</v>
       </c>
       <c r="Q166" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R166" t="str">
         <v>No</v>
       </c>
       <c r="S166">
-        <v>69</v>
+        <v>73</v>
       </c>
     </row>
     <row r="167">
@@ -10429,19 +10429,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O167" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P167" t="str">
         <v>Today</v>
       </c>
       <c r="Q167" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R167" t="str">
         <v>No</v>
       </c>
       <c r="S167">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="168">
@@ -10488,7 +10488,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O168" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P168" t="str">
         <v>Today</v>
@@ -10500,7 +10500,7 @@
         <v>Yes</v>
       </c>
       <c r="S168">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="169">
@@ -10547,7 +10547,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O169" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P169" t="str">
         <v>Today</v>
@@ -10556,10 +10556,10 @@
         <v>Yes</v>
       </c>
       <c r="R169" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S169">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="170">
@@ -10606,7 +10606,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O170" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P170" t="str">
         <v>Today</v>
@@ -10615,10 +10615,10 @@
         <v>Yes</v>
       </c>
       <c r="R170" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S170">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="171">
@@ -10665,7 +10665,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O171" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P171" t="str">
         <v>Today</v>
@@ -10677,7 +10677,7 @@
         <v>Yes</v>
       </c>
       <c r="S171">
-        <v>97</v>
+        <v>109</v>
       </c>
     </row>
     <row r="172">
@@ -10724,7 +10724,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O172" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P172" t="str">
         <v>Today</v>
@@ -10733,10 +10733,10 @@
         <v>Yes</v>
       </c>
       <c r="R172" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S172">
-        <v>60</v>
+        <v>76</v>
       </c>
     </row>
     <row r="173">
@@ -10783,7 +10783,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O173" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P173" t="str">
         <v>Today</v>
@@ -10792,10 +10792,10 @@
         <v>Yes</v>
       </c>
       <c r="R173" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S173">
-        <v>75</v>
+        <v>98</v>
       </c>
     </row>
     <row r="174">
@@ -10842,7 +10842,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O174" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P174" t="str">
         <v>Today</v>
@@ -10854,7 +10854,7 @@
         <v>Yes</v>
       </c>
       <c r="S174">
-        <v>78</v>
+        <v>57</v>
       </c>
     </row>
     <row r="175">
@@ -10901,7 +10901,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O175" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P175" t="str">
         <v>Today</v>
@@ -10913,7 +10913,7 @@
         <v>No</v>
       </c>
       <c r="S175">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="176">
@@ -10960,7 +10960,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O176" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P176" t="str">
         <v>Today</v>
@@ -10972,7 +10972,7 @@
         <v>No</v>
       </c>
       <c r="S176">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="177">
@@ -11019,7 +11019,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O177" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P177" t="str">
         <v>Today</v>
@@ -11028,10 +11028,10 @@
         <v>Yes</v>
       </c>
       <c r="R177" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S177">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="178">
@@ -11078,7 +11078,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O178" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P178" t="str">
         <v>Today</v>
@@ -11090,7 +11090,7 @@
         <v>No</v>
       </c>
       <c r="S178">
-        <v>48</v>
+        <v>92</v>
       </c>
     </row>
     <row r="179">
@@ -11137,7 +11137,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O179" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P179" t="str">
         <v>Today</v>
@@ -11149,7 +11149,7 @@
         <v>Yes</v>
       </c>
       <c r="S179">
-        <v>110</v>
+        <v>93</v>
       </c>
     </row>
     <row r="180">
@@ -11196,7 +11196,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O180" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P180" t="str">
         <v>Today</v>
@@ -11208,7 +11208,7 @@
         <v>No</v>
       </c>
       <c r="S180">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="181">
@@ -11255,7 +11255,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O181" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P181" t="str">
         <v>Today</v>
@@ -11267,7 +11267,7 @@
         <v>Yes</v>
       </c>
       <c r="S181">
-        <v>67</v>
+        <v>101</v>
       </c>
     </row>
     <row r="182">
@@ -11314,7 +11314,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O182" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P182" t="str">
         <v>Today</v>
@@ -11323,10 +11323,10 @@
         <v>Yes</v>
       </c>
       <c r="R182" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S182">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="183">
@@ -11373,7 +11373,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O183" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P183" t="str">
         <v>Today</v>
@@ -11382,10 +11382,10 @@
         <v>Yes</v>
       </c>
       <c r="R183" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S183">
-        <v>58</v>
+        <v>113</v>
       </c>
     </row>
     <row r="184">
@@ -11432,7 +11432,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O184" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P184" t="str">
         <v>Today</v>
@@ -11441,10 +11441,10 @@
         <v>Yes</v>
       </c>
       <c r="R184" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S184">
-        <v>102</v>
+        <v>113</v>
       </c>
     </row>
     <row r="185">
@@ -11491,7 +11491,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O185" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P185" t="str">
         <v>Today</v>
@@ -11503,7 +11503,7 @@
         <v>Yes</v>
       </c>
       <c r="S185">
-        <v>58</v>
+        <v>63</v>
       </c>
     </row>
     <row r="186">
@@ -11550,7 +11550,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O186" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P186" t="str">
         <v>Today</v>
@@ -11562,7 +11562,7 @@
         <v>Yes</v>
       </c>
       <c r="S186">
-        <v>66</v>
+        <v>109</v>
       </c>
     </row>
     <row r="187">
@@ -11609,7 +11609,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O187" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P187" t="str">
         <v>Today</v>
@@ -11621,7 +11621,7 @@
         <v>Yes</v>
       </c>
       <c r="S187">
-        <v>51</v>
+        <v>117</v>
       </c>
     </row>
     <row r="188">
@@ -11668,7 +11668,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O188" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P188" t="str">
         <v>Today</v>
@@ -11677,10 +11677,10 @@
         <v>Yes</v>
       </c>
       <c r="R188" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S188">
-        <v>40</v>
+        <v>106</v>
       </c>
     </row>
     <row r="189">
@@ -11727,7 +11727,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O189" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P189" t="str">
         <v>Today</v>
@@ -11739,7 +11739,7 @@
         <v>Yes</v>
       </c>
       <c r="S189">
-        <v>51</v>
+        <v>77</v>
       </c>
     </row>
     <row r="190">
@@ -11786,7 +11786,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O190" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P190" t="str">
         <v>Today</v>
@@ -11798,7 +11798,7 @@
         <v>Yes</v>
       </c>
       <c r="S190">
-        <v>44</v>
+        <v>50</v>
       </c>
     </row>
     <row r="191">
@@ -11845,7 +11845,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O191" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P191" t="str">
         <v>Today</v>
@@ -11857,7 +11857,7 @@
         <v>Yes</v>
       </c>
       <c r="S191">
-        <v>77</v>
+        <v>68</v>
       </c>
     </row>
     <row r="192">
@@ -11904,7 +11904,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O192" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P192" t="str">
         <v>Today</v>
@@ -11916,7 +11916,7 @@
         <v>Yes</v>
       </c>
       <c r="S192">
-        <v>87</v>
+        <v>106</v>
       </c>
     </row>
     <row r="193">
@@ -11963,7 +11963,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O193" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P193" t="str">
         <v>Today</v>
@@ -11972,10 +11972,10 @@
         <v>Yes</v>
       </c>
       <c r="R193" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S193">
-        <v>114</v>
+        <v>65</v>
       </c>
     </row>
     <row r="194">
@@ -12022,7 +12022,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O194" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P194" t="str">
         <v>Today</v>
@@ -12034,7 +12034,7 @@
         <v>No</v>
       </c>
       <c r="S194">
-        <v>53</v>
+        <v>88</v>
       </c>
     </row>
     <row r="195">
@@ -12081,7 +12081,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O195" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P195" t="str">
         <v>Today</v>
@@ -12093,7 +12093,7 @@
         <v>No</v>
       </c>
       <c r="S195">
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
     <row r="196">
@@ -12140,7 +12140,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O196" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P196" t="str">
         <v>Today</v>
@@ -12152,7 +12152,7 @@
         <v>No</v>
       </c>
       <c r="S196">
-        <v>50</v>
+        <v>59</v>
       </c>
     </row>
     <row r="197">
@@ -12199,7 +12199,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O197" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P197" t="str">
         <v>Today</v>
@@ -12211,7 +12211,7 @@
         <v>No</v>
       </c>
       <c r="S197">
-        <v>53</v>
+        <v>39</v>
       </c>
     </row>
     <row r="198">
@@ -12258,7 +12258,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O198" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P198" t="str">
         <v>Today</v>
@@ -12270,7 +12270,7 @@
         <v>No</v>
       </c>
       <c r="S198">
-        <v>88</v>
+        <v>44</v>
       </c>
     </row>
     <row r="199">
@@ -12317,7 +12317,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O199" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P199" t="str">
         <v>Today</v>
@@ -12329,7 +12329,7 @@
         <v>No</v>
       </c>
       <c r="S199">
-        <v>60</v>
+        <v>87</v>
       </c>
     </row>
     <row r="200">
@@ -12376,7 +12376,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O200" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P200" t="str">
         <v>Today</v>
@@ -12388,7 +12388,7 @@
         <v>No</v>
       </c>
       <c r="S200">
-        <v>86</v>
+        <v>54</v>
       </c>
     </row>
     <row r="201">
@@ -12435,7 +12435,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O201" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P201" t="str">
         <v>Today</v>
@@ -12447,7 +12447,7 @@
         <v>No</v>
       </c>
       <c r="S201">
-        <v>57</v>
+        <v>66</v>
       </c>
     </row>
     <row r="202">
@@ -12494,7 +12494,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O202" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P202" t="str">
         <v>Today</v>
@@ -12553,7 +12553,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O203" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P203" t="str">
         <v>Today</v>
@@ -12612,7 +12612,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O204" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P204" t="str">
         <v>Today</v>
@@ -12671,7 +12671,7 @@
         <v>BROKEN / 404</v>
       </c>
       <c r="O205" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P205" t="str">
         <v>Today</v>
@@ -12730,7 +12730,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O206" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P206" t="str">
         <v>Today</v>
@@ -12789,7 +12789,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O207" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P207" t="str">
         <v>1d ago</v>
@@ -12848,7 +12848,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O208" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P208" t="str">
         <v>1d ago</v>
@@ -12907,7 +12907,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O209" t="str">
-        <v>2026-09-19</v>
+        <v>2026-09-20</v>
       </c>
       <c r="P209" t="str">
         <v>1d ago</v>

--- a/GreenPath_PM_Jobs_Test_Report.xlsx
+++ b/GreenPath_PM_Jobs_Test_Report.xlsx
@@ -428,7 +428,7 @@
         <v>Test Execution Date</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-09-21T01:50:23.581Z</v>
+        <v>2026-09-22T01:59:27.904Z</v>
       </c>
     </row>
     <row r="4">
@@ -524,7 +524,7 @@
         <v>Cities Supported</v>
       </c>
       <c r="B15" t="str">
-        <v>San Francisco, Toronto, Dublin, N/A, New York, Remote, USA, London, Seattle, United States, Bengaluru, Paris, Menlo Park, Hybrid, In-Office, Spain, Switzerland, Ireland, Canada, Hungary, Greece, Doha, Vancouver, Pittsburgh, Beijing, Vienna, North America, Stockholm, Washington, Mumbai, Gurgaon</v>
+        <v>San Francisco, Toronto, Dublin, N/A, New York, Remote, USA, London, Seattle, United States, Paris, Menlo Park, Hybrid, In-Office, Spain, Switzerland, Greece, Canada, Poland, Doha, Vancouver, Pittsburgh, Beijing, Bengaluru, Vienna, North America, Stockholm, Washington, Mumbai, Gurgaon</v>
       </c>
     </row>
     <row r="16">
@@ -532,7 +532,7 @@
         <v>Remote / Hybrid Roles</v>
       </c>
       <c r="B16" t="str">
-        <v>63 (30%)</v>
+        <v>64 (31%)</v>
       </c>
     </row>
     <row r="17">
@@ -694,19 +694,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O2" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P2" t="str">
         <v>Today</v>
       </c>
       <c r="Q2" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R2" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S2">
-        <v>91</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3">
@@ -753,19 +753,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O3" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P3" t="str">
         <v>Today</v>
       </c>
       <c r="Q3" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R3" t="str">
         <v>No</v>
       </c>
       <c r="S3">
-        <v>36</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4">
@@ -812,19 +812,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O4" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P4" t="str">
         <v>Today</v>
       </c>
       <c r="Q4" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R4" t="str">
         <v>No</v>
       </c>
       <c r="S4">
-        <v>73</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5">
@@ -871,7 +871,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O5" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P5" t="str">
         <v>Today</v>
@@ -883,7 +883,7 @@
         <v>No</v>
       </c>
       <c r="S5">
-        <v>64</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6">
@@ -930,7 +930,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O6" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P6" t="str">
         <v>Today</v>
@@ -942,7 +942,7 @@
         <v>No</v>
       </c>
       <c r="S6">
-        <v>45</v>
+        <v>86</v>
       </c>
     </row>
     <row r="7">
@@ -989,19 +989,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O7" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P7" t="str">
         <v>Today</v>
       </c>
       <c r="Q7" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R7" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S7">
-        <v>62</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -1048,7 +1048,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O8" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P8" t="str">
         <v>Today</v>
@@ -1057,10 +1057,10 @@
         <v>No</v>
       </c>
       <c r="R8" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S8">
-        <v>37</v>
+        <v>57</v>
       </c>
     </row>
     <row r="9">
@@ -1107,7 +1107,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O9" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P9" t="str">
         <v>Today</v>
@@ -1116,10 +1116,10 @@
         <v>No</v>
       </c>
       <c r="R9" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S9">
-        <v>52</v>
+        <v>25</v>
       </c>
     </row>
     <row r="10">
@@ -1166,19 +1166,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O10" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P10" t="str">
         <v>Today</v>
       </c>
       <c r="Q10" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R10" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S10">
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
     <row r="11">
@@ -1225,19 +1225,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O11" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P11" t="str">
         <v>Today</v>
       </c>
       <c r="Q11" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R11" t="str">
         <v>No</v>
       </c>
       <c r="S11">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12">
@@ -1284,19 +1284,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O12" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P12" t="str">
         <v>Today</v>
       </c>
       <c r="Q12" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R12" t="str">
         <v>No</v>
       </c>
       <c r="S12">
-        <v>38</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13">
@@ -1343,7 +1343,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O13" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P13" t="str">
         <v>Today</v>
@@ -1355,7 +1355,7 @@
         <v>No</v>
       </c>
       <c r="S13">
-        <v>40</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14">
@@ -1402,19 +1402,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O14" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P14" t="str">
         <v>Today</v>
       </c>
       <c r="Q14" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R14" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S14">
-        <v>47</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1461,7 +1461,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O15" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P15" t="str">
         <v>Today</v>
@@ -1470,10 +1470,10 @@
         <v>No</v>
       </c>
       <c r="R15" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S15">
-        <v>35</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16">
@@ -1520,19 +1520,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O16" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P16" t="str">
         <v>Today</v>
       </c>
       <c r="Q16" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R16" t="str">
         <v>No</v>
       </c>
       <c r="S16">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17">
@@ -1579,19 +1579,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O17" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P17" t="str">
         <v>Today</v>
       </c>
       <c r="Q17" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R17" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S17">
-        <v>90</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18">
@@ -1638,7 +1638,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O18" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P18" t="str">
         <v>Today</v>
@@ -1647,10 +1647,10 @@
         <v>Yes</v>
       </c>
       <c r="R18" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S18">
-        <v>74</v>
+        <v>30</v>
       </c>
     </row>
     <row r="19">
@@ -1697,7 +1697,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O19" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P19" t="str">
         <v>Today</v>
@@ -1709,15 +1709,15 @@
         <v>No</v>
       </c>
       <c r="S19">
-        <v>30</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>job-74abb1d3</v>
+        <v>job-6ab13196</v>
       </c>
       <c r="B20" t="str">
-        <v>Staff Product Manager, AI</v>
+        <v>Senior Product Manager, Enterprise</v>
       </c>
       <c r="C20" t="str">
         <v>Stripe</v>
@@ -1735,19 +1735,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H20" t="str">
-        <v>San Francisco, Seattle, New York, Chicago</v>
+        <v>San Francisco, Seattle, New York, Chicago, Atlanta, Remote</v>
       </c>
       <c r="I20" t="str">
         <v>San Francisco</v>
       </c>
       <c r="J20" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K20" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L20" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/7655023</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/7812856</v>
       </c>
       <c r="M20">
         <v>200</v>
@@ -1756,7 +1756,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O20" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P20" t="str">
         <v>Today</v>
@@ -1765,18 +1765,18 @@
         <v>No</v>
       </c>
       <c r="R20" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S20">
-        <v>81</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>job-53d16ec0</v>
+        <v>job-74abb1d3</v>
       </c>
       <c r="B21" t="str">
-        <v>Staff Product Manager, Billing</v>
+        <v>Staff Product Manager, AI</v>
       </c>
       <c r="C21" t="str">
         <v>Stripe</v>
@@ -1794,19 +1794,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H21" t="str">
-        <v>SF, NY, SEA, Remote-US</v>
+        <v>San Francisco, Seattle, New York, Chicago</v>
       </c>
       <c r="I21" t="str">
         <v>San Francisco</v>
       </c>
       <c r="J21" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K21" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L21" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/7983725</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/7655023</v>
       </c>
       <c r="M21">
         <v>200</v>
@@ -1815,7 +1815,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O21" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P21" t="str">
         <v>Today</v>
@@ -1824,18 +1824,18 @@
         <v>Yes</v>
       </c>
       <c r="R21" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S21">
-        <v>67</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>job-2cc707b1</v>
+        <v>job-53d16ec0</v>
       </c>
       <c r="B22" t="str">
-        <v>Staff Product Manager, Connect</v>
+        <v>Staff Product Manager, Billing</v>
       </c>
       <c r="C22" t="str">
         <v>Stripe</v>
@@ -1853,19 +1853,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H22" t="str">
-        <v>N/A</v>
+        <v>SF, NY, SEA, Remote-US</v>
       </c>
       <c r="I22" t="str">
-        <v>N/A</v>
+        <v>San Francisco</v>
       </c>
       <c r="J22" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K22" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L22" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/8065034</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/7983725</v>
       </c>
       <c r="M22">
         <v>200</v>
@@ -1874,27 +1874,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O22" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P22" t="str">
         <v>Today</v>
       </c>
       <c r="Q22" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R22" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S22">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>job-7b58caba</v>
+        <v>job-2cc707b1</v>
       </c>
       <c r="B23" t="str">
-        <v>Staff Product Manager, Enterprise</v>
+        <v>Staff Product Manager, Connect</v>
       </c>
       <c r="C23" t="str">
         <v>Stripe</v>
@@ -1912,19 +1912,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H23" t="str">
-        <v>San Francisco, Seattle, New York, Chicago, Atlanta, Remote</v>
+        <v>N/A</v>
       </c>
       <c r="I23" t="str">
-        <v>San Francisco</v>
+        <v>N/A</v>
       </c>
       <c r="J23" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K23" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L23" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/7812856</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/8065034</v>
       </c>
       <c r="M23">
         <v>200</v>
@@ -1933,19 +1933,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O23" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P23" t="str">
         <v>Today</v>
       </c>
       <c r="Q23" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R23" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S23">
-        <v>40</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24">
@@ -1992,7 +1992,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O24" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P24" t="str">
         <v>Today</v>
@@ -2001,10 +2001,10 @@
         <v>Yes</v>
       </c>
       <c r="R24" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S24">
-        <v>30</v>
+        <v>69</v>
       </c>
     </row>
     <row r="25">
@@ -2051,7 +2051,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O25" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P25" t="str">
         <v>Today</v>
@@ -2060,10 +2060,10 @@
         <v>Yes</v>
       </c>
       <c r="R25" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S25">
-        <v>61</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26">
@@ -2110,7 +2110,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O26" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P26" t="str">
         <v>Today</v>
@@ -2122,7 +2122,7 @@
         <v>No</v>
       </c>
       <c r="S26">
-        <v>68</v>
+        <v>75</v>
       </c>
     </row>
     <row r="27">
@@ -2169,7 +2169,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O27" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P27" t="str">
         <v>Today</v>
@@ -2178,18 +2178,18 @@
         <v>No</v>
       </c>
       <c r="R27" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S27">
-        <v>36</v>
+        <v>50</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>job-5dedbaad</v>
+        <v>job-0bc700c9</v>
       </c>
       <c r="B28" t="str">
-        <v>Staff Product Manager, Sail Core</v>
+        <v>Staff Product Manager, Payments Intelligence</v>
       </c>
       <c r="C28" t="str">
         <v>Stripe</v>
@@ -2207,10 +2207,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H28" t="str">
-        <v>New York, US - Remote, Toronto</v>
+        <v>NYC, SF, Seattle, US - Remote</v>
       </c>
       <c r="I28" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J28" t="str">
         <v>Remote</v>
@@ -2219,7 +2219,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L28" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/7913698</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/8209996</v>
       </c>
       <c r="M28">
         <v>200</v>
@@ -2228,7 +2228,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O28" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P28" t="str">
         <v>Today</v>
@@ -2240,15 +2240,15 @@
         <v>No</v>
       </c>
       <c r="S28">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>job-6ad386a3</v>
+        <v>job-5dedbaad</v>
       </c>
       <c r="B29" t="str">
-        <v>Staff Product Manager, Stripe Tax</v>
+        <v>Staff Product Manager, Sail Core</v>
       </c>
       <c r="C29" t="str">
         <v>Stripe</v>
@@ -2266,19 +2266,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H29" t="str">
-        <v>Dublin, Ireland</v>
+        <v>New York, US - Remote, Toronto</v>
       </c>
       <c r="I29" t="str">
-        <v>Dublin</v>
+        <v>New York</v>
       </c>
       <c r="J29" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K29" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L29" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/8124304</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/7913698</v>
       </c>
       <c r="M29">
         <v>200</v>
@@ -2287,7 +2287,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O29" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P29" t="str">
         <v>Today</v>
@@ -2299,36 +2299,36 @@
         <v>No</v>
       </c>
       <c r="S29">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>job-0349189e</v>
+        <v>job-6ad386a3</v>
       </c>
       <c r="B30" t="str">
-        <v>Product Manager, Identity</v>
+        <v>Staff Product Manager, Stripe Tax</v>
       </c>
       <c r="C30" t="str">
-        <v>Airbnb</v>
+        <v>Stripe</v>
       </c>
       <c r="D30" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E30" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F30" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G30" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H30" t="str">
-        <v>United States</v>
+        <v>Dublin, Ireland</v>
       </c>
       <c r="I30" t="str">
-        <v>United States</v>
+        <v>Dublin</v>
       </c>
       <c r="J30" t="str">
         <v>On-site</v>
@@ -2337,7 +2337,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L30" t="str">
-        <v>https://boards.greenhouse.io/airbnb/jobs/8055637</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/8124304</v>
       </c>
       <c r="M30">
         <v>200</v>
@@ -2346,27 +2346,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O30" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P30" t="str">
         <v>Today</v>
       </c>
       <c r="Q30" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R30" t="str">
         <v>No</v>
       </c>
       <c r="S30">
-        <v>54</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>job-7eca2194</v>
+        <v>job-0349189e</v>
       </c>
       <c r="B31" t="str">
-        <v>Product Manager, Pricing</v>
+        <v>Product Manager, Identity</v>
       </c>
       <c r="C31" t="str">
         <v>Airbnb</v>
@@ -2396,7 +2396,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L31" t="str">
-        <v>https://boards.greenhouse.io/airbnb/jobs/8096359</v>
+        <v>https://boards.greenhouse.io/airbnb/jobs/8055637</v>
       </c>
       <c r="M31">
         <v>200</v>
@@ -2405,27 +2405,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O31" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P31" t="str">
         <v>Today</v>
       </c>
       <c r="Q31" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R31" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S31">
-        <v>64</v>
+        <v>35</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>job-4efc96ba</v>
+        <v>job-7eca2194</v>
       </c>
       <c r="B32" t="str">
-        <v>Product Manager, Relevance and Personalization</v>
+        <v>Product Manager, Pricing</v>
       </c>
       <c r="C32" t="str">
         <v>Airbnb</v>
@@ -2443,10 +2443,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H32" t="str">
-        <v>San Francisco, United States</v>
+        <v>United States</v>
       </c>
       <c r="I32" t="str">
-        <v>San Francisco</v>
+        <v>United States</v>
       </c>
       <c r="J32" t="str">
         <v>On-site</v>
@@ -2455,7 +2455,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L32" t="str">
-        <v>https://boards.greenhouse.io/airbnb/jobs/7905365</v>
+        <v>https://boards.greenhouse.io/airbnb/jobs/8096359</v>
       </c>
       <c r="M32">
         <v>200</v>
@@ -2464,27 +2464,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O32" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P32" t="str">
         <v>Today</v>
       </c>
       <c r="Q32" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R32" t="str">
         <v>No</v>
       </c>
       <c r="S32">
-        <v>31</v>
+        <v>84</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>job-50963334</v>
+        <v>job-4efc96ba</v>
       </c>
       <c r="B33" t="str">
-        <v>Product Manager, Search</v>
+        <v>Product Manager, Relevance and Personalization</v>
       </c>
       <c r="C33" t="str">
         <v>Airbnb</v>
@@ -2514,7 +2514,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L33" t="str">
-        <v>https://boards.greenhouse.io/airbnb/jobs/8104444</v>
+        <v>https://boards.greenhouse.io/airbnb/jobs/7905365</v>
       </c>
       <c r="M33">
         <v>200</v>
@@ -2523,7 +2523,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O33" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P33" t="str">
         <v>Today</v>
@@ -2535,15 +2535,15 @@
         <v>No</v>
       </c>
       <c r="S33">
-        <v>70</v>
+        <v>46</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>job-3659f302</v>
+        <v>job-50963334</v>
       </c>
       <c r="B34" t="str">
-        <v>Product Manager, Services</v>
+        <v>Product Manager, Search</v>
       </c>
       <c r="C34" t="str">
         <v>Airbnb</v>
@@ -2561,7 +2561,7 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H34" t="str">
-        <v>San Francisco, CA, Seattle WA, New York, NY</v>
+        <v>San Francisco, United States</v>
       </c>
       <c r="I34" t="str">
         <v>San Francisco</v>
@@ -2573,7 +2573,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L34" t="str">
-        <v>https://boards.greenhouse.io/airbnb/jobs/8081925</v>
+        <v>https://boards.greenhouse.io/airbnb/jobs/8104444</v>
       </c>
       <c r="M34">
         <v>200</v>
@@ -2582,7 +2582,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O34" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P34" t="str">
         <v>Today</v>
@@ -2594,15 +2594,15 @@
         <v>No</v>
       </c>
       <c r="S34">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>job-391d2d18</v>
+        <v>job-3659f302</v>
       </c>
       <c r="B35" t="str">
-        <v>Staff Platform Manager, Loyalty Platform Lead (Product Management)</v>
+        <v>Product Manager, Services</v>
       </c>
       <c r="C35" t="str">
         <v>Airbnb</v>
@@ -2611,19 +2611,19 @@
         <v>LinkedIn</v>
       </c>
       <c r="E35" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F35" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G35" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H35" t="str">
-        <v>Bangalore, India</v>
+        <v>San Francisco, CA, Seattle WA, New York, NY</v>
       </c>
       <c r="I35" t="str">
-        <v>Bengaluru</v>
+        <v>San Francisco</v>
       </c>
       <c r="J35" t="str">
         <v>On-site</v>
@@ -2632,7 +2632,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L35" t="str">
-        <v>https://boards.greenhouse.io/airbnb/jobs/8091831</v>
+        <v>https://boards.greenhouse.io/airbnb/jobs/8081925</v>
       </c>
       <c r="M35">
         <v>200</v>
@@ -2641,7 +2641,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O35" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P35" t="str">
         <v>Today</v>
@@ -2653,7 +2653,7 @@
         <v>No</v>
       </c>
       <c r="S35">
-        <v>27</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36">
@@ -2700,7 +2700,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O36" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P36" t="str">
         <v>Today</v>
@@ -2709,10 +2709,10 @@
         <v>Yes</v>
       </c>
       <c r="R36" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S36">
-        <v>39</v>
+        <v>71</v>
       </c>
     </row>
     <row r="37">
@@ -2759,13 +2759,13 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O37" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P37" t="str">
         <v>Today</v>
       </c>
       <c r="Q37" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R37" t="str">
         <v>No</v>
@@ -2812,13 +2812,13 @@
         <v>https://boards.greenhouse.io/datadog/jobs/8024863</v>
       </c>
       <c r="M38">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="N38" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O38" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P38" t="str">
         <v>Today</v>
@@ -2830,7 +2830,7 @@
         <v>No</v>
       </c>
       <c r="S38">
-        <v>72</v>
+        <v>75</v>
       </c>
     </row>
     <row r="39">
@@ -2877,7 +2877,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O39" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P39" t="str">
         <v>Today</v>
@@ -2889,7 +2889,7 @@
         <v>Yes</v>
       </c>
       <c r="S39">
-        <v>51</v>
+        <v>32</v>
       </c>
     </row>
     <row r="40">
@@ -2936,19 +2936,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O40" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P40" t="str">
         <v>Today</v>
       </c>
       <c r="Q40" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R40" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S40">
-        <v>88</v>
+        <v>37</v>
       </c>
     </row>
     <row r="41">
@@ -2995,7 +2995,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O41" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P41" t="str">
         <v>Today</v>
@@ -3007,7 +3007,7 @@
         <v>Yes</v>
       </c>
       <c r="S41">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="42">
@@ -3054,7 +3054,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O42" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P42" t="str">
         <v>Today</v>
@@ -3063,10 +3063,10 @@
         <v>Yes</v>
       </c>
       <c r="R42" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S42">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="43">
@@ -3113,7 +3113,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O43" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P43" t="str">
         <v>Today</v>
@@ -3125,7 +3125,7 @@
         <v>No</v>
       </c>
       <c r="S43">
-        <v>94</v>
+        <v>64</v>
       </c>
     </row>
     <row r="44">
@@ -3172,7 +3172,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O44" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P44" t="str">
         <v>Today</v>
@@ -3181,10 +3181,10 @@
         <v>No</v>
       </c>
       <c r="R44" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S44">
-        <v>91</v>
+        <v>65</v>
       </c>
     </row>
     <row r="45">
@@ -3225,25 +3225,25 @@
         <v>https://boards.greenhouse.io/datadog/jobs/7947683</v>
       </c>
       <c r="M45">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="N45" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O45" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P45" t="str">
         <v>Today</v>
       </c>
       <c r="Q45" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R45" t="str">
         <v>No</v>
       </c>
       <c r="S45">
-        <v>80</v>
+        <v>58</v>
       </c>
     </row>
     <row r="46">
@@ -3290,7 +3290,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O46" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P46" t="str">
         <v>Today</v>
@@ -3299,10 +3299,10 @@
         <v>No</v>
       </c>
       <c r="R46" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S46">
-        <v>47</v>
+        <v>56</v>
       </c>
     </row>
     <row r="47">
@@ -3349,7 +3349,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O47" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P47" t="str">
         <v>Today</v>
@@ -3358,10 +3358,10 @@
         <v>No</v>
       </c>
       <c r="R47" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S47">
-        <v>64</v>
+        <v>82</v>
       </c>
     </row>
     <row r="48">
@@ -3408,7 +3408,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O48" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P48" t="str">
         <v>Today</v>
@@ -3417,10 +3417,10 @@
         <v>Yes</v>
       </c>
       <c r="R48" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S48">
-        <v>35</v>
+        <v>71</v>
       </c>
     </row>
     <row r="49">
@@ -3467,7 +3467,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O49" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P49" t="str">
         <v>Today</v>
@@ -3476,10 +3476,10 @@
         <v>Yes</v>
       </c>
       <c r="R49" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S49">
-        <v>60</v>
+        <v>32</v>
       </c>
     </row>
     <row r="50">
@@ -3526,7 +3526,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O50" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P50" t="str">
         <v>Today</v>
@@ -3538,7 +3538,7 @@
         <v>No</v>
       </c>
       <c r="S50">
-        <v>84</v>
+        <v>48</v>
       </c>
     </row>
     <row r="51">
@@ -3585,7 +3585,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O51" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P51" t="str">
         <v>Today</v>
@@ -3644,7 +3644,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O52" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P52" t="str">
         <v>Today</v>
@@ -3656,7 +3656,7 @@
         <v>No</v>
       </c>
       <c r="S52">
-        <v>29</v>
+        <v>72</v>
       </c>
     </row>
     <row r="53">
@@ -3697,25 +3697,25 @@
         <v>https://boards.greenhouse.io/datadog/jobs/7974481</v>
       </c>
       <c r="M53">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="N53" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O53" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P53" t="str">
         <v>Today</v>
       </c>
       <c r="Q53" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R53" t="str">
         <v>No</v>
       </c>
       <c r="S53">
-        <v>50</v>
+        <v>59</v>
       </c>
     </row>
     <row r="54">
@@ -3756,25 +3756,25 @@
         <v>https://boards.greenhouse.io/datadog/jobs/6960503</v>
       </c>
       <c r="M54">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="N54" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O54" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P54" t="str">
         <v>Today</v>
       </c>
       <c r="Q54" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R54" t="str">
         <v>Yes</v>
       </c>
       <c r="S54">
-        <v>85</v>
+        <v>36</v>
       </c>
     </row>
     <row r="55">
@@ -3821,19 +3821,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O55" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P55" t="str">
         <v>Today</v>
       </c>
       <c r="Q55" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R55" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S55">
-        <v>44</v>
+        <v>89</v>
       </c>
     </row>
     <row r="56">
@@ -3880,19 +3880,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O56" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P56" t="str">
         <v>Today</v>
       </c>
       <c r="Q56" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R56" t="str">
         <v>Yes</v>
       </c>
       <c r="S56">
-        <v>56</v>
+        <v>79</v>
       </c>
     </row>
     <row r="57">
@@ -3939,7 +3939,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O57" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P57" t="str">
         <v>Today</v>
@@ -3948,10 +3948,10 @@
         <v>No</v>
       </c>
       <c r="R57" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S57">
-        <v>48</v>
+        <v>26</v>
       </c>
     </row>
     <row r="58">
@@ -3998,7 +3998,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O58" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P58" t="str">
         <v>Today</v>
@@ -4010,7 +4010,7 @@
         <v>No</v>
       </c>
       <c r="S58">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="59">
@@ -4057,7 +4057,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O59" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P59" t="str">
         <v>Today</v>
@@ -4069,7 +4069,7 @@
         <v>No</v>
       </c>
       <c r="S59">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="60">
@@ -4116,19 +4116,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O60" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P60" t="str">
         <v>Today</v>
       </c>
       <c r="Q60" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R60" t="str">
         <v>No</v>
       </c>
       <c r="S60">
-        <v>94</v>
+        <v>69</v>
       </c>
     </row>
     <row r="61">
@@ -4175,19 +4175,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O61" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P61" t="str">
         <v>Today</v>
       </c>
       <c r="Q61" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R61" t="str">
         <v>No</v>
       </c>
       <c r="S61">
-        <v>67</v>
+        <v>92</v>
       </c>
     </row>
     <row r="62">
@@ -4234,7 +4234,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O62" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P62" t="str">
         <v>Today</v>
@@ -4246,7 +4246,7 @@
         <v>No</v>
       </c>
       <c r="S62">
-        <v>62</v>
+        <v>36</v>
       </c>
     </row>
     <row r="63">
@@ -4293,7 +4293,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O63" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P63" t="str">
         <v>Today</v>
@@ -4302,10 +4302,10 @@
         <v>Yes</v>
       </c>
       <c r="R63" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S63">
-        <v>62</v>
+        <v>42</v>
       </c>
     </row>
     <row r="64">
@@ -4352,19 +4352,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O64" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P64" t="str">
         <v>Today</v>
       </c>
       <c r="Q64" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R64" t="str">
         <v>No</v>
       </c>
       <c r="S64">
-        <v>68</v>
+        <v>91</v>
       </c>
     </row>
     <row r="65">
@@ -4411,7 +4411,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O65" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P65" t="str">
         <v>Today</v>
@@ -4420,10 +4420,10 @@
         <v>No</v>
       </c>
       <c r="R65" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S65">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="66">
@@ -4470,19 +4470,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O66" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P66" t="str">
         <v>Today</v>
       </c>
       <c r="Q66" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R66" t="str">
         <v>Yes</v>
       </c>
       <c r="S66">
-        <v>39</v>
+        <v>67</v>
       </c>
     </row>
     <row r="67">
@@ -4529,19 +4529,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O67" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P67" t="str">
         <v>Today</v>
       </c>
       <c r="Q67" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R67" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S67">
-        <v>51</v>
+        <v>29</v>
       </c>
     </row>
     <row r="68">
@@ -4588,19 +4588,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O68" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P68" t="str">
         <v>Today</v>
       </c>
       <c r="Q68" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R68" t="str">
         <v>No</v>
       </c>
       <c r="S68">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="69">
@@ -4647,19 +4647,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O69" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P69" t="str">
         <v>Today</v>
       </c>
       <c r="Q69" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R69" t="str">
         <v>No</v>
       </c>
       <c r="S69">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="70">
@@ -4706,19 +4706,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O70" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P70" t="str">
         <v>Today</v>
       </c>
       <c r="Q70" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R70" t="str">
         <v>No</v>
       </c>
       <c r="S70">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="71">
@@ -4765,19 +4765,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O71" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P71" t="str">
         <v>Today</v>
       </c>
       <c r="Q71" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R71" t="str">
         <v>Yes</v>
       </c>
       <c r="S71">
-        <v>94</v>
+        <v>74</v>
       </c>
     </row>
     <row r="72">
@@ -4824,7 +4824,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O72" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P72" t="str">
         <v>Today</v>
@@ -4833,10 +4833,10 @@
         <v>No</v>
       </c>
       <c r="R72" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S72">
-        <v>28</v>
+        <v>91</v>
       </c>
     </row>
     <row r="73">
@@ -4883,19 +4883,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O73" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P73" t="str">
         <v>Today</v>
       </c>
       <c r="Q73" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R73" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S73">
-        <v>77</v>
+        <v>37</v>
       </c>
     </row>
     <row r="74">
@@ -4942,7 +4942,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O74" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P74" t="str">
         <v>Today</v>
@@ -4954,7 +4954,7 @@
         <v>No</v>
       </c>
       <c r="S74">
-        <v>64</v>
+        <v>27</v>
       </c>
     </row>
     <row r="75">
@@ -5001,7 +5001,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O75" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P75" t="str">
         <v>Today</v>
@@ -5013,7 +5013,7 @@
         <v>No</v>
       </c>
       <c r="S75">
-        <v>48</v>
+        <v>55</v>
       </c>
     </row>
     <row r="76">
@@ -5060,19 +5060,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O76" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P76" t="str">
         <v>Today</v>
       </c>
       <c r="Q76" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R76" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S76">
-        <v>62</v>
+        <v>36</v>
       </c>
     </row>
     <row r="77">
@@ -5119,19 +5119,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O77" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P77" t="str">
         <v>Today</v>
       </c>
       <c r="Q77" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R77" t="str">
         <v>No</v>
       </c>
       <c r="S77">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="78">
@@ -5178,19 +5178,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O78" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P78" t="str">
         <v>Today</v>
       </c>
       <c r="Q78" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R78" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S78">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="79">
@@ -5237,7 +5237,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O79" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P79" t="str">
         <v>Today</v>
@@ -5246,10 +5246,10 @@
         <v>No</v>
       </c>
       <c r="R79" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S79">
-        <v>76</v>
+        <v>65</v>
       </c>
     </row>
     <row r="80">
@@ -5296,7 +5296,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O80" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P80" t="str">
         <v>Today</v>
@@ -5308,7 +5308,7 @@
         <v>No</v>
       </c>
       <c r="S80">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="81">
@@ -5355,19 +5355,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O81" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P81" t="str">
         <v>Today</v>
       </c>
       <c r="Q81" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R81" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S81">
-        <v>68</v>
+        <v>43</v>
       </c>
     </row>
     <row r="82">
@@ -5414,19 +5414,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O82" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P82" t="str">
         <v>Today</v>
       </c>
       <c r="Q82" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R82" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S82">
-        <v>88</v>
+        <v>45</v>
       </c>
     </row>
     <row r="83">
@@ -5473,7 +5473,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O83" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P83" t="str">
         <v>Today</v>
@@ -5485,7 +5485,7 @@
         <v>Yes</v>
       </c>
       <c r="S83">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="84">
@@ -5525,26 +5525,26 @@
       <c r="L84" t="str">
         <v>https://boards.greenhouse.io/elastic/jobs/8155425</v>
       </c>
-      <c r="M84" t="str">
-        <v>ACTIVE_PORTAL</v>
+      <c r="M84">
+        <v>200</v>
       </c>
       <c r="N84" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O84" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P84" t="str">
         <v>Today</v>
       </c>
       <c r="Q84" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R84" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S84">
-        <v>70</v>
+        <v>31</v>
       </c>
     </row>
     <row r="85">
@@ -5570,10 +5570,10 @@
         <v>8+ yrs</v>
       </c>
       <c r="H85" t="str">
-        <v>Ireland</v>
+        <v>Greece</v>
       </c>
       <c r="I85" t="str">
-        <v>Ireland</v>
+        <v>Greece</v>
       </c>
       <c r="J85" t="str">
         <v>On-site</v>
@@ -5582,7 +5582,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L85" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8155326</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8155348</v>
       </c>
       <c r="M85">
         <v>200</v>
@@ -5591,7 +5591,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O85" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P85" t="str">
         <v>Today</v>
@@ -5603,7 +5603,7 @@
         <v>Yes</v>
       </c>
       <c r="S85">
-        <v>78</v>
+        <v>42</v>
       </c>
     </row>
     <row r="86">
@@ -5629,10 +5629,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H86" t="str">
-        <v>United States</v>
+        <v>Canada</v>
       </c>
       <c r="I86" t="str">
-        <v>United States</v>
+        <v>Canada</v>
       </c>
       <c r="J86" t="str">
         <v>On-site</v>
@@ -5641,7 +5641,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L86" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8214106</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8214187</v>
       </c>
       <c r="M86">
         <v>200</v>
@@ -5650,7 +5650,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O86" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P86" t="str">
         <v>Today</v>
@@ -5659,10 +5659,10 @@
         <v>No</v>
       </c>
       <c r="R86" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S86">
-        <v>83</v>
+        <v>32</v>
       </c>
     </row>
     <row r="87">
@@ -5688,10 +5688,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H87" t="str">
-        <v>Canada</v>
+        <v>United States</v>
       </c>
       <c r="I87" t="str">
-        <v>Canada</v>
+        <v>United States</v>
       </c>
       <c r="J87" t="str">
         <v>On-site</v>
@@ -5700,7 +5700,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L87" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8093933</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8088818</v>
       </c>
       <c r="M87">
         <v>200</v>
@@ -5709,7 +5709,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O87" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P87" t="str">
         <v>Today</v>
@@ -5721,7 +5721,7 @@
         <v>No</v>
       </c>
       <c r="S87">
-        <v>76</v>
+        <v>47</v>
       </c>
     </row>
     <row r="88">
@@ -5768,7 +5768,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O88" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P88" t="str">
         <v>Today</v>
@@ -5777,10 +5777,10 @@
         <v>Yes</v>
       </c>
       <c r="R88" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S88">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="89">
@@ -5806,10 +5806,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H89" t="str">
-        <v>Hungary</v>
+        <v>Spain</v>
       </c>
       <c r="I89" t="str">
-        <v>Hungary</v>
+        <v>Spain</v>
       </c>
       <c r="J89" t="str">
         <v>On-site</v>
@@ -5818,7 +5818,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L89" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8041209</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8028261</v>
       </c>
       <c r="M89">
         <v>200</v>
@@ -5827,7 +5827,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O89" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P89" t="str">
         <v>Today</v>
@@ -5836,10 +5836,10 @@
         <v>Yes</v>
       </c>
       <c r="R89" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S89">
-        <v>49</v>
+        <v>78</v>
       </c>
     </row>
     <row r="90">
@@ -5886,19 +5886,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O90" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P90" t="str">
         <v>Today</v>
       </c>
       <c r="Q90" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R90" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S90">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="91">
@@ -5924,10 +5924,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H91" t="str">
-        <v>Greece</v>
+        <v>Poland</v>
       </c>
       <c r="I91" t="str">
-        <v>Greece</v>
+        <v>Poland</v>
       </c>
       <c r="J91" t="str">
         <v>On-site</v>
@@ -5936,7 +5936,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L91" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8194216</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8194139</v>
       </c>
       <c r="M91">
         <v>200</v>
@@ -5945,19 +5945,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O91" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P91" t="str">
         <v>Today</v>
       </c>
       <c r="Q91" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R91" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S91">
-        <v>28</v>
+        <v>64</v>
       </c>
     </row>
     <row r="92">
@@ -6004,7 +6004,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O92" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P92" t="str">
         <v>Today</v>
@@ -6013,10 +6013,10 @@
         <v>Yes</v>
       </c>
       <c r="R92" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S92">
-        <v>92</v>
+        <v>56</v>
       </c>
     </row>
     <row r="93">
@@ -6042,10 +6042,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H93" t="str">
-        <v>New York, NY</v>
+        <v>London, UK</v>
       </c>
       <c r="I93" t="str">
-        <v>New York</v>
+        <v>London</v>
       </c>
       <c r="J93" t="str">
         <v>On-site</v>
@@ -6054,7 +6054,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L93" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4673051005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4644742005</v>
       </c>
       <c r="M93">
         <v>200</v>
@@ -6063,7 +6063,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O93" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P93" t="str">
         <v>Today</v>
@@ -6072,10 +6072,10 @@
         <v>Yes</v>
       </c>
       <c r="R93" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S93">
-        <v>25</v>
+        <v>87</v>
       </c>
     </row>
     <row r="94">
@@ -6122,7 +6122,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O94" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P94" t="str">
         <v>Today</v>
@@ -6134,7 +6134,7 @@
         <v>No</v>
       </c>
       <c r="S94">
-        <v>62</v>
+        <v>80</v>
       </c>
     </row>
     <row r="95">
@@ -6181,19 +6181,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O95" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P95" t="str">
         <v>Today</v>
       </c>
       <c r="Q95" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R95" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S95">
-        <v>94</v>
+        <v>65</v>
       </c>
     </row>
     <row r="96">
@@ -6240,7 +6240,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O96" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P96" t="str">
         <v>Today</v>
@@ -6249,10 +6249,10 @@
         <v>No</v>
       </c>
       <c r="R96" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S96">
-        <v>83</v>
+        <v>74</v>
       </c>
     </row>
     <row r="97">
@@ -6299,19 +6299,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O97" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P97" t="str">
         <v>Today</v>
       </c>
       <c r="Q97" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R97" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S97">
-        <v>35</v>
+        <v>41</v>
       </c>
     </row>
     <row r="98">
@@ -6358,19 +6358,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O98" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P98" t="str">
         <v>Today</v>
       </c>
       <c r="Q98" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R98" t="str">
         <v>No</v>
       </c>
       <c r="S98">
-        <v>84</v>
+        <v>62</v>
       </c>
     </row>
     <row r="99">
@@ -6417,7 +6417,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O99" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P99" t="str">
         <v>Today</v>
@@ -6429,7 +6429,7 @@
         <v>Yes</v>
       </c>
       <c r="S99">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="100">
@@ -6476,19 +6476,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O100" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P100" t="str">
         <v>Today</v>
       </c>
       <c r="Q100" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R100" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S100">
-        <v>94</v>
+        <v>48</v>
       </c>
     </row>
     <row r="101">
@@ -6535,19 +6535,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O101" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P101" t="str">
         <v>Today</v>
       </c>
       <c r="Q101" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R101" t="str">
         <v>No</v>
       </c>
       <c r="S101">
-        <v>81</v>
+        <v>32</v>
       </c>
     </row>
     <row r="102">
@@ -6594,7 +6594,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O102" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P102" t="str">
         <v>Today</v>
@@ -6606,7 +6606,7 @@
         <v>No</v>
       </c>
       <c r="S102">
-        <v>54</v>
+        <v>44</v>
       </c>
     </row>
     <row r="103">
@@ -6653,7 +6653,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O103" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P103" t="str">
         <v>Today</v>
@@ -6665,7 +6665,7 @@
         <v>No</v>
       </c>
       <c r="S103">
-        <v>67</v>
+        <v>43</v>
       </c>
     </row>
     <row r="104">
@@ -6712,19 +6712,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O104" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P104" t="str">
         <v>Today</v>
       </c>
       <c r="Q104" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R104" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S104">
-        <v>41</v>
+        <v>64</v>
       </c>
     </row>
     <row r="105">
@@ -6771,7 +6771,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O105" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P105" t="str">
         <v>Today</v>
@@ -6783,7 +6783,7 @@
         <v>No</v>
       </c>
       <c r="S105">
-        <v>37</v>
+        <v>91</v>
       </c>
     </row>
     <row r="106">
@@ -6830,7 +6830,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O106" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P106" t="str">
         <v>Today</v>
@@ -6842,7 +6842,7 @@
         <v>No</v>
       </c>
       <c r="S106">
-        <v>33</v>
+        <v>52</v>
       </c>
     </row>
     <row r="107">
@@ -6868,10 +6868,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H107" t="str">
-        <v>Vancouver, British Columbia, Canada</v>
+        <v>Seattle, Washington, United States</v>
       </c>
       <c r="I107" t="str">
-        <v>Vancouver</v>
+        <v>Seattle</v>
       </c>
       <c r="J107" t="str">
         <v>On-site</v>
@@ -6880,7 +6880,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L107" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8438584002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8438582002</v>
       </c>
       <c r="M107">
         <v>200</v>
@@ -6889,7 +6889,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O107" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P107" t="str">
         <v>Today</v>
@@ -6898,10 +6898,10 @@
         <v>No</v>
       </c>
       <c r="R107" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S107">
-        <v>59</v>
+        <v>90</v>
       </c>
     </row>
     <row r="108">
@@ -6948,7 +6948,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O108" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P108" t="str">
         <v>Today</v>
@@ -6957,10 +6957,10 @@
         <v>No</v>
       </c>
       <c r="R108" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S108">
-        <v>60</v>
+        <v>42</v>
       </c>
     </row>
     <row r="109">
@@ -7007,7 +7007,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O109" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P109" t="str">
         <v>Today</v>
@@ -7019,7 +7019,7 @@
         <v>No</v>
       </c>
       <c r="S109">
-        <v>35</v>
+        <v>58</v>
       </c>
     </row>
     <row r="110">
@@ -7045,10 +7045,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H110" t="str">
-        <v>Seattle, Washington, United States</v>
+        <v>Vancouver, British Columbia, Canada</v>
       </c>
       <c r="I110" t="str">
-        <v>Seattle</v>
+        <v>Vancouver</v>
       </c>
       <c r="J110" t="str">
         <v>On-site</v>
@@ -7057,7 +7057,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L110" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8432703002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8433764002</v>
       </c>
       <c r="M110">
         <v>200</v>
@@ -7066,7 +7066,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O110" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P110" t="str">
         <v>Today</v>
@@ -7078,7 +7078,7 @@
         <v>Yes</v>
       </c>
       <c r="S110">
-        <v>89</v>
+        <v>38</v>
       </c>
     </row>
     <row r="111">
@@ -7125,7 +7125,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O111" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P111" t="str">
         <v>Today</v>
@@ -7137,7 +7137,7 @@
         <v>No</v>
       </c>
       <c r="S111">
-        <v>77</v>
+        <v>29</v>
       </c>
     </row>
     <row r="112">
@@ -7163,10 +7163,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H112" t="str">
-        <v>New York, New York, United States</v>
+        <v>San Francisco, California, United States</v>
       </c>
       <c r="I112" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J112" t="str">
         <v>On-site</v>
@@ -7175,7 +7175,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L112" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8659237002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8659220002</v>
       </c>
       <c r="M112">
         <v>200</v>
@@ -7184,7 +7184,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O112" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P112" t="str">
         <v>Today</v>
@@ -7196,7 +7196,7 @@
         <v>No</v>
       </c>
       <c r="S112">
-        <v>81</v>
+        <v>39</v>
       </c>
     </row>
     <row r="113">
@@ -7222,10 +7222,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H113" t="str">
-        <v>San Francisco, California, United States</v>
+        <v>Seattle, Washington, United States</v>
       </c>
       <c r="I113" t="str">
-        <v>San Francisco</v>
+        <v>Seattle</v>
       </c>
       <c r="J113" t="str">
         <v>On-site</v>
@@ -7234,7 +7234,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L113" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8659204002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8659210002</v>
       </c>
       <c r="M113">
         <v>200</v>
@@ -7243,19 +7243,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O113" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P113" t="str">
         <v>Today</v>
       </c>
       <c r="Q113" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R113" t="str">
         <v>No</v>
       </c>
       <c r="S113">
-        <v>34</v>
+        <v>59</v>
       </c>
     </row>
     <row r="114">
@@ -7302,19 +7302,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O114" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P114" t="str">
         <v>Today</v>
       </c>
       <c r="Q114" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R114" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S114">
-        <v>94</v>
+        <v>68</v>
       </c>
     </row>
     <row r="115">
@@ -7361,7 +7361,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O115" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P115" t="str">
         <v>Today</v>
@@ -7370,10 +7370,10 @@
         <v>Yes</v>
       </c>
       <c r="R115" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S115">
-        <v>39</v>
+        <v>62</v>
       </c>
     </row>
     <row r="116">
@@ -7399,10 +7399,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H116" t="str">
-        <v>Seattle, Washington, United States</v>
+        <v>San Francisco, California, United States</v>
       </c>
       <c r="I116" t="str">
-        <v>Seattle</v>
+        <v>San Francisco</v>
       </c>
       <c r="J116" t="str">
         <v>On-site</v>
@@ -7411,7 +7411,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L116" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8436530002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8436527002</v>
       </c>
       <c r="M116">
         <v>200</v>
@@ -7420,7 +7420,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O116" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P116" t="str">
         <v>Today</v>
@@ -7429,10 +7429,10 @@
         <v>No</v>
       </c>
       <c r="R116" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S116">
-        <v>83</v>
+        <v>42</v>
       </c>
     </row>
     <row r="117">
@@ -7479,7 +7479,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O117" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P117" t="str">
         <v>Today</v>
@@ -7491,7 +7491,7 @@
         <v>No</v>
       </c>
       <c r="S117">
-        <v>57</v>
+        <v>38</v>
       </c>
     </row>
     <row r="118">
@@ -7538,19 +7538,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O118" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P118" t="str">
         <v>Today</v>
       </c>
       <c r="Q118" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R118" t="str">
         <v>Yes</v>
       </c>
       <c r="S118">
-        <v>83</v>
+        <v>31</v>
       </c>
     </row>
     <row r="119">
@@ -7576,10 +7576,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H119" t="str">
-        <v>Pittsburgh, PA</v>
+        <v>New York, NY</v>
       </c>
       <c r="I119" t="str">
-        <v>Pittsburgh</v>
+        <v>New York</v>
       </c>
       <c r="J119" t="str">
         <v>On-site</v>
@@ -7588,7 +7588,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L119" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8530395002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8737859002</v>
       </c>
       <c r="M119">
         <v>200</v>
@@ -7597,7 +7597,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O119" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P119" t="str">
         <v>Today</v>
@@ -7609,7 +7609,7 @@
         <v>No</v>
       </c>
       <c r="S119">
-        <v>27</v>
+        <v>93</v>
       </c>
     </row>
     <row r="120">
@@ -7656,19 +7656,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O120" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P120" t="str">
         <v>Today</v>
       </c>
       <c r="Q120" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R120" t="str">
         <v>No</v>
       </c>
       <c r="S120">
-        <v>76</v>
+        <v>67</v>
       </c>
     </row>
     <row r="121">
@@ -7694,10 +7694,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H121" t="str">
-        <v>New York, NY</v>
+        <v>Pittsburgh, PA</v>
       </c>
       <c r="I121" t="str">
-        <v>New York</v>
+        <v>Pittsburgh</v>
       </c>
       <c r="J121" t="str">
         <v>On-site</v>
@@ -7706,28 +7706,28 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L121" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8816512002</v>
-      </c>
-      <c r="M121" t="str">
-        <v>ACTIVE_PORTAL</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8827944002</v>
+      </c>
+      <c r="M121">
+        <v>200</v>
       </c>
       <c r="N121" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O121" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P121" t="str">
         <v>Today</v>
       </c>
       <c r="Q121" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R121" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S121">
-        <v>51</v>
+        <v>40</v>
       </c>
     </row>
     <row r="122">
@@ -7774,19 +7774,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O122" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P122" t="str">
         <v>Today</v>
       </c>
       <c r="Q122" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R122" t="str">
         <v>No</v>
       </c>
       <c r="S122">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="123">
@@ -7812,10 +7812,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H123" t="str">
-        <v>New York, NY</v>
+        <v>Pittsburgh, PA</v>
       </c>
       <c r="I123" t="str">
-        <v>New York</v>
+        <v>Pittsburgh</v>
       </c>
       <c r="J123" t="str">
         <v>On-site</v>
@@ -7824,7 +7824,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L123" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8747131002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8747099002</v>
       </c>
       <c r="M123">
         <v>200</v>
@@ -7833,7 +7833,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O123" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P123" t="str">
         <v>Today</v>
@@ -7842,10 +7842,10 @@
         <v>Yes</v>
       </c>
       <c r="R123" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S123">
-        <v>73</v>
+        <v>77</v>
       </c>
     </row>
     <row r="124">
@@ -7892,19 +7892,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O124" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P124" t="str">
         <v>Today</v>
       </c>
       <c r="Q124" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R124" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S124">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="125">
@@ -7951,19 +7951,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O125" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P125" t="str">
         <v>Today</v>
       </c>
       <c r="Q125" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R125" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S125">
-        <v>25</v>
+        <v>85</v>
       </c>
     </row>
     <row r="126">
@@ -8010,7 +8010,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O126" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P126" t="str">
         <v>Today</v>
@@ -8022,7 +8022,7 @@
         <v>No</v>
       </c>
       <c r="S126">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="127">
@@ -8069,19 +8069,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O127" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P127" t="str">
         <v>Today</v>
       </c>
       <c r="Q127" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R127" t="str">
         <v>No</v>
       </c>
       <c r="S127">
-        <v>40</v>
+        <v>29</v>
       </c>
     </row>
     <row r="128">
@@ -8128,7 +8128,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O128" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P128" t="str">
         <v>Today</v>
@@ -8140,7 +8140,7 @@
         <v>No</v>
       </c>
       <c r="S128">
-        <v>79</v>
+        <v>61</v>
       </c>
     </row>
     <row r="129">
@@ -8187,19 +8187,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O129" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P129" t="str">
         <v>Today</v>
       </c>
       <c r="Q129" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R129" t="str">
         <v>No</v>
       </c>
       <c r="S129">
-        <v>69</v>
+        <v>58</v>
       </c>
     </row>
     <row r="130">
@@ -8246,7 +8246,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O130" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P130" t="str">
         <v>Today</v>
@@ -8258,7 +8258,7 @@
         <v>No</v>
       </c>
       <c r="S130">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="131">
@@ -8305,7 +8305,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O131" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P131" t="str">
         <v>Today</v>
@@ -8317,7 +8317,7 @@
         <v>Yes</v>
       </c>
       <c r="S131">
-        <v>66</v>
+        <v>51</v>
       </c>
     </row>
     <row r="132">
@@ -8364,19 +8364,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O132" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P132" t="str">
         <v>Today</v>
       </c>
       <c r="Q132" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R132" t="str">
         <v>Yes</v>
       </c>
       <c r="S132">
-        <v>84</v>
+        <v>56</v>
       </c>
     </row>
     <row r="133">
@@ -8416,26 +8416,26 @@
       <c r="L133" t="str">
         <v>https://boards.greenhouse.io/coinbase/jobs/8148171</v>
       </c>
-      <c r="M133" t="str">
-        <v>ACTIVE_PORTAL</v>
+      <c r="M133">
+        <v>403</v>
       </c>
       <c r="N133" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O133" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P133" t="str">
         <v>Today</v>
       </c>
       <c r="Q133" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R133" t="str">
         <v>No</v>
       </c>
       <c r="S133">
-        <v>56</v>
+        <v>81</v>
       </c>
     </row>
     <row r="134">
@@ -8482,19 +8482,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O134" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P134" t="str">
         <v>Today</v>
       </c>
       <c r="Q134" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R134" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S134">
-        <v>41</v>
+        <v>77</v>
       </c>
     </row>
     <row r="135">
@@ -8535,13 +8535,13 @@
         <v>https://boards.greenhouse.io/gitlab/jobs/8806017002</v>
       </c>
       <c r="M135">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N135" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O135" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P135" t="str">
         <v>Today</v>
@@ -8550,10 +8550,10 @@
         <v>No</v>
       </c>
       <c r="R135" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S135">
-        <v>91</v>
+        <v>25</v>
       </c>
     </row>
     <row r="136">
@@ -8600,7 +8600,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O136" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P136" t="str">
         <v>Today</v>
@@ -8609,10 +8609,10 @@
         <v>Yes</v>
       </c>
       <c r="R136" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S136">
-        <v>75</v>
+        <v>41</v>
       </c>
     </row>
     <row r="137">
@@ -8659,7 +8659,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O137" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P137" t="str">
         <v>Today</v>
@@ -8671,7 +8671,7 @@
         <v>No</v>
       </c>
       <c r="S137">
-        <v>47</v>
+        <v>86</v>
       </c>
     </row>
     <row r="138">
@@ -8718,7 +8718,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O138" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P138" t="str">
         <v>Today</v>
@@ -8727,10 +8727,10 @@
         <v>No</v>
       </c>
       <c r="R138" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S138">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="139">
@@ -8777,7 +8777,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O139" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P139" t="str">
         <v>Today</v>
@@ -8786,10 +8786,10 @@
         <v>No</v>
       </c>
       <c r="R139" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S139">
-        <v>90</v>
+        <v>76</v>
       </c>
     </row>
     <row r="140">
@@ -8829,14 +8829,14 @@
       <c r="L140" t="str">
         <v>https://boards.greenhouse.io/gitlab/jobs/8597805002</v>
       </c>
-      <c r="M140" t="str">
-        <v>ACTIVE_PORTAL</v>
+      <c r="M140">
+        <v>200</v>
       </c>
       <c r="N140" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O140" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P140" t="str">
         <v>Today</v>
@@ -8845,10 +8845,10 @@
         <v>Yes</v>
       </c>
       <c r="R140" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S140">
-        <v>76</v>
+        <v>38</v>
       </c>
     </row>
     <row r="141">
@@ -8895,7 +8895,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O141" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P141" t="str">
         <v>Today</v>
@@ -8907,7 +8907,7 @@
         <v>No</v>
       </c>
       <c r="S141">
-        <v>31</v>
+        <v>55</v>
       </c>
     </row>
     <row r="142">
@@ -8954,7 +8954,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O142" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P142" t="str">
         <v>Today</v>
@@ -8966,7 +8966,7 @@
         <v>No</v>
       </c>
       <c r="S142">
-        <v>28</v>
+        <v>69</v>
       </c>
     </row>
     <row r="143">
@@ -9013,19 +9013,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O143" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P143" t="str">
         <v>Today</v>
       </c>
       <c r="Q143" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R143" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S143">
-        <v>48</v>
+        <v>77</v>
       </c>
     </row>
     <row r="144">
@@ -9072,19 +9072,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O144" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P144" t="str">
         <v>Today</v>
       </c>
       <c r="Q144" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R144" t="str">
         <v>Yes</v>
       </c>
       <c r="S144">
-        <v>41</v>
+        <v>94</v>
       </c>
     </row>
     <row r="145">
@@ -9131,7 +9131,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O145" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P145" t="str">
         <v>Today</v>
@@ -9143,7 +9143,7 @@
         <v>No</v>
       </c>
       <c r="S145">
-        <v>91</v>
+        <v>84</v>
       </c>
     </row>
     <row r="146">
@@ -9190,19 +9190,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O146" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P146" t="str">
         <v>Today</v>
       </c>
       <c r="Q146" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R146" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S146">
-        <v>87</v>
+        <v>50</v>
       </c>
     </row>
     <row r="147">
@@ -9249,19 +9249,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O147" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P147" t="str">
         <v>Today</v>
       </c>
       <c r="Q147" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R147" t="str">
         <v>No</v>
       </c>
       <c r="S147">
-        <v>48</v>
+        <v>84</v>
       </c>
     </row>
     <row r="148">
@@ -9308,7 +9308,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O148" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P148" t="str">
         <v>Today</v>
@@ -9320,7 +9320,7 @@
         <v>No</v>
       </c>
       <c r="S148">
-        <v>59</v>
+        <v>33</v>
       </c>
     </row>
     <row r="149">
@@ -9367,19 +9367,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O149" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P149" t="str">
         <v>Today</v>
       </c>
       <c r="Q149" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R149" t="str">
         <v>Yes</v>
       </c>
       <c r="S149">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="150">
@@ -9426,7 +9426,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O150" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P150" t="str">
         <v>Today</v>
@@ -9438,7 +9438,7 @@
         <v>Yes</v>
       </c>
       <c r="S150">
-        <v>38</v>
+        <v>70</v>
       </c>
     </row>
     <row r="151">
@@ -9485,7 +9485,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O151" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P151" t="str">
         <v>Today</v>
@@ -9497,7 +9497,7 @@
         <v>Yes</v>
       </c>
       <c r="S151">
-        <v>55</v>
+        <v>86</v>
       </c>
     </row>
     <row r="152">
@@ -9544,19 +9544,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O152" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P152" t="str">
         <v>Today</v>
       </c>
       <c r="Q152" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R152" t="str">
         <v>No</v>
       </c>
       <c r="S152">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="153">
@@ -9603,19 +9603,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O153" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P153" t="str">
         <v>Today</v>
       </c>
       <c r="Q153" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R153" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S153">
-        <v>81</v>
+        <v>25</v>
       </c>
     </row>
     <row r="154">
@@ -9662,19 +9662,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O154" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P154" t="str">
         <v>Today</v>
       </c>
       <c r="Q154" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R154" t="str">
         <v>No</v>
       </c>
       <c r="S154">
-        <v>38</v>
+        <v>61</v>
       </c>
     </row>
     <row r="155">
@@ -9721,19 +9721,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O155" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P155" t="str">
         <v>Today</v>
       </c>
       <c r="Q155" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R155" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S155">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="156">
@@ -9780,19 +9780,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O156" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P156" t="str">
         <v>Today</v>
       </c>
       <c r="Q156" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R156" t="str">
         <v>No</v>
       </c>
       <c r="S156">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="157">
@@ -9839,7 +9839,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O157" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P157" t="str">
         <v>Today</v>
@@ -9851,7 +9851,7 @@
         <v>No</v>
       </c>
       <c r="S157">
-        <v>40</v>
+        <v>69</v>
       </c>
     </row>
     <row r="158">
@@ -9898,19 +9898,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O158" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P158" t="str">
         <v>Today</v>
       </c>
       <c r="Q158" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R158" t="str">
         <v>No</v>
       </c>
       <c r="S158">
-        <v>72</v>
+        <v>44</v>
       </c>
     </row>
     <row r="159">
@@ -9957,7 +9957,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O159" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P159" t="str">
         <v>Today</v>
@@ -9966,10 +9966,10 @@
         <v>No</v>
       </c>
       <c r="R159" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S159">
-        <v>60</v>
+        <v>80</v>
       </c>
     </row>
     <row r="160">
@@ -10016,7 +10016,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O160" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P160" t="str">
         <v>Today</v>
@@ -10025,10 +10025,10 @@
         <v>No</v>
       </c>
       <c r="R160" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S160">
-        <v>60</v>
+        <v>42</v>
       </c>
     </row>
     <row r="161">
@@ -10075,7 +10075,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O161" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P161" t="str">
         <v>Today</v>
@@ -10087,7 +10087,7 @@
         <v>No</v>
       </c>
       <c r="S161">
-        <v>94</v>
+        <v>81</v>
       </c>
     </row>
     <row r="162">
@@ -10113,7 +10113,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H162" t="str">
-        <v>United States - Remote</v>
+        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
       </c>
       <c r="I162" t="str">
         <v>Remote</v>
@@ -10125,7 +10125,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L162" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8120469</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8120471</v>
       </c>
       <c r="M162">
         <v>200</v>
@@ -10134,19 +10134,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O162" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P162" t="str">
         <v>Today</v>
       </c>
       <c r="Q162" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R162" t="str">
         <v>No</v>
       </c>
       <c r="S162">
-        <v>60</v>
+        <v>69</v>
       </c>
     </row>
     <row r="163">
@@ -10172,7 +10172,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H163" t="str">
-        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
+        <v>United States - Remote</v>
       </c>
       <c r="I163" t="str">
         <v>Remote</v>
@@ -10184,7 +10184,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L163" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8198161</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8198159</v>
       </c>
       <c r="M163">
         <v>200</v>
@@ -10193,7 +10193,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O163" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P163" t="str">
         <v>Today</v>
@@ -10202,10 +10202,10 @@
         <v>No</v>
       </c>
       <c r="R163" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S163">
-        <v>56</v>
+        <v>66</v>
       </c>
     </row>
     <row r="164">
@@ -10231,7 +10231,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H164" t="str">
-        <v>United States - Remote</v>
+        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
       </c>
       <c r="I164" t="str">
         <v>Remote</v>
@@ -10243,7 +10243,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L164" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8143270</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8143272</v>
       </c>
       <c r="M164">
         <v>200</v>
@@ -10252,7 +10252,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O164" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P164" t="str">
         <v>Today</v>
@@ -10264,7 +10264,7 @@
         <v>No</v>
       </c>
       <c r="S164">
-        <v>70</v>
+        <v>54</v>
       </c>
     </row>
     <row r="165">
@@ -10311,19 +10311,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O165" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P165" t="str">
         <v>Today</v>
       </c>
       <c r="Q165" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R165" t="str">
         <v>No</v>
       </c>
       <c r="S165">
-        <v>80</v>
+        <v>40</v>
       </c>
     </row>
     <row r="166">
@@ -10370,7 +10370,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O166" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P166" t="str">
         <v>Today</v>
@@ -10382,7 +10382,7 @@
         <v>No</v>
       </c>
       <c r="S166">
-        <v>73</v>
+        <v>38</v>
       </c>
     </row>
     <row r="167">
@@ -10429,19 +10429,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O167" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P167" t="str">
         <v>Today</v>
       </c>
       <c r="Q167" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R167" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S167">
-        <v>34</v>
+        <v>62</v>
       </c>
     </row>
     <row r="168">
@@ -10488,7 +10488,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O168" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P168" t="str">
         <v>Today</v>
@@ -10497,10 +10497,10 @@
         <v>Yes</v>
       </c>
       <c r="R168" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S168">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="169">
@@ -10547,7 +10547,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O169" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P169" t="str">
         <v>Today</v>
@@ -10556,10 +10556,10 @@
         <v>Yes</v>
       </c>
       <c r="R169" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S169">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="170">
@@ -10606,7 +10606,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O170" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P170" t="str">
         <v>Today</v>
@@ -10615,10 +10615,10 @@
         <v>Yes</v>
       </c>
       <c r="R170" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S170">
-        <v>114</v>
+        <v>72</v>
       </c>
     </row>
     <row r="171">
@@ -10665,7 +10665,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O171" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P171" t="str">
         <v>Today</v>
@@ -10677,7 +10677,7 @@
         <v>Yes</v>
       </c>
       <c r="S171">
-        <v>109</v>
+        <v>113</v>
       </c>
     </row>
     <row r="172">
@@ -10724,7 +10724,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O172" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P172" t="str">
         <v>Today</v>
@@ -10736,7 +10736,7 @@
         <v>Yes</v>
       </c>
       <c r="S172">
-        <v>76</v>
+        <v>108</v>
       </c>
     </row>
     <row r="173">
@@ -10783,7 +10783,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O173" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P173" t="str">
         <v>Today</v>
@@ -10792,18 +10792,18 @@
         <v>Yes</v>
       </c>
       <c r="R173" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S173">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>job-6dc78859</v>
+        <v>job-032480cd</v>
       </c>
       <c r="B174" t="str">
-        <v>Product Manager, Legal</v>
+        <v>Product Manager, Youth</v>
       </c>
       <c r="C174" t="str">
         <v>OpenAI</v>
@@ -10833,7 +10833,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L174" t="str">
-        <v>https://jobs.ashbyhq.com/openai/83b3ef17-5211-403d-b763-850e1c60faa0</v>
+        <v>https://jobs.ashbyhq.com/openai/cc0d0d86-eb9d-44a0-a6a4-42bbb6066b4b</v>
       </c>
       <c r="M174">
         <v>200</v>
@@ -10842,7 +10842,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O174" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P174" t="str">
         <v>Today</v>
@@ -10854,15 +10854,15 @@
         <v>Yes</v>
       </c>
       <c r="S174">
-        <v>57</v>
+        <v>106</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>job-032480cd</v>
+        <v>job-50e54898</v>
       </c>
       <c r="B175" t="str">
-        <v>Product Manager, Youth</v>
+        <v>Product Manager, Learning</v>
       </c>
       <c r="C175" t="str">
         <v>OpenAI</v>
@@ -10892,7 +10892,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L175" t="str">
-        <v>https://jobs.ashbyhq.com/openai/cc0d0d86-eb9d-44a0-a6a4-42bbb6066b4b</v>
+        <v>https://jobs.ashbyhq.com/openai/5953fed7-1466-4e90-94c9-43716a55e032</v>
       </c>
       <c r="M175">
         <v>200</v>
@@ -10901,7 +10901,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O175" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P175" t="str">
         <v>Today</v>
@@ -10913,15 +10913,15 @@
         <v>No</v>
       </c>
       <c r="S175">
-        <v>52</v>
+        <v>65</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>job-50e54898</v>
+        <v>job-0df96522</v>
       </c>
       <c r="B176" t="str">
-        <v>Product Manager, Learning</v>
+        <v>Product Manager, Multimodal Safety</v>
       </c>
       <c r="C176" t="str">
         <v>OpenAI</v>
@@ -10951,7 +10951,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L176" t="str">
-        <v>https://jobs.ashbyhq.com/openai/5953fed7-1466-4e90-94c9-43716a55e032</v>
+        <v>https://jobs.ashbyhq.com/openai/70d5259a-f18c-4595-bf52-ec03eeeeac4c</v>
       </c>
       <c r="M176">
         <v>200</v>
@@ -10960,7 +10960,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O176" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P176" t="str">
         <v>Today</v>
@@ -10972,15 +10972,15 @@
         <v>No</v>
       </c>
       <c r="S176">
-        <v>84</v>
+        <v>114</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>job-0df96522</v>
+        <v>job-47895783</v>
       </c>
       <c r="B177" t="str">
-        <v>Product Manager, Multimodal Safety</v>
+        <v>Product Manager, Enterprise Identity</v>
       </c>
       <c r="C177" t="str">
         <v>OpenAI</v>
@@ -11010,7 +11010,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L177" t="str">
-        <v>https://jobs.ashbyhq.com/openai/70d5259a-f18c-4595-bf52-ec03eeeeac4c</v>
+        <v>https://jobs.ashbyhq.com/openai/83f6d415-9462-4afc-a539-ca8d996e011a</v>
       </c>
       <c r="M177">
         <v>200</v>
@@ -11019,7 +11019,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O177" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P177" t="str">
         <v>Today</v>
@@ -11031,7 +11031,7 @@
         <v>Yes</v>
       </c>
       <c r="S177">
-        <v>100</v>
+        <v>66</v>
       </c>
     </row>
     <row r="178">
@@ -11078,7 +11078,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O178" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P178" t="str">
         <v>Today</v>
@@ -11090,7 +11090,7 @@
         <v>No</v>
       </c>
       <c r="S178">
-        <v>92</v>
+        <v>48</v>
       </c>
     </row>
     <row r="179">
@@ -11137,7 +11137,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O179" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P179" t="str">
         <v>Today</v>
@@ -11146,10 +11146,10 @@
         <v>Yes</v>
       </c>
       <c r="R179" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S179">
-        <v>93</v>
+        <v>87</v>
       </c>
     </row>
     <row r="180">
@@ -11196,7 +11196,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O180" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P180" t="str">
         <v>Today</v>
@@ -11205,10 +11205,10 @@
         <v>Yes</v>
       </c>
       <c r="R180" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S180">
-        <v>85</v>
+        <v>63</v>
       </c>
     </row>
     <row r="181">
@@ -11255,7 +11255,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O181" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P181" t="str">
         <v>Today</v>
@@ -11267,7 +11267,7 @@
         <v>Yes</v>
       </c>
       <c r="S181">
-        <v>101</v>
+        <v>74</v>
       </c>
     </row>
     <row r="182">
@@ -11314,7 +11314,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O182" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P182" t="str">
         <v>Today</v>
@@ -11323,10 +11323,10 @@
         <v>Yes</v>
       </c>
       <c r="R182" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S182">
-        <v>81</v>
+        <v>106</v>
       </c>
     </row>
     <row r="183">
@@ -11373,7 +11373,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O183" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P183" t="str">
         <v>Today</v>
@@ -11385,7 +11385,7 @@
         <v>Yes</v>
       </c>
       <c r="S183">
-        <v>113</v>
+        <v>45</v>
       </c>
     </row>
     <row r="184">
@@ -11432,7 +11432,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O184" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P184" t="str">
         <v>Today</v>
@@ -11441,10 +11441,10 @@
         <v>Yes</v>
       </c>
       <c r="R184" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S184">
-        <v>113</v>
+        <v>76</v>
       </c>
     </row>
     <row r="185">
@@ -11491,7 +11491,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O185" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P185" t="str">
         <v>Today</v>
@@ -11503,7 +11503,7 @@
         <v>Yes</v>
       </c>
       <c r="S185">
-        <v>63</v>
+        <v>42</v>
       </c>
     </row>
     <row r="186">
@@ -11550,7 +11550,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O186" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P186" t="str">
         <v>Today</v>
@@ -11559,10 +11559,10 @@
         <v>Yes</v>
       </c>
       <c r="R186" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S186">
-        <v>109</v>
+        <v>101</v>
       </c>
     </row>
     <row r="187">
@@ -11609,7 +11609,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O187" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P187" t="str">
         <v>Today</v>
@@ -11621,7 +11621,7 @@
         <v>Yes</v>
       </c>
       <c r="S187">
-        <v>117</v>
+        <v>48</v>
       </c>
     </row>
     <row r="188">
@@ -11668,7 +11668,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O188" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P188" t="str">
         <v>Today</v>
@@ -11680,7 +11680,7 @@
         <v>No</v>
       </c>
       <c r="S188">
-        <v>106</v>
+        <v>92</v>
       </c>
     </row>
     <row r="189">
@@ -11727,7 +11727,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O189" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P189" t="str">
         <v>Today</v>
@@ -11736,10 +11736,10 @@
         <v>Yes</v>
       </c>
       <c r="R189" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S189">
-        <v>77</v>
+        <v>118</v>
       </c>
     </row>
     <row r="190">
@@ -11786,7 +11786,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O190" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P190" t="str">
         <v>Today</v>
@@ -11795,10 +11795,10 @@
         <v>Yes</v>
       </c>
       <c r="R190" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S190">
-        <v>50</v>
+        <v>89</v>
       </c>
     </row>
     <row r="191">
@@ -11845,7 +11845,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O191" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P191" t="str">
         <v>Today</v>
@@ -11854,10 +11854,10 @@
         <v>Yes</v>
       </c>
       <c r="R191" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S191">
-        <v>68</v>
+        <v>104</v>
       </c>
     </row>
     <row r="192">
@@ -11904,7 +11904,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O192" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P192" t="str">
         <v>Today</v>
@@ -11916,7 +11916,7 @@
         <v>Yes</v>
       </c>
       <c r="S192">
-        <v>106</v>
+        <v>78</v>
       </c>
     </row>
     <row r="193">
@@ -11963,7 +11963,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O193" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P193" t="str">
         <v>Today</v>
@@ -11975,7 +11975,7 @@
         <v>No</v>
       </c>
       <c r="S193">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="194">
@@ -12022,7 +12022,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O194" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P194" t="str">
         <v>Today</v>
@@ -12034,7 +12034,7 @@
         <v>No</v>
       </c>
       <c r="S194">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="195">
@@ -12081,7 +12081,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O195" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P195" t="str">
         <v>Today</v>
@@ -12093,7 +12093,7 @@
         <v>No</v>
       </c>
       <c r="S195">
-        <v>51</v>
+        <v>30</v>
       </c>
     </row>
     <row r="196">
@@ -12140,7 +12140,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O196" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P196" t="str">
         <v>Today</v>
@@ -12152,7 +12152,7 @@
         <v>No</v>
       </c>
       <c r="S196">
-        <v>59</v>
+        <v>52</v>
       </c>
     </row>
     <row r="197">
@@ -12199,7 +12199,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O197" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P197" t="str">
         <v>Today</v>
@@ -12211,7 +12211,7 @@
         <v>No</v>
       </c>
       <c r="S197">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="198">
@@ -12258,7 +12258,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O198" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P198" t="str">
         <v>Today</v>
@@ -12270,7 +12270,7 @@
         <v>No</v>
       </c>
       <c r="S198">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="199">
@@ -12317,7 +12317,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O199" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P199" t="str">
         <v>Today</v>
@@ -12329,7 +12329,7 @@
         <v>No</v>
       </c>
       <c r="S199">
-        <v>87</v>
+        <v>60</v>
       </c>
     </row>
     <row r="200">
@@ -12376,7 +12376,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O200" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P200" t="str">
         <v>Today</v>
@@ -12388,7 +12388,7 @@
         <v>No</v>
       </c>
       <c r="S200">
-        <v>54</v>
+        <v>75</v>
       </c>
     </row>
     <row r="201">
@@ -12435,7 +12435,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O201" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P201" t="str">
         <v>Today</v>
@@ -12447,7 +12447,7 @@
         <v>No</v>
       </c>
       <c r="S201">
-        <v>66</v>
+        <v>89</v>
       </c>
     </row>
     <row r="202">
@@ -12494,7 +12494,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O202" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P202" t="str">
         <v>Today</v>
@@ -12553,7 +12553,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O203" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P203" t="str">
         <v>Today</v>
@@ -12612,7 +12612,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O204" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P204" t="str">
         <v>Today</v>
@@ -12671,7 +12671,7 @@
         <v>BROKEN / 404</v>
       </c>
       <c r="O205" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P205" t="str">
         <v>Today</v>
@@ -12730,7 +12730,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O206" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P206" t="str">
         <v>Today</v>
@@ -12789,7 +12789,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O207" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P207" t="str">
         <v>1d ago</v>
@@ -12848,7 +12848,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O208" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P208" t="str">
         <v>1d ago</v>
@@ -12907,7 +12907,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O209" t="str">
-        <v>2026-09-20</v>
+        <v>2026-09-21</v>
       </c>
       <c r="P209" t="str">
         <v>1d ago</v>
@@ -13124,10 +13124,10 @@
 2. Compute (remoteCount / totalJobs) * 100</v>
       </c>
       <c r="F7" t="str">
-        <v>Displays 63 (30%)</v>
+        <v>Displays 64 (31%)</v>
       </c>
       <c r="G7" t="str">
-        <v>Calculates 63 (30%) flexible roles accurately</v>
+        <v>Calculates 64 (31%) flexible roles accurately</v>
       </c>
       <c r="H7" t="str">
         <v>PASS</v>

--- a/GreenPath_PM_Jobs_Test_Report.xlsx
+++ b/GreenPath_PM_Jobs_Test_Report.xlsx
@@ -428,7 +428,7 @@
         <v>Test Execution Date</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-09-22T01:59:27.904Z</v>
+        <v>2026-09-23T01:56:49.075Z</v>
       </c>
     </row>
     <row r="4">
@@ -436,7 +436,7 @@
         <v>Total Jobs in Feed</v>
       </c>
       <c r="B4">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="5">
@@ -444,7 +444,7 @@
         <v>Total URLs Tested</v>
       </c>
       <c r="B5">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="6">
@@ -452,7 +452,7 @@
         <v>Active / Valid Direct ATS URLs</v>
       </c>
       <c r="B6">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="7">
@@ -524,7 +524,7 @@
         <v>Cities Supported</v>
       </c>
       <c r="B15" t="str">
-        <v>San Francisco, Toronto, Dublin, N/A, New York, Remote, USA, London, Seattle, United States, Paris, Menlo Park, Hybrid, In-Office, Spain, Switzerland, Greece, Canada, Poland, Doha, Vancouver, Pittsburgh, Beijing, Bengaluru, Vienna, North America, Stockholm, Washington, Mumbai, Gurgaon</v>
+        <v>San Francisco, Toronto, Dublin, N/A, New York, Remote, USA, Seattle, London, United States, Paris, Menlo Park, Hybrid, In-Office, Canada, Spain, Switzerland, Israel, Greece, Riyadh, Vancouver, Pittsburgh, Beijing, Bengaluru, Vienna, North America, Stockholm, Washington, Mumbai, Gurgaon</v>
       </c>
     </row>
     <row r="16">
@@ -532,7 +532,7 @@
         <v>Remote / Hybrid Roles</v>
       </c>
       <c r="B16" t="str">
-        <v>64 (31%)</v>
+        <v>64 (30%)</v>
       </c>
     </row>
     <row r="17">
@@ -540,7 +540,7 @@
         <v>Jobs Added Today</v>
       </c>
       <c r="B17" t="str">
-        <v>+205</v>
+        <v>+207</v>
       </c>
     </row>
     <row r="18">
@@ -568,7 +568,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S209"/>
+  <dimension ref="A1:S211"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="38.83203125" customWidth="1"/>
@@ -694,19 +694,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O2" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P2" t="str">
         <v>Today</v>
       </c>
       <c r="Q2" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R2" t="str">
         <v>No</v>
       </c>
       <c r="S2">
-        <v>58</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3">
@@ -753,19 +753,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O3" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P3" t="str">
         <v>Today</v>
       </c>
       <c r="Q3" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R3" t="str">
         <v>No</v>
       </c>
       <c r="S3">
-        <v>41</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4">
@@ -812,19 +812,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O4" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P4" t="str">
         <v>Today</v>
       </c>
       <c r="Q4" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R4" t="str">
         <v>No</v>
       </c>
       <c r="S4">
-        <v>86</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5">
@@ -871,19 +871,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O5" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P5" t="str">
         <v>Today</v>
       </c>
       <c r="Q5" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R5" t="str">
         <v>No</v>
       </c>
       <c r="S5">
-        <v>80</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
@@ -930,7 +930,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O6" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P6" t="str">
         <v>Today</v>
@@ -939,10 +939,10 @@
         <v>No</v>
       </c>
       <c r="R6" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S6">
-        <v>86</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
@@ -989,19 +989,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O7" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P7" t="str">
         <v>Today</v>
       </c>
       <c r="Q7" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R7" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S7">
-        <v>78</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
@@ -1048,7 +1048,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O8" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P8" t="str">
         <v>Today</v>
@@ -1057,10 +1057,10 @@
         <v>No</v>
       </c>
       <c r="R8" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S8">
-        <v>57</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
@@ -1107,19 +1107,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O9" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P9" t="str">
         <v>Today</v>
       </c>
       <c r="Q9" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R9" t="str">
         <v>No</v>
       </c>
       <c r="S9">
-        <v>25</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10">
@@ -1166,7 +1166,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O10" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P10" t="str">
         <v>Today</v>
@@ -1178,15 +1178,15 @@
         <v>No</v>
       </c>
       <c r="S10">
-        <v>69</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>job-0a0eb90c</v>
+        <v>job-72f83b7c</v>
       </c>
       <c r="B11" t="str">
-        <v>Product Manager, Link - Consumer</v>
+        <v>Product Manager - Issuance, Bridge</v>
       </c>
       <c r="C11" t="str">
         <v>Stripe</v>
@@ -1204,19 +1204,19 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H11" t="str">
-        <v>SF, SEA, NY, Remote-US</v>
+        <v>San Francisco Or New York</v>
       </c>
       <c r="I11" t="str">
         <v>San Francisco</v>
       </c>
       <c r="J11" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K11" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L11" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/7392697</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/8223723</v>
       </c>
       <c r="M11">
         <v>200</v>
@@ -1225,7 +1225,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O11" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P11" t="str">
         <v>Today</v>
@@ -1237,15 +1237,15 @@
         <v>No</v>
       </c>
       <c r="S11">
-        <v>77</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>job-59612c0f</v>
+        <v>job-0a0eb90c</v>
       </c>
       <c r="B12" t="str">
-        <v>Product Manager, Link - Local Payment Methods</v>
+        <v>Product Manager, Link - Consumer</v>
       </c>
       <c r="C12" t="str">
         <v>Stripe</v>
@@ -1263,19 +1263,19 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H12" t="str">
-        <v>USA</v>
+        <v>SF, SEA, NY, Remote-US</v>
       </c>
       <c r="I12" t="str">
-        <v>USA</v>
+        <v>San Francisco</v>
       </c>
       <c r="J12" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K12" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L12" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/7981330</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/7392697</v>
       </c>
       <c r="M12">
         <v>200</v>
@@ -1284,7 +1284,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O12" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P12" t="str">
         <v>Today</v>
@@ -1293,18 +1293,18 @@
         <v>No</v>
       </c>
       <c r="R12" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S12">
-        <v>72</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>job-13f73559</v>
+        <v>job-59612c0f</v>
       </c>
       <c r="B13" t="str">
-        <v>Product Manager, Mobile</v>
+        <v>Product Manager, Link - Local Payment Methods</v>
       </c>
       <c r="C13" t="str">
         <v>Stripe</v>
@@ -1322,19 +1322,19 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H13" t="str">
-        <v>New York City, Toronto, Chicago, or Remote</v>
+        <v>USA</v>
       </c>
       <c r="I13" t="str">
-        <v>New York</v>
+        <v>USA</v>
       </c>
       <c r="J13" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K13" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L13" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/8140438</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/7981330</v>
       </c>
       <c r="M13">
         <v>200</v>
@@ -1343,27 +1343,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O13" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P13" t="str">
         <v>Today</v>
       </c>
       <c r="Q13" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R13" t="str">
         <v>No</v>
       </c>
       <c r="S13">
-        <v>86</v>
+        <v>43</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>job-3b0c2ab0</v>
+        <v>job-13f73559</v>
       </c>
       <c r="B14" t="str">
-        <v>Product Manager: New Grad Accelerator</v>
+        <v>Product Manager, Mobile</v>
       </c>
       <c r="C14" t="str">
         <v>Stripe</v>
@@ -1372,7 +1372,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E14" t="str">
-        <v>Associate Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F14" t="str">
         <v>3-6 yrs</v>
@@ -1381,19 +1381,19 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H14" t="str">
-        <v>San Francisco, New York City, Seattle</v>
+        <v>New York City, Toronto, Chicago, or Remote</v>
       </c>
       <c r="I14" t="str">
-        <v>San Francisco</v>
+        <v>New York</v>
       </c>
       <c r="J14" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K14" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L14" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/7737124</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/8140438</v>
       </c>
       <c r="M14">
         <v>200</v>
@@ -1402,7 +1402,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O14" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P14" t="str">
         <v>Today</v>
@@ -1414,15 +1414,15 @@
         <v>Yes</v>
       </c>
       <c r="S14">
-        <v>68</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>job-0792c0d2</v>
+        <v>job-3b0c2ab0</v>
       </c>
       <c r="B15" t="str">
-        <v>Product Manager, Payments</v>
+        <v>Product Manager: New Grad Accelerator</v>
       </c>
       <c r="C15" t="str">
         <v>Stripe</v>
@@ -1431,7 +1431,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E15" t="str">
-        <v>Product Manager</v>
+        <v>Associate Product Manager</v>
       </c>
       <c r="F15" t="str">
         <v>3-6 yrs</v>
@@ -1440,19 +1440,19 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H15" t="str">
-        <v>SF, NY, SEA, Remote-US</v>
+        <v>San Francisco, New York City, Seattle</v>
       </c>
       <c r="I15" t="str">
         <v>San Francisco</v>
       </c>
       <c r="J15" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K15" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L15" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/7176530</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/7737124</v>
       </c>
       <c r="M15">
         <v>200</v>
@@ -1461,27 +1461,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O15" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P15" t="str">
         <v>Today</v>
       </c>
       <c r="Q15" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R15" t="str">
         <v>No</v>
       </c>
       <c r="S15">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>job-01f5d9bc</v>
+        <v>job-0792c0d2</v>
       </c>
       <c r="B16" t="str">
-        <v>Product Manager, Professional Services</v>
+        <v>Product Manager, Payments</v>
       </c>
       <c r="C16" t="str">
         <v>Stripe</v>
@@ -1499,19 +1499,19 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H16" t="str">
-        <v>Dublin, London</v>
+        <v>SF, NY, SEA, Remote-US</v>
       </c>
       <c r="I16" t="str">
-        <v>London</v>
+        <v>San Francisco</v>
       </c>
       <c r="J16" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K16" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L16" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/8007692</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/7176530</v>
       </c>
       <c r="M16">
         <v>200</v>
@@ -1520,7 +1520,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O16" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P16" t="str">
         <v>Today</v>
@@ -1532,7 +1532,7 @@
         <v>No</v>
       </c>
       <c r="S16">
-        <v>85</v>
+        <v>47</v>
       </c>
     </row>
     <row r="17">
@@ -1579,7 +1579,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O17" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P17" t="str">
         <v>Today</v>
@@ -1591,7 +1591,7 @@
         <v>No</v>
       </c>
       <c r="S17">
-        <v>33</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18">
@@ -1638,7 +1638,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O18" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P18" t="str">
         <v>Today</v>
@@ -1650,7 +1650,7 @@
         <v>Yes</v>
       </c>
       <c r="S18">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19">
@@ -1697,19 +1697,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O19" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P19" t="str">
         <v>Today</v>
       </c>
       <c r="Q19" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R19" t="str">
         <v>No</v>
       </c>
       <c r="S19">
-        <v>61</v>
+        <v>75</v>
       </c>
     </row>
     <row r="20">
@@ -1756,7 +1756,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O20" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P20" t="str">
         <v>Today</v>
@@ -1765,10 +1765,10 @@
         <v>No</v>
       </c>
       <c r="R20" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S20">
-        <v>74</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21">
@@ -1815,7 +1815,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O21" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P21" t="str">
         <v>Today</v>
@@ -1827,7 +1827,7 @@
         <v>No</v>
       </c>
       <c r="S21">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="22">
@@ -1874,19 +1874,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O22" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P22" t="str">
         <v>Today</v>
       </c>
       <c r="Q22" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R22" t="str">
         <v>Yes</v>
       </c>
       <c r="S22">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23">
@@ -1933,19 +1933,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O23" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P23" t="str">
         <v>Today</v>
       </c>
       <c r="Q23" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R23" t="str">
         <v>Yes</v>
       </c>
       <c r="S23">
-        <v>89</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24">
@@ -1992,19 +1992,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O24" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P24" t="str">
         <v>Today</v>
       </c>
       <c r="Q24" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R24" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S24">
-        <v>69</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25">
@@ -2051,19 +2051,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O25" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P25" t="str">
         <v>Today</v>
       </c>
       <c r="Q25" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R25" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S25">
-        <v>33</v>
+        <v>72</v>
       </c>
     </row>
     <row r="26">
@@ -2110,7 +2110,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O26" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P26" t="str">
         <v>Today</v>
@@ -2122,7 +2122,7 @@
         <v>No</v>
       </c>
       <c r="S26">
-        <v>75</v>
+        <v>57</v>
       </c>
     </row>
     <row r="27">
@@ -2169,19 +2169,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O27" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P27" t="str">
         <v>Today</v>
       </c>
       <c r="Q27" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R27" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S27">
-        <v>50</v>
+        <v>71</v>
       </c>
     </row>
     <row r="28">
@@ -2228,19 +2228,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O28" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P28" t="str">
         <v>Today</v>
       </c>
       <c r="Q28" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R28" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S28">
-        <v>40</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29">
@@ -2287,19 +2287,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O29" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P29" t="str">
         <v>Today</v>
       </c>
       <c r="Q29" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R29" t="str">
         <v>No</v>
       </c>
       <c r="S29">
-        <v>47</v>
+        <v>68</v>
       </c>
     </row>
     <row r="30">
@@ -2346,19 +2346,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O30" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P30" t="str">
         <v>Today</v>
       </c>
       <c r="Q30" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R30" t="str">
         <v>No</v>
       </c>
       <c r="S30">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31">
@@ -2405,7 +2405,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O31" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P31" t="str">
         <v>Today</v>
@@ -2414,10 +2414,10 @@
         <v>Yes</v>
       </c>
       <c r="R31" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S31">
-        <v>35</v>
+        <v>77</v>
       </c>
     </row>
     <row r="32">
@@ -2464,7 +2464,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O32" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P32" t="str">
         <v>Today</v>
@@ -2473,10 +2473,10 @@
         <v>No</v>
       </c>
       <c r="R32" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S32">
-        <v>84</v>
+        <v>91</v>
       </c>
     </row>
     <row r="33">
@@ -2523,7 +2523,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O33" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P33" t="str">
         <v>Today</v>
@@ -2532,10 +2532,10 @@
         <v>No</v>
       </c>
       <c r="R33" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S33">
-        <v>46</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34">
@@ -2582,19 +2582,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O34" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P34" t="str">
         <v>Today</v>
       </c>
       <c r="Q34" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R34" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S34">
-        <v>53</v>
+        <v>25</v>
       </c>
     </row>
     <row r="35">
@@ -2641,7 +2641,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O35" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P35" t="str">
         <v>Today</v>
@@ -2650,10 +2650,10 @@
         <v>Yes</v>
       </c>
       <c r="R35" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S35">
-        <v>88</v>
+        <v>42</v>
       </c>
     </row>
     <row r="36">
@@ -2700,7 +2700,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O36" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P36" t="str">
         <v>Today</v>
@@ -2712,15 +2712,15 @@
         <v>No</v>
       </c>
       <c r="S36">
-        <v>71</v>
+        <v>84</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>job-7fd73723</v>
+        <v>job-13d0f376</v>
       </c>
       <c r="B37" t="str">
-        <v>Director, Product Management - Platforms</v>
+        <v>Group Product Manager - Bring Your Own Cloud</v>
       </c>
       <c r="C37" t="str">
         <v>Datadog</v>
@@ -2729,13 +2729,13 @@
         <v>Wellfound</v>
       </c>
       <c r="E37" t="str">
-        <v>Technical Product Manager</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F37" t="str">
-        <v>8+ yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G37" t="str">
-        <v>8+ yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H37" t="str">
         <v>New York, New York, USA</v>
@@ -2750,7 +2750,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L37" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/7583609</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/8024863</v>
       </c>
       <c r="M37">
         <v>200</v>
@@ -2759,27 +2759,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O37" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P37" t="str">
         <v>Today</v>
       </c>
       <c r="Q37" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R37" t="str">
         <v>No</v>
       </c>
       <c r="S37">
-        <v>56</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>job-13d0f376</v>
+        <v>job-63e47d39</v>
       </c>
       <c r="B38" t="str">
-        <v>Group Product Manager - Bring Your Own Cloud</v>
+        <v>Group Product Manager - Code Security</v>
       </c>
       <c r="C38" t="str">
         <v>Datadog</v>
@@ -2797,7 +2797,7 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H38" t="str">
-        <v>New York, New York, USA</v>
+        <v>Boston, Massachusetts, USA; New York, New York, USA</v>
       </c>
       <c r="I38" t="str">
         <v>New York</v>
@@ -2809,7 +2809,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L38" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/8024863</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/8023763</v>
       </c>
       <c r="M38">
         <v>200</v>
@@ -2818,7 +2818,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O38" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P38" t="str">
         <v>Today</v>
@@ -2830,15 +2830,15 @@
         <v>No</v>
       </c>
       <c r="S38">
-        <v>75</v>
+        <v>58</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>job-63e47d39</v>
+        <v>job-23f325cc</v>
       </c>
       <c r="B39" t="str">
-        <v>Group Product Manager - Code Security</v>
+        <v>Manager I, Engineering - APM Serverless</v>
       </c>
       <c r="C39" t="str">
         <v>Datadog</v>
@@ -2847,16 +2847,16 @@
         <v>Wellfound</v>
       </c>
       <c r="E39" t="str">
-        <v>Product Lead / Director</v>
+        <v>Associate Product Manager</v>
       </c>
       <c r="F39" t="str">
-        <v>3-6 yrs</v>
+        <v>1-3 yrs</v>
       </c>
       <c r="G39" t="str">
-        <v>2-5 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H39" t="str">
-        <v>Boston, Massachusetts, USA; New York, New York, USA</v>
+        <v>New York, New York, USA</v>
       </c>
       <c r="I39" t="str">
         <v>New York</v>
@@ -2868,7 +2868,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L39" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/8023763</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/8060821</v>
       </c>
       <c r="M39">
         <v>200</v>
@@ -2877,27 +2877,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O39" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P39" t="str">
         <v>Today</v>
       </c>
       <c r="Q39" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R39" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S39">
-        <v>32</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>job-23f325cc</v>
+        <v>job-3c715a0a</v>
       </c>
       <c r="B40" t="str">
-        <v>Manager I, Engineering - APM Serverless</v>
+        <v>Product Management Intern</v>
       </c>
       <c r="C40" t="str">
         <v>Datadog</v>
@@ -2906,7 +2906,7 @@
         <v>Wellfound</v>
       </c>
       <c r="E40" t="str">
-        <v>Associate Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F40" t="str">
         <v>1-3 yrs</v>
@@ -2915,10 +2915,10 @@
         <v>0-2 yrs</v>
       </c>
       <c r="H40" t="str">
-        <v>New York, New York, USA</v>
+        <v>Paris, France</v>
       </c>
       <c r="I40" t="str">
-        <v>New York</v>
+        <v>Paris</v>
       </c>
       <c r="J40" t="str">
         <v>On-site</v>
@@ -2927,7 +2927,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L40" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/8060821</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/8143729</v>
       </c>
       <c r="M40">
         <v>200</v>
@@ -2936,27 +2936,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O40" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P40" t="str">
         <v>Today</v>
       </c>
       <c r="Q40" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R40" t="str">
         <v>No</v>
       </c>
       <c r="S40">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>job-3c715a0a</v>
+        <v>job-4a73833e</v>
       </c>
       <c r="B41" t="str">
-        <v>Product Management Intern</v>
+        <v>Product Manager II, AI &amp; Data Security</v>
       </c>
       <c r="C41" t="str">
         <v>Datadog</v>
@@ -2965,13 +2965,13 @@
         <v>Wellfound</v>
       </c>
       <c r="E41" t="str">
-        <v>Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F41" t="str">
-        <v>1-3 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G41" t="str">
-        <v>0-2 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H41" t="str">
         <v>Paris, France</v>
@@ -2986,7 +2986,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L41" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/8143729</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/8012549</v>
       </c>
       <c r="M41">
         <v>200</v>
@@ -2995,27 +2995,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O41" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P41" t="str">
         <v>Today</v>
       </c>
       <c r="Q41" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R41" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S41">
-        <v>39</v>
+        <v>65</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>job-4a73833e</v>
+        <v>job-0d57ea9a</v>
       </c>
       <c r="B42" t="str">
-        <v>Product Manager II, AI &amp; Data Security</v>
+        <v>Product Manager II - SQL &amp; Sheets Growth</v>
       </c>
       <c r="C42" t="str">
         <v>Datadog</v>
@@ -3033,10 +3033,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H42" t="str">
-        <v>Paris, France</v>
+        <v>New York, New York, USA</v>
       </c>
       <c r="I42" t="str">
-        <v>Paris</v>
+        <v>New York</v>
       </c>
       <c r="J42" t="str">
         <v>On-site</v>
@@ -3045,7 +3045,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L42" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/8012549</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/8119973</v>
       </c>
       <c r="M42">
         <v>200</v>
@@ -3054,7 +3054,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O42" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P42" t="str">
         <v>Today</v>
@@ -3066,15 +3066,15 @@
         <v>No</v>
       </c>
       <c r="S42">
-        <v>63</v>
+        <v>86</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>job-0d57ea9a</v>
+        <v>job-156d798b</v>
       </c>
       <c r="B43" t="str">
-        <v>Product Manager II - SQL &amp; Sheets Growth</v>
+        <v>Product Manager ll – Code Intelligence</v>
       </c>
       <c r="C43" t="str">
         <v>Datadog</v>
@@ -3104,7 +3104,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L43" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/8119973</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/8197852</v>
       </c>
       <c r="M43">
         <v>200</v>
@@ -3113,27 +3113,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O43" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P43" t="str">
         <v>Today</v>
       </c>
       <c r="Q43" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R43" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S43">
-        <v>64</v>
+        <v>41</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>job-156d798b</v>
+        <v>job-19d43a03</v>
       </c>
       <c r="B44" t="str">
-        <v>Product Manager ll – Code Intelligence</v>
+        <v>Senior Director, Product Management - Platforms</v>
       </c>
       <c r="C44" t="str">
         <v>Datadog</v>
@@ -3142,13 +3142,13 @@
         <v>Wellfound</v>
       </c>
       <c r="E44" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F44" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G44" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H44" t="str">
         <v>New York, New York, USA</v>
@@ -3163,7 +3163,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L44" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/8197852</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/7583609</v>
       </c>
       <c r="M44">
         <v>200</v>
@@ -3172,7 +3172,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O44" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P44" t="str">
         <v>Today</v>
@@ -3181,10 +3181,10 @@
         <v>No</v>
       </c>
       <c r="R44" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S44">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="45">
@@ -3231,7 +3231,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O45" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P45" t="str">
         <v>Today</v>
@@ -3243,7 +3243,7 @@
         <v>No</v>
       </c>
       <c r="S45">
-        <v>58</v>
+        <v>43</v>
       </c>
     </row>
     <row r="46">
@@ -3290,19 +3290,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O46" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P46" t="str">
         <v>Today</v>
       </c>
       <c r="Q46" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R46" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S46">
-        <v>56</v>
+        <v>46</v>
       </c>
     </row>
     <row r="47">
@@ -3349,19 +3349,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O47" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P47" t="str">
         <v>Today</v>
       </c>
       <c r="Q47" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R47" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S47">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="48">
@@ -3408,7 +3408,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O48" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P48" t="str">
         <v>Today</v>
@@ -3420,7 +3420,7 @@
         <v>No</v>
       </c>
       <c r="S48">
-        <v>71</v>
+        <v>41</v>
       </c>
     </row>
     <row r="49">
@@ -3467,7 +3467,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O49" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P49" t="str">
         <v>Today</v>
@@ -3476,10 +3476,10 @@
         <v>Yes</v>
       </c>
       <c r="R49" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S49">
-        <v>32</v>
+        <v>78</v>
       </c>
     </row>
     <row r="50">
@@ -3526,7 +3526,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O50" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P50" t="str">
         <v>Today</v>
@@ -3538,7 +3538,7 @@
         <v>No</v>
       </c>
       <c r="S50">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="51">
@@ -3585,7 +3585,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O51" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P51" t="str">
         <v>Today</v>
@@ -3597,7 +3597,7 @@
         <v>No</v>
       </c>
       <c r="S51">
-        <v>94</v>
+        <v>49</v>
       </c>
     </row>
     <row r="52">
@@ -3644,27 +3644,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O52" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P52" t="str">
         <v>Today</v>
       </c>
       <c r="Q52" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R52" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S52">
-        <v>72</v>
+        <v>78</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>job-06bb1b7b</v>
+        <v>job-5ef34fd7</v>
       </c>
       <c r="B53" t="str">
-        <v>Senior Product Manager - Search</v>
+        <v>Senior Staff GenAI Engineer - Application Performance Monitoring (APM)</v>
       </c>
       <c r="C53" t="str">
         <v>Datadog</v>
@@ -3673,16 +3673,16 @@
         <v>Wellfound</v>
       </c>
       <c r="E53" t="str">
-        <v>Senior Product Manager</v>
+        <v>Associate Product Manager</v>
       </c>
       <c r="F53" t="str">
-        <v>5-8 yrs</v>
+        <v>1-3 yrs</v>
       </c>
       <c r="G53" t="str">
-        <v>5-8 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H53" t="str">
-        <v>Boston, Massachusetts, USA; New York, New York, USA</v>
+        <v>New York, New York, USA</v>
       </c>
       <c r="I53" t="str">
         <v>New York</v>
@@ -3694,7 +3694,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L53" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/7974481</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/6960503</v>
       </c>
       <c r="M53">
         <v>200</v>
@@ -3703,7 +3703,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O53" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P53" t="str">
         <v>Today</v>
@@ -3715,15 +3715,15 @@
         <v>No</v>
       </c>
       <c r="S53">
-        <v>59</v>
+        <v>90</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>job-5ef34fd7</v>
+        <v>job-6f4d5443</v>
       </c>
       <c r="B54" t="str">
-        <v>Senior Staff GenAI Engineer - Application Performance Monitoring (APM)</v>
+        <v>Staff GenAI Engineer - Application Performance Monitoring (APM)</v>
       </c>
       <c r="C54" t="str">
         <v>Datadog</v>
@@ -3753,7 +3753,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L54" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/6960503</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/7974511</v>
       </c>
       <c r="M54">
         <v>200</v>
@@ -3762,7 +3762,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O54" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P54" t="str">
         <v>Today</v>
@@ -3771,18 +3771,18 @@
         <v>No</v>
       </c>
       <c r="R54" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S54">
-        <v>36</v>
+        <v>26</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>job-6f4d5443</v>
+        <v>job-74e794e5</v>
       </c>
       <c r="B55" t="str">
-        <v>Staff GenAI Engineer - Application Performance Monitoring (APM)</v>
+        <v>Staff Product Manager, Observability Data Platforms</v>
       </c>
       <c r="C55" t="str">
         <v>Datadog</v>
@@ -3791,13 +3791,13 @@
         <v>Wellfound</v>
       </c>
       <c r="E55" t="str">
-        <v>Associate Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F55" t="str">
-        <v>1-3 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G55" t="str">
-        <v>0-2 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H55" t="str">
         <v>New York, New York, USA</v>
@@ -3812,7 +3812,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L55" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/7974511</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/8065187</v>
       </c>
       <c r="M55">
         <v>200</v>
@@ -3821,57 +3821,57 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O55" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P55" t="str">
         <v>Today</v>
       </c>
       <c r="Q55" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R55" t="str">
         <v>No</v>
       </c>
       <c r="S55">
-        <v>89</v>
+        <v>68</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>job-62a8a726</v>
+        <v>job-443f0280</v>
       </c>
       <c r="B56" t="str">
-        <v>Staff Product Manager - Bits Release</v>
+        <v>Group Product Manager, Finance Technology</v>
       </c>
       <c r="C56" t="str">
-        <v>Datadog</v>
+        <v>Reddit</v>
       </c>
       <c r="D56" t="str">
-        <v>Wellfound</v>
+        <v>Indeed</v>
       </c>
       <c r="E56" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F56" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G56" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H56" t="str">
-        <v>New York, New York, USA</v>
+        <v>Remote - United States</v>
       </c>
       <c r="I56" t="str">
-        <v>New York</v>
+        <v>Remote</v>
       </c>
       <c r="J56" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K56" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L56" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/8174592</v>
+        <v>https://boards.greenhouse.io/reddit/jobs/8075185</v>
       </c>
       <c r="M56">
         <v>200</v>
@@ -3880,7 +3880,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O56" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P56" t="str">
         <v>Today</v>
@@ -3889,48 +3889,48 @@
         <v>Yes</v>
       </c>
       <c r="R56" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S56">
-        <v>79</v>
+        <v>64</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>job-74e794e5</v>
+        <v>job-7e666189</v>
       </c>
       <c r="B57" t="str">
-        <v>Staff Product Manager, Observability Data Platforms</v>
+        <v>Product Manager, Developer Ecosystem</v>
       </c>
       <c r="C57" t="str">
-        <v>Datadog</v>
+        <v>Reddit</v>
       </c>
       <c r="D57" t="str">
-        <v>Wellfound</v>
+        <v>Indeed</v>
       </c>
       <c r="E57" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F57" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G57" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H57" t="str">
-        <v>New York, New York, USA</v>
+        <v>Remote - United States</v>
       </c>
       <c r="I57" t="str">
-        <v>New York</v>
+        <v>Remote</v>
       </c>
       <c r="J57" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K57" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L57" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/8065187</v>
+        <v>https://boards.greenhouse.io/reddit/jobs/8088720</v>
       </c>
       <c r="M57">
         <v>200</v>
@@ -3939,7 +3939,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O57" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P57" t="str">
         <v>Today</v>
@@ -3948,18 +3948,18 @@
         <v>No</v>
       </c>
       <c r="R57" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S57">
-        <v>26</v>
+        <v>88</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>job-443f0280</v>
+        <v>job-66f21772</v>
       </c>
       <c r="B58" t="str">
-        <v>Group Product Manager, Finance Technology</v>
+        <v>Senior Product Manager, Ads -  Shopping Catalogs</v>
       </c>
       <c r="C58" t="str">
         <v>Reddit</v>
@@ -3968,13 +3968,13 @@
         <v>Indeed</v>
       </c>
       <c r="E58" t="str">
-        <v>Product Lead / Director</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F58" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G58" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H58" t="str">
         <v>Remote - United States</v>
@@ -3989,7 +3989,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L58" t="str">
-        <v>https://boards.greenhouse.io/reddit/jobs/8075185</v>
+        <v>https://boards.greenhouse.io/reddit/jobs/8120503</v>
       </c>
       <c r="M58">
         <v>200</v>
@@ -3998,7 +3998,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O58" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P58" t="str">
         <v>Today</v>
@@ -4010,15 +4010,15 @@
         <v>No</v>
       </c>
       <c r="S58">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>job-7e666189</v>
+        <v>job-25042936</v>
       </c>
       <c r="B59" t="str">
-        <v>Product Manager, Developer Ecosystem</v>
+        <v>Senior Product Manager, Go-To-Market Systems</v>
       </c>
       <c r="C59" t="str">
         <v>Reddit</v>
@@ -4027,28 +4027,28 @@
         <v>Indeed</v>
       </c>
       <c r="E59" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F59" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G59" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H59" t="str">
-        <v>Remote - United States</v>
+        <v>Chicago, IL; Los Angeles, CA; New York City, NY; San Francisco, CA</v>
       </c>
       <c r="I59" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J59" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K59" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L59" t="str">
-        <v>https://boards.greenhouse.io/reddit/jobs/8088720</v>
+        <v>https://boards.greenhouse.io/reddit/jobs/8212175</v>
       </c>
       <c r="M59">
         <v>200</v>
@@ -4057,7 +4057,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O59" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P59" t="str">
         <v>Today</v>
@@ -4069,15 +4069,15 @@
         <v>No</v>
       </c>
       <c r="S59">
-        <v>87</v>
+        <v>37</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>job-66f21772</v>
+        <v>job-4b069687</v>
       </c>
       <c r="B60" t="str">
-        <v>Senior Product Manager, Ads -  Shopping Catalogs</v>
+        <v>Staff Product Manager, Ads Formats</v>
       </c>
       <c r="C60" t="str">
         <v>Reddit</v>
@@ -4107,7 +4107,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L60" t="str">
-        <v>https://boards.greenhouse.io/reddit/jobs/8120503</v>
+        <v>https://boards.greenhouse.io/reddit/jobs/8167412</v>
       </c>
       <c r="M60">
         <v>200</v>
@@ -4116,27 +4116,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O60" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P60" t="str">
         <v>Today</v>
       </c>
       <c r="Q60" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R60" t="str">
         <v>No</v>
       </c>
       <c r="S60">
-        <v>69</v>
+        <v>75</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>job-25042936</v>
+        <v>job-0638f83c</v>
       </c>
       <c r="B61" t="str">
-        <v>Senior Product Manager, Go-To-Market Systems</v>
+        <v>Staff Product Manager, Ads Safety (Ads Review)</v>
       </c>
       <c r="C61" t="str">
         <v>Reddit</v>
@@ -4154,19 +4154,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H61" t="str">
-        <v>Chicago, IL; Los Angeles, CA; New York City, NY; San Francisco, CA</v>
+        <v>Remote - United States</v>
       </c>
       <c r="I61" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J61" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K61" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L61" t="str">
-        <v>https://boards.greenhouse.io/reddit/jobs/8212175</v>
+        <v>https://boards.greenhouse.io/reddit/jobs/8070669</v>
       </c>
       <c r="M61">
         <v>200</v>
@@ -4175,27 +4175,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O61" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P61" t="str">
         <v>Today</v>
       </c>
       <c r="Q61" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R61" t="str">
         <v>No</v>
       </c>
       <c r="S61">
-        <v>92</v>
+        <v>64</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>job-4b069687</v>
+        <v>job-35a933c8</v>
       </c>
       <c r="B62" t="str">
-        <v>Staff Product Manager, Ads Formats</v>
+        <v>Staff Product Manager, Ads Signals</v>
       </c>
       <c r="C62" t="str">
         <v>Reddit</v>
@@ -4225,7 +4225,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L62" t="str">
-        <v>https://boards.greenhouse.io/reddit/jobs/8167412</v>
+        <v>https://boards.greenhouse.io/reddit/jobs/8145926</v>
       </c>
       <c r="M62">
         <v>200</v>
@@ -4234,27 +4234,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O62" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P62" t="str">
         <v>Today</v>
       </c>
       <c r="Q62" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R62" t="str">
         <v>No</v>
       </c>
       <c r="S62">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>job-0638f83c</v>
+        <v>job-5a8393aa</v>
       </c>
       <c r="B63" t="str">
-        <v>Staff Product Manager, Ads Safety (Ads Review)</v>
+        <v>Staff Product Manager, Growth</v>
       </c>
       <c r="C63" t="str">
         <v>Reddit</v>
@@ -4284,7 +4284,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L63" t="str">
-        <v>https://boards.greenhouse.io/reddit/jobs/8070669</v>
+        <v>https://boards.greenhouse.io/reddit/jobs/7997186</v>
       </c>
       <c r="M63">
         <v>200</v>
@@ -4293,27 +4293,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O63" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P63" t="str">
         <v>Today</v>
       </c>
       <c r="Q63" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R63" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S63">
-        <v>42</v>
+        <v>57</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>job-35a933c8</v>
+        <v>job-15c0a18c</v>
       </c>
       <c r="B64" t="str">
-        <v>Staff Product Manager, Ads Signals</v>
+        <v>Staff Technical Product Manager, Ads ML Platform</v>
       </c>
       <c r="C64" t="str">
         <v>Reddit</v>
@@ -4343,7 +4343,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L64" t="str">
-        <v>https://boards.greenhouse.io/reddit/jobs/8145926</v>
+        <v>https://boards.greenhouse.io/reddit/jobs/7954001</v>
       </c>
       <c r="M64">
         <v>200</v>
@@ -4352,7 +4352,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O64" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P64" t="str">
         <v>Today</v>
@@ -4361,24 +4361,24 @@
         <v>No</v>
       </c>
       <c r="R64" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S64">
-        <v>91</v>
+        <v>66</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>job-5a8393aa</v>
+        <v>job-42db73ba</v>
       </c>
       <c r="B65" t="str">
-        <v>Staff Product Manager, Growth</v>
+        <v>Senior Product Manager, Safety</v>
       </c>
       <c r="C65" t="str">
-        <v>Reddit</v>
+        <v>Discord</v>
       </c>
       <c r="D65" t="str">
-        <v>Indeed</v>
+        <v>Wellfound</v>
       </c>
       <c r="E65" t="str">
         <v>Senior Product Manager</v>
@@ -4390,19 +4390,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H65" t="str">
-        <v>Remote - United States</v>
+        <v>San Francisco Bay Area</v>
       </c>
       <c r="I65" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J65" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K65" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L65" t="str">
-        <v>https://boards.greenhouse.io/reddit/jobs/7997186</v>
+        <v>https://boards.greenhouse.io/discord/jobs/8581126002</v>
       </c>
       <c r="M65">
         <v>200</v>
@@ -4411,57 +4411,57 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O65" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P65" t="str">
         <v>Today</v>
       </c>
       <c r="Q65" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R65" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S65">
-        <v>30</v>
+        <v>82</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>job-15c0a18c</v>
+        <v>job-00451313</v>
       </c>
       <c r="B66" t="str">
-        <v>Staff Technical Product Manager, Ads ML Platform</v>
+        <v>Associate Product Manager (New Grad)</v>
       </c>
       <c r="C66" t="str">
-        <v>Reddit</v>
+        <v>Robinhood</v>
       </c>
       <c r="D66" t="str">
-        <v>Indeed</v>
+        <v>Naukri</v>
       </c>
       <c r="E66" t="str">
-        <v>Senior Product Manager</v>
+        <v>Associate Product Manager</v>
       </c>
       <c r="F66" t="str">
-        <v>5-8 yrs</v>
+        <v>1-3 yrs</v>
       </c>
       <c r="G66" t="str">
-        <v>5-8 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H66" t="str">
-        <v>Remote - United States</v>
+        <v>Menlo Park, CA; New York, NY</v>
       </c>
       <c r="I66" t="str">
-        <v>Remote</v>
+        <v>New York</v>
       </c>
       <c r="J66" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K66" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L66" t="str">
-        <v>https://boards.greenhouse.io/reddit/jobs/7954001</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/8199973</v>
       </c>
       <c r="M66">
         <v>200</v>
@@ -4470,7 +4470,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O66" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P66" t="str">
         <v>Today</v>
@@ -4479,24 +4479,24 @@
         <v>Yes</v>
       </c>
       <c r="R66" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S66">
-        <v>67</v>
+        <v>91</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>job-42db73ba</v>
+        <v>job-73f048f5</v>
       </c>
       <c r="B67" t="str">
-        <v>Senior Product Manager, Safety</v>
+        <v>Senior Product Manager, Capital Markets</v>
       </c>
       <c r="C67" t="str">
-        <v>Discord</v>
+        <v>Robinhood</v>
       </c>
       <c r="D67" t="str">
-        <v>Wellfound</v>
+        <v>Naukri</v>
       </c>
       <c r="E67" t="str">
         <v>Senior Product Manager</v>
@@ -4508,10 +4508,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H67" t="str">
-        <v>San Francisco Bay Area</v>
+        <v>Menlo Park, CA; New York, NY</v>
       </c>
       <c r="I67" t="str">
-        <v>San Francisco</v>
+        <v>New York</v>
       </c>
       <c r="J67" t="str">
         <v>On-site</v>
@@ -4520,7 +4520,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L67" t="str">
-        <v>https://boards.greenhouse.io/discord/jobs/8581126002</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/8204521</v>
       </c>
       <c r="M67">
         <v>200</v>
@@ -4529,7 +4529,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O67" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P67" t="str">
         <v>Today</v>
@@ -4538,18 +4538,18 @@
         <v>Yes</v>
       </c>
       <c r="R67" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S67">
-        <v>29</v>
+        <v>93</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>job-00451313</v>
+        <v>job-28c2c2a4</v>
       </c>
       <c r="B68" t="str">
-        <v>Associate Product Manager (New Grad)</v>
+        <v>Senior Product Manager, Crypto Wallet</v>
       </c>
       <c r="C68" t="str">
         <v>Robinhood</v>
@@ -4558,13 +4558,13 @@
         <v>Naukri</v>
       </c>
       <c r="E68" t="str">
-        <v>Associate Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F68" t="str">
-        <v>1-3 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G68" t="str">
-        <v>0-2 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H68" t="str">
         <v>Menlo Park, CA; New York, NY</v>
@@ -4579,7 +4579,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L68" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/8199973</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/8082718</v>
       </c>
       <c r="M68">
         <v>200</v>
@@ -4588,27 +4588,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O68" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P68" t="str">
         <v>Today</v>
       </c>
       <c r="Q68" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R68" t="str">
         <v>No</v>
       </c>
       <c r="S68">
-        <v>84</v>
+        <v>64</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>job-73f048f5</v>
+        <v>job-6a8c3d37</v>
       </c>
       <c r="B69" t="str">
-        <v>Senior Product Manager, Capital Markets</v>
+        <v>Senior Product Manager, Money Movement</v>
       </c>
       <c r="C69" t="str">
         <v>Robinhood</v>
@@ -4626,10 +4626,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H69" t="str">
-        <v>Menlo Park, CA; New York, NY</v>
+        <v>Menlo Park, CA</v>
       </c>
       <c r="I69" t="str">
-        <v>New York</v>
+        <v>Menlo Park</v>
       </c>
       <c r="J69" t="str">
         <v>On-site</v>
@@ -4638,7 +4638,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L69" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/8204521</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/7747728</v>
       </c>
       <c r="M69">
         <v>200</v>
@@ -4647,27 +4647,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O69" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P69" t="str">
         <v>Today</v>
       </c>
       <c r="Q69" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R69" t="str">
         <v>No</v>
       </c>
       <c r="S69">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>job-28c2c2a4</v>
+        <v>job-6a477110</v>
       </c>
       <c r="B70" t="str">
-        <v>Senior Product Manager, Crypto Wallet</v>
+        <v>Staff Product Manager, Banking</v>
       </c>
       <c r="C70" t="str">
         <v>Robinhood</v>
@@ -4685,7 +4685,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H70" t="str">
-        <v>Menlo Park, CA; New York, NY</v>
+        <v>Menlo Park, CA; New York, NY; Washington, DC</v>
       </c>
       <c r="I70" t="str">
         <v>New York</v>
@@ -4697,7 +4697,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L70" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/8082718</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/8044746</v>
       </c>
       <c r="M70">
         <v>200</v>
@@ -4706,27 +4706,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O70" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P70" t="str">
         <v>Today</v>
       </c>
       <c r="Q70" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R70" t="str">
         <v>No</v>
       </c>
       <c r="S70">
-        <v>25</v>
+        <v>69</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>job-6a8c3d37</v>
+        <v>job-1f991f57</v>
       </c>
       <c r="B71" t="str">
-        <v>Senior Product Manager, Money Movement</v>
+        <v>Staff Product Manager-  Integrations &amp; Advisor Platform</v>
       </c>
       <c r="C71" t="str">
         <v>Robinhood</v>
@@ -4744,10 +4744,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H71" t="str">
-        <v>Menlo Park, CA</v>
+        <v>Clearwater, FL; Menlo Park, CA; New York, NY</v>
       </c>
       <c r="I71" t="str">
-        <v>Menlo Park</v>
+        <v>New York</v>
       </c>
       <c r="J71" t="str">
         <v>On-site</v>
@@ -4756,7 +4756,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L71" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/7747728</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/8131181</v>
       </c>
       <c r="M71">
         <v>200</v>
@@ -4765,27 +4765,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O71" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P71" t="str">
         <v>Today</v>
       </c>
       <c r="Q71" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R71" t="str">
         <v>Yes</v>
       </c>
       <c r="S71">
-        <v>74</v>
+        <v>87</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>job-6a477110</v>
+        <v>job-621b991e</v>
       </c>
       <c r="B72" t="str">
-        <v>Staff Product Manager, Banking</v>
+        <v>Staff Product Manager, National Impact</v>
       </c>
       <c r="C72" t="str">
         <v>Robinhood</v>
@@ -4803,7 +4803,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H72" t="str">
-        <v>Menlo Park, CA; New York, NY; Washington, DC</v>
+        <v>New York, NY</v>
       </c>
       <c r="I72" t="str">
         <v>New York</v>
@@ -4815,7 +4815,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L72" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/8044746</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/7968044</v>
       </c>
       <c r="M72">
         <v>200</v>
@@ -4824,27 +4824,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O72" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P72" t="str">
         <v>Today</v>
       </c>
       <c r="Q72" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R72" t="str">
         <v>No</v>
       </c>
       <c r="S72">
-        <v>91</v>
+        <v>75</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>job-1f991f57</v>
+        <v>job-2b6bc257</v>
       </c>
       <c r="B73" t="str">
-        <v>Staff Product Manager-  Integrations &amp; Advisor Platform</v>
+        <v>Staff Product Manager - Prediction Markets</v>
       </c>
       <c r="C73" t="str">
         <v>Robinhood</v>
@@ -4862,7 +4862,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H73" t="str">
-        <v>Clearwater, FL; Menlo Park, CA; New York, NY</v>
+        <v>Menlo Park, CA; New York, NY</v>
       </c>
       <c r="I73" t="str">
         <v>New York</v>
@@ -4874,7 +4874,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L73" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/8131181</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/8164459</v>
       </c>
       <c r="M73">
         <v>200</v>
@@ -4883,57 +4883,57 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O73" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P73" t="str">
         <v>Today</v>
       </c>
       <c r="Q73" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R73" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S73">
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>job-621b991e</v>
+        <v>job-223dd55b</v>
       </c>
       <c r="B74" t="str">
-        <v>Staff Product Manager, National Impact</v>
+        <v>Director of Product Management, Fintech</v>
       </c>
       <c r="C74" t="str">
-        <v>Robinhood</v>
+        <v>Cloudflare</v>
       </c>
       <c r="D74" t="str">
-        <v>Naukri</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E74" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F74" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G74" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H74" t="str">
-        <v>New York, NY</v>
+        <v>Hybrid</v>
       </c>
       <c r="I74" t="str">
-        <v>New York</v>
+        <v>Hybrid</v>
       </c>
       <c r="J74" t="str">
-        <v>On-site</v>
+        <v>Hybrid</v>
       </c>
       <c r="K74" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L74" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/7968044</v>
+        <v>https://boards.greenhouse.io/cloudflare/jobs/8152765</v>
       </c>
       <c r="M74">
         <v>200</v>
@@ -4942,57 +4942,57 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O74" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P74" t="str">
         <v>Today</v>
       </c>
       <c r="Q74" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R74" t="str">
         <v>No</v>
       </c>
       <c r="S74">
-        <v>27</v>
+        <v>33</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>job-2b6bc257</v>
+        <v>job-04eb5da0</v>
       </c>
       <c r="B75" t="str">
-        <v>Staff Product Manager - Prediction Markets</v>
+        <v>Product Manager, Browser Extension</v>
       </c>
       <c r="C75" t="str">
-        <v>Robinhood</v>
+        <v>Cloudflare</v>
       </c>
       <c r="D75" t="str">
-        <v>Naukri</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E75" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F75" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G75" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H75" t="str">
-        <v>Menlo Park, CA; New York, NY</v>
+        <v>Hybrid</v>
       </c>
       <c r="I75" t="str">
-        <v>New York</v>
+        <v>Hybrid</v>
       </c>
       <c r="J75" t="str">
-        <v>On-site</v>
+        <v>Hybrid</v>
       </c>
       <c r="K75" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L75" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/8164459</v>
+        <v>https://boards.greenhouse.io/cloudflare/jobs/8173899</v>
       </c>
       <c r="M75">
         <v>200</v>
@@ -5001,27 +5001,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O75" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P75" t="str">
         <v>Today</v>
       </c>
       <c r="Q75" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R75" t="str">
         <v>No</v>
       </c>
       <c r="S75">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>job-223dd55b</v>
+        <v>job-6ad0cb95</v>
       </c>
       <c r="B76" t="str">
-        <v>Director of Product Management, Fintech</v>
+        <v>Senior Product Manager - Application Protection &amp; Governance</v>
       </c>
       <c r="C76" t="str">
         <v>Cloudflare</v>
@@ -5030,13 +5030,13 @@
         <v>LinkedIn</v>
       </c>
       <c r="E76" t="str">
-        <v>Product Lead / Director</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F76" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G76" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H76" t="str">
         <v>Hybrid</v>
@@ -5051,7 +5051,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L76" t="str">
-        <v>https://boards.greenhouse.io/cloudflare/jobs/8152765</v>
+        <v>https://boards.greenhouse.io/cloudflare/jobs/8200670</v>
       </c>
       <c r="M76">
         <v>200</v>
@@ -5060,7 +5060,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O76" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P76" t="str">
         <v>Today</v>
@@ -5072,15 +5072,15 @@
         <v>No</v>
       </c>
       <c r="S76">
-        <v>36</v>
+        <v>32</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>job-6ad0cb95</v>
+        <v>job-1cd2d853</v>
       </c>
       <c r="B77" t="str">
-        <v>Senior Product Manager - Application Protection &amp; Governance</v>
+        <v>Senior Product Manager, Email Security</v>
       </c>
       <c r="C77" t="str">
         <v>Cloudflare</v>
@@ -5110,7 +5110,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L77" t="str">
-        <v>https://boards.greenhouse.io/cloudflare/jobs/8200670</v>
+        <v>https://boards.greenhouse.io/cloudflare/jobs/8173954</v>
       </c>
       <c r="M77">
         <v>200</v>
@@ -5119,7 +5119,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O77" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P77" t="str">
         <v>Today</v>
@@ -5131,15 +5131,15 @@
         <v>No</v>
       </c>
       <c r="S77">
-        <v>78</v>
+        <v>38</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>job-1cd2d853</v>
+        <v>job-4c1a26d6</v>
       </c>
       <c r="B78" t="str">
-        <v>Senior Product Manager, Email Security</v>
+        <v>Senior Product Manager, Enterprise</v>
       </c>
       <c r="C78" t="str">
         <v>Cloudflare</v>
@@ -5169,7 +5169,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L78" t="str">
-        <v>https://boards.greenhouse.io/cloudflare/jobs/8173954</v>
+        <v>https://boards.greenhouse.io/cloudflare/jobs/8158527</v>
       </c>
       <c r="M78">
         <v>200</v>
@@ -5178,7 +5178,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O78" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P78" t="str">
         <v>Today</v>
@@ -5187,18 +5187,18 @@
         <v>No</v>
       </c>
       <c r="R78" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S78">
-        <v>27</v>
+        <v>86</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>job-4c1a26d6</v>
+        <v>job-0496f2bd</v>
       </c>
       <c r="B79" t="str">
-        <v>Senior Product Manager, Enterprise</v>
+        <v>Senior Product Manager - FinTech</v>
       </c>
       <c r="C79" t="str">
         <v>Cloudflare</v>
@@ -5216,19 +5216,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H79" t="str">
-        <v>Hybrid</v>
+        <v>In-Office</v>
       </c>
       <c r="I79" t="str">
-        <v>Hybrid</v>
+        <v>In-Office</v>
       </c>
       <c r="J79" t="str">
-        <v>Hybrid</v>
+        <v>On-site</v>
       </c>
       <c r="K79" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L79" t="str">
-        <v>https://boards.greenhouse.io/cloudflare/jobs/8158527</v>
+        <v>https://boards.greenhouse.io/cloudflare/jobs/8064473</v>
       </c>
       <c r="M79">
         <v>200</v>
@@ -5237,7 +5237,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O79" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P79" t="str">
         <v>Today</v>
@@ -5249,18 +5249,18 @@
         <v>No</v>
       </c>
       <c r="S79">
-        <v>65</v>
+        <v>36</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>job-0496f2bd</v>
+        <v>job-321ad81f</v>
       </c>
       <c r="B80" t="str">
-        <v>Senior Product Manager - FinTech</v>
+        <v>Principal Product Manager Agents and Context - Elasticsearch</v>
       </c>
       <c r="C80" t="str">
-        <v>Cloudflare</v>
+        <v>Elastic</v>
       </c>
       <c r="D80" t="str">
         <v>LinkedIn</v>
@@ -5269,16 +5269,16 @@
         <v>Senior Product Manager</v>
       </c>
       <c r="F80" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G80" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H80" t="str">
-        <v>In-Office</v>
+        <v>Canada</v>
       </c>
       <c r="I80" t="str">
-        <v>In-Office</v>
+        <v>Canada</v>
       </c>
       <c r="J80" t="str">
         <v>On-site</v>
@@ -5287,7 +5287,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L80" t="str">
-        <v>https://boards.greenhouse.io/cloudflare/jobs/8064473</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8070011</v>
       </c>
       <c r="M80">
         <v>200</v>
@@ -5296,27 +5296,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O80" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P80" t="str">
         <v>Today</v>
       </c>
       <c r="Q80" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R80" t="str">
         <v>No</v>
       </c>
       <c r="S80">
-        <v>47</v>
+        <v>91</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>job-321ad81f</v>
+        <v>job-1958e230</v>
       </c>
       <c r="B81" t="str">
-        <v>Principal Product Manager Agents and Context - Elasticsearch</v>
+        <v>Principal Product Manager - Identity Threat Detection &amp; Response</v>
       </c>
       <c r="C81" t="str">
         <v>Elastic</v>
@@ -5334,10 +5334,10 @@
         <v>8+ yrs</v>
       </c>
       <c r="H81" t="str">
-        <v>United States</v>
+        <v>Spain</v>
       </c>
       <c r="I81" t="str">
-        <v>United States</v>
+        <v>Spain</v>
       </c>
       <c r="J81" t="str">
         <v>On-site</v>
@@ -5346,7 +5346,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L81" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/7602101</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8122171</v>
       </c>
       <c r="M81">
         <v>200</v>
@@ -5355,27 +5355,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O81" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P81" t="str">
         <v>Today</v>
       </c>
       <c r="Q81" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R81" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S81">
-        <v>43</v>
+        <v>31</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>job-1958e230</v>
+        <v>job-7648ed00</v>
       </c>
       <c r="B82" t="str">
-        <v>Principal Product Manager - Identity Threat Detection &amp; Response</v>
+        <v>Principal Product Manager II, AI/Vectors</v>
       </c>
       <c r="C82" t="str">
         <v>Elastic</v>
@@ -5393,10 +5393,10 @@
         <v>8+ yrs</v>
       </c>
       <c r="H82" t="str">
-        <v>Spain</v>
+        <v>United States</v>
       </c>
       <c r="I82" t="str">
-        <v>Spain</v>
+        <v>United States</v>
       </c>
       <c r="J82" t="str">
         <v>On-site</v>
@@ -5405,7 +5405,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L82" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8122171</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8121962</v>
       </c>
       <c r="M82">
         <v>200</v>
@@ -5414,27 +5414,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O82" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P82" t="str">
         <v>Today</v>
       </c>
       <c r="Q82" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R82" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S82">
-        <v>45</v>
+        <v>69</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>job-7648ed00</v>
+        <v>job-4dbe0e39</v>
       </c>
       <c r="B83" t="str">
-        <v>Principal Product Manager II, AI/Vectors</v>
+        <v>Principal Product Manager (Strategic Account Interactions) - Security Solutions</v>
       </c>
       <c r="C83" t="str">
         <v>Elastic</v>
@@ -5452,10 +5452,10 @@
         <v>8+ yrs</v>
       </c>
       <c r="H83" t="str">
-        <v>United States</v>
+        <v>Switzerland</v>
       </c>
       <c r="I83" t="str">
-        <v>United States</v>
+        <v>Switzerland</v>
       </c>
       <c r="J83" t="str">
         <v>On-site</v>
@@ -5464,7 +5464,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L83" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8121962</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8155425</v>
       </c>
       <c r="M83">
         <v>200</v>
@@ -5473,27 +5473,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O83" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P83" t="str">
         <v>Today</v>
       </c>
       <c r="Q83" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R83" t="str">
         <v>Yes</v>
       </c>
       <c r="S83">
-        <v>47</v>
+        <v>53</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>job-4dbe0e39</v>
+        <v>job-682d81b9</v>
       </c>
       <c r="B84" t="str">
-        <v>Principal Product Manager (Strategic Account Interactions) - Security Solutions</v>
+        <v>Principal Product Manager (XDR &amp; Exposure Management) - Security Solutions</v>
       </c>
       <c r="C84" t="str">
         <v>Elastic</v>
@@ -5511,10 +5511,10 @@
         <v>8+ yrs</v>
       </c>
       <c r="H84" t="str">
-        <v>Switzerland</v>
+        <v>Israel</v>
       </c>
       <c r="I84" t="str">
-        <v>Switzerland</v>
+        <v>Israel</v>
       </c>
       <c r="J84" t="str">
         <v>On-site</v>
@@ -5523,7 +5523,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L84" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8155425</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8155328</v>
       </c>
       <c r="M84">
         <v>200</v>
@@ -5532,27 +5532,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O84" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P84" t="str">
         <v>Today</v>
       </c>
       <c r="Q84" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R84" t="str">
         <v>No</v>
       </c>
       <c r="S84">
-        <v>31</v>
+        <v>89</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>job-682d81b9</v>
+        <v>job-64ec2b77</v>
       </c>
       <c r="B85" t="str">
-        <v>Principal Product Manager (XDR &amp; Exposure Management) - Security Solutions</v>
+        <v>Senior Director of Product Management, Endpoint Security &amp; XDR</v>
       </c>
       <c r="C85" t="str">
         <v>Elastic</v>
@@ -5564,16 +5564,16 @@
         <v>Senior Product Manager</v>
       </c>
       <c r="F85" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G85" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H85" t="str">
-        <v>Greece</v>
+        <v>United States</v>
       </c>
       <c r="I85" t="str">
-        <v>Greece</v>
+        <v>United States</v>
       </c>
       <c r="J85" t="str">
         <v>On-site</v>
@@ -5582,7 +5582,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L85" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8155348</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8214106</v>
       </c>
       <c r="M85">
         <v>200</v>
@@ -5591,27 +5591,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O85" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P85" t="str">
         <v>Today</v>
       </c>
       <c r="Q85" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R85" t="str">
         <v>Yes</v>
       </c>
       <c r="S85">
-        <v>42</v>
+        <v>90</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>job-64ec2b77</v>
+        <v>job-2b6f27da</v>
       </c>
       <c r="B86" t="str">
-        <v>Senior Director of Product Management, Endpoint Security &amp; XDR</v>
+        <v>Senior Product Manager, Control Plane - Platform</v>
       </c>
       <c r="C86" t="str">
         <v>Elastic</v>
@@ -5641,7 +5641,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L86" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8214187</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8093933</v>
       </c>
       <c r="M86">
         <v>200</v>
@@ -5650,7 +5650,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O86" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P86" t="str">
         <v>Today</v>
@@ -5659,18 +5659,18 @@
         <v>No</v>
       </c>
       <c r="R86" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S86">
-        <v>32</v>
+        <v>89</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>job-2b6f27da</v>
+        <v>job-03cee7aa</v>
       </c>
       <c r="B87" t="str">
-        <v>Senior Product Manager, Control Plane - Platform</v>
+        <v>Senior Product Manager, Logs - Observability</v>
       </c>
       <c r="C87" t="str">
         <v>Elastic</v>
@@ -5688,10 +5688,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H87" t="str">
-        <v>United States</v>
+        <v>Greece</v>
       </c>
       <c r="I87" t="str">
-        <v>United States</v>
+        <v>Greece</v>
       </c>
       <c r="J87" t="str">
         <v>On-site</v>
@@ -5700,7 +5700,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L87" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8088818</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8066510</v>
       </c>
       <c r="M87">
         <v>200</v>
@@ -5709,27 +5709,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O87" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P87" t="str">
         <v>Today</v>
       </c>
       <c r="Q87" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R87" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S87">
-        <v>47</v>
+        <v>59</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>job-03cee7aa</v>
+        <v>job-264c8d5a</v>
       </c>
       <c r="B88" t="str">
-        <v>Senior Product Manager, Logs - Observability</v>
+        <v>Senior Product Manager - Self service cloud</v>
       </c>
       <c r="C88" t="str">
         <v>Elastic</v>
@@ -5747,10 +5747,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H88" t="str">
-        <v>Canada</v>
+        <v>Spain</v>
       </c>
       <c r="I88" t="str">
-        <v>Canada</v>
+        <v>Spain</v>
       </c>
       <c r="J88" t="str">
         <v>On-site</v>
@@ -5759,7 +5759,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L88" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8066646</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8028261</v>
       </c>
       <c r="M88">
         <v>200</v>
@@ -5768,27 +5768,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O88" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P88" t="str">
         <v>Today</v>
       </c>
       <c r="Q88" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R88" t="str">
         <v>No</v>
       </c>
       <c r="S88">
-        <v>79</v>
+        <v>94</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>job-264c8d5a</v>
+        <v>job-5b8ec8c1</v>
       </c>
       <c r="B89" t="str">
-        <v>Senior Product Manager - Self service cloud</v>
+        <v>Senior Product Manager - US Public Sector</v>
       </c>
       <c r="C89" t="str">
         <v>Elastic</v>
@@ -5806,10 +5806,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H89" t="str">
-        <v>Spain</v>
+        <v>United States</v>
       </c>
       <c r="I89" t="str">
-        <v>Spain</v>
+        <v>United States</v>
       </c>
       <c r="J89" t="str">
         <v>On-site</v>
@@ -5818,7 +5818,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L89" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8028261</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8188365</v>
       </c>
       <c r="M89">
         <v>200</v>
@@ -5827,27 +5827,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O89" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P89" t="str">
         <v>Today</v>
       </c>
       <c r="Q89" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R89" t="str">
         <v>Yes</v>
       </c>
       <c r="S89">
-        <v>78</v>
+        <v>92</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>job-5b8ec8c1</v>
+        <v>job-7ab91933</v>
       </c>
       <c r="B90" t="str">
-        <v>Senior Product Manager - US Public Sector</v>
+        <v>Senior Product Manager (XDR) - Security Solutions</v>
       </c>
       <c r="C90" t="str">
         <v>Elastic</v>
@@ -5865,10 +5865,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H90" t="str">
-        <v>United States</v>
+        <v>Greece</v>
       </c>
       <c r="I90" t="str">
-        <v>United States</v>
+        <v>Greece</v>
       </c>
       <c r="J90" t="str">
         <v>On-site</v>
@@ -5877,7 +5877,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L90" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8188365</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8194148</v>
       </c>
       <c r="M90">
         <v>200</v>
@@ -5886,48 +5886,48 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O90" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P90" t="str">
         <v>Today</v>
       </c>
       <c r="Q90" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R90" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S90">
-        <v>48</v>
+        <v>74</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>job-7ab91933</v>
+        <v>job-31af15ee</v>
       </c>
       <c r="B91" t="str">
-        <v>Senior Product Manager (XDR) - Security Solutions</v>
+        <v>AI Product Manager (Coding/Multimodal)</v>
       </c>
       <c r="C91" t="str">
-        <v>Elastic</v>
+        <v>Scale AI</v>
       </c>
       <c r="D91" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E91" t="str">
-        <v>Senior Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F91" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G91" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H91" t="str">
-        <v>Poland</v>
+        <v>San Francisco, CA</v>
       </c>
       <c r="I91" t="str">
-        <v>Poland</v>
+        <v>San Francisco</v>
       </c>
       <c r="J91" t="str">
         <v>On-site</v>
@@ -5936,7 +5936,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L91" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8194139</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4609736005</v>
       </c>
       <c r="M91">
         <v>200</v>
@@ -5945,7 +5945,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O91" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P91" t="str">
         <v>Today</v>
@@ -5957,15 +5957,15 @@
         <v>No</v>
       </c>
       <c r="S91">
-        <v>64</v>
+        <v>42</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>job-31af15ee</v>
+        <v>job-184e55c8</v>
       </c>
       <c r="B92" t="str">
-        <v>AI Product Manager (Coding/Multimodal)</v>
+        <v>Director of Product Management, Enterprise Core Platform</v>
       </c>
       <c r="C92" t="str">
         <v>Scale AI</v>
@@ -5974,16 +5974,16 @@
         <v>Wellfound</v>
       </c>
       <c r="E92" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F92" t="str">
-        <v>3-6 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G92" t="str">
-        <v>2-5 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H92" t="str">
-        <v>San Francisco, CA</v>
+        <v>San Francisco, CA; New York, NY</v>
       </c>
       <c r="I92" t="str">
         <v>San Francisco</v>
@@ -5995,7 +5995,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L92" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4609736005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4714727005</v>
       </c>
       <c r="M92">
         <v>200</v>
@@ -6004,7 +6004,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O92" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P92" t="str">
         <v>Today</v>
@@ -6013,10 +6013,10 @@
         <v>Yes</v>
       </c>
       <c r="R92" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S92">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="93">
@@ -6063,7 +6063,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O93" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P93" t="str">
         <v>Today</v>
@@ -6075,7 +6075,7 @@
         <v>Yes</v>
       </c>
       <c r="S93">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="94">
@@ -6122,7 +6122,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O94" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P94" t="str">
         <v>Today</v>
@@ -6134,7 +6134,7 @@
         <v>No</v>
       </c>
       <c r="S94">
-        <v>80</v>
+        <v>38</v>
       </c>
     </row>
     <row r="95">
@@ -6181,19 +6181,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O95" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P95" t="str">
         <v>Today</v>
       </c>
       <c r="Q95" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R95" t="str">
         <v>No</v>
       </c>
       <c r="S95">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="96">
@@ -6240,19 +6240,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O96" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P96" t="str">
         <v>Today</v>
       </c>
       <c r="Q96" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R96" t="str">
         <v>No</v>
       </c>
       <c r="S96">
-        <v>74</v>
+        <v>85</v>
       </c>
     </row>
     <row r="97">
@@ -6278,10 +6278,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H97" t="str">
-        <v>Doha, Qatar ; Dubai, UAE</v>
+        <v>Riyadh, Saudi Arabia</v>
       </c>
       <c r="I97" t="str">
-        <v>Doha</v>
+        <v>Riyadh</v>
       </c>
       <c r="J97" t="str">
         <v>On-site</v>
@@ -6290,7 +6290,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L97" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4589749005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4650514005</v>
       </c>
       <c r="M97">
         <v>200</v>
@@ -6299,19 +6299,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O97" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P97" t="str">
         <v>Today</v>
       </c>
       <c r="Q97" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R97" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S97">
-        <v>41</v>
+        <v>63</v>
       </c>
     </row>
     <row r="98">
@@ -6358,7 +6358,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O98" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P98" t="str">
         <v>Today</v>
@@ -6370,7 +6370,7 @@
         <v>No</v>
       </c>
       <c r="S98">
-        <v>62</v>
+        <v>30</v>
       </c>
     </row>
     <row r="99">
@@ -6417,7 +6417,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O99" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P99" t="str">
         <v>Today</v>
@@ -6426,10 +6426,10 @@
         <v>Yes</v>
       </c>
       <c r="R99" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S99">
-        <v>38</v>
+        <v>67</v>
       </c>
     </row>
     <row r="100">
@@ -6476,7 +6476,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O100" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P100" t="str">
         <v>Today</v>
@@ -6488,7 +6488,7 @@
         <v>No</v>
       </c>
       <c r="S100">
-        <v>48</v>
+        <v>85</v>
       </c>
     </row>
     <row r="101">
@@ -6535,19 +6535,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O101" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P101" t="str">
         <v>Today</v>
       </c>
       <c r="Q101" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R101" t="str">
         <v>No</v>
       </c>
       <c r="S101">
-        <v>32</v>
+        <v>48</v>
       </c>
     </row>
     <row r="102">
@@ -6594,19 +6594,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O102" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P102" t="str">
         <v>Today</v>
       </c>
       <c r="Q102" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R102" t="str">
         <v>No</v>
       </c>
       <c r="S102">
-        <v>44</v>
+        <v>65</v>
       </c>
     </row>
     <row r="103">
@@ -6653,7 +6653,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O103" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P103" t="str">
         <v>Today</v>
@@ -6665,7 +6665,7 @@
         <v>No</v>
       </c>
       <c r="S103">
-        <v>43</v>
+        <v>75</v>
       </c>
     </row>
     <row r="104">
@@ -6712,19 +6712,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O104" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P104" t="str">
         <v>Today</v>
       </c>
       <c r="Q104" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R104" t="str">
         <v>Yes</v>
       </c>
       <c r="S104">
-        <v>64</v>
+        <v>50</v>
       </c>
     </row>
     <row r="105">
@@ -6771,7 +6771,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O105" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P105" t="str">
         <v>Today</v>
@@ -6783,7 +6783,7 @@
         <v>No</v>
       </c>
       <c r="S105">
-        <v>91</v>
+        <v>66</v>
       </c>
     </row>
     <row r="106">
@@ -6830,7 +6830,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O106" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P106" t="str">
         <v>Today</v>
@@ -6839,10 +6839,10 @@
         <v>Yes</v>
       </c>
       <c r="R106" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S106">
-        <v>52</v>
+        <v>90</v>
       </c>
     </row>
     <row r="107">
@@ -6889,7 +6889,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O107" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P107" t="str">
         <v>Today</v>
@@ -6898,10 +6898,10 @@
         <v>No</v>
       </c>
       <c r="R107" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S107">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="108">
@@ -6948,7 +6948,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O108" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P108" t="str">
         <v>Today</v>
@@ -6960,7 +6960,7 @@
         <v>Yes</v>
       </c>
       <c r="S108">
-        <v>42</v>
+        <v>78</v>
       </c>
     </row>
     <row r="109">
@@ -6986,10 +6986,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H109" t="str">
-        <v>New York, New York, United States</v>
+        <v>San Francisco, California, United States</v>
       </c>
       <c r="I109" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J109" t="str">
         <v>On-site</v>
@@ -6998,7 +6998,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L109" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8659251002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8659249002</v>
       </c>
       <c r="M109">
         <v>200</v>
@@ -7007,7 +7007,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O109" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P109" t="str">
         <v>Today</v>
@@ -7016,10 +7016,10 @@
         <v>No</v>
       </c>
       <c r="R109" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S109">
-        <v>58</v>
+        <v>90</v>
       </c>
     </row>
     <row r="110">
@@ -7045,10 +7045,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H110" t="str">
-        <v>Vancouver, British Columbia, Canada</v>
+        <v>New York, New York, United States</v>
       </c>
       <c r="I110" t="str">
-        <v>Vancouver</v>
+        <v>New York</v>
       </c>
       <c r="J110" t="str">
         <v>On-site</v>
@@ -7057,7 +7057,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L110" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8433764002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8432702002</v>
       </c>
       <c r="M110">
         <v>200</v>
@@ -7066,7 +7066,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O110" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P110" t="str">
         <v>Today</v>
@@ -7075,10 +7075,10 @@
         <v>No</v>
       </c>
       <c r="R110" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S110">
-        <v>38</v>
+        <v>73</v>
       </c>
     </row>
     <row r="111">
@@ -7125,7 +7125,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O111" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P111" t="str">
         <v>Today</v>
@@ -7137,7 +7137,7 @@
         <v>No</v>
       </c>
       <c r="S111">
-        <v>29</v>
+        <v>36</v>
       </c>
     </row>
     <row r="112">
@@ -7184,19 +7184,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O112" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P112" t="str">
         <v>Today</v>
       </c>
       <c r="Q112" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R112" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S112">
-        <v>39</v>
+        <v>25</v>
       </c>
     </row>
     <row r="113">
@@ -7243,7 +7243,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O113" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P113" t="str">
         <v>Today</v>
@@ -7255,7 +7255,7 @@
         <v>No</v>
       </c>
       <c r="S113">
-        <v>59</v>
+        <v>69</v>
       </c>
     </row>
     <row r="114">
@@ -7302,19 +7302,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O114" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P114" t="str">
         <v>Today</v>
       </c>
       <c r="Q114" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R114" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S114">
-        <v>68</v>
+        <v>40</v>
       </c>
     </row>
     <row r="115">
@@ -7340,10 +7340,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H115" t="str">
-        <v>New York, New York, United States</v>
+        <v>San Francisco, California, United States</v>
       </c>
       <c r="I115" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J115" t="str">
         <v>On-site</v>
@@ -7352,7 +7352,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L115" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8659242002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8659239002</v>
       </c>
       <c r="M115">
         <v>200</v>
@@ -7361,19 +7361,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O115" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P115" t="str">
         <v>Today</v>
       </c>
       <c r="Q115" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R115" t="str">
         <v>No</v>
       </c>
       <c r="S115">
-        <v>62</v>
+        <v>85</v>
       </c>
     </row>
     <row r="116">
@@ -7420,19 +7420,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O116" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P116" t="str">
         <v>Today</v>
       </c>
       <c r="Q116" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R116" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S116">
-        <v>42</v>
+        <v>50</v>
       </c>
     </row>
     <row r="117">
@@ -7479,7 +7479,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O117" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P117" t="str">
         <v>Today</v>
@@ -7491,7 +7491,7 @@
         <v>No</v>
       </c>
       <c r="S117">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="118">
@@ -7538,19 +7538,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O118" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P118" t="str">
         <v>Today</v>
       </c>
       <c r="Q118" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R118" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S118">
-        <v>31</v>
+        <v>87</v>
       </c>
     </row>
     <row r="119">
@@ -7576,10 +7576,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H119" t="str">
-        <v>New York, NY</v>
+        <v>Pittsburgh, PA</v>
       </c>
       <c r="I119" t="str">
-        <v>New York</v>
+        <v>Pittsburgh</v>
       </c>
       <c r="J119" t="str">
         <v>On-site</v>
@@ -7588,7 +7588,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L119" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8737859002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8530395002</v>
       </c>
       <c r="M119">
         <v>200</v>
@@ -7597,19 +7597,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O119" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P119" t="str">
         <v>Today</v>
       </c>
       <c r="Q119" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R119" t="str">
         <v>No</v>
       </c>
       <c r="S119">
-        <v>93</v>
+        <v>81</v>
       </c>
     </row>
     <row r="120">
@@ -7635,10 +7635,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H120" t="str">
-        <v>Pittsburgh, PA</v>
+        <v>New York, NY</v>
       </c>
       <c r="I120" t="str">
-        <v>Pittsburgh</v>
+        <v>New York</v>
       </c>
       <c r="J120" t="str">
         <v>On-site</v>
@@ -7647,7 +7647,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L120" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8747171002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8747275002</v>
       </c>
       <c r="M120">
         <v>200</v>
@@ -7656,7 +7656,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O120" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P120" t="str">
         <v>Today</v>
@@ -7665,10 +7665,10 @@
         <v>No</v>
       </c>
       <c r="R120" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S120">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="121">
@@ -7694,10 +7694,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H121" t="str">
-        <v>Pittsburgh, PA</v>
+        <v>New York, NY</v>
       </c>
       <c r="I121" t="str">
-        <v>Pittsburgh</v>
+        <v>New York</v>
       </c>
       <c r="J121" t="str">
         <v>On-site</v>
@@ -7706,7 +7706,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L121" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8827944002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8816512002</v>
       </c>
       <c r="M121">
         <v>200</v>
@@ -7715,27 +7715,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O121" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P121" t="str">
         <v>Today</v>
       </c>
       <c r="Q121" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R121" t="str">
         <v>Yes</v>
       </c>
       <c r="S121">
-        <v>40</v>
+        <v>90</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>job-587bfc02</v>
+        <v>job-256f50fd</v>
       </c>
       <c r="B122" t="str">
-        <v>Senior Product Manager, Monetization</v>
+        <v>Senior Product Manager, Notifications</v>
       </c>
       <c r="C122" t="str">
         <v>Duolingo</v>
@@ -7753,10 +7753,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H122" t="str">
-        <v>New York, NY</v>
+        <v>Pittsburgh, PA</v>
       </c>
       <c r="I122" t="str">
-        <v>New York</v>
+        <v>Pittsburgh</v>
       </c>
       <c r="J122" t="str">
         <v>On-site</v>
@@ -7765,7 +7765,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L122" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8474673002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8747099002</v>
       </c>
       <c r="M122">
         <v>200</v>
@@ -7774,27 +7774,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O122" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P122" t="str">
         <v>Today</v>
       </c>
       <c r="Q122" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R122" t="str">
         <v>No</v>
       </c>
       <c r="S122">
-        <v>53</v>
+        <v>91</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>job-256f50fd</v>
+        <v>job-2666664e</v>
       </c>
       <c r="B123" t="str">
-        <v>Senior Product Manager, Notifications</v>
+        <v>Staff Product Manager, Monetization</v>
       </c>
       <c r="C123" t="str">
         <v>Duolingo</v>
@@ -7812,10 +7812,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H123" t="str">
-        <v>Pittsburgh, PA</v>
+        <v>New York, NY</v>
       </c>
       <c r="I123" t="str">
-        <v>Pittsburgh</v>
+        <v>New York</v>
       </c>
       <c r="J123" t="str">
         <v>On-site</v>
@@ -7824,7 +7824,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L123" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8747099002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8474673002</v>
       </c>
       <c r="M123">
         <v>200</v>
@@ -7833,7 +7833,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O123" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P123" t="str">
         <v>Today</v>
@@ -7845,7 +7845,7 @@
         <v>No</v>
       </c>
       <c r="S123">
-        <v>77</v>
+        <v>66</v>
       </c>
     </row>
     <row r="124">
@@ -7892,19 +7892,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O124" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P124" t="str">
         <v>Today</v>
       </c>
       <c r="Q124" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R124" t="str">
         <v>No</v>
       </c>
       <c r="S124">
-        <v>83</v>
+        <v>87</v>
       </c>
     </row>
     <row r="125">
@@ -7951,19 +7951,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O125" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P125" t="str">
         <v>Today</v>
       </c>
       <c r="Q125" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R125" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S125">
-        <v>85</v>
+        <v>48</v>
       </c>
     </row>
     <row r="126">
@@ -8010,19 +8010,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O126" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P126" t="str">
         <v>Today</v>
       </c>
       <c r="Q126" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R126" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S126">
-        <v>25</v>
+        <v>80</v>
       </c>
     </row>
     <row r="127">
@@ -8069,19 +8069,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O127" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P127" t="str">
         <v>Today</v>
       </c>
       <c r="Q127" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R127" t="str">
         <v>No</v>
       </c>
       <c r="S127">
-        <v>29</v>
+        <v>61</v>
       </c>
     </row>
     <row r="128">
@@ -8128,7 +8128,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O128" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P128" t="str">
         <v>Today</v>
@@ -8140,7 +8140,7 @@
         <v>No</v>
       </c>
       <c r="S128">
-        <v>61</v>
+        <v>52</v>
       </c>
     </row>
     <row r="129">
@@ -8187,7 +8187,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O129" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P129" t="str">
         <v>Today</v>
@@ -8199,7 +8199,7 @@
         <v>No</v>
       </c>
       <c r="S129">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="130">
@@ -8246,7 +8246,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O130" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P130" t="str">
         <v>Today</v>
@@ -8258,7 +8258,7 @@
         <v>No</v>
       </c>
       <c r="S130">
-        <v>36</v>
+        <v>47</v>
       </c>
     </row>
     <row r="131">
@@ -8305,19 +8305,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O131" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P131" t="str">
         <v>Today</v>
       </c>
       <c r="Q131" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R131" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S131">
-        <v>51</v>
+        <v>66</v>
       </c>
     </row>
     <row r="132">
@@ -8364,7 +8364,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O132" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P132" t="str">
         <v>Today</v>
@@ -8373,10 +8373,10 @@
         <v>No</v>
       </c>
       <c r="R132" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S132">
-        <v>56</v>
+        <v>29</v>
       </c>
     </row>
     <row r="133">
@@ -8423,7 +8423,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O133" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P133" t="str">
         <v>Today</v>
@@ -8435,7 +8435,7 @@
         <v>No</v>
       </c>
       <c r="S133">
-        <v>81</v>
+        <v>48</v>
       </c>
     </row>
     <row r="134">
@@ -8482,7 +8482,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O134" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P134" t="str">
         <v>Today</v>
@@ -8494,7 +8494,7 @@
         <v>No</v>
       </c>
       <c r="S134">
-        <v>77</v>
+        <v>67</v>
       </c>
     </row>
     <row r="135">
@@ -8541,7 +8541,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O135" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P135" t="str">
         <v>Today</v>
@@ -8553,7 +8553,7 @@
         <v>No</v>
       </c>
       <c r="S135">
-        <v>25</v>
+        <v>29</v>
       </c>
     </row>
     <row r="136">
@@ -8600,19 +8600,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O136" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P136" t="str">
         <v>Today</v>
       </c>
       <c r="Q136" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R136" t="str">
         <v>No</v>
       </c>
       <c r="S136">
-        <v>41</v>
+        <v>57</v>
       </c>
     </row>
     <row r="137">
@@ -8659,19 +8659,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O137" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P137" t="str">
         <v>Today</v>
       </c>
       <c r="Q137" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R137" t="str">
         <v>No</v>
       </c>
       <c r="S137">
-        <v>86</v>
+        <v>37</v>
       </c>
     </row>
     <row r="138">
@@ -8718,7 +8718,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O138" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P138" t="str">
         <v>Today</v>
@@ -8727,10 +8727,10 @@
         <v>No</v>
       </c>
       <c r="R138" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S138">
-        <v>74</v>
+        <v>63</v>
       </c>
     </row>
     <row r="139">
@@ -8777,7 +8777,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O139" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P139" t="str">
         <v>Today</v>
@@ -8786,10 +8786,10 @@
         <v>No</v>
       </c>
       <c r="R139" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S139">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="140">
@@ -8836,19 +8836,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O140" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P140" t="str">
         <v>Today</v>
       </c>
       <c r="Q140" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R140" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S140">
-        <v>38</v>
+        <v>28</v>
       </c>
     </row>
     <row r="141">
@@ -8895,7 +8895,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O141" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P141" t="str">
         <v>Today</v>
@@ -8904,10 +8904,10 @@
         <v>Yes</v>
       </c>
       <c r="R141" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S141">
-        <v>55</v>
+        <v>37</v>
       </c>
     </row>
     <row r="142">
@@ -8954,19 +8954,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O142" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P142" t="str">
         <v>Today</v>
       </c>
       <c r="Q142" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R142" t="str">
         <v>No</v>
       </c>
       <c r="S142">
-        <v>69</v>
+        <v>83</v>
       </c>
     </row>
     <row r="143">
@@ -9013,7 +9013,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O143" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P143" t="str">
         <v>Today</v>
@@ -9022,10 +9022,10 @@
         <v>Yes</v>
       </c>
       <c r="R143" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S143">
-        <v>77</v>
+        <v>37</v>
       </c>
     </row>
     <row r="144">
@@ -9072,7 +9072,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O144" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P144" t="str">
         <v>Today</v>
@@ -9081,10 +9081,10 @@
         <v>No</v>
       </c>
       <c r="R144" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S144">
-        <v>94</v>
+        <v>75</v>
       </c>
     </row>
     <row r="145">
@@ -9131,7 +9131,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O145" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P145" t="str">
         <v>Today</v>
@@ -9143,7 +9143,7 @@
         <v>No</v>
       </c>
       <c r="S145">
-        <v>84</v>
+        <v>40</v>
       </c>
     </row>
     <row r="146">
@@ -9190,7 +9190,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O146" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P146" t="str">
         <v>Today</v>
@@ -9199,10 +9199,10 @@
         <v>No</v>
       </c>
       <c r="R146" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S146">
-        <v>50</v>
+        <v>71</v>
       </c>
     </row>
     <row r="147">
@@ -9249,19 +9249,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O147" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P147" t="str">
         <v>Today</v>
       </c>
       <c r="Q147" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R147" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S147">
-        <v>84</v>
+        <v>41</v>
       </c>
     </row>
     <row r="148">
@@ -9308,19 +9308,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O148" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P148" t="str">
         <v>Today</v>
       </c>
       <c r="Q148" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R148" t="str">
         <v>No</v>
       </c>
       <c r="S148">
-        <v>33</v>
+        <v>69</v>
       </c>
     </row>
     <row r="149">
@@ -9367,19 +9367,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O149" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P149" t="str">
         <v>Today</v>
       </c>
       <c r="Q149" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R149" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S149">
-        <v>34</v>
+        <v>71</v>
       </c>
     </row>
     <row r="150">
@@ -9426,19 +9426,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O150" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P150" t="str">
         <v>Today</v>
       </c>
       <c r="Q150" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R150" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S150">
-        <v>70</v>
+        <v>32</v>
       </c>
     </row>
     <row r="151">
@@ -9485,7 +9485,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O151" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P151" t="str">
         <v>Today</v>
@@ -9494,10 +9494,10 @@
         <v>No</v>
       </c>
       <c r="R151" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S151">
-        <v>86</v>
+        <v>47</v>
       </c>
     </row>
     <row r="152">
@@ -9544,19 +9544,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O152" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P152" t="str">
         <v>Today</v>
       </c>
       <c r="Q152" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R152" t="str">
         <v>No</v>
       </c>
       <c r="S152">
-        <v>26</v>
+        <v>91</v>
       </c>
     </row>
     <row r="153">
@@ -9603,19 +9603,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O153" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P153" t="str">
         <v>Today</v>
       </c>
       <c r="Q153" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R153" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S153">
-        <v>25</v>
+        <v>74</v>
       </c>
     </row>
     <row r="154">
@@ -9662,7 +9662,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O154" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P154" t="str">
         <v>Today</v>
@@ -9671,10 +9671,10 @@
         <v>No</v>
       </c>
       <c r="R154" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S154">
-        <v>61</v>
+        <v>89</v>
       </c>
     </row>
     <row r="155">
@@ -9721,7 +9721,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O155" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P155" t="str">
         <v>Today</v>
@@ -9730,10 +9730,10 @@
         <v>No</v>
       </c>
       <c r="R155" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S155">
-        <v>92</v>
+        <v>33</v>
       </c>
     </row>
     <row r="156">
@@ -9780,7 +9780,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O156" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P156" t="str">
         <v>Today</v>
@@ -9792,7 +9792,7 @@
         <v>No</v>
       </c>
       <c r="S156">
-        <v>29</v>
+        <v>94</v>
       </c>
     </row>
     <row r="157">
@@ -9839,19 +9839,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O157" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P157" t="str">
         <v>Today</v>
       </c>
       <c r="Q157" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R157" t="str">
         <v>No</v>
       </c>
       <c r="S157">
-        <v>69</v>
+        <v>48</v>
       </c>
     </row>
     <row r="158">
@@ -9898,7 +9898,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O158" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P158" t="str">
         <v>Today</v>
@@ -9910,7 +9910,7 @@
         <v>No</v>
       </c>
       <c r="S158">
-        <v>44</v>
+        <v>93</v>
       </c>
     </row>
     <row r="159">
@@ -9957,19 +9957,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O159" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P159" t="str">
         <v>Today</v>
       </c>
       <c r="Q159" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R159" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S159">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="160">
@@ -9995,7 +9995,7 @@
         <v>8+ yrs</v>
       </c>
       <c r="H160" t="str">
-        <v>United States - Remote</v>
+        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
       </c>
       <c r="I160" t="str">
         <v>Remote</v>
@@ -10007,7 +10007,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L160" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8198282</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8198284</v>
       </c>
       <c r="M160">
         <v>200</v>
@@ -10016,19 +10016,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O160" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P160" t="str">
         <v>Today</v>
       </c>
       <c r="Q160" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R160" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S160">
-        <v>42</v>
+        <v>77</v>
       </c>
     </row>
     <row r="161">
@@ -10054,7 +10054,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H161" t="str">
-        <v>United States - Remote</v>
+        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
       </c>
       <c r="I161" t="str">
         <v>Remote</v>
@@ -10066,7 +10066,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L161" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8077510</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8077512</v>
       </c>
       <c r="M161">
         <v>200</v>
@@ -10075,19 +10075,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O161" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P161" t="str">
         <v>Today</v>
       </c>
       <c r="Q161" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R161" t="str">
         <v>No</v>
       </c>
       <c r="S161">
-        <v>81</v>
+        <v>58</v>
       </c>
     </row>
     <row r="162">
@@ -10134,7 +10134,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O162" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P162" t="str">
         <v>Today</v>
@@ -10143,10 +10143,10 @@
         <v>No</v>
       </c>
       <c r="R162" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S162">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="163">
@@ -10193,19 +10193,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O163" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P163" t="str">
         <v>Today</v>
       </c>
       <c r="Q163" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R163" t="str">
         <v>Yes</v>
       </c>
       <c r="S163">
-        <v>66</v>
+        <v>28</v>
       </c>
     </row>
     <row r="164">
@@ -10231,7 +10231,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H164" t="str">
-        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
+        <v>United States - Remote</v>
       </c>
       <c r="I164" t="str">
         <v>Remote</v>
@@ -10243,7 +10243,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L164" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8143272</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8143270</v>
       </c>
       <c r="M164">
         <v>200</v>
@@ -10252,19 +10252,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O164" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P164" t="str">
         <v>Today</v>
       </c>
       <c r="Q164" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R164" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S164">
-        <v>54</v>
+        <v>25</v>
       </c>
     </row>
     <row r="165">
@@ -10290,7 +10290,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H165" t="str">
-        <v>United States - Remote</v>
+        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
       </c>
       <c r="I165" t="str">
         <v>Remote</v>
@@ -10302,7 +10302,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L165" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8203107</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8203109</v>
       </c>
       <c r="M165">
         <v>200</v>
@@ -10311,19 +10311,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O165" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P165" t="str">
         <v>Today</v>
       </c>
       <c r="Q165" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R165" t="str">
         <v>No</v>
       </c>
       <c r="S165">
-        <v>40</v>
+        <v>70</v>
       </c>
     </row>
     <row r="166">
@@ -10349,7 +10349,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H166" t="str">
-        <v>United States - Remote</v>
+        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
       </c>
       <c r="I166" t="str">
         <v>Remote</v>
@@ -10361,7 +10361,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L166" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8014060</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8014062</v>
       </c>
       <c r="M166">
         <v>200</v>
@@ -10370,7 +10370,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O166" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P166" t="str">
         <v>Today</v>
@@ -10379,10 +10379,10 @@
         <v>No</v>
       </c>
       <c r="R166" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S166">
-        <v>38</v>
+        <v>53</v>
       </c>
     </row>
     <row r="167">
@@ -10429,30 +10429,30 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O167" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P167" t="str">
         <v>Today</v>
       </c>
       <c r="Q167" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R167" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S167">
-        <v>62</v>
+        <v>72</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>job-1c3166e2</v>
+        <v>job-7c247a79</v>
       </c>
       <c r="B168" t="str">
-        <v>Product Manager, API Agents</v>
+        <v>Product Manager II - AI</v>
       </c>
       <c r="C168" t="str">
-        <v>OpenAI</v>
+        <v>Razorpay</v>
       </c>
       <c r="D168" t="str">
         <v>LinkedIn</v>
@@ -10467,19 +10467,19 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H168" t="str">
-        <v>San Francisco</v>
+        <v>Bengaluru</v>
       </c>
       <c r="I168" t="str">
-        <v>San Francisco</v>
+        <v>Bengaluru</v>
       </c>
       <c r="J168" t="str">
         <v>On-site</v>
       </c>
       <c r="K168" t="str">
-        <v>$160k - $240k USD + Equity</v>
+        <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L168" t="str">
-        <v>https://jobs.ashbyhq.com/openai/fc38c6bf-5330-435c-99b6-1bcf1f5829a8</v>
+        <v>https://boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4699107005</v>
       </c>
       <c r="M168">
         <v>200</v>
@@ -10488,7 +10488,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O168" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P168" t="str">
         <v>Today</v>
@@ -10500,15 +10500,15 @@
         <v>No</v>
       </c>
       <c r="S168">
-        <v>54</v>
+        <v>79</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>job-6d2b24fc</v>
+        <v>job-1c3166e2</v>
       </c>
       <c r="B169" t="str">
-        <v>Product Manager, Sensitive Deployments</v>
+        <v>Product Manager, API Agents</v>
       </c>
       <c r="C169" t="str">
         <v>OpenAI</v>
@@ -10517,7 +10517,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E169" t="str">
-        <v>Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F169" t="str">
         <v>3-6 yrs</v>
@@ -10538,7 +10538,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L169" t="str">
-        <v>https://jobs.ashbyhq.com/openai/05a8cae8-81bd-4f7b-bc48-41ef1bd67e5d</v>
+        <v>https://jobs.ashbyhq.com/openai/fc38c6bf-5330-435c-99b6-1bcf1f5829a8</v>
       </c>
       <c r="M169">
         <v>200</v>
@@ -10547,7 +10547,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O169" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P169" t="str">
         <v>Today</v>
@@ -10559,15 +10559,15 @@
         <v>Yes</v>
       </c>
       <c r="S169">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>job-184a9e13</v>
+        <v>job-6d2b24fc</v>
       </c>
       <c r="B170" t="str">
-        <v>Product Manager, API Infrastructure</v>
+        <v>Product Manager, Sensitive Deployments</v>
       </c>
       <c r="C170" t="str">
         <v>OpenAI</v>
@@ -10576,7 +10576,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E170" t="str">
-        <v>Technical Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F170" t="str">
         <v>3-6 yrs</v>
@@ -10597,7 +10597,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L170" t="str">
-        <v>https://jobs.ashbyhq.com/openai/7ffa2a14-fa9c-46cb-a30a-1f7a35ae904a</v>
+        <v>https://jobs.ashbyhq.com/openai/05a8cae8-81bd-4f7b-bc48-41ef1bd67e5d</v>
       </c>
       <c r="M170">
         <v>200</v>
@@ -10606,7 +10606,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O170" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P170" t="str">
         <v>Today</v>
@@ -10618,15 +10618,15 @@
         <v>No</v>
       </c>
       <c r="S170">
-        <v>72</v>
+        <v>90</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>job-61ec6778</v>
+        <v>job-184a9e13</v>
       </c>
       <c r="B171" t="str">
-        <v>Product Manager, Safety Measurement</v>
+        <v>Product Manager, API Infrastructure</v>
       </c>
       <c r="C171" t="str">
         <v>OpenAI</v>
@@ -10635,7 +10635,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E171" t="str">
-        <v>Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F171" t="str">
         <v>3-6 yrs</v>
@@ -10656,7 +10656,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L171" t="str">
-        <v>https://jobs.ashbyhq.com/openai/fbc7ebaf-3a26-406d-9ff6-f166f3e246a2</v>
+        <v>https://jobs.ashbyhq.com/openai/7ffa2a14-fa9c-46cb-a30a-1f7a35ae904a</v>
       </c>
       <c r="M171">
         <v>200</v>
@@ -10665,7 +10665,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O171" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P171" t="str">
         <v>Today</v>
@@ -10674,18 +10674,18 @@
         <v>Yes</v>
       </c>
       <c r="R171" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S171">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>job-32d0b9c4</v>
+        <v>job-61ec6778</v>
       </c>
       <c r="B172" t="str">
-        <v>Product Manager, Financial Engineering</v>
+        <v>Product Manager, Safety Measurement</v>
       </c>
       <c r="C172" t="str">
         <v>OpenAI</v>
@@ -10715,7 +10715,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L172" t="str">
-        <v>https://jobs.ashbyhq.com/openai/0f4da2b4-df8a-4560-809d-d0a6ac1ad9bc</v>
+        <v>https://jobs.ashbyhq.com/openai/fbc7ebaf-3a26-406d-9ff6-f166f3e246a2</v>
       </c>
       <c r="M172">
         <v>200</v>
@@ -10724,7 +10724,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O172" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P172" t="str">
         <v>Today</v>
@@ -10733,18 +10733,18 @@
         <v>Yes</v>
       </c>
       <c r="R172" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S172">
-        <v>108</v>
+        <v>89</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>job-675130d5</v>
+        <v>job-32d0b9c4</v>
       </c>
       <c r="B173" t="str">
-        <v>Product Manager, Core Models</v>
+        <v>Product Manager, Financial Engineering</v>
       </c>
       <c r="C173" t="str">
         <v>OpenAI</v>
@@ -10753,7 +10753,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E173" t="str">
-        <v>Technical Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F173" t="str">
         <v>3-6 yrs</v>
@@ -10774,7 +10774,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L173" t="str">
-        <v>https://jobs.ashbyhq.com/openai/33b8effb-b048-4934-a279-87fff192a330</v>
+        <v>https://jobs.ashbyhq.com/openai/0f4da2b4-df8a-4560-809d-d0a6ac1ad9bc</v>
       </c>
       <c r="M173">
         <v>200</v>
@@ -10783,7 +10783,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O173" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P173" t="str">
         <v>Today</v>
@@ -10792,18 +10792,18 @@
         <v>Yes</v>
       </c>
       <c r="R173" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S173">
-        <v>100</v>
+        <v>50</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>job-032480cd</v>
+        <v>job-675130d5</v>
       </c>
       <c r="B174" t="str">
-        <v>Product Manager, Youth</v>
+        <v>Product Manager, Core Models</v>
       </c>
       <c r="C174" t="str">
         <v>OpenAI</v>
@@ -10812,7 +10812,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E174" t="str">
-        <v>Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F174" t="str">
         <v>3-6 yrs</v>
@@ -10833,7 +10833,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L174" t="str">
-        <v>https://jobs.ashbyhq.com/openai/cc0d0d86-eb9d-44a0-a6a4-42bbb6066b4b</v>
+        <v>https://jobs.ashbyhq.com/openai/33b8effb-b048-4934-a279-87fff192a330</v>
       </c>
       <c r="M174">
         <v>200</v>
@@ -10842,7 +10842,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O174" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P174" t="str">
         <v>Today</v>
@@ -10854,15 +10854,15 @@
         <v>Yes</v>
       </c>
       <c r="S174">
-        <v>106</v>
+        <v>87</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>job-50e54898</v>
+        <v>job-032480cd</v>
       </c>
       <c r="B175" t="str">
-        <v>Product Manager, Learning</v>
+        <v>Product Manager, Youth</v>
       </c>
       <c r="C175" t="str">
         <v>OpenAI</v>
@@ -10892,7 +10892,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L175" t="str">
-        <v>https://jobs.ashbyhq.com/openai/5953fed7-1466-4e90-94c9-43716a55e032</v>
+        <v>https://jobs.ashbyhq.com/openai/cc0d0d86-eb9d-44a0-a6a4-42bbb6066b4b</v>
       </c>
       <c r="M175">
         <v>200</v>
@@ -10901,7 +10901,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O175" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P175" t="str">
         <v>Today</v>
@@ -10910,18 +10910,18 @@
         <v>Yes</v>
       </c>
       <c r="R175" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S175">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>job-0df96522</v>
+        <v>job-50e54898</v>
       </c>
       <c r="B176" t="str">
-        <v>Product Manager, Multimodal Safety</v>
+        <v>Product Manager, Learning</v>
       </c>
       <c r="C176" t="str">
         <v>OpenAI</v>
@@ -10951,7 +10951,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L176" t="str">
-        <v>https://jobs.ashbyhq.com/openai/70d5259a-f18c-4595-bf52-ec03eeeeac4c</v>
+        <v>https://jobs.ashbyhq.com/openai/5953fed7-1466-4e90-94c9-43716a55e032</v>
       </c>
       <c r="M176">
         <v>200</v>
@@ -10960,7 +10960,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O176" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P176" t="str">
         <v>Today</v>
@@ -10969,18 +10969,18 @@
         <v>Yes</v>
       </c>
       <c r="R176" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S176">
-        <v>114</v>
+        <v>54</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>job-47895783</v>
+        <v>job-0df96522</v>
       </c>
       <c r="B177" t="str">
-        <v>Product Manager, Enterprise Identity</v>
+        <v>Product Manager, Multimodal Safety</v>
       </c>
       <c r="C177" t="str">
         <v>OpenAI</v>
@@ -11010,7 +11010,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L177" t="str">
-        <v>https://jobs.ashbyhq.com/openai/83f6d415-9462-4afc-a539-ca8d996e011a</v>
+        <v>https://jobs.ashbyhq.com/openai/70d5259a-f18c-4595-bf52-ec03eeeeac4c</v>
       </c>
       <c r="M177">
         <v>200</v>
@@ -11019,7 +11019,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O177" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P177" t="str">
         <v>Today</v>
@@ -11031,21 +11031,21 @@
         <v>Yes</v>
       </c>
       <c r="S177">
-        <v>66</v>
+        <v>106</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>job-5db12f92</v>
+        <v>job-47895783</v>
       </c>
       <c r="B178" t="str">
-        <v>Product Manager (Builder)</v>
+        <v>Product Manager, Enterprise Identity</v>
       </c>
       <c r="C178" t="str">
-        <v>Perplexity</v>
+        <v>OpenAI</v>
       </c>
       <c r="D178" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E178" t="str">
         <v>Product Manager</v>
@@ -11069,7 +11069,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L178" t="str">
-        <v>https://jobs.ashbyhq.com/perplexity/f25e190e-0508-4707-b575-fcaed358dc13</v>
+        <v>https://jobs.ashbyhq.com/openai/83f6d415-9462-4afc-a539-ca8d996e011a</v>
       </c>
       <c r="M178">
         <v>200</v>
@@ -11078,7 +11078,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O178" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P178" t="str">
         <v>Today</v>
@@ -11090,30 +11090,30 @@
         <v>No</v>
       </c>
       <c r="S178">
-        <v>48</v>
+        <v>94</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>job-1fe57ea5</v>
+        <v>job-3fd38143</v>
       </c>
       <c r="B179" t="str">
-        <v>Member of Technical Staff (TPM, Inference)</v>
+        <v>Rosalind Life Sciences Product Manager</v>
       </c>
       <c r="C179" t="str">
-        <v>Perplexity</v>
+        <v>OpenAI</v>
       </c>
       <c r="D179" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E179" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F179" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G179" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H179" t="str">
         <v>San Francisco</v>
@@ -11128,7 +11128,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L179" t="str">
-        <v>https://jobs.ashbyhq.com/perplexity/0c5d5a82-bfed-4786-b411-79073979af07</v>
+        <v>https://jobs.ashbyhq.com/openai/2b5c3a30-8e8b-4845-be40-0617b0c9fd43</v>
       </c>
       <c r="M179">
         <v>200</v>
@@ -11137,7 +11137,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O179" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P179" t="str">
         <v>Today</v>
@@ -11149,15 +11149,15 @@
         <v>No</v>
       </c>
       <c r="S179">
-        <v>87</v>
+        <v>66</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>job-12403072</v>
+        <v>job-5db12f92</v>
       </c>
       <c r="B180" t="str">
-        <v>Product Manager, Mobile Apps</v>
+        <v>Product Manager (Builder)</v>
       </c>
       <c r="C180" t="str">
         <v>Perplexity</v>
@@ -11187,7 +11187,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L180" t="str">
-        <v>https://jobs.ashbyhq.com/perplexity/3c9c051f-e6ca-4a70-9abf-1f640e154ee1</v>
+        <v>https://jobs.ashbyhq.com/perplexity/f25e190e-0508-4707-b575-fcaed358dc13</v>
       </c>
       <c r="M180">
         <v>200</v>
@@ -11196,7 +11196,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O180" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P180" t="str">
         <v>Today</v>
@@ -11208,15 +11208,15 @@
         <v>Yes</v>
       </c>
       <c r="S180">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>job-10379173</v>
+        <v>job-1fe57ea5</v>
       </c>
       <c r="B181" t="str">
-        <v>Product Manager, Core Experience</v>
+        <v>Member of Technical Staff (TPM, Inference)</v>
       </c>
       <c r="C181" t="str">
         <v>Perplexity</v>
@@ -11225,13 +11225,13 @@
         <v>Wellfound</v>
       </c>
       <c r="E181" t="str">
-        <v>Technical Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F181" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G181" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H181" t="str">
         <v>San Francisco</v>
@@ -11246,7 +11246,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L181" t="str">
-        <v>https://jobs.ashbyhq.com/perplexity/6f3c5131-2efa-400c-8248-44203a4dbfbb</v>
+        <v>https://jobs.ashbyhq.com/perplexity/0c5d5a82-bfed-4786-b411-79073979af07</v>
       </c>
       <c r="M181">
         <v>200</v>
@@ -11255,7 +11255,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O181" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P181" t="str">
         <v>Today</v>
@@ -11264,7 +11264,7 @@
         <v>Yes</v>
       </c>
       <c r="R181" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S181">
         <v>74</v>
@@ -11272,10 +11272,10 @@
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>job-247da510</v>
+        <v>job-12403072</v>
       </c>
       <c r="B182" t="str">
-        <v>Product Manager, AI Capabilities</v>
+        <v>Product Manager, Mobile Apps</v>
       </c>
       <c r="C182" t="str">
         <v>Perplexity</v>
@@ -11284,7 +11284,7 @@
         <v>Wellfound</v>
       </c>
       <c r="E182" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Product Manager</v>
       </c>
       <c r="F182" t="str">
         <v>3-6 yrs</v>
@@ -11305,7 +11305,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L182" t="str">
-        <v>https://jobs.ashbyhq.com/perplexity/7f880194-7276-4b46-8a50-58b48da8882e</v>
+        <v>https://jobs.ashbyhq.com/perplexity/3c9c051f-e6ca-4a70-9abf-1f640e154ee1</v>
       </c>
       <c r="M182">
         <v>200</v>
@@ -11314,7 +11314,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O182" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P182" t="str">
         <v>Today</v>
@@ -11323,18 +11323,18 @@
         <v>Yes</v>
       </c>
       <c r="R182" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S182">
-        <v>106</v>
+        <v>53</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>job-757a314d</v>
+        <v>job-10379173</v>
       </c>
       <c r="B183" t="str">
-        <v>Product Manager, Growth</v>
+        <v>Product Manager, Core Experience</v>
       </c>
       <c r="C183" t="str">
         <v>Perplexity</v>
@@ -11343,7 +11343,7 @@
         <v>Wellfound</v>
       </c>
       <c r="E183" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F183" t="str">
         <v>3-6 yrs</v>
@@ -11352,10 +11352,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H183" t="str">
-        <v>New York City</v>
+        <v>San Francisco</v>
       </c>
       <c r="I183" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J183" t="str">
         <v>On-site</v>
@@ -11364,7 +11364,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L183" t="str">
-        <v>https://jobs.ashbyhq.com/perplexity/fa088d92-b08b-43f7-9232-275b0ae08827</v>
+        <v>https://jobs.ashbyhq.com/perplexity/6f3c5131-2efa-400c-8248-44203a4dbfbb</v>
       </c>
       <c r="M183">
         <v>200</v>
@@ -11373,7 +11373,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O183" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P183" t="str">
         <v>Today</v>
@@ -11382,18 +11382,18 @@
         <v>Yes</v>
       </c>
       <c r="R183" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S183">
-        <v>45</v>
+        <v>70</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>job-376e5ff5</v>
+        <v>job-247da510</v>
       </c>
       <c r="B184" t="str">
-        <v>Product Manager, SMB Growth</v>
+        <v>Product Manager, AI Capabilities</v>
       </c>
       <c r="C184" t="str">
         <v>Perplexity</v>
@@ -11411,10 +11411,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H184" t="str">
-        <v>New York City</v>
+        <v>San Francisco</v>
       </c>
       <c r="I184" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J184" t="str">
         <v>On-site</v>
@@ -11423,7 +11423,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L184" t="str">
-        <v>https://jobs.ashbyhq.com/perplexity/182ab2ec-6fb1-409b-a2dc-63c7832b0a13</v>
+        <v>https://jobs.ashbyhq.com/perplexity/7f880194-7276-4b46-8a50-58b48da8882e</v>
       </c>
       <c r="M184">
         <v>200</v>
@@ -11432,7 +11432,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O184" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P184" t="str">
         <v>Today</v>
@@ -11444,24 +11444,24 @@
         <v>No</v>
       </c>
       <c r="S184">
-        <v>76</v>
+        <v>110</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>job-6fff938e</v>
+        <v>job-757a314d</v>
       </c>
       <c r="B185" t="str">
-        <v>Product Manager - Marketplace</v>
+        <v>Product Manager, Growth</v>
       </c>
       <c r="C185" t="str">
-        <v>Supabase</v>
+        <v>Perplexity</v>
       </c>
       <c r="D185" t="str">
         <v>Wellfound</v>
       </c>
       <c r="E185" t="str">
-        <v>Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F185" t="str">
         <v>3-6 yrs</v>
@@ -11470,19 +11470,19 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H185" t="str">
-        <v>Remote, Global</v>
+        <v>New York City</v>
       </c>
       <c r="I185" t="str">
-        <v>Remote</v>
+        <v>New York</v>
       </c>
       <c r="J185" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K185" t="str">
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L185" t="str">
-        <v>https://jobs.ashbyhq.com/supabase/23c9ce7e-6b7b-4316-8f00-8f318e902441</v>
+        <v>https://jobs.ashbyhq.com/perplexity/fa088d92-b08b-43f7-9232-275b0ae08827</v>
       </c>
       <c r="M185">
         <v>200</v>
@@ -11491,7 +11491,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O185" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P185" t="str">
         <v>Today</v>
@@ -11500,27 +11500,27 @@
         <v>Yes</v>
       </c>
       <c r="R185" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S185">
-        <v>42</v>
+        <v>86</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>job-49f97312</v>
+        <v>job-376e5ff5</v>
       </c>
       <c r="B186" t="str">
-        <v>Product Manager - Security &amp; Trust (EMEA/AMER)</v>
+        <v>Product Manager, SMB Growth</v>
       </c>
       <c r="C186" t="str">
-        <v>Supabase</v>
+        <v>Perplexity</v>
       </c>
       <c r="D186" t="str">
         <v>Wellfound</v>
       </c>
       <c r="E186" t="str">
-        <v>Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F186" t="str">
         <v>3-6 yrs</v>
@@ -11529,19 +11529,19 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H186" t="str">
-        <v>Remote, Global</v>
+        <v>New York City</v>
       </c>
       <c r="I186" t="str">
-        <v>Remote</v>
+        <v>New York</v>
       </c>
       <c r="J186" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K186" t="str">
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L186" t="str">
-        <v>https://jobs.ashbyhq.com/supabase/b8010a28-109c-46a9-b8b7-c7f9b24077fa</v>
+        <v>https://jobs.ashbyhq.com/perplexity/182ab2ec-6fb1-409b-a2dc-63c7832b0a13</v>
       </c>
       <c r="M186">
         <v>200</v>
@@ -11550,7 +11550,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O186" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P186" t="str">
         <v>Today</v>
@@ -11559,18 +11559,18 @@
         <v>Yes</v>
       </c>
       <c r="R186" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S186">
-        <v>101</v>
+        <v>67</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>job-5ee8bae7</v>
+        <v>job-6fff938e</v>
       </c>
       <c r="B187" t="str">
-        <v>Product Manager - Branching</v>
+        <v>Product Manager - Marketplace</v>
       </c>
       <c r="C187" t="str">
         <v>Supabase</v>
@@ -11600,7 +11600,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L187" t="str">
-        <v>https://jobs.ashbyhq.com/supabase/9773ea1b-e25b-437c-bdbd-3fce0c69101e</v>
+        <v>https://jobs.ashbyhq.com/supabase/23c9ce7e-6b7b-4316-8f00-8f318e902441</v>
       </c>
       <c r="M187">
         <v>200</v>
@@ -11609,7 +11609,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O187" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P187" t="str">
         <v>Today</v>
@@ -11618,18 +11618,18 @@
         <v>Yes</v>
       </c>
       <c r="R187" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S187">
-        <v>48</v>
+        <v>67</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>job-064fa6b5</v>
+        <v>job-49f97312</v>
       </c>
       <c r="B188" t="str">
-        <v>Product Manager - Strategic Partner Integrations (Bay Area based)</v>
+        <v>Product Manager - Security &amp; Trust (EMEA/AMER)</v>
       </c>
       <c r="C188" t="str">
         <v>Supabase</v>
@@ -11647,10 +11647,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H188" t="str">
-        <v>Remote, Bay Area, CA</v>
+        <v>Remote, Global</v>
       </c>
       <c r="I188" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J188" t="str">
         <v>Remote</v>
@@ -11659,7 +11659,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L188" t="str">
-        <v>https://jobs.ashbyhq.com/supabase/68a397e7-8a1a-4566-ae41-e8c61dd6ed93</v>
+        <v>https://jobs.ashbyhq.com/supabase/b8010a28-109c-46a9-b8b7-c7f9b24077fa</v>
       </c>
       <c r="M188">
         <v>200</v>
@@ -11668,7 +11668,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O188" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P188" t="str">
         <v>Today</v>
@@ -11677,27 +11677,27 @@
         <v>Yes</v>
       </c>
       <c r="R188" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S188">
-        <v>92</v>
+        <v>69</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>job-7da017c6</v>
+        <v>job-064fa6b5</v>
       </c>
       <c r="B189" t="str">
-        <v>Product Manager | Vendor Intelligence &amp; Marketplace</v>
+        <v>Product Manager - Strategic Partner Integrations (Bay Area based)</v>
       </c>
       <c r="C189" t="str">
-        <v>Ramp</v>
+        <v>Supabase</v>
       </c>
       <c r="D189" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E189" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Product Manager</v>
       </c>
       <c r="F189" t="str">
         <v>3-6 yrs</v>
@@ -11706,19 +11706,19 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H189" t="str">
-        <v>New York, NY (HQ)</v>
+        <v>Remote, Bay Area, CA</v>
       </c>
       <c r="I189" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J189" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K189" t="str">
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L189" t="str">
-        <v>https://jobs.ashbyhq.com/ramp/cf3516f6-4d6b-4872-831f-c8ef4a3078ee</v>
+        <v>https://jobs.ashbyhq.com/supabase/68a397e7-8a1a-4566-ae41-e8c61dd6ed93</v>
       </c>
       <c r="M189">
         <v>200</v>
@@ -11727,7 +11727,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O189" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P189" t="str">
         <v>Today</v>
@@ -11739,15 +11739,15 @@
         <v>No</v>
       </c>
       <c r="S189">
-        <v>118</v>
+        <v>82</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>job-338455bd</v>
+        <v>job-7da017c6</v>
       </c>
       <c r="B190" t="str">
-        <v>Product Manager | Tax</v>
+        <v>Product Manager | Vendor Intelligence &amp; Marketplace</v>
       </c>
       <c r="C190" t="str">
         <v>Ramp</v>
@@ -11756,7 +11756,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E190" t="str">
-        <v>Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F190" t="str">
         <v>3-6 yrs</v>
@@ -11777,7 +11777,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L190" t="str">
-        <v>https://jobs.ashbyhq.com/ramp/881f9f7d-9ec5-4b69-b50d-a67000264ca8</v>
+        <v>https://jobs.ashbyhq.com/ramp/cf3516f6-4d6b-4872-831f-c8ef4a3078ee</v>
       </c>
       <c r="M190">
         <v>200</v>
@@ -11786,7 +11786,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O190" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P190" t="str">
         <v>Today</v>
@@ -11795,18 +11795,18 @@
         <v>Yes</v>
       </c>
       <c r="R190" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S190">
-        <v>89</v>
+        <v>95</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>job-6744eb00</v>
+        <v>job-338455bd</v>
       </c>
       <c r="B191" t="str">
-        <v>Product Manager | International</v>
+        <v>Product Manager | Tax</v>
       </c>
       <c r="C191" t="str">
         <v>Ramp</v>
@@ -11818,10 +11818,10 @@
         <v>Product Manager</v>
       </c>
       <c r="F191" t="str">
-        <v>1-3 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G191" t="str">
-        <v>0-2 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H191" t="str">
         <v>New York, NY (HQ)</v>
@@ -11836,7 +11836,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L191" t="str">
-        <v>https://jobs.ashbyhq.com/ramp/8baec095-2235-41ab-ab64-9abc57823b4b</v>
+        <v>https://jobs.ashbyhq.com/ramp/881f9f7d-9ec5-4b69-b50d-a67000264ca8</v>
       </c>
       <c r="M191">
         <v>200</v>
@@ -11845,7 +11845,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O191" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P191" t="str">
         <v>Today</v>
@@ -11854,39 +11854,39 @@
         <v>Yes</v>
       </c>
       <c r="R191" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S191">
-        <v>104</v>
+        <v>50</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>job-497b065e</v>
+        <v>job-6744eb00</v>
       </c>
       <c r="B192" t="str">
-        <v>Senior Product Manager, Mobile</v>
+        <v>Product Manager | International</v>
       </c>
       <c r="C192" t="str">
-        <v>Sentry</v>
+        <v>Ramp</v>
       </c>
       <c r="D192" t="str">
-        <v>Indeed</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E192" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F192" t="str">
-        <v>5-8 yrs</v>
+        <v>1-3 yrs</v>
       </c>
       <c r="G192" t="str">
-        <v>5-8 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H192" t="str">
-        <v>Vienna, Austria</v>
+        <v>New York, NY (HQ)</v>
       </c>
       <c r="I192" t="str">
-        <v>Vienna</v>
+        <v>New York</v>
       </c>
       <c r="J192" t="str">
         <v>On-site</v>
@@ -11895,7 +11895,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L192" t="str">
-        <v>https://jobs.ashbyhq.com/sentry/6a973e19-6736-4973-8a87-043fcbcd553e</v>
+        <v>https://jobs.ashbyhq.com/ramp/8baec095-2235-41ab-ab64-9abc57823b4b</v>
       </c>
       <c r="M192">
         <v>200</v>
@@ -11904,7 +11904,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O192" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P192" t="str">
         <v>Today</v>
@@ -11916,36 +11916,36 @@
         <v>Yes</v>
       </c>
       <c r="S192">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>job-33169045</v>
+        <v>job-497b065e</v>
       </c>
       <c r="B193" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager, Mobile</v>
       </c>
       <c r="C193" t="str">
-        <v>Linear</v>
+        <v>Sentry</v>
       </c>
       <c r="D193" t="str">
-        <v>Wellfound</v>
+        <v>Indeed</v>
       </c>
       <c r="E193" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F193" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G193" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H193" t="str">
-        <v>North America</v>
+        <v>Vienna, Austria</v>
       </c>
       <c r="I193" t="str">
-        <v>North America</v>
+        <v>Vienna</v>
       </c>
       <c r="J193" t="str">
         <v>On-site</v>
@@ -11954,7 +11954,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L193" t="str">
-        <v>https://jobs.ashbyhq.com/linear/b7669c4b-eeca-421d-ba9a-d90203f6fcb2</v>
+        <v>https://jobs.ashbyhq.com/sentry/6a973e19-6736-4973-8a87-043fcbcd553e</v>
       </c>
       <c r="M193">
         <v>200</v>
@@ -11963,7 +11963,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O193" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P193" t="str">
         <v>Today</v>
@@ -11972,48 +11972,48 @@
         <v>Yes</v>
       </c>
       <c r="R193" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S193">
-        <v>66</v>
+        <v>109</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>job-048a3bb1</v>
+        <v>job-33169045</v>
       </c>
       <c r="B194" t="str">
-        <v>Head of Product Management - Artist Products</v>
+        <v>Product Manager</v>
       </c>
       <c r="C194" t="str">
-        <v>Spotify</v>
+        <v>Linear</v>
       </c>
       <c r="D194" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E194" t="str">
-        <v>Product Lead / Director</v>
+        <v>Product Manager</v>
       </c>
       <c r="F194" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G194" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H194" t="str">
-        <v>New York, NY</v>
+        <v>North America</v>
       </c>
       <c r="I194" t="str">
-        <v>New York</v>
+        <v>North America</v>
       </c>
       <c r="J194" t="str">
         <v>On-site</v>
       </c>
       <c r="K194" t="str">
-        <v>$150k - $220k USD + RSUs</v>
+        <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L194" t="str">
-        <v>https://jobs.lever.co/spotify/e2c7bbb8-f873-42c7-811f-0bd45bf452ae</v>
+        <v>https://jobs.ashbyhq.com/linear/b7669c4b-eeca-421d-ba9a-d90203f6fcb2</v>
       </c>
       <c r="M194">
         <v>200</v>
@@ -12022,7 +12022,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O194" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P194" t="str">
         <v>Today</v>
@@ -12034,15 +12034,15 @@
         <v>No</v>
       </c>
       <c r="S194">
-        <v>82</v>
+        <v>59</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>job-39d9f7fb</v>
+        <v>job-048a3bb1</v>
       </c>
       <c r="B195" t="str">
-        <v>Principal Product Manager - Audio and Media Playback</v>
+        <v>Head of Product Management - Artist Products</v>
       </c>
       <c r="C195" t="str">
         <v>Spotify</v>
@@ -12051,7 +12051,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E195" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F195" t="str">
         <v>5-8 yrs</v>
@@ -12060,10 +12060,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H195" t="str">
-        <v>Stockholm</v>
+        <v>New York, NY</v>
       </c>
       <c r="I195" t="str">
-        <v>Stockholm</v>
+        <v>New York</v>
       </c>
       <c r="J195" t="str">
         <v>On-site</v>
@@ -12072,7 +12072,7 @@
         <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L195" t="str">
-        <v>https://jobs.lever.co/spotify/080868dd-fc8c-4648-b6ab-6780d8ca3d63</v>
+        <v>https://jobs.lever.co/spotify/e2c7bbb8-f873-42c7-811f-0bd45bf452ae</v>
       </c>
       <c r="M195">
         <v>200</v>
@@ -12081,7 +12081,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O195" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P195" t="str">
         <v>Today</v>
@@ -12093,15 +12093,15 @@
         <v>No</v>
       </c>
       <c r="S195">
-        <v>30</v>
+        <v>64</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>job-61f86f2b</v>
+        <v>job-39d9f7fb</v>
       </c>
       <c r="B196" t="str">
-        <v>Product Manager - Customer Service Platform</v>
+        <v>Principal Product Manager - Audio and Media Playback</v>
       </c>
       <c r="C196" t="str">
         <v>Spotify</v>
@@ -12110,7 +12110,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E196" t="str">
-        <v>Technical Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F196" t="str">
         <v>5-8 yrs</v>
@@ -12119,10 +12119,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H196" t="str">
-        <v>London</v>
+        <v>Stockholm</v>
       </c>
       <c r="I196" t="str">
-        <v>London</v>
+        <v>Stockholm</v>
       </c>
       <c r="J196" t="str">
         <v>On-site</v>
@@ -12131,7 +12131,7 @@
         <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L196" t="str">
-        <v>https://jobs.lever.co/spotify/7f0a8faa-f4f5-4db9-9f51-4101d6a29b34</v>
+        <v>https://jobs.lever.co/spotify/080868dd-fc8c-4648-b6ab-6780d8ca3d63</v>
       </c>
       <c r="M196">
         <v>200</v>
@@ -12140,7 +12140,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O196" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P196" t="str">
         <v>Today</v>
@@ -12152,15 +12152,15 @@
         <v>No</v>
       </c>
       <c r="S196">
-        <v>52</v>
+        <v>32</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>job-1a230b4c</v>
+        <v>job-5b32c75d</v>
       </c>
       <c r="B197" t="str">
-        <v>Product Manager - Data Platform</v>
+        <v>Principal Product Manager - Personalization</v>
       </c>
       <c r="C197" t="str">
         <v>Spotify</v>
@@ -12169,7 +12169,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E197" t="str">
-        <v>Technical Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F197" t="str">
         <v>5-8 yrs</v>
@@ -12178,10 +12178,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H197" t="str">
-        <v>Toronto</v>
+        <v>London</v>
       </c>
       <c r="I197" t="str">
-        <v>Toronto</v>
+        <v>London</v>
       </c>
       <c r="J197" t="str">
         <v>On-site</v>
@@ -12190,7 +12190,7 @@
         <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L197" t="str">
-        <v>https://jobs.lever.co/spotify/03437e2a-2d5e-4593-9e97-11271014932e</v>
+        <v>https://jobs.lever.co/spotify/e74bfb24-55de-4d93-b228-ae38b8fdfbea</v>
       </c>
       <c r="M197">
         <v>200</v>
@@ -12199,7 +12199,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O197" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P197" t="str">
         <v>Today</v>
@@ -12211,15 +12211,15 @@
         <v>No</v>
       </c>
       <c r="S197">
-        <v>41</v>
+        <v>75</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>job-1ba340a4</v>
+        <v>job-61f86f2b</v>
       </c>
       <c r="B198" t="str">
-        <v>Senior Product Manager - Audiobooks Format Foundations</v>
+        <v>Product Manager - Customer Service Platform</v>
       </c>
       <c r="C198" t="str">
         <v>Spotify</v>
@@ -12228,7 +12228,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E198" t="str">
-        <v>Senior Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F198" t="str">
         <v>5-8 yrs</v>
@@ -12249,7 +12249,7 @@
         <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L198" t="str">
-        <v>https://jobs.lever.co/spotify/e7b01c1e-4246-4f31-83ea-9219c8b22c83</v>
+        <v>https://jobs.lever.co/spotify/7f0a8faa-f4f5-4db9-9f51-4101d6a29b34</v>
       </c>
       <c r="M198">
         <v>200</v>
@@ -12258,7 +12258,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O198" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P198" t="str">
         <v>Today</v>
@@ -12270,15 +12270,15 @@
         <v>No</v>
       </c>
       <c r="S198">
-        <v>48</v>
+        <v>72</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>job-3a0c9449</v>
+        <v>job-1a230b4c</v>
       </c>
       <c r="B199" t="str">
-        <v>Senior Product Manager - Subscriptions</v>
+        <v>Product Manager - Data Platform</v>
       </c>
       <c r="C199" t="str">
         <v>Spotify</v>
@@ -12287,7 +12287,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E199" t="str">
-        <v>Senior Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F199" t="str">
         <v>5-8 yrs</v>
@@ -12296,10 +12296,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H199" t="str">
-        <v>London</v>
+        <v>Toronto</v>
       </c>
       <c r="I199" t="str">
-        <v>London</v>
+        <v>Toronto</v>
       </c>
       <c r="J199" t="str">
         <v>On-site</v>
@@ -12308,7 +12308,7 @@
         <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L199" t="str">
-        <v>https://jobs.lever.co/spotify/a57db22d-dc0d-4f36-9a2e-34acdf1ec046</v>
+        <v>https://jobs.lever.co/spotify/03437e2a-2d5e-4593-9e97-11271014932e</v>
       </c>
       <c r="M199">
         <v>200</v>
@@ -12317,7 +12317,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O199" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P199" t="str">
         <v>Today</v>
@@ -12329,24 +12329,24 @@
         <v>No</v>
       </c>
       <c r="S199">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>job-4d0308c8</v>
+        <v>job-1ba340a4</v>
       </c>
       <c r="B200" t="str">
-        <v>Technical Program Manager (TPM)</v>
+        <v>Senior Product Manager - Audiobooks Format Foundations</v>
       </c>
       <c r="C200" t="str">
-        <v>Palantir</v>
+        <v>Spotify</v>
       </c>
       <c r="D200" t="str">
-        <v>Instahyre</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E200" t="str">
-        <v>Technical Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F200" t="str">
         <v>5-8 yrs</v>
@@ -12355,10 +12355,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H200" t="str">
-        <v>New York, NY</v>
+        <v>London</v>
       </c>
       <c r="I200" t="str">
-        <v>New York</v>
+        <v>London</v>
       </c>
       <c r="J200" t="str">
         <v>On-site</v>
@@ -12367,7 +12367,7 @@
         <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L200" t="str">
-        <v>https://jobs.lever.co/palantir/7eb0dedb-37ee-4175-b29f-10a9e4340076</v>
+        <v>https://jobs.lever.co/spotify/e7b01c1e-4246-4f31-83ea-9219c8b22c83</v>
       </c>
       <c r="M200">
         <v>200</v>
@@ -12376,7 +12376,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O200" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P200" t="str">
         <v>Today</v>
@@ -12388,24 +12388,24 @@
         <v>No</v>
       </c>
       <c r="S200">
-        <v>75</v>
+        <v>86</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>job-593275cb</v>
+        <v>job-3a0c9449</v>
       </c>
       <c r="B201" t="str">
-        <v>Technical Program Manager (TPM) - Defense</v>
+        <v>Senior Product Manager - Subscriptions</v>
       </c>
       <c r="C201" t="str">
-        <v>Palantir</v>
+        <v>Spotify</v>
       </c>
       <c r="D201" t="str">
-        <v>Instahyre</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E201" t="str">
-        <v>Technical Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F201" t="str">
         <v>5-8 yrs</v>
@@ -12414,10 +12414,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H201" t="str">
-        <v>Washington, D.C.</v>
+        <v>London</v>
       </c>
       <c r="I201" t="str">
-        <v>Washington</v>
+        <v>London</v>
       </c>
       <c r="J201" t="str">
         <v>On-site</v>
@@ -12426,7 +12426,7 @@
         <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L201" t="str">
-        <v>https://jobs.lever.co/palantir/bd16f7ad-3bee-48fd-9902-b3ee9698b608</v>
+        <v>https://jobs.lever.co/spotify/a57db22d-dc0d-4f36-9a2e-34acdf1ec046</v>
       </c>
       <c r="M201">
         <v>200</v>
@@ -12435,7 +12435,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O201" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P201" t="str">
         <v>Today</v>
@@ -12447,45 +12447,45 @@
         <v>No</v>
       </c>
       <c r="S201">
-        <v>89</v>
+        <v>49</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>job-343d8912</v>
+        <v>job-4d0308c8</v>
       </c>
       <c r="B202" t="str">
-        <v>Associate Product Manager (APM) - Growth &amp; Merchant Onboarding</v>
+        <v>Technical Program Manager (TPM)</v>
       </c>
       <c r="C202" t="str">
-        <v>Razorpay</v>
+        <v>Palantir</v>
       </c>
       <c r="D202" t="str">
-        <v>LinkedIn</v>
+        <v>Instahyre</v>
       </c>
       <c r="E202" t="str">
-        <v>Associate Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F202" t="str">
-        <v>1-3 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G202" t="str">
-        <v>0-2 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H202" t="str">
-        <v>Bengaluru, Karnataka</v>
+        <v>New York, NY</v>
       </c>
       <c r="I202" t="str">
-        <v>Bengaluru</v>
+        <v>New York</v>
       </c>
       <c r="J202" t="str">
-        <v>Hybrid</v>
+        <v>On-site</v>
       </c>
       <c r="K202" t="str">
-        <v>₹18L - ₹26L PA + ESOPs</v>
+        <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L202" t="str">
-        <v>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited</v>
+        <v>https://jobs.lever.co/palantir/7eb0dedb-37ee-4175-b29f-10a9e4340076</v>
       </c>
       <c r="M202">
         <v>200</v>
@@ -12494,7 +12494,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O202" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P202" t="str">
         <v>Today</v>
@@ -12503,27 +12503,27 @@
         <v>Yes</v>
       </c>
       <c r="R202" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S202">
-        <v>42</v>
+        <v>53</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>job-739e0b9f</v>
+        <v>job-593275cb</v>
       </c>
       <c r="B203" t="str">
-        <v>Senior Product Manager - Consumer Checkout &amp; Loyalty</v>
+        <v>Technical Program Manager (TPM) - Defense</v>
       </c>
       <c r="C203" t="str">
-        <v>Swiggy</v>
+        <v>Palantir</v>
       </c>
       <c r="D203" t="str">
-        <v>Naukri</v>
+        <v>Instahyre</v>
       </c>
       <c r="E203" t="str">
-        <v>Senior Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F203" t="str">
         <v>5-8 yrs</v>
@@ -12532,19 +12532,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H203" t="str">
-        <v>Bengaluru, Karnataka</v>
+        <v>Washington, D.C.</v>
       </c>
       <c r="I203" t="str">
-        <v>Bengaluru</v>
+        <v>Washington</v>
       </c>
       <c r="J203" t="str">
-        <v>Hybrid</v>
+        <v>On-site</v>
       </c>
       <c r="K203" t="str">
-        <v>₹45L - ₹65L PA + ESOPs</v>
+        <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L203" t="str">
-        <v>https://careers.swiggy.com/</v>
+        <v>https://jobs.lever.co/palantir/bd16f7ad-3bee-48fd-9902-b3ee9698b608</v>
       </c>
       <c r="M203">
         <v>200</v>
@@ -12553,7 +12553,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O203" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P203" t="str">
         <v>Today</v>
@@ -12562,57 +12562,57 @@
         <v>Yes</v>
       </c>
       <c r="R203" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S203">
-        <v>115</v>
+        <v>58</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>job-66154b1b</v>
+        <v>job-343d8912</v>
       </c>
       <c r="B204" t="str">
-        <v>Senior Product Manager - 10-Minute Dark Store &amp; Logistics Dispatch</v>
+        <v>Associate Product Manager (APM) - Growth &amp; Merchant Onboarding</v>
       </c>
       <c r="C204" t="str">
-        <v>Zepto</v>
+        <v>Razorpay</v>
       </c>
       <c r="D204" t="str">
-        <v>Naukri</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E204" t="str">
-        <v>Senior Product Manager</v>
+        <v>Associate Product Manager</v>
       </c>
       <c r="F204" t="str">
-        <v>4-7 yrs</v>
+        <v>1-3 yrs</v>
       </c>
       <c r="G204" t="str">
-        <v>2-5 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H204" t="str">
-        <v>Mumbai, Maharashtra</v>
+        <v>Bengaluru, Karnataka</v>
       </c>
       <c r="I204" t="str">
-        <v>Mumbai</v>
+        <v>Bengaluru</v>
       </c>
       <c r="J204" t="str">
-        <v>On-site</v>
+        <v>Hybrid</v>
       </c>
       <c r="K204" t="str">
-        <v>₹42L - ₹60L PA + ESOPs</v>
+        <v>₹18L - ₹26L PA + ESOPs</v>
       </c>
       <c r="L204" t="str">
-        <v>https://www.zeptonow.com/careers</v>
+        <v>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited</v>
       </c>
       <c r="M204">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N204" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O204" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P204" t="str">
         <v>Today</v>
@@ -12624,18 +12624,18 @@
         <v>Yes</v>
       </c>
       <c r="S204">
-        <v>94</v>
+        <v>42</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>job-169943b4</v>
+        <v>job-739e0b9f</v>
       </c>
       <c r="B205" t="str">
-        <v>Senior Product Manager - Customer Experience &amp; Live Support AI</v>
+        <v>Senior Product Manager - Consumer Checkout &amp; Loyalty</v>
       </c>
       <c r="C205" t="str">
-        <v>Zomato</v>
+        <v>Swiggy</v>
       </c>
       <c r="D205" t="str">
         <v>Naukri</v>
@@ -12650,28 +12650,28 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H205" t="str">
-        <v>Gurgaon, Haryana</v>
+        <v>Bengaluru, Karnataka</v>
       </c>
       <c r="I205" t="str">
-        <v>Gurgaon</v>
+        <v>Bengaluru</v>
       </c>
       <c r="J205" t="str">
-        <v>On-site</v>
+        <v>Hybrid</v>
       </c>
       <c r="K205" t="str">
         <v>₹45L - ₹65L PA + ESOPs</v>
       </c>
       <c r="L205" t="str">
-        <v>https://www.zomato.com/careers</v>
+        <v>https://careers.swiggy.com/</v>
       </c>
       <c r="M205">
-        <v>503</v>
+        <v>200</v>
       </c>
       <c r="N205" t="str">
-        <v>BROKEN / 404</v>
+        <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O205" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P205" t="str">
         <v>Today</v>
@@ -12683,54 +12683,54 @@
         <v>Yes</v>
       </c>
       <c r="S205">
-        <v>95</v>
+        <v>115</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>job-23756e58</v>
+        <v>job-66154b1b</v>
       </c>
       <c r="B206" t="str">
-        <v>Associate Product Manager (APM) - Social Commerce &amp; Creator Tools</v>
+        <v>Senior Product Manager - 10-Minute Dark Store &amp; Logistics Dispatch</v>
       </c>
       <c r="C206" t="str">
-        <v>Meesho</v>
+        <v>Zepto</v>
       </c>
       <c r="D206" t="str">
         <v>Naukri</v>
       </c>
       <c r="E206" t="str">
-        <v>Associate Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F206" t="str">
-        <v>0-2 yrs</v>
+        <v>4-7 yrs</v>
       </c>
       <c r="G206" t="str">
-        <v>0-2 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H206" t="str">
-        <v>Bengaluru, Karnataka</v>
+        <v>Mumbai, Maharashtra</v>
       </c>
       <c r="I206" t="str">
-        <v>Bengaluru</v>
+        <v>Mumbai</v>
       </c>
       <c r="J206" t="str">
-        <v>Hybrid</v>
+        <v>On-site</v>
       </c>
       <c r="K206" t="str">
-        <v>₹18L - ₹25L PA + ESOPs</v>
+        <v>₹42L - ₹60L PA + ESOPs</v>
       </c>
       <c r="L206" t="str">
-        <v>https://www.meesho.io/jobs</v>
+        <v>https://www.zeptonow.com/careers</v>
       </c>
       <c r="M206">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="N206" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O206" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P206" t="str">
         <v>Today</v>
@@ -12742,89 +12742,89 @@
         <v>Yes</v>
       </c>
       <c r="S206">
-        <v>65</v>
+        <v>94</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>job-6900691e</v>
+        <v>job-169943b4</v>
       </c>
       <c r="B207" t="str">
-        <v>Product Owner - Core Banking &amp; Credit Line Engine</v>
+        <v>Senior Product Manager - Customer Experience &amp; Live Support AI</v>
       </c>
       <c r="C207" t="str">
-        <v>CRED</v>
+        <v>Zomato</v>
       </c>
       <c r="D207" t="str">
-        <v>Instahyre</v>
+        <v>Naukri</v>
       </c>
       <c r="E207" t="str">
-        <v>Technical Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F207" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G207" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H207" t="str">
-        <v>Bengaluru, Karnataka</v>
+        <v>Gurgaon, Haryana</v>
       </c>
       <c r="I207" t="str">
-        <v>Bengaluru</v>
+        <v>Gurgaon</v>
       </c>
       <c r="J207" t="str">
         <v>On-site</v>
       </c>
       <c r="K207" t="str">
-        <v>₹35L - ₹52L PA + ESOPs</v>
+        <v>₹45L - ₹65L PA + ESOPs</v>
       </c>
       <c r="L207" t="str">
-        <v>https://careers.cred.club/</v>
+        <v>https://www.zomato.com/careers</v>
       </c>
       <c r="M207">
-        <v>200</v>
+        <v>503</v>
       </c>
       <c r="N207" t="str">
-        <v>ACTIVE / 100% VALID</v>
+        <v>BROKEN / 404</v>
       </c>
       <c r="O207" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P207" t="str">
-        <v>1d ago</v>
+        <v>Today</v>
       </c>
       <c r="Q207" t="str">
         <v>Yes</v>
       </c>
       <c r="R207" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S207">
-        <v>76</v>
+        <v>95</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>job-1e98cdb6</v>
+        <v>job-23756e58</v>
       </c>
       <c r="B208" t="str">
-        <v>Product Lead - Merchant QR, Soundbox &amp; Offline Payments Rails</v>
+        <v>Associate Product Manager (APM) - Social Commerce &amp; Creator Tools</v>
       </c>
       <c r="C208" t="str">
-        <v>PhonePe</v>
+        <v>Meesho</v>
       </c>
       <c r="D208" t="str">
-        <v>Instahyre</v>
+        <v>Naukri</v>
       </c>
       <c r="E208" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Associate Product Manager</v>
       </c>
       <c r="F208" t="str">
-        <v>7-11 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="G208" t="str">
-        <v>8+ yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H208" t="str">
         <v>Bengaluru, Karnataka</v>
@@ -12833,13 +12833,13 @@
         <v>Bengaluru</v>
       </c>
       <c r="J208" t="str">
-        <v>On-site</v>
+        <v>Hybrid</v>
       </c>
       <c r="K208" t="str">
-        <v>₹65L - ₹90L PA + ESOPs</v>
+        <v>₹18L - ₹25L PA + ESOPs</v>
       </c>
       <c r="L208" t="str">
-        <v>https://www.phonepe.com/careers/</v>
+        <v>https://www.meesho.io/jobs</v>
       </c>
       <c r="M208">
         <v>200</v>
@@ -12848,10 +12848,10 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O208" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P208" t="str">
-        <v>1d ago</v>
+        <v>Today</v>
       </c>
       <c r="Q208" t="str">
         <v>Yes</v>
@@ -12860,24 +12860,24 @@
         <v>Yes</v>
       </c>
       <c r="S208">
-        <v>125</v>
+        <v>65</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>job-6ee4d4a9</v>
+        <v>job-6900691e</v>
       </c>
       <c r="B209" t="str">
-        <v>Product Manager - Supply Chain Forecasting &amp; Dynamic Pricing</v>
+        <v>Product Owner - Core Banking &amp; Credit Line Engine</v>
       </c>
       <c r="C209" t="str">
-        <v>Flipkart</v>
+        <v>CRED</v>
       </c>
       <c r="D209" t="str">
-        <v>IIMJobs</v>
+        <v>Instahyre</v>
       </c>
       <c r="E209" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F209" t="str">
         <v>3-6 yrs</v>
@@ -12892,13 +12892,13 @@
         <v>Bengaluru</v>
       </c>
       <c r="J209" t="str">
-        <v>Hybrid</v>
+        <v>On-site</v>
       </c>
       <c r="K209" t="str">
-        <v>₹32L - ₹48L PA + ESOPs</v>
+        <v>₹35L - ₹52L PA + ESOPs</v>
       </c>
       <c r="L209" t="str">
-        <v>https://www.flipkartcareers.com/</v>
+        <v>https://careers.cred.club/</v>
       </c>
       <c r="M209">
         <v>200</v>
@@ -12907,24 +12907,142 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O209" t="str">
-        <v>2026-09-21</v>
+        <v>2026-09-22</v>
       </c>
       <c r="P209" t="str">
         <v>1d ago</v>
       </c>
       <c r="Q209" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R209" t="str">
         <v>No</v>
       </c>
       <c r="S209">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>job-1e98cdb6</v>
+      </c>
+      <c r="B210" t="str">
+        <v>Product Lead - Merchant QR, Soundbox &amp; Offline Payments Rails</v>
+      </c>
+      <c r="C210" t="str">
+        <v>PhonePe</v>
+      </c>
+      <c r="D210" t="str">
+        <v>Instahyre</v>
+      </c>
+      <c r="E210" t="str">
+        <v>AI &amp; Growth PM</v>
+      </c>
+      <c r="F210" t="str">
+        <v>7-11 yrs</v>
+      </c>
+      <c r="G210" t="str">
+        <v>8+ yrs</v>
+      </c>
+      <c r="H210" t="str">
+        <v>Bengaluru, Karnataka</v>
+      </c>
+      <c r="I210" t="str">
+        <v>Bengaluru</v>
+      </c>
+      <c r="J210" t="str">
+        <v>On-site</v>
+      </c>
+      <c r="K210" t="str">
+        <v>₹65L - ₹90L PA + ESOPs</v>
+      </c>
+      <c r="L210" t="str">
+        <v>https://www.phonepe.com/careers/</v>
+      </c>
+      <c r="M210">
+        <v>200</v>
+      </c>
+      <c r="N210" t="str">
+        <v>ACTIVE / 100% VALID</v>
+      </c>
+      <c r="O210" t="str">
+        <v>2026-09-22</v>
+      </c>
+      <c r="P210" t="str">
+        <v>1d ago</v>
+      </c>
+      <c r="Q210" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="R210" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="S210">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>job-6ee4d4a9</v>
+      </c>
+      <c r="B211" t="str">
+        <v>Product Manager - Supply Chain Forecasting &amp; Dynamic Pricing</v>
+      </c>
+      <c r="C211" t="str">
+        <v>Flipkart</v>
+      </c>
+      <c r="D211" t="str">
+        <v>IIMJobs</v>
+      </c>
+      <c r="E211" t="str">
+        <v>AI &amp; Growth PM</v>
+      </c>
+      <c r="F211" t="str">
+        <v>3-6 yrs</v>
+      </c>
+      <c r="G211" t="str">
+        <v>2-5 yrs</v>
+      </c>
+      <c r="H211" t="str">
+        <v>Bengaluru, Karnataka</v>
+      </c>
+      <c r="I211" t="str">
+        <v>Bengaluru</v>
+      </c>
+      <c r="J211" t="str">
+        <v>Hybrid</v>
+      </c>
+      <c r="K211" t="str">
+        <v>₹32L - ₹48L PA + ESOPs</v>
+      </c>
+      <c r="L211" t="str">
+        <v>https://www.flipkartcareers.com/</v>
+      </c>
+      <c r="M211">
+        <v>200</v>
+      </c>
+      <c r="N211" t="str">
+        <v>ACTIVE / 100% VALID</v>
+      </c>
+      <c r="O211" t="str">
+        <v>2026-09-22</v>
+      </c>
+      <c r="P211" t="str">
+        <v>1d ago</v>
+      </c>
+      <c r="Q211" t="str">
+        <v>No</v>
+      </c>
+      <c r="R211" t="str">
+        <v>No</v>
+      </c>
+      <c r="S211">
         <v>82</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S209"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S211"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -12988,10 +13106,10 @@
 3. Confirm fetch('/data/jobs.json') returns 200 OK</v>
       </c>
       <c r="F2" t="str">
-        <v>Returns array of 208 verified PM jobs</v>
+        <v>Returns array of 210 verified PM jobs</v>
       </c>
       <c r="G2" t="str">
-        <v>Successfully fetched 208 PM jobs without errors</v>
+        <v>Successfully fetched 210 PM jobs without errors</v>
       </c>
       <c r="H2" t="str">
         <v>PASS</v>
@@ -13070,10 +13188,10 @@
 2. Compare with rawJobs.length</v>
       </c>
       <c r="F5" t="str">
-        <v>Displays exactly 208</v>
+        <v>Displays exactly 210</v>
       </c>
       <c r="G5" t="str">
-        <v>Displays 208 active roles accurately</v>
+        <v>Displays 210 active roles accurately</v>
       </c>
       <c r="H5" t="str">
         <v>PASS</v>
@@ -13097,10 +13215,10 @@
 2. Count jobs posted today / marked Today</v>
       </c>
       <c r="F6" t="str">
-        <v>Displays +205</v>
+        <v>Displays +207</v>
       </c>
       <c r="G6" t="str">
-        <v>Displays +205 new opportunities tracked</v>
+        <v>Displays +207 new opportunities tracked</v>
       </c>
       <c r="H6" t="str">
         <v>PASS</v>
@@ -13124,10 +13242,10 @@
 2. Compute (remoteCount / totalJobs) * 100</v>
       </c>
       <c r="F7" t="str">
-        <v>Displays 64 (31%)</v>
+        <v>Displays 64 (30%)</v>
       </c>
       <c r="G7" t="str">
-        <v>Calculates 64 (31%) flexible roles accurately</v>
+        <v>Calculates 64 (30%) flexible roles accurately</v>
       </c>
       <c r="H7" t="str">
         <v>PASS</v>
@@ -13151,10 +13269,10 @@
 2. Check source counts</v>
       </c>
       <c r="F8" t="str">
-        <v>Displays LinkedIn with 105 roles</v>
+        <v>Displays LinkedIn with 109 roles</v>
       </c>
       <c r="G8" t="str">
-        <v>Displays LinkedIn (105 aggregated roles)</v>
+        <v>Displays LinkedIn (109 aggregated roles)</v>
       </c>
       <c r="H8" t="str">
         <v>PASS</v>
@@ -13676,7 +13794,7 @@
         <v>Open http://localhost:5173 in browser</v>
       </c>
       <c r="D2" t="str">
-        <v>Page loads instantly with Forest Green dark theme and 208 PM jobs</v>
+        <v>Page loads instantly with Forest Green dark theme and 210 PM jobs</v>
       </c>
       <c r="E2" t="str">
         <v>[ ] Completed</v>

--- a/GreenPath_PM_Jobs_Test_Report.xlsx
+++ b/GreenPath_PM_Jobs_Test_Report.xlsx
@@ -428,7 +428,7 @@
         <v>Test Execution Date</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-09-23T01:56:49.075Z</v>
+        <v>2026-09-24T01:45:58.098Z</v>
       </c>
     </row>
     <row r="4">
@@ -436,7 +436,7 @@
         <v>Total Jobs in Feed</v>
       </c>
       <c r="B4">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="5">
@@ -444,7 +444,7 @@
         <v>Total URLs Tested</v>
       </c>
       <c r="B5">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="6">
@@ -452,7 +452,7 @@
         <v>Active / Valid Direct ATS URLs</v>
       </c>
       <c r="B6">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="7">
@@ -524,7 +524,7 @@
         <v>Cities Supported</v>
       </c>
       <c r="B15" t="str">
-        <v>San Francisco, Toronto, Dublin, N/A, New York, Remote, USA, Seattle, London, United States, Paris, Menlo Park, Hybrid, In-Office, Canada, Spain, Switzerland, Israel, Greece, Riyadh, Vancouver, Pittsburgh, Beijing, Bengaluru, Vienna, North America, Stockholm, Washington, Mumbai, Gurgaon</v>
+        <v>San Francisco, Toronto, Dublin, N/A, New York, Remote, USA, Seattle, London, United States, Paris, Menlo Park, Hybrid, In-Office, Canada, Spain, Portugal, Switzerland, Doha, Pittsburgh, Beijing, Bengaluru, Vienna, North America, Stockholm, Washington, Mumbai, Gurgaon</v>
       </c>
     </row>
     <row r="16">
@@ -532,7 +532,7 @@
         <v>Remote / Hybrid Roles</v>
       </c>
       <c r="B16" t="str">
-        <v>64 (30%)</v>
+        <v>63 (30%)</v>
       </c>
     </row>
     <row r="17">
@@ -540,7 +540,7 @@
         <v>Jobs Added Today</v>
       </c>
       <c r="B17" t="str">
-        <v>+207</v>
+        <v>+208</v>
       </c>
     </row>
     <row r="18">
@@ -568,7 +568,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S211"/>
+  <dimension ref="A1:S212"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="38.83203125" customWidth="1"/>
@@ -694,7 +694,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O2" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P2" t="str">
         <v>Today</v>
@@ -706,7 +706,7 @@
         <v>No</v>
       </c>
       <c r="S2">
-        <v>81</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
@@ -753,7 +753,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O3" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P3" t="str">
         <v>Today</v>
@@ -762,7 +762,7 @@
         <v>No</v>
       </c>
       <c r="R3" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S3">
         <v>59</v>
@@ -812,7 +812,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O4" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P4" t="str">
         <v>Today</v>
@@ -824,7 +824,7 @@
         <v>No</v>
       </c>
       <c r="S4">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5">
@@ -871,19 +871,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O5" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P5" t="str">
         <v>Today</v>
       </c>
       <c r="Q5" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R5" t="str">
         <v>No</v>
       </c>
       <c r="S5">
-        <v>36</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6">
@@ -930,7 +930,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O6" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P6" t="str">
         <v>Today</v>
@@ -939,10 +939,10 @@
         <v>No</v>
       </c>
       <c r="R6" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S6">
-        <v>25</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7">
@@ -989,19 +989,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O7" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P7" t="str">
         <v>Today</v>
       </c>
       <c r="Q7" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R7" t="str">
         <v>No</v>
       </c>
       <c r="S7">
-        <v>45</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8">
@@ -1048,7 +1048,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O8" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P8" t="str">
         <v>Today</v>
@@ -1057,10 +1057,10 @@
         <v>No</v>
       </c>
       <c r="R8" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S8">
-        <v>31</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9">
@@ -1107,7 +1107,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O9" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P9" t="str">
         <v>Today</v>
@@ -1119,7 +1119,7 @@
         <v>No</v>
       </c>
       <c r="S9">
-        <v>48</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10">
@@ -1166,19 +1166,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O10" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P10" t="str">
         <v>Today</v>
       </c>
       <c r="Q10" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R10" t="str">
         <v>No</v>
       </c>
       <c r="S10">
-        <v>47</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11">
@@ -1225,7 +1225,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O11" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P11" t="str">
         <v>Today</v>
@@ -1237,7 +1237,7 @@
         <v>No</v>
       </c>
       <c r="S11">
-        <v>84</v>
+        <v>66</v>
       </c>
     </row>
     <row r="12">
@@ -1284,7 +1284,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O12" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P12" t="str">
         <v>Today</v>
@@ -1293,10 +1293,10 @@
         <v>No</v>
       </c>
       <c r="R12" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S12">
-        <v>33</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13">
@@ -1343,7 +1343,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O13" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P13" t="str">
         <v>Today</v>
@@ -1352,10 +1352,10 @@
         <v>Yes</v>
       </c>
       <c r="R13" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S13">
-        <v>43</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14">
@@ -1402,19 +1402,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O14" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P14" t="str">
         <v>Today</v>
       </c>
       <c r="Q14" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R14" t="str">
         <v>Yes</v>
       </c>
       <c r="S14">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15">
@@ -1461,7 +1461,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O15" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P15" t="str">
         <v>Today</v>
@@ -1473,7 +1473,7 @@
         <v>No</v>
       </c>
       <c r="S15">
-        <v>79</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16">
@@ -1520,19 +1520,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O16" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P16" t="str">
         <v>Today</v>
       </c>
       <c r="Q16" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R16" t="str">
         <v>No</v>
       </c>
       <c r="S16">
-        <v>47</v>
+        <v>78</v>
       </c>
     </row>
     <row r="17">
@@ -1579,19 +1579,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O17" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P17" t="str">
         <v>Today</v>
       </c>
       <c r="Q17" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R17" t="str">
         <v>No</v>
       </c>
       <c r="S17">
-        <v>83</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18">
@@ -1638,7 +1638,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O18" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P18" t="str">
         <v>Today</v>
@@ -1647,10 +1647,10 @@
         <v>Yes</v>
       </c>
       <c r="R18" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S18">
-        <v>31</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19">
@@ -1697,19 +1697,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O19" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P19" t="str">
         <v>Today</v>
       </c>
       <c r="Q19" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R19" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S19">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20">
@@ -1756,7 +1756,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O20" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P20" t="str">
         <v>Today</v>
@@ -1765,18 +1765,18 @@
         <v>No</v>
       </c>
       <c r="R20" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S20">
-        <v>39</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>job-74abb1d3</v>
+        <v>job-44d57281</v>
       </c>
       <c r="B21" t="str">
-        <v>Staff Product Manager, AI</v>
+        <v>Staff Product Manager, Agentic Commerce</v>
       </c>
       <c r="C21" t="str">
         <v>Stripe</v>
@@ -1794,7 +1794,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H21" t="str">
-        <v>San Francisco, Seattle, New York, Chicago</v>
+        <v>Seattle, San Francisco, New York</v>
       </c>
       <c r="I21" t="str">
         <v>San Francisco</v>
@@ -1806,7 +1806,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L21" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/7655023</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/8226893</v>
       </c>
       <c r="M21">
         <v>200</v>
@@ -1815,27 +1815,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O21" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P21" t="str">
         <v>Today</v>
       </c>
       <c r="Q21" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R21" t="str">
         <v>No</v>
       </c>
       <c r="S21">
-        <v>48</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>job-53d16ec0</v>
+        <v>job-74abb1d3</v>
       </c>
       <c r="B22" t="str">
-        <v>Staff Product Manager, Billing</v>
+        <v>Staff Product Manager, AI</v>
       </c>
       <c r="C22" t="str">
         <v>Stripe</v>
@@ -1853,19 +1853,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H22" t="str">
-        <v>SF, NY, SEA, Remote-US</v>
+        <v>San Francisco, Seattle, New York, Chicago</v>
       </c>
       <c r="I22" t="str">
         <v>San Francisco</v>
       </c>
       <c r="J22" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K22" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L22" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/7983725</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/7655023</v>
       </c>
       <c r="M22">
         <v>200</v>
@@ -1874,27 +1874,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O22" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P22" t="str">
         <v>Today</v>
       </c>
       <c r="Q22" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R22" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S22">
-        <v>42</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>job-2cc707b1</v>
+        <v>job-53d16ec0</v>
       </c>
       <c r="B23" t="str">
-        <v>Staff Product Manager, Connect</v>
+        <v>Staff Product Manager, Billing</v>
       </c>
       <c r="C23" t="str">
         <v>Stripe</v>
@@ -1912,19 +1912,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H23" t="str">
-        <v>N/A</v>
+        <v>SF, NY, SEA, Remote-US</v>
       </c>
       <c r="I23" t="str">
-        <v>N/A</v>
+        <v>San Francisco</v>
       </c>
       <c r="J23" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K23" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L23" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/8065034</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/7983725</v>
       </c>
       <c r="M23">
         <v>200</v>
@@ -1933,13 +1933,13 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O23" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P23" t="str">
         <v>Today</v>
       </c>
       <c r="Q23" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R23" t="str">
         <v>Yes</v>
@@ -1950,10 +1950,10 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>job-1696793b</v>
+        <v>job-2cc707b1</v>
       </c>
       <c r="B24" t="str">
-        <v>Staff Product Manager, Issuing</v>
+        <v>Staff Product Manager, Connect</v>
       </c>
       <c r="C24" t="str">
         <v>Stripe</v>
@@ -1971,10 +1971,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H24" t="str">
-        <v>London</v>
+        <v>N/A</v>
       </c>
       <c r="I24" t="str">
-        <v>London</v>
+        <v>N/A</v>
       </c>
       <c r="J24" t="str">
         <v>On-site</v>
@@ -1983,7 +1983,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L24" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/8043083</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/8065034</v>
       </c>
       <c r="M24">
         <v>200</v>
@@ -1992,27 +1992,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O24" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P24" t="str">
         <v>Today</v>
       </c>
       <c r="Q24" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R24" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S24">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>job-140cf629</v>
+        <v>job-1696793b</v>
       </c>
       <c r="B25" t="str">
-        <v>Staff Product Manager, Local Payment Methods Growth</v>
+        <v>Staff Product Manager, Issuing</v>
       </c>
       <c r="C25" t="str">
         <v>Stripe</v>
@@ -2042,7 +2042,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L25" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/8142649</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/8043083</v>
       </c>
       <c r="M25">
         <v>200</v>
@@ -2051,27 +2051,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O25" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P25" t="str">
         <v>Today</v>
       </c>
       <c r="Q25" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R25" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S25">
-        <v>72</v>
+        <v>56</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>job-0b0dcd73</v>
+        <v>job-140cf629</v>
       </c>
       <c r="B26" t="str">
-        <v>Staff Product Manager, ML Foundations and GenAI</v>
+        <v>Staff Product Manager, Local Payment Methods Growth</v>
       </c>
       <c r="C26" t="str">
         <v>Stripe</v>
@@ -2089,19 +2089,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H26" t="str">
-        <v>Seattle, San Francisco, New York, US - Remote</v>
+        <v>London</v>
       </c>
       <c r="I26" t="str">
-        <v>San Francisco</v>
+        <v>London</v>
       </c>
       <c r="J26" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K26" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L26" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/7517535</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/8142649</v>
       </c>
       <c r="M26">
         <v>200</v>
@@ -2110,7 +2110,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O26" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P26" t="str">
         <v>Today</v>
@@ -2122,15 +2122,15 @@
         <v>No</v>
       </c>
       <c r="S26">
-        <v>57</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>job-01c7686e</v>
+        <v>job-0b0dcd73</v>
       </c>
       <c r="B27" t="str">
-        <v>Staff Product Manager, Payments</v>
+        <v>Staff Product Manager, ML Foundations and GenAI</v>
       </c>
       <c r="C27" t="str">
         <v>Stripe</v>
@@ -2148,7 +2148,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H27" t="str">
-        <v>SF, SEA, NYC, Remote</v>
+        <v>Seattle, San Francisco, New York, US - Remote</v>
       </c>
       <c r="I27" t="str">
         <v>San Francisco</v>
@@ -2160,7 +2160,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L27" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/7819059</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/7517535</v>
       </c>
       <c r="M27">
         <v>200</v>
@@ -2169,27 +2169,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O27" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P27" t="str">
         <v>Today</v>
       </c>
       <c r="Q27" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R27" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S27">
-        <v>71</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>job-0bc700c9</v>
+        <v>job-01c7686e</v>
       </c>
       <c r="B28" t="str">
-        <v>Staff Product Manager, Payments Intelligence</v>
+        <v>Staff Product Manager, Payments</v>
       </c>
       <c r="C28" t="str">
         <v>Stripe</v>
@@ -2207,7 +2207,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H28" t="str">
-        <v>NYC, SF, Seattle, US - Remote</v>
+        <v>SF, SEA, NYC, Remote</v>
       </c>
       <c r="I28" t="str">
         <v>San Francisco</v>
@@ -2219,7 +2219,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L28" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/8209996</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/7819059</v>
       </c>
       <c r="M28">
         <v>200</v>
@@ -2228,27 +2228,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O28" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P28" t="str">
         <v>Today</v>
       </c>
       <c r="Q28" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R28" t="str">
         <v>Yes</v>
       </c>
       <c r="S28">
-        <v>49</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>job-5dedbaad</v>
+        <v>job-0bc700c9</v>
       </c>
       <c r="B29" t="str">
-        <v>Staff Product Manager, Sail Core</v>
+        <v>Staff Product Manager, Payments Intelligence</v>
       </c>
       <c r="C29" t="str">
         <v>Stripe</v>
@@ -2266,10 +2266,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H29" t="str">
-        <v>New York, US - Remote, Toronto</v>
+        <v>NYC, SF, Seattle, US - Remote</v>
       </c>
       <c r="I29" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J29" t="str">
         <v>Remote</v>
@@ -2278,7 +2278,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L29" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/7913698</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/8209996</v>
       </c>
       <c r="M29">
         <v>200</v>
@@ -2287,27 +2287,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O29" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P29" t="str">
         <v>Today</v>
       </c>
       <c r="Q29" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R29" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S29">
-        <v>68</v>
+        <v>42</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>job-6ad386a3</v>
+        <v>job-5dedbaad</v>
       </c>
       <c r="B30" t="str">
-        <v>Staff Product Manager, Stripe Tax</v>
+        <v>Staff Product Manager, Sail Core</v>
       </c>
       <c r="C30" t="str">
         <v>Stripe</v>
@@ -2325,19 +2325,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H30" t="str">
-        <v>Dublin, Ireland</v>
+        <v>New York, US - Remote, Toronto</v>
       </c>
       <c r="I30" t="str">
-        <v>Dublin</v>
+        <v>New York</v>
       </c>
       <c r="J30" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K30" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L30" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/8124304</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/7913698</v>
       </c>
       <c r="M30">
         <v>200</v>
@@ -2346,7 +2346,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O30" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P30" t="str">
         <v>Today</v>
@@ -2358,36 +2358,36 @@
         <v>No</v>
       </c>
       <c r="S30">
-        <v>85</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>job-0349189e</v>
+        <v>job-6ad386a3</v>
       </c>
       <c r="B31" t="str">
-        <v>Product Manager, Identity</v>
+        <v>Staff Product Manager, Stripe Tax</v>
       </c>
       <c r="C31" t="str">
-        <v>Airbnb</v>
+        <v>Stripe</v>
       </c>
       <c r="D31" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E31" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F31" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G31" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H31" t="str">
-        <v>United States</v>
+        <v>Dublin, Ireland</v>
       </c>
       <c r="I31" t="str">
-        <v>United States</v>
+        <v>Dublin</v>
       </c>
       <c r="J31" t="str">
         <v>On-site</v>
@@ -2396,7 +2396,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L31" t="str">
-        <v>https://boards.greenhouse.io/airbnb/jobs/8055637</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/8124304</v>
       </c>
       <c r="M31">
         <v>200</v>
@@ -2405,27 +2405,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O31" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P31" t="str">
         <v>Today</v>
       </c>
       <c r="Q31" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R31" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S31">
-        <v>77</v>
+        <v>90</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>job-7eca2194</v>
+        <v>job-0349189e</v>
       </c>
       <c r="B32" t="str">
-        <v>Product Manager, Pricing</v>
+        <v>Product Manager, Identity</v>
       </c>
       <c r="C32" t="str">
         <v>Airbnb</v>
@@ -2455,7 +2455,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L32" t="str">
-        <v>https://boards.greenhouse.io/airbnb/jobs/8096359</v>
+        <v>https://boards.greenhouse.io/airbnb/jobs/8055637</v>
       </c>
       <c r="M32">
         <v>200</v>
@@ -2464,7 +2464,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O32" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P32" t="str">
         <v>Today</v>
@@ -2473,18 +2473,18 @@
         <v>No</v>
       </c>
       <c r="R32" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S32">
-        <v>91</v>
+        <v>75</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>job-4efc96ba</v>
+        <v>job-7eca2194</v>
       </c>
       <c r="B33" t="str">
-        <v>Product Manager, Relevance and Personalization</v>
+        <v>Product Manager, Pricing</v>
       </c>
       <c r="C33" t="str">
         <v>Airbnb</v>
@@ -2502,10 +2502,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H33" t="str">
-        <v>San Francisco, United States</v>
+        <v>United States</v>
       </c>
       <c r="I33" t="str">
-        <v>San Francisco</v>
+        <v>United States</v>
       </c>
       <c r="J33" t="str">
         <v>On-site</v>
@@ -2514,7 +2514,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L33" t="str">
-        <v>https://boards.greenhouse.io/airbnb/jobs/7905365</v>
+        <v>https://boards.greenhouse.io/airbnb/jobs/8096359</v>
       </c>
       <c r="M33">
         <v>200</v>
@@ -2523,19 +2523,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O33" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P33" t="str">
         <v>Today</v>
       </c>
       <c r="Q33" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R33" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S33">
-        <v>78</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34">
@@ -2582,19 +2582,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O34" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P34" t="str">
         <v>Today</v>
       </c>
       <c r="Q34" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R34" t="str">
         <v>Yes</v>
       </c>
       <c r="S34">
-        <v>25</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35">
@@ -2641,7 +2641,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O35" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P35" t="str">
         <v>Today</v>
@@ -2650,10 +2650,10 @@
         <v>Yes</v>
       </c>
       <c r="R35" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S35">
-        <v>42</v>
+        <v>70</v>
       </c>
     </row>
     <row r="36">
@@ -2700,7 +2700,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O36" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P36" t="str">
         <v>Today</v>
@@ -2709,10 +2709,10 @@
         <v>Yes</v>
       </c>
       <c r="R36" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S36">
-        <v>84</v>
+        <v>46</v>
       </c>
     </row>
     <row r="37">
@@ -2759,19 +2759,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O37" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P37" t="str">
         <v>Today</v>
       </c>
       <c r="Q37" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R37" t="str">
         <v>No</v>
       </c>
       <c r="S37">
-        <v>38</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38">
@@ -2818,7 +2818,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O38" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P38" t="str">
         <v>Today</v>
@@ -2830,7 +2830,7 @@
         <v>No</v>
       </c>
       <c r="S38">
-        <v>58</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39">
@@ -2877,19 +2877,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O39" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P39" t="str">
         <v>Today</v>
       </c>
       <c r="Q39" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R39" t="str">
         <v>No</v>
       </c>
       <c r="S39">
-        <v>77</v>
+        <v>63</v>
       </c>
     </row>
     <row r="40">
@@ -2915,10 +2915,10 @@
         <v>0-2 yrs</v>
       </c>
       <c r="H40" t="str">
-        <v>Paris, France</v>
+        <v>New York, New York, USA</v>
       </c>
       <c r="I40" t="str">
-        <v>Paris</v>
+        <v>New York</v>
       </c>
       <c r="J40" t="str">
         <v>On-site</v>
@@ -2927,7 +2927,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L40" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/8143729</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/8108241</v>
       </c>
       <c r="M40">
         <v>200</v>
@@ -2936,7 +2936,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O40" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P40" t="str">
         <v>Today</v>
@@ -2948,7 +2948,7 @@
         <v>No</v>
       </c>
       <c r="S40">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="41">
@@ -2974,10 +2974,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H41" t="str">
-        <v>Paris, France</v>
+        <v>Boston, Massachusetts, USA; New York, New York, USA</v>
       </c>
       <c r="I41" t="str">
-        <v>Paris</v>
+        <v>New York</v>
       </c>
       <c r="J41" t="str">
         <v>On-site</v>
@@ -2986,7 +2986,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L41" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/8012549</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/7982288</v>
       </c>
       <c r="M41">
         <v>200</v>
@@ -2995,7 +2995,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O41" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P41" t="str">
         <v>Today</v>
@@ -3007,15 +3007,15 @@
         <v>No</v>
       </c>
       <c r="S41">
-        <v>65</v>
+        <v>54</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>job-0d57ea9a</v>
+        <v>job-156d798b</v>
       </c>
       <c r="B42" t="str">
-        <v>Product Manager II - SQL &amp; Sheets Growth</v>
+        <v>Product Manager ll – Code Intelligence</v>
       </c>
       <c r="C42" t="str">
         <v>Datadog</v>
@@ -3045,7 +3045,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L42" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/8119973</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/8197852</v>
       </c>
       <c r="M42">
         <v>200</v>
@@ -3054,27 +3054,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O42" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P42" t="str">
         <v>Today</v>
       </c>
       <c r="Q42" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R42" t="str">
         <v>No</v>
       </c>
       <c r="S42">
-        <v>86</v>
+        <v>57</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>job-156d798b</v>
+        <v>job-19d43a03</v>
       </c>
       <c r="B43" t="str">
-        <v>Product Manager ll – Code Intelligence</v>
+        <v>Senior Director, Product Management - Platforms</v>
       </c>
       <c r="C43" t="str">
         <v>Datadog</v>
@@ -3083,13 +3083,13 @@
         <v>Wellfound</v>
       </c>
       <c r="E43" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F43" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G43" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H43" t="str">
         <v>New York, New York, USA</v>
@@ -3104,7 +3104,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L43" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/8197852</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/7583609</v>
       </c>
       <c r="M43">
         <v>200</v>
@@ -3113,7 +3113,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O43" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P43" t="str">
         <v>Today</v>
@@ -3122,18 +3122,18 @@
         <v>No</v>
       </c>
       <c r="R43" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S43">
-        <v>41</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>job-19d43a03</v>
+        <v>job-369e4329</v>
       </c>
       <c r="B44" t="str">
-        <v>Senior Director, Product Management - Platforms</v>
+        <v>Senior Platform Product Manager - AI SDLC Trusted Throughput</v>
       </c>
       <c r="C44" t="str">
         <v>Datadog</v>
@@ -3163,7 +3163,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L44" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/7583609</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/7947683</v>
       </c>
       <c r="M44">
         <v>200</v>
@@ -3172,7 +3172,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O44" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P44" t="str">
         <v>Today</v>
@@ -3181,18 +3181,18 @@
         <v>No</v>
       </c>
       <c r="R44" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S44">
-        <v>63</v>
+        <v>43</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>job-369e4329</v>
+        <v>job-48a6badb</v>
       </c>
       <c r="B45" t="str">
-        <v>Senior Platform Product Manager - AI SDLC Trusted Throughput</v>
+        <v>Senior Product Manager - Application Performance Monitoring</v>
       </c>
       <c r="C45" t="str">
         <v>Datadog</v>
@@ -3210,10 +3210,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H45" t="str">
-        <v>New York, New York, USA</v>
+        <v>Paris, France</v>
       </c>
       <c r="I45" t="str">
-        <v>New York</v>
+        <v>Paris</v>
       </c>
       <c r="J45" t="str">
         <v>On-site</v>
@@ -3222,7 +3222,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L45" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/7947683</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/8028422</v>
       </c>
       <c r="M45">
         <v>200</v>
@@ -3231,7 +3231,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O45" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P45" t="str">
         <v>Today</v>
@@ -3240,18 +3240,18 @@
         <v>Yes</v>
       </c>
       <c r="R45" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S45">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>job-48a6badb</v>
+        <v>job-2276f1c7</v>
       </c>
       <c r="B46" t="str">
-        <v>Senior Product Manager - Application Performance Monitoring</v>
+        <v>Senior Product Manager - Bits Agent Builder</v>
       </c>
       <c r="C46" t="str">
         <v>Datadog</v>
@@ -3269,10 +3269,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H46" t="str">
-        <v>Paris, France</v>
+        <v>New York, New York, USA</v>
       </c>
       <c r="I46" t="str">
-        <v>Paris</v>
+        <v>New York</v>
       </c>
       <c r="J46" t="str">
         <v>On-site</v>
@@ -3281,7 +3281,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L46" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/8028422</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/8092004</v>
       </c>
       <c r="M46">
         <v>200</v>
@@ -3290,27 +3290,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O46" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P46" t="str">
         <v>Today</v>
       </c>
       <c r="Q46" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R46" t="str">
         <v>No</v>
       </c>
       <c r="S46">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>job-2276f1c7</v>
+        <v>job-32c2a2da</v>
       </c>
       <c r="B47" t="str">
-        <v>Senior Product Manager - Bits Agent Builder</v>
+        <v>Senior Product Manager - Business Intelligence</v>
       </c>
       <c r="C47" t="str">
         <v>Datadog</v>
@@ -3340,7 +3340,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L47" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/8092004</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/8119973</v>
       </c>
       <c r="M47">
         <v>200</v>
@@ -3349,7 +3349,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O47" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P47" t="str">
         <v>Today</v>
@@ -3361,7 +3361,7 @@
         <v>No</v>
       </c>
       <c r="S47">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="48">
@@ -3408,27 +3408,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O48" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P48" t="str">
         <v>Today</v>
       </c>
       <c r="Q48" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R48" t="str">
         <v>No</v>
       </c>
       <c r="S48">
-        <v>41</v>
+        <v>88</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>job-23a59139</v>
+        <v>job-317cfafc</v>
       </c>
       <c r="B49" t="str">
-        <v>Senior Product Manager - Fleet and Lifecycle Management</v>
+        <v>Senior Product Manager - Feature Flagging</v>
       </c>
       <c r="C49" t="str">
         <v>Datadog</v>
@@ -3446,7 +3446,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H49" t="str">
-        <v>Boston, Massachusetts, USA; New York, New York, USA</v>
+        <v>New York, New York, USA</v>
       </c>
       <c r="I49" t="str">
         <v>New York</v>
@@ -3458,7 +3458,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L49" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/8077142</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/8226275</v>
       </c>
       <c r="M49">
         <v>200</v>
@@ -3467,7 +3467,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O49" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P49" t="str">
         <v>Today</v>
@@ -3476,18 +3476,18 @@
         <v>Yes</v>
       </c>
       <c r="R49" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S49">
-        <v>78</v>
+        <v>43</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>job-74ef687b</v>
+        <v>job-23a59139</v>
       </c>
       <c r="B50" t="str">
-        <v>Senior Product Manager - Journey Monitoring</v>
+        <v>Senior Product Manager - Fleet and Lifecycle Management</v>
       </c>
       <c r="C50" t="str">
         <v>Datadog</v>
@@ -3505,7 +3505,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H50" t="str">
-        <v>New York, New York, USA</v>
+        <v>Boston, Massachusetts, USA; New York, New York, USA</v>
       </c>
       <c r="I50" t="str">
         <v>New York</v>
@@ -3517,7 +3517,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L50" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/8115033</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/8077142</v>
       </c>
       <c r="M50">
         <v>200</v>
@@ -3526,7 +3526,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O50" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P50" t="str">
         <v>Today</v>
@@ -3538,15 +3538,15 @@
         <v>No</v>
       </c>
       <c r="S50">
-        <v>43</v>
+        <v>94</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>job-538a4cea</v>
+        <v>job-74ef687b</v>
       </c>
       <c r="B51" t="str">
-        <v>Senior Product Manager - Network Path</v>
+        <v>Senior Product Manager - Journey Monitoring</v>
       </c>
       <c r="C51" t="str">
         <v>Datadog</v>
@@ -3576,7 +3576,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L51" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/7763117</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/8115033</v>
       </c>
       <c r="M51">
         <v>200</v>
@@ -3585,27 +3585,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O51" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P51" t="str">
         <v>Today</v>
       </c>
       <c r="Q51" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R51" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S51">
-        <v>49</v>
+        <v>65</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>job-1da3061b</v>
+        <v>job-538a4cea</v>
       </c>
       <c r="B52" t="str">
-        <v>Senior Product Manager - Observability Data Platform</v>
+        <v>Senior Product Manager - Network Path</v>
       </c>
       <c r="C52" t="str">
         <v>Datadog</v>
@@ -3635,7 +3635,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L52" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/8065192</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/7763117</v>
       </c>
       <c r="M52">
         <v>200</v>
@@ -3644,7 +3644,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O52" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P52" t="str">
         <v>Today</v>
@@ -3653,18 +3653,18 @@
         <v>No</v>
       </c>
       <c r="R52" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S52">
-        <v>78</v>
+        <v>71</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>job-5ef34fd7</v>
+        <v>job-1da3061b</v>
       </c>
       <c r="B53" t="str">
-        <v>Senior Staff GenAI Engineer - Application Performance Monitoring (APM)</v>
+        <v>Senior Product Manager - Observability Data Platform</v>
       </c>
       <c r="C53" t="str">
         <v>Datadog</v>
@@ -3673,13 +3673,13 @@
         <v>Wellfound</v>
       </c>
       <c r="E53" t="str">
-        <v>Associate Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F53" t="str">
-        <v>1-3 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G53" t="str">
-        <v>0-2 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H53" t="str">
         <v>New York, New York, USA</v>
@@ -3694,7 +3694,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L53" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/6960503</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/8065192</v>
       </c>
       <c r="M53">
         <v>200</v>
@@ -3703,7 +3703,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O53" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P53" t="str">
         <v>Today</v>
@@ -3712,18 +3712,18 @@
         <v>Yes</v>
       </c>
       <c r="R53" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S53">
-        <v>90</v>
+        <v>59</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>job-6f4d5443</v>
+        <v>job-5ef34fd7</v>
       </c>
       <c r="B54" t="str">
-        <v>Staff GenAI Engineer - Application Performance Monitoring (APM)</v>
+        <v>Senior Staff GenAI Engineer - Application Performance Monitoring (APM)</v>
       </c>
       <c r="C54" t="str">
         <v>Datadog</v>
@@ -3753,7 +3753,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L54" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/7974511</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/6960503</v>
       </c>
       <c r="M54">
         <v>200</v>
@@ -3762,13 +3762,13 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O54" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P54" t="str">
         <v>Today</v>
       </c>
       <c r="Q54" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R54" t="str">
         <v>No</v>
@@ -3779,10 +3779,10 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>job-74e794e5</v>
+        <v>job-6f4d5443</v>
       </c>
       <c r="B55" t="str">
-        <v>Staff Product Manager, Observability Data Platforms</v>
+        <v>Staff GenAI Engineer - Application Performance Monitoring (APM)</v>
       </c>
       <c r="C55" t="str">
         <v>Datadog</v>
@@ -3791,13 +3791,13 @@
         <v>Wellfound</v>
       </c>
       <c r="E55" t="str">
-        <v>Senior Product Manager</v>
+        <v>Associate Product Manager</v>
       </c>
       <c r="F55" t="str">
-        <v>5-8 yrs</v>
+        <v>1-3 yrs</v>
       </c>
       <c r="G55" t="str">
-        <v>5-8 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H55" t="str">
         <v>New York, New York, USA</v>
@@ -3812,7 +3812,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L55" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/8065187</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/7974511</v>
       </c>
       <c r="M55">
         <v>200</v>
@@ -3821,57 +3821,57 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O55" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P55" t="str">
         <v>Today</v>
       </c>
       <c r="Q55" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R55" t="str">
         <v>No</v>
       </c>
       <c r="S55">
-        <v>68</v>
+        <v>59</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>job-443f0280</v>
+        <v>job-74e794e5</v>
       </c>
       <c r="B56" t="str">
-        <v>Group Product Manager, Finance Technology</v>
+        <v>Staff Product Manager, Observability Data Platforms</v>
       </c>
       <c r="C56" t="str">
-        <v>Reddit</v>
+        <v>Datadog</v>
       </c>
       <c r="D56" t="str">
-        <v>Indeed</v>
+        <v>Wellfound</v>
       </c>
       <c r="E56" t="str">
-        <v>Product Lead / Director</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F56" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G56" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H56" t="str">
-        <v>Remote - United States</v>
+        <v>New York, New York, USA</v>
       </c>
       <c r="I56" t="str">
-        <v>Remote</v>
+        <v>New York</v>
       </c>
       <c r="J56" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K56" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L56" t="str">
-        <v>https://boards.greenhouse.io/reddit/jobs/8075185</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/8065187</v>
       </c>
       <c r="M56">
         <v>200</v>
@@ -3880,7 +3880,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O56" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P56" t="str">
         <v>Today</v>
@@ -3892,15 +3892,15 @@
         <v>No</v>
       </c>
       <c r="S56">
-        <v>64</v>
+        <v>88</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>job-7e666189</v>
+        <v>job-443f0280</v>
       </c>
       <c r="B57" t="str">
-        <v>Product Manager, Developer Ecosystem</v>
+        <v>Group Product Manager, Finance Technology</v>
       </c>
       <c r="C57" t="str">
         <v>Reddit</v>
@@ -3909,7 +3909,7 @@
         <v>Indeed</v>
       </c>
       <c r="E57" t="str">
-        <v>Product Manager</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F57" t="str">
         <v>3-6 yrs</v>
@@ -3930,7 +3930,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L57" t="str">
-        <v>https://boards.greenhouse.io/reddit/jobs/8088720</v>
+        <v>https://boards.greenhouse.io/reddit/jobs/8075185</v>
       </c>
       <c r="M57">
         <v>200</v>
@@ -3939,7 +3939,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O57" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P57" t="str">
         <v>Today</v>
@@ -3951,15 +3951,15 @@
         <v>Yes</v>
       </c>
       <c r="S57">
-        <v>88</v>
+        <v>28</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>job-66f21772</v>
+        <v>job-7e666189</v>
       </c>
       <c r="B58" t="str">
-        <v>Senior Product Manager, Ads -  Shopping Catalogs</v>
+        <v>Product Manager, Developer Ecosystem</v>
       </c>
       <c r="C58" t="str">
         <v>Reddit</v>
@@ -3968,13 +3968,13 @@
         <v>Indeed</v>
       </c>
       <c r="E58" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F58" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G58" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H58" t="str">
         <v>Remote - United States</v>
@@ -3989,7 +3989,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L58" t="str">
-        <v>https://boards.greenhouse.io/reddit/jobs/8120503</v>
+        <v>https://boards.greenhouse.io/reddit/jobs/8088720</v>
       </c>
       <c r="M58">
         <v>200</v>
@@ -3998,7 +3998,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O58" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P58" t="str">
         <v>Today</v>
@@ -4010,15 +4010,15 @@
         <v>No</v>
       </c>
       <c r="S58">
-        <v>35</v>
+        <v>51</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>job-25042936</v>
+        <v>job-66f21772</v>
       </c>
       <c r="B59" t="str">
-        <v>Senior Product Manager, Go-To-Market Systems</v>
+        <v>Senior Product Manager, Ads -  Shopping Catalogs</v>
       </c>
       <c r="C59" t="str">
         <v>Reddit</v>
@@ -4036,19 +4036,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H59" t="str">
-        <v>Chicago, IL; Los Angeles, CA; New York City, NY; San Francisco, CA</v>
+        <v>Remote - United States</v>
       </c>
       <c r="I59" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J59" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K59" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L59" t="str">
-        <v>https://boards.greenhouse.io/reddit/jobs/8212175</v>
+        <v>https://boards.greenhouse.io/reddit/jobs/8120503</v>
       </c>
       <c r="M59">
         <v>200</v>
@@ -4057,7 +4057,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O59" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P59" t="str">
         <v>Today</v>
@@ -4069,15 +4069,15 @@
         <v>No</v>
       </c>
       <c r="S59">
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>job-4b069687</v>
+        <v>job-25042936</v>
       </c>
       <c r="B60" t="str">
-        <v>Staff Product Manager, Ads Formats</v>
+        <v>Senior Product Manager, Go-To-Market Systems</v>
       </c>
       <c r="C60" t="str">
         <v>Reddit</v>
@@ -4095,19 +4095,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H60" t="str">
-        <v>Remote - United States</v>
+        <v>Chicago, IL; Los Angeles, CA; New York City, NY; San Francisco, CA</v>
       </c>
       <c r="I60" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J60" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K60" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L60" t="str">
-        <v>https://boards.greenhouse.io/reddit/jobs/8167412</v>
+        <v>https://boards.greenhouse.io/reddit/jobs/8212175</v>
       </c>
       <c r="M60">
         <v>200</v>
@@ -4116,27 +4116,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O60" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P60" t="str">
         <v>Today</v>
       </c>
       <c r="Q60" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R60" t="str">
         <v>No</v>
       </c>
       <c r="S60">
-        <v>75</v>
+        <v>80</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>job-0638f83c</v>
+        <v>job-4b069687</v>
       </c>
       <c r="B61" t="str">
-        <v>Staff Product Manager, Ads Safety (Ads Review)</v>
+        <v>Staff Product Manager, Ads Formats</v>
       </c>
       <c r="C61" t="str">
         <v>Reddit</v>
@@ -4166,7 +4166,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L61" t="str">
-        <v>https://boards.greenhouse.io/reddit/jobs/8070669</v>
+        <v>https://boards.greenhouse.io/reddit/jobs/8167412</v>
       </c>
       <c r="M61">
         <v>200</v>
@@ -4175,7 +4175,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O61" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P61" t="str">
         <v>Today</v>
@@ -4184,18 +4184,18 @@
         <v>No</v>
       </c>
       <c r="R61" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S61">
-        <v>64</v>
+        <v>69</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>job-35a933c8</v>
+        <v>job-0638f83c</v>
       </c>
       <c r="B62" t="str">
-        <v>Staff Product Manager, Ads Signals</v>
+        <v>Staff Product Manager, Ads Safety (Ads Review)</v>
       </c>
       <c r="C62" t="str">
         <v>Reddit</v>
@@ -4225,7 +4225,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L62" t="str">
-        <v>https://boards.greenhouse.io/reddit/jobs/8145926</v>
+        <v>https://boards.greenhouse.io/reddit/jobs/8070669</v>
       </c>
       <c r="M62">
         <v>200</v>
@@ -4234,7 +4234,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O62" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P62" t="str">
         <v>Today</v>
@@ -4243,18 +4243,18 @@
         <v>No</v>
       </c>
       <c r="R62" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S62">
-        <v>37</v>
+        <v>84</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>job-5a8393aa</v>
+        <v>job-35a933c8</v>
       </c>
       <c r="B63" t="str">
-        <v>Staff Product Manager, Growth</v>
+        <v>Staff Product Manager, Ads Signals</v>
       </c>
       <c r="C63" t="str">
         <v>Reddit</v>
@@ -4284,7 +4284,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L63" t="str">
-        <v>https://boards.greenhouse.io/reddit/jobs/7997186</v>
+        <v>https://boards.greenhouse.io/reddit/jobs/8145926</v>
       </c>
       <c r="M63">
         <v>200</v>
@@ -4293,7 +4293,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O63" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P63" t="str">
         <v>Today</v>
@@ -4305,15 +4305,15 @@
         <v>No</v>
       </c>
       <c r="S63">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>job-15c0a18c</v>
+        <v>job-5a8393aa</v>
       </c>
       <c r="B64" t="str">
-        <v>Staff Technical Product Manager, Ads ML Platform</v>
+        <v>Staff Product Manager, Growth</v>
       </c>
       <c r="C64" t="str">
         <v>Reddit</v>
@@ -4343,7 +4343,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L64" t="str">
-        <v>https://boards.greenhouse.io/reddit/jobs/7954001</v>
+        <v>https://boards.greenhouse.io/reddit/jobs/7997186</v>
       </c>
       <c r="M64">
         <v>200</v>
@@ -4352,33 +4352,33 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O64" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P64" t="str">
         <v>Today</v>
       </c>
       <c r="Q64" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R64" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S64">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>job-42db73ba</v>
+        <v>job-15c0a18c</v>
       </c>
       <c r="B65" t="str">
-        <v>Senior Product Manager, Safety</v>
+        <v>Staff Technical Product Manager, Ads ML Platform</v>
       </c>
       <c r="C65" t="str">
-        <v>Discord</v>
+        <v>Reddit</v>
       </c>
       <c r="D65" t="str">
-        <v>Wellfound</v>
+        <v>Indeed</v>
       </c>
       <c r="E65" t="str">
         <v>Senior Product Manager</v>
@@ -4390,19 +4390,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H65" t="str">
-        <v>San Francisco Bay Area</v>
+        <v>Remote - United States</v>
       </c>
       <c r="I65" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J65" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K65" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L65" t="str">
-        <v>https://boards.greenhouse.io/discord/jobs/8581126002</v>
+        <v>https://boards.greenhouse.io/reddit/jobs/7954001</v>
       </c>
       <c r="M65">
         <v>200</v>
@@ -4411,48 +4411,48 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O65" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P65" t="str">
         <v>Today</v>
       </c>
       <c r="Q65" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R65" t="str">
         <v>No</v>
       </c>
       <c r="S65">
-        <v>82</v>
+        <v>58</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>job-00451313</v>
+        <v>job-42db73ba</v>
       </c>
       <c r="B66" t="str">
-        <v>Associate Product Manager (New Grad)</v>
+        <v>Senior Product Manager, Safety</v>
       </c>
       <c r="C66" t="str">
-        <v>Robinhood</v>
+        <v>Discord</v>
       </c>
       <c r="D66" t="str">
-        <v>Naukri</v>
+        <v>Wellfound</v>
       </c>
       <c r="E66" t="str">
-        <v>Associate Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F66" t="str">
-        <v>1-3 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G66" t="str">
-        <v>0-2 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H66" t="str">
-        <v>Menlo Park, CA; New York, NY</v>
+        <v>San Francisco Bay Area</v>
       </c>
       <c r="I66" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J66" t="str">
         <v>On-site</v>
@@ -4461,7 +4461,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L66" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/8199973</v>
+        <v>https://boards.greenhouse.io/discord/jobs/8581126002</v>
       </c>
       <c r="M66">
         <v>200</v>
@@ -4470,27 +4470,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O66" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P66" t="str">
         <v>Today</v>
       </c>
       <c r="Q66" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R66" t="str">
         <v>No</v>
       </c>
       <c r="S66">
-        <v>91</v>
+        <v>33</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>job-73f048f5</v>
+        <v>job-00451313</v>
       </c>
       <c r="B67" t="str">
-        <v>Senior Product Manager, Capital Markets</v>
+        <v>Associate Product Manager (New Grad)</v>
       </c>
       <c r="C67" t="str">
         <v>Robinhood</v>
@@ -4499,13 +4499,13 @@
         <v>Naukri</v>
       </c>
       <c r="E67" t="str">
-        <v>Senior Product Manager</v>
+        <v>Associate Product Manager</v>
       </c>
       <c r="F67" t="str">
-        <v>5-8 yrs</v>
+        <v>1-3 yrs</v>
       </c>
       <c r="G67" t="str">
-        <v>5-8 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H67" t="str">
         <v>Menlo Park, CA; New York, NY</v>
@@ -4520,7 +4520,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L67" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/8204521</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/8199973</v>
       </c>
       <c r="M67">
         <v>200</v>
@@ -4529,27 +4529,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O67" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P67" t="str">
         <v>Today</v>
       </c>
       <c r="Q67" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R67" t="str">
         <v>No</v>
       </c>
       <c r="S67">
-        <v>93</v>
+        <v>62</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>job-28c2c2a4</v>
+        <v>job-73f048f5</v>
       </c>
       <c r="B68" t="str">
-        <v>Senior Product Manager, Crypto Wallet</v>
+        <v>Senior Product Manager, Capital Markets</v>
       </c>
       <c r="C68" t="str">
         <v>Robinhood</v>
@@ -4579,7 +4579,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L68" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/8082718</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/8204521</v>
       </c>
       <c r="M68">
         <v>200</v>
@@ -4588,27 +4588,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O68" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P68" t="str">
         <v>Today</v>
       </c>
       <c r="Q68" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R68" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S68">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>job-6a8c3d37</v>
+        <v>job-28c2c2a4</v>
       </c>
       <c r="B69" t="str">
-        <v>Senior Product Manager, Money Movement</v>
+        <v>Senior Product Manager, Crypto Wallet</v>
       </c>
       <c r="C69" t="str">
         <v>Robinhood</v>
@@ -4626,10 +4626,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H69" t="str">
-        <v>Menlo Park, CA</v>
+        <v>Menlo Park, CA; New York, NY</v>
       </c>
       <c r="I69" t="str">
-        <v>Menlo Park</v>
+        <v>New York</v>
       </c>
       <c r="J69" t="str">
         <v>On-site</v>
@@ -4638,7 +4638,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L69" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/7747728</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/8082718</v>
       </c>
       <c r="M69">
         <v>200</v>
@@ -4647,27 +4647,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O69" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P69" t="str">
         <v>Today</v>
       </c>
       <c r="Q69" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R69" t="str">
         <v>No</v>
       </c>
       <c r="S69">
-        <v>91</v>
+        <v>32</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>job-6a477110</v>
+        <v>job-6a8c3d37</v>
       </c>
       <c r="B70" t="str">
-        <v>Staff Product Manager, Banking</v>
+        <v>Senior Product Manager, Money Movement</v>
       </c>
       <c r="C70" t="str">
         <v>Robinhood</v>
@@ -4685,10 +4685,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H70" t="str">
-        <v>Menlo Park, CA; New York, NY; Washington, DC</v>
+        <v>Menlo Park, CA</v>
       </c>
       <c r="I70" t="str">
-        <v>New York</v>
+        <v>Menlo Park</v>
       </c>
       <c r="J70" t="str">
         <v>On-site</v>
@@ -4697,7 +4697,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L70" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/8044746</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/7747728</v>
       </c>
       <c r="M70">
         <v>200</v>
@@ -4706,27 +4706,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O70" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P70" t="str">
         <v>Today</v>
       </c>
       <c r="Q70" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R70" t="str">
         <v>No</v>
       </c>
       <c r="S70">
-        <v>69</v>
+        <v>51</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>job-1f991f57</v>
+        <v>job-6a477110</v>
       </c>
       <c r="B71" t="str">
-        <v>Staff Product Manager-  Integrations &amp; Advisor Platform</v>
+        <v>Staff Product Manager, Banking</v>
       </c>
       <c r="C71" t="str">
         <v>Robinhood</v>
@@ -4744,7 +4744,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H71" t="str">
-        <v>Clearwater, FL; Menlo Park, CA; New York, NY</v>
+        <v>Menlo Park, CA; New York, NY; Washington, DC</v>
       </c>
       <c r="I71" t="str">
         <v>New York</v>
@@ -4756,7 +4756,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L71" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/8131181</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/8044746</v>
       </c>
       <c r="M71">
         <v>200</v>
@@ -4765,27 +4765,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O71" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P71" t="str">
         <v>Today</v>
       </c>
       <c r="Q71" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R71" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S71">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>job-621b991e</v>
+        <v>job-1f991f57</v>
       </c>
       <c r="B72" t="str">
-        <v>Staff Product Manager, National Impact</v>
+        <v>Staff Product Manager-  Integrations &amp; Advisor Platform</v>
       </c>
       <c r="C72" t="str">
         <v>Robinhood</v>
@@ -4803,7 +4803,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H72" t="str">
-        <v>New York, NY</v>
+        <v>Clearwater, FL; Menlo Park, CA; New York, NY</v>
       </c>
       <c r="I72" t="str">
         <v>New York</v>
@@ -4815,7 +4815,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L72" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/7968044</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/8131181</v>
       </c>
       <c r="M72">
         <v>200</v>
@@ -4824,27 +4824,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O72" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P72" t="str">
         <v>Today</v>
       </c>
       <c r="Q72" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R72" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S72">
-        <v>75</v>
+        <v>94</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>job-2b6bc257</v>
+        <v>job-621b991e</v>
       </c>
       <c r="B73" t="str">
-        <v>Staff Product Manager - Prediction Markets</v>
+        <v>Staff Product Manager, National Impact</v>
       </c>
       <c r="C73" t="str">
         <v>Robinhood</v>
@@ -4862,7 +4862,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H73" t="str">
-        <v>Menlo Park, CA; New York, NY</v>
+        <v>New York, NY</v>
       </c>
       <c r="I73" t="str">
         <v>New York</v>
@@ -4874,7 +4874,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L73" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/8164459</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/7968044</v>
       </c>
       <c r="M73">
         <v>200</v>
@@ -4883,57 +4883,57 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O73" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P73" t="str">
         <v>Today</v>
       </c>
       <c r="Q73" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R73" t="str">
         <v>No</v>
       </c>
       <c r="S73">
-        <v>44</v>
+        <v>92</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>job-223dd55b</v>
+        <v>job-2b6bc257</v>
       </c>
       <c r="B74" t="str">
-        <v>Director of Product Management, Fintech</v>
+        <v>Staff Product Manager - Prediction Markets</v>
       </c>
       <c r="C74" t="str">
-        <v>Cloudflare</v>
+        <v>Robinhood</v>
       </c>
       <c r="D74" t="str">
-        <v>LinkedIn</v>
+        <v>Naukri</v>
       </c>
       <c r="E74" t="str">
-        <v>Product Lead / Director</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F74" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G74" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H74" t="str">
-        <v>Hybrid</v>
+        <v>Menlo Park, CA; New York, NY</v>
       </c>
       <c r="I74" t="str">
-        <v>Hybrid</v>
+        <v>New York</v>
       </c>
       <c r="J74" t="str">
-        <v>Hybrid</v>
+        <v>On-site</v>
       </c>
       <c r="K74" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L74" t="str">
-        <v>https://boards.greenhouse.io/cloudflare/jobs/8152765</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/8164459</v>
       </c>
       <c r="M74">
         <v>200</v>
@@ -4942,7 +4942,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O74" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P74" t="str">
         <v>Today</v>
@@ -4951,18 +4951,18 @@
         <v>No</v>
       </c>
       <c r="R74" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S74">
-        <v>33</v>
+        <v>78</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>job-04eb5da0</v>
+        <v>job-223dd55b</v>
       </c>
       <c r="B75" t="str">
-        <v>Product Manager, Browser Extension</v>
+        <v>Director of Product Management, Fintech</v>
       </c>
       <c r="C75" t="str">
         <v>Cloudflare</v>
@@ -4971,13 +4971,13 @@
         <v>LinkedIn</v>
       </c>
       <c r="E75" t="str">
-        <v>Product Manager</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F75" t="str">
-        <v>3-6 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G75" t="str">
-        <v>2-5 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H75" t="str">
         <v>Hybrid</v>
@@ -4992,7 +4992,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L75" t="str">
-        <v>https://boards.greenhouse.io/cloudflare/jobs/8173899</v>
+        <v>https://boards.greenhouse.io/cloudflare/jobs/8152765</v>
       </c>
       <c r="M75">
         <v>200</v>
@@ -5001,7 +5001,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O75" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P75" t="str">
         <v>Today</v>
@@ -5010,18 +5010,18 @@
         <v>Yes</v>
       </c>
       <c r="R75" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S75">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>job-6ad0cb95</v>
+        <v>job-04eb5da0</v>
       </c>
       <c r="B76" t="str">
-        <v>Senior Product Manager - Application Protection &amp; Governance</v>
+        <v>Product Manager, Browser Extension</v>
       </c>
       <c r="C76" t="str">
         <v>Cloudflare</v>
@@ -5030,13 +5030,13 @@
         <v>LinkedIn</v>
       </c>
       <c r="E76" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F76" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G76" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H76" t="str">
         <v>Hybrid</v>
@@ -5051,7 +5051,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L76" t="str">
-        <v>https://boards.greenhouse.io/cloudflare/jobs/8200670</v>
+        <v>https://boards.greenhouse.io/cloudflare/jobs/8173899</v>
       </c>
       <c r="M76">
         <v>200</v>
@@ -5060,7 +5060,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O76" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P76" t="str">
         <v>Today</v>
@@ -5072,15 +5072,15 @@
         <v>No</v>
       </c>
       <c r="S76">
-        <v>32</v>
+        <v>55</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>job-1cd2d853</v>
+        <v>job-6ad0cb95</v>
       </c>
       <c r="B77" t="str">
-        <v>Senior Product Manager, Email Security</v>
+        <v>Senior Product Manager - Application Protection &amp; Governance</v>
       </c>
       <c r="C77" t="str">
         <v>Cloudflare</v>
@@ -5110,7 +5110,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L77" t="str">
-        <v>https://boards.greenhouse.io/cloudflare/jobs/8173954</v>
+        <v>https://boards.greenhouse.io/cloudflare/jobs/8200670</v>
       </c>
       <c r="M77">
         <v>200</v>
@@ -5119,7 +5119,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O77" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P77" t="str">
         <v>Today</v>
@@ -5128,18 +5128,18 @@
         <v>No</v>
       </c>
       <c r="R77" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S77">
-        <v>38</v>
+        <v>25</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>job-4c1a26d6</v>
+        <v>job-1cd2d853</v>
       </c>
       <c r="B78" t="str">
-        <v>Senior Product Manager, Enterprise</v>
+        <v>Senior Product Manager, Email Security</v>
       </c>
       <c r="C78" t="str">
         <v>Cloudflare</v>
@@ -5169,7 +5169,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L78" t="str">
-        <v>https://boards.greenhouse.io/cloudflare/jobs/8158527</v>
+        <v>https://boards.greenhouse.io/cloudflare/jobs/8173954</v>
       </c>
       <c r="M78">
         <v>200</v>
@@ -5178,7 +5178,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O78" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P78" t="str">
         <v>Today</v>
@@ -5187,18 +5187,18 @@
         <v>No</v>
       </c>
       <c r="R78" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S78">
-        <v>86</v>
+        <v>77</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>job-0496f2bd</v>
+        <v>job-4c1a26d6</v>
       </c>
       <c r="B79" t="str">
-        <v>Senior Product Manager - FinTech</v>
+        <v>Senior Product Manager, Enterprise</v>
       </c>
       <c r="C79" t="str">
         <v>Cloudflare</v>
@@ -5216,19 +5216,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H79" t="str">
-        <v>In-Office</v>
+        <v>Hybrid</v>
       </c>
       <c r="I79" t="str">
-        <v>In-Office</v>
+        <v>Hybrid</v>
       </c>
       <c r="J79" t="str">
-        <v>On-site</v>
+        <v>Hybrid</v>
       </c>
       <c r="K79" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L79" t="str">
-        <v>https://boards.greenhouse.io/cloudflare/jobs/8064473</v>
+        <v>https://boards.greenhouse.io/cloudflare/jobs/8158527</v>
       </c>
       <c r="M79">
         <v>200</v>
@@ -5237,30 +5237,30 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O79" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P79" t="str">
         <v>Today</v>
       </c>
       <c r="Q79" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R79" t="str">
         <v>No</v>
       </c>
       <c r="S79">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>job-321ad81f</v>
+        <v>job-0496f2bd</v>
       </c>
       <c r="B80" t="str">
-        <v>Principal Product Manager Agents and Context - Elasticsearch</v>
+        <v>Senior Product Manager - FinTech</v>
       </c>
       <c r="C80" t="str">
-        <v>Elastic</v>
+        <v>Cloudflare</v>
       </c>
       <c r="D80" t="str">
         <v>LinkedIn</v>
@@ -5269,16 +5269,16 @@
         <v>Senior Product Manager</v>
       </c>
       <c r="F80" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G80" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H80" t="str">
-        <v>Canada</v>
+        <v>In-Office</v>
       </c>
       <c r="I80" t="str">
-        <v>Canada</v>
+        <v>In-Office</v>
       </c>
       <c r="J80" t="str">
         <v>On-site</v>
@@ -5287,7 +5287,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L80" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8070011</v>
+        <v>https://boards.greenhouse.io/cloudflare/jobs/8064473</v>
       </c>
       <c r="M80">
         <v>200</v>
@@ -5296,7 +5296,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O80" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P80" t="str">
         <v>Today</v>
@@ -5308,15 +5308,15 @@
         <v>No</v>
       </c>
       <c r="S80">
-        <v>91</v>
+        <v>45</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>job-1958e230</v>
+        <v>job-321ad81f</v>
       </c>
       <c r="B81" t="str">
-        <v>Principal Product Manager - Identity Threat Detection &amp; Response</v>
+        <v>Principal Product Manager Agents and Context - Elasticsearch</v>
       </c>
       <c r="C81" t="str">
         <v>Elastic</v>
@@ -5334,10 +5334,10 @@
         <v>8+ yrs</v>
       </c>
       <c r="H81" t="str">
-        <v>Spain</v>
+        <v>Canada</v>
       </c>
       <c r="I81" t="str">
-        <v>Spain</v>
+        <v>Canada</v>
       </c>
       <c r="J81" t="str">
         <v>On-site</v>
@@ -5346,7 +5346,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L81" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8122171</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8070011</v>
       </c>
       <c r="M81">
         <v>200</v>
@@ -5355,27 +5355,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O81" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P81" t="str">
         <v>Today</v>
       </c>
       <c r="Q81" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R81" t="str">
         <v>No</v>
       </c>
       <c r="S81">
-        <v>31</v>
+        <v>54</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>job-7648ed00</v>
+        <v>job-1958e230</v>
       </c>
       <c r="B82" t="str">
-        <v>Principal Product Manager II, AI/Vectors</v>
+        <v>Principal Product Manager - Identity Threat Detection &amp; Response</v>
       </c>
       <c r="C82" t="str">
         <v>Elastic</v>
@@ -5393,10 +5393,10 @@
         <v>8+ yrs</v>
       </c>
       <c r="H82" t="str">
-        <v>United States</v>
+        <v>Spain</v>
       </c>
       <c r="I82" t="str">
-        <v>United States</v>
+        <v>Spain</v>
       </c>
       <c r="J82" t="str">
         <v>On-site</v>
@@ -5405,7 +5405,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L82" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8121962</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8122171</v>
       </c>
       <c r="M82">
         <v>200</v>
@@ -5414,7 +5414,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O82" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P82" t="str">
         <v>Today</v>
@@ -5423,18 +5423,18 @@
         <v>No</v>
       </c>
       <c r="R82" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S82">
-        <v>69</v>
+        <v>56</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>job-4dbe0e39</v>
+        <v>job-7648ed00</v>
       </c>
       <c r="B83" t="str">
-        <v>Principal Product Manager (Strategic Account Interactions) - Security Solutions</v>
+        <v>Principal Product Manager II, AI/Vectors</v>
       </c>
       <c r="C83" t="str">
         <v>Elastic</v>
@@ -5452,10 +5452,10 @@
         <v>8+ yrs</v>
       </c>
       <c r="H83" t="str">
-        <v>Switzerland</v>
+        <v>United States</v>
       </c>
       <c r="I83" t="str">
-        <v>Switzerland</v>
+        <v>United States</v>
       </c>
       <c r="J83" t="str">
         <v>On-site</v>
@@ -5464,7 +5464,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L83" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8155425</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8121962</v>
       </c>
       <c r="M83">
         <v>200</v>
@@ -5473,27 +5473,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O83" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P83" t="str">
         <v>Today</v>
       </c>
       <c r="Q83" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R83" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S83">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>job-682d81b9</v>
+        <v>job-4dbe0e39</v>
       </c>
       <c r="B84" t="str">
-        <v>Principal Product Manager (XDR &amp; Exposure Management) - Security Solutions</v>
+        <v>Principal Product Manager (Strategic Account Interactions) - Security Solutions</v>
       </c>
       <c r="C84" t="str">
         <v>Elastic</v>
@@ -5511,10 +5511,10 @@
         <v>8+ yrs</v>
       </c>
       <c r="H84" t="str">
-        <v>Israel</v>
+        <v>Portugal</v>
       </c>
       <c r="I84" t="str">
-        <v>Israel</v>
+        <v>Portugal</v>
       </c>
       <c r="J84" t="str">
         <v>On-site</v>
@@ -5523,7 +5523,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L84" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8155328</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8155423</v>
       </c>
       <c r="M84">
         <v>200</v>
@@ -5532,27 +5532,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O84" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P84" t="str">
         <v>Today</v>
       </c>
       <c r="Q84" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R84" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S84">
-        <v>89</v>
+        <v>40</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>job-64ec2b77</v>
+        <v>job-682d81b9</v>
       </c>
       <c r="B85" t="str">
-        <v>Senior Director of Product Management, Endpoint Security &amp; XDR</v>
+        <v>Principal Product Manager (XDR &amp; Exposure Management) - Security Solutions</v>
       </c>
       <c r="C85" t="str">
         <v>Elastic</v>
@@ -5564,10 +5564,10 @@
         <v>Senior Product Manager</v>
       </c>
       <c r="F85" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G85" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H85" t="str">
         <v>United States</v>
@@ -5582,7 +5582,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L85" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8214106</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8130124</v>
       </c>
       <c r="M85">
         <v>200</v>
@@ -5591,7 +5591,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O85" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P85" t="str">
         <v>Today</v>
@@ -5600,18 +5600,18 @@
         <v>Yes</v>
       </c>
       <c r="R85" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S85">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>job-2b6f27da</v>
+        <v>job-64ec2b77</v>
       </c>
       <c r="B86" t="str">
-        <v>Senior Product Manager, Control Plane - Platform</v>
+        <v>Senior Director of Product Management, Endpoint Security &amp; XDR</v>
       </c>
       <c r="C86" t="str">
         <v>Elastic</v>
@@ -5629,10 +5629,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H86" t="str">
-        <v>Canada</v>
+        <v>United States</v>
       </c>
       <c r="I86" t="str">
-        <v>Canada</v>
+        <v>United States</v>
       </c>
       <c r="J86" t="str">
         <v>On-site</v>
@@ -5641,7 +5641,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L86" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8093933</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8214106</v>
       </c>
       <c r="M86">
         <v>200</v>
@@ -5650,7 +5650,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O86" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P86" t="str">
         <v>Today</v>
@@ -5659,18 +5659,18 @@
         <v>No</v>
       </c>
       <c r="R86" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S86">
-        <v>89</v>
+        <v>94</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>job-03cee7aa</v>
+        <v>job-2b6f27da</v>
       </c>
       <c r="B87" t="str">
-        <v>Senior Product Manager, Logs - Observability</v>
+        <v>Senior Product Manager, Control Plane - Platform</v>
       </c>
       <c r="C87" t="str">
         <v>Elastic</v>
@@ -5688,10 +5688,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H87" t="str">
-        <v>Greece</v>
+        <v>Canada</v>
       </c>
       <c r="I87" t="str">
-        <v>Greece</v>
+        <v>Canada</v>
       </c>
       <c r="J87" t="str">
         <v>On-site</v>
@@ -5700,7 +5700,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L87" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8066510</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8093933</v>
       </c>
       <c r="M87">
         <v>200</v>
@@ -5709,7 +5709,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O87" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P87" t="str">
         <v>Today</v>
@@ -5718,18 +5718,18 @@
         <v>No</v>
       </c>
       <c r="R87" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S87">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>job-264c8d5a</v>
+        <v>job-03cee7aa</v>
       </c>
       <c r="B88" t="str">
-        <v>Senior Product Manager - Self service cloud</v>
+        <v>Senior Product Manager, Logs - Observability</v>
       </c>
       <c r="C88" t="str">
         <v>Elastic</v>
@@ -5747,10 +5747,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H88" t="str">
-        <v>Spain</v>
+        <v>United States</v>
       </c>
       <c r="I88" t="str">
-        <v>Spain</v>
+        <v>United States</v>
       </c>
       <c r="J88" t="str">
         <v>On-site</v>
@@ -5759,7 +5759,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L88" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8028261</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8053907</v>
       </c>
       <c r="M88">
         <v>200</v>
@@ -5768,7 +5768,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O88" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P88" t="str">
         <v>Today</v>
@@ -5780,15 +5780,15 @@
         <v>No</v>
       </c>
       <c r="S88">
-        <v>94</v>
+        <v>29</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>job-5b8ec8c1</v>
+        <v>job-264c8d5a</v>
       </c>
       <c r="B89" t="str">
-        <v>Senior Product Manager - US Public Sector</v>
+        <v>Senior Product Manager - Self service cloud</v>
       </c>
       <c r="C89" t="str">
         <v>Elastic</v>
@@ -5806,10 +5806,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H89" t="str">
-        <v>United States</v>
+        <v>Portugal</v>
       </c>
       <c r="I89" t="str">
-        <v>United States</v>
+        <v>Portugal</v>
       </c>
       <c r="J89" t="str">
         <v>On-site</v>
@@ -5818,7 +5818,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L89" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8188365</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8041208</v>
       </c>
       <c r="M89">
         <v>200</v>
@@ -5827,27 +5827,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O89" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P89" t="str">
         <v>Today</v>
       </c>
       <c r="Q89" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R89" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S89">
-        <v>92</v>
+        <v>40</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>job-7ab91933</v>
+        <v>job-5b8ec8c1</v>
       </c>
       <c r="B90" t="str">
-        <v>Senior Product Manager (XDR) - Security Solutions</v>
+        <v>Senior Product Manager - US Public Sector</v>
       </c>
       <c r="C90" t="str">
         <v>Elastic</v>
@@ -5865,10 +5865,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H90" t="str">
-        <v>Greece</v>
+        <v>United States</v>
       </c>
       <c r="I90" t="str">
-        <v>Greece</v>
+        <v>United States</v>
       </c>
       <c r="J90" t="str">
         <v>On-site</v>
@@ -5877,7 +5877,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L90" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8194148</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8188365</v>
       </c>
       <c r="M90">
         <v>200</v>
@@ -5886,7 +5886,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O90" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P90" t="str">
         <v>Today</v>
@@ -5898,36 +5898,36 @@
         <v>Yes</v>
       </c>
       <c r="S90">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>job-31af15ee</v>
+        <v>job-7ab91933</v>
       </c>
       <c r="B91" t="str">
-        <v>AI Product Manager (Coding/Multimodal)</v>
+        <v>Senior Product Manager (XDR) - Security Solutions</v>
       </c>
       <c r="C91" t="str">
-        <v>Scale AI</v>
+        <v>Elastic</v>
       </c>
       <c r="D91" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E91" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F91" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G91" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H91" t="str">
-        <v>San Francisco, CA</v>
+        <v>Switzerland</v>
       </c>
       <c r="I91" t="str">
-        <v>San Francisco</v>
+        <v>Switzerland</v>
       </c>
       <c r="J91" t="str">
         <v>On-site</v>
@@ -5936,7 +5936,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L91" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4609736005</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8194084</v>
       </c>
       <c r="M91">
         <v>200</v>
@@ -5945,7 +5945,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O91" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P91" t="str">
         <v>Today</v>
@@ -5954,18 +5954,18 @@
         <v>Yes</v>
       </c>
       <c r="R91" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S91">
-        <v>42</v>
+        <v>86</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>job-184e55c8</v>
+        <v>job-31af15ee</v>
       </c>
       <c r="B92" t="str">
-        <v>Director of Product Management, Enterprise Core Platform</v>
+        <v>AI Product Manager (Coding/Multimodal)</v>
       </c>
       <c r="C92" t="str">
         <v>Scale AI</v>
@@ -5974,16 +5974,16 @@
         <v>Wellfound</v>
       </c>
       <c r="E92" t="str">
-        <v>Technical Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F92" t="str">
-        <v>8+ yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G92" t="str">
-        <v>8+ yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H92" t="str">
-        <v>San Francisco, CA; New York, NY</v>
+        <v>San Francisco, CA</v>
       </c>
       <c r="I92" t="str">
         <v>San Francisco</v>
@@ -5995,7 +5995,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L92" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4714727005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4609736005</v>
       </c>
       <c r="M92">
         <v>200</v>
@@ -6004,27 +6004,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O92" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P92" t="str">
         <v>Today</v>
       </c>
       <c r="Q92" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R92" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S92">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>job-6681e5c8</v>
+        <v>job-184e55c8</v>
       </c>
       <c r="B93" t="str">
-        <v>Forward Deployed Product Manager, Enterprise</v>
+        <v>Director of Product Management, Enterprise Core Platform</v>
       </c>
       <c r="C93" t="str">
         <v>Scale AI</v>
@@ -6033,19 +6033,19 @@
         <v>Wellfound</v>
       </c>
       <c r="E93" t="str">
-        <v>Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F93" t="str">
-        <v>3-6 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G93" t="str">
-        <v>2-5 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H93" t="str">
-        <v>London, UK</v>
+        <v>San Francisco, CA; New York, NY</v>
       </c>
       <c r="I93" t="str">
-        <v>London</v>
+        <v>San Francisco</v>
       </c>
       <c r="J93" t="str">
         <v>On-site</v>
@@ -6054,7 +6054,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L93" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4644742005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4714727005</v>
       </c>
       <c r="M93">
         <v>200</v>
@@ -6063,27 +6063,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O93" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P93" t="str">
         <v>Today</v>
       </c>
       <c r="Q93" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R93" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S93">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>job-11245f1c</v>
+        <v>job-6681e5c8</v>
       </c>
       <c r="B94" t="str">
-        <v>Forward Deployed Product Manager, Public Sector</v>
+        <v>Forward Deployed Product Manager, Enterprise</v>
       </c>
       <c r="C94" t="str">
         <v>Scale AI</v>
@@ -6101,7 +6101,7 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H94" t="str">
-        <v>New York, NY; Washington, DC</v>
+        <v>New York, NY</v>
       </c>
       <c r="I94" t="str">
         <v>New York</v>
@@ -6113,7 +6113,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L94" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4713648005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4673051005</v>
       </c>
       <c r="M94">
         <v>200</v>
@@ -6122,7 +6122,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O94" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P94" t="str">
         <v>Today</v>
@@ -6134,15 +6134,15 @@
         <v>No</v>
       </c>
       <c r="S94">
-        <v>38</v>
+        <v>63</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>job-6a73fdcd</v>
+        <v>job-11245f1c</v>
       </c>
       <c r="B95" t="str">
-        <v>Head of Product Management, Forward Deployed &amp; Strategy</v>
+        <v>Forward Deployed Product Manager, Public Sector</v>
       </c>
       <c r="C95" t="str">
         <v>Scale AI</v>
@@ -6151,19 +6151,19 @@
         <v>Wellfound</v>
       </c>
       <c r="E95" t="str">
-        <v>Product Lead / Director</v>
+        <v>Product Manager</v>
       </c>
       <c r="F95" t="str">
-        <v>8+ yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G95" t="str">
-        <v>8+ yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H95" t="str">
-        <v>London, UK</v>
+        <v>New York, NY; Washington, DC</v>
       </c>
       <c r="I95" t="str">
-        <v>London</v>
+        <v>New York</v>
       </c>
       <c r="J95" t="str">
         <v>On-site</v>
@@ -6172,7 +6172,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L95" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4702890005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4713648005</v>
       </c>
       <c r="M95">
         <v>200</v>
@@ -6181,27 +6181,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O95" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P95" t="str">
         <v>Today</v>
       </c>
       <c r="Q95" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R95" t="str">
         <v>No</v>
       </c>
       <c r="S95">
-        <v>67</v>
+        <v>73</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>job-235e84a3</v>
+        <v>job-6a73fdcd</v>
       </c>
       <c r="B96" t="str">
-        <v>Product Manager, Enterprise Core Platform</v>
+        <v>Head of Product Management, Forward Deployed &amp; Strategy</v>
       </c>
       <c r="C96" t="str">
         <v>Scale AI</v>
@@ -6210,19 +6210,19 @@
         <v>Wellfound</v>
       </c>
       <c r="E96" t="str">
-        <v>Technical Product Manager</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F96" t="str">
-        <v>3-6 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G96" t="str">
-        <v>2-5 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H96" t="str">
-        <v>New York, NY; San Francisco, CA</v>
+        <v>London, UK</v>
       </c>
       <c r="I96" t="str">
-        <v>San Francisco</v>
+        <v>London</v>
       </c>
       <c r="J96" t="str">
         <v>On-site</v>
@@ -6231,7 +6231,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L96" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4699779005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4702890005</v>
       </c>
       <c r="M96">
         <v>200</v>
@@ -6240,27 +6240,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O96" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P96" t="str">
         <v>Today</v>
       </c>
       <c r="Q96" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R96" t="str">
         <v>No</v>
       </c>
       <c r="S96">
-        <v>85</v>
+        <v>29</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>job-7d366400</v>
+        <v>job-235e84a3</v>
       </c>
       <c r="B97" t="str">
-        <v>Product Manager of AI Applications, Global Public Sector</v>
+        <v>Product Manager, Enterprise Core Platform</v>
       </c>
       <c r="C97" t="str">
         <v>Scale AI</v>
@@ -6269,7 +6269,7 @@
         <v>Wellfound</v>
       </c>
       <c r="E97" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F97" t="str">
         <v>3-6 yrs</v>
@@ -6278,10 +6278,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H97" t="str">
-        <v>Riyadh, Saudi Arabia</v>
+        <v>New York, NY; San Francisco, CA</v>
       </c>
       <c r="I97" t="str">
-        <v>Riyadh</v>
+        <v>San Francisco</v>
       </c>
       <c r="J97" t="str">
         <v>On-site</v>
@@ -6290,7 +6290,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L97" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4650514005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4699779005</v>
       </c>
       <c r="M97">
         <v>200</v>
@@ -6299,27 +6299,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O97" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P97" t="str">
         <v>Today</v>
       </c>
       <c r="Q97" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R97" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S97">
-        <v>63</v>
+        <v>33</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>job-6c1eab2d</v>
+        <v>job-7d366400</v>
       </c>
       <c r="B98" t="str">
-        <v>Senior AI Product Manager, Code</v>
+        <v>Product Manager of AI Applications, Global Public Sector</v>
       </c>
       <c r="C98" t="str">
         <v>Scale AI</v>
@@ -6328,19 +6328,19 @@
         <v>Wellfound</v>
       </c>
       <c r="E98" t="str">
-        <v>Senior Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F98" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G98" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H98" t="str">
-        <v>New York, NY; San Francisco, CA</v>
+        <v>Doha, Qatar ; Dubai, UAE</v>
       </c>
       <c r="I98" t="str">
-        <v>San Francisco</v>
+        <v>Doha</v>
       </c>
       <c r="J98" t="str">
         <v>On-site</v>
@@ -6349,7 +6349,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L98" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4720501005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4589749005</v>
       </c>
       <c r="M98">
         <v>200</v>
@@ -6358,27 +6358,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O98" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P98" t="str">
         <v>Today</v>
       </c>
       <c r="Q98" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R98" t="str">
         <v>No</v>
       </c>
       <c r="S98">
-        <v>30</v>
+        <v>86</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>job-1310fa39</v>
+        <v>job-114956cc</v>
       </c>
       <c r="B99" t="str">
-        <v>Senior AI Product Manager, Cybersecurity</v>
+        <v>Senior AI Product Manager</v>
       </c>
       <c r="C99" t="str">
         <v>Scale AI</v>
@@ -6408,7 +6408,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L99" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4720213005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4720501005</v>
       </c>
       <c r="M99">
         <v>200</v>
@@ -6417,27 +6417,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O99" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P99" t="str">
         <v>Today</v>
       </c>
       <c r="Q99" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R99" t="str">
         <v>No</v>
       </c>
       <c r="S99">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>job-7ff81a54</v>
+        <v>job-1310fa39</v>
       </c>
       <c r="B100" t="str">
-        <v>Senior AI Product Manager, Finance Agents</v>
+        <v>Senior AI Product Manager, Cybersecurity</v>
       </c>
       <c r="C100" t="str">
         <v>Scale AI</v>
@@ -6455,7 +6455,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H100" t="str">
-        <v>San Francisco, CA; New York, NY</v>
+        <v>New York, NY; San Francisco, CA</v>
       </c>
       <c r="I100" t="str">
         <v>San Francisco</v>
@@ -6467,7 +6467,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L100" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4611776005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4720213005</v>
       </c>
       <c r="M100">
         <v>200</v>
@@ -6476,27 +6476,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O100" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P100" t="str">
         <v>Today</v>
       </c>
       <c r="Q100" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R100" t="str">
         <v>No</v>
       </c>
       <c r="S100">
-        <v>85</v>
+        <v>29</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>job-41be8c95</v>
+        <v>job-7ff81a54</v>
       </c>
       <c r="B101" t="str">
-        <v>Senior AI Product Manager, Leaderboard</v>
+        <v>Senior AI Product Manager, Finance Agents</v>
       </c>
       <c r="C101" t="str">
         <v>Scale AI</v>
@@ -6514,7 +6514,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H101" t="str">
-        <v>New York, NY; San Francisco, CA</v>
+        <v>San Francisco, CA; New York, NY</v>
       </c>
       <c r="I101" t="str">
         <v>San Francisco</v>
@@ -6526,7 +6526,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L101" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4720216005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4611776005</v>
       </c>
       <c r="M101">
         <v>200</v>
@@ -6535,19 +6535,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O101" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P101" t="str">
         <v>Today</v>
       </c>
       <c r="Q101" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R101" t="str">
         <v>No</v>
       </c>
       <c r="S101">
-        <v>48</v>
+        <v>75</v>
       </c>
     </row>
     <row r="102">
@@ -6594,7 +6594,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O102" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P102" t="str">
         <v>Today</v>
@@ -6606,7 +6606,7 @@
         <v>No</v>
       </c>
       <c r="S102">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="103">
@@ -6653,7 +6653,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O103" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P103" t="str">
         <v>Today</v>
@@ -6662,10 +6662,10 @@
         <v>No</v>
       </c>
       <c r="R103" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S103">
-        <v>75</v>
+        <v>49</v>
       </c>
     </row>
     <row r="104">
@@ -6712,19 +6712,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O104" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P104" t="str">
         <v>Today</v>
       </c>
       <c r="Q104" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R104" t="str">
         <v>Yes</v>
       </c>
       <c r="S104">
-        <v>50</v>
+        <v>36</v>
       </c>
     </row>
     <row r="105">
@@ -6771,19 +6771,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O105" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P105" t="str">
         <v>Today</v>
       </c>
       <c r="Q105" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R105" t="str">
         <v>No</v>
       </c>
       <c r="S105">
-        <v>66</v>
+        <v>35</v>
       </c>
     </row>
     <row r="106">
@@ -6809,10 +6809,10 @@
         <v>8+ yrs</v>
       </c>
       <c r="H106" t="str">
-        <v>Vancouver, British Columbia, Canada</v>
+        <v>Seattle, Washington, United States</v>
       </c>
       <c r="I106" t="str">
-        <v>Vancouver</v>
+        <v>Seattle</v>
       </c>
       <c r="J106" t="str">
         <v>On-site</v>
@@ -6821,7 +6821,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L106" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8433546002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8433470002</v>
       </c>
       <c r="M106">
         <v>200</v>
@@ -6830,19 +6830,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O106" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P106" t="str">
         <v>Today</v>
       </c>
       <c r="Q106" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R106" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S106">
-        <v>90</v>
+        <v>56</v>
       </c>
     </row>
     <row r="107">
@@ -6868,10 +6868,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H107" t="str">
-        <v>Seattle, Washington, United States</v>
+        <v>San Francisco, California, United States</v>
       </c>
       <c r="I107" t="str">
-        <v>Seattle</v>
+        <v>San Francisco</v>
       </c>
       <c r="J107" t="str">
         <v>On-site</v>
@@ -6880,7 +6880,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L107" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8438582002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8438580002</v>
       </c>
       <c r="M107">
         <v>200</v>
@@ -6889,7 +6889,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O107" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P107" t="str">
         <v>Today</v>
@@ -6901,7 +6901,7 @@
         <v>No</v>
       </c>
       <c r="S107">
-        <v>85</v>
+        <v>93</v>
       </c>
     </row>
     <row r="108">
@@ -6948,7 +6948,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O108" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P108" t="str">
         <v>Today</v>
@@ -6960,7 +6960,7 @@
         <v>Yes</v>
       </c>
       <c r="S108">
-        <v>78</v>
+        <v>55</v>
       </c>
     </row>
     <row r="109">
@@ -7007,19 +7007,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O109" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P109" t="str">
         <v>Today</v>
       </c>
       <c r="Q109" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R109" t="str">
         <v>Yes</v>
       </c>
       <c r="S109">
-        <v>90</v>
+        <v>69</v>
       </c>
     </row>
     <row r="110">
@@ -7045,10 +7045,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H110" t="str">
-        <v>New York, New York, United States</v>
+        <v>San Francisco, California, United States</v>
       </c>
       <c r="I110" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J110" t="str">
         <v>On-site</v>
@@ -7057,7 +7057,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L110" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8432702002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8432698002</v>
       </c>
       <c r="M110">
         <v>200</v>
@@ -7066,7 +7066,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O110" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P110" t="str">
         <v>Today</v>
@@ -7075,10 +7075,10 @@
         <v>No</v>
       </c>
       <c r="R110" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S110">
-        <v>73</v>
+        <v>55</v>
       </c>
     </row>
     <row r="111">
@@ -7125,19 +7125,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O111" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P111" t="str">
         <v>Today</v>
       </c>
       <c r="Q111" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R111" t="str">
         <v>No</v>
       </c>
       <c r="S111">
-        <v>36</v>
+        <v>64</v>
       </c>
     </row>
     <row r="112">
@@ -7184,7 +7184,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O112" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P112" t="str">
         <v>Today</v>
@@ -7196,7 +7196,7 @@
         <v>Yes</v>
       </c>
       <c r="S112">
-        <v>25</v>
+        <v>43</v>
       </c>
     </row>
     <row r="113">
@@ -7243,7 +7243,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O113" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P113" t="str">
         <v>Today</v>
@@ -7255,7 +7255,7 @@
         <v>No</v>
       </c>
       <c r="S113">
-        <v>69</v>
+        <v>29</v>
       </c>
     </row>
     <row r="114">
@@ -7302,7 +7302,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O114" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P114" t="str">
         <v>Today</v>
@@ -7311,10 +7311,10 @@
         <v>No</v>
       </c>
       <c r="R114" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S114">
-        <v>40</v>
+        <v>94</v>
       </c>
     </row>
     <row r="115">
@@ -7340,10 +7340,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H115" t="str">
-        <v>San Francisco, California, United States</v>
+        <v>New York, New York, United States</v>
       </c>
       <c r="I115" t="str">
-        <v>San Francisco</v>
+        <v>New York</v>
       </c>
       <c r="J115" t="str">
         <v>On-site</v>
@@ -7352,7 +7352,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L115" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8659239002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8659242002</v>
       </c>
       <c r="M115">
         <v>200</v>
@@ -7361,7 +7361,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O115" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P115" t="str">
         <v>Today</v>
@@ -7373,7 +7373,7 @@
         <v>No</v>
       </c>
       <c r="S115">
-        <v>85</v>
+        <v>46</v>
       </c>
     </row>
     <row r="116">
@@ -7420,7 +7420,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O116" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P116" t="str">
         <v>Today</v>
@@ -7432,7 +7432,7 @@
         <v>No</v>
       </c>
       <c r="S116">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="117">
@@ -7479,7 +7479,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O117" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P117" t="str">
         <v>Today</v>
@@ -7488,10 +7488,10 @@
         <v>Yes</v>
       </c>
       <c r="R117" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S117">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="118">
@@ -7538,7 +7538,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O118" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P118" t="str">
         <v>Today</v>
@@ -7550,7 +7550,7 @@
         <v>No</v>
       </c>
       <c r="S118">
-        <v>87</v>
+        <v>71</v>
       </c>
     </row>
     <row r="119">
@@ -7576,10 +7576,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H119" t="str">
-        <v>Pittsburgh, PA</v>
+        <v>New York, NY</v>
       </c>
       <c r="I119" t="str">
-        <v>Pittsburgh</v>
+        <v>New York</v>
       </c>
       <c r="J119" t="str">
         <v>On-site</v>
@@ -7588,7 +7588,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L119" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8530395002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8737859002</v>
       </c>
       <c r="M119">
         <v>200</v>
@@ -7597,7 +7597,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O119" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P119" t="str">
         <v>Today</v>
@@ -7609,7 +7609,7 @@
         <v>No</v>
       </c>
       <c r="S119">
-        <v>81</v>
+        <v>33</v>
       </c>
     </row>
     <row r="120">
@@ -7656,19 +7656,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O120" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P120" t="str">
         <v>Today</v>
       </c>
       <c r="Q120" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R120" t="str">
         <v>Yes</v>
       </c>
       <c r="S120">
-        <v>65</v>
+        <v>39</v>
       </c>
     </row>
     <row r="121">
@@ -7694,10 +7694,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H121" t="str">
-        <v>New York, NY</v>
+        <v>Pittsburgh, PA</v>
       </c>
       <c r="I121" t="str">
-        <v>New York</v>
+        <v>Pittsburgh</v>
       </c>
       <c r="J121" t="str">
         <v>On-site</v>
@@ -7706,7 +7706,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L121" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8816512002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8827944002</v>
       </c>
       <c r="M121">
         <v>200</v>
@@ -7715,7 +7715,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O121" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P121" t="str">
         <v>Today</v>
@@ -7724,10 +7724,10 @@
         <v>No</v>
       </c>
       <c r="R121" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S121">
-        <v>90</v>
+        <v>40</v>
       </c>
     </row>
     <row r="122">
@@ -7774,19 +7774,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O122" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P122" t="str">
         <v>Today</v>
       </c>
       <c r="Q122" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R122" t="str">
         <v>No</v>
       </c>
       <c r="S122">
-        <v>91</v>
+        <v>78</v>
       </c>
     </row>
     <row r="123">
@@ -7833,19 +7833,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O123" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P123" t="str">
         <v>Today</v>
       </c>
       <c r="Q123" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R123" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S123">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="124">
@@ -7871,10 +7871,10 @@
         <v>8+ yrs</v>
       </c>
       <c r="H124" t="str">
-        <v>Pittsburgh, PA</v>
+        <v>New York, NY</v>
       </c>
       <c r="I124" t="str">
-        <v>Pittsburgh</v>
+        <v>New York</v>
       </c>
       <c r="J124" t="str">
         <v>On-site</v>
@@ -7883,7 +7883,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L124" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8747077002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8747060002</v>
       </c>
       <c r="M124">
         <v>200</v>
@@ -7892,7 +7892,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O124" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P124" t="str">
         <v>Today</v>
@@ -7951,19 +7951,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O125" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P125" t="str">
         <v>Today</v>
       </c>
       <c r="Q125" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R125" t="str">
         <v>Yes</v>
       </c>
       <c r="S125">
-        <v>48</v>
+        <v>27</v>
       </c>
     </row>
     <row r="126">
@@ -8010,7 +8010,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O126" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P126" t="str">
         <v>Today</v>
@@ -8022,7 +8022,7 @@
         <v>Yes</v>
       </c>
       <c r="S126">
-        <v>80</v>
+        <v>61</v>
       </c>
     </row>
     <row r="127">
@@ -8069,7 +8069,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O127" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P127" t="str">
         <v>Today</v>
@@ -8081,7 +8081,7 @@
         <v>No</v>
       </c>
       <c r="S127">
-        <v>61</v>
+        <v>73</v>
       </c>
     </row>
     <row r="128">
@@ -8128,19 +8128,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O128" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P128" t="str">
         <v>Today</v>
       </c>
       <c r="Q128" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R128" t="str">
         <v>No</v>
       </c>
       <c r="S128">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="129">
@@ -8187,19 +8187,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O129" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P129" t="str">
         <v>Today</v>
       </c>
       <c r="Q129" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R129" t="str">
         <v>No</v>
       </c>
       <c r="S129">
-        <v>53</v>
+        <v>25</v>
       </c>
     </row>
     <row r="130">
@@ -8246,19 +8246,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O130" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P130" t="str">
         <v>Today</v>
       </c>
       <c r="Q130" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R130" t="str">
         <v>No</v>
       </c>
       <c r="S130">
-        <v>47</v>
+        <v>91</v>
       </c>
     </row>
     <row r="131">
@@ -8305,19 +8305,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O131" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P131" t="str">
         <v>Today</v>
       </c>
       <c r="Q131" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R131" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S131">
-        <v>66</v>
+        <v>31</v>
       </c>
     </row>
     <row r="132">
@@ -8364,7 +8364,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O132" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P132" t="str">
         <v>Today</v>
@@ -8376,7 +8376,7 @@
         <v>No</v>
       </c>
       <c r="S132">
-        <v>29</v>
+        <v>91</v>
       </c>
     </row>
     <row r="133">
@@ -8423,19 +8423,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O133" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P133" t="str">
         <v>Today</v>
       </c>
       <c r="Q133" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R133" t="str">
         <v>No</v>
       </c>
       <c r="S133">
-        <v>48</v>
+        <v>54</v>
       </c>
     </row>
     <row r="134">
@@ -8482,19 +8482,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O134" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P134" t="str">
         <v>Today</v>
       </c>
       <c r="Q134" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R134" t="str">
         <v>No</v>
       </c>
       <c r="S134">
-        <v>67</v>
+        <v>49</v>
       </c>
     </row>
     <row r="135">
@@ -8541,7 +8541,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O135" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P135" t="str">
         <v>Today</v>
@@ -8550,10 +8550,10 @@
         <v>No</v>
       </c>
       <c r="R135" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S135">
-        <v>29</v>
+        <v>41</v>
       </c>
     </row>
     <row r="136">
@@ -8600,7 +8600,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O136" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P136" t="str">
         <v>Today</v>
@@ -8609,10 +8609,10 @@
         <v>No</v>
       </c>
       <c r="R136" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S136">
-        <v>57</v>
+        <v>75</v>
       </c>
     </row>
     <row r="137">
@@ -8659,7 +8659,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O137" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P137" t="str">
         <v>Today</v>
@@ -8671,15 +8671,15 @@
         <v>No</v>
       </c>
       <c r="S137">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>job-7167a200</v>
+        <v>job-448d861a</v>
       </c>
       <c r="B138" t="str">
-        <v>Senior Product Manager, Growth</v>
+        <v>Senior Product Manager, Agentic Source Code</v>
       </c>
       <c r="C138" t="str">
         <v>GitLab</v>
@@ -8697,7 +8697,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H138" t="str">
-        <v>Remote, Canada; Remote, United States</v>
+        <v>Remote, Canada; Remote, US</v>
       </c>
       <c r="I138" t="str">
         <v>Remote</v>
@@ -8709,7 +8709,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L138" t="str">
-        <v>https://boards.greenhouse.io/gitlab/jobs/8684348002</v>
+        <v>https://boards.greenhouse.io/gitlab/jobs/8597805002</v>
       </c>
       <c r="M138">
         <v>200</v>
@@ -8718,7 +8718,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O138" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P138" t="str">
         <v>Today</v>
@@ -8730,7 +8730,7 @@
         <v>No</v>
       </c>
       <c r="S138">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="139">
@@ -8777,7 +8777,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O139" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P139" t="str">
         <v>Today</v>
@@ -8786,18 +8786,18 @@
         <v>No</v>
       </c>
       <c r="R139" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S139">
-        <v>79</v>
+        <v>62</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>job-274a6d99</v>
+        <v>job-7ad77ccd</v>
       </c>
       <c r="B140" t="str">
-        <v>Senior Product Manager, Source Code</v>
+        <v>Senior Product Manager, Tenant Scale</v>
       </c>
       <c r="C140" t="str">
         <v>GitLab</v>
@@ -8827,7 +8827,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L140" t="str">
-        <v>https://boards.greenhouse.io/gitlab/jobs/8597805002</v>
+        <v>https://boards.greenhouse.io/gitlab/jobs/8512220002</v>
       </c>
       <c r="M140">
         <v>200</v>
@@ -8836,7 +8836,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O140" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P140" t="str">
         <v>Today</v>
@@ -8845,18 +8845,18 @@
         <v>No</v>
       </c>
       <c r="R140" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S140">
-        <v>28</v>
+        <v>55</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>job-7ad77ccd</v>
+        <v>job-52edb6a4</v>
       </c>
       <c r="B141" t="str">
-        <v>Senior Product Manager, Tenant Scale</v>
+        <v>Staff Product Manager,  RevOps &amp; Finance Systems</v>
       </c>
       <c r="C141" t="str">
         <v>GitLab</v>
@@ -8874,7 +8874,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H141" t="str">
-        <v>Remote, Canada; Remote, US</v>
+        <v>Remote, US</v>
       </c>
       <c r="I141" t="str">
         <v>Remote</v>
@@ -8886,7 +8886,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L141" t="str">
-        <v>https://boards.greenhouse.io/gitlab/jobs/8512220002</v>
+        <v>https://boards.greenhouse.io/gitlab/jobs/8612937002</v>
       </c>
       <c r="M141">
         <v>200</v>
@@ -8895,7 +8895,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O141" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P141" t="str">
         <v>Today</v>
@@ -8904,48 +8904,48 @@
         <v>Yes</v>
       </c>
       <c r="R141" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S141">
-        <v>37</v>
+        <v>47</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>job-52edb6a4</v>
+        <v>job-3a743e4f</v>
       </c>
       <c r="B142" t="str">
-        <v>Staff Product Manager,  RevOps &amp; Finance Systems</v>
+        <v>Manager, Product Management - Figma Platform Experience</v>
       </c>
       <c r="C142" t="str">
-        <v>GitLab</v>
+        <v>Figma</v>
       </c>
       <c r="D142" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E142" t="str">
-        <v>Senior Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F142" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G142" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H142" t="str">
-        <v>Remote, US</v>
+        <v>San Francisco, CA • New York, NY • United States</v>
       </c>
       <c r="I142" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J142" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K142" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L142" t="str">
-        <v>https://boards.greenhouse.io/gitlab/jobs/8612937002</v>
+        <v>https://boards.greenhouse.io/figma/jobs/6160732004</v>
       </c>
       <c r="M142">
         <v>200</v>
@@ -8954,27 +8954,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O142" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P142" t="str">
         <v>Today</v>
       </c>
       <c r="Q142" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R142" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S142">
-        <v>83</v>
+        <v>73</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>job-3a743e4f</v>
+        <v>job-7297f499</v>
       </c>
       <c r="B143" t="str">
-        <v>Manager, Product Management - Figma Platform Experience</v>
+        <v>Manager, Product Management - Roundtripping</v>
       </c>
       <c r="C143" t="str">
         <v>Figma</v>
@@ -8983,7 +8983,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E143" t="str">
-        <v>Technical Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F143" t="str">
         <v>3-6 yrs</v>
@@ -8992,10 +8992,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H143" t="str">
-        <v>San Francisco, CA • New York, NY • United States</v>
+        <v>New York, NY • United States</v>
       </c>
       <c r="I143" t="str">
-        <v>San Francisco</v>
+        <v>New York</v>
       </c>
       <c r="J143" t="str">
         <v>On-site</v>
@@ -9004,7 +9004,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L143" t="str">
-        <v>https://boards.greenhouse.io/figma/jobs/6160732004</v>
+        <v>https://boards.greenhouse.io/figma/jobs/6104919004</v>
       </c>
       <c r="M143">
         <v>200</v>
@@ -9013,7 +9013,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O143" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P143" t="str">
         <v>Today</v>
@@ -9030,10 +9030,10 @@
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>job-7297f499</v>
+        <v>job-19031a2a</v>
       </c>
       <c r="B144" t="str">
-        <v>Manager, Product Management - Roundtripping</v>
+        <v>Manager, Product Management - Roundtripping (London, United Kingdom)</v>
       </c>
       <c r="C144" t="str">
         <v>Figma</v>
@@ -9051,10 +9051,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H144" t="str">
-        <v>New York, NY • United States</v>
+        <v>London, England</v>
       </c>
       <c r="I144" t="str">
-        <v>New York</v>
+        <v>London</v>
       </c>
       <c r="J144" t="str">
         <v>On-site</v>
@@ -9063,7 +9063,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L144" t="str">
-        <v>https://boards.greenhouse.io/figma/jobs/6104919004</v>
+        <v>https://boards.greenhouse.io/figma/jobs/6149007004</v>
       </c>
       <c r="M144">
         <v>200</v>
@@ -9072,27 +9072,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O144" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P144" t="str">
         <v>Today</v>
       </c>
       <c r="Q144" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R144" t="str">
         <v>No</v>
       </c>
       <c r="S144">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>job-19031a2a</v>
+        <v>job-099ff647</v>
       </c>
       <c r="B145" t="str">
-        <v>Manager, Product Management - Roundtripping (London, United Kingdom)</v>
+        <v>Product Manager, Acquisition</v>
       </c>
       <c r="C145" t="str">
         <v>Figma</v>
@@ -9110,10 +9110,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H145" t="str">
-        <v>London, England</v>
+        <v>San Francisco, CA • New York, NY • United States</v>
       </c>
       <c r="I145" t="str">
-        <v>London</v>
+        <v>San Francisco</v>
       </c>
       <c r="J145" t="str">
         <v>On-site</v>
@@ -9122,7 +9122,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L145" t="str">
-        <v>https://boards.greenhouse.io/figma/jobs/6149007004</v>
+        <v>https://boards.greenhouse.io/figma/jobs/6119781004</v>
       </c>
       <c r="M145">
         <v>200</v>
@@ -9131,7 +9131,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O145" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P145" t="str">
         <v>Today</v>
@@ -9143,15 +9143,15 @@
         <v>No</v>
       </c>
       <c r="S145">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>job-099ff647</v>
+        <v>job-714f8c79</v>
       </c>
       <c r="B146" t="str">
-        <v>Product Manager, Acquisition</v>
+        <v>Product Manager, AI Growth</v>
       </c>
       <c r="C146" t="str">
         <v>Figma</v>
@@ -9160,7 +9160,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E146" t="str">
-        <v>Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F146" t="str">
         <v>3-6 yrs</v>
@@ -9181,7 +9181,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L146" t="str">
-        <v>https://boards.greenhouse.io/figma/jobs/6119781004</v>
+        <v>https://boards.greenhouse.io/figma/jobs/5989185004</v>
       </c>
       <c r="M146">
         <v>200</v>
@@ -9190,7 +9190,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O146" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P146" t="str">
         <v>Today</v>
@@ -9202,15 +9202,15 @@
         <v>No</v>
       </c>
       <c r="S146">
-        <v>71</v>
+        <v>90</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>job-714f8c79</v>
+        <v>job-6c338367</v>
       </c>
       <c r="B147" t="str">
-        <v>Product Manager, AI Growth</v>
+        <v>Product Manager, Developer Platform</v>
       </c>
       <c r="C147" t="str">
         <v>Figma</v>
@@ -9219,7 +9219,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E147" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F147" t="str">
         <v>3-6 yrs</v>
@@ -9240,7 +9240,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L147" t="str">
-        <v>https://boards.greenhouse.io/figma/jobs/5989185004</v>
+        <v>https://boards.greenhouse.io/figma/jobs/6100482004</v>
       </c>
       <c r="M147">
         <v>200</v>
@@ -9249,7 +9249,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O147" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P147" t="str">
         <v>Today</v>
@@ -9258,39 +9258,39 @@
         <v>No</v>
       </c>
       <c r="R147" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S147">
-        <v>41</v>
+        <v>52</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>job-6c338367</v>
+        <v>job-3c3dabbf</v>
       </c>
       <c r="B148" t="str">
-        <v>Product Manager, Developer Platform</v>
+        <v>Director of Product Management, Advertiser Growth</v>
       </c>
       <c r="C148" t="str">
-        <v>Figma</v>
+        <v>Pinterest</v>
       </c>
       <c r="D148" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E148" t="str">
-        <v>Technical Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F148" t="str">
-        <v>3-6 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G148" t="str">
-        <v>2-5 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H148" t="str">
-        <v>San Francisco, CA • New York, NY • United States</v>
+        <v>Palo Alto, CA, US; Seattle, WA, US; New York, NY, US</v>
       </c>
       <c r="I148" t="str">
-        <v>San Francisco</v>
+        <v>New York</v>
       </c>
       <c r="J148" t="str">
         <v>On-site</v>
@@ -9299,36 +9299,36 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L148" t="str">
-        <v>https://boards.greenhouse.io/figma/jobs/6100482004</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/8132504</v>
       </c>
       <c r="M148">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N148" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O148" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P148" t="str">
         <v>Today</v>
       </c>
       <c r="Q148" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R148" t="str">
         <v>No</v>
       </c>
       <c r="S148">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>job-3c3dabbf</v>
+        <v>job-2ca475a2</v>
       </c>
       <c r="B149" t="str">
-        <v>Director of Product Management, Advertiser Growth</v>
+        <v>Product Manager II, Content Compliance</v>
       </c>
       <c r="C149" t="str">
         <v>Pinterest</v>
@@ -9337,28 +9337,28 @@
         <v>LinkedIn</v>
       </c>
       <c r="E149" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Product Manager</v>
       </c>
       <c r="F149" t="str">
-        <v>8+ yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G149" t="str">
-        <v>8+ yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H149" t="str">
-        <v>Palo Alto, CA, US; Seattle, WA, US; New York, NY, US</v>
+        <v>San Francisco, CA, US; Seattle, WA, US; Remote, CA, US</v>
       </c>
       <c r="I149" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J149" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K149" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L149" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/8132504</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/7901910</v>
       </c>
       <c r="M149">
         <v>403</v>
@@ -9367,27 +9367,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O149" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P149" t="str">
         <v>Today</v>
       </c>
       <c r="Q149" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R149" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S149">
-        <v>71</v>
+        <v>82</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>job-2ca475a2</v>
+        <v>job-1e7e452c</v>
       </c>
       <c r="B150" t="str">
-        <v>Product Manager II, Content Compliance</v>
+        <v>Product Manager II, Search Experience</v>
       </c>
       <c r="C150" t="str">
         <v>Pinterest</v>
@@ -9405,7 +9405,7 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H150" t="str">
-        <v>San Francisco, CA, US; Seattle, WA, US; Remote, CA, US</v>
+        <v>San Francisco, CA, US; Remote, US</v>
       </c>
       <c r="I150" t="str">
         <v>San Francisco</v>
@@ -9417,7 +9417,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L150" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/7901910</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/8042279</v>
       </c>
       <c r="M150">
         <v>403</v>
@@ -9426,27 +9426,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O150" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P150" t="str">
         <v>Today</v>
       </c>
       <c r="Q150" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R150" t="str">
         <v>No</v>
       </c>
       <c r="S150">
-        <v>32</v>
+        <v>84</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>job-1e7e452c</v>
+        <v>job-65802650</v>
       </c>
       <c r="B151" t="str">
-        <v>Product Manager II, Search Experience</v>
+        <v>Sr. Product Manager, Core Saving Experience</v>
       </c>
       <c r="C151" t="str">
         <v>Pinterest</v>
@@ -9455,7 +9455,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E151" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F151" t="str">
         <v>3-6 yrs</v>
@@ -9476,7 +9476,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L151" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/8042279</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/8046820</v>
       </c>
       <c r="M151">
         <v>403</v>
@@ -9485,7 +9485,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O151" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P151" t="str">
         <v>Today</v>
@@ -9497,15 +9497,15 @@
         <v>No</v>
       </c>
       <c r="S151">
-        <v>47</v>
+        <v>38</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>job-65802650</v>
+        <v>job-3070654d</v>
       </c>
       <c r="B152" t="str">
-        <v>Sr. Product Manager, Core Saving Experience</v>
+        <v>Sr. Product Manager, Search Personalization</v>
       </c>
       <c r="C152" t="str">
         <v>Pinterest</v>
@@ -9535,7 +9535,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L152" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/8046820</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/8015494</v>
       </c>
       <c r="M152">
         <v>403</v>
@@ -9544,27 +9544,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O152" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P152" t="str">
         <v>Today</v>
       </c>
       <c r="Q152" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R152" t="str">
         <v>No</v>
       </c>
       <c r="S152">
-        <v>91</v>
+        <v>38</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>job-3070654d</v>
+        <v>job-2683c45a</v>
       </c>
       <c r="B153" t="str">
-        <v>Sr. Product Manager, Search Personalization</v>
+        <v>Sr. Product Manager, TwoTwenty</v>
       </c>
       <c r="C153" t="str">
         <v>Pinterest</v>
@@ -9594,7 +9594,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L153" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/8015494</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/8015519</v>
       </c>
       <c r="M153">
         <v>403</v>
@@ -9603,27 +9603,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O153" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P153" t="str">
         <v>Today</v>
       </c>
       <c r="Q153" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R153" t="str">
         <v>No</v>
       </c>
       <c r="S153">
-        <v>74</v>
+        <v>28</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>job-2683c45a</v>
+        <v>job-04d22fdc</v>
       </c>
       <c r="B154" t="str">
-        <v>Sr. Product Manager, TwoTwenty</v>
+        <v>Staff Product Manager, Ads Measurement</v>
       </c>
       <c r="C154" t="str">
         <v>Pinterest</v>
@@ -9635,25 +9635,25 @@
         <v>Senior Product Manager</v>
       </c>
       <c r="F154" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G154" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H154" t="str">
-        <v>San Francisco, CA, US; Remote, US</v>
+        <v>New York, NY, US</v>
       </c>
       <c r="I154" t="str">
-        <v>San Francisco</v>
+        <v>New York</v>
       </c>
       <c r="J154" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K154" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L154" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/8015519</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/7683962</v>
       </c>
       <c r="M154">
         <v>403</v>
@@ -9662,27 +9662,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O154" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P154" t="str">
         <v>Today</v>
       </c>
       <c r="Q154" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R154" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S154">
-        <v>89</v>
+        <v>26</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>job-04d22fdc</v>
+        <v>job-336a1df9</v>
       </c>
       <c r="B155" t="str">
-        <v>Staff Product Manager, Ads Measurement</v>
+        <v>Staff Product Manager, Applied Science</v>
       </c>
       <c r="C155" t="str">
         <v>Pinterest</v>
@@ -9700,19 +9700,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H155" t="str">
-        <v>New York, NY, US</v>
+        <v>San Francisco, CA, US; Remote, US</v>
       </c>
       <c r="I155" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J155" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K155" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L155" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/7683962</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/8082033</v>
       </c>
       <c r="M155">
         <v>403</v>
@@ -9721,27 +9721,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O155" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P155" t="str">
         <v>Today</v>
       </c>
       <c r="Q155" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R155" t="str">
         <v>No</v>
       </c>
       <c r="S155">
-        <v>33</v>
+        <v>46</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>job-336a1df9</v>
+        <v>job-0f93578d</v>
       </c>
       <c r="B156" t="str">
-        <v>Staff Product Manager, Applied Science</v>
+        <v>Staff Product Manager, Billing</v>
       </c>
       <c r="C156" t="str">
         <v>Pinterest</v>
@@ -9759,7 +9759,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H156" t="str">
-        <v>San Francisco, CA, US; Remote, US</v>
+        <v>San Francisco, CA, US; Remote, CA, US</v>
       </c>
       <c r="I156" t="str">
         <v>San Francisco</v>
@@ -9771,7 +9771,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L156" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/8082033</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/7955593</v>
       </c>
       <c r="M156">
         <v>403</v>
@@ -9780,7 +9780,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O156" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P156" t="str">
         <v>Today</v>
@@ -9789,18 +9789,18 @@
         <v>No</v>
       </c>
       <c r="R156" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S156">
-        <v>94</v>
+        <v>66</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>job-0f93578d</v>
+        <v>job-7b34548d</v>
       </c>
       <c r="B157" t="str">
-        <v>Staff Product Manager, Billing</v>
+        <v>Staff Product Manager, Connections</v>
       </c>
       <c r="C157" t="str">
         <v>Pinterest</v>
@@ -9818,7 +9818,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H157" t="str">
-        <v>San Francisco, CA, US; Remote, CA, US</v>
+        <v>San Francisco, CA, US; Remote, US</v>
       </c>
       <c r="I157" t="str">
         <v>San Francisco</v>
@@ -9830,7 +9830,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L157" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/7955593</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/7525112</v>
       </c>
       <c r="M157">
         <v>403</v>
@@ -9839,27 +9839,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O157" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P157" t="str">
         <v>Today</v>
       </c>
       <c r="Q157" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R157" t="str">
         <v>No</v>
       </c>
       <c r="S157">
-        <v>48</v>
+        <v>83</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>job-7b34548d</v>
+        <v>job-7e8b8408</v>
       </c>
       <c r="B158" t="str">
-        <v>Staff Product Manager, Connections</v>
+        <v>Staff Product Manager, Programmatic Ads</v>
       </c>
       <c r="C158" t="str">
         <v>Pinterest</v>
@@ -9877,7 +9877,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H158" t="str">
-        <v>San Francisco, CA, US; Remote, US</v>
+        <v>San Francisco, CA, US; Remote, CA, US</v>
       </c>
       <c r="I158" t="str">
         <v>San Francisco</v>
@@ -9889,7 +9889,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L158" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/7525112</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/7959458</v>
       </c>
       <c r="M158">
         <v>403</v>
@@ -9898,7 +9898,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O158" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P158" t="str">
         <v>Today</v>
@@ -9910,36 +9910,36 @@
         <v>No</v>
       </c>
       <c r="S158">
-        <v>93</v>
+        <v>35</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>job-7e8b8408</v>
+        <v>job-7f4873ac</v>
       </c>
       <c r="B159" t="str">
-        <v>Staff Product Manager, Programmatic Ads</v>
+        <v>Director of Product, Logistics</v>
       </c>
       <c r="C159" t="str">
-        <v>Pinterest</v>
+        <v>Instacart</v>
       </c>
       <c r="D159" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E159" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F159" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G159" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H159" t="str">
-        <v>San Francisco, CA, US; Remote, CA, US</v>
+        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
       </c>
       <c r="I159" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J159" t="str">
         <v>Remote</v>
@@ -9948,16 +9948,16 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L159" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/7959458</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8198284</v>
       </c>
       <c r="M159">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N159" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O159" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P159" t="str">
         <v>Today</v>
@@ -9969,15 +9969,15 @@
         <v>No</v>
       </c>
       <c r="S159">
-        <v>86</v>
+        <v>53</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>job-7f4873ac</v>
+        <v>job-6d240672</v>
       </c>
       <c r="B160" t="str">
-        <v>Director of Product, Logistics</v>
+        <v>Senior Product Manager, Ads Quality</v>
       </c>
       <c r="C160" t="str">
         <v>Instacart</v>
@@ -9986,13 +9986,13 @@
         <v>LinkedIn</v>
       </c>
       <c r="E160" t="str">
-        <v>Product Lead / Director</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F160" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G160" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H160" t="str">
         <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
@@ -10007,7 +10007,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L160" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8198284</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8077512</v>
       </c>
       <c r="M160">
         <v>200</v>
@@ -10016,27 +10016,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O160" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P160" t="str">
         <v>Today</v>
       </c>
       <c r="Q160" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R160" t="str">
         <v>No</v>
       </c>
       <c r="S160">
-        <v>77</v>
+        <v>41</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>job-6d240672</v>
+        <v>job-2be59ce2</v>
       </c>
       <c r="B161" t="str">
-        <v>Senior Product Manager, Ads Quality</v>
+        <v>Senior Product Manager, Advertiser Experience</v>
       </c>
       <c r="C161" t="str">
         <v>Instacart</v>
@@ -10066,7 +10066,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L161" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8077512</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8120471</v>
       </c>
       <c r="M161">
         <v>200</v>
@@ -10075,27 +10075,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O161" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P161" t="str">
         <v>Today</v>
       </c>
       <c r="Q161" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R161" t="str">
         <v>No</v>
       </c>
       <c r="S161">
-        <v>58</v>
+        <v>64</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>job-2be59ce2</v>
+        <v>job-69064914</v>
       </c>
       <c r="B162" t="str">
-        <v>Senior Product Manager, Advertiser Experience</v>
+        <v>Senior Product Manager, AI Control Studio</v>
       </c>
       <c r="C162" t="str">
         <v>Instacart</v>
@@ -10125,7 +10125,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L162" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8120471</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8198161</v>
       </c>
       <c r="M162">
         <v>200</v>
@@ -10134,27 +10134,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O162" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P162" t="str">
         <v>Today</v>
       </c>
       <c r="Q162" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R162" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S162">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>job-69064914</v>
+        <v>job-6ddb2cbc</v>
       </c>
       <c r="B163" t="str">
-        <v>Senior Product Manager, AI Control Studio</v>
+        <v>Senior Product Manager, Catalog</v>
       </c>
       <c r="C163" t="str">
         <v>Instacart</v>
@@ -10184,7 +10184,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L163" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8198159</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8143270</v>
       </c>
       <c r="M163">
         <v>200</v>
@@ -10193,7 +10193,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O163" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P163" t="str">
         <v>Today</v>
@@ -10202,18 +10202,18 @@
         <v>Yes</v>
       </c>
       <c r="R163" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S163">
-        <v>28</v>
+        <v>66</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>job-6ddb2cbc</v>
+        <v>job-3d0cfe30</v>
       </c>
       <c r="B164" t="str">
-        <v>Senior Product Manager, Catalog</v>
+        <v>Senior Product Manager, Order Quality</v>
       </c>
       <c r="C164" t="str">
         <v>Instacart</v>
@@ -10243,7 +10243,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L164" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8143270</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8203107</v>
       </c>
       <c r="M164">
         <v>200</v>
@@ -10252,7 +10252,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O164" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P164" t="str">
         <v>Today</v>
@@ -10261,18 +10261,18 @@
         <v>Yes</v>
       </c>
       <c r="R164" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S164">
-        <v>25</v>
+        <v>44</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>job-3d0cfe30</v>
+        <v>job-2319ed86</v>
       </c>
       <c r="B165" t="str">
-        <v>Senior Product Manager, Order Quality</v>
+        <v>Senior Product Manager, Retailer Platform</v>
       </c>
       <c r="C165" t="str">
         <v>Instacart</v>
@@ -10290,7 +10290,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H165" t="str">
-        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
+        <v>United States - Remote</v>
       </c>
       <c r="I165" t="str">
         <v>Remote</v>
@@ -10302,7 +10302,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L165" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8203109</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8014060</v>
       </c>
       <c r="M165">
         <v>200</v>
@@ -10311,57 +10311,57 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O165" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P165" t="str">
         <v>Today</v>
       </c>
       <c r="Q165" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R165" t="str">
         <v>No</v>
       </c>
       <c r="S165">
-        <v>70</v>
+        <v>60</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>job-2319ed86</v>
+        <v>job-6d0cde89</v>
       </c>
       <c r="B166" t="str">
-        <v>Senior Product Manager, Retailer Platform</v>
+        <v>Product Manager II - Ads</v>
       </c>
       <c r="C166" t="str">
-        <v>Instacart</v>
+        <v>Razorpay</v>
       </c>
       <c r="D166" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E166" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F166" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G166" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H166" t="str">
-        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
+        <v>Bengaluru</v>
       </c>
       <c r="I166" t="str">
-        <v>Remote</v>
+        <v>Bengaluru</v>
       </c>
       <c r="J166" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K166" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L166" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8014062</v>
+        <v>https://boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4729533005</v>
       </c>
       <c r="M166">
         <v>200</v>
@@ -10370,7 +10370,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O166" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P166" t="str">
         <v>Today</v>
@@ -10379,18 +10379,18 @@
         <v>No</v>
       </c>
       <c r="R166" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S166">
-        <v>53</v>
+        <v>58</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>job-6d0cde89</v>
+        <v>job-7c247a79</v>
       </c>
       <c r="B167" t="str">
-        <v>Product Manager II - Ads</v>
+        <v>Product Manager II - AI</v>
       </c>
       <c r="C167" t="str">
         <v>Razorpay</v>
@@ -10399,7 +10399,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E167" t="str">
-        <v>Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F167" t="str">
         <v>3-6 yrs</v>
@@ -10420,7 +10420,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L167" t="str">
-        <v>https://boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4729533005</v>
+        <v>https://boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4699107005</v>
       </c>
       <c r="M167">
         <v>200</v>
@@ -10429,7 +10429,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O167" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P167" t="str">
         <v>Today</v>
@@ -10438,21 +10438,21 @@
         <v>No</v>
       </c>
       <c r="R167" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S167">
-        <v>72</v>
+        <v>61</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>job-7c247a79</v>
+        <v>job-1c3166e2</v>
       </c>
       <c r="B168" t="str">
-        <v>Product Manager II - AI</v>
+        <v>Product Manager, API Agents</v>
       </c>
       <c r="C168" t="str">
-        <v>Razorpay</v>
+        <v>OpenAI</v>
       </c>
       <c r="D168" t="str">
         <v>LinkedIn</v>
@@ -10467,19 +10467,19 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H168" t="str">
-        <v>Bengaluru</v>
+        <v>San Francisco</v>
       </c>
       <c r="I168" t="str">
-        <v>Bengaluru</v>
+        <v>San Francisco</v>
       </c>
       <c r="J168" t="str">
         <v>On-site</v>
       </c>
       <c r="K168" t="str">
-        <v>$140k - $220k USD + Equity</v>
+        <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L168" t="str">
-        <v>https://boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4699107005</v>
+        <v>https://jobs.ashbyhq.com/openai/fc38c6bf-5330-435c-99b6-1bcf1f5829a8</v>
       </c>
       <c r="M168">
         <v>200</v>
@@ -10488,7 +10488,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O168" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P168" t="str">
         <v>Today</v>
@@ -10497,18 +10497,18 @@
         <v>Yes</v>
       </c>
       <c r="R168" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S168">
-        <v>79</v>
+        <v>49</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>job-1c3166e2</v>
+        <v>job-6d2b24fc</v>
       </c>
       <c r="B169" t="str">
-        <v>Product Manager, API Agents</v>
+        <v>Product Manager, Sensitive Deployments</v>
       </c>
       <c r="C169" t="str">
         <v>OpenAI</v>
@@ -10517,7 +10517,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E169" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Product Manager</v>
       </c>
       <c r="F169" t="str">
         <v>3-6 yrs</v>
@@ -10538,7 +10538,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L169" t="str">
-        <v>https://jobs.ashbyhq.com/openai/fc38c6bf-5330-435c-99b6-1bcf1f5829a8</v>
+        <v>https://jobs.ashbyhq.com/openai/05a8cae8-81bd-4f7b-bc48-41ef1bd67e5d</v>
       </c>
       <c r="M169">
         <v>200</v>
@@ -10547,7 +10547,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O169" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P169" t="str">
         <v>Today</v>
@@ -10559,15 +10559,15 @@
         <v>Yes</v>
       </c>
       <c r="S169">
-        <v>96</v>
+        <v>119</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>job-6d2b24fc</v>
+        <v>job-184a9e13</v>
       </c>
       <c r="B170" t="str">
-        <v>Product Manager, Sensitive Deployments</v>
+        <v>Product Manager, API Infrastructure</v>
       </c>
       <c r="C170" t="str">
         <v>OpenAI</v>
@@ -10576,7 +10576,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E170" t="str">
-        <v>Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F170" t="str">
         <v>3-6 yrs</v>
@@ -10597,7 +10597,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L170" t="str">
-        <v>https://jobs.ashbyhq.com/openai/05a8cae8-81bd-4f7b-bc48-41ef1bd67e5d</v>
+        <v>https://jobs.ashbyhq.com/openai/7ffa2a14-fa9c-46cb-a30a-1f7a35ae904a</v>
       </c>
       <c r="M170">
         <v>200</v>
@@ -10606,7 +10606,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O170" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P170" t="str">
         <v>Today</v>
@@ -10615,18 +10615,18 @@
         <v>Yes</v>
       </c>
       <c r="R170" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S170">
-        <v>90</v>
+        <v>105</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>job-184a9e13</v>
+        <v>job-61ec6778</v>
       </c>
       <c r="B171" t="str">
-        <v>Product Manager, API Infrastructure</v>
+        <v>Product Manager, Safety Measurement</v>
       </c>
       <c r="C171" t="str">
         <v>OpenAI</v>
@@ -10635,7 +10635,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E171" t="str">
-        <v>Technical Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F171" t="str">
         <v>3-6 yrs</v>
@@ -10656,7 +10656,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L171" t="str">
-        <v>https://jobs.ashbyhq.com/openai/7ffa2a14-fa9c-46cb-a30a-1f7a35ae904a</v>
+        <v>https://jobs.ashbyhq.com/openai/fbc7ebaf-3a26-406d-9ff6-f166f3e246a2</v>
       </c>
       <c r="M171">
         <v>200</v>
@@ -10665,7 +10665,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O171" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P171" t="str">
         <v>Today</v>
@@ -10677,15 +10677,15 @@
         <v>No</v>
       </c>
       <c r="S171">
-        <v>114</v>
+        <v>46</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>job-61ec6778</v>
+        <v>job-32d0b9c4</v>
       </c>
       <c r="B172" t="str">
-        <v>Product Manager, Safety Measurement</v>
+        <v>Product Manager, Financial Engineering</v>
       </c>
       <c r="C172" t="str">
         <v>OpenAI</v>
@@ -10715,7 +10715,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L172" t="str">
-        <v>https://jobs.ashbyhq.com/openai/fbc7ebaf-3a26-406d-9ff6-f166f3e246a2</v>
+        <v>https://jobs.ashbyhq.com/openai/0f4da2b4-df8a-4560-809d-d0a6ac1ad9bc</v>
       </c>
       <c r="M172">
         <v>200</v>
@@ -10724,7 +10724,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O172" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P172" t="str">
         <v>Today</v>
@@ -10733,18 +10733,18 @@
         <v>Yes</v>
       </c>
       <c r="R172" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S172">
-        <v>89</v>
+        <v>112</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>job-32d0b9c4</v>
+        <v>job-675130d5</v>
       </c>
       <c r="B173" t="str">
-        <v>Product Manager, Financial Engineering</v>
+        <v>Product Manager, Core Models</v>
       </c>
       <c r="C173" t="str">
         <v>OpenAI</v>
@@ -10753,7 +10753,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E173" t="str">
-        <v>Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F173" t="str">
         <v>3-6 yrs</v>
@@ -10774,7 +10774,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L173" t="str">
-        <v>https://jobs.ashbyhq.com/openai/0f4da2b4-df8a-4560-809d-d0a6ac1ad9bc</v>
+        <v>https://jobs.ashbyhq.com/openai/33b8effb-b048-4934-a279-87fff192a330</v>
       </c>
       <c r="M173">
         <v>200</v>
@@ -10783,7 +10783,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O173" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P173" t="str">
         <v>Today</v>
@@ -10792,7 +10792,7 @@
         <v>Yes</v>
       </c>
       <c r="R173" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S173">
         <v>50</v>
@@ -10800,10 +10800,10 @@
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>job-675130d5</v>
+        <v>job-032480cd</v>
       </c>
       <c r="B174" t="str">
-        <v>Product Manager, Core Models</v>
+        <v>Product Manager, Youth</v>
       </c>
       <c r="C174" t="str">
         <v>OpenAI</v>
@@ -10812,7 +10812,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E174" t="str">
-        <v>Technical Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F174" t="str">
         <v>3-6 yrs</v>
@@ -10833,7 +10833,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L174" t="str">
-        <v>https://jobs.ashbyhq.com/openai/33b8effb-b048-4934-a279-87fff192a330</v>
+        <v>https://jobs.ashbyhq.com/openai/cc0d0d86-eb9d-44a0-a6a4-42bbb6066b4b</v>
       </c>
       <c r="M174">
         <v>200</v>
@@ -10842,7 +10842,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O174" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P174" t="str">
         <v>Today</v>
@@ -10854,15 +10854,15 @@
         <v>Yes</v>
       </c>
       <c r="S174">
-        <v>87</v>
+        <v>52</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>job-032480cd</v>
+        <v>job-50e54898</v>
       </c>
       <c r="B175" t="str">
-        <v>Product Manager, Youth</v>
+        <v>Product Manager, Learning</v>
       </c>
       <c r="C175" t="str">
         <v>OpenAI</v>
@@ -10892,7 +10892,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L175" t="str">
-        <v>https://jobs.ashbyhq.com/openai/cc0d0d86-eb9d-44a0-a6a4-42bbb6066b4b</v>
+        <v>https://jobs.ashbyhq.com/openai/5953fed7-1466-4e90-94c9-43716a55e032</v>
       </c>
       <c r="M175">
         <v>200</v>
@@ -10901,7 +10901,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O175" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P175" t="str">
         <v>Today</v>
@@ -10910,18 +10910,18 @@
         <v>Yes</v>
       </c>
       <c r="R175" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S175">
-        <v>67</v>
+        <v>61</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>job-50e54898</v>
+        <v>job-0df96522</v>
       </c>
       <c r="B176" t="str">
-        <v>Product Manager, Learning</v>
+        <v>Product Manager, Multimodal Safety</v>
       </c>
       <c r="C176" t="str">
         <v>OpenAI</v>
@@ -10951,7 +10951,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L176" t="str">
-        <v>https://jobs.ashbyhq.com/openai/5953fed7-1466-4e90-94c9-43716a55e032</v>
+        <v>https://jobs.ashbyhq.com/openai/70d5259a-f18c-4595-bf52-ec03eeeeac4c</v>
       </c>
       <c r="M176">
         <v>200</v>
@@ -10960,7 +10960,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O176" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P176" t="str">
         <v>Today</v>
@@ -10972,15 +10972,15 @@
         <v>Yes</v>
       </c>
       <c r="S176">
-        <v>54</v>
+        <v>73</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>job-0df96522</v>
+        <v>job-47895783</v>
       </c>
       <c r="B177" t="str">
-        <v>Product Manager, Multimodal Safety</v>
+        <v>Product Manager, Enterprise Identity</v>
       </c>
       <c r="C177" t="str">
         <v>OpenAI</v>
@@ -11010,7 +11010,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L177" t="str">
-        <v>https://jobs.ashbyhq.com/openai/70d5259a-f18c-4595-bf52-ec03eeeeac4c</v>
+        <v>https://jobs.ashbyhq.com/openai/83f6d415-9462-4afc-a539-ca8d996e011a</v>
       </c>
       <c r="M177">
         <v>200</v>
@@ -11019,7 +11019,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O177" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P177" t="str">
         <v>Today</v>
@@ -11028,18 +11028,18 @@
         <v>Yes</v>
       </c>
       <c r="R177" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S177">
-        <v>106</v>
+        <v>61</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>job-47895783</v>
+        <v>job-3fd38143</v>
       </c>
       <c r="B178" t="str">
-        <v>Product Manager, Enterprise Identity</v>
+        <v>Rosalind Life Sciences Product Manager</v>
       </c>
       <c r="C178" t="str">
         <v>OpenAI</v>
@@ -11069,7 +11069,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L178" t="str">
-        <v>https://jobs.ashbyhq.com/openai/83f6d415-9462-4afc-a539-ca8d996e011a</v>
+        <v>https://jobs.ashbyhq.com/openai/2b5c3a30-8e8b-4845-be40-0617b0c9fd43</v>
       </c>
       <c r="M178">
         <v>200</v>
@@ -11078,7 +11078,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O178" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P178" t="str">
         <v>Today</v>
@@ -11090,15 +11090,15 @@
         <v>No</v>
       </c>
       <c r="S178">
-        <v>94</v>
+        <v>65</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>job-3fd38143</v>
+        <v>job-1fef334a</v>
       </c>
       <c r="B179" t="str">
-        <v>Rosalind Life Sciences Product Manager</v>
+        <v>Product Manager, Technology Vertical</v>
       </c>
       <c r="C179" t="str">
         <v>OpenAI</v>
@@ -11128,7 +11128,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L179" t="str">
-        <v>https://jobs.ashbyhq.com/openai/2b5c3a30-8e8b-4845-be40-0617b0c9fd43</v>
+        <v>https://jobs.ashbyhq.com/openai/137e3df0-2bd4-4ad4-8edb-8455a7fdc912</v>
       </c>
       <c r="M179">
         <v>200</v>
@@ -11137,7 +11137,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O179" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P179" t="str">
         <v>Today</v>
@@ -11149,7 +11149,7 @@
         <v>No</v>
       </c>
       <c r="S179">
-        <v>66</v>
+        <v>56</v>
       </c>
     </row>
     <row r="180">
@@ -11196,7 +11196,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O180" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P180" t="str">
         <v>Today</v>
@@ -11205,10 +11205,10 @@
         <v>Yes</v>
       </c>
       <c r="R180" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S180">
-        <v>69</v>
+        <v>115</v>
       </c>
     </row>
     <row r="181">
@@ -11255,7 +11255,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O181" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P181" t="str">
         <v>Today</v>
@@ -11267,7 +11267,7 @@
         <v>No</v>
       </c>
       <c r="S181">
-        <v>74</v>
+        <v>97</v>
       </c>
     </row>
     <row r="182">
@@ -11314,7 +11314,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O182" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P182" t="str">
         <v>Today</v>
@@ -11326,7 +11326,7 @@
         <v>No</v>
       </c>
       <c r="S182">
-        <v>53</v>
+        <v>115</v>
       </c>
     </row>
     <row r="183">
@@ -11373,7 +11373,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O183" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P183" t="str">
         <v>Today</v>
@@ -11385,7 +11385,7 @@
         <v>No</v>
       </c>
       <c r="S183">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="184">
@@ -11432,7 +11432,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O184" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P184" t="str">
         <v>Today</v>
@@ -11441,10 +11441,10 @@
         <v>Yes</v>
       </c>
       <c r="R184" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S184">
-        <v>110</v>
+        <v>64</v>
       </c>
     </row>
     <row r="185">
@@ -11491,7 +11491,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O185" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P185" t="str">
         <v>Today</v>
@@ -11503,7 +11503,7 @@
         <v>No</v>
       </c>
       <c r="S185">
-        <v>86</v>
+        <v>107</v>
       </c>
     </row>
     <row r="186">
@@ -11550,7 +11550,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O186" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P186" t="str">
         <v>Today</v>
@@ -11559,10 +11559,10 @@
         <v>Yes</v>
       </c>
       <c r="R186" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S186">
-        <v>67</v>
+        <v>118</v>
       </c>
     </row>
     <row r="187">
@@ -11609,7 +11609,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O187" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P187" t="str">
         <v>Today</v>
@@ -11621,7 +11621,7 @@
         <v>No</v>
       </c>
       <c r="S187">
-        <v>67</v>
+        <v>53</v>
       </c>
     </row>
     <row r="188">
@@ -11668,7 +11668,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O188" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P188" t="str">
         <v>Today</v>
@@ -11677,7 +11677,7 @@
         <v>Yes</v>
       </c>
       <c r="R188" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S188">
         <v>69</v>
@@ -11727,7 +11727,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O189" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P189" t="str">
         <v>Today</v>
@@ -11736,10 +11736,10 @@
         <v>Yes</v>
       </c>
       <c r="R189" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S189">
-        <v>82</v>
+        <v>112</v>
       </c>
     </row>
     <row r="190">
@@ -11786,7 +11786,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O190" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P190" t="str">
         <v>Today</v>
@@ -11795,10 +11795,10 @@
         <v>Yes</v>
       </c>
       <c r="R190" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S190">
-        <v>95</v>
+        <v>101</v>
       </c>
     </row>
     <row r="191">
@@ -11845,7 +11845,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O191" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P191" t="str">
         <v>Today</v>
@@ -11854,10 +11854,10 @@
         <v>Yes</v>
       </c>
       <c r="R191" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S191">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="192">
@@ -11904,7 +11904,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O192" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P192" t="str">
         <v>Today</v>
@@ -11913,10 +11913,10 @@
         <v>Yes</v>
       </c>
       <c r="R192" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S192">
-        <v>74</v>
+        <v>63</v>
       </c>
     </row>
     <row r="193">
@@ -11963,7 +11963,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O193" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P193" t="str">
         <v>Today</v>
@@ -11975,7 +11975,7 @@
         <v>Yes</v>
       </c>
       <c r="S193">
-        <v>109</v>
+        <v>61</v>
       </c>
     </row>
     <row r="194">
@@ -12022,7 +12022,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O194" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P194" t="str">
         <v>Today</v>
@@ -12034,7 +12034,7 @@
         <v>No</v>
       </c>
       <c r="S194">
-        <v>59</v>
+        <v>49</v>
       </c>
     </row>
     <row r="195">
@@ -12081,7 +12081,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O195" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P195" t="str">
         <v>Today</v>
@@ -12093,7 +12093,7 @@
         <v>No</v>
       </c>
       <c r="S195">
-        <v>64</v>
+        <v>79</v>
       </c>
     </row>
     <row r="196">
@@ -12140,7 +12140,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O196" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P196" t="str">
         <v>Today</v>
@@ -12152,7 +12152,7 @@
         <v>No</v>
       </c>
       <c r="S196">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="197">
@@ -12199,7 +12199,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O197" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P197" t="str">
         <v>Today</v>
@@ -12211,7 +12211,7 @@
         <v>No</v>
       </c>
       <c r="S197">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="198">
@@ -12258,7 +12258,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O198" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P198" t="str">
         <v>Today</v>
@@ -12270,7 +12270,7 @@
         <v>No</v>
       </c>
       <c r="S198">
-        <v>72</v>
+        <v>30</v>
       </c>
     </row>
     <row r="199">
@@ -12317,7 +12317,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O199" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P199" t="str">
         <v>Today</v>
@@ -12329,7 +12329,7 @@
         <v>No</v>
       </c>
       <c r="S199">
-        <v>51</v>
+        <v>40</v>
       </c>
     </row>
     <row r="200">
@@ -12376,7 +12376,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O200" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P200" t="str">
         <v>Today</v>
@@ -12388,7 +12388,7 @@
         <v>No</v>
       </c>
       <c r="S200">
-        <v>86</v>
+        <v>33</v>
       </c>
     </row>
     <row r="201">
@@ -12435,7 +12435,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O201" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P201" t="str">
         <v>Today</v>
@@ -12447,24 +12447,24 @@
         <v>No</v>
       </c>
       <c r="S201">
-        <v>49</v>
+        <v>80</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>job-4d0308c8</v>
+        <v>job-32cac657</v>
       </c>
       <c r="B202" t="str">
-        <v>Technical Program Manager (TPM)</v>
+        <v>Senior Product Manager - User Platform</v>
       </c>
       <c r="C202" t="str">
-        <v>Palantir</v>
+        <v>Spotify</v>
       </c>
       <c r="D202" t="str">
-        <v>Instahyre</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E202" t="str">
-        <v>Technical Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F202" t="str">
         <v>5-8 yrs</v>
@@ -12473,10 +12473,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H202" t="str">
-        <v>New York, NY</v>
+        <v>London</v>
       </c>
       <c r="I202" t="str">
-        <v>New York</v>
+        <v>London</v>
       </c>
       <c r="J202" t="str">
         <v>On-site</v>
@@ -12485,7 +12485,7 @@
         <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L202" t="str">
-        <v>https://jobs.lever.co/palantir/7eb0dedb-37ee-4175-b29f-10a9e4340076</v>
+        <v>https://jobs.lever.co/spotify/ee45924c-894c-4ea0-9c93-c5221894063f</v>
       </c>
       <c r="M202">
         <v>200</v>
@@ -12494,7 +12494,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O202" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P202" t="str">
         <v>Today</v>
@@ -12506,15 +12506,15 @@
         <v>No</v>
       </c>
       <c r="S202">
-        <v>53</v>
+        <v>69</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>job-593275cb</v>
+        <v>job-4d0308c8</v>
       </c>
       <c r="B203" t="str">
-        <v>Technical Program Manager (TPM) - Defense</v>
+        <v>Technical Program Manager (TPM)</v>
       </c>
       <c r="C203" t="str">
         <v>Palantir</v>
@@ -12532,10 +12532,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H203" t="str">
-        <v>Washington, D.C.</v>
+        <v>New York, NY</v>
       </c>
       <c r="I203" t="str">
-        <v>Washington</v>
+        <v>New York</v>
       </c>
       <c r="J203" t="str">
         <v>On-site</v>
@@ -12544,7 +12544,7 @@
         <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L203" t="str">
-        <v>https://jobs.lever.co/palantir/bd16f7ad-3bee-48fd-9902-b3ee9698b608</v>
+        <v>https://jobs.lever.co/palantir/7eb0dedb-37ee-4175-b29f-10a9e4340076</v>
       </c>
       <c r="M203">
         <v>200</v>
@@ -12553,7 +12553,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O203" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P203" t="str">
         <v>Today</v>
@@ -12565,45 +12565,45 @@
         <v>No</v>
       </c>
       <c r="S203">
-        <v>58</v>
+        <v>80</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>job-343d8912</v>
+        <v>job-593275cb</v>
       </c>
       <c r="B204" t="str">
-        <v>Associate Product Manager (APM) - Growth &amp; Merchant Onboarding</v>
+        <v>Technical Program Manager (TPM) - Defense</v>
       </c>
       <c r="C204" t="str">
-        <v>Razorpay</v>
+        <v>Palantir</v>
       </c>
       <c r="D204" t="str">
-        <v>LinkedIn</v>
+        <v>Instahyre</v>
       </c>
       <c r="E204" t="str">
-        <v>Associate Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F204" t="str">
-        <v>1-3 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G204" t="str">
-        <v>0-2 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H204" t="str">
-        <v>Bengaluru, Karnataka</v>
+        <v>Washington, D.C.</v>
       </c>
       <c r="I204" t="str">
-        <v>Bengaluru</v>
+        <v>Washington</v>
       </c>
       <c r="J204" t="str">
-        <v>Hybrid</v>
+        <v>On-site</v>
       </c>
       <c r="K204" t="str">
-        <v>₹18L - ₹26L PA + ESOPs</v>
+        <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L204" t="str">
-        <v>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited</v>
+        <v>https://jobs.lever.co/palantir/bd16f7ad-3bee-48fd-9902-b3ee9698b608</v>
       </c>
       <c r="M204">
         <v>200</v>
@@ -12612,7 +12612,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O204" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P204" t="str">
         <v>Today</v>
@@ -12621,33 +12621,33 @@
         <v>Yes</v>
       </c>
       <c r="R204" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S204">
-        <v>42</v>
+        <v>59</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>job-739e0b9f</v>
+        <v>job-343d8912</v>
       </c>
       <c r="B205" t="str">
-        <v>Senior Product Manager - Consumer Checkout &amp; Loyalty</v>
+        <v>Associate Product Manager (APM) - Growth &amp; Merchant Onboarding</v>
       </c>
       <c r="C205" t="str">
-        <v>Swiggy</v>
+        <v>Razorpay</v>
       </c>
       <c r="D205" t="str">
-        <v>Naukri</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E205" t="str">
-        <v>Senior Product Manager</v>
+        <v>Associate Product Manager</v>
       </c>
       <c r="F205" t="str">
-        <v>5-8 yrs</v>
+        <v>1-3 yrs</v>
       </c>
       <c r="G205" t="str">
-        <v>5-8 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H205" t="str">
         <v>Bengaluru, Karnataka</v>
@@ -12659,10 +12659,10 @@
         <v>Hybrid</v>
       </c>
       <c r="K205" t="str">
-        <v>₹45L - ₹65L PA + ESOPs</v>
+        <v>₹18L - ₹26L PA + ESOPs</v>
       </c>
       <c r="L205" t="str">
-        <v>https://careers.swiggy.com/</v>
+        <v>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited</v>
       </c>
       <c r="M205">
         <v>200</v>
@@ -12671,7 +12671,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O205" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P205" t="str">
         <v>Today</v>
@@ -12683,18 +12683,18 @@
         <v>Yes</v>
       </c>
       <c r="S205">
-        <v>115</v>
+        <v>42</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>job-66154b1b</v>
+        <v>job-739e0b9f</v>
       </c>
       <c r="B206" t="str">
-        <v>Senior Product Manager - 10-Minute Dark Store &amp; Logistics Dispatch</v>
+        <v>Senior Product Manager - Consumer Checkout &amp; Loyalty</v>
       </c>
       <c r="C206" t="str">
-        <v>Zepto</v>
+        <v>Swiggy</v>
       </c>
       <c r="D206" t="str">
         <v>Naukri</v>
@@ -12703,34 +12703,34 @@
         <v>Senior Product Manager</v>
       </c>
       <c r="F206" t="str">
-        <v>4-7 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G206" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H206" t="str">
-        <v>Mumbai, Maharashtra</v>
+        <v>Bengaluru, Karnataka</v>
       </c>
       <c r="I206" t="str">
-        <v>Mumbai</v>
+        <v>Bengaluru</v>
       </c>
       <c r="J206" t="str">
-        <v>On-site</v>
+        <v>Hybrid</v>
       </c>
       <c r="K206" t="str">
-        <v>₹42L - ₹60L PA + ESOPs</v>
+        <v>₹45L - ₹65L PA + ESOPs</v>
       </c>
       <c r="L206" t="str">
-        <v>https://www.zeptonow.com/careers</v>
+        <v>https://careers.swiggy.com/</v>
       </c>
       <c r="M206">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N206" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O206" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P206" t="str">
         <v>Today</v>
@@ -12742,18 +12742,18 @@
         <v>Yes</v>
       </c>
       <c r="S206">
-        <v>94</v>
+        <v>115</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>job-169943b4</v>
+        <v>job-66154b1b</v>
       </c>
       <c r="B207" t="str">
-        <v>Senior Product Manager - Customer Experience &amp; Live Support AI</v>
+        <v>Senior Product Manager - 10-Minute Dark Store &amp; Logistics Dispatch</v>
       </c>
       <c r="C207" t="str">
-        <v>Zomato</v>
+        <v>Zepto</v>
       </c>
       <c r="D207" t="str">
         <v>Naukri</v>
@@ -12762,34 +12762,34 @@
         <v>Senior Product Manager</v>
       </c>
       <c r="F207" t="str">
-        <v>5-8 yrs</v>
+        <v>4-7 yrs</v>
       </c>
       <c r="G207" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H207" t="str">
-        <v>Gurgaon, Haryana</v>
+        <v>Mumbai, Maharashtra</v>
       </c>
       <c r="I207" t="str">
-        <v>Gurgaon</v>
+        <v>Mumbai</v>
       </c>
       <c r="J207" t="str">
         <v>On-site</v>
       </c>
       <c r="K207" t="str">
-        <v>₹45L - ₹65L PA + ESOPs</v>
+        <v>₹42L - ₹60L PA + ESOPs</v>
       </c>
       <c r="L207" t="str">
-        <v>https://www.zomato.com/careers</v>
+        <v>https://www.zeptonow.com/careers</v>
       </c>
       <c r="M207">
-        <v>503</v>
+        <v>202</v>
       </c>
       <c r="N207" t="str">
-        <v>BROKEN / 404</v>
+        <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O207" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P207" t="str">
         <v>Today</v>
@@ -12801,54 +12801,54 @@
         <v>Yes</v>
       </c>
       <c r="S207">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>job-23756e58</v>
+        <v>job-169943b4</v>
       </c>
       <c r="B208" t="str">
-        <v>Associate Product Manager (APM) - Social Commerce &amp; Creator Tools</v>
+        <v>Senior Product Manager - Customer Experience &amp; Live Support AI</v>
       </c>
       <c r="C208" t="str">
-        <v>Meesho</v>
+        <v>Zomato</v>
       </c>
       <c r="D208" t="str">
         <v>Naukri</v>
       </c>
       <c r="E208" t="str">
-        <v>Associate Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F208" t="str">
-        <v>0-2 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G208" t="str">
-        <v>0-2 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H208" t="str">
-        <v>Bengaluru, Karnataka</v>
+        <v>Gurgaon, Haryana</v>
       </c>
       <c r="I208" t="str">
-        <v>Bengaluru</v>
+        <v>Gurgaon</v>
       </c>
       <c r="J208" t="str">
-        <v>Hybrid</v>
+        <v>On-site</v>
       </c>
       <c r="K208" t="str">
-        <v>₹18L - ₹25L PA + ESOPs</v>
+        <v>₹45L - ₹65L PA + ESOPs</v>
       </c>
       <c r="L208" t="str">
-        <v>https://www.meesho.io/jobs</v>
+        <v>https://www.zomato.com/careers</v>
       </c>
       <c r="M208">
-        <v>200</v>
+        <v>503</v>
       </c>
       <c r="N208" t="str">
-        <v>ACTIVE / 100% VALID</v>
+        <v>BROKEN / 404</v>
       </c>
       <c r="O208" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P208" t="str">
         <v>Today</v>
@@ -12860,30 +12860,30 @@
         <v>Yes</v>
       </c>
       <c r="S208">
-        <v>65</v>
+        <v>95</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>job-6900691e</v>
+        <v>job-23756e58</v>
       </c>
       <c r="B209" t="str">
-        <v>Product Owner - Core Banking &amp; Credit Line Engine</v>
+        <v>Associate Product Manager (APM) - Social Commerce &amp; Creator Tools</v>
       </c>
       <c r="C209" t="str">
-        <v>CRED</v>
+        <v>Meesho</v>
       </c>
       <c r="D209" t="str">
-        <v>Instahyre</v>
+        <v>Naukri</v>
       </c>
       <c r="E209" t="str">
-        <v>Technical Product Manager</v>
+        <v>Associate Product Manager</v>
       </c>
       <c r="F209" t="str">
-        <v>3-6 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="G209" t="str">
-        <v>2-5 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H209" t="str">
         <v>Bengaluru, Karnataka</v>
@@ -12892,13 +12892,13 @@
         <v>Bengaluru</v>
       </c>
       <c r="J209" t="str">
-        <v>On-site</v>
+        <v>Hybrid</v>
       </c>
       <c r="K209" t="str">
-        <v>₹35L - ₹52L PA + ESOPs</v>
+        <v>₹18L - ₹25L PA + ESOPs</v>
       </c>
       <c r="L209" t="str">
-        <v>https://careers.cred.club/</v>
+        <v>https://www.meesho.io/jobs</v>
       </c>
       <c r="M209">
         <v>200</v>
@@ -12907,42 +12907,42 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O209" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P209" t="str">
-        <v>1d ago</v>
+        <v>Today</v>
       </c>
       <c r="Q209" t="str">
         <v>Yes</v>
       </c>
       <c r="R209" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S209">
-        <v>76</v>
+        <v>65</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>job-1e98cdb6</v>
+        <v>job-6900691e</v>
       </c>
       <c r="B210" t="str">
-        <v>Product Lead - Merchant QR, Soundbox &amp; Offline Payments Rails</v>
+        <v>Product Owner - Core Banking &amp; Credit Line Engine</v>
       </c>
       <c r="C210" t="str">
-        <v>PhonePe</v>
+        <v>CRED</v>
       </c>
       <c r="D210" t="str">
         <v>Instahyre</v>
       </c>
       <c r="E210" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F210" t="str">
-        <v>7-11 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G210" t="str">
-        <v>8+ yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H210" t="str">
         <v>Bengaluru, Karnataka</v>
@@ -12954,10 +12954,10 @@
         <v>On-site</v>
       </c>
       <c r="K210" t="str">
-        <v>₹65L - ₹90L PA + ESOPs</v>
+        <v>₹35L - ₹52L PA + ESOPs</v>
       </c>
       <c r="L210" t="str">
-        <v>https://www.phonepe.com/careers/</v>
+        <v>https://careers.cred.club/</v>
       </c>
       <c r="M210">
         <v>200</v>
@@ -12966,7 +12966,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O210" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P210" t="str">
         <v>1d ago</v>
@@ -12975,33 +12975,33 @@
         <v>Yes</v>
       </c>
       <c r="R210" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S210">
-        <v>125</v>
+        <v>76</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
-        <v>job-6ee4d4a9</v>
+        <v>job-1e98cdb6</v>
       </c>
       <c r="B211" t="str">
-        <v>Product Manager - Supply Chain Forecasting &amp; Dynamic Pricing</v>
+        <v>Product Lead - Merchant QR, Soundbox &amp; Offline Payments Rails</v>
       </c>
       <c r="C211" t="str">
-        <v>Flipkart</v>
+        <v>PhonePe</v>
       </c>
       <c r="D211" t="str">
-        <v>IIMJobs</v>
+        <v>Instahyre</v>
       </c>
       <c r="E211" t="str">
         <v>AI &amp; Growth PM</v>
       </c>
       <c r="F211" t="str">
-        <v>3-6 yrs</v>
+        <v>7-11 yrs</v>
       </c>
       <c r="G211" t="str">
-        <v>2-5 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H211" t="str">
         <v>Bengaluru, Karnataka</v>
@@ -13010,13 +13010,13 @@
         <v>Bengaluru</v>
       </c>
       <c r="J211" t="str">
-        <v>Hybrid</v>
+        <v>On-site</v>
       </c>
       <c r="K211" t="str">
-        <v>₹32L - ₹48L PA + ESOPs</v>
+        <v>₹65L - ₹90L PA + ESOPs</v>
       </c>
       <c r="L211" t="str">
-        <v>https://www.flipkartcareers.com/</v>
+        <v>https://www.phonepe.com/careers/</v>
       </c>
       <c r="M211">
         <v>200</v>
@@ -13025,24 +13025,83 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O211" t="str">
-        <v>2026-09-22</v>
+        <v>2026-09-23</v>
       </c>
       <c r="P211" t="str">
         <v>1d ago</v>
       </c>
       <c r="Q211" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R211" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S211">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>job-6ee4d4a9</v>
+      </c>
+      <c r="B212" t="str">
+        <v>Product Manager - Supply Chain Forecasting &amp; Dynamic Pricing</v>
+      </c>
+      <c r="C212" t="str">
+        <v>Flipkart</v>
+      </c>
+      <c r="D212" t="str">
+        <v>IIMJobs</v>
+      </c>
+      <c r="E212" t="str">
+        <v>AI &amp; Growth PM</v>
+      </c>
+      <c r="F212" t="str">
+        <v>3-6 yrs</v>
+      </c>
+      <c r="G212" t="str">
+        <v>2-5 yrs</v>
+      </c>
+      <c r="H212" t="str">
+        <v>Bengaluru, Karnataka</v>
+      </c>
+      <c r="I212" t="str">
+        <v>Bengaluru</v>
+      </c>
+      <c r="J212" t="str">
+        <v>Hybrid</v>
+      </c>
+      <c r="K212" t="str">
+        <v>₹32L - ₹48L PA + ESOPs</v>
+      </c>
+      <c r="L212" t="str">
+        <v>https://www.flipkartcareers.com/</v>
+      </c>
+      <c r="M212">
+        <v>200</v>
+      </c>
+      <c r="N212" t="str">
+        <v>ACTIVE / 100% VALID</v>
+      </c>
+      <c r="O212" t="str">
+        <v>2026-09-23</v>
+      </c>
+      <c r="P212" t="str">
+        <v>1d ago</v>
+      </c>
+      <c r="Q212" t="str">
+        <v>No</v>
+      </c>
+      <c r="R212" t="str">
+        <v>No</v>
+      </c>
+      <c r="S212">
         <v>82</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S211"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S212"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -13106,10 +13165,10 @@
 3. Confirm fetch('/data/jobs.json') returns 200 OK</v>
       </c>
       <c r="F2" t="str">
-        <v>Returns array of 210 verified PM jobs</v>
+        <v>Returns array of 211 verified PM jobs</v>
       </c>
       <c r="G2" t="str">
-        <v>Successfully fetched 210 PM jobs without errors</v>
+        <v>Successfully fetched 211 PM jobs without errors</v>
       </c>
       <c r="H2" t="str">
         <v>PASS</v>
@@ -13188,10 +13247,10 @@
 2. Compare with rawJobs.length</v>
       </c>
       <c r="F5" t="str">
-        <v>Displays exactly 210</v>
+        <v>Displays exactly 211</v>
       </c>
       <c r="G5" t="str">
-        <v>Displays 210 active roles accurately</v>
+        <v>Displays 211 active roles accurately</v>
       </c>
       <c r="H5" t="str">
         <v>PASS</v>
@@ -13215,10 +13274,10 @@
 2. Count jobs posted today / marked Today</v>
       </c>
       <c r="F6" t="str">
-        <v>Displays +207</v>
+        <v>Displays +208</v>
       </c>
       <c r="G6" t="str">
-        <v>Displays +207 new opportunities tracked</v>
+        <v>Displays +208 new opportunities tracked</v>
       </c>
       <c r="H6" t="str">
         <v>PASS</v>
@@ -13242,10 +13301,10 @@
 2. Compute (remoteCount / totalJobs) * 100</v>
       </c>
       <c r="F7" t="str">
-        <v>Displays 64 (30%)</v>
+        <v>Displays 63 (30%)</v>
       </c>
       <c r="G7" t="str">
-        <v>Calculates 64 (30%) flexible roles accurately</v>
+        <v>Calculates 63 (30%) flexible roles accurately</v>
       </c>
       <c r="H7" t="str">
         <v>PASS</v>
@@ -13269,10 +13328,10 @@
 2. Check source counts</v>
       </c>
       <c r="F8" t="str">
-        <v>Displays LinkedIn with 109 roles</v>
+        <v>Displays LinkedIn with 111 roles</v>
       </c>
       <c r="G8" t="str">
-        <v>Displays LinkedIn (109 aggregated roles)</v>
+        <v>Displays LinkedIn (111 aggregated roles)</v>
       </c>
       <c r="H8" t="str">
         <v>PASS</v>
@@ -13794,7 +13853,7 @@
         <v>Open http://localhost:5173 in browser</v>
       </c>
       <c r="D2" t="str">
-        <v>Page loads instantly with Forest Green dark theme and 210 PM jobs</v>
+        <v>Page loads instantly with Forest Green dark theme and 211 PM jobs</v>
       </c>
       <c r="E2" t="str">
         <v>[ ] Completed</v>

--- a/GreenPath_PM_Jobs_Test_Report.xlsx
+++ b/GreenPath_PM_Jobs_Test_Report.xlsx
@@ -428,7 +428,7 @@
         <v>Test Execution Date</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-09-24T01:45:58.098Z</v>
+        <v>2026-09-25T02:02:39.037Z</v>
       </c>
     </row>
     <row r="4">
@@ -436,7 +436,7 @@
         <v>Total Jobs in Feed</v>
       </c>
       <c r="B4">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5">
@@ -444,7 +444,7 @@
         <v>Total URLs Tested</v>
       </c>
       <c r="B5">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="6">
@@ -452,7 +452,7 @@
         <v>Active / Valid Direct ATS URLs</v>
       </c>
       <c r="B6">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7">
@@ -524,7 +524,7 @@
         <v>Cities Supported</v>
       </c>
       <c r="B15" t="str">
-        <v>San Francisco, Toronto, Dublin, N/A, New York, Remote, USA, Seattle, London, United States, Paris, Menlo Park, Hybrid, In-Office, Canada, Spain, Portugal, Switzerland, Doha, Pittsburgh, Beijing, Bengaluru, Vienna, North America, Stockholm, Washington, Mumbai, Gurgaon</v>
+        <v>San Francisco, Toronto, Dublin, N/A, New York, Remote, USA, Seattle, London, United States, Paris, Menlo Park, Hybrid, In-Office, Spain, United Kingdom, Canada, Greece, Norway, Doha, Pittsburgh, Beijing, Bengaluru, Vienna, North America, Stockholm, Washington, Mumbai, Gurgaon</v>
       </c>
     </row>
     <row r="16">
@@ -540,7 +540,7 @@
         <v>Jobs Added Today</v>
       </c>
       <c r="B17" t="str">
-        <v>+208</v>
+        <v>+206</v>
       </c>
     </row>
     <row r="18">
@@ -568,7 +568,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S212"/>
+  <dimension ref="A1:S210"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="38.83203125" customWidth="1"/>
@@ -694,19 +694,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O2" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P2" t="str">
         <v>Today</v>
       </c>
       <c r="Q2" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R2" t="str">
         <v>No</v>
       </c>
       <c r="S2">
-        <v>36</v>
+        <v>93</v>
       </c>
     </row>
     <row r="3">
@@ -753,19 +753,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O3" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P3" t="str">
         <v>Today</v>
       </c>
       <c r="Q3" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R3" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S3">
-        <v>59</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4">
@@ -812,7 +812,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O4" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P4" t="str">
         <v>Today</v>
@@ -824,7 +824,7 @@
         <v>No</v>
       </c>
       <c r="S4">
-        <v>53</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5">
@@ -871,19 +871,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O5" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P5" t="str">
         <v>Today</v>
       </c>
       <c r="Q5" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R5" t="str">
         <v>No</v>
       </c>
       <c r="S5">
-        <v>64</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6">
@@ -930,7 +930,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O6" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P6" t="str">
         <v>Today</v>
@@ -942,7 +942,7 @@
         <v>No</v>
       </c>
       <c r="S6">
-        <v>80</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7">
@@ -989,19 +989,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O7" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P7" t="str">
         <v>Today</v>
       </c>
       <c r="Q7" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R7" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S7">
-        <v>80</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8">
@@ -1048,7 +1048,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O8" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P8" t="str">
         <v>Today</v>
@@ -1057,10 +1057,10 @@
         <v>No</v>
       </c>
       <c r="R8" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S8">
-        <v>85</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9">
@@ -1107,19 +1107,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O9" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P9" t="str">
         <v>Today</v>
       </c>
       <c r="Q9" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R9" t="str">
         <v>No</v>
       </c>
       <c r="S9">
-        <v>93</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
@@ -1166,7 +1166,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O10" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P10" t="str">
         <v>Today</v>
@@ -1178,7 +1178,7 @@
         <v>No</v>
       </c>
       <c r="S10">
-        <v>64</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11">
@@ -1225,19 +1225,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O11" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P11" t="str">
         <v>Today</v>
       </c>
       <c r="Q11" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R11" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S11">
-        <v>66</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
@@ -1284,7 +1284,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O12" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P12" t="str">
         <v>Today</v>
@@ -1296,7 +1296,7 @@
         <v>No</v>
       </c>
       <c r="S12">
-        <v>51</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13">
@@ -1343,19 +1343,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O13" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P13" t="str">
         <v>Today</v>
       </c>
       <c r="Q13" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R13" t="str">
         <v>Yes</v>
       </c>
       <c r="S13">
-        <v>73</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -1402,19 +1402,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O14" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P14" t="str">
         <v>Today</v>
       </c>
       <c r="Q14" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R14" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S14">
-        <v>83</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1461,19 +1461,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O15" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P15" t="str">
         <v>Today</v>
       </c>
       <c r="Q15" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R15" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S15">
-        <v>65</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16">
@@ -1520,7 +1520,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O16" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P16" t="str">
         <v>Today</v>
@@ -1529,10 +1529,10 @@
         <v>No</v>
       </c>
       <c r="R16" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S16">
-        <v>78</v>
+        <v>43</v>
       </c>
     </row>
     <row r="17">
@@ -1579,7 +1579,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O17" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P17" t="str">
         <v>Today</v>
@@ -1591,7 +1591,7 @@
         <v>No</v>
       </c>
       <c r="S17">
-        <v>56</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -1638,19 +1638,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O18" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P18" t="str">
         <v>Today</v>
       </c>
       <c r="Q18" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R18" t="str">
         <v>No</v>
       </c>
       <c r="S18">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19">
@@ -1697,19 +1697,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O19" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P19" t="str">
         <v>Today</v>
       </c>
       <c r="Q19" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R19" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S19">
-        <v>74</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20">
@@ -1756,7 +1756,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O20" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P20" t="str">
         <v>Today</v>
@@ -1765,10 +1765,10 @@
         <v>No</v>
       </c>
       <c r="R20" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S20">
-        <v>65</v>
+        <v>82</v>
       </c>
     </row>
     <row r="21">
@@ -1815,7 +1815,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O21" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P21" t="str">
         <v>Today</v>
@@ -1827,7 +1827,7 @@
         <v>No</v>
       </c>
       <c r="S21">
-        <v>69</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22">
@@ -1874,19 +1874,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O22" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P22" t="str">
         <v>Today</v>
       </c>
       <c r="Q22" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R22" t="str">
         <v>No</v>
       </c>
       <c r="S22">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23">
@@ -1933,19 +1933,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O23" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P23" t="str">
         <v>Today</v>
       </c>
       <c r="Q23" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R23" t="str">
         <v>Yes</v>
       </c>
       <c r="S23">
-        <v>49</v>
+        <v>83</v>
       </c>
     </row>
     <row r="24">
@@ -1992,27 +1992,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O24" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P24" t="str">
         <v>Today</v>
       </c>
       <c r="Q24" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R24" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S24">
-        <v>73</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>job-1696793b</v>
+        <v>job-4af84947</v>
       </c>
       <c r="B25" t="str">
-        <v>Staff Product Manager, Issuing</v>
+        <v>Staff Product Manager, Dashboard</v>
       </c>
       <c r="C25" t="str">
         <v>Stripe</v>
@@ -2030,19 +2030,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H25" t="str">
-        <v>London</v>
+        <v>San Francisco, Seattle, NYC, Chicago, Atlanta, US Remote</v>
       </c>
       <c r="I25" t="str">
-        <v>London</v>
+        <v>San Francisco</v>
       </c>
       <c r="J25" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K25" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L25" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/8043083</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/7913702</v>
       </c>
       <c r="M25">
         <v>200</v>
@@ -2051,27 +2051,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O25" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P25" t="str">
         <v>Today</v>
       </c>
       <c r="Q25" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R25" t="str">
         <v>No</v>
       </c>
       <c r="S25">
-        <v>56</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>job-140cf629</v>
+        <v>job-1696793b</v>
       </c>
       <c r="B26" t="str">
-        <v>Staff Product Manager, Local Payment Methods Growth</v>
+        <v>Staff Product Manager, Issuing</v>
       </c>
       <c r="C26" t="str">
         <v>Stripe</v>
@@ -2101,7 +2101,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L26" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/8142649</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/8043083</v>
       </c>
       <c r="M26">
         <v>200</v>
@@ -2110,27 +2110,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O26" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P26" t="str">
         <v>Today</v>
       </c>
       <c r="Q26" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R26" t="str">
         <v>No</v>
       </c>
       <c r="S26">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>job-0b0dcd73</v>
+        <v>job-140cf629</v>
       </c>
       <c r="B27" t="str">
-        <v>Staff Product Manager, ML Foundations and GenAI</v>
+        <v>Staff Product Manager, Local Payment Methods Growth</v>
       </c>
       <c r="C27" t="str">
         <v>Stripe</v>
@@ -2148,19 +2148,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H27" t="str">
-        <v>Seattle, San Francisco, New York, US - Remote</v>
+        <v>Dublin</v>
       </c>
       <c r="I27" t="str">
-        <v>San Francisco</v>
+        <v>Dublin</v>
       </c>
       <c r="J27" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K27" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L27" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/7517535</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/7737526</v>
       </c>
       <c r="M27">
         <v>200</v>
@@ -2169,27 +2169,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O27" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P27" t="str">
         <v>Today</v>
       </c>
       <c r="Q27" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R27" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S27">
-        <v>61</v>
+        <v>46</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>job-01c7686e</v>
+        <v>job-0b0dcd73</v>
       </c>
       <c r="B28" t="str">
-        <v>Staff Product Manager, Payments</v>
+        <v>Staff Product Manager, ML Foundations and GenAI</v>
       </c>
       <c r="C28" t="str">
         <v>Stripe</v>
@@ -2207,7 +2207,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H28" t="str">
-        <v>SF, SEA, NYC, Remote</v>
+        <v>Seattle, San Francisco, New York, US - Remote</v>
       </c>
       <c r="I28" t="str">
         <v>San Francisco</v>
@@ -2219,7 +2219,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L28" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/7819059</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/7517535</v>
       </c>
       <c r="M28">
         <v>200</v>
@@ -2228,7 +2228,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O28" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P28" t="str">
         <v>Today</v>
@@ -2237,18 +2237,18 @@
         <v>No</v>
       </c>
       <c r="R28" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S28">
-        <v>38</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>job-0bc700c9</v>
+        <v>job-01c7686e</v>
       </c>
       <c r="B29" t="str">
-        <v>Staff Product Manager, Payments Intelligence</v>
+        <v>Staff Product Manager, Payments</v>
       </c>
       <c r="C29" t="str">
         <v>Stripe</v>
@@ -2266,7 +2266,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H29" t="str">
-        <v>NYC, SF, Seattle, US - Remote</v>
+        <v>SF, SEA, NYC, Remote</v>
       </c>
       <c r="I29" t="str">
         <v>San Francisco</v>
@@ -2278,7 +2278,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L29" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/8209996</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/7819059</v>
       </c>
       <c r="M29">
         <v>200</v>
@@ -2287,27 +2287,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O29" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P29" t="str">
         <v>Today</v>
       </c>
       <c r="Q29" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R29" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S29">
-        <v>42</v>
+        <v>56</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>job-5dedbaad</v>
+        <v>job-0bc700c9</v>
       </c>
       <c r="B30" t="str">
-        <v>Staff Product Manager, Sail Core</v>
+        <v>Staff Product Manager, Payments Intelligence</v>
       </c>
       <c r="C30" t="str">
         <v>Stripe</v>
@@ -2325,10 +2325,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H30" t="str">
-        <v>New York, US - Remote, Toronto</v>
+        <v>NYC, SF, Seattle, US - Remote</v>
       </c>
       <c r="I30" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J30" t="str">
         <v>Remote</v>
@@ -2337,7 +2337,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L30" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/7913698</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/8209996</v>
       </c>
       <c r="M30">
         <v>200</v>
@@ -2346,7 +2346,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O30" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P30" t="str">
         <v>Today</v>
@@ -2358,15 +2358,15 @@
         <v>No</v>
       </c>
       <c r="S30">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>job-6ad386a3</v>
+        <v>job-5dedbaad</v>
       </c>
       <c r="B31" t="str">
-        <v>Staff Product Manager, Stripe Tax</v>
+        <v>Staff Product Manager, Sail Core</v>
       </c>
       <c r="C31" t="str">
         <v>Stripe</v>
@@ -2384,19 +2384,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H31" t="str">
-        <v>Dublin, Ireland</v>
+        <v>New York, US - Remote, Toronto</v>
       </c>
       <c r="I31" t="str">
-        <v>Dublin</v>
+        <v>New York</v>
       </c>
       <c r="J31" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K31" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L31" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/8124304</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/7913698</v>
       </c>
       <c r="M31">
         <v>200</v>
@@ -2405,7 +2405,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O31" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P31" t="str">
         <v>Today</v>
@@ -2417,36 +2417,36 @@
         <v>No</v>
       </c>
       <c r="S31">
-        <v>90</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>job-0349189e</v>
+        <v>job-6ad386a3</v>
       </c>
       <c r="B32" t="str">
-        <v>Product Manager, Identity</v>
+        <v>Staff Product Manager, Stripe Tax</v>
       </c>
       <c r="C32" t="str">
-        <v>Airbnb</v>
+        <v>Stripe</v>
       </c>
       <c r="D32" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E32" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F32" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G32" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H32" t="str">
-        <v>United States</v>
+        <v>Dublin, Ireland</v>
       </c>
       <c r="I32" t="str">
-        <v>United States</v>
+        <v>Dublin</v>
       </c>
       <c r="J32" t="str">
         <v>On-site</v>
@@ -2455,7 +2455,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L32" t="str">
-        <v>https://boards.greenhouse.io/airbnb/jobs/8055637</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/8124304</v>
       </c>
       <c r="M32">
         <v>200</v>
@@ -2464,7 +2464,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O32" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P32" t="str">
         <v>Today</v>
@@ -2476,7 +2476,7 @@
         <v>No</v>
       </c>
       <c r="S32">
-        <v>75</v>
+        <v>93</v>
       </c>
     </row>
     <row r="33">
@@ -2523,7 +2523,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O33" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P33" t="str">
         <v>Today</v>
@@ -2535,7 +2535,7 @@
         <v>No</v>
       </c>
       <c r="S33">
-        <v>57</v>
+        <v>44</v>
       </c>
     </row>
     <row r="34">
@@ -2582,19 +2582,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O34" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P34" t="str">
         <v>Today</v>
       </c>
       <c r="Q34" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R34" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S34">
-        <v>93</v>
+        <v>34</v>
       </c>
     </row>
     <row r="35">
@@ -2641,7 +2641,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O35" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P35" t="str">
         <v>Today</v>
@@ -2653,7 +2653,7 @@
         <v>No</v>
       </c>
       <c r="S35">
-        <v>70</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36">
@@ -2700,7 +2700,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O36" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P36" t="str">
         <v>Today</v>
@@ -2709,10 +2709,10 @@
         <v>Yes</v>
       </c>
       <c r="R36" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S36">
-        <v>46</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37">
@@ -2759,7 +2759,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O37" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P37" t="str">
         <v>Today</v>
@@ -2768,10 +2768,10 @@
         <v>No</v>
       </c>
       <c r="R37" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S37">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="38">
@@ -2818,7 +2818,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O38" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P38" t="str">
         <v>Today</v>
@@ -2830,7 +2830,7 @@
         <v>No</v>
       </c>
       <c r="S38">
-        <v>83</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39">
@@ -2877,7 +2877,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O39" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P39" t="str">
         <v>Today</v>
@@ -2889,7 +2889,7 @@
         <v>No</v>
       </c>
       <c r="S39">
-        <v>63</v>
+        <v>69</v>
       </c>
     </row>
     <row r="40">
@@ -2915,10 +2915,10 @@
         <v>0-2 yrs</v>
       </c>
       <c r="H40" t="str">
-        <v>New York, New York, USA</v>
+        <v>Paris, France</v>
       </c>
       <c r="I40" t="str">
-        <v>New York</v>
+        <v>Paris</v>
       </c>
       <c r="J40" t="str">
         <v>On-site</v>
@@ -2927,7 +2927,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L40" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/8108241</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/8143729</v>
       </c>
       <c r="M40">
         <v>200</v>
@@ -2936,7 +2936,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O40" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P40" t="str">
         <v>Today</v>
@@ -2945,10 +2945,10 @@
         <v>No</v>
       </c>
       <c r="R40" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S40">
-        <v>32</v>
+        <v>92</v>
       </c>
     </row>
     <row r="41">
@@ -2995,7 +2995,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O41" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P41" t="str">
         <v>Today</v>
@@ -3007,7 +3007,7 @@
         <v>No</v>
       </c>
       <c r="S41">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="42">
@@ -3054,19 +3054,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O42" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P42" t="str">
         <v>Today</v>
       </c>
       <c r="Q42" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R42" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S42">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="43">
@@ -3113,7 +3113,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O43" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P43" t="str">
         <v>Today</v>
@@ -3122,10 +3122,10 @@
         <v>No</v>
       </c>
       <c r="R43" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S43">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="44">
@@ -3172,19 +3172,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O44" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P44" t="str">
         <v>Today</v>
       </c>
       <c r="Q44" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R44" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S44">
-        <v>43</v>
+        <v>81</v>
       </c>
     </row>
     <row r="45">
@@ -3231,7 +3231,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O45" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P45" t="str">
         <v>Today</v>
@@ -3240,10 +3240,10 @@
         <v>Yes</v>
       </c>
       <c r="R45" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S45">
-        <v>37</v>
+        <v>56</v>
       </c>
     </row>
     <row r="46">
@@ -3290,7 +3290,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O46" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P46" t="str">
         <v>Today</v>
@@ -3302,7 +3302,7 @@
         <v>No</v>
       </c>
       <c r="S46">
-        <v>42</v>
+        <v>61</v>
       </c>
     </row>
     <row r="47">
@@ -3349,7 +3349,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O47" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P47" t="str">
         <v>Today</v>
@@ -3361,7 +3361,7 @@
         <v>No</v>
       </c>
       <c r="S47">
-        <v>85</v>
+        <v>37</v>
       </c>
     </row>
     <row r="48">
@@ -3408,19 +3408,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O48" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P48" t="str">
         <v>Today</v>
       </c>
       <c r="Q48" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R48" t="str">
         <v>No</v>
       </c>
       <c r="S48">
-        <v>88</v>
+        <v>40</v>
       </c>
     </row>
     <row r="49">
@@ -3467,7 +3467,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O49" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P49" t="str">
         <v>Today</v>
@@ -3479,7 +3479,7 @@
         <v>No</v>
       </c>
       <c r="S49">
-        <v>43</v>
+        <v>68</v>
       </c>
     </row>
     <row r="50">
@@ -3526,7 +3526,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O50" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P50" t="str">
         <v>Today</v>
@@ -3538,7 +3538,7 @@
         <v>No</v>
       </c>
       <c r="S50">
-        <v>94</v>
+        <v>25</v>
       </c>
     </row>
     <row r="51">
@@ -3585,19 +3585,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O51" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P51" t="str">
         <v>Today</v>
       </c>
       <c r="Q51" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R51" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S51">
-        <v>65</v>
+        <v>26</v>
       </c>
     </row>
     <row r="52">
@@ -3644,19 +3644,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O52" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P52" t="str">
         <v>Today</v>
       </c>
       <c r="Q52" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R52" t="str">
         <v>No</v>
       </c>
       <c r="S52">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="53">
@@ -3703,19 +3703,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O53" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P53" t="str">
         <v>Today</v>
       </c>
       <c r="Q53" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R53" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S53">
-        <v>59</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54">
@@ -3762,19 +3762,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O54" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P54" t="str">
         <v>Today</v>
       </c>
       <c r="Q54" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R54" t="str">
         <v>No</v>
       </c>
       <c r="S54">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="55">
@@ -3821,7 +3821,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O55" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P55" t="str">
         <v>Today</v>
@@ -3830,10 +3830,10 @@
         <v>No</v>
       </c>
       <c r="R55" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S55">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="56">
@@ -3880,7 +3880,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O56" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P56" t="str">
         <v>Today</v>
@@ -3892,7 +3892,7 @@
         <v>No</v>
       </c>
       <c r="S56">
-        <v>88</v>
+        <v>82</v>
       </c>
     </row>
     <row r="57">
@@ -3939,19 +3939,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O57" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P57" t="str">
         <v>Today</v>
       </c>
       <c r="Q57" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R57" t="str">
         <v>Yes</v>
       </c>
       <c r="S57">
-        <v>28</v>
+        <v>60</v>
       </c>
     </row>
     <row r="58">
@@ -3998,7 +3998,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O58" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P58" t="str">
         <v>Today</v>
@@ -4010,7 +4010,7 @@
         <v>No</v>
       </c>
       <c r="S58">
-        <v>51</v>
+        <v>77</v>
       </c>
     </row>
     <row r="59">
@@ -4057,19 +4057,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O59" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P59" t="str">
         <v>Today</v>
       </c>
       <c r="Q59" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R59" t="str">
         <v>No</v>
       </c>
       <c r="S59">
-        <v>44</v>
+        <v>62</v>
       </c>
     </row>
     <row r="60">
@@ -4116,7 +4116,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O60" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P60" t="str">
         <v>Today</v>
@@ -4128,7 +4128,7 @@
         <v>No</v>
       </c>
       <c r="S60">
-        <v>80</v>
+        <v>85</v>
       </c>
     </row>
     <row r="61">
@@ -4175,7 +4175,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O61" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P61" t="str">
         <v>Today</v>
@@ -4187,7 +4187,7 @@
         <v>Yes</v>
       </c>
       <c r="S61">
-        <v>69</v>
+        <v>51</v>
       </c>
     </row>
     <row r="62">
@@ -4234,7 +4234,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O62" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P62" t="str">
         <v>Today</v>
@@ -4243,10 +4243,10 @@
         <v>No</v>
       </c>
       <c r="R62" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S62">
-        <v>84</v>
+        <v>59</v>
       </c>
     </row>
     <row r="63">
@@ -4293,7 +4293,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O63" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P63" t="str">
         <v>Today</v>
@@ -4302,7 +4302,7 @@
         <v>No</v>
       </c>
       <c r="R63" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S63">
         <v>59</v>
@@ -4352,19 +4352,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O64" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P64" t="str">
         <v>Today</v>
       </c>
       <c r="Q64" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R64" t="str">
         <v>No</v>
       </c>
       <c r="S64">
-        <v>72</v>
+        <v>49</v>
       </c>
     </row>
     <row r="65">
@@ -4411,7 +4411,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O65" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P65" t="str">
         <v>Today</v>
@@ -4423,7 +4423,7 @@
         <v>No</v>
       </c>
       <c r="S65">
-        <v>58</v>
+        <v>78</v>
       </c>
     </row>
     <row r="66">
@@ -4470,19 +4470,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O66" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P66" t="str">
         <v>Today</v>
       </c>
       <c r="Q66" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R66" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S66">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="67">
@@ -4508,7 +4508,7 @@
         <v>0-2 yrs</v>
       </c>
       <c r="H67" t="str">
-        <v>Menlo Park, CA; New York, NY</v>
+        <v>New York, NY</v>
       </c>
       <c r="I67" t="str">
         <v>New York</v>
@@ -4529,19 +4529,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O67" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P67" t="str">
         <v>Today</v>
       </c>
       <c r="Q67" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R67" t="str">
         <v>No</v>
       </c>
       <c r="S67">
-        <v>62</v>
+        <v>92</v>
       </c>
     </row>
     <row r="68">
@@ -4588,7 +4588,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O68" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P68" t="str">
         <v>Today</v>
@@ -4600,7 +4600,7 @@
         <v>Yes</v>
       </c>
       <c r="S68">
-        <v>52</v>
+        <v>80</v>
       </c>
     </row>
     <row r="69">
@@ -4647,19 +4647,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O69" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P69" t="str">
         <v>Today</v>
       </c>
       <c r="Q69" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R69" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S69">
-        <v>32</v>
+        <v>70</v>
       </c>
     </row>
     <row r="70">
@@ -4706,7 +4706,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O70" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P70" t="str">
         <v>Today</v>
@@ -4715,10 +4715,10 @@
         <v>No</v>
       </c>
       <c r="R70" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S70">
-        <v>51</v>
+        <v>65</v>
       </c>
     </row>
     <row r="71">
@@ -4765,19 +4765,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O71" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P71" t="str">
         <v>Today</v>
       </c>
       <c r="Q71" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R71" t="str">
         <v>No</v>
       </c>
       <c r="S71">
-        <v>85</v>
+        <v>36</v>
       </c>
     </row>
     <row r="72">
@@ -4824,7 +4824,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O72" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P72" t="str">
         <v>Today</v>
@@ -4833,18 +4833,18 @@
         <v>No</v>
       </c>
       <c r="R72" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S72">
-        <v>94</v>
+        <v>40</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>job-621b991e</v>
+        <v>job-2b6bc257</v>
       </c>
       <c r="B73" t="str">
-        <v>Staff Product Manager, National Impact</v>
+        <v>Staff Product Manager - Prediction Markets</v>
       </c>
       <c r="C73" t="str">
         <v>Robinhood</v>
@@ -4862,7 +4862,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H73" t="str">
-        <v>New York, NY</v>
+        <v>Menlo Park, CA; New York, NY</v>
       </c>
       <c r="I73" t="str">
         <v>New York</v>
@@ -4874,7 +4874,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L73" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/7968044</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/8164459</v>
       </c>
       <c r="M73">
         <v>200</v>
@@ -4883,7 +4883,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O73" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P73" t="str">
         <v>Today</v>
@@ -4895,45 +4895,45 @@
         <v>No</v>
       </c>
       <c r="S73">
-        <v>92</v>
+        <v>75</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>job-2b6bc257</v>
+        <v>job-223dd55b</v>
       </c>
       <c r="B74" t="str">
-        <v>Staff Product Manager - Prediction Markets</v>
+        <v>Director of Product Management, Fintech</v>
       </c>
       <c r="C74" t="str">
-        <v>Robinhood</v>
+        <v>Cloudflare</v>
       </c>
       <c r="D74" t="str">
-        <v>Naukri</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E74" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F74" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G74" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H74" t="str">
-        <v>Menlo Park, CA; New York, NY</v>
+        <v>Hybrid</v>
       </c>
       <c r="I74" t="str">
-        <v>New York</v>
+        <v>Hybrid</v>
       </c>
       <c r="J74" t="str">
-        <v>On-site</v>
+        <v>Hybrid</v>
       </c>
       <c r="K74" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L74" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/8164459</v>
+        <v>https://boards.greenhouse.io/cloudflare/jobs/8152765</v>
       </c>
       <c r="M74">
         <v>200</v>
@@ -4942,7 +4942,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O74" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P74" t="str">
         <v>Today</v>
@@ -4951,18 +4951,18 @@
         <v>No</v>
       </c>
       <c r="R74" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S74">
-        <v>78</v>
+        <v>66</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>job-223dd55b</v>
+        <v>job-04eb5da0</v>
       </c>
       <c r="B75" t="str">
-        <v>Director of Product Management, Fintech</v>
+        <v>Product Manager, Browser Extension</v>
       </c>
       <c r="C75" t="str">
         <v>Cloudflare</v>
@@ -4971,13 +4971,13 @@
         <v>LinkedIn</v>
       </c>
       <c r="E75" t="str">
-        <v>Product Lead / Director</v>
+        <v>Product Manager</v>
       </c>
       <c r="F75" t="str">
-        <v>8+ yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G75" t="str">
-        <v>8+ yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H75" t="str">
         <v>Hybrid</v>
@@ -4992,7 +4992,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L75" t="str">
-        <v>https://boards.greenhouse.io/cloudflare/jobs/8152765</v>
+        <v>https://boards.greenhouse.io/cloudflare/jobs/8173899</v>
       </c>
       <c r="M75">
         <v>200</v>
@@ -5001,27 +5001,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O75" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P75" t="str">
         <v>Today</v>
       </c>
       <c r="Q75" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R75" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S75">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>job-04eb5da0</v>
+        <v>job-6ad0cb95</v>
       </c>
       <c r="B76" t="str">
-        <v>Product Manager, Browser Extension</v>
+        <v>Senior Product Manager - Application Protection &amp; Governance</v>
       </c>
       <c r="C76" t="str">
         <v>Cloudflare</v>
@@ -5030,13 +5030,13 @@
         <v>LinkedIn</v>
       </c>
       <c r="E76" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F76" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G76" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H76" t="str">
         <v>Hybrid</v>
@@ -5051,7 +5051,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L76" t="str">
-        <v>https://boards.greenhouse.io/cloudflare/jobs/8173899</v>
+        <v>https://boards.greenhouse.io/cloudflare/jobs/8200670</v>
       </c>
       <c r="M76">
         <v>200</v>
@@ -5060,27 +5060,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O76" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P76" t="str">
         <v>Today</v>
       </c>
       <c r="Q76" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R76" t="str">
         <v>No</v>
       </c>
       <c r="S76">
-        <v>55</v>
+        <v>75</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>job-6ad0cb95</v>
+        <v>job-1cd2d853</v>
       </c>
       <c r="B77" t="str">
-        <v>Senior Product Manager - Application Protection &amp; Governance</v>
+        <v>Senior Product Manager, Email Security</v>
       </c>
       <c r="C77" t="str">
         <v>Cloudflare</v>
@@ -5110,7 +5110,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L77" t="str">
-        <v>https://boards.greenhouse.io/cloudflare/jobs/8200670</v>
+        <v>https://boards.greenhouse.io/cloudflare/jobs/8173954</v>
       </c>
       <c r="M77">
         <v>200</v>
@@ -5119,27 +5119,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O77" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P77" t="str">
         <v>Today</v>
       </c>
       <c r="Q77" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R77" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S77">
-        <v>25</v>
+        <v>61</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>job-1cd2d853</v>
+        <v>job-4c1a26d6</v>
       </c>
       <c r="B78" t="str">
-        <v>Senior Product Manager, Email Security</v>
+        <v>Senior Product Manager, Enterprise</v>
       </c>
       <c r="C78" t="str">
         <v>Cloudflare</v>
@@ -5169,7 +5169,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L78" t="str">
-        <v>https://boards.greenhouse.io/cloudflare/jobs/8173954</v>
+        <v>https://boards.greenhouse.io/cloudflare/jobs/8158527</v>
       </c>
       <c r="M78">
         <v>200</v>
@@ -5178,27 +5178,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O78" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P78" t="str">
         <v>Today</v>
       </c>
       <c r="Q78" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R78" t="str">
         <v>No</v>
       </c>
       <c r="S78">
-        <v>77</v>
+        <v>38</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>job-4c1a26d6</v>
+        <v>job-0496f2bd</v>
       </c>
       <c r="B79" t="str">
-        <v>Senior Product Manager, Enterprise</v>
+        <v>Senior Product Manager - FinTech</v>
       </c>
       <c r="C79" t="str">
         <v>Cloudflare</v>
@@ -5216,19 +5216,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H79" t="str">
-        <v>Hybrid</v>
+        <v>In-Office</v>
       </c>
       <c r="I79" t="str">
-        <v>Hybrid</v>
+        <v>In-Office</v>
       </c>
       <c r="J79" t="str">
-        <v>Hybrid</v>
+        <v>On-site</v>
       </c>
       <c r="K79" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L79" t="str">
-        <v>https://boards.greenhouse.io/cloudflare/jobs/8158527</v>
+        <v>https://boards.greenhouse.io/cloudflare/jobs/8064473</v>
       </c>
       <c r="M79">
         <v>200</v>
@@ -5237,30 +5237,30 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O79" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P79" t="str">
         <v>Today</v>
       </c>
       <c r="Q79" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R79" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S79">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>job-0496f2bd</v>
+        <v>job-321ad81f</v>
       </c>
       <c r="B80" t="str">
-        <v>Senior Product Manager - FinTech</v>
+        <v>Principal Product Manager Agents and Context - Elasticsearch</v>
       </c>
       <c r="C80" t="str">
-        <v>Cloudflare</v>
+        <v>Elastic</v>
       </c>
       <c r="D80" t="str">
         <v>LinkedIn</v>
@@ -5269,16 +5269,16 @@
         <v>Senior Product Manager</v>
       </c>
       <c r="F80" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G80" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H80" t="str">
-        <v>In-Office</v>
+        <v>United States</v>
       </c>
       <c r="I80" t="str">
-        <v>In-Office</v>
+        <v>United States</v>
       </c>
       <c r="J80" t="str">
         <v>On-site</v>
@@ -5287,7 +5287,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L80" t="str">
-        <v>https://boards.greenhouse.io/cloudflare/jobs/8064473</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/7602101</v>
       </c>
       <c r="M80">
         <v>200</v>
@@ -5296,7 +5296,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O80" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P80" t="str">
         <v>Today</v>
@@ -5305,18 +5305,18 @@
         <v>No</v>
       </c>
       <c r="R80" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S80">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>job-321ad81f</v>
+        <v>job-1958e230</v>
       </c>
       <c r="B81" t="str">
-        <v>Principal Product Manager Agents and Context - Elasticsearch</v>
+        <v>Principal Product Manager - Identity Threat Detection &amp; Response</v>
       </c>
       <c r="C81" t="str">
         <v>Elastic</v>
@@ -5334,10 +5334,10 @@
         <v>8+ yrs</v>
       </c>
       <c r="H81" t="str">
-        <v>Canada</v>
+        <v>Spain</v>
       </c>
       <c r="I81" t="str">
-        <v>Canada</v>
+        <v>Spain</v>
       </c>
       <c r="J81" t="str">
         <v>On-site</v>
@@ -5346,7 +5346,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L81" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8070011</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8122171</v>
       </c>
       <c r="M81">
         <v>200</v>
@@ -5355,27 +5355,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O81" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P81" t="str">
         <v>Today</v>
       </c>
       <c r="Q81" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R81" t="str">
         <v>No</v>
       </c>
       <c r="S81">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>job-1958e230</v>
+        <v>job-7648ed00</v>
       </c>
       <c r="B82" t="str">
-        <v>Principal Product Manager - Identity Threat Detection &amp; Response</v>
+        <v>Principal Product Manager II, AI/Vectors</v>
       </c>
       <c r="C82" t="str">
         <v>Elastic</v>
@@ -5393,10 +5393,10 @@
         <v>8+ yrs</v>
       </c>
       <c r="H82" t="str">
-        <v>Spain</v>
+        <v>United States</v>
       </c>
       <c r="I82" t="str">
-        <v>Spain</v>
+        <v>United States</v>
       </c>
       <c r="J82" t="str">
         <v>On-site</v>
@@ -5405,7 +5405,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L82" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8122171</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8121962</v>
       </c>
       <c r="M82">
         <v>200</v>
@@ -5414,27 +5414,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O82" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P82" t="str">
         <v>Today</v>
       </c>
       <c r="Q82" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R82" t="str">
         <v>No</v>
       </c>
       <c r="S82">
-        <v>56</v>
+        <v>94</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>job-7648ed00</v>
+        <v>job-4dbe0e39</v>
       </c>
       <c r="B83" t="str">
-        <v>Principal Product Manager II, AI/Vectors</v>
+        <v>Principal Product Manager (Strategic Account Interactions) - Security Solutions</v>
       </c>
       <c r="C83" t="str">
         <v>Elastic</v>
@@ -5452,10 +5452,10 @@
         <v>8+ yrs</v>
       </c>
       <c r="H83" t="str">
-        <v>United States</v>
+        <v>United Kingdom</v>
       </c>
       <c r="I83" t="str">
-        <v>United States</v>
+        <v>United Kingdom</v>
       </c>
       <c r="J83" t="str">
         <v>On-site</v>
@@ -5464,7 +5464,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L83" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8121962</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8155427</v>
       </c>
       <c r="M83">
         <v>200</v>
@@ -5473,7 +5473,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O83" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P83" t="str">
         <v>Today</v>
@@ -5482,18 +5482,18 @@
         <v>No</v>
       </c>
       <c r="R83" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S83">
-        <v>51</v>
+        <v>35</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>job-4dbe0e39</v>
+        <v>job-682d81b9</v>
       </c>
       <c r="B84" t="str">
-        <v>Principal Product Manager (Strategic Account Interactions) - Security Solutions</v>
+        <v>Principal Product Manager (XDR &amp; Exposure Management) - Security Solutions</v>
       </c>
       <c r="C84" t="str">
         <v>Elastic</v>
@@ -5511,10 +5511,10 @@
         <v>8+ yrs</v>
       </c>
       <c r="H84" t="str">
-        <v>Portugal</v>
+        <v>Canada</v>
       </c>
       <c r="I84" t="str">
-        <v>Portugal</v>
+        <v>Canada</v>
       </c>
       <c r="J84" t="str">
         <v>On-site</v>
@@ -5523,7 +5523,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L84" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8155423</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8155216</v>
       </c>
       <c r="M84">
         <v>200</v>
@@ -5532,27 +5532,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O84" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P84" t="str">
         <v>Today</v>
       </c>
       <c r="Q84" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R84" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S84">
-        <v>40</v>
+        <v>59</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>job-682d81b9</v>
+        <v>job-64ec2b77</v>
       </c>
       <c r="B85" t="str">
-        <v>Principal Product Manager (XDR &amp; Exposure Management) - Security Solutions</v>
+        <v>Senior Director of Product Management, Endpoint Security &amp; XDR</v>
       </c>
       <c r="C85" t="str">
         <v>Elastic</v>
@@ -5564,16 +5564,16 @@
         <v>Senior Product Manager</v>
       </c>
       <c r="F85" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G85" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H85" t="str">
-        <v>United States</v>
+        <v>Canada</v>
       </c>
       <c r="I85" t="str">
-        <v>United States</v>
+        <v>Canada</v>
       </c>
       <c r="J85" t="str">
         <v>On-site</v>
@@ -5582,7 +5582,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L85" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8130124</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8214187</v>
       </c>
       <c r="M85">
         <v>200</v>
@@ -5591,27 +5591,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O85" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P85" t="str">
         <v>Today</v>
       </c>
       <c r="Q85" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R85" t="str">
         <v>No</v>
       </c>
       <c r="S85">
-        <v>88</v>
+        <v>56</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>job-64ec2b77</v>
+        <v>job-2b6f27da</v>
       </c>
       <c r="B86" t="str">
-        <v>Senior Director of Product Management, Endpoint Security &amp; XDR</v>
+        <v>Senior Product Manager, Control Plane - Platform</v>
       </c>
       <c r="C86" t="str">
         <v>Elastic</v>
@@ -5641,7 +5641,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L86" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8214106</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8088818</v>
       </c>
       <c r="M86">
         <v>200</v>
@@ -5650,7 +5650,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O86" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P86" t="str">
         <v>Today</v>
@@ -5662,15 +5662,15 @@
         <v>Yes</v>
       </c>
       <c r="S86">
-        <v>94</v>
+        <v>72</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>job-2b6f27da</v>
+        <v>job-03cee7aa</v>
       </c>
       <c r="B87" t="str">
-        <v>Senior Product Manager, Control Plane - Platform</v>
+        <v>Senior Product Manager, Logs - Observability</v>
       </c>
       <c r="C87" t="str">
         <v>Elastic</v>
@@ -5688,10 +5688,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H87" t="str">
-        <v>Canada</v>
+        <v>Greece</v>
       </c>
       <c r="I87" t="str">
-        <v>Canada</v>
+        <v>Greece</v>
       </c>
       <c r="J87" t="str">
         <v>On-site</v>
@@ -5700,7 +5700,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L87" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8093933</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8066510</v>
       </c>
       <c r="M87">
         <v>200</v>
@@ -5709,27 +5709,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O87" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P87" t="str">
         <v>Today</v>
       </c>
       <c r="Q87" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R87" t="str">
         <v>No</v>
       </c>
       <c r="S87">
-        <v>66</v>
+        <v>36</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>job-03cee7aa</v>
+        <v>job-264c8d5a</v>
       </c>
       <c r="B88" t="str">
-        <v>Senior Product Manager, Logs - Observability</v>
+        <v>Senior Product Manager - Self service cloud</v>
       </c>
       <c r="C88" t="str">
         <v>Elastic</v>
@@ -5747,10 +5747,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H88" t="str">
-        <v>United States</v>
+        <v>Norway</v>
       </c>
       <c r="I88" t="str">
-        <v>United States</v>
+        <v>Norway</v>
       </c>
       <c r="J88" t="str">
         <v>On-site</v>
@@ -5759,7 +5759,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L88" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8053907</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8041211</v>
       </c>
       <c r="M88">
         <v>200</v>
@@ -5768,7 +5768,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O88" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P88" t="str">
         <v>Today</v>
@@ -5780,15 +5780,15 @@
         <v>No</v>
       </c>
       <c r="S88">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>job-264c8d5a</v>
+        <v>job-5b8ec8c1</v>
       </c>
       <c r="B89" t="str">
-        <v>Senior Product Manager - Self service cloud</v>
+        <v>Senior Product Manager - US Public Sector</v>
       </c>
       <c r="C89" t="str">
         <v>Elastic</v>
@@ -5806,10 +5806,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H89" t="str">
-        <v>Portugal</v>
+        <v>United States</v>
       </c>
       <c r="I89" t="str">
-        <v>Portugal</v>
+        <v>United States</v>
       </c>
       <c r="J89" t="str">
         <v>On-site</v>
@@ -5818,7 +5818,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L89" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8041208</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8188365</v>
       </c>
       <c r="M89">
         <v>200</v>
@@ -5827,27 +5827,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O89" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P89" t="str">
         <v>Today</v>
       </c>
       <c r="Q89" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R89" t="str">
         <v>No</v>
       </c>
       <c r="S89">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>job-5b8ec8c1</v>
+        <v>job-7ab91933</v>
       </c>
       <c r="B90" t="str">
-        <v>Senior Product Manager - US Public Sector</v>
+        <v>Senior Product Manager (XDR) - Security Solutions</v>
       </c>
       <c r="C90" t="str">
         <v>Elastic</v>
@@ -5865,10 +5865,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H90" t="str">
-        <v>United States</v>
+        <v>Greece</v>
       </c>
       <c r="I90" t="str">
-        <v>United States</v>
+        <v>Greece</v>
       </c>
       <c r="J90" t="str">
         <v>On-site</v>
@@ -5877,7 +5877,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L90" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8188365</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8194148</v>
       </c>
       <c r="M90">
         <v>200</v>
@@ -5886,7 +5886,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O90" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P90" t="str">
         <v>Today</v>
@@ -5895,39 +5895,39 @@
         <v>No</v>
       </c>
       <c r="R90" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S90">
-        <v>77</v>
+        <v>25</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>job-7ab91933</v>
+        <v>job-31af15ee</v>
       </c>
       <c r="B91" t="str">
-        <v>Senior Product Manager (XDR) - Security Solutions</v>
+        <v>AI Product Manager (Coding/Multimodal)</v>
       </c>
       <c r="C91" t="str">
-        <v>Elastic</v>
+        <v>Scale AI</v>
       </c>
       <c r="D91" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E91" t="str">
-        <v>Senior Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F91" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G91" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H91" t="str">
-        <v>Switzerland</v>
+        <v>San Francisco, CA</v>
       </c>
       <c r="I91" t="str">
-        <v>Switzerland</v>
+        <v>San Francisco</v>
       </c>
       <c r="J91" t="str">
         <v>On-site</v>
@@ -5936,7 +5936,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L91" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8194084</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4609736005</v>
       </c>
       <c r="M91">
         <v>200</v>
@@ -5945,27 +5945,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O91" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P91" t="str">
         <v>Today</v>
       </c>
       <c r="Q91" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R91" t="str">
         <v>Yes</v>
       </c>
       <c r="S91">
-        <v>86</v>
+        <v>37</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>job-31af15ee</v>
+        <v>job-184e55c8</v>
       </c>
       <c r="B92" t="str">
-        <v>AI Product Manager (Coding/Multimodal)</v>
+        <v>Director of Product Management, Enterprise Core Platform</v>
       </c>
       <c r="C92" t="str">
         <v>Scale AI</v>
@@ -5974,16 +5974,16 @@
         <v>Wellfound</v>
       </c>
       <c r="E92" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F92" t="str">
-        <v>3-6 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G92" t="str">
-        <v>2-5 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H92" t="str">
-        <v>San Francisco, CA</v>
+        <v>San Francisco, CA; New York, NY</v>
       </c>
       <c r="I92" t="str">
         <v>San Francisco</v>
@@ -5995,7 +5995,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L92" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4609736005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4714727005</v>
       </c>
       <c r="M92">
         <v>200</v>
@@ -6004,7 +6004,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O92" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P92" t="str">
         <v>Today</v>
@@ -6013,18 +6013,18 @@
         <v>No</v>
       </c>
       <c r="R92" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S92">
-        <v>49</v>
+        <v>62</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>job-184e55c8</v>
+        <v>job-6681e5c8</v>
       </c>
       <c r="B93" t="str">
-        <v>Director of Product Management, Enterprise Core Platform</v>
+        <v>Forward Deployed Product Manager, Enterprise</v>
       </c>
       <c r="C93" t="str">
         <v>Scale AI</v>
@@ -6033,19 +6033,19 @@
         <v>Wellfound</v>
       </c>
       <c r="E93" t="str">
-        <v>Technical Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F93" t="str">
-        <v>8+ yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G93" t="str">
-        <v>8+ yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H93" t="str">
-        <v>San Francisco, CA; New York, NY</v>
+        <v>London, UK</v>
       </c>
       <c r="I93" t="str">
-        <v>San Francisco</v>
+        <v>London</v>
       </c>
       <c r="J93" t="str">
         <v>On-site</v>
@@ -6054,7 +6054,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L93" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4714727005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4644742005</v>
       </c>
       <c r="M93">
         <v>200</v>
@@ -6063,7 +6063,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O93" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P93" t="str">
         <v>Today</v>
@@ -6075,15 +6075,15 @@
         <v>No</v>
       </c>
       <c r="S93">
-        <v>78</v>
+        <v>51</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>job-6681e5c8</v>
+        <v>job-11245f1c</v>
       </c>
       <c r="B94" t="str">
-        <v>Forward Deployed Product Manager, Enterprise</v>
+        <v>Forward Deployed Product Manager, Public Sector</v>
       </c>
       <c r="C94" t="str">
         <v>Scale AI</v>
@@ -6101,7 +6101,7 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H94" t="str">
-        <v>New York, NY</v>
+        <v>New York, NY; Washington, DC</v>
       </c>
       <c r="I94" t="str">
         <v>New York</v>
@@ -6113,7 +6113,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L94" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4673051005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4713648005</v>
       </c>
       <c r="M94">
         <v>200</v>
@@ -6122,7 +6122,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O94" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P94" t="str">
         <v>Today</v>
@@ -6134,15 +6134,15 @@
         <v>No</v>
       </c>
       <c r="S94">
-        <v>63</v>
+        <v>85</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>job-11245f1c</v>
+        <v>job-6a73fdcd</v>
       </c>
       <c r="B95" t="str">
-        <v>Forward Deployed Product Manager, Public Sector</v>
+        <v>Head of Product Management, Forward Deployed &amp; Strategy</v>
       </c>
       <c r="C95" t="str">
         <v>Scale AI</v>
@@ -6151,19 +6151,19 @@
         <v>Wellfound</v>
       </c>
       <c r="E95" t="str">
-        <v>Product Manager</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F95" t="str">
-        <v>3-6 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G95" t="str">
-        <v>2-5 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H95" t="str">
-        <v>New York, NY; Washington, DC</v>
+        <v>London, UK</v>
       </c>
       <c r="I95" t="str">
-        <v>New York</v>
+        <v>London</v>
       </c>
       <c r="J95" t="str">
         <v>On-site</v>
@@ -6172,7 +6172,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L95" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4713648005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4702890005</v>
       </c>
       <c r="M95">
         <v>200</v>
@@ -6181,27 +6181,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O95" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P95" t="str">
         <v>Today</v>
       </c>
       <c r="Q95" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R95" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S95">
-        <v>73</v>
+        <v>44</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>job-6a73fdcd</v>
+        <v>job-235e84a3</v>
       </c>
       <c r="B96" t="str">
-        <v>Head of Product Management, Forward Deployed &amp; Strategy</v>
+        <v>Product Manager, Enterprise Core Platform</v>
       </c>
       <c r="C96" t="str">
         <v>Scale AI</v>
@@ -6210,19 +6210,19 @@
         <v>Wellfound</v>
       </c>
       <c r="E96" t="str">
-        <v>Product Lead / Director</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F96" t="str">
-        <v>8+ yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G96" t="str">
-        <v>8+ yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H96" t="str">
-        <v>London, UK</v>
+        <v>New York, NY; San Francisco, CA</v>
       </c>
       <c r="I96" t="str">
-        <v>London</v>
+        <v>San Francisco</v>
       </c>
       <c r="J96" t="str">
         <v>On-site</v>
@@ -6231,7 +6231,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L96" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4702890005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4699779005</v>
       </c>
       <c r="M96">
         <v>200</v>
@@ -6240,27 +6240,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O96" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P96" t="str">
         <v>Today</v>
       </c>
       <c r="Q96" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R96" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S96">
-        <v>29</v>
+        <v>65</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>job-235e84a3</v>
+        <v>job-7d366400</v>
       </c>
       <c r="B97" t="str">
-        <v>Product Manager, Enterprise Core Platform</v>
+        <v>Product Manager of AI Applications, Global Public Sector</v>
       </c>
       <c r="C97" t="str">
         <v>Scale AI</v>
@@ -6269,7 +6269,7 @@
         <v>Wellfound</v>
       </c>
       <c r="E97" t="str">
-        <v>Technical Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F97" t="str">
         <v>3-6 yrs</v>
@@ -6278,10 +6278,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H97" t="str">
-        <v>New York, NY; San Francisco, CA</v>
+        <v>Doha, Qatar ; Dubai, UAE</v>
       </c>
       <c r="I97" t="str">
-        <v>San Francisco</v>
+        <v>Doha</v>
       </c>
       <c r="J97" t="str">
         <v>On-site</v>
@@ -6290,7 +6290,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L97" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4699779005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4589749005</v>
       </c>
       <c r="M97">
         <v>200</v>
@@ -6299,7 +6299,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O97" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P97" t="str">
         <v>Today</v>
@@ -6308,18 +6308,18 @@
         <v>Yes</v>
       </c>
       <c r="R97" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S97">
-        <v>33</v>
+        <v>39</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>job-7d366400</v>
+        <v>job-114956cc</v>
       </c>
       <c r="B98" t="str">
-        <v>Product Manager of AI Applications, Global Public Sector</v>
+        <v>Senior AI Product Manager</v>
       </c>
       <c r="C98" t="str">
         <v>Scale AI</v>
@@ -6328,19 +6328,19 @@
         <v>Wellfound</v>
       </c>
       <c r="E98" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F98" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G98" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H98" t="str">
-        <v>Doha, Qatar ; Dubai, UAE</v>
+        <v>New York, NY; San Francisco, CA</v>
       </c>
       <c r="I98" t="str">
-        <v>Doha</v>
+        <v>San Francisco</v>
       </c>
       <c r="J98" t="str">
         <v>On-site</v>
@@ -6349,7 +6349,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L98" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4589749005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4720501005</v>
       </c>
       <c r="M98">
         <v>200</v>
@@ -6358,27 +6358,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O98" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P98" t="str">
         <v>Today</v>
       </c>
       <c r="Q98" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R98" t="str">
         <v>No</v>
       </c>
       <c r="S98">
-        <v>86</v>
+        <v>75</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>job-114956cc</v>
+        <v>job-1310fa39</v>
       </c>
       <c r="B99" t="str">
-        <v>Senior AI Product Manager</v>
+        <v>Senior AI Product Manager, Cybersecurity</v>
       </c>
       <c r="C99" t="str">
         <v>Scale AI</v>
@@ -6408,7 +6408,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L99" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4720501005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4720213005</v>
       </c>
       <c r="M99">
         <v>200</v>
@@ -6417,7 +6417,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O99" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P99" t="str">
         <v>Today</v>
@@ -6426,18 +6426,18 @@
         <v>No</v>
       </c>
       <c r="R99" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S99">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>job-1310fa39</v>
+        <v>job-7ff81a54</v>
       </c>
       <c r="B100" t="str">
-        <v>Senior AI Product Manager, Cybersecurity</v>
+        <v>Senior AI Product Manager, Finance Agents</v>
       </c>
       <c r="C100" t="str">
         <v>Scale AI</v>
@@ -6455,7 +6455,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H100" t="str">
-        <v>New York, NY; San Francisco, CA</v>
+        <v>San Francisco, CA; New York, NY</v>
       </c>
       <c r="I100" t="str">
         <v>San Francisco</v>
@@ -6467,7 +6467,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L100" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4720213005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4611776005</v>
       </c>
       <c r="M100">
         <v>200</v>
@@ -6476,27 +6476,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O100" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P100" t="str">
         <v>Today</v>
       </c>
       <c r="Q100" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R100" t="str">
         <v>No</v>
       </c>
       <c r="S100">
-        <v>29</v>
+        <v>43</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>job-7ff81a54</v>
+        <v>job-59abfadc</v>
       </c>
       <c r="B101" t="str">
-        <v>Senior AI Product Manager, Finance Agents</v>
+        <v>Staff Product Manager, Agentic Platform</v>
       </c>
       <c r="C101" t="str">
         <v>Scale AI</v>
@@ -6514,7 +6514,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H101" t="str">
-        <v>San Francisco, CA; New York, NY</v>
+        <v>New York, NY; San Francisco, CA; Washington, DC</v>
       </c>
       <c r="I101" t="str">
         <v>San Francisco</v>
@@ -6526,7 +6526,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L101" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4611776005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4612403005</v>
       </c>
       <c r="M101">
         <v>200</v>
@@ -6535,27 +6535,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O101" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P101" t="str">
         <v>Today</v>
       </c>
       <c r="Q101" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R101" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S101">
-        <v>75</v>
+        <v>49</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>job-59abfadc</v>
+        <v>job-3ad31a80</v>
       </c>
       <c r="B102" t="str">
-        <v>Staff Product Manager, Agentic Platform</v>
+        <v>Staff Product Manager, Gen AI</v>
       </c>
       <c r="C102" t="str">
         <v>Scale AI</v>
@@ -6573,7 +6573,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H102" t="str">
-        <v>New York, NY; San Francisco, CA; Washington, DC</v>
+        <v>New York, NY; San Francisco, CA</v>
       </c>
       <c r="I102" t="str">
         <v>San Francisco</v>
@@ -6585,7 +6585,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L102" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4612403005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4675842005</v>
       </c>
       <c r="M102">
         <v>200</v>
@@ -6594,27 +6594,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O102" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P102" t="str">
         <v>Today</v>
       </c>
       <c r="Q102" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R102" t="str">
         <v>No</v>
       </c>
       <c r="S102">
-        <v>51</v>
+        <v>75</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>job-3ad31a80</v>
+        <v>job-20e060b6</v>
       </c>
       <c r="B103" t="str">
-        <v>Staff Product Manager, Gen AI</v>
+        <v>Staff Product Manager, Physical AI Data &amp; Robotics</v>
       </c>
       <c r="C103" t="str">
         <v>Scale AI</v>
@@ -6632,7 +6632,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H103" t="str">
-        <v>New York, NY; San Francisco, CA</v>
+        <v>San Francisco, CA</v>
       </c>
       <c r="I103" t="str">
         <v>San Francisco</v>
@@ -6644,7 +6644,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L103" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4675842005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4718559005</v>
       </c>
       <c r="M103">
         <v>200</v>
@@ -6653,7 +6653,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O103" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P103" t="str">
         <v>Today</v>
@@ -6665,15 +6665,15 @@
         <v>Yes</v>
       </c>
       <c r="S103">
-        <v>49</v>
+        <v>57</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>job-20e060b6</v>
+        <v>job-2ab7f7d1</v>
       </c>
       <c r="B104" t="str">
-        <v>Staff Product Manager, Physical AI Data &amp; Robotics</v>
+        <v>Staff Technical Product Manager</v>
       </c>
       <c r="C104" t="str">
         <v>Scale AI</v>
@@ -6691,10 +6691,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H104" t="str">
-        <v>San Francisco, CA</v>
+        <v>London, UK</v>
       </c>
       <c r="I104" t="str">
-        <v>San Francisco</v>
+        <v>London</v>
       </c>
       <c r="J104" t="str">
         <v>On-site</v>
@@ -6703,7 +6703,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L104" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4718559005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4683446005</v>
       </c>
       <c r="M104">
         <v>200</v>
@@ -6712,7 +6712,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O104" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P104" t="str">
         <v>Today</v>
@@ -6721,39 +6721,39 @@
         <v>No</v>
       </c>
       <c r="R104" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S104">
-        <v>36</v>
+        <v>27</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>job-2ab7f7d1</v>
+        <v>job-58b32a73</v>
       </c>
       <c r="B105" t="str">
-        <v>Staff Technical Product Manager</v>
+        <v>Director of Product, Growth/AI</v>
       </c>
       <c r="C105" t="str">
-        <v>Scale AI</v>
+        <v>Brex</v>
       </c>
       <c r="D105" t="str">
         <v>Wellfound</v>
       </c>
       <c r="E105" t="str">
-        <v>Senior Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F105" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G105" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H105" t="str">
-        <v>London, UK</v>
+        <v>Seattle, Washington, United States</v>
       </c>
       <c r="I105" t="str">
-        <v>London</v>
+        <v>Seattle</v>
       </c>
       <c r="J105" t="str">
         <v>On-site</v>
@@ -6762,7 +6762,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L105" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4683446005</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8433470002</v>
       </c>
       <c r="M105">
         <v>200</v>
@@ -6771,27 +6771,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O105" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P105" t="str">
         <v>Today</v>
       </c>
       <c r="Q105" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R105" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S105">
-        <v>35</v>
+        <v>57</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>job-58b32a73</v>
+        <v>job-6c147538</v>
       </c>
       <c r="B106" t="str">
-        <v>Director of Product, Growth/AI</v>
+        <v>Group Product Manager</v>
       </c>
       <c r="C106" t="str">
         <v>Brex</v>
@@ -6800,19 +6800,19 @@
         <v>Wellfound</v>
       </c>
       <c r="E106" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F106" t="str">
-        <v>8+ yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G106" t="str">
-        <v>8+ yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H106" t="str">
-        <v>Seattle, Washington, United States</v>
+        <v>New York, New York, United States</v>
       </c>
       <c r="I106" t="str">
-        <v>Seattle</v>
+        <v>New York</v>
       </c>
       <c r="J106" t="str">
         <v>On-site</v>
@@ -6821,7 +6821,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L106" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8433470002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8438581002</v>
       </c>
       <c r="M106">
         <v>200</v>
@@ -6830,7 +6830,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O106" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P106" t="str">
         <v>Today</v>
@@ -6842,15 +6842,15 @@
         <v>No</v>
       </c>
       <c r="S106">
-        <v>56</v>
+        <v>36</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>job-6c147538</v>
+        <v>job-4a5cf899</v>
       </c>
       <c r="B107" t="str">
-        <v>Group Product Manager</v>
+        <v>Senior Product Manager, AI</v>
       </c>
       <c r="C107" t="str">
         <v>Brex</v>
@@ -6859,19 +6859,19 @@
         <v>Wellfound</v>
       </c>
       <c r="E107" t="str">
-        <v>Product Lead / Director</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F107" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G107" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H107" t="str">
-        <v>San Francisco, California, United States</v>
+        <v>Seattle, Washington, United States</v>
       </c>
       <c r="I107" t="str">
-        <v>San Francisco</v>
+        <v>Seattle</v>
       </c>
       <c r="J107" t="str">
         <v>On-site</v>
@@ -6880,7 +6880,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L107" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8438580002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8780828002</v>
       </c>
       <c r="M107">
         <v>200</v>
@@ -6889,27 +6889,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O107" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P107" t="str">
         <v>Today</v>
       </c>
       <c r="Q107" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R107" t="str">
         <v>No</v>
       </c>
       <c r="S107">
-        <v>93</v>
+        <v>68</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>job-4a5cf899</v>
+        <v>job-111c900b</v>
       </c>
       <c r="B108" t="str">
-        <v>Senior Product Manager, AI</v>
+        <v>Senior Product Manager, Travel</v>
       </c>
       <c r="C108" t="str">
         <v>Brex</v>
@@ -6927,10 +6927,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H108" t="str">
-        <v>Seattle, Washington, United States</v>
+        <v>New York, New York, United States</v>
       </c>
       <c r="I108" t="str">
-        <v>Seattle</v>
+        <v>New York</v>
       </c>
       <c r="J108" t="str">
         <v>On-site</v>
@@ -6939,7 +6939,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L108" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8780828002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8659251002</v>
       </c>
       <c r="M108">
         <v>200</v>
@@ -6948,7 +6948,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O108" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P108" t="str">
         <v>Today</v>
@@ -6957,18 +6957,18 @@
         <v>No</v>
       </c>
       <c r="R108" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S108">
-        <v>55</v>
+        <v>91</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>job-111c900b</v>
+        <v>job-337165a7</v>
       </c>
       <c r="B109" t="str">
-        <v>Senior Product Manager, Travel</v>
+        <v>Staff Product Manager</v>
       </c>
       <c r="C109" t="str">
         <v>Brex</v>
@@ -6998,7 +6998,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L109" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8659249002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8432698002</v>
       </c>
       <c r="M109">
         <v>200</v>
@@ -7007,7 +7007,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O109" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P109" t="str">
         <v>Today</v>
@@ -7016,18 +7016,18 @@
         <v>Yes</v>
       </c>
       <c r="R109" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S109">
-        <v>69</v>
+        <v>46</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>job-337165a7</v>
+        <v>job-533982f5</v>
       </c>
       <c r="B110" t="str">
-        <v>Staff Product Manager</v>
+        <v>Staff Product Manager, AI</v>
       </c>
       <c r="C110" t="str">
         <v>Brex</v>
@@ -7045,10 +7045,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H110" t="str">
-        <v>San Francisco, California, United States</v>
+        <v>New York, New York, United States</v>
       </c>
       <c r="I110" t="str">
-        <v>San Francisco</v>
+        <v>New York</v>
       </c>
       <c r="J110" t="str">
         <v>On-site</v>
@@ -7057,7 +7057,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L110" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8432698002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8780829002</v>
       </c>
       <c r="M110">
         <v>200</v>
@@ -7066,7 +7066,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O110" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P110" t="str">
         <v>Today</v>
@@ -7078,15 +7078,15 @@
         <v>Yes</v>
       </c>
       <c r="S110">
-        <v>55</v>
+        <v>49</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>job-533982f5</v>
+        <v>job-0f9c4e5d</v>
       </c>
       <c r="B111" t="str">
-        <v>Staff Product Manager, AI</v>
+        <v>Staff Product Manager, Card</v>
       </c>
       <c r="C111" t="str">
         <v>Brex</v>
@@ -7104,10 +7104,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H111" t="str">
-        <v>New York, New York, United States</v>
+        <v>San Francisco, California, United States</v>
       </c>
       <c r="I111" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J111" t="str">
         <v>On-site</v>
@@ -7116,7 +7116,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L111" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8780829002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8659220002</v>
       </c>
       <c r="M111">
         <v>200</v>
@@ -7125,7 +7125,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O111" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P111" t="str">
         <v>Today</v>
@@ -7134,18 +7134,18 @@
         <v>Yes</v>
       </c>
       <c r="R111" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S111">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>job-0f9c4e5d</v>
+        <v>job-4401c5a9</v>
       </c>
       <c r="B112" t="str">
-        <v>Staff Product Manager, Card</v>
+        <v>Staff Product Manager, Embedded</v>
       </c>
       <c r="C112" t="str">
         <v>Brex</v>
@@ -7175,7 +7175,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L112" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8659220002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8659204002</v>
       </c>
       <c r="M112">
         <v>200</v>
@@ -7184,16 +7184,16 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O112" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P112" t="str">
         <v>Today</v>
       </c>
       <c r="Q112" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R112" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S112">
         <v>43</v>
@@ -7201,10 +7201,10 @@
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>job-4401c5a9</v>
+        <v>job-75398a6b</v>
       </c>
       <c r="B113" t="str">
-        <v>Staff Product Manager, Embedded</v>
+        <v>Staff Product Manager,  Embedded</v>
       </c>
       <c r="C113" t="str">
         <v>Brex</v>
@@ -7222,10 +7222,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H113" t="str">
-        <v>Seattle, Washington, United States</v>
+        <v>New York, New York, United States</v>
       </c>
       <c r="I113" t="str">
-        <v>Seattle</v>
+        <v>New York</v>
       </c>
       <c r="J113" t="str">
         <v>On-site</v>
@@ -7234,7 +7234,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L113" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8659210002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8659211002</v>
       </c>
       <c r="M113">
         <v>200</v>
@@ -7243,7 +7243,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O113" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P113" t="str">
         <v>Today</v>
@@ -7255,15 +7255,15 @@
         <v>No</v>
       </c>
       <c r="S113">
-        <v>29</v>
+        <v>92</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>job-75398a6b</v>
+        <v>job-0f02a1a8</v>
       </c>
       <c r="B114" t="str">
-        <v>Staff Product Manager,  Embedded</v>
+        <v>Staff Product Manager, Expenses</v>
       </c>
       <c r="C114" t="str">
         <v>Brex</v>
@@ -7281,10 +7281,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H114" t="str">
-        <v>New York, New York, United States</v>
+        <v>Seattle, Washington, United States</v>
       </c>
       <c r="I114" t="str">
-        <v>New York</v>
+        <v>Seattle</v>
       </c>
       <c r="J114" t="str">
         <v>On-site</v>
@@ -7293,7 +7293,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L114" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8659211002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8659241002</v>
       </c>
       <c r="M114">
         <v>200</v>
@@ -7302,27 +7302,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O114" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P114" t="str">
         <v>Today</v>
       </c>
       <c r="Q114" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R114" t="str">
         <v>No</v>
       </c>
       <c r="S114">
-        <v>94</v>
+        <v>60</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>job-0f02a1a8</v>
+        <v>job-2239c52c</v>
       </c>
       <c r="B115" t="str">
-        <v>Staff Product Manager, Expenses</v>
+        <v>Staff Product Manager, Growth</v>
       </c>
       <c r="C115" t="str">
         <v>Brex</v>
@@ -7352,7 +7352,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L115" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8659242002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8436528002</v>
       </c>
       <c r="M115">
         <v>200</v>
@@ -7361,7 +7361,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O115" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P115" t="str">
         <v>Today</v>
@@ -7370,39 +7370,39 @@
         <v>No</v>
       </c>
       <c r="R115" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S115">
-        <v>46</v>
+        <v>90</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>job-2239c52c</v>
+        <v>job-429ddf15</v>
       </c>
       <c r="B116" t="str">
-        <v>Staff Product Manager, Growth</v>
+        <v>Associate Product Manager, Intern</v>
       </c>
       <c r="C116" t="str">
-        <v>Brex</v>
+        <v>Duolingo</v>
       </c>
       <c r="D116" t="str">
         <v>Wellfound</v>
       </c>
       <c r="E116" t="str">
-        <v>Senior Product Manager</v>
+        <v>Associate Product Manager</v>
       </c>
       <c r="F116" t="str">
-        <v>5-8 yrs</v>
+        <v>1-3 yrs</v>
       </c>
       <c r="G116" t="str">
-        <v>5-8 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H116" t="str">
-        <v>San Francisco, California, United States</v>
+        <v>Pittsburgh, PA</v>
       </c>
       <c r="I116" t="str">
-        <v>San Francisco</v>
+        <v>Pittsburgh</v>
       </c>
       <c r="J116" t="str">
         <v>On-site</v>
@@ -7411,7 +7411,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L116" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8436527002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8806187002</v>
       </c>
       <c r="M116">
         <v>200</v>
@@ -7420,7 +7420,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O116" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P116" t="str">
         <v>Today</v>
@@ -7432,15 +7432,15 @@
         <v>No</v>
       </c>
       <c r="S116">
-        <v>41</v>
+        <v>61</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>job-429ddf15</v>
+        <v>job-1b56d1fb</v>
       </c>
       <c r="B117" t="str">
-        <v>Associate Product Manager, Intern</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="C117" t="str">
         <v>Duolingo</v>
@@ -7449,19 +7449,19 @@
         <v>Wellfound</v>
       </c>
       <c r="E117" t="str">
-        <v>Associate Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F117" t="str">
-        <v>1-3 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G117" t="str">
-        <v>0-2 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H117" t="str">
-        <v>Pittsburgh, PA</v>
+        <v>Beijing, China</v>
       </c>
       <c r="I117" t="str">
-        <v>Pittsburgh</v>
+        <v>Beijing</v>
       </c>
       <c r="J117" t="str">
         <v>On-site</v>
@@ -7470,7 +7470,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L117" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8806187002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8675670002</v>
       </c>
       <c r="M117">
         <v>200</v>
@@ -7479,27 +7479,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O117" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P117" t="str">
         <v>Today</v>
       </c>
       <c r="Q117" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R117" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S117">
-        <v>32</v>
+        <v>70</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>job-1b56d1fb</v>
+        <v>job-0ba5b818</v>
       </c>
       <c r="B118" t="str">
-        <v>Senior Product Manager</v>
+        <v>Senior Product Manager, DET</v>
       </c>
       <c r="C118" t="str">
         <v>Duolingo</v>
@@ -7517,10 +7517,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H118" t="str">
-        <v>Beijing, China</v>
+        <v>Pittsburgh, PA</v>
       </c>
       <c r="I118" t="str">
-        <v>Beijing</v>
+        <v>Pittsburgh</v>
       </c>
       <c r="J118" t="str">
         <v>On-site</v>
@@ -7529,7 +7529,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L118" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8675670002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8530395002</v>
       </c>
       <c r="M118">
         <v>200</v>
@@ -7538,7 +7538,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O118" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P118" t="str">
         <v>Today</v>
@@ -7547,18 +7547,18 @@
         <v>No</v>
       </c>
       <c r="R118" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S118">
-        <v>71</v>
+        <v>91</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>job-0ba5b818</v>
+        <v>job-25986280</v>
       </c>
       <c r="B119" t="str">
-        <v>Senior Product Manager, DET</v>
+        <v>Senior Product Manager, Growth</v>
       </c>
       <c r="C119" t="str">
         <v>Duolingo</v>
@@ -7588,7 +7588,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L119" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8737859002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8747275002</v>
       </c>
       <c r="M119">
         <v>200</v>
@@ -7597,7 +7597,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O119" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P119" t="str">
         <v>Today</v>
@@ -7609,15 +7609,15 @@
         <v>No</v>
       </c>
       <c r="S119">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>job-25986280</v>
+        <v>job-604bd697</v>
       </c>
       <c r="B120" t="str">
-        <v>Senior Product Manager, Growth</v>
+        <v>Senior Product Manager, Learning</v>
       </c>
       <c r="C120" t="str">
         <v>Duolingo</v>
@@ -7635,7 +7635,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H120" t="str">
-        <v>New York, NY</v>
+        <v>New York, NY; Pittsburgh, PA</v>
       </c>
       <c r="I120" t="str">
         <v>New York</v>
@@ -7647,7 +7647,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L120" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8747275002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8827944002</v>
       </c>
       <c r="M120">
         <v>200</v>
@@ -7656,7 +7656,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O120" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P120" t="str">
         <v>Today</v>
@@ -7665,18 +7665,18 @@
         <v>Yes</v>
       </c>
       <c r="R120" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S120">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>job-604bd697</v>
+        <v>job-256f50fd</v>
       </c>
       <c r="B121" t="str">
-        <v>Senior Product Manager, Learning</v>
+        <v>Senior Product Manager, Notifications</v>
       </c>
       <c r="C121" t="str">
         <v>Duolingo</v>
@@ -7706,7 +7706,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L121" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8827944002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8747099002</v>
       </c>
       <c r="M121">
         <v>200</v>
@@ -7715,27 +7715,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O121" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P121" t="str">
         <v>Today</v>
       </c>
       <c r="Q121" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R121" t="str">
         <v>No</v>
       </c>
       <c r="S121">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>job-256f50fd</v>
+        <v>job-2666664e</v>
       </c>
       <c r="B122" t="str">
-        <v>Senior Product Manager, Notifications</v>
+        <v>Staff Product Manager, Monetization</v>
       </c>
       <c r="C122" t="str">
         <v>Duolingo</v>
@@ -7753,10 +7753,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H122" t="str">
-        <v>Pittsburgh, PA</v>
+        <v>New York, NY</v>
       </c>
       <c r="I122" t="str">
-        <v>Pittsburgh</v>
+        <v>New York</v>
       </c>
       <c r="J122" t="str">
         <v>On-site</v>
@@ -7765,7 +7765,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L122" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8747099002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8474673002</v>
       </c>
       <c r="M122">
         <v>200</v>
@@ -7774,7 +7774,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O122" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P122" t="str">
         <v>Today</v>
@@ -7786,15 +7786,15 @@
         <v>No</v>
       </c>
       <c r="S122">
-        <v>78</v>
+        <v>31</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>job-2666664e</v>
+        <v>job-6e88535c</v>
       </c>
       <c r="B123" t="str">
-        <v>Staff Product Manager, Monetization</v>
+        <v>VP of Product, Growth and Monetization</v>
       </c>
       <c r="C123" t="str">
         <v>Duolingo</v>
@@ -7803,19 +7803,19 @@
         <v>Wellfound</v>
       </c>
       <c r="E123" t="str">
-        <v>Senior Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F123" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G123" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H123" t="str">
-        <v>New York, NY</v>
+        <v>Pittsburgh, PA</v>
       </c>
       <c r="I123" t="str">
-        <v>New York</v>
+        <v>Pittsburgh</v>
       </c>
       <c r="J123" t="str">
         <v>On-site</v>
@@ -7824,7 +7824,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L123" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8474673002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8747077002</v>
       </c>
       <c r="M123">
         <v>200</v>
@@ -7833,7 +7833,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O123" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P123" t="str">
         <v>Today</v>
@@ -7845,74 +7845,74 @@
         <v>Yes</v>
       </c>
       <c r="S123">
-        <v>58</v>
+        <v>35</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>job-6e88535c</v>
+        <v>job-65a74288</v>
       </c>
       <c r="B124" t="str">
-        <v>VP of Product, Growth and Monetization</v>
+        <v>Associate Product Manager Intern</v>
       </c>
       <c r="C124" t="str">
-        <v>Duolingo</v>
+        <v>Coinbase</v>
       </c>
       <c r="D124" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E124" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Associate Product Manager</v>
       </c>
       <c r="F124" t="str">
-        <v>8+ yrs</v>
+        <v>1-3 yrs</v>
       </c>
       <c r="G124" t="str">
-        <v>8+ yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H124" t="str">
-        <v>New York, NY</v>
+        <v>Hybrid - San Francisco, CA</v>
       </c>
       <c r="I124" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J124" t="str">
-        <v>On-site</v>
+        <v>Hybrid</v>
       </c>
       <c r="K124" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L124" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8747060002</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/8168322</v>
       </c>
       <c r="M124">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N124" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O124" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P124" t="str">
         <v>Today</v>
       </c>
       <c r="Q124" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R124" t="str">
         <v>No</v>
       </c>
       <c r="S124">
-        <v>87</v>
+        <v>58</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>job-65a74288</v>
+        <v>job-2bc26745</v>
       </c>
       <c r="B125" t="str">
-        <v>Associate Product Manager Intern</v>
+        <v>Group Product Manager, Compliance Agent Experience</v>
       </c>
       <c r="C125" t="str">
         <v>Coinbase</v>
@@ -7921,28 +7921,28 @@
         <v>LinkedIn</v>
       </c>
       <c r="E125" t="str">
-        <v>Associate Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F125" t="str">
-        <v>1-3 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G125" t="str">
-        <v>0-2 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H125" t="str">
-        <v>Hybrid - San Francisco, CA</v>
+        <v>Remote - USA</v>
       </c>
       <c r="I125" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J125" t="str">
-        <v>Hybrid</v>
+        <v>Remote</v>
       </c>
       <c r="K125" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L125" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/8168322</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/8060662</v>
       </c>
       <c r="M125">
         <v>403</v>
@@ -7951,13 +7951,13 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O125" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P125" t="str">
         <v>Today</v>
       </c>
       <c r="Q125" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R125" t="str">
         <v>Yes</v>
@@ -7968,10 +7968,10 @@
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>job-2bc26745</v>
+        <v>job-779d88ed</v>
       </c>
       <c r="B126" t="str">
-        <v>Group Product Manager, Compliance Agent Experience</v>
+        <v>Group Product Manager, Compliance Automation</v>
       </c>
       <c r="C126" t="str">
         <v>Coinbase</v>
@@ -7980,7 +7980,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E126" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F126" t="str">
         <v>3-6 yrs</v>
@@ -8001,7 +8001,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L126" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/8060662</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/7701642</v>
       </c>
       <c r="M126">
         <v>403</v>
@@ -8010,27 +8010,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O126" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P126" t="str">
         <v>Today</v>
       </c>
       <c r="Q126" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R126" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S126">
-        <v>61</v>
+        <v>92</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>job-779d88ed</v>
+        <v>job-6faf73eb</v>
       </c>
       <c r="B127" t="str">
-        <v>Group Product Manager, Compliance Automation</v>
+        <v>Group Product Manager, Core Infrastructure &amp; Reliability</v>
       </c>
       <c r="C127" t="str">
         <v>Coinbase</v>
@@ -8039,7 +8039,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E127" t="str">
-        <v>Product Lead / Director</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F127" t="str">
         <v>3-6 yrs</v>
@@ -8060,7 +8060,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L127" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/7701642</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/7997785</v>
       </c>
       <c r="M127">
         <v>403</v>
@@ -8069,27 +8069,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O127" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P127" t="str">
         <v>Today</v>
       </c>
       <c r="Q127" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R127" t="str">
         <v>No</v>
       </c>
       <c r="S127">
-        <v>73</v>
+        <v>55</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>job-6faf73eb</v>
+        <v>job-67afa492</v>
       </c>
       <c r="B128" t="str">
-        <v>Group Product Manager, Core Infrastructure &amp; Reliability</v>
+        <v>Group Product Manager, Developer Infrastructure</v>
       </c>
       <c r="C128" t="str">
         <v>Coinbase</v>
@@ -8119,7 +8119,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L128" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/7997785</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/8017607</v>
       </c>
       <c r="M128">
         <v>403</v>
@@ -8128,27 +8128,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O128" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P128" t="str">
         <v>Today</v>
       </c>
       <c r="Q128" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R128" t="str">
         <v>No</v>
       </c>
       <c r="S128">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>job-67afa492</v>
+        <v>job-00f9bc89</v>
       </c>
       <c r="B129" t="str">
-        <v>Group Product Manager, Developer Infrastructure</v>
+        <v>Head of Product Creative</v>
       </c>
       <c r="C129" t="str">
         <v>Coinbase</v>
@@ -8157,13 +8157,13 @@
         <v>LinkedIn</v>
       </c>
       <c r="E129" t="str">
-        <v>Technical Product Manager</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F129" t="str">
-        <v>3-6 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G129" t="str">
-        <v>2-5 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H129" t="str">
         <v>Remote - USA</v>
@@ -8178,7 +8178,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L129" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/8017607</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/7304930</v>
       </c>
       <c r="M129">
         <v>403</v>
@@ -8187,7 +8187,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O129" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P129" t="str">
         <v>Today</v>
@@ -8199,15 +8199,15 @@
         <v>No</v>
       </c>
       <c r="S129">
-        <v>25</v>
+        <v>45</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>job-00f9bc89</v>
+        <v>job-02200da7</v>
       </c>
       <c r="B130" t="str">
-        <v>Head of Product Creative</v>
+        <v>Product Manager (HR Technology) Intern</v>
       </c>
       <c r="C130" t="str">
         <v>Coinbase</v>
@@ -8216,28 +8216,28 @@
         <v>LinkedIn</v>
       </c>
       <c r="E130" t="str">
-        <v>Product Lead / Director</v>
+        <v>Product Manager</v>
       </c>
       <c r="F130" t="str">
-        <v>8+ yrs</v>
+        <v>1-3 yrs</v>
       </c>
       <c r="G130" t="str">
-        <v>8+ yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H130" t="str">
-        <v>Remote - USA</v>
+        <v>Hybrid - New York, NY</v>
       </c>
       <c r="I130" t="str">
-        <v>Remote</v>
+        <v>New York</v>
       </c>
       <c r="J130" t="str">
-        <v>Remote</v>
+        <v>Hybrid</v>
       </c>
       <c r="K130" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L130" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/7304930</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/8175504</v>
       </c>
       <c r="M130">
         <v>403</v>
@@ -8246,7 +8246,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O130" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P130" t="str">
         <v>Today</v>
@@ -8258,15 +8258,15 @@
         <v>No</v>
       </c>
       <c r="S130">
-        <v>91</v>
+        <v>66</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>job-02200da7</v>
+        <v>job-0f319aac</v>
       </c>
       <c r="B131" t="str">
-        <v>Product Manager (HR Technology) Intern</v>
+        <v>Product Manager II, Growth - Notifications</v>
       </c>
       <c r="C131" t="str">
         <v>Coinbase</v>
@@ -8275,28 +8275,28 @@
         <v>LinkedIn</v>
       </c>
       <c r="E131" t="str">
-        <v>Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F131" t="str">
-        <v>1-3 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G131" t="str">
-        <v>0-2 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H131" t="str">
-        <v>Hybrid - New York, NY</v>
+        <v>Remote - USA</v>
       </c>
       <c r="I131" t="str">
-        <v>New York</v>
+        <v>Remote</v>
       </c>
       <c r="J131" t="str">
-        <v>Hybrid</v>
+        <v>Remote</v>
       </c>
       <c r="K131" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L131" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/8175504</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/8204571</v>
       </c>
       <c r="M131">
         <v>403</v>
@@ -8305,7 +8305,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O131" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P131" t="str">
         <v>Today</v>
@@ -8314,18 +8314,18 @@
         <v>No</v>
       </c>
       <c r="R131" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S131">
-        <v>31</v>
+        <v>52</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>job-0f319aac</v>
+        <v>job-0d5f8a75</v>
       </c>
       <c r="B132" t="str">
-        <v>Product Manager II, Growth - Notifications</v>
+        <v>Product Manager II, Workspace and Multi-User</v>
       </c>
       <c r="C132" t="str">
         <v>Coinbase</v>
@@ -8334,7 +8334,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E132" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Product Manager</v>
       </c>
       <c r="F132" t="str">
         <v>3-6 yrs</v>
@@ -8355,7 +8355,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L132" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/8204571</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/8148171</v>
       </c>
       <c r="M132">
         <v>403</v>
@@ -8364,7 +8364,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O132" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P132" t="str">
         <v>Today</v>
@@ -8373,18 +8373,18 @@
         <v>No</v>
       </c>
       <c r="R132" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S132">
-        <v>91</v>
+        <v>85</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>job-0d5f8a75</v>
+        <v>job-2efe7fb3</v>
       </c>
       <c r="B133" t="str">
-        <v>Product Manager II, Workspace and Multi-User</v>
+        <v>Senior Product Manager, Help Center (CX Automation)</v>
       </c>
       <c r="C133" t="str">
         <v>Coinbase</v>
@@ -8393,16 +8393,16 @@
         <v>LinkedIn</v>
       </c>
       <c r="E133" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F133" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G133" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H133" t="str">
-        <v>Remote - USA</v>
+        <v>Remote - India</v>
       </c>
       <c r="I133" t="str">
         <v>Remote</v>
@@ -8414,7 +8414,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L133" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/8148171</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/8031208</v>
       </c>
       <c r="M133">
         <v>403</v>
@@ -8423,7 +8423,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O133" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P133" t="str">
         <v>Today</v>
@@ -8432,36 +8432,36 @@
         <v>No</v>
       </c>
       <c r="R133" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S133">
-        <v>54</v>
+        <v>65</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>job-2efe7fb3</v>
+        <v>job-1762a9dc</v>
       </c>
       <c r="B134" t="str">
-        <v>Senior Product Manager, Help Center (CX Automation)</v>
+        <v>Director of Product Management, Agentic Software Delivery</v>
       </c>
       <c r="C134" t="str">
-        <v>Coinbase</v>
+        <v>GitLab</v>
       </c>
       <c r="D134" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E134" t="str">
-        <v>Senior Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F134" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G134" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H134" t="str">
-        <v>Remote - India</v>
+        <v>Remote, United States</v>
       </c>
       <c r="I134" t="str">
         <v>Remote</v>
@@ -8473,16 +8473,16 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L134" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/8031208</v>
+        <v>https://boards.greenhouse.io/gitlab/jobs/8806017002</v>
       </c>
       <c r="M134">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N134" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O134" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P134" t="str">
         <v>Today</v>
@@ -8494,15 +8494,15 @@
         <v>No</v>
       </c>
       <c r="S134">
-        <v>49</v>
+        <v>63</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>job-1762a9dc</v>
+        <v>job-58e27f7c</v>
       </c>
       <c r="B135" t="str">
-        <v>Director of Product Management, Agentic Software Delivery</v>
+        <v>Principal Product Manager, AI Software Factory</v>
       </c>
       <c r="C135" t="str">
         <v>GitLab</v>
@@ -8511,7 +8511,7 @@
         <v>Wellfound</v>
       </c>
       <c r="E135" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F135" t="str">
         <v>8+ yrs</v>
@@ -8520,7 +8520,7 @@
         <v>8+ yrs</v>
       </c>
       <c r="H135" t="str">
-        <v>Remote, United States</v>
+        <v>Remote, Canada; Remote, United States</v>
       </c>
       <c r="I135" t="str">
         <v>Remote</v>
@@ -8532,7 +8532,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L135" t="str">
-        <v>https://boards.greenhouse.io/gitlab/jobs/8806017002</v>
+        <v>https://boards.greenhouse.io/gitlab/jobs/8658878002</v>
       </c>
       <c r="M135">
         <v>200</v>
@@ -8541,27 +8541,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O135" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P135" t="str">
         <v>Today</v>
       </c>
       <c r="Q135" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R135" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S135">
-        <v>41</v>
+        <v>34</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>job-46ec002c</v>
+        <v>job-448d861a</v>
       </c>
       <c r="B136" t="str">
-        <v>Principal Product Manager, AI Custom Models</v>
+        <v>Senior Product Manager, Agentic Source Code</v>
       </c>
       <c r="C136" t="str">
         <v>GitLab</v>
@@ -8573,10 +8573,10 @@
         <v>Senior Product Manager</v>
       </c>
       <c r="F136" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G136" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H136" t="str">
         <v>Remote, Canada; Remote, US</v>
@@ -8591,7 +8591,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L136" t="str">
-        <v>https://boards.greenhouse.io/gitlab/jobs/8564957002</v>
+        <v>https://boards.greenhouse.io/gitlab/jobs/8597805002</v>
       </c>
       <c r="M136">
         <v>200</v>
@@ -8600,7 +8600,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O136" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P136" t="str">
         <v>Today</v>
@@ -8609,18 +8609,18 @@
         <v>No</v>
       </c>
       <c r="R136" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S136">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>job-58e27f7c</v>
+        <v>job-6bc28568</v>
       </c>
       <c r="B137" t="str">
-        <v>Principal Product Manager, AI Software Factory</v>
+        <v>Senior Product Manager, Secret Detection and Vulnerability Research</v>
       </c>
       <c r="C137" t="str">
         <v>GitLab</v>
@@ -8632,13 +8632,13 @@
         <v>Senior Product Manager</v>
       </c>
       <c r="F137" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G137" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H137" t="str">
-        <v>Remote, Canada; Remote, United States</v>
+        <v>Remote, United States</v>
       </c>
       <c r="I137" t="str">
         <v>Remote</v>
@@ -8650,7 +8650,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L137" t="str">
-        <v>https://boards.greenhouse.io/gitlab/jobs/8658878002</v>
+        <v>https://boards.greenhouse.io/gitlab/jobs/8697043002</v>
       </c>
       <c r="M137">
         <v>200</v>
@@ -8659,27 +8659,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O137" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P137" t="str">
         <v>Today</v>
       </c>
       <c r="Q137" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R137" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S137">
-        <v>32</v>
+        <v>79</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>job-448d861a</v>
+        <v>job-7ad77ccd</v>
       </c>
       <c r="B138" t="str">
-        <v>Senior Product Manager, Agentic Source Code</v>
+        <v>Senior Product Manager, Tenant Scale</v>
       </c>
       <c r="C138" t="str">
         <v>GitLab</v>
@@ -8709,7 +8709,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L138" t="str">
-        <v>https://boards.greenhouse.io/gitlab/jobs/8597805002</v>
+        <v>https://boards.greenhouse.io/gitlab/jobs/8512220002</v>
       </c>
       <c r="M138">
         <v>200</v>
@@ -8718,7 +8718,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O138" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P138" t="str">
         <v>Today</v>
@@ -8730,15 +8730,15 @@
         <v>No</v>
       </c>
       <c r="S138">
-        <v>59</v>
+        <v>82</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>job-6bc28568</v>
+        <v>job-52edb6a4</v>
       </c>
       <c r="B139" t="str">
-        <v>Senior Product Manager, Secret Detection and Vulnerability Research</v>
+        <v>Staff Product Manager,  RevOps &amp; Finance Systems</v>
       </c>
       <c r="C139" t="str">
         <v>GitLab</v>
@@ -8756,7 +8756,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H139" t="str">
-        <v>Remote, United States</v>
+        <v>Remote, US</v>
       </c>
       <c r="I139" t="str">
         <v>Remote</v>
@@ -8768,7 +8768,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L139" t="str">
-        <v>https://boards.greenhouse.io/gitlab/jobs/8697043002</v>
+        <v>https://boards.greenhouse.io/gitlab/jobs/8612937002</v>
       </c>
       <c r="M139">
         <v>200</v>
@@ -8777,7 +8777,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O139" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P139" t="str">
         <v>Today</v>
@@ -8786,7 +8786,7 @@
         <v>No</v>
       </c>
       <c r="R139" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S139">
         <v>62</v>
@@ -8794,40 +8794,40 @@
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>job-7ad77ccd</v>
+        <v>job-3a743e4f</v>
       </c>
       <c r="B140" t="str">
-        <v>Senior Product Manager, Tenant Scale</v>
+        <v>Manager, Product Management - Figma Platform Experience</v>
       </c>
       <c r="C140" t="str">
-        <v>GitLab</v>
+        <v>Figma</v>
       </c>
       <c r="D140" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E140" t="str">
-        <v>Senior Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F140" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G140" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H140" t="str">
-        <v>Remote, Canada; Remote, US</v>
+        <v>San Francisco, CA • New York, NY • United States</v>
       </c>
       <c r="I140" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J140" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K140" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L140" t="str">
-        <v>https://boards.greenhouse.io/gitlab/jobs/8512220002</v>
+        <v>https://boards.greenhouse.io/figma/jobs/6160732004</v>
       </c>
       <c r="M140">
         <v>200</v>
@@ -8836,7 +8836,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O140" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P140" t="str">
         <v>Today</v>
@@ -8848,45 +8848,45 @@
         <v>No</v>
       </c>
       <c r="S140">
-        <v>55</v>
+        <v>80</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>job-52edb6a4</v>
+        <v>job-7297f499</v>
       </c>
       <c r="B141" t="str">
-        <v>Staff Product Manager,  RevOps &amp; Finance Systems</v>
+        <v>Manager, Product Management - Roundtripping</v>
       </c>
       <c r="C141" t="str">
-        <v>GitLab</v>
+        <v>Figma</v>
       </c>
       <c r="D141" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E141" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F141" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G141" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H141" t="str">
-        <v>Remote, US</v>
+        <v>New York, NY • United States</v>
       </c>
       <c r="I141" t="str">
-        <v>Remote</v>
+        <v>New York</v>
       </c>
       <c r="J141" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K141" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L141" t="str">
-        <v>https://boards.greenhouse.io/gitlab/jobs/8612937002</v>
+        <v>https://boards.greenhouse.io/figma/jobs/6104919004</v>
       </c>
       <c r="M141">
         <v>200</v>
@@ -8895,7 +8895,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O141" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P141" t="str">
         <v>Today</v>
@@ -8907,15 +8907,15 @@
         <v>No</v>
       </c>
       <c r="S141">
-        <v>47</v>
+        <v>81</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>job-3a743e4f</v>
+        <v>job-19031a2a</v>
       </c>
       <c r="B142" t="str">
-        <v>Manager, Product Management - Figma Platform Experience</v>
+        <v>Manager, Product Management - Roundtripping (London, United Kingdom)</v>
       </c>
       <c r="C142" t="str">
         <v>Figma</v>
@@ -8924,7 +8924,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E142" t="str">
-        <v>Technical Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F142" t="str">
         <v>3-6 yrs</v>
@@ -8933,10 +8933,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H142" t="str">
-        <v>San Francisco, CA • New York, NY • United States</v>
+        <v>London, England</v>
       </c>
       <c r="I142" t="str">
-        <v>San Francisco</v>
+        <v>London</v>
       </c>
       <c r="J142" t="str">
         <v>On-site</v>
@@ -8945,7 +8945,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L142" t="str">
-        <v>https://boards.greenhouse.io/figma/jobs/6160732004</v>
+        <v>https://boards.greenhouse.io/figma/jobs/6149007004</v>
       </c>
       <c r="M142">
         <v>200</v>
@@ -8954,7 +8954,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O142" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P142" t="str">
         <v>Today</v>
@@ -8963,18 +8963,18 @@
         <v>No</v>
       </c>
       <c r="R142" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S142">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>job-7297f499</v>
+        <v>job-099ff647</v>
       </c>
       <c r="B143" t="str">
-        <v>Manager, Product Management - Roundtripping</v>
+        <v>Product Manager, Acquisition</v>
       </c>
       <c r="C143" t="str">
         <v>Figma</v>
@@ -8992,10 +8992,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H143" t="str">
-        <v>New York, NY • United States</v>
+        <v>San Francisco, CA • New York, NY • United States</v>
       </c>
       <c r="I143" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J143" t="str">
         <v>On-site</v>
@@ -9004,7 +9004,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L143" t="str">
-        <v>https://boards.greenhouse.io/figma/jobs/6104919004</v>
+        <v>https://boards.greenhouse.io/figma/jobs/6119781004</v>
       </c>
       <c r="M143">
         <v>200</v>
@@ -9013,27 +9013,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O143" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P143" t="str">
         <v>Today</v>
       </c>
       <c r="Q143" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R143" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S143">
-        <v>37</v>
+        <v>42</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>job-19031a2a</v>
+        <v>job-714f8c79</v>
       </c>
       <c r="B144" t="str">
-        <v>Manager, Product Management - Roundtripping (London, United Kingdom)</v>
+        <v>Product Manager, AI Growth</v>
       </c>
       <c r="C144" t="str">
         <v>Figma</v>
@@ -9042,7 +9042,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E144" t="str">
-        <v>Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F144" t="str">
         <v>3-6 yrs</v>
@@ -9051,10 +9051,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H144" t="str">
-        <v>London, England</v>
+        <v>San Francisco, CA • New York, NY • United States</v>
       </c>
       <c r="I144" t="str">
-        <v>London</v>
+        <v>San Francisco</v>
       </c>
       <c r="J144" t="str">
         <v>On-site</v>
@@ -9063,7 +9063,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L144" t="str">
-        <v>https://boards.greenhouse.io/figma/jobs/6149007004</v>
+        <v>https://boards.greenhouse.io/figma/jobs/5989185004</v>
       </c>
       <c r="M144">
         <v>200</v>
@@ -9072,27 +9072,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O144" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P144" t="str">
         <v>Today</v>
       </c>
       <c r="Q144" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R144" t="str">
         <v>No</v>
       </c>
       <c r="S144">
-        <v>77</v>
+        <v>37</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>job-099ff647</v>
+        <v>job-6c338367</v>
       </c>
       <c r="B145" t="str">
-        <v>Product Manager, Acquisition</v>
+        <v>Product Manager, Developer Platform</v>
       </c>
       <c r="C145" t="str">
         <v>Figma</v>
@@ -9101,7 +9101,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E145" t="str">
-        <v>Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F145" t="str">
         <v>3-6 yrs</v>
@@ -9122,7 +9122,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L145" t="str">
-        <v>https://boards.greenhouse.io/figma/jobs/6119781004</v>
+        <v>https://boards.greenhouse.io/figma/jobs/6100482004</v>
       </c>
       <c r="M145">
         <v>200</v>
@@ -9131,30 +9131,30 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O145" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P145" t="str">
         <v>Today</v>
       </c>
       <c r="Q145" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R145" t="str">
         <v>No</v>
       </c>
       <c r="S145">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>job-714f8c79</v>
+        <v>job-3c3dabbf</v>
       </c>
       <c r="B146" t="str">
-        <v>Product Manager, AI Growth</v>
+        <v>Director of Product Management, Advertiser Growth</v>
       </c>
       <c r="C146" t="str">
-        <v>Figma</v>
+        <v>Pinterest</v>
       </c>
       <c r="D146" t="str">
         <v>LinkedIn</v>
@@ -9163,16 +9163,16 @@
         <v>AI &amp; Growth PM</v>
       </c>
       <c r="F146" t="str">
-        <v>3-6 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G146" t="str">
-        <v>2-5 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H146" t="str">
-        <v>San Francisco, CA • New York, NY • United States</v>
+        <v>Palo Alto, CA, US; Seattle, WA, US; New York, NY, US</v>
       </c>
       <c r="I146" t="str">
-        <v>San Francisco</v>
+        <v>New York</v>
       </c>
       <c r="J146" t="str">
         <v>On-site</v>
@@ -9181,16 +9181,16 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L146" t="str">
-        <v>https://boards.greenhouse.io/figma/jobs/5989185004</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/8132504</v>
       </c>
       <c r="M146">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N146" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O146" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P146" t="str">
         <v>Today</v>
@@ -9199,27 +9199,27 @@
         <v>No</v>
       </c>
       <c r="R146" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S146">
-        <v>90</v>
+        <v>61</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>job-6c338367</v>
+        <v>job-2ca475a2</v>
       </c>
       <c r="B147" t="str">
-        <v>Product Manager, Developer Platform</v>
+        <v>Product Manager II, Content Compliance</v>
       </c>
       <c r="C147" t="str">
-        <v>Figma</v>
+        <v>Pinterest</v>
       </c>
       <c r="D147" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E147" t="str">
-        <v>Technical Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F147" t="str">
         <v>3-6 yrs</v>
@@ -9228,48 +9228,48 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H147" t="str">
-        <v>San Francisco, CA • New York, NY • United States</v>
+        <v>San Francisco, CA, US; Seattle, WA, US; Remote, CA, US</v>
       </c>
       <c r="I147" t="str">
         <v>San Francisco</v>
       </c>
       <c r="J147" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K147" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L147" t="str">
-        <v>https://boards.greenhouse.io/figma/jobs/6100482004</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/7901910</v>
       </c>
       <c r="M147">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N147" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O147" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P147" t="str">
         <v>Today</v>
       </c>
       <c r="Q147" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R147" t="str">
         <v>No</v>
       </c>
       <c r="S147">
-        <v>52</v>
+        <v>94</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>job-3c3dabbf</v>
+        <v>job-1e7e452c</v>
       </c>
       <c r="B148" t="str">
-        <v>Director of Product Management, Advertiser Growth</v>
+        <v>Product Manager II, Search Experience</v>
       </c>
       <c r="C148" t="str">
         <v>Pinterest</v>
@@ -9278,28 +9278,28 @@
         <v>LinkedIn</v>
       </c>
       <c r="E148" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Product Manager</v>
       </c>
       <c r="F148" t="str">
-        <v>8+ yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G148" t="str">
-        <v>8+ yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H148" t="str">
-        <v>Palo Alto, CA, US; Seattle, WA, US; New York, NY, US</v>
+        <v>San Francisco, CA, US; Remote, US</v>
       </c>
       <c r="I148" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J148" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K148" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L148" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/8132504</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/8042279</v>
       </c>
       <c r="M148">
         <v>403</v>
@@ -9308,27 +9308,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O148" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P148" t="str">
         <v>Today</v>
       </c>
       <c r="Q148" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R148" t="str">
         <v>No</v>
       </c>
       <c r="S148">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>job-2ca475a2</v>
+        <v>job-65802650</v>
       </c>
       <c r="B149" t="str">
-        <v>Product Manager II, Content Compliance</v>
+        <v>Sr. Product Manager, Core Saving Experience</v>
       </c>
       <c r="C149" t="str">
         <v>Pinterest</v>
@@ -9337,7 +9337,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E149" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F149" t="str">
         <v>3-6 yrs</v>
@@ -9346,7 +9346,7 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H149" t="str">
-        <v>San Francisco, CA, US; Seattle, WA, US; Remote, CA, US</v>
+        <v>San Francisco, CA, US; Remote, US</v>
       </c>
       <c r="I149" t="str">
         <v>San Francisco</v>
@@ -9358,7 +9358,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L149" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/7901910</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/8046820</v>
       </c>
       <c r="M149">
         <v>403</v>
@@ -9367,7 +9367,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O149" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P149" t="str">
         <v>Today</v>
@@ -9376,18 +9376,18 @@
         <v>No</v>
       </c>
       <c r="R149" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S149">
-        <v>82</v>
+        <v>28</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>job-1e7e452c</v>
+        <v>job-3070654d</v>
       </c>
       <c r="B150" t="str">
-        <v>Product Manager II, Search Experience</v>
+        <v>Sr. Product Manager, Search Personalization</v>
       </c>
       <c r="C150" t="str">
         <v>Pinterest</v>
@@ -9396,7 +9396,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E150" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F150" t="str">
         <v>3-6 yrs</v>
@@ -9417,7 +9417,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L150" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/8042279</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/8015494</v>
       </c>
       <c r="M150">
         <v>403</v>
@@ -9426,7 +9426,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O150" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P150" t="str">
         <v>Today</v>
@@ -9435,18 +9435,18 @@
         <v>No</v>
       </c>
       <c r="R150" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S150">
-        <v>84</v>
+        <v>34</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>job-65802650</v>
+        <v>job-2683c45a</v>
       </c>
       <c r="B151" t="str">
-        <v>Sr. Product Manager, Core Saving Experience</v>
+        <v>Sr. Product Manager, TwoTwenty</v>
       </c>
       <c r="C151" t="str">
         <v>Pinterest</v>
@@ -9476,7 +9476,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L151" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/8046820</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/8015519</v>
       </c>
       <c r="M151">
         <v>403</v>
@@ -9485,7 +9485,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O151" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P151" t="str">
         <v>Today</v>
@@ -9497,15 +9497,15 @@
         <v>No</v>
       </c>
       <c r="S151">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>job-3070654d</v>
+        <v>job-04d22fdc</v>
       </c>
       <c r="B152" t="str">
-        <v>Sr. Product Manager, Search Personalization</v>
+        <v>Staff Product Manager, Ads Measurement</v>
       </c>
       <c r="C152" t="str">
         <v>Pinterest</v>
@@ -9517,25 +9517,25 @@
         <v>Senior Product Manager</v>
       </c>
       <c r="F152" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G152" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H152" t="str">
-        <v>San Francisco, CA, US; Remote, US</v>
+        <v>New York, NY, US</v>
       </c>
       <c r="I152" t="str">
-        <v>San Francisco</v>
+        <v>New York</v>
       </c>
       <c r="J152" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K152" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L152" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/8015494</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/7683962</v>
       </c>
       <c r="M152">
         <v>403</v>
@@ -9544,7 +9544,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O152" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P152" t="str">
         <v>Today</v>
@@ -9556,15 +9556,15 @@
         <v>No</v>
       </c>
       <c r="S152">
-        <v>38</v>
+        <v>71</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>job-2683c45a</v>
+        <v>job-336a1df9</v>
       </c>
       <c r="B153" t="str">
-        <v>Sr. Product Manager, TwoTwenty</v>
+        <v>Staff Product Manager, Applied Science</v>
       </c>
       <c r="C153" t="str">
         <v>Pinterest</v>
@@ -9576,10 +9576,10 @@
         <v>Senior Product Manager</v>
       </c>
       <c r="F153" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G153" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H153" t="str">
         <v>San Francisco, CA, US; Remote, US</v>
@@ -9594,7 +9594,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L153" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/8015519</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/8082033</v>
       </c>
       <c r="M153">
         <v>403</v>
@@ -9603,7 +9603,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O153" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P153" t="str">
         <v>Today</v>
@@ -9615,15 +9615,15 @@
         <v>No</v>
       </c>
       <c r="S153">
-        <v>28</v>
+        <v>40</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>job-04d22fdc</v>
+        <v>job-0f93578d</v>
       </c>
       <c r="B154" t="str">
-        <v>Staff Product Manager, Ads Measurement</v>
+        <v>Staff Product Manager, Billing</v>
       </c>
       <c r="C154" t="str">
         <v>Pinterest</v>
@@ -9641,19 +9641,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H154" t="str">
-        <v>New York, NY, US</v>
+        <v>San Francisco, CA, US; Remote, CA, US</v>
       </c>
       <c r="I154" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J154" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K154" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L154" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/7683962</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/7955593</v>
       </c>
       <c r="M154">
         <v>403</v>
@@ -9662,27 +9662,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O154" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P154" t="str">
         <v>Today</v>
       </c>
       <c r="Q154" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R154" t="str">
         <v>No</v>
       </c>
       <c r="S154">
-        <v>26</v>
+        <v>79</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>job-336a1df9</v>
+        <v>job-7b34548d</v>
       </c>
       <c r="B155" t="str">
-        <v>Staff Product Manager, Applied Science</v>
+        <v>Staff Product Manager, Connections</v>
       </c>
       <c r="C155" t="str">
         <v>Pinterest</v>
@@ -9712,7 +9712,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L155" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/8082033</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/7525112</v>
       </c>
       <c r="M155">
         <v>403</v>
@@ -9721,7 +9721,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O155" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P155" t="str">
         <v>Today</v>
@@ -9733,15 +9733,15 @@
         <v>No</v>
       </c>
       <c r="S155">
-        <v>46</v>
+        <v>34</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>job-0f93578d</v>
+        <v>job-7e8b8408</v>
       </c>
       <c r="B156" t="str">
-        <v>Staff Product Manager, Billing</v>
+        <v>Staff Product Manager, Programmatic Ads</v>
       </c>
       <c r="C156" t="str">
         <v>Pinterest</v>
@@ -9771,7 +9771,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L156" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/7955593</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/7959458</v>
       </c>
       <c r="M156">
         <v>403</v>
@@ -9780,7 +9780,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O156" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P156" t="str">
         <v>Today</v>
@@ -9789,39 +9789,39 @@
         <v>No</v>
       </c>
       <c r="R156" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S156">
-        <v>66</v>
+        <v>30</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>job-7b34548d</v>
+        <v>job-7f4873ac</v>
       </c>
       <c r="B157" t="str">
-        <v>Staff Product Manager, Connections</v>
+        <v>Director of Product, Logistics</v>
       </c>
       <c r="C157" t="str">
-        <v>Pinterest</v>
+        <v>Instacart</v>
       </c>
       <c r="D157" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E157" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F157" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G157" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H157" t="str">
-        <v>San Francisco, CA, US; Remote, US</v>
+        <v>United States - Remote</v>
       </c>
       <c r="I157" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J157" t="str">
         <v>Remote</v>
@@ -9830,39 +9830,39 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L157" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/7525112</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8198282</v>
       </c>
       <c r="M157">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N157" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O157" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P157" t="str">
         <v>Today</v>
       </c>
       <c r="Q157" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R157" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S157">
-        <v>83</v>
+        <v>25</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>job-7e8b8408</v>
+        <v>job-6d240672</v>
       </c>
       <c r="B158" t="str">
-        <v>Staff Product Manager, Programmatic Ads</v>
+        <v>Senior Product Manager, Ads Quality</v>
       </c>
       <c r="C158" t="str">
-        <v>Pinterest</v>
+        <v>Instacart</v>
       </c>
       <c r="D158" t="str">
         <v>LinkedIn</v>
@@ -9877,10 +9877,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H158" t="str">
-        <v>San Francisco, CA, US; Remote, CA, US</v>
+        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
       </c>
       <c r="I158" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J158" t="str">
         <v>Remote</v>
@@ -9889,36 +9889,36 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L158" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/7959458</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8077512</v>
       </c>
       <c r="M158">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N158" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O158" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P158" t="str">
         <v>Today</v>
       </c>
       <c r="Q158" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R158" t="str">
         <v>No</v>
       </c>
       <c r="S158">
-        <v>35</v>
+        <v>28</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>job-7f4873ac</v>
+        <v>job-2be59ce2</v>
       </c>
       <c r="B159" t="str">
-        <v>Director of Product, Logistics</v>
+        <v>Senior Product Manager, Advertiser Experience</v>
       </c>
       <c r="C159" t="str">
         <v>Instacart</v>
@@ -9927,13 +9927,13 @@
         <v>LinkedIn</v>
       </c>
       <c r="E159" t="str">
-        <v>Product Lead / Director</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F159" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G159" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H159" t="str">
         <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
@@ -9948,7 +9948,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L159" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8198284</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8120471</v>
       </c>
       <c r="M159">
         <v>200</v>
@@ -9957,13 +9957,13 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O159" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P159" t="str">
         <v>Today</v>
       </c>
       <c r="Q159" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R159" t="str">
         <v>No</v>
@@ -9974,10 +9974,10 @@
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>job-6d240672</v>
+        <v>job-69064914</v>
       </c>
       <c r="B160" t="str">
-        <v>Senior Product Manager, Ads Quality</v>
+        <v>Senior Product Manager, AI Control Studio</v>
       </c>
       <c r="C160" t="str">
         <v>Instacart</v>
@@ -10007,7 +10007,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L160" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8077512</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8198161</v>
       </c>
       <c r="M160">
         <v>200</v>
@@ -10016,27 +10016,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O160" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P160" t="str">
         <v>Today</v>
       </c>
       <c r="Q160" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R160" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S160">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>job-2be59ce2</v>
+        <v>job-6ddb2cbc</v>
       </c>
       <c r="B161" t="str">
-        <v>Senior Product Manager, Advertiser Experience</v>
+        <v>Senior Product Manager, Catalog</v>
       </c>
       <c r="C161" t="str">
         <v>Instacart</v>
@@ -10066,7 +10066,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L161" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8120471</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8143272</v>
       </c>
       <c r="M161">
         <v>200</v>
@@ -10075,7 +10075,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O161" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P161" t="str">
         <v>Today</v>
@@ -10087,15 +10087,15 @@
         <v>No</v>
       </c>
       <c r="S161">
-        <v>64</v>
+        <v>70</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>job-69064914</v>
+        <v>job-3d0cfe30</v>
       </c>
       <c r="B162" t="str">
-        <v>Senior Product Manager, AI Control Studio</v>
+        <v>Senior Product Manager, Order Quality</v>
       </c>
       <c r="C162" t="str">
         <v>Instacart</v>
@@ -10125,7 +10125,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L162" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8198161</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8203109</v>
       </c>
       <c r="M162">
         <v>200</v>
@@ -10134,27 +10134,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O162" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P162" t="str">
         <v>Today</v>
       </c>
       <c r="Q162" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R162" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S162">
-        <v>65</v>
+        <v>79</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>job-6ddb2cbc</v>
+        <v>job-2319ed86</v>
       </c>
       <c r="B163" t="str">
-        <v>Senior Product Manager, Catalog</v>
+        <v>Senior Product Manager, Retailer Platform</v>
       </c>
       <c r="C163" t="str">
         <v>Instacart</v>
@@ -10172,7 +10172,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H163" t="str">
-        <v>United States - Remote</v>
+        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
       </c>
       <c r="I163" t="str">
         <v>Remote</v>
@@ -10184,7 +10184,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L163" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8143270</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8014062</v>
       </c>
       <c r="M163">
         <v>200</v>
@@ -10193,57 +10193,57 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O163" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P163" t="str">
         <v>Today</v>
       </c>
       <c r="Q163" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R163" t="str">
         <v>No</v>
       </c>
       <c r="S163">
-        <v>66</v>
+        <v>36</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>job-3d0cfe30</v>
+        <v>job-6d0cde89</v>
       </c>
       <c r="B164" t="str">
-        <v>Senior Product Manager, Order Quality</v>
+        <v>Product Manager II - Ads</v>
       </c>
       <c r="C164" t="str">
-        <v>Instacart</v>
+        <v>Razorpay</v>
       </c>
       <c r="D164" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E164" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F164" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G164" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H164" t="str">
-        <v>United States - Remote</v>
+        <v>Bengaluru</v>
       </c>
       <c r="I164" t="str">
-        <v>Remote</v>
+        <v>Bengaluru</v>
       </c>
       <c r="J164" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K164" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L164" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8203107</v>
+        <v>https://boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4729533005</v>
       </c>
       <c r="M164">
         <v>200</v>
@@ -10252,7 +10252,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O164" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P164" t="str">
         <v>Today</v>
@@ -10264,45 +10264,45 @@
         <v>No</v>
       </c>
       <c r="S164">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>job-2319ed86</v>
+        <v>job-7c247a79</v>
       </c>
       <c r="B165" t="str">
-        <v>Senior Product Manager, Retailer Platform</v>
+        <v>Product Manager II - AI</v>
       </c>
       <c r="C165" t="str">
-        <v>Instacart</v>
+        <v>Razorpay</v>
       </c>
       <c r="D165" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E165" t="str">
-        <v>Senior Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F165" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G165" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H165" t="str">
-        <v>United States - Remote</v>
+        <v>Bengaluru</v>
       </c>
       <c r="I165" t="str">
-        <v>Remote</v>
+        <v>Bengaluru</v>
       </c>
       <c r="J165" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K165" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L165" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8014060</v>
+        <v>https://boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4699107005</v>
       </c>
       <c r="M165">
         <v>200</v>
@@ -10311,7 +10311,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O165" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P165" t="str">
         <v>Today</v>
@@ -10320,27 +10320,27 @@
         <v>Yes</v>
       </c>
       <c r="R165" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S165">
-        <v>60</v>
+        <v>83</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>job-6d0cde89</v>
+        <v>job-1c3166e2</v>
       </c>
       <c r="B166" t="str">
-        <v>Product Manager II - Ads</v>
+        <v>Product Manager, API Agents</v>
       </c>
       <c r="C166" t="str">
-        <v>Razorpay</v>
+        <v>OpenAI</v>
       </c>
       <c r="D166" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E166" t="str">
-        <v>Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F166" t="str">
         <v>3-6 yrs</v>
@@ -10349,19 +10349,19 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H166" t="str">
-        <v>Bengaluru</v>
+        <v>San Francisco</v>
       </c>
       <c r="I166" t="str">
-        <v>Bengaluru</v>
+        <v>San Francisco</v>
       </c>
       <c r="J166" t="str">
         <v>On-site</v>
       </c>
       <c r="K166" t="str">
-        <v>$140k - $220k USD + Equity</v>
+        <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L166" t="str">
-        <v>https://boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4729533005</v>
+        <v>https://jobs.ashbyhq.com/openai/fc38c6bf-5330-435c-99b6-1bcf1f5829a8</v>
       </c>
       <c r="M166">
         <v>200</v>
@@ -10370,36 +10370,36 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O166" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P166" t="str">
         <v>Today</v>
       </c>
       <c r="Q166" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R166" t="str">
         <v>No</v>
       </c>
       <c r="S166">
-        <v>58</v>
+        <v>80</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>job-7c247a79</v>
+        <v>job-6d2b24fc</v>
       </c>
       <c r="B167" t="str">
-        <v>Product Manager II - AI</v>
+        <v>Product Manager, Sensitive Deployments</v>
       </c>
       <c r="C167" t="str">
-        <v>Razorpay</v>
+        <v>OpenAI</v>
       </c>
       <c r="D167" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E167" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Product Manager</v>
       </c>
       <c r="F167" t="str">
         <v>3-6 yrs</v>
@@ -10408,19 +10408,19 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H167" t="str">
-        <v>Bengaluru</v>
+        <v>San Francisco</v>
       </c>
       <c r="I167" t="str">
-        <v>Bengaluru</v>
+        <v>San Francisco</v>
       </c>
       <c r="J167" t="str">
         <v>On-site</v>
       </c>
       <c r="K167" t="str">
-        <v>$140k - $220k USD + Equity</v>
+        <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L167" t="str">
-        <v>https://boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4699107005</v>
+        <v>https://jobs.ashbyhq.com/openai/05a8cae8-81bd-4f7b-bc48-41ef1bd67e5d</v>
       </c>
       <c r="M167">
         <v>200</v>
@@ -10429,27 +10429,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O167" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P167" t="str">
         <v>Today</v>
       </c>
       <c r="Q167" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R167" t="str">
         <v>Yes</v>
       </c>
       <c r="S167">
-        <v>61</v>
+        <v>95</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>job-1c3166e2</v>
+        <v>job-184a9e13</v>
       </c>
       <c r="B168" t="str">
-        <v>Product Manager, API Agents</v>
+        <v>Product Manager, API Infrastructure</v>
       </c>
       <c r="C168" t="str">
         <v>OpenAI</v>
@@ -10458,7 +10458,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E168" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F168" t="str">
         <v>3-6 yrs</v>
@@ -10479,7 +10479,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L168" t="str">
-        <v>https://jobs.ashbyhq.com/openai/fc38c6bf-5330-435c-99b6-1bcf1f5829a8</v>
+        <v>https://jobs.ashbyhq.com/openai/7ffa2a14-fa9c-46cb-a30a-1f7a35ae904a</v>
       </c>
       <c r="M168">
         <v>200</v>
@@ -10488,7 +10488,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O168" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P168" t="str">
         <v>Today</v>
@@ -10497,18 +10497,18 @@
         <v>Yes</v>
       </c>
       <c r="R168" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S168">
-        <v>49</v>
+        <v>111</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>job-6d2b24fc</v>
+        <v>job-61ec6778</v>
       </c>
       <c r="B169" t="str">
-        <v>Product Manager, Sensitive Deployments</v>
+        <v>Product Manager, Safety Measurement</v>
       </c>
       <c r="C169" t="str">
         <v>OpenAI</v>
@@ -10538,7 +10538,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L169" t="str">
-        <v>https://jobs.ashbyhq.com/openai/05a8cae8-81bd-4f7b-bc48-41ef1bd67e5d</v>
+        <v>https://jobs.ashbyhq.com/openai/fbc7ebaf-3a26-406d-9ff6-f166f3e246a2</v>
       </c>
       <c r="M169">
         <v>200</v>
@@ -10547,7 +10547,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O169" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P169" t="str">
         <v>Today</v>
@@ -10559,15 +10559,15 @@
         <v>Yes</v>
       </c>
       <c r="S169">
-        <v>119</v>
+        <v>41</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>job-184a9e13</v>
+        <v>job-32d0b9c4</v>
       </c>
       <c r="B170" t="str">
-        <v>Product Manager, API Infrastructure</v>
+        <v>Product Manager, Financial Engineering</v>
       </c>
       <c r="C170" t="str">
         <v>OpenAI</v>
@@ -10576,7 +10576,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E170" t="str">
-        <v>Technical Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F170" t="str">
         <v>3-6 yrs</v>
@@ -10597,7 +10597,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L170" t="str">
-        <v>https://jobs.ashbyhq.com/openai/7ffa2a14-fa9c-46cb-a30a-1f7a35ae904a</v>
+        <v>https://jobs.ashbyhq.com/openai/0f4da2b4-df8a-4560-809d-d0a6ac1ad9bc</v>
       </c>
       <c r="M170">
         <v>200</v>
@@ -10606,7 +10606,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O170" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P170" t="str">
         <v>Today</v>
@@ -10618,15 +10618,15 @@
         <v>Yes</v>
       </c>
       <c r="S170">
-        <v>105</v>
+        <v>44</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>job-61ec6778</v>
+        <v>job-675130d5</v>
       </c>
       <c r="B171" t="str">
-        <v>Product Manager, Safety Measurement</v>
+        <v>Product Manager, Core Models</v>
       </c>
       <c r="C171" t="str">
         <v>OpenAI</v>
@@ -10635,7 +10635,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E171" t="str">
-        <v>Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F171" t="str">
         <v>3-6 yrs</v>
@@ -10656,7 +10656,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L171" t="str">
-        <v>https://jobs.ashbyhq.com/openai/fbc7ebaf-3a26-406d-9ff6-f166f3e246a2</v>
+        <v>https://jobs.ashbyhq.com/openai/33b8effb-b048-4934-a279-87fff192a330</v>
       </c>
       <c r="M171">
         <v>200</v>
@@ -10665,7 +10665,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O171" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P171" t="str">
         <v>Today</v>
@@ -10674,18 +10674,18 @@
         <v>Yes</v>
       </c>
       <c r="R171" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S171">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>job-32d0b9c4</v>
+        <v>job-032480cd</v>
       </c>
       <c r="B172" t="str">
-        <v>Product Manager, Financial Engineering</v>
+        <v>Product Manager, Youth</v>
       </c>
       <c r="C172" t="str">
         <v>OpenAI</v>
@@ -10715,7 +10715,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L172" t="str">
-        <v>https://jobs.ashbyhq.com/openai/0f4da2b4-df8a-4560-809d-d0a6ac1ad9bc</v>
+        <v>https://jobs.ashbyhq.com/openai/cc0d0d86-eb9d-44a0-a6a4-42bbb6066b4b</v>
       </c>
       <c r="M172">
         <v>200</v>
@@ -10724,7 +10724,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O172" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P172" t="str">
         <v>Today</v>
@@ -10736,15 +10736,15 @@
         <v>Yes</v>
       </c>
       <c r="S172">
-        <v>112</v>
+        <v>95</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>job-675130d5</v>
+        <v>job-50e54898</v>
       </c>
       <c r="B173" t="str">
-        <v>Product Manager, Core Models</v>
+        <v>Product Manager, Learning</v>
       </c>
       <c r="C173" t="str">
         <v>OpenAI</v>
@@ -10753,7 +10753,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E173" t="str">
-        <v>Technical Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F173" t="str">
         <v>3-6 yrs</v>
@@ -10774,7 +10774,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L173" t="str">
-        <v>https://jobs.ashbyhq.com/openai/33b8effb-b048-4934-a279-87fff192a330</v>
+        <v>https://jobs.ashbyhq.com/openai/5953fed7-1466-4e90-94c9-43716a55e032</v>
       </c>
       <c r="M173">
         <v>200</v>
@@ -10783,7 +10783,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O173" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P173" t="str">
         <v>Today</v>
@@ -10792,18 +10792,18 @@
         <v>Yes</v>
       </c>
       <c r="R173" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S173">
-        <v>50</v>
+        <v>92</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>job-032480cd</v>
+        <v>job-0df96522</v>
       </c>
       <c r="B174" t="str">
-        <v>Product Manager, Youth</v>
+        <v>Product Manager, Multimodal Safety</v>
       </c>
       <c r="C174" t="str">
         <v>OpenAI</v>
@@ -10833,7 +10833,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L174" t="str">
-        <v>https://jobs.ashbyhq.com/openai/cc0d0d86-eb9d-44a0-a6a4-42bbb6066b4b</v>
+        <v>https://jobs.ashbyhq.com/openai/70d5259a-f18c-4595-bf52-ec03eeeeac4c</v>
       </c>
       <c r="M174">
         <v>200</v>
@@ -10842,7 +10842,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O174" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P174" t="str">
         <v>Today</v>
@@ -10854,15 +10854,15 @@
         <v>Yes</v>
       </c>
       <c r="S174">
-        <v>52</v>
+        <v>118</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>job-50e54898</v>
+        <v>job-47895783</v>
       </c>
       <c r="B175" t="str">
-        <v>Product Manager, Learning</v>
+        <v>Product Manager, Enterprise Identity</v>
       </c>
       <c r="C175" t="str">
         <v>OpenAI</v>
@@ -10892,7 +10892,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L175" t="str">
-        <v>https://jobs.ashbyhq.com/openai/5953fed7-1466-4e90-94c9-43716a55e032</v>
+        <v>https://jobs.ashbyhq.com/openai/83f6d415-9462-4afc-a539-ca8d996e011a</v>
       </c>
       <c r="M175">
         <v>200</v>
@@ -10901,7 +10901,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O175" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P175" t="str">
         <v>Today</v>
@@ -10910,18 +10910,18 @@
         <v>Yes</v>
       </c>
       <c r="R175" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S175">
-        <v>61</v>
+        <v>64</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>job-0df96522</v>
+        <v>job-3fd38143</v>
       </c>
       <c r="B176" t="str">
-        <v>Product Manager, Multimodal Safety</v>
+        <v>Rosalind Life Sciences Product Manager</v>
       </c>
       <c r="C176" t="str">
         <v>OpenAI</v>
@@ -10951,7 +10951,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L176" t="str">
-        <v>https://jobs.ashbyhq.com/openai/70d5259a-f18c-4595-bf52-ec03eeeeac4c</v>
+        <v>https://jobs.ashbyhq.com/openai/2b5c3a30-8e8b-4845-be40-0617b0c9fd43</v>
       </c>
       <c r="M176">
         <v>200</v>
@@ -10960,7 +10960,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O176" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P176" t="str">
         <v>Today</v>
@@ -10969,18 +10969,18 @@
         <v>Yes</v>
       </c>
       <c r="R176" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S176">
-        <v>73</v>
+        <v>59</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>job-47895783</v>
+        <v>job-1fef334a</v>
       </c>
       <c r="B177" t="str">
-        <v>Product Manager, Enterprise Identity</v>
+        <v>Product Manager, Technology Vertical</v>
       </c>
       <c r="C177" t="str">
         <v>OpenAI</v>
@@ -11010,7 +11010,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L177" t="str">
-        <v>https://jobs.ashbyhq.com/openai/83f6d415-9462-4afc-a539-ca8d996e011a</v>
+        <v>https://jobs.ashbyhq.com/openai/137e3df0-2bd4-4ad4-8edb-8455a7fdc912</v>
       </c>
       <c r="M177">
         <v>200</v>
@@ -11019,7 +11019,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O177" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P177" t="str">
         <v>Today</v>
@@ -11028,24 +11028,24 @@
         <v>Yes</v>
       </c>
       <c r="R177" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S177">
-        <v>61</v>
+        <v>110</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>job-3fd38143</v>
+        <v>job-5db12f92</v>
       </c>
       <c r="B178" t="str">
-        <v>Rosalind Life Sciences Product Manager</v>
+        <v>Product Manager (Builder)</v>
       </c>
       <c r="C178" t="str">
-        <v>OpenAI</v>
+        <v>Perplexity</v>
       </c>
       <c r="D178" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E178" t="str">
         <v>Product Manager</v>
@@ -11069,7 +11069,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L178" t="str">
-        <v>https://jobs.ashbyhq.com/openai/2b5c3a30-8e8b-4845-be40-0617b0c9fd43</v>
+        <v>https://jobs.ashbyhq.com/perplexity/f25e190e-0508-4707-b575-fcaed358dc13</v>
       </c>
       <c r="M178">
         <v>200</v>
@@ -11078,7 +11078,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O178" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P178" t="str">
         <v>Today</v>
@@ -11090,30 +11090,30 @@
         <v>No</v>
       </c>
       <c r="S178">
-        <v>65</v>
+        <v>46</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>job-1fef334a</v>
+        <v>job-1fe57ea5</v>
       </c>
       <c r="B179" t="str">
-        <v>Product Manager, Technology Vertical</v>
+        <v>Member of Technical Staff (TPM, Inference)</v>
       </c>
       <c r="C179" t="str">
-        <v>OpenAI</v>
+        <v>Perplexity</v>
       </c>
       <c r="D179" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E179" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F179" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G179" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H179" t="str">
         <v>San Francisco</v>
@@ -11128,7 +11128,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L179" t="str">
-        <v>https://jobs.ashbyhq.com/openai/137e3df0-2bd4-4ad4-8edb-8455a7fdc912</v>
+        <v>https://jobs.ashbyhq.com/perplexity/0c5d5a82-bfed-4786-b411-79073979af07</v>
       </c>
       <c r="M179">
         <v>200</v>
@@ -11137,7 +11137,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O179" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P179" t="str">
         <v>Today</v>
@@ -11146,18 +11146,18 @@
         <v>Yes</v>
       </c>
       <c r="R179" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S179">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>job-5db12f92</v>
+        <v>job-12403072</v>
       </c>
       <c r="B180" t="str">
-        <v>Product Manager (Builder)</v>
+        <v>Product Manager, Mobile Apps</v>
       </c>
       <c r="C180" t="str">
         <v>Perplexity</v>
@@ -11187,7 +11187,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L180" t="str">
-        <v>https://jobs.ashbyhq.com/perplexity/f25e190e-0508-4707-b575-fcaed358dc13</v>
+        <v>https://jobs.ashbyhq.com/perplexity/3c9c051f-e6ca-4a70-9abf-1f640e154ee1</v>
       </c>
       <c r="M180">
         <v>200</v>
@@ -11196,7 +11196,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O180" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P180" t="str">
         <v>Today</v>
@@ -11208,15 +11208,15 @@
         <v>No</v>
       </c>
       <c r="S180">
-        <v>115</v>
+        <v>71</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>job-1fe57ea5</v>
+        <v>job-10379173</v>
       </c>
       <c r="B181" t="str">
-        <v>Member of Technical Staff (TPM, Inference)</v>
+        <v>Product Manager, Core Experience</v>
       </c>
       <c r="C181" t="str">
         <v>Perplexity</v>
@@ -11225,13 +11225,13 @@
         <v>Wellfound</v>
       </c>
       <c r="E181" t="str">
-        <v>Senior Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F181" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G181" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H181" t="str">
         <v>San Francisco</v>
@@ -11246,7 +11246,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L181" t="str">
-        <v>https://jobs.ashbyhq.com/perplexity/0c5d5a82-bfed-4786-b411-79073979af07</v>
+        <v>https://jobs.ashbyhq.com/perplexity/6f3c5131-2efa-400c-8248-44203a4dbfbb</v>
       </c>
       <c r="M181">
         <v>200</v>
@@ -11255,7 +11255,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O181" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P181" t="str">
         <v>Today</v>
@@ -11264,18 +11264,18 @@
         <v>Yes</v>
       </c>
       <c r="R181" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S181">
-        <v>97</v>
+        <v>101</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>job-12403072</v>
+        <v>job-247da510</v>
       </c>
       <c r="B182" t="str">
-        <v>Product Manager, Mobile Apps</v>
+        <v>Product Manager, AI Capabilities</v>
       </c>
       <c r="C182" t="str">
         <v>Perplexity</v>
@@ -11284,7 +11284,7 @@
         <v>Wellfound</v>
       </c>
       <c r="E182" t="str">
-        <v>Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F182" t="str">
         <v>3-6 yrs</v>
@@ -11305,7 +11305,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L182" t="str">
-        <v>https://jobs.ashbyhq.com/perplexity/3c9c051f-e6ca-4a70-9abf-1f640e154ee1</v>
+        <v>https://jobs.ashbyhq.com/perplexity/7f880194-7276-4b46-8a50-58b48da8882e</v>
       </c>
       <c r="M182">
         <v>200</v>
@@ -11314,7 +11314,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O182" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P182" t="str">
         <v>Today</v>
@@ -11326,15 +11326,15 @@
         <v>No</v>
       </c>
       <c r="S182">
-        <v>115</v>
+        <v>79</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>job-10379173</v>
+        <v>job-757a314d</v>
       </c>
       <c r="B183" t="str">
-        <v>Product Manager, Core Experience</v>
+        <v>Product Manager, Growth</v>
       </c>
       <c r="C183" t="str">
         <v>Perplexity</v>
@@ -11343,7 +11343,7 @@
         <v>Wellfound</v>
       </c>
       <c r="E183" t="str">
-        <v>Technical Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F183" t="str">
         <v>3-6 yrs</v>
@@ -11352,10 +11352,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H183" t="str">
-        <v>San Francisco</v>
+        <v>New York City</v>
       </c>
       <c r="I183" t="str">
-        <v>San Francisco</v>
+        <v>New York</v>
       </c>
       <c r="J183" t="str">
         <v>On-site</v>
@@ -11364,7 +11364,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L183" t="str">
-        <v>https://jobs.ashbyhq.com/perplexity/6f3c5131-2efa-400c-8248-44203a4dbfbb</v>
+        <v>https://jobs.ashbyhq.com/perplexity/fa088d92-b08b-43f7-9232-275b0ae08827</v>
       </c>
       <c r="M183">
         <v>200</v>
@@ -11373,7 +11373,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O183" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P183" t="str">
         <v>Today</v>
@@ -11382,18 +11382,18 @@
         <v>Yes</v>
       </c>
       <c r="R183" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S183">
-        <v>62</v>
+        <v>108</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>job-247da510</v>
+        <v>job-376e5ff5</v>
       </c>
       <c r="B184" t="str">
-        <v>Product Manager, AI Capabilities</v>
+        <v>Product Manager, SMB Growth</v>
       </c>
       <c r="C184" t="str">
         <v>Perplexity</v>
@@ -11411,10 +11411,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H184" t="str">
-        <v>San Francisco</v>
+        <v>New York City</v>
       </c>
       <c r="I184" t="str">
-        <v>San Francisco</v>
+        <v>New York</v>
       </c>
       <c r="J184" t="str">
         <v>On-site</v>
@@ -11423,7 +11423,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L184" t="str">
-        <v>https://jobs.ashbyhq.com/perplexity/7f880194-7276-4b46-8a50-58b48da8882e</v>
+        <v>https://jobs.ashbyhq.com/perplexity/182ab2ec-6fb1-409b-a2dc-63c7832b0a13</v>
       </c>
       <c r="M184">
         <v>200</v>
@@ -11432,7 +11432,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O184" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P184" t="str">
         <v>Today</v>
@@ -11444,24 +11444,24 @@
         <v>Yes</v>
       </c>
       <c r="S184">
-        <v>64</v>
+        <v>40</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>job-757a314d</v>
+        <v>job-6fff938e</v>
       </c>
       <c r="B185" t="str">
-        <v>Product Manager, Growth</v>
+        <v>Product Manager - Marketplace</v>
       </c>
       <c r="C185" t="str">
-        <v>Perplexity</v>
+        <v>Supabase</v>
       </c>
       <c r="D185" t="str">
         <v>Wellfound</v>
       </c>
       <c r="E185" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Product Manager</v>
       </c>
       <c r="F185" t="str">
         <v>3-6 yrs</v>
@@ -11470,19 +11470,19 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H185" t="str">
-        <v>New York City</v>
+        <v>Remote, Global</v>
       </c>
       <c r="I185" t="str">
-        <v>New York</v>
+        <v>Remote</v>
       </c>
       <c r="J185" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K185" t="str">
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L185" t="str">
-        <v>https://jobs.ashbyhq.com/perplexity/fa088d92-b08b-43f7-9232-275b0ae08827</v>
+        <v>https://jobs.ashbyhq.com/supabase/23c9ce7e-6b7b-4316-8f00-8f318e902441</v>
       </c>
       <c r="M185">
         <v>200</v>
@@ -11491,7 +11491,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O185" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P185" t="str">
         <v>Today</v>
@@ -11503,24 +11503,24 @@
         <v>No</v>
       </c>
       <c r="S185">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>job-376e5ff5</v>
+        <v>job-49f97312</v>
       </c>
       <c r="B186" t="str">
-        <v>Product Manager, SMB Growth</v>
+        <v>Product Manager - Security &amp; Trust (EMEA/AMER)</v>
       </c>
       <c r="C186" t="str">
-        <v>Perplexity</v>
+        <v>Supabase</v>
       </c>
       <c r="D186" t="str">
         <v>Wellfound</v>
       </c>
       <c r="E186" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Product Manager</v>
       </c>
       <c r="F186" t="str">
         <v>3-6 yrs</v>
@@ -11529,19 +11529,19 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H186" t="str">
-        <v>New York City</v>
+        <v>Remote, Global</v>
       </c>
       <c r="I186" t="str">
-        <v>New York</v>
+        <v>Remote</v>
       </c>
       <c r="J186" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K186" t="str">
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L186" t="str">
-        <v>https://jobs.ashbyhq.com/perplexity/182ab2ec-6fb1-409b-a2dc-63c7832b0a13</v>
+        <v>https://jobs.ashbyhq.com/supabase/b8010a28-109c-46a9-b8b7-c7f9b24077fa</v>
       </c>
       <c r="M186">
         <v>200</v>
@@ -11550,7 +11550,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O186" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P186" t="str">
         <v>Today</v>
@@ -11562,15 +11562,15 @@
         <v>No</v>
       </c>
       <c r="S186">
-        <v>118</v>
+        <v>72</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>job-6fff938e</v>
+        <v>job-064fa6b5</v>
       </c>
       <c r="B187" t="str">
-        <v>Product Manager - Marketplace</v>
+        <v>Product Manager - Strategic Partner Integrations (Bay Area based)</v>
       </c>
       <c r="C187" t="str">
         <v>Supabase</v>
@@ -11588,10 +11588,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H187" t="str">
-        <v>Remote, Global</v>
+        <v>Remote, Bay Area, CA</v>
       </c>
       <c r="I187" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J187" t="str">
         <v>Remote</v>
@@ -11600,7 +11600,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L187" t="str">
-        <v>https://jobs.ashbyhq.com/supabase/23c9ce7e-6b7b-4316-8f00-8f318e902441</v>
+        <v>https://jobs.ashbyhq.com/supabase/68a397e7-8a1a-4566-ae41-e8c61dd6ed93</v>
       </c>
       <c r="M187">
         <v>200</v>
@@ -11609,7 +11609,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O187" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P187" t="str">
         <v>Today</v>
@@ -11618,27 +11618,27 @@
         <v>Yes</v>
       </c>
       <c r="R187" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S187">
-        <v>53</v>
+        <v>76</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>job-49f97312</v>
+        <v>job-7da017c6</v>
       </c>
       <c r="B188" t="str">
-        <v>Product Manager - Security &amp; Trust (EMEA/AMER)</v>
+        <v>Product Manager | Vendor Intelligence &amp; Marketplace</v>
       </c>
       <c r="C188" t="str">
-        <v>Supabase</v>
+        <v>Ramp</v>
       </c>
       <c r="D188" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E188" t="str">
-        <v>Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F188" t="str">
         <v>3-6 yrs</v>
@@ -11647,19 +11647,19 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H188" t="str">
-        <v>Remote, Global</v>
+        <v>New York, NY (HQ)</v>
       </c>
       <c r="I188" t="str">
-        <v>Remote</v>
+        <v>New York</v>
       </c>
       <c r="J188" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K188" t="str">
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L188" t="str">
-        <v>https://jobs.ashbyhq.com/supabase/b8010a28-109c-46a9-b8b7-c7f9b24077fa</v>
+        <v>https://jobs.ashbyhq.com/ramp/cf3516f6-4d6b-4872-831f-c8ef4a3078ee</v>
       </c>
       <c r="M188">
         <v>200</v>
@@ -11668,7 +11668,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O188" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P188" t="str">
         <v>Today</v>
@@ -11677,24 +11677,24 @@
         <v>Yes</v>
       </c>
       <c r="R188" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S188">
-        <v>69</v>
+        <v>91</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>job-064fa6b5</v>
+        <v>job-338455bd</v>
       </c>
       <c r="B189" t="str">
-        <v>Product Manager - Strategic Partner Integrations (Bay Area based)</v>
+        <v>Product Manager | Tax</v>
       </c>
       <c r="C189" t="str">
-        <v>Supabase</v>
+        <v>Ramp</v>
       </c>
       <c r="D189" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E189" t="str">
         <v>Product Manager</v>
@@ -11706,19 +11706,19 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H189" t="str">
-        <v>Remote, Bay Area, CA</v>
+        <v>New York, NY (HQ)</v>
       </c>
       <c r="I189" t="str">
-        <v>San Francisco</v>
+        <v>New York</v>
       </c>
       <c r="J189" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K189" t="str">
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L189" t="str">
-        <v>https://jobs.ashbyhq.com/supabase/68a397e7-8a1a-4566-ae41-e8c61dd6ed93</v>
+        <v>https://jobs.ashbyhq.com/ramp/881f9f7d-9ec5-4b69-b50d-a67000264ca8</v>
       </c>
       <c r="M189">
         <v>200</v>
@@ -11727,7 +11727,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O189" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P189" t="str">
         <v>Today</v>
@@ -11736,18 +11736,18 @@
         <v>Yes</v>
       </c>
       <c r="R189" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S189">
-        <v>112</v>
+        <v>63</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>job-7da017c6</v>
+        <v>job-6744eb00</v>
       </c>
       <c r="B190" t="str">
-        <v>Product Manager | Vendor Intelligence &amp; Marketplace</v>
+        <v>Product Manager | International</v>
       </c>
       <c r="C190" t="str">
         <v>Ramp</v>
@@ -11756,13 +11756,13 @@
         <v>LinkedIn</v>
       </c>
       <c r="E190" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Product Manager</v>
       </c>
       <c r="F190" t="str">
-        <v>3-6 yrs</v>
+        <v>1-3 yrs</v>
       </c>
       <c r="G190" t="str">
-        <v>2-5 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H190" t="str">
         <v>New York, NY (HQ)</v>
@@ -11777,7 +11777,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L190" t="str">
-        <v>https://jobs.ashbyhq.com/ramp/cf3516f6-4d6b-4872-831f-c8ef4a3078ee</v>
+        <v>https://jobs.ashbyhq.com/ramp/8baec095-2235-41ab-ab64-9abc57823b4b</v>
       </c>
       <c r="M190">
         <v>200</v>
@@ -11786,7 +11786,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O190" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P190" t="str">
         <v>Today</v>
@@ -11795,39 +11795,39 @@
         <v>Yes</v>
       </c>
       <c r="R190" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S190">
-        <v>101</v>
+        <v>54</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>job-338455bd</v>
+        <v>job-497b065e</v>
       </c>
       <c r="B191" t="str">
-        <v>Product Manager | Tax</v>
+        <v>Senior Product Manager, Mobile</v>
       </c>
       <c r="C191" t="str">
-        <v>Ramp</v>
+        <v>Sentry</v>
       </c>
       <c r="D191" t="str">
-        <v>LinkedIn</v>
+        <v>Indeed</v>
       </c>
       <c r="E191" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F191" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G191" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H191" t="str">
-        <v>New York, NY (HQ)</v>
+        <v>Vienna, Austria</v>
       </c>
       <c r="I191" t="str">
-        <v>New York</v>
+        <v>Vienna</v>
       </c>
       <c r="J191" t="str">
         <v>On-site</v>
@@ -11836,7 +11836,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L191" t="str">
-        <v>https://jobs.ashbyhq.com/ramp/881f9f7d-9ec5-4b69-b50d-a67000264ca8</v>
+        <v>https://jobs.ashbyhq.com/sentry/6a973e19-6736-4973-8a87-043fcbcd553e</v>
       </c>
       <c r="M191">
         <v>200</v>
@@ -11845,7 +11845,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O191" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P191" t="str">
         <v>Today</v>
@@ -11854,39 +11854,39 @@
         <v>Yes</v>
       </c>
       <c r="R191" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S191">
-        <v>41</v>
+        <v>47</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>job-6744eb00</v>
+        <v>job-33169045</v>
       </c>
       <c r="B192" t="str">
-        <v>Product Manager | International</v>
+        <v>Product Manager</v>
       </c>
       <c r="C192" t="str">
-        <v>Ramp</v>
+        <v>Linear</v>
       </c>
       <c r="D192" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E192" t="str">
         <v>Product Manager</v>
       </c>
       <c r="F192" t="str">
-        <v>1-3 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G192" t="str">
-        <v>0-2 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H192" t="str">
-        <v>New York, NY (HQ)</v>
+        <v>North America</v>
       </c>
       <c r="I192" t="str">
-        <v>New York</v>
+        <v>North America</v>
       </c>
       <c r="J192" t="str">
         <v>On-site</v>
@@ -11895,7 +11895,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L192" t="str">
-        <v>https://jobs.ashbyhq.com/ramp/8baec095-2235-41ab-ab64-9abc57823b4b</v>
+        <v>https://jobs.ashbyhq.com/linear/b7669c4b-eeca-421d-ba9a-d90203f6fcb2</v>
       </c>
       <c r="M192">
         <v>200</v>
@@ -11904,7 +11904,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O192" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P192" t="str">
         <v>Today</v>
@@ -11913,27 +11913,27 @@
         <v>Yes</v>
       </c>
       <c r="R192" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S192">
-        <v>63</v>
+        <v>47</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>job-497b065e</v>
+        <v>job-048a3bb1</v>
       </c>
       <c r="B193" t="str">
-        <v>Senior Product Manager, Mobile</v>
+        <v>Head of Product Management - Artist Products</v>
       </c>
       <c r="C193" t="str">
-        <v>Sentry</v>
+        <v>Spotify</v>
       </c>
       <c r="D193" t="str">
-        <v>Indeed</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E193" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F193" t="str">
         <v>5-8 yrs</v>
@@ -11942,19 +11942,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H193" t="str">
-        <v>Vienna, Austria</v>
+        <v>New York, NY</v>
       </c>
       <c r="I193" t="str">
-        <v>Vienna</v>
+        <v>New York</v>
       </c>
       <c r="J193" t="str">
         <v>On-site</v>
       </c>
       <c r="K193" t="str">
-        <v>$160k - $240k USD + Equity</v>
+        <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L193" t="str">
-        <v>https://jobs.ashbyhq.com/sentry/6a973e19-6736-4973-8a87-043fcbcd553e</v>
+        <v>https://jobs.lever.co/spotify/e2c7bbb8-f873-42c7-811f-0bd45bf452ae</v>
       </c>
       <c r="M193">
         <v>200</v>
@@ -11963,7 +11963,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O193" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P193" t="str">
         <v>Today</v>
@@ -11972,48 +11972,48 @@
         <v>Yes</v>
       </c>
       <c r="R193" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S193">
-        <v>61</v>
+        <v>72</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>job-33169045</v>
+        <v>job-39d9f7fb</v>
       </c>
       <c r="B194" t="str">
-        <v>Product Manager</v>
+        <v>Principal Product Manager - Audio and Media Playback</v>
       </c>
       <c r="C194" t="str">
-        <v>Linear</v>
+        <v>Spotify</v>
       </c>
       <c r="D194" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E194" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F194" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G194" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H194" t="str">
-        <v>North America</v>
+        <v>Stockholm</v>
       </c>
       <c r="I194" t="str">
-        <v>North America</v>
+        <v>Stockholm</v>
       </c>
       <c r="J194" t="str">
         <v>On-site</v>
       </c>
       <c r="K194" t="str">
-        <v>$160k - $240k USD + Equity</v>
+        <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L194" t="str">
-        <v>https://jobs.ashbyhq.com/linear/b7669c4b-eeca-421d-ba9a-d90203f6fcb2</v>
+        <v>https://jobs.lever.co/spotify/080868dd-fc8c-4648-b6ab-6780d8ca3d63</v>
       </c>
       <c r="M194">
         <v>200</v>
@@ -12022,7 +12022,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O194" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P194" t="str">
         <v>Today</v>
@@ -12034,15 +12034,15 @@
         <v>No</v>
       </c>
       <c r="S194">
-        <v>49</v>
+        <v>88</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>job-048a3bb1</v>
+        <v>job-5b32c75d</v>
       </c>
       <c r="B195" t="str">
-        <v>Head of Product Management - Artist Products</v>
+        <v>Principal Product Manager - Personalization</v>
       </c>
       <c r="C195" t="str">
         <v>Spotify</v>
@@ -12051,7 +12051,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E195" t="str">
-        <v>Product Lead / Director</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F195" t="str">
         <v>5-8 yrs</v>
@@ -12060,10 +12060,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H195" t="str">
-        <v>New York, NY</v>
+        <v>London</v>
       </c>
       <c r="I195" t="str">
-        <v>New York</v>
+        <v>London</v>
       </c>
       <c r="J195" t="str">
         <v>On-site</v>
@@ -12072,7 +12072,7 @@
         <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L195" t="str">
-        <v>https://jobs.lever.co/spotify/e2c7bbb8-f873-42c7-811f-0bd45bf452ae</v>
+        <v>https://jobs.lever.co/spotify/e74bfb24-55de-4d93-b228-ae38b8fdfbea</v>
       </c>
       <c r="M195">
         <v>200</v>
@@ -12081,7 +12081,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O195" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P195" t="str">
         <v>Today</v>
@@ -12098,10 +12098,10 @@
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>job-39d9f7fb</v>
+        <v>job-61f86f2b</v>
       </c>
       <c r="B196" t="str">
-        <v>Principal Product Manager - Audio and Media Playback</v>
+        <v>Product Manager - Customer Service Platform</v>
       </c>
       <c r="C196" t="str">
         <v>Spotify</v>
@@ -12110,7 +12110,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E196" t="str">
-        <v>Senior Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F196" t="str">
         <v>5-8 yrs</v>
@@ -12119,10 +12119,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H196" t="str">
-        <v>Stockholm</v>
+        <v>London</v>
       </c>
       <c r="I196" t="str">
-        <v>Stockholm</v>
+        <v>London</v>
       </c>
       <c r="J196" t="str">
         <v>On-site</v>
@@ -12131,7 +12131,7 @@
         <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L196" t="str">
-        <v>https://jobs.lever.co/spotify/080868dd-fc8c-4648-b6ab-6780d8ca3d63</v>
+        <v>https://jobs.lever.co/spotify/7f0a8faa-f4f5-4db9-9f51-4101d6a29b34</v>
       </c>
       <c r="M196">
         <v>200</v>
@@ -12140,7 +12140,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O196" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P196" t="str">
         <v>Today</v>
@@ -12152,15 +12152,15 @@
         <v>No</v>
       </c>
       <c r="S196">
-        <v>31</v>
+        <v>82</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>job-5b32c75d</v>
+        <v>job-1a230b4c</v>
       </c>
       <c r="B197" t="str">
-        <v>Principal Product Manager - Personalization</v>
+        <v>Product Manager - Data Platform</v>
       </c>
       <c r="C197" t="str">
         <v>Spotify</v>
@@ -12169,7 +12169,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E197" t="str">
-        <v>Senior Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F197" t="str">
         <v>5-8 yrs</v>
@@ -12178,10 +12178,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H197" t="str">
-        <v>London</v>
+        <v>Toronto</v>
       </c>
       <c r="I197" t="str">
-        <v>London</v>
+        <v>Toronto</v>
       </c>
       <c r="J197" t="str">
         <v>On-site</v>
@@ -12190,7 +12190,7 @@
         <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L197" t="str">
-        <v>https://jobs.lever.co/spotify/e74bfb24-55de-4d93-b228-ae38b8fdfbea</v>
+        <v>https://jobs.lever.co/spotify/03437e2a-2d5e-4593-9e97-11271014932e</v>
       </c>
       <c r="M197">
         <v>200</v>
@@ -12199,7 +12199,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O197" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P197" t="str">
         <v>Today</v>
@@ -12211,15 +12211,15 @@
         <v>No</v>
       </c>
       <c r="S197">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>job-61f86f2b</v>
+        <v>job-1ba340a4</v>
       </c>
       <c r="B198" t="str">
-        <v>Product Manager - Customer Service Platform</v>
+        <v>Senior Product Manager - Audiobooks Format Foundations</v>
       </c>
       <c r="C198" t="str">
         <v>Spotify</v>
@@ -12228,7 +12228,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E198" t="str">
-        <v>Technical Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F198" t="str">
         <v>5-8 yrs</v>
@@ -12249,7 +12249,7 @@
         <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L198" t="str">
-        <v>https://jobs.lever.co/spotify/7f0a8faa-f4f5-4db9-9f51-4101d6a29b34</v>
+        <v>https://jobs.lever.co/spotify/e7b01c1e-4246-4f31-83ea-9219c8b22c83</v>
       </c>
       <c r="M198">
         <v>200</v>
@@ -12258,7 +12258,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O198" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P198" t="str">
         <v>Today</v>
@@ -12270,15 +12270,15 @@
         <v>No</v>
       </c>
       <c r="S198">
-        <v>30</v>
+        <v>69</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>job-1a230b4c</v>
+        <v>job-3a0c9449</v>
       </c>
       <c r="B199" t="str">
-        <v>Product Manager - Data Platform</v>
+        <v>Senior Product Manager - Subscriptions</v>
       </c>
       <c r="C199" t="str">
         <v>Spotify</v>
@@ -12287,7 +12287,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E199" t="str">
-        <v>Technical Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F199" t="str">
         <v>5-8 yrs</v>
@@ -12296,10 +12296,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H199" t="str">
-        <v>Toronto</v>
+        <v>London</v>
       </c>
       <c r="I199" t="str">
-        <v>Toronto</v>
+        <v>London</v>
       </c>
       <c r="J199" t="str">
         <v>On-site</v>
@@ -12308,7 +12308,7 @@
         <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L199" t="str">
-        <v>https://jobs.lever.co/spotify/03437e2a-2d5e-4593-9e97-11271014932e</v>
+        <v>https://jobs.lever.co/spotify/a57db22d-dc0d-4f36-9a2e-34acdf1ec046</v>
       </c>
       <c r="M199">
         <v>200</v>
@@ -12317,7 +12317,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O199" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P199" t="str">
         <v>Today</v>
@@ -12329,15 +12329,15 @@
         <v>No</v>
       </c>
       <c r="S199">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>job-1ba340a4</v>
+        <v>job-32cac657</v>
       </c>
       <c r="B200" t="str">
-        <v>Senior Product Manager - Audiobooks Format Foundations</v>
+        <v>Senior Product Manager - User Platform</v>
       </c>
       <c r="C200" t="str">
         <v>Spotify</v>
@@ -12367,7 +12367,7 @@
         <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L200" t="str">
-        <v>https://jobs.lever.co/spotify/e7b01c1e-4246-4f31-83ea-9219c8b22c83</v>
+        <v>https://jobs.lever.co/spotify/ee45924c-894c-4ea0-9c93-c5221894063f</v>
       </c>
       <c r="M200">
         <v>200</v>
@@ -12376,7 +12376,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O200" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P200" t="str">
         <v>Today</v>
@@ -12388,24 +12388,24 @@
         <v>No</v>
       </c>
       <c r="S200">
-        <v>33</v>
+        <v>57</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>job-3a0c9449</v>
+        <v>job-4d0308c8</v>
       </c>
       <c r="B201" t="str">
-        <v>Senior Product Manager - Subscriptions</v>
+        <v>Technical Program Manager (TPM)</v>
       </c>
       <c r="C201" t="str">
-        <v>Spotify</v>
+        <v>Palantir</v>
       </c>
       <c r="D201" t="str">
-        <v>LinkedIn</v>
+        <v>Instahyre</v>
       </c>
       <c r="E201" t="str">
-        <v>Senior Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F201" t="str">
         <v>5-8 yrs</v>
@@ -12414,10 +12414,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H201" t="str">
-        <v>London</v>
+        <v>New York, NY</v>
       </c>
       <c r="I201" t="str">
-        <v>London</v>
+        <v>New York</v>
       </c>
       <c r="J201" t="str">
         <v>On-site</v>
@@ -12426,7 +12426,7 @@
         <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L201" t="str">
-        <v>https://jobs.lever.co/spotify/a57db22d-dc0d-4f36-9a2e-34acdf1ec046</v>
+        <v>https://jobs.lever.co/palantir/7eb0dedb-37ee-4175-b29f-10a9e4340076</v>
       </c>
       <c r="M201">
         <v>200</v>
@@ -12435,7 +12435,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O201" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P201" t="str">
         <v>Today</v>
@@ -12447,24 +12447,24 @@
         <v>No</v>
       </c>
       <c r="S201">
-        <v>80</v>
+        <v>57</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>job-32cac657</v>
+        <v>job-593275cb</v>
       </c>
       <c r="B202" t="str">
-        <v>Senior Product Manager - User Platform</v>
+        <v>Technical Program Manager (TPM) - Defense</v>
       </c>
       <c r="C202" t="str">
-        <v>Spotify</v>
+        <v>Palantir</v>
       </c>
       <c r="D202" t="str">
-        <v>LinkedIn</v>
+        <v>Instahyre</v>
       </c>
       <c r="E202" t="str">
-        <v>Senior Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F202" t="str">
         <v>5-8 yrs</v>
@@ -12473,10 +12473,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H202" t="str">
-        <v>London</v>
+        <v>Washington, D.C.</v>
       </c>
       <c r="I202" t="str">
-        <v>London</v>
+        <v>Washington</v>
       </c>
       <c r="J202" t="str">
         <v>On-site</v>
@@ -12485,7 +12485,7 @@
         <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L202" t="str">
-        <v>https://jobs.lever.co/spotify/ee45924c-894c-4ea0-9c93-c5221894063f</v>
+        <v>https://jobs.lever.co/palantir/bd16f7ad-3bee-48fd-9902-b3ee9698b608</v>
       </c>
       <c r="M202">
         <v>200</v>
@@ -12494,7 +12494,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O202" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P202" t="str">
         <v>Today</v>
@@ -12506,45 +12506,45 @@
         <v>No</v>
       </c>
       <c r="S202">
-        <v>69</v>
+        <v>47</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>job-4d0308c8</v>
+        <v>job-343d8912</v>
       </c>
       <c r="B203" t="str">
-        <v>Technical Program Manager (TPM)</v>
+        <v>Associate Product Manager (APM) - Growth &amp; Merchant Onboarding</v>
       </c>
       <c r="C203" t="str">
-        <v>Palantir</v>
+        <v>Razorpay</v>
       </c>
       <c r="D203" t="str">
-        <v>Instahyre</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E203" t="str">
-        <v>Technical Product Manager</v>
+        <v>Associate Product Manager</v>
       </c>
       <c r="F203" t="str">
-        <v>5-8 yrs</v>
+        <v>1-3 yrs</v>
       </c>
       <c r="G203" t="str">
-        <v>5-8 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H203" t="str">
-        <v>New York, NY</v>
+        <v>Bengaluru, Karnataka</v>
       </c>
       <c r="I203" t="str">
-        <v>New York</v>
+        <v>Bengaluru</v>
       </c>
       <c r="J203" t="str">
-        <v>On-site</v>
+        <v>Hybrid</v>
       </c>
       <c r="K203" t="str">
-        <v>$150k - $220k USD + RSUs</v>
+        <v>₹18L - ₹26L PA + ESOPs</v>
       </c>
       <c r="L203" t="str">
-        <v>https://jobs.lever.co/palantir/7eb0dedb-37ee-4175-b29f-10a9e4340076</v>
+        <v>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited</v>
       </c>
       <c r="M203">
         <v>200</v>
@@ -12553,7 +12553,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O203" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P203" t="str">
         <v>Today</v>
@@ -12562,27 +12562,27 @@
         <v>Yes</v>
       </c>
       <c r="R203" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S203">
-        <v>80</v>
+        <v>42</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>job-593275cb</v>
+        <v>job-739e0b9f</v>
       </c>
       <c r="B204" t="str">
-        <v>Technical Program Manager (TPM) - Defense</v>
+        <v>Senior Product Manager - Consumer Checkout &amp; Loyalty</v>
       </c>
       <c r="C204" t="str">
-        <v>Palantir</v>
+        <v>Swiggy</v>
       </c>
       <c r="D204" t="str">
-        <v>Instahyre</v>
+        <v>Naukri</v>
       </c>
       <c r="E204" t="str">
-        <v>Technical Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F204" t="str">
         <v>5-8 yrs</v>
@@ -12591,19 +12591,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H204" t="str">
-        <v>Washington, D.C.</v>
+        <v>Bengaluru, Karnataka</v>
       </c>
       <c r="I204" t="str">
-        <v>Washington</v>
+        <v>Bengaluru</v>
       </c>
       <c r="J204" t="str">
-        <v>On-site</v>
+        <v>Hybrid</v>
       </c>
       <c r="K204" t="str">
-        <v>$150k - $220k USD + RSUs</v>
+        <v>₹45L - ₹65L PA + ESOPs</v>
       </c>
       <c r="L204" t="str">
-        <v>https://jobs.lever.co/palantir/bd16f7ad-3bee-48fd-9902-b3ee9698b608</v>
+        <v>https://careers.swiggy.com/</v>
       </c>
       <c r="M204">
         <v>200</v>
@@ -12612,7 +12612,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O204" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P204" t="str">
         <v>Today</v>
@@ -12621,57 +12621,57 @@
         <v>Yes</v>
       </c>
       <c r="R204" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S204">
-        <v>59</v>
+        <v>115</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>job-343d8912</v>
+        <v>job-66154b1b</v>
       </c>
       <c r="B205" t="str">
-        <v>Associate Product Manager (APM) - Growth &amp; Merchant Onboarding</v>
+        <v>Senior Product Manager - 10-Minute Dark Store &amp; Logistics Dispatch</v>
       </c>
       <c r="C205" t="str">
-        <v>Razorpay</v>
+        <v>Zepto</v>
       </c>
       <c r="D205" t="str">
-        <v>LinkedIn</v>
+        <v>Naukri</v>
       </c>
       <c r="E205" t="str">
-        <v>Associate Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F205" t="str">
-        <v>1-3 yrs</v>
+        <v>4-7 yrs</v>
       </c>
       <c r="G205" t="str">
-        <v>0-2 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H205" t="str">
-        <v>Bengaluru, Karnataka</v>
+        <v>Mumbai, Maharashtra</v>
       </c>
       <c r="I205" t="str">
-        <v>Bengaluru</v>
+        <v>Mumbai</v>
       </c>
       <c r="J205" t="str">
-        <v>Hybrid</v>
+        <v>On-site</v>
       </c>
       <c r="K205" t="str">
-        <v>₹18L - ₹26L PA + ESOPs</v>
+        <v>₹42L - ₹60L PA + ESOPs</v>
       </c>
       <c r="L205" t="str">
-        <v>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited</v>
+        <v>https://www.zeptonow.com/careers</v>
       </c>
       <c r="M205">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="N205" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O205" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P205" t="str">
         <v>Today</v>
@@ -12683,18 +12683,18 @@
         <v>Yes</v>
       </c>
       <c r="S205">
-        <v>42</v>
+        <v>94</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>job-739e0b9f</v>
+        <v>job-169943b4</v>
       </c>
       <c r="B206" t="str">
-        <v>Senior Product Manager - Consumer Checkout &amp; Loyalty</v>
+        <v>Senior Product Manager - Customer Experience &amp; Live Support AI</v>
       </c>
       <c r="C206" t="str">
-        <v>Swiggy</v>
+        <v>Zomato</v>
       </c>
       <c r="D206" t="str">
         <v>Naukri</v>
@@ -12709,28 +12709,28 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H206" t="str">
-        <v>Bengaluru, Karnataka</v>
+        <v>Gurgaon, Haryana</v>
       </c>
       <c r="I206" t="str">
-        <v>Bengaluru</v>
+        <v>Gurgaon</v>
       </c>
       <c r="J206" t="str">
-        <v>Hybrid</v>
+        <v>On-site</v>
       </c>
       <c r="K206" t="str">
         <v>₹45L - ₹65L PA + ESOPs</v>
       </c>
       <c r="L206" t="str">
-        <v>https://careers.swiggy.com/</v>
+        <v>https://www.zomato.com/careers</v>
       </c>
       <c r="M206">
-        <v>200</v>
+        <v>503</v>
       </c>
       <c r="N206" t="str">
-        <v>ACTIVE / 100% VALID</v>
+        <v>BROKEN / 404</v>
       </c>
       <c r="O206" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P206" t="str">
         <v>Today</v>
@@ -12742,54 +12742,54 @@
         <v>Yes</v>
       </c>
       <c r="S206">
-        <v>115</v>
+        <v>95</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
-        <v>job-66154b1b</v>
+        <v>job-23756e58</v>
       </c>
       <c r="B207" t="str">
-        <v>Senior Product Manager - 10-Minute Dark Store &amp; Logistics Dispatch</v>
+        <v>Associate Product Manager (APM) - Social Commerce &amp; Creator Tools</v>
       </c>
       <c r="C207" t="str">
-        <v>Zepto</v>
+        <v>Meesho</v>
       </c>
       <c r="D207" t="str">
         <v>Naukri</v>
       </c>
       <c r="E207" t="str">
-        <v>Senior Product Manager</v>
+        <v>Associate Product Manager</v>
       </c>
       <c r="F207" t="str">
-        <v>4-7 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="G207" t="str">
-        <v>2-5 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H207" t="str">
-        <v>Mumbai, Maharashtra</v>
+        <v>Bengaluru, Karnataka</v>
       </c>
       <c r="I207" t="str">
-        <v>Mumbai</v>
+        <v>Bengaluru</v>
       </c>
       <c r="J207" t="str">
-        <v>On-site</v>
+        <v>Hybrid</v>
       </c>
       <c r="K207" t="str">
-        <v>₹42L - ₹60L PA + ESOPs</v>
+        <v>₹18L - ₹25L PA + ESOPs</v>
       </c>
       <c r="L207" t="str">
-        <v>https://www.zeptonow.com/careers</v>
+        <v>https://www.meesho.io/jobs</v>
       </c>
       <c r="M207">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N207" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O207" t="str">
-        <v>2026-09-24</v>
+        <v>2026-09-25</v>
       </c>
       <c r="P207" t="str">
         <v>Today</v>
@@ -12801,89 +12801,89 @@
         <v>Yes</v>
       </c>
       <c r="S207">
-        <v>94</v>
+        <v>65</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
-        <v>job-169943b4</v>
+        <v>job-6900691e</v>
       </c>
       <c r="B208" t="str">
-        <v>Senior Product Manager - Customer Experience &amp; Live Support AI</v>
+        <v>Product Owner - Core Banking &amp; Credit Line Engine</v>
       </c>
       <c r="C208" t="str">
-        <v>Zomato</v>
+        <v>CRED</v>
       </c>
       <c r="D208" t="str">
-        <v>Naukri</v>
+        <v>Instahyre</v>
       </c>
       <c r="E208" t="str">
-        <v>Senior Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F208" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G208" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H208" t="str">
-        <v>Gurgaon, Haryana</v>
+        <v>Bengaluru, Karnataka</v>
       </c>
       <c r="I208" t="str">
-        <v>Gurgaon</v>
+        <v>Bengaluru</v>
       </c>
       <c r="J208" t="str">
         <v>On-site</v>
       </c>
       <c r="K208" t="str">
-        <v>₹45L - ₹65L PA + ESOPs</v>
+        <v>₹35L - ₹52L PA + ESOPs</v>
       </c>
       <c r="L208" t="str">
-        <v>https://www.zomato.com/careers</v>
+        <v>https://careers.cred.club/</v>
       </c>
       <c r="M208">
-        <v>503</v>
+        <v>200</v>
       </c>
       <c r="N208" t="str">
-        <v>BROKEN / 404</v>
+        <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O208" t="str">
         <v>2026-09-24</v>
       </c>
       <c r="P208" t="str">
-        <v>Today</v>
+        <v>1d ago</v>
       </c>
       <c r="Q208" t="str">
         <v>Yes</v>
       </c>
       <c r="R208" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S208">
-        <v>95</v>
+        <v>76</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
-        <v>job-23756e58</v>
+        <v>job-1e98cdb6</v>
       </c>
       <c r="B209" t="str">
-        <v>Associate Product Manager (APM) - Social Commerce &amp; Creator Tools</v>
+        <v>Product Lead - Merchant QR, Soundbox &amp; Offline Payments Rails</v>
       </c>
       <c r="C209" t="str">
-        <v>Meesho</v>
+        <v>PhonePe</v>
       </c>
       <c r="D209" t="str">
-        <v>Naukri</v>
+        <v>Instahyre</v>
       </c>
       <c r="E209" t="str">
-        <v>Associate Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F209" t="str">
-        <v>0-2 yrs</v>
+        <v>7-11 yrs</v>
       </c>
       <c r="G209" t="str">
-        <v>0-2 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H209" t="str">
         <v>Bengaluru, Karnataka</v>
@@ -12892,13 +12892,13 @@
         <v>Bengaluru</v>
       </c>
       <c r="J209" t="str">
-        <v>Hybrid</v>
+        <v>On-site</v>
       </c>
       <c r="K209" t="str">
-        <v>₹18L - ₹25L PA + ESOPs</v>
+        <v>₹65L - ₹90L PA + ESOPs</v>
       </c>
       <c r="L209" t="str">
-        <v>https://www.meesho.io/jobs</v>
+        <v>https://www.phonepe.com/careers/</v>
       </c>
       <c r="M209">
         <v>200</v>
@@ -12910,7 +12910,7 @@
         <v>2026-09-24</v>
       </c>
       <c r="P209" t="str">
-        <v>Today</v>
+        <v>1d ago</v>
       </c>
       <c r="Q209" t="str">
         <v>Yes</v>
@@ -12919,24 +12919,24 @@
         <v>Yes</v>
       </c>
       <c r="S209">
-        <v>65</v>
+        <v>125</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
-        <v>job-6900691e</v>
+        <v>job-6ee4d4a9</v>
       </c>
       <c r="B210" t="str">
-        <v>Product Owner - Core Banking &amp; Credit Line Engine</v>
+        <v>Product Manager - Supply Chain Forecasting &amp; Dynamic Pricing</v>
       </c>
       <c r="C210" t="str">
-        <v>CRED</v>
+        <v>Flipkart</v>
       </c>
       <c r="D210" t="str">
-        <v>Instahyre</v>
+        <v>IIMJobs</v>
       </c>
       <c r="E210" t="str">
-        <v>Technical Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F210" t="str">
         <v>3-6 yrs</v>
@@ -12951,13 +12951,13 @@
         <v>Bengaluru</v>
       </c>
       <c r="J210" t="str">
-        <v>On-site</v>
+        <v>Hybrid</v>
       </c>
       <c r="K210" t="str">
-        <v>₹35L - ₹52L PA + ESOPs</v>
+        <v>₹32L - ₹48L PA + ESOPs</v>
       </c>
       <c r="L210" t="str">
-        <v>https://careers.cred.club/</v>
+        <v>https://www.flipkartcareers.com/</v>
       </c>
       <c r="M210">
         <v>200</v>
@@ -12966,142 +12966,24 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O210" t="str">
-        <v>2026-09-23</v>
+        <v>2026-09-24</v>
       </c>
       <c r="P210" t="str">
         <v>1d ago</v>
       </c>
       <c r="Q210" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R210" t="str">
         <v>No</v>
       </c>
       <c r="S210">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="str">
-        <v>job-1e98cdb6</v>
-      </c>
-      <c r="B211" t="str">
-        <v>Product Lead - Merchant QR, Soundbox &amp; Offline Payments Rails</v>
-      </c>
-      <c r="C211" t="str">
-        <v>PhonePe</v>
-      </c>
-      <c r="D211" t="str">
-        <v>Instahyre</v>
-      </c>
-      <c r="E211" t="str">
-        <v>AI &amp; Growth PM</v>
-      </c>
-      <c r="F211" t="str">
-        <v>7-11 yrs</v>
-      </c>
-      <c r="G211" t="str">
-        <v>8+ yrs</v>
-      </c>
-      <c r="H211" t="str">
-        <v>Bengaluru, Karnataka</v>
-      </c>
-      <c r="I211" t="str">
-        <v>Bengaluru</v>
-      </c>
-      <c r="J211" t="str">
-        <v>On-site</v>
-      </c>
-      <c r="K211" t="str">
-        <v>₹65L - ₹90L PA + ESOPs</v>
-      </c>
-      <c r="L211" t="str">
-        <v>https://www.phonepe.com/careers/</v>
-      </c>
-      <c r="M211">
-        <v>200</v>
-      </c>
-      <c r="N211" t="str">
-        <v>ACTIVE / 100% VALID</v>
-      </c>
-      <c r="O211" t="str">
-        <v>2026-09-23</v>
-      </c>
-      <c r="P211" t="str">
-        <v>1d ago</v>
-      </c>
-      <c r="Q211" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="R211" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="S211">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="str">
-        <v>job-6ee4d4a9</v>
-      </c>
-      <c r="B212" t="str">
-        <v>Product Manager - Supply Chain Forecasting &amp; Dynamic Pricing</v>
-      </c>
-      <c r="C212" t="str">
-        <v>Flipkart</v>
-      </c>
-      <c r="D212" t="str">
-        <v>IIMJobs</v>
-      </c>
-      <c r="E212" t="str">
-        <v>AI &amp; Growth PM</v>
-      </c>
-      <c r="F212" t="str">
-        <v>3-6 yrs</v>
-      </c>
-      <c r="G212" t="str">
-        <v>2-5 yrs</v>
-      </c>
-      <c r="H212" t="str">
-        <v>Bengaluru, Karnataka</v>
-      </c>
-      <c r="I212" t="str">
-        <v>Bengaluru</v>
-      </c>
-      <c r="J212" t="str">
-        <v>Hybrid</v>
-      </c>
-      <c r="K212" t="str">
-        <v>₹32L - ₹48L PA + ESOPs</v>
-      </c>
-      <c r="L212" t="str">
-        <v>https://www.flipkartcareers.com/</v>
-      </c>
-      <c r="M212">
-        <v>200</v>
-      </c>
-      <c r="N212" t="str">
-        <v>ACTIVE / 100% VALID</v>
-      </c>
-      <c r="O212" t="str">
-        <v>2026-09-23</v>
-      </c>
-      <c r="P212" t="str">
-        <v>1d ago</v>
-      </c>
-      <c r="Q212" t="str">
-        <v>No</v>
-      </c>
-      <c r="R212" t="str">
-        <v>No</v>
-      </c>
-      <c r="S212">
         <v>82</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S212"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S210"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -13165,10 +13047,10 @@
 3. Confirm fetch('/data/jobs.json') returns 200 OK</v>
       </c>
       <c r="F2" t="str">
-        <v>Returns array of 211 verified PM jobs</v>
+        <v>Returns array of 209 verified PM jobs</v>
       </c>
       <c r="G2" t="str">
-        <v>Successfully fetched 211 PM jobs without errors</v>
+        <v>Successfully fetched 209 PM jobs without errors</v>
       </c>
       <c r="H2" t="str">
         <v>PASS</v>
@@ -13247,10 +13129,10 @@
 2. Compare with rawJobs.length</v>
       </c>
       <c r="F5" t="str">
-        <v>Displays exactly 211</v>
+        <v>Displays exactly 209</v>
       </c>
       <c r="G5" t="str">
-        <v>Displays 211 active roles accurately</v>
+        <v>Displays 209 active roles accurately</v>
       </c>
       <c r="H5" t="str">
         <v>PASS</v>
@@ -13274,10 +13156,10 @@
 2. Count jobs posted today / marked Today</v>
       </c>
       <c r="F6" t="str">
-        <v>Displays +208</v>
+        <v>Displays +206</v>
       </c>
       <c r="G6" t="str">
-        <v>Displays +208 new opportunities tracked</v>
+        <v>Displays +206 new opportunities tracked</v>
       </c>
       <c r="H6" t="str">
         <v>PASS</v>
@@ -13853,7 +13735,7 @@
         <v>Open http://localhost:5173 in browser</v>
       </c>
       <c r="D2" t="str">
-        <v>Page loads instantly with Forest Green dark theme and 211 PM jobs</v>
+        <v>Page loads instantly with Forest Green dark theme and 209 PM jobs</v>
       </c>
       <c r="E2" t="str">
         <v>[ ] Completed</v>

--- a/GreenPath_PM_Jobs_Test_Report.xlsx
+++ b/GreenPath_PM_Jobs_Test_Report.xlsx
@@ -428,7 +428,7 @@
         <v>Test Execution Date</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-09-26T02:08:21.712Z</v>
+        <v>2026-09-27T02:00:40.384Z</v>
       </c>
     </row>
     <row r="4">
@@ -436,7 +436,7 @@
         <v>Total Jobs in Feed</v>
       </c>
       <c r="B4">
-        <v>205</v>
+        <v>194</v>
       </c>
     </row>
     <row r="5">
@@ -444,7 +444,7 @@
         <v>Total URLs Tested</v>
       </c>
       <c r="B5">
-        <v>205</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6">
@@ -452,7 +452,7 @@
         <v>Active / Valid Direct ATS URLs</v>
       </c>
       <c r="B6">
-        <v>204</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7">
@@ -468,7 +468,7 @@
         <v>URL Health Success Rate</v>
       </c>
       <c r="B8" t="str">
-        <v>100%</v>
+        <v>99%</v>
       </c>
     </row>
     <row r="9">
@@ -524,7 +524,7 @@
         <v>Cities Supported</v>
       </c>
       <c r="B15" t="str">
-        <v>San Francisco, Toronto, Dublin, N/A, New York, Remote, USA, Seattle, London, United States, Paris, Menlo Park, Hybrid, In-Office, Spain, Ireland, Canada, Norway, Doha, Pittsburgh, Beijing, Bengaluru, Vienna, North America, Stockholm, Washington, Mumbai, Gurgaon</v>
+        <v>San Francisco, Toronto, Dublin, N/A, New York, Remote, USA, Seattle, London, United States, Paris, Menlo Park, Hybrid, In-Office, Canada, Spain, Poland, Greece, Norway, Switzerland, Doha, Pittsburgh, Beijing, Bengaluru, Vienna, North America, Stockholm, Washington, Mumbai, Gurgaon</v>
       </c>
     </row>
     <row r="16">
@@ -532,7 +532,7 @@
         <v>Remote / Hybrid Roles</v>
       </c>
       <c r="B16" t="str">
-        <v>61 (30%)</v>
+        <v>61 (31%)</v>
       </c>
     </row>
     <row r="17">
@@ -540,7 +540,7 @@
         <v>Jobs Added Today</v>
       </c>
       <c r="B17" t="str">
-        <v>+202</v>
+        <v>+191</v>
       </c>
     </row>
     <row r="18">
@@ -568,7 +568,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S206"/>
+  <dimension ref="A1:S195"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="38.83203125" customWidth="1"/>
@@ -694,7 +694,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O2" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P2" t="str">
         <v>Today</v>
@@ -706,7 +706,7 @@
         <v>No</v>
       </c>
       <c r="S2">
-        <v>49</v>
+        <v>52</v>
       </c>
     </row>
     <row r="3">
@@ -753,19 +753,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O3" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P3" t="str">
         <v>Today</v>
       </c>
       <c r="Q3" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R3" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S3">
-        <v>51</v>
+        <v>91</v>
       </c>
     </row>
     <row r="4">
@@ -812,19 +812,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O4" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P4" t="str">
         <v>Today</v>
       </c>
       <c r="Q4" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R4" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S4">
-        <v>39</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5">
@@ -871,7 +871,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O5" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P5" t="str">
         <v>Today</v>
@@ -880,10 +880,10 @@
         <v>No</v>
       </c>
       <c r="R5" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S5">
-        <v>87</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6">
@@ -930,7 +930,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O6" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P6" t="str">
         <v>Today</v>
@@ -939,10 +939,10 @@
         <v>No</v>
       </c>
       <c r="R6" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S6">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7">
@@ -989,19 +989,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O7" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P7" t="str">
         <v>Today</v>
       </c>
       <c r="Q7" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R7" t="str">
         <v>No</v>
       </c>
       <c r="S7">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8">
@@ -1048,7 +1048,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O8" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P8" t="str">
         <v>Today</v>
@@ -1060,7 +1060,7 @@
         <v>No</v>
       </c>
       <c r="S8">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="9">
@@ -1107,7 +1107,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O9" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P9" t="str">
         <v>Today</v>
@@ -1119,7 +1119,7 @@
         <v>Yes</v>
       </c>
       <c r="S9">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10">
@@ -1166,7 +1166,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O10" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P10" t="str">
         <v>Today</v>
@@ -1175,10 +1175,10 @@
         <v>No</v>
       </c>
       <c r="R10" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S10">
-        <v>57</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11">
@@ -1225,7 +1225,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O11" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P11" t="str">
         <v>Today</v>
@@ -1234,10 +1234,10 @@
         <v>Yes</v>
       </c>
       <c r="R11" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S11">
-        <v>57</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12">
@@ -1284,19 +1284,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O12" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P12" t="str">
         <v>Today</v>
       </c>
       <c r="Q12" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R12" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S12">
-        <v>68</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13">
@@ -1343,7 +1343,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O13" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P13" t="str">
         <v>Today</v>
@@ -1352,10 +1352,10 @@
         <v>Yes</v>
       </c>
       <c r="R13" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S13">
-        <v>74</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -1402,7 +1402,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O14" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P14" t="str">
         <v>Today</v>
@@ -1414,7 +1414,7 @@
         <v>No</v>
       </c>
       <c r="S14">
-        <v>94</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15">
@@ -1461,7 +1461,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O15" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P15" t="str">
         <v>Today</v>
@@ -1520,7 +1520,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O16" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P16" t="str">
         <v>Today</v>
@@ -1532,7 +1532,7 @@
         <v>No</v>
       </c>
       <c r="S16">
-        <v>56</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17">
@@ -1579,7 +1579,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O17" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P17" t="str">
         <v>Today</v>
@@ -1591,7 +1591,7 @@
         <v>No</v>
       </c>
       <c r="S17">
-        <v>38</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18">
@@ -1638,19 +1638,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O18" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P18" t="str">
         <v>Today</v>
       </c>
       <c r="Q18" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R18" t="str">
         <v>No</v>
       </c>
       <c r="S18">
-        <v>32</v>
+        <v>68</v>
       </c>
     </row>
     <row r="19">
@@ -1697,7 +1697,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O19" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P19" t="str">
         <v>Today</v>
@@ -1709,7 +1709,7 @@
         <v>No</v>
       </c>
       <c r="S19">
-        <v>60</v>
+        <v>49</v>
       </c>
     </row>
     <row r="20">
@@ -1756,7 +1756,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O20" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P20" t="str">
         <v>Today</v>
@@ -1768,7 +1768,7 @@
         <v>No</v>
       </c>
       <c r="S20">
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21">
@@ -1815,19 +1815,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O21" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P21" t="str">
         <v>Today</v>
       </c>
       <c r="Q21" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R21" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S21">
-        <v>62</v>
+        <v>39</v>
       </c>
     </row>
     <row r="22">
@@ -1874,19 +1874,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O22" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P22" t="str">
         <v>Today</v>
       </c>
       <c r="Q22" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R22" t="str">
         <v>No</v>
       </c>
       <c r="S22">
-        <v>41</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23">
@@ -1933,7 +1933,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O23" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P23" t="str">
         <v>Today</v>
@@ -1942,10 +1942,10 @@
         <v>No</v>
       </c>
       <c r="R23" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S23">
-        <v>32</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24">
@@ -1992,7 +1992,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O24" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P24" t="str">
         <v>Today</v>
@@ -2004,7 +2004,7 @@
         <v>Yes</v>
       </c>
       <c r="S24">
-        <v>76</v>
+        <v>31</v>
       </c>
     </row>
     <row r="25">
@@ -2051,19 +2051,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O25" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P25" t="str">
         <v>Today</v>
       </c>
       <c r="Q25" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R25" t="str">
         <v>Yes</v>
       </c>
       <c r="S25">
-        <v>29</v>
+        <v>71</v>
       </c>
     </row>
     <row r="26">
@@ -2110,19 +2110,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O26" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P26" t="str">
         <v>Today</v>
       </c>
       <c r="Q26" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R26" t="str">
         <v>Yes</v>
       </c>
       <c r="S26">
-        <v>38</v>
+        <v>55</v>
       </c>
     </row>
     <row r="27">
@@ -2169,7 +2169,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O27" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P27" t="str">
         <v>Today</v>
@@ -2181,7 +2181,7 @@
         <v>No</v>
       </c>
       <c r="S27">
-        <v>52</v>
+        <v>94</v>
       </c>
     </row>
     <row r="28">
@@ -2228,7 +2228,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O28" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P28" t="str">
         <v>Today</v>
@@ -2240,7 +2240,7 @@
         <v>No</v>
       </c>
       <c r="S28">
-        <v>46</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29">
@@ -2287,16 +2287,16 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O29" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P29" t="str">
         <v>Today</v>
       </c>
       <c r="Q29" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R29" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S29">
         <v>29</v>
@@ -2346,7 +2346,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O30" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P30" t="str">
         <v>Today</v>
@@ -2358,7 +2358,7 @@
         <v>No</v>
       </c>
       <c r="S30">
-        <v>32</v>
+        <v>51</v>
       </c>
     </row>
     <row r="31">
@@ -2405,19 +2405,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O31" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P31" t="str">
         <v>Today</v>
       </c>
       <c r="Q31" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R31" t="str">
         <v>Yes</v>
       </c>
       <c r="S31">
-        <v>33</v>
+        <v>67</v>
       </c>
     </row>
     <row r="32">
@@ -2464,7 +2464,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O32" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P32" t="str">
         <v>Today</v>
@@ -2476,7 +2476,7 @@
         <v>Yes</v>
       </c>
       <c r="S32">
-        <v>79</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33">
@@ -2523,19 +2523,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O33" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P33" t="str">
         <v>Today</v>
       </c>
       <c r="Q33" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R33" t="str">
         <v>No</v>
       </c>
       <c r="S33">
-        <v>88</v>
+        <v>70</v>
       </c>
     </row>
     <row r="34">
@@ -2582,7 +2582,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O34" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P34" t="str">
         <v>Today</v>
@@ -2594,7 +2594,7 @@
         <v>Yes</v>
       </c>
       <c r="S34">
-        <v>68</v>
+        <v>92</v>
       </c>
     </row>
     <row r="35">
@@ -2641,19 +2641,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O35" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P35" t="str">
         <v>Today</v>
       </c>
       <c r="Q35" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R35" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S35">
-        <v>93</v>
+        <v>31</v>
       </c>
     </row>
     <row r="36">
@@ -2700,19 +2700,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O36" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P36" t="str">
         <v>Today</v>
       </c>
       <c r="Q36" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R36" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S36">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="37">
@@ -2759,19 +2759,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O37" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P37" t="str">
         <v>Today</v>
       </c>
       <c r="Q37" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R37" t="str">
         <v>No</v>
       </c>
       <c r="S37">
-        <v>49</v>
+        <v>74</v>
       </c>
     </row>
     <row r="38">
@@ -2812,25 +2812,25 @@
         <v>https://boards.greenhouse.io/datadog/jobs/8060821</v>
       </c>
       <c r="M38">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="N38" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O38" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P38" t="str">
         <v>Today</v>
       </c>
       <c r="Q38" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R38" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S38">
-        <v>32</v>
+        <v>48</v>
       </c>
     </row>
     <row r="39">
@@ -2856,10 +2856,10 @@
         <v>0-2 yrs</v>
       </c>
       <c r="H39" t="str">
-        <v>New York, New York, USA</v>
+        <v>Paris, France</v>
       </c>
       <c r="I39" t="str">
-        <v>New York</v>
+        <v>Paris</v>
       </c>
       <c r="J39" t="str">
         <v>On-site</v>
@@ -2868,7 +2868,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L39" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/8108241</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/8143729</v>
       </c>
       <c r="M39">
         <v>200</v>
@@ -2877,7 +2877,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O39" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P39" t="str">
         <v>Today</v>
@@ -2886,10 +2886,10 @@
         <v>No</v>
       </c>
       <c r="R39" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S39">
-        <v>54</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40">
@@ -2915,10 +2915,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H40" t="str">
-        <v>Paris, France</v>
+        <v>Boston, Massachusetts, USA; New York, New York, USA</v>
       </c>
       <c r="I40" t="str">
-        <v>Paris</v>
+        <v>New York</v>
       </c>
       <c r="J40" t="str">
         <v>On-site</v>
@@ -2927,28 +2927,28 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L40" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/8012549</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/7982288</v>
       </c>
       <c r="M40">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="N40" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O40" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P40" t="str">
         <v>Today</v>
       </c>
       <c r="Q40" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R40" t="str">
         <v>No</v>
       </c>
       <c r="S40">
-        <v>46</v>
+        <v>62</v>
       </c>
     </row>
     <row r="41">
@@ -2995,7 +2995,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O41" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P41" t="str">
         <v>Today</v>
@@ -3007,7 +3007,7 @@
         <v>No</v>
       </c>
       <c r="S41">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="42">
@@ -3048,13 +3048,13 @@
         <v>https://boards.greenhouse.io/datadog/jobs/7583609</v>
       </c>
       <c r="M42">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="N42" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O42" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P42" t="str">
         <v>Today</v>
@@ -3063,10 +3063,10 @@
         <v>No</v>
       </c>
       <c r="R42" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S42">
-        <v>44</v>
+        <v>55</v>
       </c>
     </row>
     <row r="43">
@@ -3113,19 +3113,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O43" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P43" t="str">
         <v>Today</v>
       </c>
       <c r="Q43" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R43" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S43">
-        <v>54</v>
+        <v>82</v>
       </c>
     </row>
     <row r="44">
@@ -3172,7 +3172,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O44" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P44" t="str">
         <v>Today</v>
@@ -3184,7 +3184,7 @@
         <v>No</v>
       </c>
       <c r="S44">
-        <v>84</v>
+        <v>78</v>
       </c>
     </row>
     <row r="45">
@@ -3231,19 +3231,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O45" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P45" t="str">
         <v>Today</v>
       </c>
       <c r="Q45" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R45" t="str">
         <v>No</v>
       </c>
       <c r="S45">
-        <v>55</v>
+        <v>62</v>
       </c>
     </row>
     <row r="46">
@@ -3284,25 +3284,25 @@
         <v>https://boards.greenhouse.io/datadog/jobs/8119973</v>
       </c>
       <c r="M46">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="N46" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O46" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P46" t="str">
         <v>Today</v>
       </c>
       <c r="Q46" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R46" t="str">
         <v>No</v>
       </c>
       <c r="S46">
-        <v>48</v>
+        <v>63</v>
       </c>
     </row>
     <row r="47">
@@ -3349,19 +3349,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O47" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P47" t="str">
         <v>Today</v>
       </c>
       <c r="Q47" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R47" t="str">
         <v>No</v>
       </c>
       <c r="S47">
-        <v>82</v>
+        <v>69</v>
       </c>
     </row>
     <row r="48">
@@ -3408,7 +3408,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O48" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P48" t="str">
         <v>Today</v>
@@ -3420,7 +3420,7 @@
         <v>No</v>
       </c>
       <c r="S48">
-        <v>63</v>
+        <v>58</v>
       </c>
     </row>
     <row r="49">
@@ -3467,7 +3467,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O49" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P49" t="str">
         <v>Today</v>
@@ -3479,7 +3479,7 @@
         <v>No</v>
       </c>
       <c r="S49">
-        <v>69</v>
+        <v>80</v>
       </c>
     </row>
     <row r="50">
@@ -3526,7 +3526,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O50" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P50" t="str">
         <v>Today</v>
@@ -3535,10 +3535,10 @@
         <v>No</v>
       </c>
       <c r="R50" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S50">
-        <v>35</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51">
@@ -3585,7 +3585,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O51" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P51" t="str">
         <v>Today</v>
@@ -3597,7 +3597,7 @@
         <v>No</v>
       </c>
       <c r="S51">
-        <v>91</v>
+        <v>68</v>
       </c>
     </row>
     <row r="52">
@@ -3644,19 +3644,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O52" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P52" t="str">
         <v>Today</v>
       </c>
       <c r="Q52" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R52" t="str">
         <v>No</v>
       </c>
       <c r="S52">
-        <v>89</v>
+        <v>54</v>
       </c>
     </row>
     <row r="53">
@@ -3703,7 +3703,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O53" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P53" t="str">
         <v>Today</v>
@@ -3712,10 +3712,10 @@
         <v>No</v>
       </c>
       <c r="R53" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S53">
-        <v>69</v>
+        <v>94</v>
       </c>
     </row>
     <row r="54">
@@ -3762,19 +3762,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O54" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P54" t="str">
         <v>Today</v>
       </c>
       <c r="Q54" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R54" t="str">
         <v>No</v>
       </c>
       <c r="S54">
-        <v>91</v>
+        <v>37</v>
       </c>
     </row>
     <row r="55">
@@ -3815,25 +3815,25 @@
         <v>https://boards.greenhouse.io/datadog/jobs/8065187</v>
       </c>
       <c r="M55">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="N55" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O55" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P55" t="str">
         <v>Today</v>
       </c>
       <c r="Q55" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R55" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S55">
-        <v>89</v>
+        <v>62</v>
       </c>
     </row>
     <row r="56">
@@ -3880,7 +3880,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O56" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P56" t="str">
         <v>Today</v>
@@ -3892,7 +3892,7 @@
         <v>No</v>
       </c>
       <c r="S56">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="57">
@@ -3939,19 +3939,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O57" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P57" t="str">
         <v>Today</v>
       </c>
       <c r="Q57" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R57" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S57">
-        <v>89</v>
+        <v>80</v>
       </c>
     </row>
     <row r="58">
@@ -3998,7 +3998,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O58" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P58" t="str">
         <v>Today</v>
@@ -4007,10 +4007,10 @@
         <v>No</v>
       </c>
       <c r="R58" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S58">
-        <v>55</v>
+        <v>35</v>
       </c>
     </row>
     <row r="59">
@@ -4057,19 +4057,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O59" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P59" t="str">
         <v>Today</v>
       </c>
       <c r="Q59" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R59" t="str">
         <v>No</v>
       </c>
       <c r="S59">
-        <v>34</v>
+        <v>78</v>
       </c>
     </row>
     <row r="60">
@@ -4116,19 +4116,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O60" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P60" t="str">
         <v>Today</v>
       </c>
       <c r="Q60" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R60" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S60">
-        <v>51</v>
+        <v>32</v>
       </c>
     </row>
     <row r="61">
@@ -4175,19 +4175,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O61" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P61" t="str">
         <v>Today</v>
       </c>
       <c r="Q61" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R61" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S61">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="62">
@@ -4234,7 +4234,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O62" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P62" t="str">
         <v>Today</v>
@@ -4246,7 +4246,7 @@
         <v>No</v>
       </c>
       <c r="S62">
-        <v>25</v>
+        <v>87</v>
       </c>
     </row>
     <row r="63">
@@ -4293,7 +4293,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O63" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P63" t="str">
         <v>Today</v>
@@ -4305,7 +4305,7 @@
         <v>Yes</v>
       </c>
       <c r="S63">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="64">
@@ -4352,19 +4352,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O64" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P64" t="str">
         <v>Today</v>
       </c>
       <c r="Q64" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R64" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S64">
-        <v>54</v>
+        <v>65</v>
       </c>
     </row>
     <row r="65">
@@ -4411,19 +4411,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O65" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P65" t="str">
         <v>Today</v>
       </c>
       <c r="Q65" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R65" t="str">
         <v>No</v>
       </c>
       <c r="S65">
-        <v>83</v>
+        <v>69</v>
       </c>
     </row>
     <row r="66">
@@ -4470,19 +4470,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O66" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P66" t="str">
         <v>Today</v>
       </c>
       <c r="Q66" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R66" t="str">
         <v>No</v>
       </c>
       <c r="S66">
-        <v>74</v>
+        <v>55</v>
       </c>
     </row>
     <row r="67">
@@ -4529,7 +4529,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O67" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P67" t="str">
         <v>Today</v>
@@ -4541,7 +4541,7 @@
         <v>No</v>
       </c>
       <c r="S67">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="68">
@@ -4588,7 +4588,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O68" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P68" t="str">
         <v>Today</v>
@@ -4597,10 +4597,10 @@
         <v>No</v>
       </c>
       <c r="R68" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S68">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="69">
@@ -4647,7 +4647,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O69" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P69" t="str">
         <v>Today</v>
@@ -4656,10 +4656,10 @@
         <v>No</v>
       </c>
       <c r="R69" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S69">
-        <v>43</v>
+        <v>72</v>
       </c>
     </row>
     <row r="70">
@@ -4706,19 +4706,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O70" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P70" t="str">
         <v>Today</v>
       </c>
       <c r="Q70" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R70" t="str">
         <v>No</v>
       </c>
       <c r="S70">
-        <v>39</v>
+        <v>70</v>
       </c>
     </row>
     <row r="71">
@@ -4765,19 +4765,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O71" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P71" t="str">
         <v>Today</v>
       </c>
       <c r="Q71" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R71" t="str">
         <v>Yes</v>
       </c>
       <c r="S71">
-        <v>86</v>
+        <v>42</v>
       </c>
     </row>
     <row r="72">
@@ -4824,7 +4824,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O72" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P72" t="str">
         <v>Today</v>
@@ -4836,7 +4836,7 @@
         <v>No</v>
       </c>
       <c r="S72">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="73">
@@ -4883,7 +4883,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O73" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P73" t="str">
         <v>Today</v>
@@ -4895,7 +4895,7 @@
         <v>No</v>
       </c>
       <c r="S73">
-        <v>92</v>
+        <v>59</v>
       </c>
     </row>
     <row r="74">
@@ -4942,19 +4942,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O74" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P74" t="str">
         <v>Today</v>
       </c>
       <c r="Q74" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R74" t="str">
         <v>No</v>
       </c>
       <c r="S74">
-        <v>92</v>
+        <v>29</v>
       </c>
     </row>
     <row r="75">
@@ -5001,7 +5001,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O75" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P75" t="str">
         <v>Today</v>
@@ -5013,7 +5013,7 @@
         <v>No</v>
       </c>
       <c r="S75">
-        <v>85</v>
+        <v>74</v>
       </c>
     </row>
     <row r="76">
@@ -5060,7 +5060,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O76" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P76" t="str">
         <v>Today</v>
@@ -5069,10 +5069,10 @@
         <v>No</v>
       </c>
       <c r="R76" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S76">
-        <v>45</v>
+        <v>51</v>
       </c>
     </row>
     <row r="77">
@@ -5119,19 +5119,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O77" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P77" t="str">
         <v>Today</v>
       </c>
       <c r="Q77" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R77" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S77">
-        <v>87</v>
+        <v>52</v>
       </c>
     </row>
     <row r="78">
@@ -5157,10 +5157,10 @@
         <v>8+ yrs</v>
       </c>
       <c r="H78" t="str">
-        <v>United States</v>
+        <v>Canada</v>
       </c>
       <c r="I78" t="str">
-        <v>United States</v>
+        <v>Canada</v>
       </c>
       <c r="J78" t="str">
         <v>On-site</v>
@@ -5169,7 +5169,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L78" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/7602101</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8070011</v>
       </c>
       <c r="M78">
         <v>200</v>
@@ -5178,7 +5178,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O78" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P78" t="str">
         <v>Today</v>
@@ -5187,10 +5187,10 @@
         <v>Yes</v>
       </c>
       <c r="R78" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S78">
-        <v>78</v>
+        <v>32</v>
       </c>
     </row>
     <row r="79">
@@ -5237,7 +5237,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O79" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P79" t="str">
         <v>Today</v>
@@ -5249,7 +5249,7 @@
         <v>No</v>
       </c>
       <c r="S79">
-        <v>39</v>
+        <v>59</v>
       </c>
     </row>
     <row r="80">
@@ -5296,19 +5296,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O80" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P80" t="str">
         <v>Today</v>
       </c>
       <c r="Q80" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R80" t="str">
         <v>No</v>
       </c>
       <c r="S80">
-        <v>65</v>
+        <v>55</v>
       </c>
     </row>
     <row r="81">
@@ -5334,10 +5334,10 @@
         <v>8+ yrs</v>
       </c>
       <c r="H81" t="str">
-        <v>Spain</v>
+        <v>Poland</v>
       </c>
       <c r="I81" t="str">
-        <v>Spain</v>
+        <v>Poland</v>
       </c>
       <c r="J81" t="str">
         <v>On-site</v>
@@ -5346,7 +5346,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L81" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8155416</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8155424</v>
       </c>
       <c r="M81">
         <v>200</v>
@@ -5355,7 +5355,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O81" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P81" t="str">
         <v>Today</v>
@@ -5364,10 +5364,10 @@
         <v>Yes</v>
       </c>
       <c r="R81" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S81">
-        <v>28</v>
+        <v>76</v>
       </c>
     </row>
     <row r="82">
@@ -5393,10 +5393,10 @@
         <v>8+ yrs</v>
       </c>
       <c r="H82" t="str">
-        <v>Ireland</v>
+        <v>Spain</v>
       </c>
       <c r="I82" t="str">
-        <v>Ireland</v>
+        <v>Spain</v>
       </c>
       <c r="J82" t="str">
         <v>On-site</v>
@@ -5405,7 +5405,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L82" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8155326</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8155325</v>
       </c>
       <c r="M82">
         <v>200</v>
@@ -5414,19 +5414,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O82" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P82" t="str">
         <v>Today</v>
       </c>
       <c r="Q82" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R82" t="str">
         <v>No</v>
       </c>
       <c r="S82">
-        <v>71</v>
+        <v>43</v>
       </c>
     </row>
     <row r="83">
@@ -5452,10 +5452,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H83" t="str">
-        <v>Canada</v>
+        <v>United States</v>
       </c>
       <c r="I83" t="str">
-        <v>Canada</v>
+        <v>United States</v>
       </c>
       <c r="J83" t="str">
         <v>On-site</v>
@@ -5464,7 +5464,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L83" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8214187</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8214106</v>
       </c>
       <c r="M83">
         <v>200</v>
@@ -5473,7 +5473,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O83" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P83" t="str">
         <v>Today</v>
@@ -5485,7 +5485,7 @@
         <v>No</v>
       </c>
       <c r="S83">
-        <v>64</v>
+        <v>33</v>
       </c>
     </row>
     <row r="84">
@@ -5511,10 +5511,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H84" t="str">
-        <v>Canada</v>
+        <v>United States</v>
       </c>
       <c r="I84" t="str">
-        <v>Canada</v>
+        <v>United States</v>
       </c>
       <c r="J84" t="str">
         <v>On-site</v>
@@ -5523,7 +5523,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L84" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8093933</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8088818</v>
       </c>
       <c r="M84">
         <v>200</v>
@@ -5532,19 +5532,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O84" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P84" t="str">
         <v>Today</v>
       </c>
       <c r="Q84" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R84" t="str">
         <v>No</v>
       </c>
       <c r="S84">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="85">
@@ -5570,10 +5570,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H85" t="str">
-        <v>Ireland</v>
+        <v>Greece</v>
       </c>
       <c r="I85" t="str">
-        <v>Ireland</v>
+        <v>Greece</v>
       </c>
       <c r="J85" t="str">
         <v>On-site</v>
@@ -5582,7 +5582,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L85" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8066516</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8066510</v>
       </c>
       <c r="M85">
         <v>200</v>
@@ -5591,19 +5591,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O85" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P85" t="str">
         <v>Today</v>
       </c>
       <c r="Q85" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R85" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S85">
-        <v>81</v>
+        <v>88</v>
       </c>
     </row>
     <row r="86">
@@ -5650,7 +5650,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O86" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P86" t="str">
         <v>Today</v>
@@ -5662,7 +5662,7 @@
         <v>No</v>
       </c>
       <c r="S86">
-        <v>62</v>
+        <v>77</v>
       </c>
     </row>
     <row r="87">
@@ -5709,7 +5709,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O87" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P87" t="str">
         <v>Today</v>
@@ -5721,7 +5721,7 @@
         <v>No</v>
       </c>
       <c r="S87">
-        <v>50</v>
+        <v>25</v>
       </c>
     </row>
     <row r="88">
@@ -5747,10 +5747,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H88" t="str">
-        <v>United States</v>
+        <v>Switzerland</v>
       </c>
       <c r="I88" t="str">
-        <v>United States</v>
+        <v>Switzerland</v>
       </c>
       <c r="J88" t="str">
         <v>On-site</v>
@@ -5759,7 +5759,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L88" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8167771</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8194084</v>
       </c>
       <c r="M88">
         <v>200</v>
@@ -5768,7 +5768,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O88" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P88" t="str">
         <v>Today</v>
@@ -5780,7 +5780,7 @@
         <v>No</v>
       </c>
       <c r="S88">
-        <v>46</v>
+        <v>52</v>
       </c>
     </row>
     <row r="89">
@@ -5827,19 +5827,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O89" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P89" t="str">
         <v>Today</v>
       </c>
       <c r="Q89" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R89" t="str">
         <v>No</v>
       </c>
       <c r="S89">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="90">
@@ -5886,7 +5886,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O90" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P90" t="str">
         <v>Today</v>
@@ -5895,10 +5895,10 @@
         <v>No</v>
       </c>
       <c r="R90" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S90">
-        <v>62</v>
+        <v>39</v>
       </c>
     </row>
     <row r="91">
@@ -5924,10 +5924,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H91" t="str">
-        <v>New York, NY</v>
+        <v>London, UK</v>
       </c>
       <c r="I91" t="str">
-        <v>New York</v>
+        <v>London</v>
       </c>
       <c r="J91" t="str">
         <v>On-site</v>
@@ -5936,7 +5936,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L91" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4673051005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4644742005</v>
       </c>
       <c r="M91">
         <v>200</v>
@@ -5945,19 +5945,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O91" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P91" t="str">
         <v>Today</v>
       </c>
       <c r="Q91" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R91" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S91">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="92">
@@ -6004,19 +6004,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O92" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P92" t="str">
         <v>Today</v>
       </c>
       <c r="Q92" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R92" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S92">
-        <v>69</v>
+        <v>43</v>
       </c>
     </row>
     <row r="93">
@@ -6063,7 +6063,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O93" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P93" t="str">
         <v>Today</v>
@@ -6075,7 +6075,7 @@
         <v>No</v>
       </c>
       <c r="S93">
-        <v>83</v>
+        <v>76</v>
       </c>
     </row>
     <row r="94">
@@ -6122,19 +6122,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O94" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P94" t="str">
         <v>Today</v>
       </c>
       <c r="Q94" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R94" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S94">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="95">
@@ -6181,7 +6181,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O95" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P95" t="str">
         <v>Today</v>
@@ -6193,7 +6193,7 @@
         <v>Yes</v>
       </c>
       <c r="S95">
-        <v>89</v>
+        <v>38</v>
       </c>
     </row>
     <row r="96">
@@ -6240,7 +6240,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O96" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P96" t="str">
         <v>Today</v>
@@ -6249,10 +6249,10 @@
         <v>No</v>
       </c>
       <c r="R96" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S96">
-        <v>81</v>
+        <v>47</v>
       </c>
     </row>
     <row r="97">
@@ -6299,19 +6299,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O97" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P97" t="str">
         <v>Today</v>
       </c>
       <c r="Q97" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R97" t="str">
         <v>No</v>
       </c>
       <c r="S97">
-        <v>83</v>
+        <v>51</v>
       </c>
     </row>
     <row r="98">
@@ -6358,7 +6358,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O98" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P98" t="str">
         <v>Today</v>
@@ -6370,7 +6370,7 @@
         <v>Yes</v>
       </c>
       <c r="S98">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="99">
@@ -6417,19 +6417,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O99" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P99" t="str">
         <v>Today</v>
       </c>
       <c r="Q99" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R99" t="str">
         <v>No</v>
       </c>
       <c r="S99">
-        <v>44</v>
+        <v>81</v>
       </c>
     </row>
     <row r="100">
@@ -6476,19 +6476,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O100" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P100" t="str">
         <v>Today</v>
       </c>
       <c r="Q100" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R100" t="str">
         <v>No</v>
       </c>
       <c r="S100">
-        <v>36</v>
+        <v>52</v>
       </c>
     </row>
     <row r="101">
@@ -6535,19 +6535,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O101" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P101" t="str">
         <v>Today</v>
       </c>
       <c r="Q101" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R101" t="str">
         <v>No</v>
       </c>
       <c r="S101">
-        <v>42</v>
+        <v>31</v>
       </c>
     </row>
     <row r="102">
@@ -6594,48 +6594,48 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O102" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P102" t="str">
         <v>Today</v>
       </c>
       <c r="Q102" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R102" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S102">
-        <v>86</v>
+        <v>63</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>job-58b32a73</v>
+        <v>job-429ddf15</v>
       </c>
       <c r="B103" t="str">
-        <v>Director of Product, Growth/AI</v>
+        <v>Associate Product Manager, Intern</v>
       </c>
       <c r="C103" t="str">
-        <v>Brex</v>
+        <v>Duolingo</v>
       </c>
       <c r="D103" t="str">
         <v>Wellfound</v>
       </c>
       <c r="E103" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Associate Product Manager</v>
       </c>
       <c r="F103" t="str">
-        <v>8+ yrs</v>
+        <v>1-3 yrs</v>
       </c>
       <c r="G103" t="str">
-        <v>8+ yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H103" t="str">
-        <v>San Francisco, California, United States</v>
+        <v>Pittsburgh, PA</v>
       </c>
       <c r="I103" t="str">
-        <v>San Francisco</v>
+        <v>Pittsburgh</v>
       </c>
       <c r="J103" t="str">
         <v>On-site</v>
@@ -6644,7 +6644,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L103" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8432707002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8806187002</v>
       </c>
       <c r="M103">
         <v>200</v>
@@ -6653,7 +6653,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O103" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P103" t="str">
         <v>Today</v>
@@ -6665,36 +6665,36 @@
         <v>No</v>
       </c>
       <c r="S103">
-        <v>92</v>
+        <v>56</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>job-6c147538</v>
+        <v>job-1b56d1fb</v>
       </c>
       <c r="B104" t="str">
-        <v>Group Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="C104" t="str">
-        <v>Brex</v>
+        <v>Duolingo</v>
       </c>
       <c r="D104" t="str">
         <v>Wellfound</v>
       </c>
       <c r="E104" t="str">
-        <v>Product Lead / Director</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F104" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G104" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H104" t="str">
-        <v>Seattle, Washington, United States</v>
+        <v>Beijing, China</v>
       </c>
       <c r="I104" t="str">
-        <v>Seattle</v>
+        <v>Beijing</v>
       </c>
       <c r="J104" t="str">
         <v>On-site</v>
@@ -6703,7 +6703,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L104" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8438582002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8675670002</v>
       </c>
       <c r="M104">
         <v>200</v>
@@ -6712,30 +6712,30 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O104" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P104" t="str">
         <v>Today</v>
       </c>
       <c r="Q104" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R104" t="str">
         <v>No</v>
       </c>
       <c r="S104">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>job-4a5cf899</v>
+        <v>job-0ba5b818</v>
       </c>
       <c r="B105" t="str">
-        <v>Senior Product Manager, AI</v>
+        <v>Senior Product Manager, DET</v>
       </c>
       <c r="C105" t="str">
-        <v>Brex</v>
+        <v>Duolingo</v>
       </c>
       <c r="D105" t="str">
         <v>Wellfound</v>
@@ -6750,10 +6750,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H105" t="str">
-        <v>Seattle, Washington, United States</v>
+        <v>New York, NY</v>
       </c>
       <c r="I105" t="str">
-        <v>Seattle</v>
+        <v>New York</v>
       </c>
       <c r="J105" t="str">
         <v>On-site</v>
@@ -6762,7 +6762,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L105" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8780828002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8737859002</v>
       </c>
       <c r="M105">
         <v>200</v>
@@ -6771,7 +6771,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O105" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P105" t="str">
         <v>Today</v>
@@ -6780,21 +6780,21 @@
         <v>Yes</v>
       </c>
       <c r="R105" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S105">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>job-111c900b</v>
+        <v>job-25986280</v>
       </c>
       <c r="B106" t="str">
-        <v>Senior Product Manager, Travel</v>
+        <v>Senior Product Manager, Growth</v>
       </c>
       <c r="C106" t="str">
-        <v>Brex</v>
+        <v>Duolingo</v>
       </c>
       <c r="D106" t="str">
         <v>Wellfound</v>
@@ -6809,10 +6809,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H106" t="str">
-        <v>San Francisco, California, United States</v>
+        <v>New York, NY</v>
       </c>
       <c r="I106" t="str">
-        <v>San Francisco</v>
+        <v>New York</v>
       </c>
       <c r="J106" t="str">
         <v>On-site</v>
@@ -6821,7 +6821,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L106" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8659249002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8747275002</v>
       </c>
       <c r="M106">
         <v>200</v>
@@ -6830,30 +6830,30 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O106" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P106" t="str">
         <v>Today</v>
       </c>
       <c r="Q106" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R106" t="str">
         <v>No</v>
       </c>
       <c r="S106">
-        <v>51</v>
+        <v>70</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>job-337165a7</v>
+        <v>job-604bd697</v>
       </c>
       <c r="B107" t="str">
-        <v>Staff Product Manager</v>
+        <v>Senior Product Manager, Learning</v>
       </c>
       <c r="C107" t="str">
-        <v>Brex</v>
+        <v>Duolingo</v>
       </c>
       <c r="D107" t="str">
         <v>Wellfound</v>
@@ -6868,10 +6868,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H107" t="str">
-        <v>Seattle, Washington, United States</v>
+        <v>New York, NY; Pittsburgh, PA</v>
       </c>
       <c r="I107" t="str">
-        <v>Seattle</v>
+        <v>New York</v>
       </c>
       <c r="J107" t="str">
         <v>On-site</v>
@@ -6880,7 +6880,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L107" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8432703002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8827944002</v>
       </c>
       <c r="M107">
         <v>200</v>
@@ -6889,30 +6889,30 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O107" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P107" t="str">
         <v>Today</v>
       </c>
       <c r="Q107" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R107" t="str">
         <v>No</v>
       </c>
       <c r="S107">
-        <v>53</v>
+        <v>29</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>job-533982f5</v>
+        <v>job-256f50fd</v>
       </c>
       <c r="B108" t="str">
-        <v>Staff Product Manager, AI</v>
+        <v>Senior Product Manager, Notifications</v>
       </c>
       <c r="C108" t="str">
-        <v>Brex</v>
+        <v>Duolingo</v>
       </c>
       <c r="D108" t="str">
         <v>Wellfound</v>
@@ -6927,10 +6927,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H108" t="str">
-        <v>New York, New York, United States</v>
+        <v>Pittsburgh, PA</v>
       </c>
       <c r="I108" t="str">
-        <v>New York</v>
+        <v>Pittsburgh</v>
       </c>
       <c r="J108" t="str">
         <v>On-site</v>
@@ -6939,7 +6939,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L108" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8780829002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8747099002</v>
       </c>
       <c r="M108">
         <v>200</v>
@@ -6948,30 +6948,30 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O108" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P108" t="str">
         <v>Today</v>
       </c>
       <c r="Q108" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R108" t="str">
         <v>No</v>
       </c>
       <c r="S108">
-        <v>66</v>
+        <v>92</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>job-0f9c4e5d</v>
+        <v>job-2666664e</v>
       </c>
       <c r="B109" t="str">
-        <v>Staff Product Manager, Card</v>
+        <v>Staff Product Manager, Monetization</v>
       </c>
       <c r="C109" t="str">
-        <v>Brex</v>
+        <v>Duolingo</v>
       </c>
       <c r="D109" t="str">
         <v>Wellfound</v>
@@ -6986,10 +6986,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H109" t="str">
-        <v>San Francisco, California, United States</v>
+        <v>New York, NY</v>
       </c>
       <c r="I109" t="str">
-        <v>San Francisco</v>
+        <v>New York</v>
       </c>
       <c r="J109" t="str">
         <v>On-site</v>
@@ -6998,7 +6998,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L109" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8659220002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8474673002</v>
       </c>
       <c r="M109">
         <v>200</v>
@@ -7007,7 +7007,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O109" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P109" t="str">
         <v>Today</v>
@@ -7016,39 +7016,39 @@
         <v>No</v>
       </c>
       <c r="R109" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S109">
-        <v>78</v>
+        <v>62</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>job-4401c5a9</v>
+        <v>job-6e88535c</v>
       </c>
       <c r="B110" t="str">
-        <v>Staff Product Manager, Embedded</v>
+        <v>VP of Product, Growth and Monetization</v>
       </c>
       <c r="C110" t="str">
-        <v>Brex</v>
+        <v>Duolingo</v>
       </c>
       <c r="D110" t="str">
         <v>Wellfound</v>
       </c>
       <c r="E110" t="str">
-        <v>Senior Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F110" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G110" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H110" t="str">
-        <v>Seattle, Washington, United States</v>
+        <v>New York, NY</v>
       </c>
       <c r="I110" t="str">
-        <v>Seattle</v>
+        <v>New York</v>
       </c>
       <c r="J110" t="str">
         <v>On-site</v>
@@ -7057,7 +7057,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L110" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8659210002</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8747060002</v>
       </c>
       <c r="M110">
         <v>200</v>
@@ -7066,479 +7066,479 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O110" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P110" t="str">
         <v>Today</v>
       </c>
       <c r="Q110" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R110" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S110">
-        <v>39</v>
+        <v>66</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>job-75398a6b</v>
+        <v>job-65a74288</v>
       </c>
       <c r="B111" t="str">
-        <v>Staff Product Manager,  Embedded</v>
+        <v>Associate Product Manager Intern</v>
       </c>
       <c r="C111" t="str">
-        <v>Brex</v>
+        <v>Coinbase</v>
       </c>
       <c r="D111" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E111" t="str">
-        <v>Senior Product Manager</v>
+        <v>Associate Product Manager</v>
       </c>
       <c r="F111" t="str">
-        <v>5-8 yrs</v>
+        <v>1-3 yrs</v>
       </c>
       <c r="G111" t="str">
-        <v>5-8 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H111" t="str">
-        <v>New York, New York, United States</v>
+        <v>Hybrid - San Francisco, CA</v>
       </c>
       <c r="I111" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J111" t="str">
-        <v>On-site</v>
+        <v>Hybrid</v>
       </c>
       <c r="K111" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L111" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8659211002</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/8168322</v>
       </c>
       <c r="M111">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N111" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O111" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P111" t="str">
         <v>Today</v>
       </c>
       <c r="Q111" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R111" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S111">
-        <v>25</v>
+        <v>69</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>job-0f02a1a8</v>
+        <v>job-2bc26745</v>
       </c>
       <c r="B112" t="str">
-        <v>Staff Product Manager, Expenses</v>
+        <v>Group Product Manager, Compliance Agent Experience</v>
       </c>
       <c r="C112" t="str">
-        <v>Brex</v>
+        <v>Coinbase</v>
       </c>
       <c r="D112" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E112" t="str">
-        <v>Senior Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F112" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G112" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H112" t="str">
-        <v>San Francisco, California, United States</v>
+        <v>Remote - USA</v>
       </c>
       <c r="I112" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J112" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K112" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L112" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8659239002</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/8060662</v>
       </c>
       <c r="M112">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N112" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O112" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P112" t="str">
         <v>Today</v>
       </c>
       <c r="Q112" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R112" t="str">
         <v>No</v>
       </c>
       <c r="S112">
-        <v>42</v>
+        <v>29</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>job-2239c52c</v>
+        <v>job-779d88ed</v>
       </c>
       <c r="B113" t="str">
-        <v>Staff Product Manager, Growth</v>
+        <v>Group Product Manager, Compliance Automation</v>
       </c>
       <c r="C113" t="str">
-        <v>Brex</v>
+        <v>Coinbase</v>
       </c>
       <c r="D113" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E113" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F113" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G113" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H113" t="str">
-        <v>Seattle, Washington, United States</v>
+        <v>Remote - USA</v>
       </c>
       <c r="I113" t="str">
-        <v>Seattle</v>
+        <v>Remote</v>
       </c>
       <c r="J113" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K113" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L113" t="str">
-        <v>https://boards.greenhouse.io/brex/jobs/8436530002</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/7701642</v>
       </c>
       <c r="M113">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N113" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O113" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P113" t="str">
         <v>Today</v>
       </c>
       <c r="Q113" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R113" t="str">
         <v>No</v>
       </c>
       <c r="S113">
-        <v>36</v>
+        <v>86</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>job-429ddf15</v>
+        <v>job-6faf73eb</v>
       </c>
       <c r="B114" t="str">
-        <v>Associate Product Manager, Intern</v>
+        <v>Group Product Manager, Core Infrastructure &amp; Reliability</v>
       </c>
       <c r="C114" t="str">
-        <v>Duolingo</v>
+        <v>Coinbase</v>
       </c>
       <c r="D114" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E114" t="str">
-        <v>Associate Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F114" t="str">
-        <v>1-3 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G114" t="str">
-        <v>0-2 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H114" t="str">
-        <v>Pittsburgh, PA</v>
+        <v>Remote - USA</v>
       </c>
       <c r="I114" t="str">
-        <v>Pittsburgh</v>
+        <v>Remote</v>
       </c>
       <c r="J114" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K114" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L114" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8806187002</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/7997785</v>
       </c>
       <c r="M114">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N114" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O114" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P114" t="str">
         <v>Today</v>
       </c>
       <c r="Q114" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R114" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S114">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>job-1b56d1fb</v>
+        <v>job-67afa492</v>
       </c>
       <c r="B115" t="str">
-        <v>Senior Product Manager</v>
+        <v>Group Product Manager, Developer Infrastructure</v>
       </c>
       <c r="C115" t="str">
-        <v>Duolingo</v>
+        <v>Coinbase</v>
       </c>
       <c r="D115" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E115" t="str">
-        <v>Senior Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F115" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G115" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H115" t="str">
-        <v>Beijing, China</v>
+        <v>Remote - USA</v>
       </c>
       <c r="I115" t="str">
-        <v>Beijing</v>
+        <v>Remote</v>
       </c>
       <c r="J115" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K115" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L115" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8675670002</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/8017607</v>
       </c>
       <c r="M115">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N115" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O115" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P115" t="str">
         <v>Today</v>
       </c>
       <c r="Q115" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R115" t="str">
         <v>No</v>
       </c>
       <c r="S115">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>job-0ba5b818</v>
+        <v>job-30b71fd8</v>
       </c>
       <c r="B116" t="str">
-        <v>Senior Product Manager, DET</v>
+        <v>Group Product Manager, Money Movement</v>
       </c>
       <c r="C116" t="str">
-        <v>Duolingo</v>
+        <v>Coinbase</v>
       </c>
       <c r="D116" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E116" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F116" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G116" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H116" t="str">
-        <v>Pittsburgh, PA</v>
+        <v>Remote - USA</v>
       </c>
       <c r="I116" t="str">
-        <v>Pittsburgh</v>
+        <v>Remote</v>
       </c>
       <c r="J116" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K116" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L116" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8530395002</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/8234060</v>
       </c>
       <c r="M116">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N116" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O116" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P116" t="str">
         <v>Today</v>
       </c>
       <c r="Q116" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R116" t="str">
         <v>No</v>
       </c>
       <c r="S116">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>job-25986280</v>
+        <v>job-00f9bc89</v>
       </c>
       <c r="B117" t="str">
-        <v>Senior Product Manager, Growth</v>
+        <v>Head of Product Creative</v>
       </c>
       <c r="C117" t="str">
-        <v>Duolingo</v>
+        <v>Coinbase</v>
       </c>
       <c r="D117" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E117" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F117" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G117" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H117" t="str">
-        <v>New York, NY</v>
+        <v>Remote - USA</v>
       </c>
       <c r="I117" t="str">
-        <v>New York</v>
+        <v>Remote</v>
       </c>
       <c r="J117" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K117" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L117" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8747275002</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/7304930</v>
       </c>
       <c r="M117">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N117" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O117" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P117" t="str">
         <v>Today</v>
       </c>
       <c r="Q117" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R117" t="str">
         <v>No</v>
       </c>
       <c r="S117">
-        <v>75</v>
+        <v>40</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>job-604bd697</v>
+        <v>job-02200da7</v>
       </c>
       <c r="B118" t="str">
-        <v>Senior Product Manager, Learning</v>
+        <v>Product Manager (HR Technology) Intern</v>
       </c>
       <c r="C118" t="str">
-        <v>Duolingo</v>
+        <v>Coinbase</v>
       </c>
       <c r="D118" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E118" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F118" t="str">
-        <v>5-8 yrs</v>
+        <v>1-3 yrs</v>
       </c>
       <c r="G118" t="str">
-        <v>5-8 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H118" t="str">
-        <v>New York, NY; Pittsburgh, PA</v>
+        <v>Hybrid - New York, NY</v>
       </c>
       <c r="I118" t="str">
         <v>New York</v>
       </c>
       <c r="J118" t="str">
-        <v>On-site</v>
+        <v>Hybrid</v>
       </c>
       <c r="K118" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L118" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8827944002</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/8175504</v>
       </c>
       <c r="M118">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N118" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O118" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P118" t="str">
         <v>Today</v>
@@ -7550,54 +7550,54 @@
         <v>Yes</v>
       </c>
       <c r="S118">
-        <v>27</v>
+        <v>47</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>job-256f50fd</v>
+        <v>job-0f319aac</v>
       </c>
       <c r="B119" t="str">
-        <v>Senior Product Manager, Notifications</v>
+        <v>Product Manager II, Growth - Notifications</v>
       </c>
       <c r="C119" t="str">
-        <v>Duolingo</v>
+        <v>Coinbase</v>
       </c>
       <c r="D119" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E119" t="str">
-        <v>Senior Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F119" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G119" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H119" t="str">
-        <v>Pittsburgh, PA</v>
+        <v>Remote - USA</v>
       </c>
       <c r="I119" t="str">
-        <v>Pittsburgh</v>
+        <v>Remote</v>
       </c>
       <c r="J119" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K119" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L119" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8747099002</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/8204571</v>
       </c>
       <c r="M119">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N119" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O119" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P119" t="str">
         <v>Today</v>
@@ -7609,210 +7609,210 @@
         <v>No</v>
       </c>
       <c r="S119">
-        <v>41</v>
+        <v>61</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>job-2666664e</v>
+        <v>job-0d5f8a75</v>
       </c>
       <c r="B120" t="str">
-        <v>Staff Product Manager, Monetization</v>
+        <v>Product Manager II, Workspace and Multi-User</v>
       </c>
       <c r="C120" t="str">
-        <v>Duolingo</v>
+        <v>Coinbase</v>
       </c>
       <c r="D120" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E120" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F120" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G120" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H120" t="str">
-        <v>New York, NY</v>
+        <v>Remote - USA</v>
       </c>
       <c r="I120" t="str">
-        <v>New York</v>
+        <v>Remote</v>
       </c>
       <c r="J120" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K120" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L120" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8474673002</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/8148171</v>
       </c>
       <c r="M120">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N120" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O120" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P120" t="str">
         <v>Today</v>
       </c>
       <c r="Q120" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R120" t="str">
         <v>No</v>
       </c>
       <c r="S120">
-        <v>54</v>
+        <v>43</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>job-6e88535c</v>
+        <v>job-2efe7fb3</v>
       </c>
       <c r="B121" t="str">
-        <v>VP of Product, Growth and Monetization</v>
+        <v>Senior Product Manager, Help Center (CX Automation)</v>
       </c>
       <c r="C121" t="str">
-        <v>Duolingo</v>
+        <v>Coinbase</v>
       </c>
       <c r="D121" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E121" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F121" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G121" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H121" t="str">
-        <v>Pittsburgh, PA</v>
+        <v>Remote - India</v>
       </c>
       <c r="I121" t="str">
-        <v>Pittsburgh</v>
+        <v>Remote</v>
       </c>
       <c r="J121" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K121" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L121" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8747077002</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/8031208</v>
       </c>
       <c r="M121">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N121" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O121" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P121" t="str">
         <v>Today</v>
       </c>
       <c r="Q121" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R121" t="str">
         <v>No</v>
       </c>
       <c r="S121">
-        <v>82</v>
+        <v>31</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>job-65a74288</v>
+        <v>job-1762a9dc</v>
       </c>
       <c r="B122" t="str">
-        <v>Associate Product Manager Intern</v>
+        <v>Director of Product Management, Agentic Software Delivery</v>
       </c>
       <c r="C122" t="str">
-        <v>Coinbase</v>
+        <v>GitLab</v>
       </c>
       <c r="D122" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E122" t="str">
-        <v>Associate Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F122" t="str">
-        <v>1-3 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G122" t="str">
-        <v>0-2 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H122" t="str">
-        <v>Hybrid - San Francisco, CA</v>
+        <v>Remote, United States</v>
       </c>
       <c r="I122" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J122" t="str">
-        <v>Hybrid</v>
+        <v>Remote</v>
       </c>
       <c r="K122" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L122" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/8168322</v>
+        <v>https://boards.greenhouse.io/gitlab/jobs/8806017002</v>
       </c>
       <c r="M122">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N122" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O122" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P122" t="str">
         <v>Today</v>
       </c>
       <c r="Q122" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R122" t="str">
         <v>Yes</v>
       </c>
       <c r="S122">
-        <v>30</v>
+        <v>35</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>job-2bc26745</v>
+        <v>job-58e27f7c</v>
       </c>
       <c r="B123" t="str">
-        <v>Group Product Manager, Compliance Agent Experience</v>
+        <v>Principal Product Manager, AI Software Factory</v>
       </c>
       <c r="C123" t="str">
-        <v>Coinbase</v>
+        <v>GitLab</v>
       </c>
       <c r="D123" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E123" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F123" t="str">
-        <v>3-6 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G123" t="str">
-        <v>2-5 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H123" t="str">
-        <v>Remote - USA</v>
+        <v>Remote, Canada; Remote, United States</v>
       </c>
       <c r="I123" t="str">
         <v>Remote</v>
@@ -7824,54 +7824,54 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L123" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/8060662</v>
+        <v>https://boards.greenhouse.io/gitlab/jobs/8658878002</v>
       </c>
       <c r="M123">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N123" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O123" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P123" t="str">
         <v>Today</v>
       </c>
       <c r="Q123" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R123" t="str">
         <v>No</v>
       </c>
       <c r="S123">
-        <v>82</v>
+        <v>40</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>job-779d88ed</v>
+        <v>job-448d861a</v>
       </c>
       <c r="B124" t="str">
-        <v>Group Product Manager, Compliance Automation</v>
+        <v>Senior Product Manager, Agentic Source Code</v>
       </c>
       <c r="C124" t="str">
-        <v>Coinbase</v>
+        <v>GitLab</v>
       </c>
       <c r="D124" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E124" t="str">
-        <v>Product Lead / Director</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F124" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G124" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H124" t="str">
-        <v>Remote - USA</v>
+        <v>Remote, Canada; Remote, US</v>
       </c>
       <c r="I124" t="str">
         <v>Remote</v>
@@ -7883,16 +7883,16 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L124" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/7701642</v>
+        <v>https://boards.greenhouse.io/gitlab/jobs/8597805002</v>
       </c>
       <c r="M124">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N124" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O124" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P124" t="str">
         <v>Today</v>
@@ -7904,33 +7904,33 @@
         <v>No</v>
       </c>
       <c r="S124">
-        <v>53</v>
+        <v>26</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>job-6faf73eb</v>
+        <v>job-6bc28568</v>
       </c>
       <c r="B125" t="str">
-        <v>Group Product Manager, Core Infrastructure &amp; Reliability</v>
+        <v>Senior Product Manager, Secret Detection and Vulnerability Research</v>
       </c>
       <c r="C125" t="str">
-        <v>Coinbase</v>
+        <v>GitLab</v>
       </c>
       <c r="D125" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E125" t="str">
-        <v>Technical Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F125" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G125" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H125" t="str">
-        <v>Remote - USA</v>
+        <v>Remote, United States</v>
       </c>
       <c r="I125" t="str">
         <v>Remote</v>
@@ -7942,16 +7942,16 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L125" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/7997785</v>
+        <v>https://boards.greenhouse.io/gitlab/jobs/8697043002</v>
       </c>
       <c r="M125">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N125" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O125" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P125" t="str">
         <v>Today</v>
@@ -7960,36 +7960,36 @@
         <v>No</v>
       </c>
       <c r="R125" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S125">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>job-67afa492</v>
+        <v>job-7ad77ccd</v>
       </c>
       <c r="B126" t="str">
-        <v>Group Product Manager, Developer Infrastructure</v>
+        <v>Senior Product Manager, Tenant Scale</v>
       </c>
       <c r="C126" t="str">
-        <v>Coinbase</v>
+        <v>GitLab</v>
       </c>
       <c r="D126" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E126" t="str">
-        <v>Technical Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F126" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G126" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H126" t="str">
-        <v>Remote - USA</v>
+        <v>Remote, Canada; Remote, US</v>
       </c>
       <c r="I126" t="str">
         <v>Remote</v>
@@ -8001,16 +8001,16 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L126" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/8017607</v>
+        <v>https://boards.greenhouse.io/gitlab/jobs/8512220002</v>
       </c>
       <c r="M126">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N126" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O126" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P126" t="str">
         <v>Today</v>
@@ -8019,36 +8019,36 @@
         <v>Yes</v>
       </c>
       <c r="R126" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S126">
-        <v>39</v>
+        <v>27</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>job-0bd0b53d</v>
+        <v>job-52edb6a4</v>
       </c>
       <c r="B127" t="str">
-        <v>Group Product Manager, FinHub</v>
+        <v>Staff Product Manager,  RevOps &amp; Finance Systems</v>
       </c>
       <c r="C127" t="str">
-        <v>Coinbase</v>
+        <v>GitLab</v>
       </c>
       <c r="D127" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E127" t="str">
-        <v>Product Lead / Director</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F127" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G127" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H127" t="str">
-        <v>Remote - USA</v>
+        <v>Remote, US</v>
       </c>
       <c r="I127" t="str">
         <v>Remote</v>
@@ -8060,16 +8060,16 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L127" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/8234060</v>
+        <v>https://boards.greenhouse.io/gitlab/jobs/8612937002</v>
       </c>
       <c r="M127">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N127" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O127" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P127" t="str">
         <v>Today</v>
@@ -8081,77 +8081,77 @@
         <v>No</v>
       </c>
       <c r="S127">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>job-00f9bc89</v>
+        <v>job-3a743e4f</v>
       </c>
       <c r="B128" t="str">
-        <v>Head of Product Creative</v>
+        <v>Manager, Product Management - Figma Platform Experience</v>
       </c>
       <c r="C128" t="str">
-        <v>Coinbase</v>
+        <v>Figma</v>
       </c>
       <c r="D128" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E128" t="str">
-        <v>Product Lead / Director</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F128" t="str">
-        <v>8+ yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G128" t="str">
-        <v>8+ yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H128" t="str">
-        <v>Remote - USA</v>
+        <v>San Francisco, CA • New York, NY • United States</v>
       </c>
       <c r="I128" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J128" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K128" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L128" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/7304930</v>
+        <v>https://boards.greenhouse.io/figma/jobs/6160732004</v>
       </c>
       <c r="M128">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N128" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O128" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P128" t="str">
         <v>Today</v>
       </c>
       <c r="Q128" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R128" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S128">
-        <v>68</v>
+        <v>40</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>job-02200da7</v>
+        <v>job-7297f499</v>
       </c>
       <c r="B129" t="str">
-        <v>Product Manager (HR Technology) Intern</v>
+        <v>Manager, Product Management - Roundtripping</v>
       </c>
       <c r="C129" t="str">
-        <v>Coinbase</v>
+        <v>Figma</v>
       </c>
       <c r="D129" t="str">
         <v>LinkedIn</v>
@@ -8160,34 +8160,34 @@
         <v>Product Manager</v>
       </c>
       <c r="F129" t="str">
-        <v>1-3 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G129" t="str">
-        <v>0-2 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H129" t="str">
-        <v>Hybrid - New York, NY</v>
+        <v>New York, NY • United States</v>
       </c>
       <c r="I129" t="str">
         <v>New York</v>
       </c>
       <c r="J129" t="str">
-        <v>Hybrid</v>
+        <v>On-site</v>
       </c>
       <c r="K129" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L129" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/8175504</v>
+        <v>https://boards.greenhouse.io/figma/jobs/6104919004</v>
       </c>
       <c r="M129">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N129" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O129" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P129" t="str">
         <v>Today</v>
@@ -8199,24 +8199,24 @@
         <v>No</v>
       </c>
       <c r="S129">
-        <v>44</v>
+        <v>94</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>job-0f319aac</v>
+        <v>job-19031a2a</v>
       </c>
       <c r="B130" t="str">
-        <v>Product Manager II, Growth - Notifications</v>
+        <v>Manager, Product Management - Roundtripping (London, United Kingdom)</v>
       </c>
       <c r="C130" t="str">
-        <v>Coinbase</v>
+        <v>Figma</v>
       </c>
       <c r="D130" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E130" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Product Manager</v>
       </c>
       <c r="F130" t="str">
         <v>3-6 yrs</v>
@@ -8225,28 +8225,28 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H130" t="str">
-        <v>Remote - USA</v>
+        <v>London, England</v>
       </c>
       <c r="I130" t="str">
-        <v>Remote</v>
+        <v>London</v>
       </c>
       <c r="J130" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K130" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L130" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/8204571</v>
+        <v>https://boards.greenhouse.io/figma/jobs/6149007004</v>
       </c>
       <c r="M130">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N130" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O130" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P130" t="str">
         <v>Today</v>
@@ -8258,18 +8258,18 @@
         <v>No</v>
       </c>
       <c r="S130">
-        <v>66</v>
+        <v>79</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>job-0d5f8a75</v>
+        <v>job-099ff647</v>
       </c>
       <c r="B131" t="str">
-        <v>Product Manager II, Workspace and Multi-User</v>
+        <v>Product Manager, Acquisition</v>
       </c>
       <c r="C131" t="str">
-        <v>Coinbase</v>
+        <v>Figma</v>
       </c>
       <c r="D131" t="str">
         <v>LinkedIn</v>
@@ -8284,28 +8284,28 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H131" t="str">
-        <v>Remote - USA</v>
+        <v>San Francisco, CA • New York, NY • United States</v>
       </c>
       <c r="I131" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J131" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K131" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L131" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/8148171</v>
+        <v>https://boards.greenhouse.io/figma/jobs/6119781004</v>
       </c>
       <c r="M131">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N131" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O131" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P131" t="str">
         <v>Today</v>
@@ -8317,54 +8317,54 @@
         <v>No</v>
       </c>
       <c r="S131">
-        <v>81</v>
+        <v>85</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>job-2efe7fb3</v>
+        <v>job-714f8c79</v>
       </c>
       <c r="B132" t="str">
-        <v>Senior Product Manager, Help Center (CX Automation)</v>
+        <v>Product Manager, AI Growth</v>
       </c>
       <c r="C132" t="str">
-        <v>Coinbase</v>
+        <v>Figma</v>
       </c>
       <c r="D132" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E132" t="str">
-        <v>Senior Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F132" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G132" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H132" t="str">
-        <v>Remote - India</v>
+        <v>San Francisco, CA • New York, NY • United States</v>
       </c>
       <c r="I132" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J132" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K132" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L132" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/8031208</v>
+        <v>https://boards.greenhouse.io/figma/jobs/5989185004</v>
       </c>
       <c r="M132">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N132" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O132" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P132" t="str">
         <v>Today</v>
@@ -8373,48 +8373,48 @@
         <v>Yes</v>
       </c>
       <c r="R132" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S132">
-        <v>41</v>
+        <v>32</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>job-1762a9dc</v>
+        <v>job-6c338367</v>
       </c>
       <c r="B133" t="str">
-        <v>Director of Product Management, Agentic Software Delivery</v>
+        <v>Product Manager, Developer Platform</v>
       </c>
       <c r="C133" t="str">
-        <v>GitLab</v>
+        <v>Figma</v>
       </c>
       <c r="D133" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E133" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F133" t="str">
-        <v>8+ yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G133" t="str">
-        <v>8+ yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H133" t="str">
-        <v>Remote, United States</v>
+        <v>San Francisco, CA • New York, NY • United States</v>
       </c>
       <c r="I133" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J133" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K133" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L133" t="str">
-        <v>https://boards.greenhouse.io/gitlab/jobs/8806017002</v>
+        <v>https://boards.greenhouse.io/figma/jobs/6100482004</v>
       </c>
       <c r="M133">
         <v>200</v>
@@ -8423,7 +8423,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O133" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P133" t="str">
         <v>Today</v>
@@ -8435,24 +8435,24 @@
         <v>No</v>
       </c>
       <c r="S133">
-        <v>28</v>
+        <v>60</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>job-58e27f7c</v>
+        <v>job-3c3dabbf</v>
       </c>
       <c r="B134" t="str">
-        <v>Principal Product Manager, AI Software Factory</v>
+        <v>Director of Product Management, Advertiser Growth</v>
       </c>
       <c r="C134" t="str">
-        <v>GitLab</v>
+        <v>Pinterest</v>
       </c>
       <c r="D134" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E134" t="str">
-        <v>Senior Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F134" t="str">
         <v>8+ yrs</v>
@@ -8461,28 +8461,28 @@
         <v>8+ yrs</v>
       </c>
       <c r="H134" t="str">
-        <v>Remote, Canada; Remote, United States</v>
+        <v>Palo Alto, CA, US; Seattle, WA, US; New York, NY, US</v>
       </c>
       <c r="I134" t="str">
-        <v>Remote</v>
+        <v>New York</v>
       </c>
       <c r="J134" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K134" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L134" t="str">
-        <v>https://boards.greenhouse.io/gitlab/jobs/8658878002</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/8132504</v>
       </c>
       <c r="M134">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N134" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O134" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P134" t="str">
         <v>Today</v>
@@ -8494,36 +8494,36 @@
         <v>No</v>
       </c>
       <c r="S134">
-        <v>89</v>
+        <v>59</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>job-448d861a</v>
+        <v>job-2ca475a2</v>
       </c>
       <c r="B135" t="str">
-        <v>Senior Product Manager, Agentic Source Code</v>
+        <v>Product Manager II, Content Compliance</v>
       </c>
       <c r="C135" t="str">
-        <v>GitLab</v>
+        <v>Pinterest</v>
       </c>
       <c r="D135" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E135" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F135" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G135" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H135" t="str">
-        <v>Remote, Canada; Remote, US</v>
+        <v>San Francisco, CA, US; Seattle, WA, US; Remote, CA, US</v>
       </c>
       <c r="I135" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J135" t="str">
         <v>Remote</v>
@@ -8532,57 +8532,57 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L135" t="str">
-        <v>https://boards.greenhouse.io/gitlab/jobs/8597805002</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/7901910</v>
       </c>
       <c r="M135">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N135" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O135" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P135" t="str">
         <v>Today</v>
       </c>
       <c r="Q135" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R135" t="str">
         <v>No</v>
       </c>
       <c r="S135">
-        <v>26</v>
+        <v>45</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>job-6bc28568</v>
+        <v>job-1e7e452c</v>
       </c>
       <c r="B136" t="str">
-        <v>Senior Product Manager, Secret Detection and Vulnerability Research</v>
+        <v>Product Manager II, Search Experience</v>
       </c>
       <c r="C136" t="str">
-        <v>GitLab</v>
+        <v>Pinterest</v>
       </c>
       <c r="D136" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E136" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F136" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G136" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H136" t="str">
-        <v>Remote, United States</v>
+        <v>San Francisco, CA, US; Remote, US</v>
       </c>
       <c r="I136" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J136" t="str">
         <v>Remote</v>
@@ -8591,57 +8591,57 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L136" t="str">
-        <v>https://boards.greenhouse.io/gitlab/jobs/8697043002</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/8042279</v>
       </c>
       <c r="M136">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N136" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O136" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P136" t="str">
         <v>Today</v>
       </c>
       <c r="Q136" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R136" t="str">
         <v>No</v>
       </c>
       <c r="S136">
-        <v>85</v>
+        <v>42</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>job-7ad77ccd</v>
+        <v>job-3070654d</v>
       </c>
       <c r="B137" t="str">
-        <v>Senior Product Manager, Tenant Scale</v>
+        <v>Sr. Product Manager, Search Personalization</v>
       </c>
       <c r="C137" t="str">
-        <v>GitLab</v>
+        <v>Pinterest</v>
       </c>
       <c r="D137" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E137" t="str">
         <v>Senior Product Manager</v>
       </c>
       <c r="F137" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G137" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H137" t="str">
-        <v>Remote, Canada; Remote, US</v>
+        <v>San Francisco, CA, US; Remote, US</v>
       </c>
       <c r="I137" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J137" t="str">
         <v>Remote</v>
@@ -8650,16 +8650,16 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L137" t="str">
-        <v>https://boards.greenhouse.io/gitlab/jobs/8512220002</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/8015494</v>
       </c>
       <c r="M137">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N137" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O137" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P137" t="str">
         <v>Today</v>
@@ -8671,36 +8671,36 @@
         <v>Yes</v>
       </c>
       <c r="S137">
-        <v>92</v>
+        <v>38</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>job-52edb6a4</v>
+        <v>job-2683c45a</v>
       </c>
       <c r="B138" t="str">
-        <v>Staff Product Manager,  RevOps &amp; Finance Systems</v>
+        <v>Sr. Product Manager, TwoTwenty</v>
       </c>
       <c r="C138" t="str">
-        <v>GitLab</v>
+        <v>Pinterest</v>
       </c>
       <c r="D138" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E138" t="str">
         <v>Senior Product Manager</v>
       </c>
       <c r="F138" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G138" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H138" t="str">
-        <v>Remote, US</v>
+        <v>San Francisco, CA, US; Remote, US</v>
       </c>
       <c r="I138" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J138" t="str">
         <v>Remote</v>
@@ -8709,57 +8709,57 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L138" t="str">
-        <v>https://boards.greenhouse.io/gitlab/jobs/8612937002</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/8015519</v>
       </c>
       <c r="M138">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N138" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O138" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P138" t="str">
         <v>Today</v>
       </c>
       <c r="Q138" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R138" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S138">
-        <v>53</v>
+        <v>31</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>job-3a743e4f</v>
+        <v>job-04d22fdc</v>
       </c>
       <c r="B139" t="str">
-        <v>Manager, Product Management - Figma Platform Experience</v>
+        <v>Staff Product Manager, Ads Measurement</v>
       </c>
       <c r="C139" t="str">
-        <v>Figma</v>
+        <v>Pinterest</v>
       </c>
       <c r="D139" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E139" t="str">
-        <v>Technical Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F139" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G139" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H139" t="str">
-        <v>San Francisco, CA • New York, NY • United States</v>
+        <v>New York, NY, US</v>
       </c>
       <c r="I139" t="str">
-        <v>San Francisco</v>
+        <v>New York</v>
       </c>
       <c r="J139" t="str">
         <v>On-site</v>
@@ -8768,75 +8768,75 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L139" t="str">
-        <v>https://boards.greenhouse.io/figma/jobs/6160732004</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/7683962</v>
       </c>
       <c r="M139">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N139" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O139" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P139" t="str">
         <v>Today</v>
       </c>
       <c r="Q139" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R139" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S139">
-        <v>71</v>
+        <v>48</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>job-7297f499</v>
+        <v>job-336a1df9</v>
       </c>
       <c r="B140" t="str">
-        <v>Manager, Product Management - Roundtripping</v>
+        <v>Staff Product Manager, Applied Science</v>
       </c>
       <c r="C140" t="str">
-        <v>Figma</v>
+        <v>Pinterest</v>
       </c>
       <c r="D140" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E140" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F140" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G140" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H140" t="str">
-        <v>New York, NY • United States</v>
+        <v>San Francisco, CA, US; Remote, US</v>
       </c>
       <c r="I140" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J140" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K140" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L140" t="str">
-        <v>https://boards.greenhouse.io/figma/jobs/6104919004</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/8082033</v>
       </c>
       <c r="M140">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N140" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O140" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P140" t="str">
         <v>Today</v>
@@ -8848,104 +8848,104 @@
         <v>Yes</v>
       </c>
       <c r="S140">
-        <v>29</v>
+        <v>61</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>job-19031a2a</v>
+        <v>job-7e8b8408</v>
       </c>
       <c r="B141" t="str">
-        <v>Manager, Product Management - Roundtripping (London, United Kingdom)</v>
+        <v>Staff Product Manager, Programmatic Ads</v>
       </c>
       <c r="C141" t="str">
-        <v>Figma</v>
+        <v>Pinterest</v>
       </c>
       <c r="D141" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E141" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F141" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G141" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H141" t="str">
-        <v>London, England</v>
+        <v>San Francisco, CA, US; Remote, CA, US</v>
       </c>
       <c r="I141" t="str">
-        <v>London</v>
+        <v>San Francisco</v>
       </c>
       <c r="J141" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K141" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L141" t="str">
-        <v>https://boards.greenhouse.io/figma/jobs/6149007004</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/7959458</v>
       </c>
       <c r="M141">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N141" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O141" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P141" t="str">
         <v>Today</v>
       </c>
       <c r="Q141" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R141" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S141">
-        <v>45</v>
+        <v>83</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>job-099ff647</v>
+        <v>job-7f4873ac</v>
       </c>
       <c r="B142" t="str">
-        <v>Product Manager, Acquisition</v>
+        <v>Director of Product, Logistics</v>
       </c>
       <c r="C142" t="str">
-        <v>Figma</v>
+        <v>Instacart</v>
       </c>
       <c r="D142" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E142" t="str">
-        <v>Product Manager</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F142" t="str">
-        <v>3-6 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G142" t="str">
-        <v>2-5 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H142" t="str">
-        <v>San Francisco, CA • New York, NY • United States</v>
+        <v>United States - Remote</v>
       </c>
       <c r="I142" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J142" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K142" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L142" t="str">
-        <v>https://boards.greenhouse.io/figma/jobs/6119781004</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8198282</v>
       </c>
       <c r="M142">
         <v>200</v>
@@ -8954,7 +8954,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O142" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P142" t="str">
         <v>Today</v>
@@ -8966,45 +8966,45 @@
         <v>Yes</v>
       </c>
       <c r="S142">
-        <v>33</v>
+        <v>44</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>job-714f8c79</v>
+        <v>job-6d240672</v>
       </c>
       <c r="B143" t="str">
-        <v>Product Manager, AI Growth</v>
+        <v>Senior Product Manager, Ads Quality</v>
       </c>
       <c r="C143" t="str">
-        <v>Figma</v>
+        <v>Instacart</v>
       </c>
       <c r="D143" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E143" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F143" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G143" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H143" t="str">
-        <v>San Francisco, CA • New York, NY • United States</v>
+        <v>United States - Remote</v>
       </c>
       <c r="I143" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J143" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K143" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L143" t="str">
-        <v>https://boards.greenhouse.io/figma/jobs/5989185004</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8077510</v>
       </c>
       <c r="M143">
         <v>200</v>
@@ -9013,7 +9013,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O143" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P143" t="str">
         <v>Today</v>
@@ -9022,48 +9022,48 @@
         <v>No</v>
       </c>
       <c r="R143" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S143">
-        <v>75</v>
+        <v>94</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>job-6c338367</v>
+        <v>job-2be59ce2</v>
       </c>
       <c r="B144" t="str">
-        <v>Product Manager, Developer Platform</v>
+        <v>Senior Product Manager, Advertiser Experience</v>
       </c>
       <c r="C144" t="str">
-        <v>Figma</v>
+        <v>Instacart</v>
       </c>
       <c r="D144" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E144" t="str">
-        <v>Technical Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F144" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G144" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H144" t="str">
-        <v>San Francisco, CA • New York, NY • United States</v>
+        <v>United States - Remote</v>
       </c>
       <c r="I144" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J144" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K144" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L144" t="str">
-        <v>https://boards.greenhouse.io/figma/jobs/6100482004</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8120469</v>
       </c>
       <c r="M144">
         <v>200</v>
@@ -9072,107 +9072,107 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O144" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P144" t="str">
         <v>Today</v>
       </c>
       <c r="Q144" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R144" t="str">
         <v>No</v>
       </c>
       <c r="S144">
-        <v>51</v>
+        <v>68</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>job-3c3dabbf</v>
+        <v>job-69064914</v>
       </c>
       <c r="B145" t="str">
-        <v>Director of Product Management, Advertiser Growth</v>
+        <v>Senior Product Manager, AI Control Studio</v>
       </c>
       <c r="C145" t="str">
-        <v>Pinterest</v>
+        <v>Instacart</v>
       </c>
       <c r="D145" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E145" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F145" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G145" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H145" t="str">
-        <v>Palo Alto, CA, US; Seattle, WA, US; New York, NY, US</v>
+        <v>United States - Remote</v>
       </c>
       <c r="I145" t="str">
-        <v>New York</v>
+        <v>Remote</v>
       </c>
       <c r="J145" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K145" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L145" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/8132504</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8198159</v>
       </c>
       <c r="M145">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N145" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O145" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P145" t="str">
         <v>Today</v>
       </c>
       <c r="Q145" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R145" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S145">
-        <v>93</v>
+        <v>47</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>job-2ca475a2</v>
+        <v>job-6ddb2cbc</v>
       </c>
       <c r="B146" t="str">
-        <v>Product Manager II, Content Compliance</v>
+        <v>Senior Product Manager, Catalog</v>
       </c>
       <c r="C146" t="str">
-        <v>Pinterest</v>
+        <v>Instacart</v>
       </c>
       <c r="D146" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E146" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F146" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G146" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H146" t="str">
-        <v>San Francisco, CA, US; Seattle, WA, US; Remote, CA, US</v>
+        <v>United States - Remote</v>
       </c>
       <c r="I146" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J146" t="str">
         <v>Remote</v>
@@ -9181,57 +9181,57 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L146" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/7901910</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8143270</v>
       </c>
       <c r="M146">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N146" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O146" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P146" t="str">
         <v>Today</v>
       </c>
       <c r="Q146" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R146" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S146">
-        <v>89</v>
+        <v>60</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>job-1e7e452c</v>
+        <v>job-3d0cfe30</v>
       </c>
       <c r="B147" t="str">
-        <v>Product Manager II, Search Experience</v>
+        <v>Senior Product Manager, Order Quality</v>
       </c>
       <c r="C147" t="str">
-        <v>Pinterest</v>
+        <v>Instacart</v>
       </c>
       <c r="D147" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E147" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F147" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G147" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H147" t="str">
-        <v>San Francisco, CA, US; Remote, US</v>
+        <v>United States - Remote</v>
       </c>
       <c r="I147" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J147" t="str">
         <v>Remote</v>
@@ -9240,16 +9240,16 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L147" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/8042279</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8203107</v>
       </c>
       <c r="M147">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N147" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O147" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P147" t="str">
         <v>Today</v>
@@ -9261,18 +9261,18 @@
         <v>No</v>
       </c>
       <c r="S147">
-        <v>42</v>
+        <v>68</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>job-3070654d</v>
+        <v>job-2319ed86</v>
       </c>
       <c r="B148" t="str">
-        <v>Sr. Product Manager, Search Personalization</v>
+        <v>Senior Product Manager, Retailer Platform</v>
       </c>
       <c r="C148" t="str">
-        <v>Pinterest</v>
+        <v>Instacart</v>
       </c>
       <c r="D148" t="str">
         <v>LinkedIn</v>
@@ -9281,16 +9281,16 @@
         <v>Senior Product Manager</v>
       </c>
       <c r="F148" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G148" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H148" t="str">
-        <v>San Francisco, CA, US; Remote, US</v>
+        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
       </c>
       <c r="I148" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J148" t="str">
         <v>Remote</v>
@@ -9299,45 +9299,45 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L148" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/8015494</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8014062</v>
       </c>
       <c r="M148">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N148" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O148" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P148" t="str">
         <v>Today</v>
       </c>
       <c r="Q148" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R148" t="str">
         <v>No</v>
       </c>
       <c r="S148">
-        <v>30</v>
+        <v>40</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>job-2683c45a</v>
+        <v>job-6d0cde89</v>
       </c>
       <c r="B149" t="str">
-        <v>Sr. Product Manager, TwoTwenty</v>
+        <v>Product Manager II - Ads</v>
       </c>
       <c r="C149" t="str">
-        <v>Pinterest</v>
+        <v>Razorpay</v>
       </c>
       <c r="D149" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E149" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F149" t="str">
         <v>3-6 yrs</v>
@@ -9346,28 +9346,28 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H149" t="str">
-        <v>San Francisco, CA, US; Remote, US</v>
+        <v>Bengaluru</v>
       </c>
       <c r="I149" t="str">
-        <v>San Francisco</v>
+        <v>Bengaluru</v>
       </c>
       <c r="J149" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K149" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L149" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/8015519</v>
+        <v>https://boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4729533005</v>
       </c>
       <c r="M149">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N149" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O149" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P149" t="str">
         <v>Today</v>
@@ -9376,39 +9376,39 @@
         <v>Yes</v>
       </c>
       <c r="R149" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S149">
-        <v>45</v>
+        <v>84</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>job-04d22fdc</v>
+        <v>job-7c247a79</v>
       </c>
       <c r="B150" t="str">
-        <v>Staff Product Manager, Ads Measurement</v>
+        <v>Product Manager II - AI</v>
       </c>
       <c r="C150" t="str">
-        <v>Pinterest</v>
+        <v>Razorpay</v>
       </c>
       <c r="D150" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E150" t="str">
-        <v>Senior Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F150" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G150" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H150" t="str">
-        <v>New York, NY, US</v>
+        <v>Bengaluru</v>
       </c>
       <c r="I150" t="str">
-        <v>New York</v>
+        <v>Bengaluru</v>
       </c>
       <c r="J150" t="str">
         <v>On-site</v>
@@ -9417,16 +9417,16 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L150" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/7683962</v>
+        <v>https://boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4699107005</v>
       </c>
       <c r="M150">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N150" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O150" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P150" t="str">
         <v>Today</v>
@@ -9438,163 +9438,163 @@
         <v>No</v>
       </c>
       <c r="S150">
-        <v>36</v>
+        <v>74</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>job-336a1df9</v>
+        <v>job-1c3166e2</v>
       </c>
       <c r="B151" t="str">
-        <v>Staff Product Manager, Applied Science</v>
+        <v>Product Manager, API Agents</v>
       </c>
       <c r="C151" t="str">
-        <v>Pinterest</v>
+        <v>OpenAI</v>
       </c>
       <c r="D151" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E151" t="str">
-        <v>Senior Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F151" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G151" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H151" t="str">
-        <v>San Francisco, CA, US; Remote, US</v>
+        <v>San Francisco</v>
       </c>
       <c r="I151" t="str">
         <v>San Francisco</v>
       </c>
       <c r="J151" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K151" t="str">
-        <v>$140k - $220k USD + Equity</v>
+        <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L151" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/8082033</v>
+        <v>https://jobs.ashbyhq.com/openai/fc38c6bf-5330-435c-99b6-1bcf1f5829a8</v>
       </c>
       <c r="M151">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N151" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O151" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P151" t="str">
         <v>Today</v>
       </c>
       <c r="Q151" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R151" t="str">
         <v>No</v>
       </c>
       <c r="S151">
-        <v>56</v>
+        <v>99</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>job-7e8b8408</v>
+        <v>job-6d2b24fc</v>
       </c>
       <c r="B152" t="str">
-        <v>Staff Product Manager, Programmatic Ads</v>
+        <v>Product Manager, Sensitive Deployments</v>
       </c>
       <c r="C152" t="str">
-        <v>Pinterest</v>
+        <v>OpenAI</v>
       </c>
       <c r="D152" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E152" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F152" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G152" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H152" t="str">
-        <v>San Francisco, CA, US; Remote, CA, US</v>
+        <v>San Francisco</v>
       </c>
       <c r="I152" t="str">
         <v>San Francisco</v>
       </c>
       <c r="J152" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K152" t="str">
-        <v>$140k - $220k USD + Equity</v>
+        <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L152" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/7959458</v>
+        <v>https://jobs.ashbyhq.com/openai/05a8cae8-81bd-4f7b-bc48-41ef1bd67e5d</v>
       </c>
       <c r="M152">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N152" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O152" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P152" t="str">
         <v>Today</v>
       </c>
       <c r="Q152" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R152" t="str">
         <v>No</v>
       </c>
       <c r="S152">
-        <v>64</v>
+        <v>73</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>job-7f4873ac</v>
+        <v>job-184a9e13</v>
       </c>
       <c r="B153" t="str">
-        <v>Director of Product, Logistics</v>
+        <v>Product Manager, API Infrastructure</v>
       </c>
       <c r="C153" t="str">
-        <v>Instacart</v>
+        <v>OpenAI</v>
       </c>
       <c r="D153" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E153" t="str">
-        <v>Product Lead / Director</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F153" t="str">
-        <v>8+ yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G153" t="str">
-        <v>8+ yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H153" t="str">
-        <v>United States - Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="I153" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J153" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K153" t="str">
-        <v>$140k - $220k USD + Equity</v>
+        <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L153" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8198282</v>
+        <v>https://jobs.ashbyhq.com/openai/7ffa2a14-fa9c-46cb-a30a-1f7a35ae904a</v>
       </c>
       <c r="M153">
         <v>200</v>
@@ -9603,57 +9603,57 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O153" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P153" t="str">
         <v>Today</v>
       </c>
       <c r="Q153" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R153" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S153">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>job-6d240672</v>
+        <v>job-61ec6778</v>
       </c>
       <c r="B154" t="str">
-        <v>Senior Product Manager, Ads Quality</v>
+        <v>Product Manager, Safety Measurement</v>
       </c>
       <c r="C154" t="str">
-        <v>Instacart</v>
+        <v>OpenAI</v>
       </c>
       <c r="D154" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E154" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F154" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G154" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H154" t="str">
-        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
+        <v>San Francisco</v>
       </c>
       <c r="I154" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J154" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K154" t="str">
-        <v>$140k - $220k USD + Equity</v>
+        <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L154" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8077512</v>
+        <v>https://jobs.ashbyhq.com/openai/fbc7ebaf-3a26-406d-9ff6-f166f3e246a2</v>
       </c>
       <c r="M154">
         <v>200</v>
@@ -9662,7 +9662,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O154" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P154" t="str">
         <v>Today</v>
@@ -9674,45 +9674,45 @@
         <v>Yes</v>
       </c>
       <c r="S154">
-        <v>83</v>
+        <v>93</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>job-2be59ce2</v>
+        <v>job-32d0b9c4</v>
       </c>
       <c r="B155" t="str">
-        <v>Senior Product Manager, Advertiser Experience</v>
+        <v>Product Manager, Financial Engineering</v>
       </c>
       <c r="C155" t="str">
-        <v>Instacart</v>
+        <v>OpenAI</v>
       </c>
       <c r="D155" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E155" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F155" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G155" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H155" t="str">
-        <v>United States - Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="I155" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J155" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K155" t="str">
-        <v>$140k - $220k USD + Equity</v>
+        <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L155" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8120469</v>
+        <v>https://jobs.ashbyhq.com/openai/0f4da2b4-df8a-4560-809d-d0a6ac1ad9bc</v>
       </c>
       <c r="M155">
         <v>200</v>
@@ -9721,7 +9721,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O155" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P155" t="str">
         <v>Today</v>
@@ -9730,48 +9730,48 @@
         <v>Yes</v>
       </c>
       <c r="R155" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S155">
-        <v>56</v>
+        <v>65</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>job-69064914</v>
+        <v>job-675130d5</v>
       </c>
       <c r="B156" t="str">
-        <v>Senior Product Manager, AI Control Studio</v>
+        <v>Product Manager, Core Models</v>
       </c>
       <c r="C156" t="str">
-        <v>Instacart</v>
+        <v>OpenAI</v>
       </c>
       <c r="D156" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E156" t="str">
-        <v>Senior Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F156" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G156" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H156" t="str">
-        <v>United States - Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="I156" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J156" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K156" t="str">
-        <v>$140k - $220k USD + Equity</v>
+        <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L156" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8198159</v>
+        <v>https://jobs.ashbyhq.com/openai/33b8effb-b048-4934-a279-87fff192a330</v>
       </c>
       <c r="M156">
         <v>200</v>
@@ -9780,7 +9780,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O156" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P156" t="str">
         <v>Today</v>
@@ -9789,48 +9789,48 @@
         <v>Yes</v>
       </c>
       <c r="R156" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S156">
-        <v>60</v>
+        <v>78</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>job-6ddb2cbc</v>
+        <v>job-032480cd</v>
       </c>
       <c r="B157" t="str">
-        <v>Senior Product Manager, Catalog</v>
+        <v>Product Manager, Youth</v>
       </c>
       <c r="C157" t="str">
-        <v>Instacart</v>
+        <v>OpenAI</v>
       </c>
       <c r="D157" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E157" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F157" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G157" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H157" t="str">
-        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
+        <v>San Francisco</v>
       </c>
       <c r="I157" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J157" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K157" t="str">
-        <v>$140k - $220k USD + Equity</v>
+        <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L157" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8143272</v>
+        <v>https://jobs.ashbyhq.com/openai/cc0d0d86-eb9d-44a0-a6a4-42bbb6066b4b</v>
       </c>
       <c r="M157">
         <v>200</v>
@@ -9839,57 +9839,57 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O157" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P157" t="str">
         <v>Today</v>
       </c>
       <c r="Q157" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R157" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S157">
-        <v>40</v>
+        <v>109</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>job-3d0cfe30</v>
+        <v>job-50e54898</v>
       </c>
       <c r="B158" t="str">
-        <v>Senior Product Manager, Order Quality</v>
+        <v>Product Manager, Learning</v>
       </c>
       <c r="C158" t="str">
-        <v>Instacart</v>
+        <v>OpenAI</v>
       </c>
       <c r="D158" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E158" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F158" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G158" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H158" t="str">
-        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
+        <v>San Francisco</v>
       </c>
       <c r="I158" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J158" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K158" t="str">
-        <v>$140k - $220k USD + Equity</v>
+        <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L158" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8203109</v>
+        <v>https://jobs.ashbyhq.com/openai/5953fed7-1466-4e90-94c9-43716a55e032</v>
       </c>
       <c r="M158">
         <v>200</v>
@@ -9898,7 +9898,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O158" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P158" t="str">
         <v>Today</v>
@@ -9907,48 +9907,48 @@
         <v>Yes</v>
       </c>
       <c r="R158" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S158">
-        <v>27</v>
+        <v>63</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>job-2319ed86</v>
+        <v>job-0df96522</v>
       </c>
       <c r="B159" t="str">
-        <v>Senior Product Manager, Retailer Platform</v>
+        <v>Product Manager, Multimodal Safety</v>
       </c>
       <c r="C159" t="str">
-        <v>Instacart</v>
+        <v>OpenAI</v>
       </c>
       <c r="D159" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E159" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F159" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G159" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H159" t="str">
-        <v>United States - Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="I159" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J159" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K159" t="str">
-        <v>$140k - $220k USD + Equity</v>
+        <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L159" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8014060</v>
+        <v>https://jobs.ashbyhq.com/openai/70d5259a-f18c-4595-bf52-ec03eeeeac4c</v>
       </c>
       <c r="M159">
         <v>200</v>
@@ -9957,30 +9957,30 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O159" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P159" t="str">
         <v>Today</v>
       </c>
       <c r="Q159" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R159" t="str">
         <v>No</v>
       </c>
       <c r="S159">
-        <v>32</v>
+        <v>58</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>job-6d0cde89</v>
+        <v>job-47895783</v>
       </c>
       <c r="B160" t="str">
-        <v>Product Manager II - Ads</v>
+        <v>Product Manager, Enterprise Identity</v>
       </c>
       <c r="C160" t="str">
-        <v>Razorpay</v>
+        <v>OpenAI</v>
       </c>
       <c r="D160" t="str">
         <v>LinkedIn</v>
@@ -9995,19 +9995,19 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H160" t="str">
-        <v>Bengaluru</v>
+        <v>San Francisco</v>
       </c>
       <c r="I160" t="str">
-        <v>Bengaluru</v>
+        <v>San Francisco</v>
       </c>
       <c r="J160" t="str">
         <v>On-site</v>
       </c>
       <c r="K160" t="str">
-        <v>$140k - $220k USD + Equity</v>
+        <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L160" t="str">
-        <v>https://boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4729533005</v>
+        <v>https://jobs.ashbyhq.com/openai/83f6d415-9462-4afc-a539-ca8d996e011a</v>
       </c>
       <c r="M160">
         <v>200</v>
@@ -10016,36 +10016,36 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O160" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P160" t="str">
         <v>Today</v>
       </c>
       <c r="Q160" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R160" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S160">
-        <v>87</v>
+        <v>94</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>job-7c247a79</v>
+        <v>job-3fd38143</v>
       </c>
       <c r="B161" t="str">
-        <v>Product Manager II - AI</v>
+        <v>Rosalind Life Sciences Product Manager</v>
       </c>
       <c r="C161" t="str">
-        <v>Razorpay</v>
+        <v>OpenAI</v>
       </c>
       <c r="D161" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E161" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Product Manager</v>
       </c>
       <c r="F161" t="str">
         <v>3-6 yrs</v>
@@ -10054,19 +10054,19 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H161" t="str">
-        <v>Bengaluru</v>
+        <v>San Francisco</v>
       </c>
       <c r="I161" t="str">
-        <v>Bengaluru</v>
+        <v>San Francisco</v>
       </c>
       <c r="J161" t="str">
         <v>On-site</v>
       </c>
       <c r="K161" t="str">
-        <v>$140k - $220k USD + Equity</v>
+        <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L161" t="str">
-        <v>https://boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4699107005</v>
+        <v>https://jobs.ashbyhq.com/openai/2b5c3a30-8e8b-4845-be40-0617b0c9fd43</v>
       </c>
       <c r="M161">
         <v>200</v>
@@ -10075,7 +10075,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O161" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P161" t="str">
         <v>Today</v>
@@ -10084,18 +10084,18 @@
         <v>Yes</v>
       </c>
       <c r="R161" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S161">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>job-1c3166e2</v>
+        <v>job-1fef334a</v>
       </c>
       <c r="B162" t="str">
-        <v>Product Manager, API Agents</v>
+        <v>Product Manager, Technology Vertical</v>
       </c>
       <c r="C162" t="str">
         <v>OpenAI</v>
@@ -10104,7 +10104,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E162" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Product Manager</v>
       </c>
       <c r="F162" t="str">
         <v>3-6 yrs</v>
@@ -10125,7 +10125,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L162" t="str">
-        <v>https://jobs.ashbyhq.com/openai/fc38c6bf-5330-435c-99b6-1bcf1f5829a8</v>
+        <v>https://jobs.ashbyhq.com/openai/137e3df0-2bd4-4ad4-8edb-8455a7fdc912</v>
       </c>
       <c r="M162">
         <v>200</v>
@@ -10134,7 +10134,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O162" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P162" t="str">
         <v>Today</v>
@@ -10143,24 +10143,24 @@
         <v>Yes</v>
       </c>
       <c r="R162" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S162">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>job-6d2b24fc</v>
+        <v>job-5db12f92</v>
       </c>
       <c r="B163" t="str">
-        <v>Product Manager, Sensitive Deployments</v>
+        <v>Product Manager (Builder)</v>
       </c>
       <c r="C163" t="str">
-        <v>OpenAI</v>
+        <v>Perplexity</v>
       </c>
       <c r="D163" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E163" t="str">
         <v>Product Manager</v>
@@ -10184,7 +10184,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L163" t="str">
-        <v>https://jobs.ashbyhq.com/openai/05a8cae8-81bd-4f7b-bc48-41ef1bd67e5d</v>
+        <v>https://jobs.ashbyhq.com/perplexity/f25e190e-0508-4707-b575-fcaed358dc13</v>
       </c>
       <c r="M163">
         <v>200</v>
@@ -10193,7 +10193,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O163" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P163" t="str">
         <v>Today</v>
@@ -10205,30 +10205,30 @@
         <v>No</v>
       </c>
       <c r="S163">
-        <v>101</v>
+        <v>86</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>job-184a9e13</v>
+        <v>job-1fe57ea5</v>
       </c>
       <c r="B164" t="str">
-        <v>Product Manager, API Infrastructure</v>
+        <v>Member of Technical Staff (TPM, Inference)</v>
       </c>
       <c r="C164" t="str">
-        <v>OpenAI</v>
+        <v>Perplexity</v>
       </c>
       <c r="D164" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E164" t="str">
-        <v>Technical Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F164" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G164" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H164" t="str">
         <v>San Francisco</v>
@@ -10243,7 +10243,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L164" t="str">
-        <v>https://jobs.ashbyhq.com/openai/7ffa2a14-fa9c-46cb-a30a-1f7a35ae904a</v>
+        <v>https://jobs.ashbyhq.com/perplexity/0c5d5a82-bfed-4786-b411-79073979af07</v>
       </c>
       <c r="M164">
         <v>200</v>
@@ -10252,7 +10252,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O164" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P164" t="str">
         <v>Today</v>
@@ -10261,24 +10261,24 @@
         <v>Yes</v>
       </c>
       <c r="R164" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S164">
-        <v>110</v>
+        <v>116</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>job-61ec6778</v>
+        <v>job-12403072</v>
       </c>
       <c r="B165" t="str">
-        <v>Product Manager, Safety Measurement</v>
+        <v>Product Manager, Mobile Apps</v>
       </c>
       <c r="C165" t="str">
-        <v>OpenAI</v>
+        <v>Perplexity</v>
       </c>
       <c r="D165" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E165" t="str">
         <v>Product Manager</v>
@@ -10302,7 +10302,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L165" t="str">
-        <v>https://jobs.ashbyhq.com/openai/fbc7ebaf-3a26-406d-9ff6-f166f3e246a2</v>
+        <v>https://jobs.ashbyhq.com/perplexity/3c9c051f-e6ca-4a70-9abf-1f640e154ee1</v>
       </c>
       <c r="M165">
         <v>200</v>
@@ -10311,7 +10311,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O165" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P165" t="str">
         <v>Today</v>
@@ -10323,24 +10323,24 @@
         <v>No</v>
       </c>
       <c r="S165">
-        <v>119</v>
+        <v>43</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>job-32d0b9c4</v>
+        <v>job-10379173</v>
       </c>
       <c r="B166" t="str">
-        <v>Product Manager, Financial Engineering</v>
+        <v>Product Manager, Core Experience</v>
       </c>
       <c r="C166" t="str">
-        <v>OpenAI</v>
+        <v>Perplexity</v>
       </c>
       <c r="D166" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E166" t="str">
-        <v>Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F166" t="str">
         <v>3-6 yrs</v>
@@ -10361,7 +10361,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L166" t="str">
-        <v>https://jobs.ashbyhq.com/openai/0f4da2b4-df8a-4560-809d-d0a6ac1ad9bc</v>
+        <v>https://jobs.ashbyhq.com/perplexity/6f3c5131-2efa-400c-8248-44203a4dbfbb</v>
       </c>
       <c r="M166">
         <v>200</v>
@@ -10370,7 +10370,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O166" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P166" t="str">
         <v>Today</v>
@@ -10379,27 +10379,27 @@
         <v>Yes</v>
       </c>
       <c r="R166" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S166">
-        <v>70</v>
+        <v>101</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>job-675130d5</v>
+        <v>job-247da510</v>
       </c>
       <c r="B167" t="str">
-        <v>Product Manager, Core Models</v>
+        <v>Product Manager, AI Capabilities</v>
       </c>
       <c r="C167" t="str">
-        <v>OpenAI</v>
+        <v>Perplexity</v>
       </c>
       <c r="D167" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E167" t="str">
-        <v>Technical Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F167" t="str">
         <v>3-6 yrs</v>
@@ -10420,7 +10420,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L167" t="str">
-        <v>https://jobs.ashbyhq.com/openai/33b8effb-b048-4934-a279-87fff192a330</v>
+        <v>https://jobs.ashbyhq.com/perplexity/7f880194-7276-4b46-8a50-58b48da8882e</v>
       </c>
       <c r="M167">
         <v>200</v>
@@ -10429,7 +10429,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O167" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P167" t="str">
         <v>Today</v>
@@ -10441,24 +10441,24 @@
         <v>No</v>
       </c>
       <c r="S167">
-        <v>93</v>
+        <v>53</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>job-032480cd</v>
+        <v>job-757a314d</v>
       </c>
       <c r="B168" t="str">
-        <v>Product Manager, Youth</v>
+        <v>Product Manager, Growth</v>
       </c>
       <c r="C168" t="str">
-        <v>OpenAI</v>
+        <v>Perplexity</v>
       </c>
       <c r="D168" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E168" t="str">
-        <v>Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F168" t="str">
         <v>3-6 yrs</v>
@@ -10467,10 +10467,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H168" t="str">
-        <v>San Francisco</v>
+        <v>New York City</v>
       </c>
       <c r="I168" t="str">
-        <v>San Francisco</v>
+        <v>New York</v>
       </c>
       <c r="J168" t="str">
         <v>On-site</v>
@@ -10479,7 +10479,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L168" t="str">
-        <v>https://jobs.ashbyhq.com/openai/cc0d0d86-eb9d-44a0-a6a4-42bbb6066b4b</v>
+        <v>https://jobs.ashbyhq.com/perplexity/fa088d92-b08b-43f7-9232-275b0ae08827</v>
       </c>
       <c r="M168">
         <v>200</v>
@@ -10488,7 +10488,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O168" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P168" t="str">
         <v>Today</v>
@@ -10497,27 +10497,27 @@
         <v>Yes</v>
       </c>
       <c r="R168" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S168">
-        <v>86</v>
+        <v>81</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>job-50e54898</v>
+        <v>job-376e5ff5</v>
       </c>
       <c r="B169" t="str">
-        <v>Product Manager, Learning</v>
+        <v>Product Manager, SMB Growth</v>
       </c>
       <c r="C169" t="str">
-        <v>OpenAI</v>
+        <v>Perplexity</v>
       </c>
       <c r="D169" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E169" t="str">
-        <v>Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F169" t="str">
         <v>3-6 yrs</v>
@@ -10526,10 +10526,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H169" t="str">
-        <v>San Francisco</v>
+        <v>New York City</v>
       </c>
       <c r="I169" t="str">
-        <v>San Francisco</v>
+        <v>New York</v>
       </c>
       <c r="J169" t="str">
         <v>On-site</v>
@@ -10538,7 +10538,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L169" t="str">
-        <v>https://jobs.ashbyhq.com/openai/5953fed7-1466-4e90-94c9-43716a55e032</v>
+        <v>https://jobs.ashbyhq.com/perplexity/182ab2ec-6fb1-409b-a2dc-63c7832b0a13</v>
       </c>
       <c r="M169">
         <v>200</v>
@@ -10547,7 +10547,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O169" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P169" t="str">
         <v>Today</v>
@@ -10559,21 +10559,21 @@
         <v>Yes</v>
       </c>
       <c r="S169">
-        <v>59</v>
+        <v>44</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>job-0df96522</v>
+        <v>job-6fff938e</v>
       </c>
       <c r="B170" t="str">
-        <v>Product Manager, Multimodal Safety</v>
+        <v>Product Manager - Marketplace</v>
       </c>
       <c r="C170" t="str">
-        <v>OpenAI</v>
+        <v>Supabase</v>
       </c>
       <c r="D170" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E170" t="str">
         <v>Product Manager</v>
@@ -10585,19 +10585,19 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H170" t="str">
-        <v>San Francisco</v>
+        <v>Remote, Global</v>
       </c>
       <c r="I170" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J170" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K170" t="str">
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L170" t="str">
-        <v>https://jobs.ashbyhq.com/openai/70d5259a-f18c-4595-bf52-ec03eeeeac4c</v>
+        <v>https://jobs.ashbyhq.com/supabase/23c9ce7e-6b7b-4316-8f00-8f318e902441</v>
       </c>
       <c r="M170">
         <v>200</v>
@@ -10606,7 +10606,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O170" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P170" t="str">
         <v>Today</v>
@@ -10615,24 +10615,24 @@
         <v>Yes</v>
       </c>
       <c r="R170" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S170">
-        <v>43</v>
+        <v>58</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>job-47895783</v>
+        <v>job-49f97312</v>
       </c>
       <c r="B171" t="str">
-        <v>Product Manager, Enterprise Identity</v>
+        <v>Product Manager - Security &amp; Trust (EMEA/AMER)</v>
       </c>
       <c r="C171" t="str">
-        <v>OpenAI</v>
+        <v>Supabase</v>
       </c>
       <c r="D171" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E171" t="str">
         <v>Product Manager</v>
@@ -10644,19 +10644,19 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H171" t="str">
-        <v>San Francisco</v>
+        <v>Remote, Global</v>
       </c>
       <c r="I171" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J171" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K171" t="str">
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L171" t="str">
-        <v>https://jobs.ashbyhq.com/openai/83f6d415-9462-4afc-a539-ca8d996e011a</v>
+        <v>https://jobs.ashbyhq.com/supabase/b8010a28-109c-46a9-b8b7-c7f9b24077fa</v>
       </c>
       <c r="M171">
         <v>200</v>
@@ -10665,7 +10665,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O171" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P171" t="str">
         <v>Today</v>
@@ -10674,24 +10674,24 @@
         <v>Yes</v>
       </c>
       <c r="R171" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S171">
-        <v>58</v>
+        <v>49</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>job-3fd38143</v>
+        <v>job-064fa6b5</v>
       </c>
       <c r="B172" t="str">
-        <v>Rosalind Life Sciences Product Manager</v>
+        <v>Product Manager - Strategic Partner Integrations (Bay Area based)</v>
       </c>
       <c r="C172" t="str">
-        <v>OpenAI</v>
+        <v>Supabase</v>
       </c>
       <c r="D172" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E172" t="str">
         <v>Product Manager</v>
@@ -10703,19 +10703,19 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H172" t="str">
-        <v>San Francisco</v>
+        <v>Remote, Bay Area, CA</v>
       </c>
       <c r="I172" t="str">
         <v>San Francisco</v>
       </c>
       <c r="J172" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K172" t="str">
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L172" t="str">
-        <v>https://jobs.ashbyhq.com/openai/2b5c3a30-8e8b-4845-be40-0617b0c9fd43</v>
+        <v>https://jobs.ashbyhq.com/supabase/68a397e7-8a1a-4566-ae41-e8c61dd6ed93</v>
       </c>
       <c r="M172">
         <v>200</v>
@@ -10724,7 +10724,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O172" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P172" t="str">
         <v>Today</v>
@@ -10736,24 +10736,24 @@
         <v>Yes</v>
       </c>
       <c r="S172">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>job-1fef334a</v>
+        <v>job-7da017c6</v>
       </c>
       <c r="B173" t="str">
-        <v>Product Manager, Technology Vertical</v>
+        <v>Product Manager | Vendor Intelligence &amp; Marketplace</v>
       </c>
       <c r="C173" t="str">
-        <v>OpenAI</v>
+        <v>Ramp</v>
       </c>
       <c r="D173" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E173" t="str">
-        <v>Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F173" t="str">
         <v>3-6 yrs</v>
@@ -10762,10 +10762,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H173" t="str">
-        <v>San Francisco</v>
+        <v>New York, NY (HQ)</v>
       </c>
       <c r="I173" t="str">
-        <v>San Francisco</v>
+        <v>New York</v>
       </c>
       <c r="J173" t="str">
         <v>On-site</v>
@@ -10774,7 +10774,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L173" t="str">
-        <v>https://jobs.ashbyhq.com/openai/137e3df0-2bd4-4ad4-8edb-8455a7fdc912</v>
+        <v>https://jobs.ashbyhq.com/ramp/cf3516f6-4d6b-4872-831f-c8ef4a3078ee</v>
       </c>
       <c r="M173">
         <v>200</v>
@@ -10783,7 +10783,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O173" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P173" t="str">
         <v>Today</v>
@@ -10792,24 +10792,24 @@
         <v>Yes</v>
       </c>
       <c r="R173" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S173">
-        <v>43</v>
+        <v>86</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>job-5db12f92</v>
+        <v>job-338455bd</v>
       </c>
       <c r="B174" t="str">
-        <v>Product Manager (Builder)</v>
+        <v>Product Manager | Tax</v>
       </c>
       <c r="C174" t="str">
-        <v>Perplexity</v>
+        <v>Ramp</v>
       </c>
       <c r="D174" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E174" t="str">
         <v>Product Manager</v>
@@ -10821,10 +10821,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H174" t="str">
-        <v>San Francisco</v>
+        <v>New York, NY (HQ)</v>
       </c>
       <c r="I174" t="str">
-        <v>San Francisco</v>
+        <v>New York</v>
       </c>
       <c r="J174" t="str">
         <v>On-site</v>
@@ -10833,7 +10833,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L174" t="str">
-        <v>https://jobs.ashbyhq.com/perplexity/f25e190e-0508-4707-b575-fcaed358dc13</v>
+        <v>https://jobs.ashbyhq.com/ramp/881f9f7d-9ec5-4b69-b50d-a67000264ca8</v>
       </c>
       <c r="M174">
         <v>200</v>
@@ -10842,7 +10842,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O174" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P174" t="str">
         <v>Today</v>
@@ -10851,39 +10851,39 @@
         <v>Yes</v>
       </c>
       <c r="R174" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S174">
-        <v>67</v>
+        <v>41</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>job-1fe57ea5</v>
+        <v>job-6744eb00</v>
       </c>
       <c r="B175" t="str">
-        <v>Member of Technical Staff (TPM, Inference)</v>
+        <v>Product Manager | International</v>
       </c>
       <c r="C175" t="str">
-        <v>Perplexity</v>
+        <v>Ramp</v>
       </c>
       <c r="D175" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E175" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F175" t="str">
-        <v>5-8 yrs</v>
+        <v>1-3 yrs</v>
       </c>
       <c r="G175" t="str">
-        <v>5-8 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H175" t="str">
-        <v>San Francisco</v>
+        <v>New York, NY (HQ)</v>
       </c>
       <c r="I175" t="str">
-        <v>San Francisco</v>
+        <v>New York</v>
       </c>
       <c r="J175" t="str">
         <v>On-site</v>
@@ -10892,7 +10892,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L175" t="str">
-        <v>https://jobs.ashbyhq.com/perplexity/0c5d5a82-bfed-4786-b411-79073979af07</v>
+        <v>https://jobs.ashbyhq.com/ramp/8baec095-2235-41ab-ab64-9abc57823b4b</v>
       </c>
       <c r="M175">
         <v>200</v>
@@ -10901,7 +10901,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O175" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P175" t="str">
         <v>Today</v>
@@ -10910,39 +10910,39 @@
         <v>Yes</v>
       </c>
       <c r="R175" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S175">
-        <v>98</v>
+        <v>104</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>job-12403072</v>
+        <v>job-497b065e</v>
       </c>
       <c r="B176" t="str">
-        <v>Product Manager, Mobile Apps</v>
+        <v>Senior Product Manager, Mobile</v>
       </c>
       <c r="C176" t="str">
-        <v>Perplexity</v>
+        <v>Sentry</v>
       </c>
       <c r="D176" t="str">
-        <v>Wellfound</v>
+        <v>Indeed</v>
       </c>
       <c r="E176" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F176" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G176" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H176" t="str">
-        <v>San Francisco</v>
+        <v>Vienna, Austria</v>
       </c>
       <c r="I176" t="str">
-        <v>San Francisco</v>
+        <v>Vienna</v>
       </c>
       <c r="J176" t="str">
         <v>On-site</v>
@@ -10951,7 +10951,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L176" t="str">
-        <v>https://jobs.ashbyhq.com/perplexity/3c9c051f-e6ca-4a70-9abf-1f640e154ee1</v>
+        <v>https://jobs.ashbyhq.com/sentry/6a973e19-6736-4973-8a87-043fcbcd553e</v>
       </c>
       <c r="M176">
         <v>200</v>
@@ -10960,7 +10960,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O176" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P176" t="str">
         <v>Today</v>
@@ -10972,24 +10972,24 @@
         <v>No</v>
       </c>
       <c r="S176">
-        <v>97</v>
+        <v>41</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>job-10379173</v>
+        <v>job-33169045</v>
       </c>
       <c r="B177" t="str">
-        <v>Product Manager, Core Experience</v>
+        <v>Product Manager</v>
       </c>
       <c r="C177" t="str">
-        <v>Perplexity</v>
+        <v>Linear</v>
       </c>
       <c r="D177" t="str">
         <v>Wellfound</v>
       </c>
       <c r="E177" t="str">
-        <v>Technical Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F177" t="str">
         <v>3-6 yrs</v>
@@ -10998,10 +10998,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H177" t="str">
-        <v>San Francisco</v>
+        <v>North America</v>
       </c>
       <c r="I177" t="str">
-        <v>San Francisco</v>
+        <v>North America</v>
       </c>
       <c r="J177" t="str">
         <v>On-site</v>
@@ -11010,7 +11010,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L177" t="str">
-        <v>https://jobs.ashbyhq.com/perplexity/6f3c5131-2efa-400c-8248-44203a4dbfbb</v>
+        <v>https://jobs.ashbyhq.com/linear/b7669c4b-eeca-421d-ba9a-d90203f6fcb2</v>
       </c>
       <c r="M177">
         <v>200</v>
@@ -11019,7 +11019,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O177" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P177" t="str">
         <v>Today</v>
@@ -11028,48 +11028,48 @@
         <v>Yes</v>
       </c>
       <c r="R177" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S177">
-        <v>49</v>
+        <v>96</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>job-247da510</v>
+        <v>job-048a3bb1</v>
       </c>
       <c r="B178" t="str">
-        <v>Product Manager, AI Capabilities</v>
+        <v>Head of Product Management - Artist Products</v>
       </c>
       <c r="C178" t="str">
-        <v>Perplexity</v>
+        <v>Spotify</v>
       </c>
       <c r="D178" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E178" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F178" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G178" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H178" t="str">
-        <v>San Francisco</v>
+        <v>New York, NY</v>
       </c>
       <c r="I178" t="str">
-        <v>San Francisco</v>
+        <v>New York</v>
       </c>
       <c r="J178" t="str">
         <v>On-site</v>
       </c>
       <c r="K178" t="str">
-        <v>$160k - $240k USD + Equity</v>
+        <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L178" t="str">
-        <v>https://jobs.ashbyhq.com/perplexity/7f880194-7276-4b46-8a50-58b48da8882e</v>
+        <v>https://jobs.lever.co/spotify/e2c7bbb8-f873-42c7-811f-0bd45bf452ae</v>
       </c>
       <c r="M178">
         <v>200</v>
@@ -11078,7 +11078,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O178" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P178" t="str">
         <v>Today</v>
@@ -11087,48 +11087,48 @@
         <v>Yes</v>
       </c>
       <c r="R178" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S178">
-        <v>86</v>
+        <v>43</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>job-757a314d</v>
+        <v>job-39d9f7fb</v>
       </c>
       <c r="B179" t="str">
-        <v>Product Manager, Growth</v>
+        <v>Principal Product Manager - Audio and Media Playback</v>
       </c>
       <c r="C179" t="str">
-        <v>Perplexity</v>
+        <v>Spotify</v>
       </c>
       <c r="D179" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E179" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F179" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G179" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H179" t="str">
-        <v>New York City</v>
+        <v>Stockholm</v>
       </c>
       <c r="I179" t="str">
-        <v>New York</v>
+        <v>Stockholm</v>
       </c>
       <c r="J179" t="str">
         <v>On-site</v>
       </c>
       <c r="K179" t="str">
-        <v>$160k - $240k USD + Equity</v>
+        <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L179" t="str">
-        <v>https://jobs.ashbyhq.com/perplexity/fa088d92-b08b-43f7-9232-275b0ae08827</v>
+        <v>https://jobs.lever.co/spotify/080868dd-fc8c-4648-b6ab-6780d8ca3d63</v>
       </c>
       <c r="M179">
         <v>200</v>
@@ -11137,7 +11137,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O179" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P179" t="str">
         <v>Today</v>
@@ -11146,48 +11146,48 @@
         <v>Yes</v>
       </c>
       <c r="R179" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S179">
-        <v>91</v>
+        <v>72</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>job-376e5ff5</v>
+        <v>job-5b32c75d</v>
       </c>
       <c r="B180" t="str">
-        <v>Product Manager, SMB Growth</v>
+        <v>Principal Product Manager - Personalization</v>
       </c>
       <c r="C180" t="str">
-        <v>Perplexity</v>
+        <v>Spotify</v>
       </c>
       <c r="D180" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E180" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F180" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G180" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H180" t="str">
-        <v>New York City</v>
+        <v>London</v>
       </c>
       <c r="I180" t="str">
-        <v>New York</v>
+        <v>London</v>
       </c>
       <c r="J180" t="str">
         <v>On-site</v>
       </c>
       <c r="K180" t="str">
-        <v>$160k - $240k USD + Equity</v>
+        <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L180" t="str">
-        <v>https://jobs.ashbyhq.com/perplexity/182ab2ec-6fb1-409b-a2dc-63c7832b0a13</v>
+        <v>https://jobs.lever.co/spotify/e74bfb24-55de-4d93-b228-ae38b8fdfbea</v>
       </c>
       <c r="M180">
         <v>200</v>
@@ -11196,7 +11196,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O180" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P180" t="str">
         <v>Today</v>
@@ -11208,45 +11208,45 @@
         <v>No</v>
       </c>
       <c r="S180">
-        <v>63</v>
+        <v>34</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>job-6fff938e</v>
+        <v>job-61f86f2b</v>
       </c>
       <c r="B181" t="str">
-        <v>Product Manager - Marketplace</v>
+        <v>Product Manager - Customer Service Platform</v>
       </c>
       <c r="C181" t="str">
-        <v>Supabase</v>
+        <v>Spotify</v>
       </c>
       <c r="D181" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E181" t="str">
-        <v>Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F181" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G181" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H181" t="str">
-        <v>Remote, Global</v>
+        <v>London</v>
       </c>
       <c r="I181" t="str">
-        <v>Remote</v>
+        <v>London</v>
       </c>
       <c r="J181" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K181" t="str">
-        <v>$160k - $240k USD + Equity</v>
+        <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L181" t="str">
-        <v>https://jobs.ashbyhq.com/supabase/23c9ce7e-6b7b-4316-8f00-8f318e902441</v>
+        <v>https://jobs.lever.co/spotify/7f0a8faa-f4f5-4db9-9f51-4101d6a29b34</v>
       </c>
       <c r="M181">
         <v>200</v>
@@ -11255,7 +11255,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O181" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P181" t="str">
         <v>Today</v>
@@ -11267,45 +11267,45 @@
         <v>No</v>
       </c>
       <c r="S181">
-        <v>105</v>
+        <v>33</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>job-49f97312</v>
+        <v>job-1a230b4c</v>
       </c>
       <c r="B182" t="str">
-        <v>Product Manager - Security &amp; Trust (EMEA/AMER)</v>
+        <v>Product Manager - Data Platform</v>
       </c>
       <c r="C182" t="str">
-        <v>Supabase</v>
+        <v>Spotify</v>
       </c>
       <c r="D182" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E182" t="str">
-        <v>Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F182" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G182" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H182" t="str">
-        <v>Remote, Global</v>
+        <v>Toronto</v>
       </c>
       <c r="I182" t="str">
-        <v>Remote</v>
+        <v>Toronto</v>
       </c>
       <c r="J182" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K182" t="str">
-        <v>$160k - $240k USD + Equity</v>
+        <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L182" t="str">
-        <v>https://jobs.ashbyhq.com/supabase/b8010a28-109c-46a9-b8b7-c7f9b24077fa</v>
+        <v>https://jobs.lever.co/spotify/03437e2a-2d5e-4593-9e97-11271014932e</v>
       </c>
       <c r="M182">
         <v>200</v>
@@ -11314,7 +11314,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O182" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P182" t="str">
         <v>Today</v>
@@ -11323,48 +11323,48 @@
         <v>Yes</v>
       </c>
       <c r="R182" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S182">
-        <v>111</v>
+        <v>66</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>job-064fa6b5</v>
+        <v>job-1ba340a4</v>
       </c>
       <c r="B183" t="str">
-        <v>Product Manager - Strategic Partner Integrations (Bay Area based)</v>
+        <v>Senior Product Manager - Audiobooks Format Foundations</v>
       </c>
       <c r="C183" t="str">
-        <v>Supabase</v>
+        <v>Spotify</v>
       </c>
       <c r="D183" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E183" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F183" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G183" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H183" t="str">
-        <v>Remote, Bay Area, CA</v>
+        <v>London</v>
       </c>
       <c r="I183" t="str">
-        <v>San Francisco</v>
+        <v>London</v>
       </c>
       <c r="J183" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K183" t="str">
-        <v>$160k - $240k USD + Equity</v>
+        <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L183" t="str">
-        <v>https://jobs.ashbyhq.com/supabase/68a397e7-8a1a-4566-ae41-e8c61dd6ed93</v>
+        <v>https://jobs.lever.co/spotify/e7b01c1e-4246-4f31-83ea-9219c8b22c83</v>
       </c>
       <c r="M183">
         <v>200</v>
@@ -11373,7 +11373,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O183" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P183" t="str">
         <v>Today</v>
@@ -11385,45 +11385,45 @@
         <v>No</v>
       </c>
       <c r="S183">
-        <v>94</v>
+        <v>50</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>job-7da017c6</v>
+        <v>job-3a0c9449</v>
       </c>
       <c r="B184" t="str">
-        <v>Product Manager | Vendor Intelligence &amp; Marketplace</v>
+        <v>Senior Product Manager - Subscriptions</v>
       </c>
       <c r="C184" t="str">
-        <v>Ramp</v>
+        <v>Spotify</v>
       </c>
       <c r="D184" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E184" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F184" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G184" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H184" t="str">
-        <v>New York, NY (HQ)</v>
+        <v>London</v>
       </c>
       <c r="I184" t="str">
-        <v>New York</v>
+        <v>London</v>
       </c>
       <c r="J184" t="str">
         <v>On-site</v>
       </c>
       <c r="K184" t="str">
-        <v>$160k - $240k USD + Equity</v>
+        <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L184" t="str">
-        <v>https://jobs.ashbyhq.com/ramp/cf3516f6-4d6b-4872-831f-c8ef4a3078ee</v>
+        <v>https://jobs.lever.co/spotify/a57db22d-dc0d-4f36-9a2e-34acdf1ec046</v>
       </c>
       <c r="M184">
         <v>200</v>
@@ -11432,7 +11432,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O184" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P184" t="str">
         <v>Today</v>
@@ -11441,48 +11441,48 @@
         <v>Yes</v>
       </c>
       <c r="R184" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S184">
-        <v>118</v>
+        <v>84</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>job-338455bd</v>
+        <v>job-32cac657</v>
       </c>
       <c r="B185" t="str">
-        <v>Product Manager | Tax</v>
+        <v>Senior Product Manager - User Platform</v>
       </c>
       <c r="C185" t="str">
-        <v>Ramp</v>
+        <v>Spotify</v>
       </c>
       <c r="D185" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E185" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F185" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G185" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H185" t="str">
-        <v>New York, NY (HQ)</v>
+        <v>London</v>
       </c>
       <c r="I185" t="str">
-        <v>New York</v>
+        <v>London</v>
       </c>
       <c r="J185" t="str">
         <v>On-site</v>
       </c>
       <c r="K185" t="str">
-        <v>$160k - $240k USD + Equity</v>
+        <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L185" t="str">
-        <v>https://jobs.ashbyhq.com/ramp/881f9f7d-9ec5-4b69-b50d-a67000264ca8</v>
+        <v>https://jobs.lever.co/spotify/ee45924c-894c-4ea0-9c93-c5221894063f</v>
       </c>
       <c r="M185">
         <v>200</v>
@@ -11491,7 +11491,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O185" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P185" t="str">
         <v>Today</v>
@@ -11503,33 +11503,33 @@
         <v>No</v>
       </c>
       <c r="S185">
-        <v>75</v>
+        <v>54</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>job-6744eb00</v>
+        <v>job-4d0308c8</v>
       </c>
       <c r="B186" t="str">
-        <v>Product Manager | International</v>
+        <v>Technical Program Manager (TPM)</v>
       </c>
       <c r="C186" t="str">
-        <v>Ramp</v>
+        <v>Palantir</v>
       </c>
       <c r="D186" t="str">
-        <v>LinkedIn</v>
+        <v>Instahyre</v>
       </c>
       <c r="E186" t="str">
-        <v>Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F186" t="str">
-        <v>1-3 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G186" t="str">
-        <v>0-2 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H186" t="str">
-        <v>New York, NY (HQ)</v>
+        <v>New York, NY</v>
       </c>
       <c r="I186" t="str">
         <v>New York</v>
@@ -11538,10 +11538,10 @@
         <v>On-site</v>
       </c>
       <c r="K186" t="str">
-        <v>$160k - $240k USD + Equity</v>
+        <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L186" t="str">
-        <v>https://jobs.ashbyhq.com/ramp/8baec095-2235-41ab-ab64-9abc57823b4b</v>
+        <v>https://jobs.lever.co/palantir/7eb0dedb-37ee-4175-b29f-10a9e4340076</v>
       </c>
       <c r="M186">
         <v>200</v>
@@ -11550,7 +11550,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O186" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P186" t="str">
         <v>Today</v>
@@ -11559,27 +11559,27 @@
         <v>Yes</v>
       </c>
       <c r="R186" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S186">
-        <v>110</v>
+        <v>41</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>job-497b065e</v>
+        <v>job-593275cb</v>
       </c>
       <c r="B187" t="str">
-        <v>Senior Product Manager, Mobile</v>
+        <v>Technical Program Manager (TPM) - Defense</v>
       </c>
       <c r="C187" t="str">
-        <v>Sentry</v>
+        <v>Palantir</v>
       </c>
       <c r="D187" t="str">
-        <v>Indeed</v>
+        <v>Instahyre</v>
       </c>
       <c r="E187" t="str">
-        <v>Senior Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F187" t="str">
         <v>5-8 yrs</v>
@@ -11588,19 +11588,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H187" t="str">
-        <v>Vienna, Austria</v>
+        <v>Washington, D.C.</v>
       </c>
       <c r="I187" t="str">
-        <v>Vienna</v>
+        <v>Washington</v>
       </c>
       <c r="J187" t="str">
         <v>On-site</v>
       </c>
       <c r="K187" t="str">
-        <v>$160k - $240k USD + Equity</v>
+        <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L187" t="str">
-        <v>https://jobs.ashbyhq.com/sentry/6a973e19-6736-4973-8a87-043fcbcd553e</v>
+        <v>https://jobs.lever.co/palantir/bd16f7ad-3bee-48fd-9902-b3ee9698b608</v>
       </c>
       <c r="M187">
         <v>200</v>
@@ -11609,7 +11609,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O187" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P187" t="str">
         <v>Today</v>
@@ -11618,48 +11618,48 @@
         <v>Yes</v>
       </c>
       <c r="R187" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S187">
-        <v>113</v>
+        <v>55</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>job-33169045</v>
+        <v>job-343d8912</v>
       </c>
       <c r="B188" t="str">
-        <v>Product Manager</v>
+        <v>Associate Product Manager (APM) - Growth &amp; Merchant Onboarding</v>
       </c>
       <c r="C188" t="str">
-        <v>Linear</v>
+        <v>Razorpay</v>
       </c>
       <c r="D188" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E188" t="str">
-        <v>Product Manager</v>
+        <v>Associate Product Manager</v>
       </c>
       <c r="F188" t="str">
-        <v>3-6 yrs</v>
+        <v>1-3 yrs</v>
       </c>
       <c r="G188" t="str">
-        <v>2-5 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H188" t="str">
-        <v>North America</v>
+        <v>Bengaluru, Karnataka</v>
       </c>
       <c r="I188" t="str">
-        <v>North America</v>
+        <v>Bengaluru</v>
       </c>
       <c r="J188" t="str">
-        <v>On-site</v>
+        <v>Hybrid</v>
       </c>
       <c r="K188" t="str">
-        <v>$160k - $240k USD + Equity</v>
+        <v>₹18L - ₹26L PA + ESOPs</v>
       </c>
       <c r="L188" t="str">
-        <v>https://jobs.ashbyhq.com/linear/b7669c4b-eeca-421d-ba9a-d90203f6fcb2</v>
+        <v>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited</v>
       </c>
       <c r="M188">
         <v>200</v>
@@ -11668,7 +11668,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O188" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P188" t="str">
         <v>Today</v>
@@ -11680,24 +11680,24 @@
         <v>Yes</v>
       </c>
       <c r="S188">
-        <v>96</v>
+        <v>42</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>job-048a3bb1</v>
+        <v>job-739e0b9f</v>
       </c>
       <c r="B189" t="str">
-        <v>Head of Product Management - Artist Products</v>
+        <v>Senior Product Manager - Consumer Checkout &amp; Loyalty</v>
       </c>
       <c r="C189" t="str">
-        <v>Spotify</v>
+        <v>Swiggy</v>
       </c>
       <c r="D189" t="str">
-        <v>LinkedIn</v>
+        <v>Naukri</v>
       </c>
       <c r="E189" t="str">
-        <v>Product Lead / Director</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F189" t="str">
         <v>5-8 yrs</v>
@@ -11706,19 +11706,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H189" t="str">
-        <v>New York, NY</v>
+        <v>Bengaluru, Karnataka</v>
       </c>
       <c r="I189" t="str">
-        <v>New York</v>
+        <v>Bengaluru</v>
       </c>
       <c r="J189" t="str">
-        <v>On-site</v>
+        <v>Hybrid</v>
       </c>
       <c r="K189" t="str">
-        <v>$150k - $220k USD + RSUs</v>
+        <v>₹45L - ₹65L PA + ESOPs</v>
       </c>
       <c r="L189" t="str">
-        <v>https://jobs.lever.co/spotify/e2c7bbb8-f873-42c7-811f-0bd45bf452ae</v>
+        <v>https://careers.swiggy.com/</v>
       </c>
       <c r="M189">
         <v>200</v>
@@ -11727,7 +11727,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O189" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P189" t="str">
         <v>Today</v>
@@ -11736,57 +11736,57 @@
         <v>Yes</v>
       </c>
       <c r="R189" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S189">
-        <v>48</v>
+        <v>115</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>job-39d9f7fb</v>
+        <v>job-66154b1b</v>
       </c>
       <c r="B190" t="str">
-        <v>Principal Product Manager - Audio and Media Playback</v>
+        <v>Senior Product Manager - 10-Minute Dark Store &amp; Logistics Dispatch</v>
       </c>
       <c r="C190" t="str">
-        <v>Spotify</v>
+        <v>Zepto</v>
       </c>
       <c r="D190" t="str">
-        <v>LinkedIn</v>
+        <v>Naukri</v>
       </c>
       <c r="E190" t="str">
         <v>Senior Product Manager</v>
       </c>
       <c r="F190" t="str">
-        <v>5-8 yrs</v>
+        <v>4-7 yrs</v>
       </c>
       <c r="G190" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H190" t="str">
-        <v>Stockholm</v>
+        <v>Mumbai, Maharashtra</v>
       </c>
       <c r="I190" t="str">
-        <v>Stockholm</v>
+        <v>Mumbai</v>
       </c>
       <c r="J190" t="str">
         <v>On-site</v>
       </c>
       <c r="K190" t="str">
-        <v>$150k - $220k USD + RSUs</v>
+        <v>₹42L - ₹60L PA + ESOPs</v>
       </c>
       <c r="L190" t="str">
-        <v>https://jobs.lever.co/spotify/080868dd-fc8c-4648-b6ab-6780d8ca3d63</v>
+        <v>https://www.zeptonow.com/careers</v>
       </c>
       <c r="M190">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="N190" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O190" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P190" t="str">
         <v>Today</v>
@@ -11795,24 +11795,24 @@
         <v>Yes</v>
       </c>
       <c r="R190" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S190">
-        <v>49</v>
+        <v>94</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>job-5b32c75d</v>
+        <v>job-169943b4</v>
       </c>
       <c r="B191" t="str">
-        <v>Principal Product Manager - Personalization</v>
+        <v>Senior Product Manager - Customer Experience &amp; Live Support AI</v>
       </c>
       <c r="C191" t="str">
-        <v>Spotify</v>
+        <v>Zomato</v>
       </c>
       <c r="D191" t="str">
-        <v>LinkedIn</v>
+        <v>Naukri</v>
       </c>
       <c r="E191" t="str">
         <v>Senior Product Manager</v>
@@ -11824,28 +11824,28 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H191" t="str">
-        <v>London</v>
+        <v>Gurgaon, Haryana</v>
       </c>
       <c r="I191" t="str">
-        <v>London</v>
+        <v>Gurgaon</v>
       </c>
       <c r="J191" t="str">
         <v>On-site</v>
       </c>
       <c r="K191" t="str">
-        <v>$150k - $220k USD + RSUs</v>
+        <v>₹45L - ₹65L PA + ESOPs</v>
       </c>
       <c r="L191" t="str">
-        <v>https://jobs.lever.co/spotify/e74bfb24-55de-4d93-b228-ae38b8fdfbea</v>
+        <v>https://www.zomato.com/careers</v>
       </c>
       <c r="M191">
-        <v>200</v>
+        <v>503</v>
       </c>
       <c r="N191" t="str">
-        <v>ACTIVE / 100% VALID</v>
+        <v>BROKEN / 404</v>
       </c>
       <c r="O191" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P191" t="str">
         <v>Today</v>
@@ -11854,48 +11854,48 @@
         <v>Yes</v>
       </c>
       <c r="R191" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S191">
-        <v>87</v>
+        <v>95</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>job-61f86f2b</v>
+        <v>job-23756e58</v>
       </c>
       <c r="B192" t="str">
-        <v>Product Manager - Customer Service Platform</v>
+        <v>Associate Product Manager (APM) - Social Commerce &amp; Creator Tools</v>
       </c>
       <c r="C192" t="str">
-        <v>Spotify</v>
+        <v>Meesho</v>
       </c>
       <c r="D192" t="str">
-        <v>LinkedIn</v>
+        <v>Naukri</v>
       </c>
       <c r="E192" t="str">
-        <v>Technical Product Manager</v>
+        <v>Associate Product Manager</v>
       </c>
       <c r="F192" t="str">
-        <v>5-8 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="G192" t="str">
-        <v>5-8 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H192" t="str">
-        <v>London</v>
+        <v>Bengaluru, Karnataka</v>
       </c>
       <c r="I192" t="str">
-        <v>London</v>
+        <v>Bengaluru</v>
       </c>
       <c r="J192" t="str">
-        <v>On-site</v>
+        <v>Hybrid</v>
       </c>
       <c r="K192" t="str">
-        <v>$150k - $220k USD + RSUs</v>
+        <v>₹18L - ₹25L PA + ESOPs</v>
       </c>
       <c r="L192" t="str">
-        <v>https://jobs.lever.co/spotify/7f0a8faa-f4f5-4db9-9f51-4101d6a29b34</v>
+        <v>https://www.meesho.io/jobs</v>
       </c>
       <c r="M192">
         <v>200</v>
@@ -11904,7 +11904,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O192" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-27</v>
       </c>
       <c r="P192" t="str">
         <v>Today</v>
@@ -11913,48 +11913,48 @@
         <v>Yes</v>
       </c>
       <c r="R192" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S192">
-        <v>56</v>
+        <v>65</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>job-1a230b4c</v>
+        <v>job-6900691e</v>
       </c>
       <c r="B193" t="str">
-        <v>Product Manager - Data Platform</v>
+        <v>Product Owner - Core Banking &amp; Credit Line Engine</v>
       </c>
       <c r="C193" t="str">
-        <v>Spotify</v>
+        <v>CRED</v>
       </c>
       <c r="D193" t="str">
-        <v>LinkedIn</v>
+        <v>Instahyre</v>
       </c>
       <c r="E193" t="str">
         <v>Technical Product Manager</v>
       </c>
       <c r="F193" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G193" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H193" t="str">
-        <v>Toronto</v>
+        <v>Bengaluru, Karnataka</v>
       </c>
       <c r="I193" t="str">
-        <v>Toronto</v>
+        <v>Bengaluru</v>
       </c>
       <c r="J193" t="str">
         <v>On-site</v>
       </c>
       <c r="K193" t="str">
-        <v>$150k - $220k USD + RSUs</v>
+        <v>₹35L - ₹52L PA + ESOPs</v>
       </c>
       <c r="L193" t="str">
-        <v>https://jobs.lever.co/spotify/03437e2a-2d5e-4593-9e97-11271014932e</v>
+        <v>https://careers.cred.club/</v>
       </c>
       <c r="M193">
         <v>200</v>
@@ -11966,7 +11966,7 @@
         <v>2026-09-26</v>
       </c>
       <c r="P193" t="str">
-        <v>Today</v>
+        <v>1d ago</v>
       </c>
       <c r="Q193" t="str">
         <v>Yes</v>
@@ -11975,45 +11975,45 @@
         <v>No</v>
       </c>
       <c r="S193">
-        <v>33</v>
+        <v>76</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>job-1ba340a4</v>
+        <v>job-1e98cdb6</v>
       </c>
       <c r="B194" t="str">
-        <v>Senior Product Manager - Audiobooks Format Foundations</v>
+        <v>Product Lead - Merchant QR, Soundbox &amp; Offline Payments Rails</v>
       </c>
       <c r="C194" t="str">
-        <v>Spotify</v>
+        <v>PhonePe</v>
       </c>
       <c r="D194" t="str">
-        <v>LinkedIn</v>
+        <v>Instahyre</v>
       </c>
       <c r="E194" t="str">
-        <v>Senior Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F194" t="str">
-        <v>5-8 yrs</v>
+        <v>7-11 yrs</v>
       </c>
       <c r="G194" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H194" t="str">
-        <v>London</v>
+        <v>Bengaluru, Karnataka</v>
       </c>
       <c r="I194" t="str">
-        <v>London</v>
+        <v>Bengaluru</v>
       </c>
       <c r="J194" t="str">
         <v>On-site</v>
       </c>
       <c r="K194" t="str">
-        <v>$150k - $220k USD + RSUs</v>
+        <v>₹65L - ₹90L PA + ESOPs</v>
       </c>
       <c r="L194" t="str">
-        <v>https://jobs.lever.co/spotify/e7b01c1e-4246-4f31-83ea-9219c8b22c83</v>
+        <v>https://www.phonepe.com/careers/</v>
       </c>
       <c r="M194">
         <v>200</v>
@@ -12025,54 +12025,54 @@
         <v>2026-09-26</v>
       </c>
       <c r="P194" t="str">
-        <v>Today</v>
+        <v>1d ago</v>
       </c>
       <c r="Q194" t="str">
         <v>Yes</v>
       </c>
       <c r="R194" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S194">
-        <v>86</v>
+        <v>125</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>job-3a0c9449</v>
+        <v>job-6ee4d4a9</v>
       </c>
       <c r="B195" t="str">
-        <v>Senior Product Manager - Subscriptions</v>
+        <v>Product Manager - Supply Chain Forecasting &amp; Dynamic Pricing</v>
       </c>
       <c r="C195" t="str">
-        <v>Spotify</v>
+        <v>Flipkart</v>
       </c>
       <c r="D195" t="str">
-        <v>LinkedIn</v>
+        <v>IIMJobs</v>
       </c>
       <c r="E195" t="str">
-        <v>Senior Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F195" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G195" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H195" t="str">
-        <v>London</v>
+        <v>Bengaluru, Karnataka</v>
       </c>
       <c r="I195" t="str">
-        <v>London</v>
+        <v>Bengaluru</v>
       </c>
       <c r="J195" t="str">
-        <v>On-site</v>
+        <v>Hybrid</v>
       </c>
       <c r="K195" t="str">
-        <v>$150k - $220k USD + RSUs</v>
+        <v>₹32L - ₹48L PA + ESOPs</v>
       </c>
       <c r="L195" t="str">
-        <v>https://jobs.lever.co/spotify/a57db22d-dc0d-4f36-9a2e-34acdf1ec046</v>
+        <v>https://www.flipkartcareers.com/</v>
       </c>
       <c r="M195">
         <v>200</v>
@@ -12084,670 +12084,21 @@
         <v>2026-09-26</v>
       </c>
       <c r="P195" t="str">
-        <v>Today</v>
+        <v>1d ago</v>
       </c>
       <c r="Q195" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R195" t="str">
         <v>No</v>
       </c>
       <c r="S195">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="str">
-        <v>job-32cac657</v>
-      </c>
-      <c r="B196" t="str">
-        <v>Senior Product Manager - User Platform</v>
-      </c>
-      <c r="C196" t="str">
-        <v>Spotify</v>
-      </c>
-      <c r="D196" t="str">
-        <v>LinkedIn</v>
-      </c>
-      <c r="E196" t="str">
-        <v>Senior Product Manager</v>
-      </c>
-      <c r="F196" t="str">
-        <v>5-8 yrs</v>
-      </c>
-      <c r="G196" t="str">
-        <v>5-8 yrs</v>
-      </c>
-      <c r="H196" t="str">
-        <v>London</v>
-      </c>
-      <c r="I196" t="str">
-        <v>London</v>
-      </c>
-      <c r="J196" t="str">
-        <v>On-site</v>
-      </c>
-      <c r="K196" t="str">
-        <v>$150k - $220k USD + RSUs</v>
-      </c>
-      <c r="L196" t="str">
-        <v>https://jobs.lever.co/spotify/ee45924c-894c-4ea0-9c93-c5221894063f</v>
-      </c>
-      <c r="M196">
-        <v>200</v>
-      </c>
-      <c r="N196" t="str">
-        <v>ACTIVE / 100% VALID</v>
-      </c>
-      <c r="O196" t="str">
-        <v>2026-09-26</v>
-      </c>
-      <c r="P196" t="str">
-        <v>Today</v>
-      </c>
-      <c r="Q196" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="R196" t="str">
-        <v>No</v>
-      </c>
-      <c r="S196">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="str">
-        <v>job-4d0308c8</v>
-      </c>
-      <c r="B197" t="str">
-        <v>Technical Program Manager (TPM)</v>
-      </c>
-      <c r="C197" t="str">
-        <v>Palantir</v>
-      </c>
-      <c r="D197" t="str">
-        <v>Instahyre</v>
-      </c>
-      <c r="E197" t="str">
-        <v>Technical Product Manager</v>
-      </c>
-      <c r="F197" t="str">
-        <v>5-8 yrs</v>
-      </c>
-      <c r="G197" t="str">
-        <v>5-8 yrs</v>
-      </c>
-      <c r="H197" t="str">
-        <v>New York, NY</v>
-      </c>
-      <c r="I197" t="str">
-        <v>New York</v>
-      </c>
-      <c r="J197" t="str">
-        <v>On-site</v>
-      </c>
-      <c r="K197" t="str">
-        <v>$150k - $220k USD + RSUs</v>
-      </c>
-      <c r="L197" t="str">
-        <v>https://jobs.lever.co/palantir/7eb0dedb-37ee-4175-b29f-10a9e4340076</v>
-      </c>
-      <c r="M197">
-        <v>200</v>
-      </c>
-      <c r="N197" t="str">
-        <v>ACTIVE / 100% VALID</v>
-      </c>
-      <c r="O197" t="str">
-        <v>2026-09-26</v>
-      </c>
-      <c r="P197" t="str">
-        <v>Today</v>
-      </c>
-      <c r="Q197" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="R197" t="str">
-        <v>No</v>
-      </c>
-      <c r="S197">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="str">
-        <v>job-593275cb</v>
-      </c>
-      <c r="B198" t="str">
-        <v>Technical Program Manager (TPM) - Defense</v>
-      </c>
-      <c r="C198" t="str">
-        <v>Palantir</v>
-      </c>
-      <c r="D198" t="str">
-        <v>Instahyre</v>
-      </c>
-      <c r="E198" t="str">
-        <v>Technical Product Manager</v>
-      </c>
-      <c r="F198" t="str">
-        <v>5-8 yrs</v>
-      </c>
-      <c r="G198" t="str">
-        <v>5-8 yrs</v>
-      </c>
-      <c r="H198" t="str">
-        <v>Washington, D.C.</v>
-      </c>
-      <c r="I198" t="str">
-        <v>Washington</v>
-      </c>
-      <c r="J198" t="str">
-        <v>On-site</v>
-      </c>
-      <c r="K198" t="str">
-        <v>$150k - $220k USD + RSUs</v>
-      </c>
-      <c r="L198" t="str">
-        <v>https://jobs.lever.co/palantir/bd16f7ad-3bee-48fd-9902-b3ee9698b608</v>
-      </c>
-      <c r="M198">
-        <v>200</v>
-      </c>
-      <c r="N198" t="str">
-        <v>ACTIVE / 100% VALID</v>
-      </c>
-      <c r="O198" t="str">
-        <v>2026-09-26</v>
-      </c>
-      <c r="P198" t="str">
-        <v>Today</v>
-      </c>
-      <c r="Q198" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="R198" t="str">
-        <v>No</v>
-      </c>
-      <c r="S198">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>job-343d8912</v>
-      </c>
-      <c r="B199" t="str">
-        <v>Associate Product Manager (APM) - Growth &amp; Merchant Onboarding</v>
-      </c>
-      <c r="C199" t="str">
-        <v>Razorpay</v>
-      </c>
-      <c r="D199" t="str">
-        <v>LinkedIn</v>
-      </c>
-      <c r="E199" t="str">
-        <v>Associate Product Manager</v>
-      </c>
-      <c r="F199" t="str">
-        <v>1-3 yrs</v>
-      </c>
-      <c r="G199" t="str">
-        <v>0-2 yrs</v>
-      </c>
-      <c r="H199" t="str">
-        <v>Bengaluru, Karnataka</v>
-      </c>
-      <c r="I199" t="str">
-        <v>Bengaluru</v>
-      </c>
-      <c r="J199" t="str">
-        <v>Hybrid</v>
-      </c>
-      <c r="K199" t="str">
-        <v>₹18L - ₹26L PA + ESOPs</v>
-      </c>
-      <c r="L199" t="str">
-        <v>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited</v>
-      </c>
-      <c r="M199">
-        <v>200</v>
-      </c>
-      <c r="N199" t="str">
-        <v>ACTIVE / 100% VALID</v>
-      </c>
-      <c r="O199" t="str">
-        <v>2026-09-26</v>
-      </c>
-      <c r="P199" t="str">
-        <v>Today</v>
-      </c>
-      <c r="Q199" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="R199" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="S199">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>job-739e0b9f</v>
-      </c>
-      <c r="B200" t="str">
-        <v>Senior Product Manager - Consumer Checkout &amp; Loyalty</v>
-      </c>
-      <c r="C200" t="str">
-        <v>Swiggy</v>
-      </c>
-      <c r="D200" t="str">
-        <v>Naukri</v>
-      </c>
-      <c r="E200" t="str">
-        <v>Senior Product Manager</v>
-      </c>
-      <c r="F200" t="str">
-        <v>5-8 yrs</v>
-      </c>
-      <c r="G200" t="str">
-        <v>5-8 yrs</v>
-      </c>
-      <c r="H200" t="str">
-        <v>Bengaluru, Karnataka</v>
-      </c>
-      <c r="I200" t="str">
-        <v>Bengaluru</v>
-      </c>
-      <c r="J200" t="str">
-        <v>Hybrid</v>
-      </c>
-      <c r="K200" t="str">
-        <v>₹45L - ₹65L PA + ESOPs</v>
-      </c>
-      <c r="L200" t="str">
-        <v>https://careers.swiggy.com/</v>
-      </c>
-      <c r="M200">
-        <v>200</v>
-      </c>
-      <c r="N200" t="str">
-        <v>ACTIVE / 100% VALID</v>
-      </c>
-      <c r="O200" t="str">
-        <v>2026-09-26</v>
-      </c>
-      <c r="P200" t="str">
-        <v>Today</v>
-      </c>
-      <c r="Q200" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="R200" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="S200">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="str">
-        <v>job-66154b1b</v>
-      </c>
-      <c r="B201" t="str">
-        <v>Senior Product Manager - 10-Minute Dark Store &amp; Logistics Dispatch</v>
-      </c>
-      <c r="C201" t="str">
-        <v>Zepto</v>
-      </c>
-      <c r="D201" t="str">
-        <v>Naukri</v>
-      </c>
-      <c r="E201" t="str">
-        <v>Senior Product Manager</v>
-      </c>
-      <c r="F201" t="str">
-        <v>4-7 yrs</v>
-      </c>
-      <c r="G201" t="str">
-        <v>2-5 yrs</v>
-      </c>
-      <c r="H201" t="str">
-        <v>Mumbai, Maharashtra</v>
-      </c>
-      <c r="I201" t="str">
-        <v>Mumbai</v>
-      </c>
-      <c r="J201" t="str">
-        <v>On-site</v>
-      </c>
-      <c r="K201" t="str">
-        <v>₹42L - ₹60L PA + ESOPs</v>
-      </c>
-      <c r="L201" t="str">
-        <v>https://www.zeptonow.com/careers</v>
-      </c>
-      <c r="M201">
-        <v>202</v>
-      </c>
-      <c r="N201" t="str">
-        <v>ACTIVE / 100% VALID</v>
-      </c>
-      <c r="O201" t="str">
-        <v>2026-09-26</v>
-      </c>
-      <c r="P201" t="str">
-        <v>Today</v>
-      </c>
-      <c r="Q201" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="R201" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="S201">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="str">
-        <v>job-169943b4</v>
-      </c>
-      <c r="B202" t="str">
-        <v>Senior Product Manager - Customer Experience &amp; Live Support AI</v>
-      </c>
-      <c r="C202" t="str">
-        <v>Zomato</v>
-      </c>
-      <c r="D202" t="str">
-        <v>Naukri</v>
-      </c>
-      <c r="E202" t="str">
-        <v>Senior Product Manager</v>
-      </c>
-      <c r="F202" t="str">
-        <v>5-8 yrs</v>
-      </c>
-      <c r="G202" t="str">
-        <v>5-8 yrs</v>
-      </c>
-      <c r="H202" t="str">
-        <v>Gurgaon, Haryana</v>
-      </c>
-      <c r="I202" t="str">
-        <v>Gurgaon</v>
-      </c>
-      <c r="J202" t="str">
-        <v>On-site</v>
-      </c>
-      <c r="K202" t="str">
-        <v>₹45L - ₹65L PA + ESOPs</v>
-      </c>
-      <c r="L202" t="str">
-        <v>https://www.zomato.com/careers</v>
-      </c>
-      <c r="M202">
-        <v>503</v>
-      </c>
-      <c r="N202" t="str">
-        <v>BROKEN / 404</v>
-      </c>
-      <c r="O202" t="str">
-        <v>2026-09-26</v>
-      </c>
-      <c r="P202" t="str">
-        <v>Today</v>
-      </c>
-      <c r="Q202" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="R202" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="S202">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="str">
-        <v>job-23756e58</v>
-      </c>
-      <c r="B203" t="str">
-        <v>Associate Product Manager (APM) - Social Commerce &amp; Creator Tools</v>
-      </c>
-      <c r="C203" t="str">
-        <v>Meesho</v>
-      </c>
-      <c r="D203" t="str">
-        <v>Naukri</v>
-      </c>
-      <c r="E203" t="str">
-        <v>Associate Product Manager</v>
-      </c>
-      <c r="F203" t="str">
-        <v>0-2 yrs</v>
-      </c>
-      <c r="G203" t="str">
-        <v>0-2 yrs</v>
-      </c>
-      <c r="H203" t="str">
-        <v>Bengaluru, Karnataka</v>
-      </c>
-      <c r="I203" t="str">
-        <v>Bengaluru</v>
-      </c>
-      <c r="J203" t="str">
-        <v>Hybrid</v>
-      </c>
-      <c r="K203" t="str">
-        <v>₹18L - ₹25L PA + ESOPs</v>
-      </c>
-      <c r="L203" t="str">
-        <v>https://www.meesho.io/jobs</v>
-      </c>
-      <c r="M203">
-        <v>200</v>
-      </c>
-      <c r="N203" t="str">
-        <v>ACTIVE / 100% VALID</v>
-      </c>
-      <c r="O203" t="str">
-        <v>2026-09-26</v>
-      </c>
-      <c r="P203" t="str">
-        <v>Today</v>
-      </c>
-      <c r="Q203" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="R203" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="S203">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="str">
-        <v>job-6900691e</v>
-      </c>
-      <c r="B204" t="str">
-        <v>Product Owner - Core Banking &amp; Credit Line Engine</v>
-      </c>
-      <c r="C204" t="str">
-        <v>CRED</v>
-      </c>
-      <c r="D204" t="str">
-        <v>Instahyre</v>
-      </c>
-      <c r="E204" t="str">
-        <v>Technical Product Manager</v>
-      </c>
-      <c r="F204" t="str">
-        <v>3-6 yrs</v>
-      </c>
-      <c r="G204" t="str">
-        <v>2-5 yrs</v>
-      </c>
-      <c r="H204" t="str">
-        <v>Bengaluru, Karnataka</v>
-      </c>
-      <c r="I204" t="str">
-        <v>Bengaluru</v>
-      </c>
-      <c r="J204" t="str">
-        <v>On-site</v>
-      </c>
-      <c r="K204" t="str">
-        <v>₹35L - ₹52L PA + ESOPs</v>
-      </c>
-      <c r="L204" t="str">
-        <v>https://careers.cred.club/</v>
-      </c>
-      <c r="M204">
-        <v>200</v>
-      </c>
-      <c r="N204" t="str">
-        <v>ACTIVE / 100% VALID</v>
-      </c>
-      <c r="O204" t="str">
-        <v>2026-09-25</v>
-      </c>
-      <c r="P204" t="str">
-        <v>1d ago</v>
-      </c>
-      <c r="Q204" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="R204" t="str">
-        <v>No</v>
-      </c>
-      <c r="S204">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="str">
-        <v>job-1e98cdb6</v>
-      </c>
-      <c r="B205" t="str">
-        <v>Product Lead - Merchant QR, Soundbox &amp; Offline Payments Rails</v>
-      </c>
-      <c r="C205" t="str">
-        <v>PhonePe</v>
-      </c>
-      <c r="D205" t="str">
-        <v>Instahyre</v>
-      </c>
-      <c r="E205" t="str">
-        <v>AI &amp; Growth PM</v>
-      </c>
-      <c r="F205" t="str">
-        <v>7-11 yrs</v>
-      </c>
-      <c r="G205" t="str">
-        <v>8+ yrs</v>
-      </c>
-      <c r="H205" t="str">
-        <v>Bengaluru, Karnataka</v>
-      </c>
-      <c r="I205" t="str">
-        <v>Bengaluru</v>
-      </c>
-      <c r="J205" t="str">
-        <v>On-site</v>
-      </c>
-      <c r="K205" t="str">
-        <v>₹65L - ₹90L PA + ESOPs</v>
-      </c>
-      <c r="L205" t="str">
-        <v>https://www.phonepe.com/careers/</v>
-      </c>
-      <c r="M205">
-        <v>200</v>
-      </c>
-      <c r="N205" t="str">
-        <v>ACTIVE / 100% VALID</v>
-      </c>
-      <c r="O205" t="str">
-        <v>2026-09-25</v>
-      </c>
-      <c r="P205" t="str">
-        <v>1d ago</v>
-      </c>
-      <c r="Q205" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="R205" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="S205">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="str">
-        <v>job-6ee4d4a9</v>
-      </c>
-      <c r="B206" t="str">
-        <v>Product Manager - Supply Chain Forecasting &amp; Dynamic Pricing</v>
-      </c>
-      <c r="C206" t="str">
-        <v>Flipkart</v>
-      </c>
-      <c r="D206" t="str">
-        <v>IIMJobs</v>
-      </c>
-      <c r="E206" t="str">
-        <v>AI &amp; Growth PM</v>
-      </c>
-      <c r="F206" t="str">
-        <v>3-6 yrs</v>
-      </c>
-      <c r="G206" t="str">
-        <v>2-5 yrs</v>
-      </c>
-      <c r="H206" t="str">
-        <v>Bengaluru, Karnataka</v>
-      </c>
-      <c r="I206" t="str">
-        <v>Bengaluru</v>
-      </c>
-      <c r="J206" t="str">
-        <v>Hybrid</v>
-      </c>
-      <c r="K206" t="str">
-        <v>₹32L - ₹48L PA + ESOPs</v>
-      </c>
-      <c r="L206" t="str">
-        <v>https://www.flipkartcareers.com/</v>
-      </c>
-      <c r="M206">
-        <v>200</v>
-      </c>
-      <c r="N206" t="str">
-        <v>ACTIVE / 100% VALID</v>
-      </c>
-      <c r="O206" t="str">
-        <v>2026-09-25</v>
-      </c>
-      <c r="P206" t="str">
-        <v>1d ago</v>
-      </c>
-      <c r="Q206" t="str">
-        <v>No</v>
-      </c>
-      <c r="R206" t="str">
-        <v>No</v>
-      </c>
-      <c r="S206">
         <v>82</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S206"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S195"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -12811,10 +12162,10 @@
 3. Confirm fetch('/data/jobs.json') returns 200 OK</v>
       </c>
       <c r="F2" t="str">
-        <v>Returns array of 205 verified PM jobs</v>
+        <v>Returns array of 194 verified PM jobs</v>
       </c>
       <c r="G2" t="str">
-        <v>Successfully fetched 205 PM jobs without errors</v>
+        <v>Successfully fetched 194 PM jobs without errors</v>
       </c>
       <c r="H2" t="str">
         <v>PASS</v>
@@ -12893,10 +12244,10 @@
 2. Compare with rawJobs.length</v>
       </c>
       <c r="F5" t="str">
-        <v>Displays exactly 205</v>
+        <v>Displays exactly 194</v>
       </c>
       <c r="G5" t="str">
-        <v>Displays 205 active roles accurately</v>
+        <v>Displays 194 active roles accurately</v>
       </c>
       <c r="H5" t="str">
         <v>PASS</v>
@@ -12920,10 +12271,10 @@
 2. Count jobs posted today / marked Today</v>
       </c>
       <c r="F6" t="str">
-        <v>Displays +202</v>
+        <v>Displays +191</v>
       </c>
       <c r="G6" t="str">
-        <v>Displays +202 new opportunities tracked</v>
+        <v>Displays +191 new opportunities tracked</v>
       </c>
       <c r="H6" t="str">
         <v>PASS</v>
@@ -12947,10 +12298,10 @@
 2. Compute (remoteCount / totalJobs) * 100</v>
       </c>
       <c r="F7" t="str">
-        <v>Displays 61 (30%)</v>
+        <v>Displays 61 (31%)</v>
       </c>
       <c r="G7" t="str">
-        <v>Calculates 61 (30%) flexible roles accurately</v>
+        <v>Calculates 61 (31%) flexible roles accurately</v>
       </c>
       <c r="H7" t="str">
         <v>PASS</v>
@@ -13499,7 +12850,7 @@
         <v>Open http://localhost:5173 in browser</v>
       </c>
       <c r="D2" t="str">
-        <v>Page loads instantly with Forest Green dark theme and 205 PM jobs</v>
+        <v>Page loads instantly with Forest Green dark theme and 194 PM jobs</v>
       </c>
       <c r="E2" t="str">
         <v>[ ] Completed</v>

--- a/GreenPath_PM_Jobs_Test_Report.xlsx
+++ b/GreenPath_PM_Jobs_Test_Report.xlsx
@@ -428,7 +428,7 @@
         <v>Test Execution Date</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-09-27T02:00:40.384Z</v>
+        <v>2026-09-28T02:05:50.083Z</v>
       </c>
     </row>
     <row r="4">
@@ -436,7 +436,7 @@
         <v>Total Jobs in Feed</v>
       </c>
       <c r="B4">
-        <v>194</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5">
@@ -444,7 +444,7 @@
         <v>Total URLs Tested</v>
       </c>
       <c r="B5">
-        <v>194</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6">
@@ -452,7 +452,7 @@
         <v>Active / Valid Direct ATS URLs</v>
       </c>
       <c r="B6">
-        <v>193</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7">
@@ -468,7 +468,7 @@
         <v>URL Health Success Rate</v>
       </c>
       <c r="B8" t="str">
-        <v>99%</v>
+        <v>100%</v>
       </c>
     </row>
     <row r="9">
@@ -524,7 +524,7 @@
         <v>Cities Supported</v>
       </c>
       <c r="B15" t="str">
-        <v>San Francisco, Toronto, Dublin, N/A, New York, Remote, USA, Seattle, London, United States, Paris, Menlo Park, Hybrid, In-Office, Canada, Spain, Poland, Greece, Norway, Switzerland, Doha, Pittsburgh, Beijing, Bengaluru, Vienna, North America, Stockholm, Washington, Mumbai, Gurgaon</v>
+        <v>San Francisco, Toronto, Dublin, N/A, New York, Remote, USA, Seattle, London, United States, Paris, Menlo Park, Hybrid, In-Office, Spain, Ireland, Canada, Norway, Doha, Pittsburgh, Beijing, Bengaluru, Vienna, North America, Stockholm, Washington, Mumbai, Gurgaon</v>
       </c>
     </row>
     <row r="16">
@@ -532,7 +532,7 @@
         <v>Remote / Hybrid Roles</v>
       </c>
       <c r="B16" t="str">
-        <v>61 (31%)</v>
+        <v>61 (30%)</v>
       </c>
     </row>
     <row r="17">
@@ -540,7 +540,7 @@
         <v>Jobs Added Today</v>
       </c>
       <c r="B17" t="str">
-        <v>+191</v>
+        <v>+202</v>
       </c>
     </row>
     <row r="18">
@@ -568,7 +568,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S195"/>
+  <dimension ref="A1:S206"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="38.83203125" customWidth="1"/>
@@ -694,7 +694,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O2" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P2" t="str">
         <v>Today</v>
@@ -706,7 +706,7 @@
         <v>No</v>
       </c>
       <c r="S2">
-        <v>52</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
@@ -753,7 +753,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O3" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P3" t="str">
         <v>Today</v>
@@ -762,10 +762,10 @@
         <v>No</v>
       </c>
       <c r="R3" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S3">
-        <v>91</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4">
@@ -812,19 +812,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O4" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P4" t="str">
         <v>Today</v>
       </c>
       <c r="Q4" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R4" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S4">
-        <v>66</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5">
@@ -871,7 +871,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O5" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P5" t="str">
         <v>Today</v>
@@ -883,7 +883,7 @@
         <v>No</v>
       </c>
       <c r="S5">
-        <v>76</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
@@ -930,7 +930,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O6" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P6" t="str">
         <v>Today</v>
@@ -942,7 +942,7 @@
         <v>No</v>
       </c>
       <c r="S6">
-        <v>50</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7">
@@ -989,19 +989,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O7" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P7" t="str">
         <v>Today</v>
       </c>
       <c r="Q7" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R7" t="str">
         <v>No</v>
       </c>
       <c r="S7">
-        <v>68</v>
+        <v>53</v>
       </c>
     </row>
     <row r="8">
@@ -1048,19 +1048,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O8" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P8" t="str">
         <v>Today</v>
       </c>
       <c r="Q8" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R8" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S8">
-        <v>73</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9">
@@ -1107,7 +1107,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O9" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P9" t="str">
         <v>Today</v>
@@ -1116,10 +1116,10 @@
         <v>No</v>
       </c>
       <c r="R9" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S9">
-        <v>75</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -1166,19 +1166,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O10" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P10" t="str">
         <v>Today</v>
       </c>
       <c r="Q10" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R10" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S10">
-        <v>65</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11">
@@ -1225,7 +1225,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O11" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P11" t="str">
         <v>Today</v>
@@ -1234,10 +1234,10 @@
         <v>Yes</v>
       </c>
       <c r="R11" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S11">
-        <v>69</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12">
@@ -1284,19 +1284,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O12" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P12" t="str">
         <v>Today</v>
       </c>
       <c r="Q12" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R12" t="str">
         <v>No</v>
       </c>
       <c r="S12">
-        <v>44</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -1343,19 +1343,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O13" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P13" t="str">
         <v>Today</v>
       </c>
       <c r="Q13" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R13" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S13">
-        <v>59</v>
+        <v>70</v>
       </c>
     </row>
     <row r="14">
@@ -1402,7 +1402,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O14" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P14" t="str">
         <v>Today</v>
@@ -1414,7 +1414,7 @@
         <v>No</v>
       </c>
       <c r="S14">
-        <v>66</v>
+        <v>89</v>
       </c>
     </row>
     <row r="15">
@@ -1461,7 +1461,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O15" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P15" t="str">
         <v>Today</v>
@@ -1473,7 +1473,7 @@
         <v>No</v>
       </c>
       <c r="S15">
-        <v>86</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16">
@@ -1520,7 +1520,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O16" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P16" t="str">
         <v>Today</v>
@@ -1529,10 +1529,10 @@
         <v>No</v>
       </c>
       <c r="R16" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S16">
-        <v>77</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17">
@@ -1579,7 +1579,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O17" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P17" t="str">
         <v>Today</v>
@@ -1591,7 +1591,7 @@
         <v>No</v>
       </c>
       <c r="S17">
-        <v>56</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18">
@@ -1638,7 +1638,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O18" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P18" t="str">
         <v>Today</v>
@@ -1650,7 +1650,7 @@
         <v>No</v>
       </c>
       <c r="S18">
-        <v>68</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19">
@@ -1697,19 +1697,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O19" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P19" t="str">
         <v>Today</v>
       </c>
       <c r="Q19" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R19" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S19">
-        <v>49</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20">
@@ -1756,19 +1756,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O20" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P20" t="str">
         <v>Today</v>
       </c>
       <c r="Q20" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R20" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S20">
-        <v>71</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21">
@@ -1815,7 +1815,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O21" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P21" t="str">
         <v>Today</v>
@@ -1824,10 +1824,10 @@
         <v>Yes</v>
       </c>
       <c r="R21" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S21">
-        <v>39</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22">
@@ -1874,19 +1874,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O22" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P22" t="str">
         <v>Today</v>
       </c>
       <c r="Q22" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R22" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S22">
-        <v>56</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23">
@@ -1933,7 +1933,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O23" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P23" t="str">
         <v>Today</v>
@@ -1942,10 +1942,10 @@
         <v>No</v>
       </c>
       <c r="R23" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S23">
-        <v>40</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24">
@@ -1992,7 +1992,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O24" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P24" t="str">
         <v>Today</v>
@@ -2004,7 +2004,7 @@
         <v>Yes</v>
       </c>
       <c r="S24">
-        <v>31</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25">
@@ -2051,19 +2051,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O25" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P25" t="str">
         <v>Today</v>
       </c>
       <c r="Q25" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R25" t="str">
         <v>Yes</v>
       </c>
       <c r="S25">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26">
@@ -2110,7 +2110,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O26" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P26" t="str">
         <v>Today</v>
@@ -2119,10 +2119,10 @@
         <v>No</v>
       </c>
       <c r="R26" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S26">
-        <v>55</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27">
@@ -2148,10 +2148,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H27" t="str">
-        <v>London</v>
+        <v>Dublin</v>
       </c>
       <c r="I27" t="str">
-        <v>London</v>
+        <v>Dublin</v>
       </c>
       <c r="J27" t="str">
         <v>On-site</v>
@@ -2160,7 +2160,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L27" t="str">
-        <v>https://boards.greenhouse.io/stripe/jobs/8142649</v>
+        <v>https://boards.greenhouse.io/stripe/jobs/7737526</v>
       </c>
       <c r="M27">
         <v>200</v>
@@ -2169,19 +2169,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O27" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P27" t="str">
         <v>Today</v>
       </c>
       <c r="Q27" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R27" t="str">
         <v>No</v>
       </c>
       <c r="S27">
-        <v>94</v>
+        <v>48</v>
       </c>
     </row>
     <row r="28">
@@ -2228,7 +2228,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O28" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P28" t="str">
         <v>Today</v>
@@ -2237,10 +2237,10 @@
         <v>No</v>
       </c>
       <c r="R28" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S28">
-        <v>35</v>
+        <v>40</v>
       </c>
     </row>
     <row r="29">
@@ -2287,19 +2287,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O29" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P29" t="str">
         <v>Today</v>
       </c>
       <c r="Q29" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R29" t="str">
         <v>No</v>
       </c>
       <c r="S29">
-        <v>29</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30">
@@ -2346,7 +2346,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O30" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P30" t="str">
         <v>Today</v>
@@ -2358,7 +2358,7 @@
         <v>No</v>
       </c>
       <c r="S30">
-        <v>51</v>
+        <v>35</v>
       </c>
     </row>
     <row r="31">
@@ -2405,7 +2405,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O31" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P31" t="str">
         <v>Today</v>
@@ -2417,7 +2417,7 @@
         <v>Yes</v>
       </c>
       <c r="S31">
-        <v>67</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32">
@@ -2464,7 +2464,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O32" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P32" t="str">
         <v>Today</v>
@@ -2473,7 +2473,7 @@
         <v>Yes</v>
       </c>
       <c r="R32" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S32">
         <v>64</v>
@@ -2523,19 +2523,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O33" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P33" t="str">
         <v>Today</v>
       </c>
       <c r="Q33" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R33" t="str">
         <v>No</v>
       </c>
       <c r="S33">
-        <v>70</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34">
@@ -2582,19 +2582,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O34" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P34" t="str">
         <v>Today</v>
       </c>
       <c r="Q34" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R34" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S34">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35">
@@ -2641,7 +2641,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O35" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P35" t="str">
         <v>Today</v>
@@ -2653,7 +2653,7 @@
         <v>No</v>
       </c>
       <c r="S35">
-        <v>31</v>
+        <v>82</v>
       </c>
     </row>
     <row r="36">
@@ -2700,19 +2700,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O36" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P36" t="str">
         <v>Today</v>
       </c>
       <c r="Q36" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R36" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S36">
-        <v>35</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37">
@@ -2759,7 +2759,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O37" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P37" t="str">
         <v>Today</v>
@@ -2771,7 +2771,7 @@
         <v>No</v>
       </c>
       <c r="S37">
-        <v>74</v>
+        <v>93</v>
       </c>
     </row>
     <row r="38">
@@ -2812,25 +2812,25 @@
         <v>https://boards.greenhouse.io/datadog/jobs/8060821</v>
       </c>
       <c r="M38">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="N38" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O38" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P38" t="str">
         <v>Today</v>
       </c>
       <c r="Q38" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R38" t="str">
         <v>No</v>
       </c>
       <c r="S38">
-        <v>48</v>
+        <v>84</v>
       </c>
     </row>
     <row r="39">
@@ -2856,10 +2856,10 @@
         <v>0-2 yrs</v>
       </c>
       <c r="H39" t="str">
-        <v>Paris, France</v>
+        <v>New York, New York, USA</v>
       </c>
       <c r="I39" t="str">
-        <v>Paris</v>
+        <v>New York</v>
       </c>
       <c r="J39" t="str">
         <v>On-site</v>
@@ -2868,7 +2868,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L39" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/8143729</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/8108241</v>
       </c>
       <c r="M39">
         <v>200</v>
@@ -2877,19 +2877,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O39" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P39" t="str">
         <v>Today</v>
       </c>
       <c r="Q39" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R39" t="str">
         <v>No</v>
       </c>
       <c r="S39">
-        <v>82</v>
+        <v>58</v>
       </c>
     </row>
     <row r="40">
@@ -2930,13 +2930,13 @@
         <v>https://boards.greenhouse.io/datadog/jobs/7982288</v>
       </c>
       <c r="M40">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="N40" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O40" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P40" t="str">
         <v>Today</v>
@@ -2945,10 +2945,10 @@
         <v>No</v>
       </c>
       <c r="R40" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S40">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="41">
@@ -2995,19 +2995,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O41" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P41" t="str">
         <v>Today</v>
       </c>
       <c r="Q41" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R41" t="str">
         <v>No</v>
       </c>
       <c r="S41">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="42">
@@ -3048,13 +3048,13 @@
         <v>https://boards.greenhouse.io/datadog/jobs/7583609</v>
       </c>
       <c r="M42">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="N42" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O42" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P42" t="str">
         <v>Today</v>
@@ -3113,7 +3113,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O43" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P43" t="str">
         <v>Today</v>
@@ -3125,7 +3125,7 @@
         <v>No</v>
       </c>
       <c r="S43">
-        <v>82</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44">
@@ -3172,7 +3172,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O44" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P44" t="str">
         <v>Today</v>
@@ -3184,7 +3184,7 @@
         <v>No</v>
       </c>
       <c r="S44">
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="45">
@@ -3231,7 +3231,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O45" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P45" t="str">
         <v>Today</v>
@@ -3243,7 +3243,7 @@
         <v>No</v>
       </c>
       <c r="S45">
-        <v>62</v>
+        <v>50</v>
       </c>
     </row>
     <row r="46">
@@ -3284,25 +3284,25 @@
         <v>https://boards.greenhouse.io/datadog/jobs/8119973</v>
       </c>
       <c r="M46">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="N46" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O46" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P46" t="str">
         <v>Today</v>
       </c>
       <c r="Q46" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R46" t="str">
         <v>No</v>
       </c>
       <c r="S46">
-        <v>63</v>
+        <v>89</v>
       </c>
     </row>
     <row r="47">
@@ -3349,19 +3349,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O47" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P47" t="str">
         <v>Today</v>
       </c>
       <c r="Q47" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R47" t="str">
         <v>No</v>
       </c>
       <c r="S47">
-        <v>69</v>
+        <v>47</v>
       </c>
     </row>
     <row r="48">
@@ -3408,7 +3408,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O48" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P48" t="str">
         <v>Today</v>
@@ -3420,7 +3420,7 @@
         <v>No</v>
       </c>
       <c r="S48">
-        <v>58</v>
+        <v>78</v>
       </c>
     </row>
     <row r="49">
@@ -3467,19 +3467,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O49" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P49" t="str">
         <v>Today</v>
       </c>
       <c r="Q49" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R49" t="str">
         <v>No</v>
       </c>
       <c r="S49">
-        <v>80</v>
+        <v>38</v>
       </c>
     </row>
     <row r="50">
@@ -3526,19 +3526,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O50" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P50" t="str">
         <v>Today</v>
       </c>
       <c r="Q50" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R50" t="str">
         <v>Yes</v>
       </c>
       <c r="S50">
-        <v>80</v>
+        <v>58</v>
       </c>
     </row>
     <row r="51">
@@ -3585,19 +3585,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O51" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P51" t="str">
         <v>Today</v>
       </c>
       <c r="Q51" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R51" t="str">
         <v>No</v>
       </c>
       <c r="S51">
-        <v>68</v>
+        <v>82</v>
       </c>
     </row>
     <row r="52">
@@ -3644,7 +3644,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O52" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P52" t="str">
         <v>Today</v>
@@ -3656,7 +3656,7 @@
         <v>No</v>
       </c>
       <c r="S52">
-        <v>54</v>
+        <v>28</v>
       </c>
     </row>
     <row r="53">
@@ -3703,7 +3703,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O53" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P53" t="str">
         <v>Today</v>
@@ -3712,10 +3712,10 @@
         <v>No</v>
       </c>
       <c r="R53" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S53">
-        <v>94</v>
+        <v>59</v>
       </c>
     </row>
     <row r="54">
@@ -3762,7 +3762,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O54" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P54" t="str">
         <v>Today</v>
@@ -3774,7 +3774,7 @@
         <v>No</v>
       </c>
       <c r="S54">
-        <v>37</v>
+        <v>26</v>
       </c>
     </row>
     <row r="55">
@@ -3815,13 +3815,13 @@
         <v>https://boards.greenhouse.io/datadog/jobs/8065187</v>
       </c>
       <c r="M55">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="N55" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O55" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P55" t="str">
         <v>Today</v>
@@ -3833,7 +3833,7 @@
         <v>No</v>
       </c>
       <c r="S55">
-        <v>62</v>
+        <v>83</v>
       </c>
     </row>
     <row r="56">
@@ -3880,7 +3880,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O56" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P56" t="str">
         <v>Today</v>
@@ -3892,7 +3892,7 @@
         <v>No</v>
       </c>
       <c r="S56">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="57">
@@ -3939,19 +3939,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O57" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P57" t="str">
         <v>Today</v>
       </c>
       <c r="Q57" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R57" t="str">
         <v>No</v>
       </c>
       <c r="S57">
-        <v>80</v>
+        <v>32</v>
       </c>
     </row>
     <row r="58">
@@ -3998,7 +3998,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O58" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P58" t="str">
         <v>Today</v>
@@ -4010,7 +4010,7 @@
         <v>No</v>
       </c>
       <c r="S58">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="59">
@@ -4057,19 +4057,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O59" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P59" t="str">
         <v>Today</v>
       </c>
       <c r="Q59" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R59" t="str">
         <v>No</v>
       </c>
       <c r="S59">
-        <v>78</v>
+        <v>61</v>
       </c>
     </row>
     <row r="60">
@@ -4116,7 +4116,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O60" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P60" t="str">
         <v>Today</v>
@@ -4128,7 +4128,7 @@
         <v>No</v>
       </c>
       <c r="S60">
-        <v>32</v>
+        <v>51</v>
       </c>
     </row>
     <row r="61">
@@ -4175,7 +4175,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O61" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P61" t="str">
         <v>Today</v>
@@ -4184,10 +4184,10 @@
         <v>Yes</v>
       </c>
       <c r="R61" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S61">
-        <v>52</v>
+        <v>72</v>
       </c>
     </row>
     <row r="62">
@@ -4234,7 +4234,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O62" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P62" t="str">
         <v>Today</v>
@@ -4246,7 +4246,7 @@
         <v>No</v>
       </c>
       <c r="S62">
-        <v>87</v>
+        <v>42</v>
       </c>
     </row>
     <row r="63">
@@ -4293,7 +4293,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O63" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P63" t="str">
         <v>Today</v>
@@ -4305,7 +4305,7 @@
         <v>Yes</v>
       </c>
       <c r="S63">
-        <v>68</v>
+        <v>52</v>
       </c>
     </row>
     <row r="64">
@@ -4352,7 +4352,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O64" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P64" t="str">
         <v>Today</v>
@@ -4361,10 +4361,10 @@
         <v>Yes</v>
       </c>
       <c r="R64" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S64">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="65">
@@ -4411,7 +4411,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O65" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P65" t="str">
         <v>Today</v>
@@ -4420,10 +4420,10 @@
         <v>No</v>
       </c>
       <c r="R65" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S65">
-        <v>69</v>
+        <v>41</v>
       </c>
     </row>
     <row r="66">
@@ -4470,19 +4470,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O66" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P66" t="str">
         <v>Today</v>
       </c>
       <c r="Q66" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R66" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S66">
-        <v>55</v>
+        <v>71</v>
       </c>
     </row>
     <row r="67">
@@ -4529,7 +4529,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O67" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P67" t="str">
         <v>Today</v>
@@ -4541,7 +4541,7 @@
         <v>No</v>
       </c>
       <c r="S67">
-        <v>50</v>
+        <v>39</v>
       </c>
     </row>
     <row r="68">
@@ -4588,7 +4588,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O68" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P68" t="str">
         <v>Today</v>
@@ -4600,7 +4600,7 @@
         <v>No</v>
       </c>
       <c r="S68">
-        <v>49</v>
+        <v>76</v>
       </c>
     </row>
     <row r="69">
@@ -4647,19 +4647,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O69" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P69" t="str">
         <v>Today</v>
       </c>
       <c r="Q69" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R69" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S69">
-        <v>72</v>
+        <v>41</v>
       </c>
     </row>
     <row r="70">
@@ -4706,7 +4706,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O70" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P70" t="str">
         <v>Today</v>
@@ -4715,10 +4715,10 @@
         <v>Yes</v>
       </c>
       <c r="R70" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S70">
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="71">
@@ -4765,19 +4765,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O71" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P71" t="str">
         <v>Today</v>
       </c>
       <c r="Q71" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R71" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S71">
-        <v>42</v>
+        <v>92</v>
       </c>
     </row>
     <row r="72">
@@ -4824,19 +4824,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O72" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P72" t="str">
         <v>Today</v>
       </c>
       <c r="Q72" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R72" t="str">
         <v>No</v>
       </c>
       <c r="S72">
-        <v>32</v>
+        <v>61</v>
       </c>
     </row>
     <row r="73">
@@ -4883,7 +4883,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O73" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P73" t="str">
         <v>Today</v>
@@ -4895,7 +4895,7 @@
         <v>No</v>
       </c>
       <c r="S73">
-        <v>59</v>
+        <v>43</v>
       </c>
     </row>
     <row r="74">
@@ -4942,19 +4942,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O74" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P74" t="str">
         <v>Today</v>
       </c>
       <c r="Q74" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R74" t="str">
         <v>No</v>
       </c>
       <c r="S74">
-        <v>29</v>
+        <v>70</v>
       </c>
     </row>
     <row r="75">
@@ -5001,7 +5001,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O75" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P75" t="str">
         <v>Today</v>
@@ -5010,10 +5010,10 @@
         <v>No</v>
       </c>
       <c r="R75" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S75">
-        <v>74</v>
+        <v>89</v>
       </c>
     </row>
     <row r="76">
@@ -5060,19 +5060,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O76" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P76" t="str">
         <v>Today</v>
       </c>
       <c r="Q76" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R76" t="str">
         <v>No</v>
       </c>
       <c r="S76">
-        <v>51</v>
+        <v>32</v>
       </c>
     </row>
     <row r="77">
@@ -5119,7 +5119,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O77" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P77" t="str">
         <v>Today</v>
@@ -5128,10 +5128,10 @@
         <v>Yes</v>
       </c>
       <c r="R77" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S77">
-        <v>52</v>
+        <v>93</v>
       </c>
     </row>
     <row r="78">
@@ -5157,10 +5157,10 @@
         <v>8+ yrs</v>
       </c>
       <c r="H78" t="str">
-        <v>Canada</v>
+        <v>United States</v>
       </c>
       <c r="I78" t="str">
-        <v>Canada</v>
+        <v>United States</v>
       </c>
       <c r="J78" t="str">
         <v>On-site</v>
@@ -5169,7 +5169,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L78" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8070011</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/7602101</v>
       </c>
       <c r="M78">
         <v>200</v>
@@ -5178,7 +5178,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O78" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P78" t="str">
         <v>Today</v>
@@ -5187,10 +5187,10 @@
         <v>Yes</v>
       </c>
       <c r="R78" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S78">
-        <v>32</v>
+        <v>58</v>
       </c>
     </row>
     <row r="79">
@@ -5237,19 +5237,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O79" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P79" t="str">
         <v>Today</v>
       </c>
       <c r="Q79" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R79" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S79">
-        <v>59</v>
+        <v>71</v>
       </c>
     </row>
     <row r="80">
@@ -5296,19 +5296,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O80" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P80" t="str">
         <v>Today</v>
       </c>
       <c r="Q80" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R80" t="str">
         <v>No</v>
       </c>
       <c r="S80">
-        <v>55</v>
+        <v>33</v>
       </c>
     </row>
     <row r="81">
@@ -5334,10 +5334,10 @@
         <v>8+ yrs</v>
       </c>
       <c r="H81" t="str">
-        <v>Poland</v>
+        <v>Spain</v>
       </c>
       <c r="I81" t="str">
-        <v>Poland</v>
+        <v>Spain</v>
       </c>
       <c r="J81" t="str">
         <v>On-site</v>
@@ -5346,7 +5346,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L81" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8155424</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8155416</v>
       </c>
       <c r="M81">
         <v>200</v>
@@ -5355,19 +5355,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O81" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P81" t="str">
         <v>Today</v>
       </c>
       <c r="Q81" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R81" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S81">
-        <v>76</v>
+        <v>52</v>
       </c>
     </row>
     <row r="82">
@@ -5393,10 +5393,10 @@
         <v>8+ yrs</v>
       </c>
       <c r="H82" t="str">
-        <v>Spain</v>
+        <v>Ireland</v>
       </c>
       <c r="I82" t="str">
-        <v>Spain</v>
+        <v>Ireland</v>
       </c>
       <c r="J82" t="str">
         <v>On-site</v>
@@ -5405,7 +5405,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L82" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8155325</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8155326</v>
       </c>
       <c r="M82">
         <v>200</v>
@@ -5414,7 +5414,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O82" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P82" t="str">
         <v>Today</v>
@@ -5426,7 +5426,7 @@
         <v>No</v>
       </c>
       <c r="S82">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="83">
@@ -5452,10 +5452,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H83" t="str">
-        <v>United States</v>
+        <v>Canada</v>
       </c>
       <c r="I83" t="str">
-        <v>United States</v>
+        <v>Canada</v>
       </c>
       <c r="J83" t="str">
         <v>On-site</v>
@@ -5464,7 +5464,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L83" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8214106</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8214187</v>
       </c>
       <c r="M83">
         <v>200</v>
@@ -5473,7 +5473,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O83" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P83" t="str">
         <v>Today</v>
@@ -5482,10 +5482,10 @@
         <v>No</v>
       </c>
       <c r="R83" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S83">
-        <v>33</v>
+        <v>73</v>
       </c>
     </row>
     <row r="84">
@@ -5511,10 +5511,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H84" t="str">
-        <v>United States</v>
+        <v>Canada</v>
       </c>
       <c r="I84" t="str">
-        <v>United States</v>
+        <v>Canada</v>
       </c>
       <c r="J84" t="str">
         <v>On-site</v>
@@ -5523,7 +5523,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L84" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8088818</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8093933</v>
       </c>
       <c r="M84">
         <v>200</v>
@@ -5532,7 +5532,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O84" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P84" t="str">
         <v>Today</v>
@@ -5544,7 +5544,7 @@
         <v>No</v>
       </c>
       <c r="S84">
-        <v>27</v>
+        <v>73</v>
       </c>
     </row>
     <row r="85">
@@ -5570,10 +5570,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H85" t="str">
-        <v>Greece</v>
+        <v>Ireland</v>
       </c>
       <c r="I85" t="str">
-        <v>Greece</v>
+        <v>Ireland</v>
       </c>
       <c r="J85" t="str">
         <v>On-site</v>
@@ -5582,7 +5582,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L85" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8066510</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8066516</v>
       </c>
       <c r="M85">
         <v>200</v>
@@ -5591,7 +5591,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O85" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P85" t="str">
         <v>Today</v>
@@ -5603,7 +5603,7 @@
         <v>No</v>
       </c>
       <c r="S85">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="86">
@@ -5650,19 +5650,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O86" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P86" t="str">
         <v>Today</v>
       </c>
       <c r="Q86" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R86" t="str">
         <v>No</v>
       </c>
       <c r="S86">
-        <v>77</v>
+        <v>59</v>
       </c>
     </row>
     <row r="87">
@@ -5709,7 +5709,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O87" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P87" t="str">
         <v>Today</v>
@@ -5721,7 +5721,7 @@
         <v>No</v>
       </c>
       <c r="S87">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="88">
@@ -5747,10 +5747,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H88" t="str">
-        <v>Switzerland</v>
+        <v>United States</v>
       </c>
       <c r="I88" t="str">
-        <v>Switzerland</v>
+        <v>United States</v>
       </c>
       <c r="J88" t="str">
         <v>On-site</v>
@@ -5759,7 +5759,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L88" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8194084</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8167771</v>
       </c>
       <c r="M88">
         <v>200</v>
@@ -5768,19 +5768,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O88" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P88" t="str">
         <v>Today</v>
       </c>
       <c r="Q88" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R88" t="str">
         <v>No</v>
       </c>
       <c r="S88">
-        <v>52</v>
+        <v>76</v>
       </c>
     </row>
     <row r="89">
@@ -5827,19 +5827,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O89" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P89" t="str">
         <v>Today</v>
       </c>
       <c r="Q89" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R89" t="str">
         <v>No</v>
       </c>
       <c r="S89">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="90">
@@ -5886,19 +5886,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O90" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P90" t="str">
         <v>Today</v>
       </c>
       <c r="Q90" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R90" t="str">
         <v>No</v>
       </c>
       <c r="S90">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="91">
@@ -5924,10 +5924,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H91" t="str">
-        <v>London, UK</v>
+        <v>New York, NY</v>
       </c>
       <c r="I91" t="str">
-        <v>London</v>
+        <v>New York</v>
       </c>
       <c r="J91" t="str">
         <v>On-site</v>
@@ -5936,7 +5936,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L91" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4644742005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4673051005</v>
       </c>
       <c r="M91">
         <v>200</v>
@@ -5945,19 +5945,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O91" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P91" t="str">
         <v>Today</v>
       </c>
       <c r="Q91" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R91" t="str">
         <v>No</v>
       </c>
       <c r="S91">
-        <v>46</v>
+        <v>87</v>
       </c>
     </row>
     <row r="92">
@@ -6004,7 +6004,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O92" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P92" t="str">
         <v>Today</v>
@@ -6013,10 +6013,10 @@
         <v>Yes</v>
       </c>
       <c r="R92" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S92">
-        <v>43</v>
+        <v>65</v>
       </c>
     </row>
     <row r="93">
@@ -6063,19 +6063,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O93" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P93" t="str">
         <v>Today</v>
       </c>
       <c r="Q93" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R93" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S93">
-        <v>76</v>
+        <v>90</v>
       </c>
     </row>
     <row r="94">
@@ -6122,7 +6122,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O94" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P94" t="str">
         <v>Today</v>
@@ -6134,7 +6134,7 @@
         <v>Yes</v>
       </c>
       <c r="S94">
-        <v>33</v>
+        <v>72</v>
       </c>
     </row>
     <row r="95">
@@ -6181,19 +6181,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O95" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P95" t="str">
         <v>Today</v>
       </c>
       <c r="Q95" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R95" t="str">
         <v>Yes</v>
       </c>
       <c r="S95">
-        <v>38</v>
+        <v>65</v>
       </c>
     </row>
     <row r="96">
@@ -6240,19 +6240,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O96" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P96" t="str">
         <v>Today</v>
       </c>
       <c r="Q96" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R96" t="str">
         <v>No</v>
       </c>
       <c r="S96">
-        <v>47</v>
+        <v>89</v>
       </c>
     </row>
     <row r="97">
@@ -6299,19 +6299,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O97" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P97" t="str">
         <v>Today</v>
       </c>
       <c r="Q97" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R97" t="str">
         <v>No</v>
       </c>
       <c r="S97">
-        <v>51</v>
+        <v>65</v>
       </c>
     </row>
     <row r="98">
@@ -6358,7 +6358,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O98" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P98" t="str">
         <v>Today</v>
@@ -6367,10 +6367,10 @@
         <v>Yes</v>
       </c>
       <c r="R98" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S98">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="99">
@@ -6417,7 +6417,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O99" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P99" t="str">
         <v>Today</v>
@@ -6429,7 +6429,7 @@
         <v>No</v>
       </c>
       <c r="S99">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="100">
@@ -6476,13 +6476,13 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O100" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P100" t="str">
         <v>Today</v>
       </c>
       <c r="Q100" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R100" t="str">
         <v>No</v>
@@ -6535,7 +6535,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O101" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P101" t="str">
         <v>Today</v>
@@ -6544,10 +6544,10 @@
         <v>Yes</v>
       </c>
       <c r="R101" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S101">
-        <v>31</v>
+        <v>79</v>
       </c>
     </row>
     <row r="102">
@@ -6594,48 +6594,48 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O102" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P102" t="str">
         <v>Today</v>
       </c>
       <c r="Q102" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R102" t="str">
         <v>No</v>
       </c>
       <c r="S102">
-        <v>63</v>
+        <v>42</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>job-429ddf15</v>
+        <v>job-58b32a73</v>
       </c>
       <c r="B103" t="str">
-        <v>Associate Product Manager, Intern</v>
+        <v>Director of Product, Growth/AI</v>
       </c>
       <c r="C103" t="str">
-        <v>Duolingo</v>
+        <v>Brex</v>
       </c>
       <c r="D103" t="str">
         <v>Wellfound</v>
       </c>
       <c r="E103" t="str">
-        <v>Associate Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F103" t="str">
-        <v>1-3 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G103" t="str">
-        <v>0-2 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H103" t="str">
-        <v>Pittsburgh, PA</v>
+        <v>San Francisco, California, United States</v>
       </c>
       <c r="I103" t="str">
-        <v>Pittsburgh</v>
+        <v>San Francisco</v>
       </c>
       <c r="J103" t="str">
         <v>On-site</v>
@@ -6644,7 +6644,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L103" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8806187002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8432707002</v>
       </c>
       <c r="M103">
         <v>200</v>
@@ -6653,48 +6653,48 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O103" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P103" t="str">
         <v>Today</v>
       </c>
       <c r="Q103" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R103" t="str">
         <v>No</v>
       </c>
       <c r="S103">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>job-1b56d1fb</v>
+        <v>job-6c147538</v>
       </c>
       <c r="B104" t="str">
-        <v>Senior Product Manager</v>
+        <v>Group Product Manager</v>
       </c>
       <c r="C104" t="str">
-        <v>Duolingo</v>
+        <v>Brex</v>
       </c>
       <c r="D104" t="str">
         <v>Wellfound</v>
       </c>
       <c r="E104" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F104" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G104" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H104" t="str">
-        <v>Beijing, China</v>
+        <v>Seattle, Washington, United States</v>
       </c>
       <c r="I104" t="str">
-        <v>Beijing</v>
+        <v>Seattle</v>
       </c>
       <c r="J104" t="str">
         <v>On-site</v>
@@ -6703,7 +6703,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L104" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8675670002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8438582002</v>
       </c>
       <c r="M104">
         <v>200</v>
@@ -6712,30 +6712,30 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O104" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P104" t="str">
         <v>Today</v>
       </c>
       <c r="Q104" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R104" t="str">
         <v>No</v>
       </c>
       <c r="S104">
-        <v>82</v>
+        <v>65</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>job-0ba5b818</v>
+        <v>job-4a5cf899</v>
       </c>
       <c r="B105" t="str">
-        <v>Senior Product Manager, DET</v>
+        <v>Senior Product Manager, AI</v>
       </c>
       <c r="C105" t="str">
-        <v>Duolingo</v>
+        <v>Brex</v>
       </c>
       <c r="D105" t="str">
         <v>Wellfound</v>
@@ -6750,10 +6750,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H105" t="str">
-        <v>New York, NY</v>
+        <v>Seattle, Washington, United States</v>
       </c>
       <c r="I105" t="str">
-        <v>New York</v>
+        <v>Seattle</v>
       </c>
       <c r="J105" t="str">
         <v>On-site</v>
@@ -6762,7 +6762,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L105" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8737859002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8780828002</v>
       </c>
       <c r="M105">
         <v>200</v>
@@ -6771,7 +6771,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O105" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P105" t="str">
         <v>Today</v>
@@ -6780,21 +6780,21 @@
         <v>Yes</v>
       </c>
       <c r="R105" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S105">
-        <v>39</v>
+        <v>59</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>job-25986280</v>
+        <v>job-111c900b</v>
       </c>
       <c r="B106" t="str">
-        <v>Senior Product Manager, Growth</v>
+        <v>Senior Product Manager, Travel</v>
       </c>
       <c r="C106" t="str">
-        <v>Duolingo</v>
+        <v>Brex</v>
       </c>
       <c r="D106" t="str">
         <v>Wellfound</v>
@@ -6809,10 +6809,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H106" t="str">
-        <v>New York, NY</v>
+        <v>San Francisco, California, United States</v>
       </c>
       <c r="I106" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J106" t="str">
         <v>On-site</v>
@@ -6821,7 +6821,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L106" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8747275002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8659249002</v>
       </c>
       <c r="M106">
         <v>200</v>
@@ -6830,7 +6830,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O106" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P106" t="str">
         <v>Today</v>
@@ -6842,18 +6842,18 @@
         <v>No</v>
       </c>
       <c r="S106">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>job-604bd697</v>
+        <v>job-337165a7</v>
       </c>
       <c r="B107" t="str">
-        <v>Senior Product Manager, Learning</v>
+        <v>Staff Product Manager</v>
       </c>
       <c r="C107" t="str">
-        <v>Duolingo</v>
+        <v>Brex</v>
       </c>
       <c r="D107" t="str">
         <v>Wellfound</v>
@@ -6868,10 +6868,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H107" t="str">
-        <v>New York, NY; Pittsburgh, PA</v>
+        <v>Seattle, Washington, United States</v>
       </c>
       <c r="I107" t="str">
-        <v>New York</v>
+        <v>Seattle</v>
       </c>
       <c r="J107" t="str">
         <v>On-site</v>
@@ -6880,7 +6880,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L107" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8827944002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8432703002</v>
       </c>
       <c r="M107">
         <v>200</v>
@@ -6889,30 +6889,30 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O107" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P107" t="str">
         <v>Today</v>
       </c>
       <c r="Q107" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R107" t="str">
         <v>No</v>
       </c>
       <c r="S107">
-        <v>29</v>
+        <v>25</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>job-256f50fd</v>
+        <v>job-533982f5</v>
       </c>
       <c r="B108" t="str">
-        <v>Senior Product Manager, Notifications</v>
+        <v>Staff Product Manager, AI</v>
       </c>
       <c r="C108" t="str">
-        <v>Duolingo</v>
+        <v>Brex</v>
       </c>
       <c r="D108" t="str">
         <v>Wellfound</v>
@@ -6927,10 +6927,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H108" t="str">
-        <v>Pittsburgh, PA</v>
+        <v>New York, New York, United States</v>
       </c>
       <c r="I108" t="str">
-        <v>Pittsburgh</v>
+        <v>New York</v>
       </c>
       <c r="J108" t="str">
         <v>On-site</v>
@@ -6939,7 +6939,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L108" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8747099002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8780829002</v>
       </c>
       <c r="M108">
         <v>200</v>
@@ -6948,7 +6948,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O108" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P108" t="str">
         <v>Today</v>
@@ -6957,21 +6957,21 @@
         <v>Yes</v>
       </c>
       <c r="R108" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S108">
-        <v>92</v>
+        <v>43</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>job-2666664e</v>
+        <v>job-0f9c4e5d</v>
       </c>
       <c r="B109" t="str">
-        <v>Staff Product Manager, Monetization</v>
+        <v>Staff Product Manager, Card</v>
       </c>
       <c r="C109" t="str">
-        <v>Duolingo</v>
+        <v>Brex</v>
       </c>
       <c r="D109" t="str">
         <v>Wellfound</v>
@@ -6986,10 +6986,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H109" t="str">
-        <v>New York, NY</v>
+        <v>San Francisco, California, United States</v>
       </c>
       <c r="I109" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J109" t="str">
         <v>On-site</v>
@@ -6998,7 +6998,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L109" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8474673002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8659220002</v>
       </c>
       <c r="M109">
         <v>200</v>
@@ -7007,48 +7007,48 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O109" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P109" t="str">
         <v>Today</v>
       </c>
       <c r="Q109" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R109" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S109">
-        <v>62</v>
+        <v>52</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>job-6e88535c</v>
+        <v>job-4401c5a9</v>
       </c>
       <c r="B110" t="str">
-        <v>VP of Product, Growth and Monetization</v>
+        <v>Staff Product Manager, Embedded</v>
       </c>
       <c r="C110" t="str">
-        <v>Duolingo</v>
+        <v>Brex</v>
       </c>
       <c r="D110" t="str">
         <v>Wellfound</v>
       </c>
       <c r="E110" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F110" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G110" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H110" t="str">
-        <v>New York, NY</v>
+        <v>Seattle, Washington, United States</v>
       </c>
       <c r="I110" t="str">
-        <v>New York</v>
+        <v>Seattle</v>
       </c>
       <c r="J110" t="str">
         <v>On-site</v>
@@ -7057,7 +7057,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L110" t="str">
-        <v>https://boards.greenhouse.io/duolingo/jobs/8747060002</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8659210002</v>
       </c>
       <c r="M110">
         <v>200</v>
@@ -7066,125 +7066,125 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O110" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P110" t="str">
         <v>Today</v>
       </c>
       <c r="Q110" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R110" t="str">
         <v>Yes</v>
       </c>
       <c r="S110">
-        <v>66</v>
+        <v>50</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>job-65a74288</v>
+        <v>job-75398a6b</v>
       </c>
       <c r="B111" t="str">
-        <v>Associate Product Manager Intern</v>
+        <v>Staff Product Manager,  Embedded</v>
       </c>
       <c r="C111" t="str">
-        <v>Coinbase</v>
+        <v>Brex</v>
       </c>
       <c r="D111" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E111" t="str">
-        <v>Associate Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F111" t="str">
-        <v>1-3 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G111" t="str">
-        <v>0-2 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H111" t="str">
-        <v>Hybrid - San Francisco, CA</v>
+        <v>New York, New York, United States</v>
       </c>
       <c r="I111" t="str">
-        <v>San Francisco</v>
+        <v>New York</v>
       </c>
       <c r="J111" t="str">
-        <v>Hybrid</v>
+        <v>On-site</v>
       </c>
       <c r="K111" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L111" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/8168322</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8659211002</v>
       </c>
       <c r="M111">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N111" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O111" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P111" t="str">
         <v>Today</v>
       </c>
       <c r="Q111" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R111" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S111">
-        <v>69</v>
+        <v>77</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>job-2bc26745</v>
+        <v>job-0f02a1a8</v>
       </c>
       <c r="B112" t="str">
-        <v>Group Product Manager, Compliance Agent Experience</v>
+        <v>Staff Product Manager, Expenses</v>
       </c>
       <c r="C112" t="str">
-        <v>Coinbase</v>
+        <v>Brex</v>
       </c>
       <c r="D112" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E112" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F112" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G112" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H112" t="str">
-        <v>Remote - USA</v>
+        <v>San Francisco, California, United States</v>
       </c>
       <c r="I112" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J112" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K112" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L112" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/8060662</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8659239002</v>
       </c>
       <c r="M112">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N112" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O112" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P112" t="str">
         <v>Today</v>
@@ -7196,54 +7196,54 @@
         <v>No</v>
       </c>
       <c r="S112">
-        <v>29</v>
+        <v>67</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>job-779d88ed</v>
+        <v>job-2239c52c</v>
       </c>
       <c r="B113" t="str">
-        <v>Group Product Manager, Compliance Automation</v>
+        <v>Staff Product Manager, Growth</v>
       </c>
       <c r="C113" t="str">
-        <v>Coinbase</v>
+        <v>Brex</v>
       </c>
       <c r="D113" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E113" t="str">
-        <v>Product Lead / Director</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F113" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G113" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H113" t="str">
-        <v>Remote - USA</v>
+        <v>Seattle, Washington, United States</v>
       </c>
       <c r="I113" t="str">
-        <v>Remote</v>
+        <v>Seattle</v>
       </c>
       <c r="J113" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K113" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L113" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/7701642</v>
+        <v>https://boards.greenhouse.io/brex/jobs/8436530002</v>
       </c>
       <c r="M113">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N113" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O113" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P113" t="str">
         <v>Today</v>
@@ -7260,49 +7260,49 @@
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>job-6faf73eb</v>
+        <v>job-429ddf15</v>
       </c>
       <c r="B114" t="str">
-        <v>Group Product Manager, Core Infrastructure &amp; Reliability</v>
+        <v>Associate Product Manager, Intern</v>
       </c>
       <c r="C114" t="str">
-        <v>Coinbase</v>
+        <v>Duolingo</v>
       </c>
       <c r="D114" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E114" t="str">
-        <v>Technical Product Manager</v>
+        <v>Associate Product Manager</v>
       </c>
       <c r="F114" t="str">
-        <v>3-6 yrs</v>
+        <v>1-3 yrs</v>
       </c>
       <c r="G114" t="str">
-        <v>2-5 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H114" t="str">
-        <v>Remote - USA</v>
+        <v>Pittsburgh, PA</v>
       </c>
       <c r="I114" t="str">
-        <v>Remote</v>
+        <v>Pittsburgh</v>
       </c>
       <c r="J114" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K114" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L114" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/7997785</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8806187002</v>
       </c>
       <c r="M114">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N114" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O114" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P114" t="str">
         <v>Today</v>
@@ -7314,54 +7314,54 @@
         <v>Yes</v>
       </c>
       <c r="S114">
-        <v>86</v>
+        <v>36</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>job-67afa492</v>
+        <v>job-1b56d1fb</v>
       </c>
       <c r="B115" t="str">
-        <v>Group Product Manager, Developer Infrastructure</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="C115" t="str">
-        <v>Coinbase</v>
+        <v>Duolingo</v>
       </c>
       <c r="D115" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E115" t="str">
-        <v>Technical Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F115" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G115" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H115" t="str">
-        <v>Remote - USA</v>
+        <v>Beijing, China</v>
       </c>
       <c r="I115" t="str">
-        <v>Remote</v>
+        <v>Beijing</v>
       </c>
       <c r="J115" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K115" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L115" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/8017607</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8675670002</v>
       </c>
       <c r="M115">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N115" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O115" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P115" t="str">
         <v>Today</v>
@@ -7373,54 +7373,54 @@
         <v>No</v>
       </c>
       <c r="S115">
-        <v>52</v>
+        <v>91</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>job-30b71fd8</v>
+        <v>job-0ba5b818</v>
       </c>
       <c r="B116" t="str">
-        <v>Group Product Manager, Money Movement</v>
+        <v>Senior Product Manager, DET</v>
       </c>
       <c r="C116" t="str">
-        <v>Coinbase</v>
+        <v>Duolingo</v>
       </c>
       <c r="D116" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E116" t="str">
-        <v>Product Lead / Director</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F116" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G116" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H116" t="str">
-        <v>Remote - USA</v>
+        <v>Pittsburgh, PA</v>
       </c>
       <c r="I116" t="str">
-        <v>Remote</v>
+        <v>Pittsburgh</v>
       </c>
       <c r="J116" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K116" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L116" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/8234060</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8530395002</v>
       </c>
       <c r="M116">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N116" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O116" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P116" t="str">
         <v>Today</v>
@@ -7432,54 +7432,54 @@
         <v>No</v>
       </c>
       <c r="S116">
-        <v>80</v>
+        <v>53</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>job-00f9bc89</v>
+        <v>job-25986280</v>
       </c>
       <c r="B117" t="str">
-        <v>Head of Product Creative</v>
+        <v>Senior Product Manager, Growth</v>
       </c>
       <c r="C117" t="str">
-        <v>Coinbase</v>
+        <v>Duolingo</v>
       </c>
       <c r="D117" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E117" t="str">
-        <v>Product Lead / Director</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F117" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G117" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H117" t="str">
-        <v>Remote - USA</v>
+        <v>New York, NY</v>
       </c>
       <c r="I117" t="str">
-        <v>Remote</v>
+        <v>New York</v>
       </c>
       <c r="J117" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K117" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L117" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/7304930</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8747275002</v>
       </c>
       <c r="M117">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N117" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O117" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P117" t="str">
         <v>Today</v>
@@ -7488,57 +7488,57 @@
         <v>No</v>
       </c>
       <c r="R117" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S117">
-        <v>40</v>
+        <v>74</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>job-02200da7</v>
+        <v>job-604bd697</v>
       </c>
       <c r="B118" t="str">
-        <v>Product Manager (HR Technology) Intern</v>
+        <v>Senior Product Manager, Learning</v>
       </c>
       <c r="C118" t="str">
-        <v>Coinbase</v>
+        <v>Duolingo</v>
       </c>
       <c r="D118" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E118" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F118" t="str">
-        <v>1-3 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G118" t="str">
-        <v>0-2 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H118" t="str">
-        <v>Hybrid - New York, NY</v>
+        <v>New York, NY; Pittsburgh, PA</v>
       </c>
       <c r="I118" t="str">
         <v>New York</v>
       </c>
       <c r="J118" t="str">
-        <v>Hybrid</v>
+        <v>On-site</v>
       </c>
       <c r="K118" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L118" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/8175504</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8827944002</v>
       </c>
       <c r="M118">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N118" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O118" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P118" t="str">
         <v>Today</v>
@@ -7550,54 +7550,54 @@
         <v>Yes</v>
       </c>
       <c r="S118">
-        <v>47</v>
+        <v>68</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>job-0f319aac</v>
+        <v>job-256f50fd</v>
       </c>
       <c r="B119" t="str">
-        <v>Product Manager II, Growth - Notifications</v>
+        <v>Senior Product Manager, Notifications</v>
       </c>
       <c r="C119" t="str">
-        <v>Coinbase</v>
+        <v>Duolingo</v>
       </c>
       <c r="D119" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E119" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F119" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G119" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H119" t="str">
-        <v>Remote - USA</v>
+        <v>Pittsburgh, PA</v>
       </c>
       <c r="I119" t="str">
-        <v>Remote</v>
+        <v>Pittsburgh</v>
       </c>
       <c r="J119" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K119" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L119" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/8204571</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8747099002</v>
       </c>
       <c r="M119">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N119" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O119" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P119" t="str">
         <v>Today</v>
@@ -7609,172 +7609,172 @@
         <v>No</v>
       </c>
       <c r="S119">
-        <v>61</v>
+        <v>44</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>job-0d5f8a75</v>
+        <v>job-2666664e</v>
       </c>
       <c r="B120" t="str">
-        <v>Product Manager II, Workspace and Multi-User</v>
+        <v>Staff Product Manager, Monetization</v>
       </c>
       <c r="C120" t="str">
-        <v>Coinbase</v>
+        <v>Duolingo</v>
       </c>
       <c r="D120" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E120" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F120" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G120" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H120" t="str">
-        <v>Remote - USA</v>
+        <v>New York, NY</v>
       </c>
       <c r="I120" t="str">
-        <v>Remote</v>
+        <v>New York</v>
       </c>
       <c r="J120" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K120" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L120" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/8148171</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8474673002</v>
       </c>
       <c r="M120">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N120" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O120" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P120" t="str">
         <v>Today</v>
       </c>
       <c r="Q120" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R120" t="str">
         <v>No</v>
       </c>
       <c r="S120">
-        <v>43</v>
+        <v>81</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>job-2efe7fb3</v>
+        <v>job-6e88535c</v>
       </c>
       <c r="B121" t="str">
-        <v>Senior Product Manager, Help Center (CX Automation)</v>
+        <v>VP of Product, Growth and Monetization</v>
       </c>
       <c r="C121" t="str">
-        <v>Coinbase</v>
+        <v>Duolingo</v>
       </c>
       <c r="D121" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E121" t="str">
-        <v>Senior Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F121" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G121" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H121" t="str">
-        <v>Remote - India</v>
+        <v>Pittsburgh, PA</v>
       </c>
       <c r="I121" t="str">
-        <v>Remote</v>
+        <v>Pittsburgh</v>
       </c>
       <c r="J121" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K121" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L121" t="str">
-        <v>https://boards.greenhouse.io/coinbase/jobs/8031208</v>
+        <v>https://boards.greenhouse.io/duolingo/jobs/8747077002</v>
       </c>
       <c r="M121">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N121" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O121" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P121" t="str">
         <v>Today</v>
       </c>
       <c r="Q121" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R121" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S121">
-        <v>31</v>
+        <v>71</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>job-1762a9dc</v>
+        <v>job-65a74288</v>
       </c>
       <c r="B122" t="str">
-        <v>Director of Product Management, Agentic Software Delivery</v>
+        <v>Associate Product Manager Intern</v>
       </c>
       <c r="C122" t="str">
-        <v>GitLab</v>
+        <v>Coinbase</v>
       </c>
       <c r="D122" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E122" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Associate Product Manager</v>
       </c>
       <c r="F122" t="str">
-        <v>8+ yrs</v>
+        <v>1-3 yrs</v>
       </c>
       <c r="G122" t="str">
-        <v>8+ yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H122" t="str">
-        <v>Remote, United States</v>
+        <v>Hybrid - San Francisco, CA</v>
       </c>
       <c r="I122" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J122" t="str">
-        <v>Remote</v>
+        <v>Hybrid</v>
       </c>
       <c r="K122" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L122" t="str">
-        <v>https://boards.greenhouse.io/gitlab/jobs/8806017002</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/8168322</v>
       </c>
       <c r="M122">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N122" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O122" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P122" t="str">
         <v>Today</v>
@@ -7783,36 +7783,36 @@
         <v>No</v>
       </c>
       <c r="R122" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S122">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>job-58e27f7c</v>
+        <v>job-2bc26745</v>
       </c>
       <c r="B123" t="str">
-        <v>Principal Product Manager, AI Software Factory</v>
+        <v>Group Product Manager, Compliance Agent Experience</v>
       </c>
       <c r="C123" t="str">
-        <v>GitLab</v>
+        <v>Coinbase</v>
       </c>
       <c r="D123" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E123" t="str">
-        <v>Senior Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F123" t="str">
-        <v>8+ yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G123" t="str">
-        <v>8+ yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H123" t="str">
-        <v>Remote, Canada; Remote, United States</v>
+        <v>Remote - USA</v>
       </c>
       <c r="I123" t="str">
         <v>Remote</v>
@@ -7824,54 +7824,54 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L123" t="str">
-        <v>https://boards.greenhouse.io/gitlab/jobs/8658878002</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/8060662</v>
       </c>
       <c r="M123">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N123" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O123" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P123" t="str">
         <v>Today</v>
       </c>
       <c r="Q123" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R123" t="str">
         <v>No</v>
       </c>
       <c r="S123">
-        <v>40</v>
+        <v>79</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>job-448d861a</v>
+        <v>job-779d88ed</v>
       </c>
       <c r="B124" t="str">
-        <v>Senior Product Manager, Agentic Source Code</v>
+        <v>Group Product Manager, Compliance Automation</v>
       </c>
       <c r="C124" t="str">
-        <v>GitLab</v>
+        <v>Coinbase</v>
       </c>
       <c r="D124" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E124" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F124" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G124" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H124" t="str">
-        <v>Remote, Canada; Remote, US</v>
+        <v>Remote - USA</v>
       </c>
       <c r="I124" t="str">
         <v>Remote</v>
@@ -7883,16 +7883,16 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L124" t="str">
-        <v>https://boards.greenhouse.io/gitlab/jobs/8597805002</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/7701642</v>
       </c>
       <c r="M124">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N124" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O124" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P124" t="str">
         <v>Today</v>
@@ -7904,33 +7904,33 @@
         <v>No</v>
       </c>
       <c r="S124">
-        <v>26</v>
+        <v>42</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>job-6bc28568</v>
+        <v>job-6faf73eb</v>
       </c>
       <c r="B125" t="str">
-        <v>Senior Product Manager, Secret Detection and Vulnerability Research</v>
+        <v>Group Product Manager, Core Infrastructure &amp; Reliability</v>
       </c>
       <c r="C125" t="str">
-        <v>GitLab</v>
+        <v>Coinbase</v>
       </c>
       <c r="D125" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E125" t="str">
-        <v>Senior Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F125" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G125" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H125" t="str">
-        <v>Remote, United States</v>
+        <v>Remote - USA</v>
       </c>
       <c r="I125" t="str">
         <v>Remote</v>
@@ -7942,16 +7942,16 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L125" t="str">
-        <v>https://boards.greenhouse.io/gitlab/jobs/8697043002</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/7997785</v>
       </c>
       <c r="M125">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N125" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O125" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P125" t="str">
         <v>Today</v>
@@ -7963,33 +7963,33 @@
         <v>No</v>
       </c>
       <c r="S125">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>job-7ad77ccd</v>
+        <v>job-67afa492</v>
       </c>
       <c r="B126" t="str">
-        <v>Senior Product Manager, Tenant Scale</v>
+        <v>Group Product Manager, Developer Infrastructure</v>
       </c>
       <c r="C126" t="str">
-        <v>GitLab</v>
+        <v>Coinbase</v>
       </c>
       <c r="D126" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E126" t="str">
-        <v>Senior Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F126" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G126" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H126" t="str">
-        <v>Remote, Canada; Remote, US</v>
+        <v>Remote - USA</v>
       </c>
       <c r="I126" t="str">
         <v>Remote</v>
@@ -8001,54 +8001,54 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L126" t="str">
-        <v>https://boards.greenhouse.io/gitlab/jobs/8512220002</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/8017607</v>
       </c>
       <c r="M126">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N126" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O126" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P126" t="str">
         <v>Today</v>
       </c>
       <c r="Q126" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R126" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S126">
-        <v>27</v>
+        <v>35</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>job-52edb6a4</v>
+        <v>job-30b71fd8</v>
       </c>
       <c r="B127" t="str">
-        <v>Staff Product Manager,  RevOps &amp; Finance Systems</v>
+        <v>Group Product Manager, Money Movement</v>
       </c>
       <c r="C127" t="str">
-        <v>GitLab</v>
+        <v>Coinbase</v>
       </c>
       <c r="D127" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E127" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F127" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G127" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H127" t="str">
-        <v>Remote, US</v>
+        <v>Remote - USA</v>
       </c>
       <c r="I127" t="str">
         <v>Remote</v>
@@ -8060,84 +8060,84 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L127" t="str">
-        <v>https://boards.greenhouse.io/gitlab/jobs/8612937002</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/8234060</v>
       </c>
       <c r="M127">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N127" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O127" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P127" t="str">
         <v>Today</v>
       </c>
       <c r="Q127" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R127" t="str">
         <v>No</v>
       </c>
       <c r="S127">
-        <v>76</v>
+        <v>37</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>job-3a743e4f</v>
+        <v>job-00f9bc89</v>
       </c>
       <c r="B128" t="str">
-        <v>Manager, Product Management - Figma Platform Experience</v>
+        <v>Head of Product Creative</v>
       </c>
       <c r="C128" t="str">
-        <v>Figma</v>
+        <v>Coinbase</v>
       </c>
       <c r="D128" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E128" t="str">
-        <v>Technical Product Manager</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F128" t="str">
-        <v>3-6 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G128" t="str">
-        <v>2-5 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H128" t="str">
-        <v>San Francisco, CA • New York, NY • United States</v>
+        <v>Remote - USA</v>
       </c>
       <c r="I128" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J128" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K128" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L128" t="str">
-        <v>https://boards.greenhouse.io/figma/jobs/6160732004</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/7304930</v>
       </c>
       <c r="M128">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N128" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O128" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P128" t="str">
         <v>Today</v>
       </c>
       <c r="Q128" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R128" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S128">
         <v>40</v>
@@ -8145,13 +8145,13 @@
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>job-7297f499</v>
+        <v>job-02200da7</v>
       </c>
       <c r="B129" t="str">
-        <v>Manager, Product Management - Roundtripping</v>
+        <v>Product Manager (HR Technology) Intern</v>
       </c>
       <c r="C129" t="str">
-        <v>Figma</v>
+        <v>Coinbase</v>
       </c>
       <c r="D129" t="str">
         <v>LinkedIn</v>
@@ -8160,63 +8160,63 @@
         <v>Product Manager</v>
       </c>
       <c r="F129" t="str">
-        <v>3-6 yrs</v>
+        <v>1-3 yrs</v>
       </c>
       <c r="G129" t="str">
-        <v>2-5 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H129" t="str">
-        <v>New York, NY • United States</v>
+        <v>Hybrid - New York, NY</v>
       </c>
       <c r="I129" t="str">
         <v>New York</v>
       </c>
       <c r="J129" t="str">
-        <v>On-site</v>
+        <v>Hybrid</v>
       </c>
       <c r="K129" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L129" t="str">
-        <v>https://boards.greenhouse.io/figma/jobs/6104919004</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/8175504</v>
       </c>
       <c r="M129">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N129" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O129" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P129" t="str">
         <v>Today</v>
       </c>
       <c r="Q129" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R129" t="str">
         <v>No</v>
       </c>
       <c r="S129">
-        <v>94</v>
+        <v>47</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>job-19031a2a</v>
+        <v>job-0f319aac</v>
       </c>
       <c r="B130" t="str">
-        <v>Manager, Product Management - Roundtripping (London, United Kingdom)</v>
+        <v>Product Manager II, Growth - Notifications</v>
       </c>
       <c r="C130" t="str">
-        <v>Figma</v>
+        <v>Coinbase</v>
       </c>
       <c r="D130" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E130" t="str">
-        <v>Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F130" t="str">
         <v>3-6 yrs</v>
@@ -8225,51 +8225,51 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H130" t="str">
-        <v>London, England</v>
+        <v>Remote - USA</v>
       </c>
       <c r="I130" t="str">
-        <v>London</v>
+        <v>Remote</v>
       </c>
       <c r="J130" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K130" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L130" t="str">
-        <v>https://boards.greenhouse.io/figma/jobs/6149007004</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/8204571</v>
       </c>
       <c r="M130">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N130" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O130" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P130" t="str">
         <v>Today</v>
       </c>
       <c r="Q130" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R130" t="str">
         <v>No</v>
       </c>
       <c r="S130">
-        <v>79</v>
+        <v>59</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>job-099ff647</v>
+        <v>job-0d5f8a75</v>
       </c>
       <c r="B131" t="str">
-        <v>Product Manager, Acquisition</v>
+        <v>Product Manager II, Workspace and Multi-User</v>
       </c>
       <c r="C131" t="str">
-        <v>Figma</v>
+        <v>Coinbase</v>
       </c>
       <c r="D131" t="str">
         <v>LinkedIn</v>
@@ -8284,87 +8284,87 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H131" t="str">
-        <v>San Francisco, CA • New York, NY • United States</v>
+        <v>Remote - USA</v>
       </c>
       <c r="I131" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J131" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K131" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L131" t="str">
-        <v>https://boards.greenhouse.io/figma/jobs/6119781004</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/8148171</v>
       </c>
       <c r="M131">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N131" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O131" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P131" t="str">
         <v>Today</v>
       </c>
       <c r="Q131" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R131" t="str">
         <v>No</v>
       </c>
       <c r="S131">
-        <v>85</v>
+        <v>73</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>job-714f8c79</v>
+        <v>job-2efe7fb3</v>
       </c>
       <c r="B132" t="str">
-        <v>Product Manager, AI Growth</v>
+        <v>Senior Product Manager, Help Center (CX Automation)</v>
       </c>
       <c r="C132" t="str">
-        <v>Figma</v>
+        <v>Coinbase</v>
       </c>
       <c r="D132" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E132" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F132" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G132" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H132" t="str">
-        <v>San Francisco, CA • New York, NY • United States</v>
+        <v>Remote - India</v>
       </c>
       <c r="I132" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J132" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K132" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L132" t="str">
-        <v>https://boards.greenhouse.io/figma/jobs/5989185004</v>
+        <v>https://boards.greenhouse.io/coinbase/jobs/8031208</v>
       </c>
       <c r="M132">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N132" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O132" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P132" t="str">
         <v>Today</v>
@@ -8373,48 +8373,48 @@
         <v>Yes</v>
       </c>
       <c r="R132" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S132">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>job-6c338367</v>
+        <v>job-1762a9dc</v>
       </c>
       <c r="B133" t="str">
-        <v>Product Manager, Developer Platform</v>
+        <v>Director of Product Management, Agentic Software Delivery</v>
       </c>
       <c r="C133" t="str">
-        <v>Figma</v>
+        <v>GitLab</v>
       </c>
       <c r="D133" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E133" t="str">
-        <v>Technical Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F133" t="str">
-        <v>3-6 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G133" t="str">
-        <v>2-5 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H133" t="str">
-        <v>San Francisco, CA • New York, NY • United States</v>
+        <v>Remote, United States</v>
       </c>
       <c r="I133" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J133" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K133" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L133" t="str">
-        <v>https://boards.greenhouse.io/figma/jobs/6100482004</v>
+        <v>https://boards.greenhouse.io/gitlab/jobs/8806017002</v>
       </c>
       <c r="M133">
         <v>200</v>
@@ -8423,7 +8423,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O133" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P133" t="str">
         <v>Today</v>
@@ -8432,27 +8432,27 @@
         <v>No</v>
       </c>
       <c r="R133" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S133">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>job-3c3dabbf</v>
+        <v>job-58e27f7c</v>
       </c>
       <c r="B134" t="str">
-        <v>Director of Product Management, Advertiser Growth</v>
+        <v>Principal Product Manager, AI Software Factory</v>
       </c>
       <c r="C134" t="str">
-        <v>Pinterest</v>
+        <v>GitLab</v>
       </c>
       <c r="D134" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E134" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F134" t="str">
         <v>8+ yrs</v>
@@ -8461,28 +8461,28 @@
         <v>8+ yrs</v>
       </c>
       <c r="H134" t="str">
-        <v>Palo Alto, CA, US; Seattle, WA, US; New York, NY, US</v>
+        <v>Remote, Canada; Remote, United States</v>
       </c>
       <c r="I134" t="str">
-        <v>New York</v>
+        <v>Remote</v>
       </c>
       <c r="J134" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K134" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L134" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/8132504</v>
+        <v>https://boards.greenhouse.io/gitlab/jobs/8658878002</v>
       </c>
       <c r="M134">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N134" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O134" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P134" t="str">
         <v>Today</v>
@@ -8494,36 +8494,36 @@
         <v>No</v>
       </c>
       <c r="S134">
-        <v>59</v>
+        <v>76</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>job-2ca475a2</v>
+        <v>job-448d861a</v>
       </c>
       <c r="B135" t="str">
-        <v>Product Manager II, Content Compliance</v>
+        <v>Senior Product Manager, Agentic Source Code</v>
       </c>
       <c r="C135" t="str">
-        <v>Pinterest</v>
+        <v>GitLab</v>
       </c>
       <c r="D135" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E135" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F135" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G135" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H135" t="str">
-        <v>San Francisco, CA, US; Seattle, WA, US; Remote, CA, US</v>
+        <v>Remote, Canada; Remote, US</v>
       </c>
       <c r="I135" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J135" t="str">
         <v>Remote</v>
@@ -8532,16 +8532,16 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L135" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/7901910</v>
+        <v>https://boards.greenhouse.io/gitlab/jobs/8597805002</v>
       </c>
       <c r="M135">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N135" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O135" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P135" t="str">
         <v>Today</v>
@@ -8553,36 +8553,36 @@
         <v>No</v>
       </c>
       <c r="S135">
-        <v>45</v>
+        <v>79</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>job-1e7e452c</v>
+        <v>job-6bc28568</v>
       </c>
       <c r="B136" t="str">
-        <v>Product Manager II, Search Experience</v>
+        <v>Senior Product Manager, Secret Detection and Vulnerability Research</v>
       </c>
       <c r="C136" t="str">
-        <v>Pinterest</v>
+        <v>GitLab</v>
       </c>
       <c r="D136" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E136" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F136" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G136" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H136" t="str">
-        <v>San Francisco, CA, US; Remote, US</v>
+        <v>Remote, United States</v>
       </c>
       <c r="I136" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J136" t="str">
         <v>Remote</v>
@@ -8591,16 +8591,16 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L136" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/8042279</v>
+        <v>https://boards.greenhouse.io/gitlab/jobs/8697043002</v>
       </c>
       <c r="M136">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N136" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O136" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P136" t="str">
         <v>Today</v>
@@ -8612,36 +8612,36 @@
         <v>No</v>
       </c>
       <c r="S136">
-        <v>42</v>
+        <v>26</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>job-3070654d</v>
+        <v>job-7ad77ccd</v>
       </c>
       <c r="B137" t="str">
-        <v>Sr. Product Manager, Search Personalization</v>
+        <v>Senior Product Manager, Tenant Scale</v>
       </c>
       <c r="C137" t="str">
-        <v>Pinterest</v>
+        <v>GitLab</v>
       </c>
       <c r="D137" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E137" t="str">
         <v>Senior Product Manager</v>
       </c>
       <c r="F137" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G137" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H137" t="str">
-        <v>San Francisco, CA, US; Remote, US</v>
+        <v>Remote, Canada; Remote, US</v>
       </c>
       <c r="I137" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J137" t="str">
         <v>Remote</v>
@@ -8650,57 +8650,57 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L137" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/8015494</v>
+        <v>https://boards.greenhouse.io/gitlab/jobs/8512220002</v>
       </c>
       <c r="M137">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N137" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O137" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P137" t="str">
         <v>Today</v>
       </c>
       <c r="Q137" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R137" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S137">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>job-2683c45a</v>
+        <v>job-52edb6a4</v>
       </c>
       <c r="B138" t="str">
-        <v>Sr. Product Manager, TwoTwenty</v>
+        <v>Staff Product Manager,  RevOps &amp; Finance Systems</v>
       </c>
       <c r="C138" t="str">
-        <v>Pinterest</v>
+        <v>GitLab</v>
       </c>
       <c r="D138" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E138" t="str">
         <v>Senior Product Manager</v>
       </c>
       <c r="F138" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G138" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H138" t="str">
-        <v>San Francisco, CA, US; Remote, US</v>
+        <v>Remote, US</v>
       </c>
       <c r="I138" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J138" t="str">
         <v>Remote</v>
@@ -8709,57 +8709,57 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L138" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/8015519</v>
+        <v>https://boards.greenhouse.io/gitlab/jobs/8612937002</v>
       </c>
       <c r="M138">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N138" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O138" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P138" t="str">
         <v>Today</v>
       </c>
       <c r="Q138" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R138" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S138">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>job-04d22fdc</v>
+        <v>job-3a743e4f</v>
       </c>
       <c r="B139" t="str">
-        <v>Staff Product Manager, Ads Measurement</v>
+        <v>Manager, Product Management - Figma Platform Experience</v>
       </c>
       <c r="C139" t="str">
-        <v>Pinterest</v>
+        <v>Figma</v>
       </c>
       <c r="D139" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E139" t="str">
-        <v>Senior Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F139" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G139" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H139" t="str">
-        <v>New York, NY, US</v>
+        <v>San Francisco, CA • New York, NY • United States</v>
       </c>
       <c r="I139" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J139" t="str">
         <v>On-site</v>
@@ -8768,75 +8768,75 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L139" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/7683962</v>
+        <v>https://boards.greenhouse.io/figma/jobs/6160732004</v>
       </c>
       <c r="M139">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N139" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O139" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P139" t="str">
         <v>Today</v>
       </c>
       <c r="Q139" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R139" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S139">
-        <v>48</v>
+        <v>53</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>job-336a1df9</v>
+        <v>job-7297f499</v>
       </c>
       <c r="B140" t="str">
-        <v>Staff Product Manager, Applied Science</v>
+        <v>Manager, Product Management - Roundtripping</v>
       </c>
       <c r="C140" t="str">
-        <v>Pinterest</v>
+        <v>Figma</v>
       </c>
       <c r="D140" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E140" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F140" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G140" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H140" t="str">
-        <v>San Francisco, CA, US; Remote, US</v>
+        <v>New York, NY • United States</v>
       </c>
       <c r="I140" t="str">
-        <v>San Francisco</v>
+        <v>New York</v>
       </c>
       <c r="J140" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K140" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L140" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/8082033</v>
+        <v>https://boards.greenhouse.io/figma/jobs/6104919004</v>
       </c>
       <c r="M140">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N140" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O140" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P140" t="str">
         <v>Today</v>
@@ -8845,57 +8845,57 @@
         <v>No</v>
       </c>
       <c r="R140" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S140">
-        <v>61</v>
+        <v>87</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>job-7e8b8408</v>
+        <v>job-19031a2a</v>
       </c>
       <c r="B141" t="str">
-        <v>Staff Product Manager, Programmatic Ads</v>
+        <v>Manager, Product Management - Roundtripping (London, United Kingdom)</v>
       </c>
       <c r="C141" t="str">
-        <v>Pinterest</v>
+        <v>Figma</v>
       </c>
       <c r="D141" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E141" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F141" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G141" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H141" t="str">
-        <v>San Francisco, CA, US; Remote, CA, US</v>
+        <v>London, England</v>
       </c>
       <c r="I141" t="str">
-        <v>San Francisco</v>
+        <v>London</v>
       </c>
       <c r="J141" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K141" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L141" t="str">
-        <v>https://boards.greenhouse.io/pinterest/jobs/7959458</v>
+        <v>https://boards.greenhouse.io/figma/jobs/6149007004</v>
       </c>
       <c r="M141">
-        <v>403</v>
+        <v>200</v>
       </c>
       <c r="N141" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O141" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P141" t="str">
         <v>Today</v>
@@ -8912,40 +8912,40 @@
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>job-7f4873ac</v>
+        <v>job-099ff647</v>
       </c>
       <c r="B142" t="str">
-        <v>Director of Product, Logistics</v>
+        <v>Product Manager, Acquisition</v>
       </c>
       <c r="C142" t="str">
-        <v>Instacart</v>
+        <v>Figma</v>
       </c>
       <c r="D142" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E142" t="str">
-        <v>Product Lead / Director</v>
+        <v>Product Manager</v>
       </c>
       <c r="F142" t="str">
-        <v>8+ yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G142" t="str">
-        <v>8+ yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H142" t="str">
-        <v>United States - Remote</v>
+        <v>San Francisco, CA • New York, NY • United States</v>
       </c>
       <c r="I142" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J142" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K142" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L142" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8198282</v>
+        <v>https://boards.greenhouse.io/figma/jobs/6119781004</v>
       </c>
       <c r="M142">
         <v>200</v>
@@ -8954,7 +8954,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O142" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P142" t="str">
         <v>Today</v>
@@ -8963,48 +8963,48 @@
         <v>No</v>
       </c>
       <c r="R142" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S142">
-        <v>44</v>
+        <v>54</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>job-6d240672</v>
+        <v>job-714f8c79</v>
       </c>
       <c r="B143" t="str">
-        <v>Senior Product Manager, Ads Quality</v>
+        <v>Product Manager, AI Growth</v>
       </c>
       <c r="C143" t="str">
-        <v>Instacart</v>
+        <v>Figma</v>
       </c>
       <c r="D143" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E143" t="str">
-        <v>Senior Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F143" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G143" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H143" t="str">
-        <v>United States - Remote</v>
+        <v>San Francisco, CA • New York, NY • United States</v>
       </c>
       <c r="I143" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J143" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K143" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L143" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8077510</v>
+        <v>https://boards.greenhouse.io/figma/jobs/5989185004</v>
       </c>
       <c r="M143">
         <v>200</v>
@@ -9013,7 +9013,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O143" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P143" t="str">
         <v>Today</v>
@@ -9022,48 +9022,48 @@
         <v>No</v>
       </c>
       <c r="R143" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S143">
-        <v>94</v>
+        <v>61</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>job-2be59ce2</v>
+        <v>job-6c338367</v>
       </c>
       <c r="B144" t="str">
-        <v>Senior Product Manager, Advertiser Experience</v>
+        <v>Product Manager, Developer Platform</v>
       </c>
       <c r="C144" t="str">
-        <v>Instacart</v>
+        <v>Figma</v>
       </c>
       <c r="D144" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E144" t="str">
-        <v>Senior Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F144" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G144" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H144" t="str">
-        <v>United States - Remote</v>
+        <v>San Francisco, CA • New York, NY • United States</v>
       </c>
       <c r="I144" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J144" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K144" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L144" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8120469</v>
+        <v>https://boards.greenhouse.io/figma/jobs/6100482004</v>
       </c>
       <c r="M144">
         <v>200</v>
@@ -9072,7 +9072,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O144" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P144" t="str">
         <v>Today</v>
@@ -9081,98 +9081,98 @@
         <v>No</v>
       </c>
       <c r="R144" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S144">
-        <v>68</v>
+        <v>48</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>job-69064914</v>
+        <v>job-3c3dabbf</v>
       </c>
       <c r="B145" t="str">
-        <v>Senior Product Manager, AI Control Studio</v>
+        <v>Director of Product Management, Advertiser Growth</v>
       </c>
       <c r="C145" t="str">
-        <v>Instacart</v>
+        <v>Pinterest</v>
       </c>
       <c r="D145" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E145" t="str">
-        <v>Senior Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F145" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G145" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H145" t="str">
-        <v>United States - Remote</v>
+        <v>Palo Alto, CA, US; Seattle, WA, US; New York, NY, US</v>
       </c>
       <c r="I145" t="str">
-        <v>Remote</v>
+        <v>New York</v>
       </c>
       <c r="J145" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K145" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L145" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8198159</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/8132504</v>
       </c>
       <c r="M145">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N145" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O145" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P145" t="str">
         <v>Today</v>
       </c>
       <c r="Q145" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R145" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S145">
-        <v>47</v>
+        <v>70</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>job-6ddb2cbc</v>
+        <v>job-2ca475a2</v>
       </c>
       <c r="B146" t="str">
-        <v>Senior Product Manager, Catalog</v>
+        <v>Product Manager II, Content Compliance</v>
       </c>
       <c r="C146" t="str">
-        <v>Instacart</v>
+        <v>Pinterest</v>
       </c>
       <c r="D146" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E146" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F146" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G146" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H146" t="str">
-        <v>United States - Remote</v>
+        <v>San Francisco, CA, US; Seattle, WA, US; Remote, CA, US</v>
       </c>
       <c r="I146" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J146" t="str">
         <v>Remote</v>
@@ -9181,57 +9181,57 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L146" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8143270</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/7901910</v>
       </c>
       <c r="M146">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N146" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O146" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P146" t="str">
         <v>Today</v>
       </c>
       <c r="Q146" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R146" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S146">
-        <v>60</v>
+        <v>46</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>job-3d0cfe30</v>
+        <v>job-1e7e452c</v>
       </c>
       <c r="B147" t="str">
-        <v>Senior Product Manager, Order Quality</v>
+        <v>Product Manager II, Search Experience</v>
       </c>
       <c r="C147" t="str">
-        <v>Instacart</v>
+        <v>Pinterest</v>
       </c>
       <c r="D147" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E147" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F147" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G147" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H147" t="str">
-        <v>United States - Remote</v>
+        <v>San Francisco, CA, US; Remote, US</v>
       </c>
       <c r="I147" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J147" t="str">
         <v>Remote</v>
@@ -9240,39 +9240,39 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L147" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8203107</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/8042279</v>
       </c>
       <c r="M147">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N147" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O147" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P147" t="str">
         <v>Today</v>
       </c>
       <c r="Q147" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R147" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S147">
-        <v>68</v>
+        <v>78</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>job-2319ed86</v>
+        <v>job-3070654d</v>
       </c>
       <c r="B148" t="str">
-        <v>Senior Product Manager, Retailer Platform</v>
+        <v>Sr. Product Manager, Search Personalization</v>
       </c>
       <c r="C148" t="str">
-        <v>Instacart</v>
+        <v>Pinterest</v>
       </c>
       <c r="D148" t="str">
         <v>LinkedIn</v>
@@ -9281,16 +9281,16 @@
         <v>Senior Product Manager</v>
       </c>
       <c r="F148" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G148" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H148" t="str">
-        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
+        <v>San Francisco, CA, US; Remote, US</v>
       </c>
       <c r="I148" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J148" t="str">
         <v>Remote</v>
@@ -9299,45 +9299,45 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L148" t="str">
-        <v>https://boards.greenhouse.io/instacart/jobs/8014062</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/8015494</v>
       </c>
       <c r="M148">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N148" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O148" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P148" t="str">
         <v>Today</v>
       </c>
       <c r="Q148" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R148" t="str">
         <v>No</v>
       </c>
       <c r="S148">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>job-6d0cde89</v>
+        <v>job-2683c45a</v>
       </c>
       <c r="B149" t="str">
-        <v>Product Manager II - Ads</v>
+        <v>Sr. Product Manager, TwoTwenty</v>
       </c>
       <c r="C149" t="str">
-        <v>Razorpay</v>
+        <v>Pinterest</v>
       </c>
       <c r="D149" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E149" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F149" t="str">
         <v>3-6 yrs</v>
@@ -9346,69 +9346,69 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H149" t="str">
-        <v>Bengaluru</v>
+        <v>San Francisco, CA, US; Remote, US</v>
       </c>
       <c r="I149" t="str">
-        <v>Bengaluru</v>
+        <v>San Francisco</v>
       </c>
       <c r="J149" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K149" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L149" t="str">
-        <v>https://boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4729533005</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/8015519</v>
       </c>
       <c r="M149">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N149" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O149" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P149" t="str">
         <v>Today</v>
       </c>
       <c r="Q149" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R149" t="str">
         <v>No</v>
       </c>
       <c r="S149">
-        <v>84</v>
+        <v>57</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>job-7c247a79</v>
+        <v>job-04d22fdc</v>
       </c>
       <c r="B150" t="str">
-        <v>Product Manager II - AI</v>
+        <v>Staff Product Manager, Ads Measurement</v>
       </c>
       <c r="C150" t="str">
-        <v>Razorpay</v>
+        <v>Pinterest</v>
       </c>
       <c r="D150" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E150" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F150" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G150" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H150" t="str">
-        <v>Bengaluru</v>
+        <v>New York, NY, US</v>
       </c>
       <c r="I150" t="str">
-        <v>Bengaluru</v>
+        <v>New York</v>
       </c>
       <c r="J150" t="str">
         <v>On-site</v>
@@ -9417,75 +9417,75 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L150" t="str">
-        <v>https://boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4699107005</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/7683962</v>
       </c>
       <c r="M150">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N150" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O150" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P150" t="str">
         <v>Today</v>
       </c>
       <c r="Q150" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R150" t="str">
         <v>No</v>
       </c>
       <c r="S150">
-        <v>74</v>
+        <v>30</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>job-1c3166e2</v>
+        <v>job-336a1df9</v>
       </c>
       <c r="B151" t="str">
-        <v>Product Manager, API Agents</v>
+        <v>Staff Product Manager, Applied Science</v>
       </c>
       <c r="C151" t="str">
-        <v>OpenAI</v>
+        <v>Pinterest</v>
       </c>
       <c r="D151" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E151" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F151" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G151" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H151" t="str">
-        <v>San Francisco</v>
+        <v>San Francisco, CA, US; Remote, US</v>
       </c>
       <c r="I151" t="str">
         <v>San Francisco</v>
       </c>
       <c r="J151" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K151" t="str">
-        <v>$160k - $240k USD + Equity</v>
+        <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L151" t="str">
-        <v>https://jobs.ashbyhq.com/openai/fc38c6bf-5330-435c-99b6-1bcf1f5829a8</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/8082033</v>
       </c>
       <c r="M151">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N151" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O151" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P151" t="str">
         <v>Today</v>
@@ -9497,104 +9497,104 @@
         <v>No</v>
       </c>
       <c r="S151">
-        <v>99</v>
+        <v>79</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>job-6d2b24fc</v>
+        <v>job-7e8b8408</v>
       </c>
       <c r="B152" t="str">
-        <v>Product Manager, Sensitive Deployments</v>
+        <v>Staff Product Manager, Programmatic Ads</v>
       </c>
       <c r="C152" t="str">
-        <v>OpenAI</v>
+        <v>Pinterest</v>
       </c>
       <c r="D152" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E152" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F152" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G152" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H152" t="str">
-        <v>San Francisco</v>
+        <v>San Francisco, CA, US; Remote, CA, US</v>
       </c>
       <c r="I152" t="str">
         <v>San Francisco</v>
       </c>
       <c r="J152" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K152" t="str">
-        <v>$160k - $240k USD + Equity</v>
+        <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L152" t="str">
-        <v>https://jobs.ashbyhq.com/openai/05a8cae8-81bd-4f7b-bc48-41ef1bd67e5d</v>
+        <v>https://boards.greenhouse.io/pinterest/jobs/7959458</v>
       </c>
       <c r="M152">
-        <v>200</v>
+        <v>403</v>
       </c>
       <c r="N152" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O152" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P152" t="str">
         <v>Today</v>
       </c>
       <c r="Q152" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R152" t="str">
         <v>No</v>
       </c>
       <c r="S152">
-        <v>73</v>
+        <v>59</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>job-184a9e13</v>
+        <v>job-7f4873ac</v>
       </c>
       <c r="B153" t="str">
-        <v>Product Manager, API Infrastructure</v>
+        <v>Director of Product, Logistics</v>
       </c>
       <c r="C153" t="str">
-        <v>OpenAI</v>
+        <v>Instacart</v>
       </c>
       <c r="D153" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E153" t="str">
-        <v>Technical Product Manager</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F153" t="str">
-        <v>3-6 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G153" t="str">
-        <v>2-5 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H153" t="str">
-        <v>San Francisco</v>
+        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
       </c>
       <c r="I153" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J153" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K153" t="str">
-        <v>$160k - $240k USD + Equity</v>
+        <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L153" t="str">
-        <v>https://jobs.ashbyhq.com/openai/7ffa2a14-fa9c-46cb-a30a-1f7a35ae904a</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8198284</v>
       </c>
       <c r="M153">
         <v>200</v>
@@ -9603,7 +9603,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O153" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P153" t="str">
         <v>Today</v>
@@ -9615,45 +9615,45 @@
         <v>Yes</v>
       </c>
       <c r="S153">
-        <v>67</v>
+        <v>77</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>job-61ec6778</v>
+        <v>job-6d240672</v>
       </c>
       <c r="B154" t="str">
-        <v>Product Manager, Safety Measurement</v>
+        <v>Senior Product Manager, Ads Quality</v>
       </c>
       <c r="C154" t="str">
-        <v>OpenAI</v>
+        <v>Instacart</v>
       </c>
       <c r="D154" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E154" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F154" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G154" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H154" t="str">
-        <v>San Francisco</v>
+        <v>United States - Remote</v>
       </c>
       <c r="I154" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J154" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K154" t="str">
-        <v>$160k - $240k USD + Equity</v>
+        <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L154" t="str">
-        <v>https://jobs.ashbyhq.com/openai/fbc7ebaf-3a26-406d-9ff6-f166f3e246a2</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8077510</v>
       </c>
       <c r="M154">
         <v>200</v>
@@ -9662,7 +9662,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O154" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P154" t="str">
         <v>Today</v>
@@ -9671,48 +9671,48 @@
         <v>Yes</v>
       </c>
       <c r="R154" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S154">
-        <v>93</v>
+        <v>63</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>job-32d0b9c4</v>
+        <v>job-2be59ce2</v>
       </c>
       <c r="B155" t="str">
-        <v>Product Manager, Financial Engineering</v>
+        <v>Senior Product Manager, Advertiser Experience</v>
       </c>
       <c r="C155" t="str">
-        <v>OpenAI</v>
+        <v>Instacart</v>
       </c>
       <c r="D155" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E155" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F155" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G155" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H155" t="str">
-        <v>San Francisco</v>
+        <v>Canada - Remote (ON, AB, BC, or NS Only)</v>
       </c>
       <c r="I155" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J155" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K155" t="str">
-        <v>$160k - $240k USD + Equity</v>
+        <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L155" t="str">
-        <v>https://jobs.ashbyhq.com/openai/0f4da2b4-df8a-4560-809d-d0a6ac1ad9bc</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8120471</v>
       </c>
       <c r="M155">
         <v>200</v>
@@ -9721,57 +9721,57 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O155" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P155" t="str">
         <v>Today</v>
       </c>
       <c r="Q155" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R155" t="str">
         <v>Yes</v>
       </c>
       <c r="S155">
-        <v>65</v>
+        <v>44</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>job-675130d5</v>
+        <v>job-69064914</v>
       </c>
       <c r="B156" t="str">
-        <v>Product Manager, Core Models</v>
+        <v>Senior Product Manager, AI Control Studio</v>
       </c>
       <c r="C156" t="str">
-        <v>OpenAI</v>
+        <v>Instacart</v>
       </c>
       <c r="D156" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E156" t="str">
-        <v>Technical Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F156" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G156" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H156" t="str">
-        <v>San Francisco</v>
+        <v>United States - Remote</v>
       </c>
       <c r="I156" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J156" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K156" t="str">
-        <v>$160k - $240k USD + Equity</v>
+        <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L156" t="str">
-        <v>https://jobs.ashbyhq.com/openai/33b8effb-b048-4934-a279-87fff192a330</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8198159</v>
       </c>
       <c r="M156">
         <v>200</v>
@@ -9780,7 +9780,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O156" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P156" t="str">
         <v>Today</v>
@@ -9789,48 +9789,48 @@
         <v>Yes</v>
       </c>
       <c r="R156" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S156">
-        <v>78</v>
+        <v>54</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>job-032480cd</v>
+        <v>job-6ddb2cbc</v>
       </c>
       <c r="B157" t="str">
-        <v>Product Manager, Youth</v>
+        <v>Senior Product Manager, Catalog</v>
       </c>
       <c r="C157" t="str">
-        <v>OpenAI</v>
+        <v>Instacart</v>
       </c>
       <c r="D157" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E157" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F157" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G157" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H157" t="str">
-        <v>San Francisco</v>
+        <v>United States - Remote</v>
       </c>
       <c r="I157" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J157" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K157" t="str">
-        <v>$160k - $240k USD + Equity</v>
+        <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L157" t="str">
-        <v>https://jobs.ashbyhq.com/openai/cc0d0d86-eb9d-44a0-a6a4-42bbb6066b4b</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8143270</v>
       </c>
       <c r="M157">
         <v>200</v>
@@ -9839,57 +9839,57 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O157" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P157" t="str">
         <v>Today</v>
       </c>
       <c r="Q157" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R157" t="str">
         <v>No</v>
       </c>
       <c r="S157">
-        <v>109</v>
+        <v>41</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>job-50e54898</v>
+        <v>job-3d0cfe30</v>
       </c>
       <c r="B158" t="str">
-        <v>Product Manager, Learning</v>
+        <v>Senior Product Manager, Order Quality</v>
       </c>
       <c r="C158" t="str">
-        <v>OpenAI</v>
+        <v>Instacart</v>
       </c>
       <c r="D158" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E158" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F158" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G158" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H158" t="str">
-        <v>San Francisco</v>
+        <v>United States - Remote</v>
       </c>
       <c r="I158" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J158" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K158" t="str">
-        <v>$160k - $240k USD + Equity</v>
+        <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L158" t="str">
-        <v>https://jobs.ashbyhq.com/openai/5953fed7-1466-4e90-94c9-43716a55e032</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8203107</v>
       </c>
       <c r="M158">
         <v>200</v>
@@ -9898,7 +9898,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O158" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P158" t="str">
         <v>Today</v>
@@ -9910,45 +9910,45 @@
         <v>No</v>
       </c>
       <c r="S158">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>job-0df96522</v>
+        <v>job-2319ed86</v>
       </c>
       <c r="B159" t="str">
-        <v>Product Manager, Multimodal Safety</v>
+        <v>Senior Product Manager, Retailer Platform</v>
       </c>
       <c r="C159" t="str">
-        <v>OpenAI</v>
+        <v>Instacart</v>
       </c>
       <c r="D159" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E159" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F159" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G159" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H159" t="str">
-        <v>San Francisco</v>
+        <v>United States - Remote</v>
       </c>
       <c r="I159" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J159" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K159" t="str">
-        <v>$160k - $240k USD + Equity</v>
+        <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L159" t="str">
-        <v>https://jobs.ashbyhq.com/openai/70d5259a-f18c-4595-bf52-ec03eeeeac4c</v>
+        <v>https://boards.greenhouse.io/instacart/jobs/8014060</v>
       </c>
       <c r="M159">
         <v>200</v>
@@ -9957,30 +9957,30 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O159" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P159" t="str">
         <v>Today</v>
       </c>
       <c r="Q159" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R159" t="str">
         <v>No</v>
       </c>
       <c r="S159">
-        <v>58</v>
+        <v>77</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>job-47895783</v>
+        <v>job-6d0cde89</v>
       </c>
       <c r="B160" t="str">
-        <v>Product Manager, Enterprise Identity</v>
+        <v>Product Manager II - Ads</v>
       </c>
       <c r="C160" t="str">
-        <v>OpenAI</v>
+        <v>Razorpay</v>
       </c>
       <c r="D160" t="str">
         <v>LinkedIn</v>
@@ -9995,28 +9995,28 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H160" t="str">
-        <v>San Francisco</v>
+        <v>Bengaluru</v>
       </c>
       <c r="I160" t="str">
-        <v>San Francisco</v>
+        <v>Bengaluru</v>
       </c>
       <c r="J160" t="str">
         <v>On-site</v>
       </c>
       <c r="K160" t="str">
-        <v>$160k - $240k USD + Equity</v>
+        <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L160" t="str">
-        <v>https://jobs.ashbyhq.com/openai/83f6d415-9462-4afc-a539-ca8d996e011a</v>
-      </c>
-      <c r="M160">
-        <v>200</v>
+        <v>https://boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4729533005</v>
+      </c>
+      <c r="M160" t="str">
+        <v>ACTIVE_PORTAL</v>
       </c>
       <c r="N160" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O160" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P160" t="str">
         <v>Today</v>
@@ -10028,24 +10028,24 @@
         <v>No</v>
       </c>
       <c r="S160">
-        <v>94</v>
+        <v>31</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>job-3fd38143</v>
+        <v>job-7c247a79</v>
       </c>
       <c r="B161" t="str">
-        <v>Rosalind Life Sciences Product Manager</v>
+        <v>Product Manager II - AI</v>
       </c>
       <c r="C161" t="str">
-        <v>OpenAI</v>
+        <v>Razorpay</v>
       </c>
       <c r="D161" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E161" t="str">
-        <v>Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F161" t="str">
         <v>3-6 yrs</v>
@@ -10054,19 +10054,19 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H161" t="str">
-        <v>San Francisco</v>
+        <v>Bengaluru</v>
       </c>
       <c r="I161" t="str">
-        <v>San Francisco</v>
+        <v>Bengaluru</v>
       </c>
       <c r="J161" t="str">
         <v>On-site</v>
       </c>
       <c r="K161" t="str">
-        <v>$160k - $240k USD + Equity</v>
+        <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L161" t="str">
-        <v>https://jobs.ashbyhq.com/openai/2b5c3a30-8e8b-4845-be40-0617b0c9fd43</v>
+        <v>https://boards.greenhouse.io/razorpaysoftwareprivatelimited/jobs/4699107005</v>
       </c>
       <c r="M161">
         <v>200</v>
@@ -10075,27 +10075,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O161" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P161" t="str">
         <v>Today</v>
       </c>
       <c r="Q161" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R161" t="str">
         <v>No</v>
       </c>
       <c r="S161">
-        <v>85</v>
+        <v>25</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>job-1fef334a</v>
+        <v>job-1c3166e2</v>
       </c>
       <c r="B162" t="str">
-        <v>Product Manager, Technology Vertical</v>
+        <v>Product Manager, API Agents</v>
       </c>
       <c r="C162" t="str">
         <v>OpenAI</v>
@@ -10104,7 +10104,7 @@
         <v>LinkedIn</v>
       </c>
       <c r="E162" t="str">
-        <v>Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F162" t="str">
         <v>3-6 yrs</v>
@@ -10125,7 +10125,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L162" t="str">
-        <v>https://jobs.ashbyhq.com/openai/137e3df0-2bd4-4ad4-8edb-8455a7fdc912</v>
+        <v>https://jobs.ashbyhq.com/openai/fc38c6bf-5330-435c-99b6-1bcf1f5829a8</v>
       </c>
       <c r="M162">
         <v>200</v>
@@ -10134,7 +10134,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O162" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P162" t="str">
         <v>Today</v>
@@ -10143,24 +10143,24 @@
         <v>Yes</v>
       </c>
       <c r="R162" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S162">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>job-5db12f92</v>
+        <v>job-6d2b24fc</v>
       </c>
       <c r="B163" t="str">
-        <v>Product Manager (Builder)</v>
+        <v>Product Manager, Sensitive Deployments</v>
       </c>
       <c r="C163" t="str">
-        <v>Perplexity</v>
+        <v>OpenAI</v>
       </c>
       <c r="D163" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E163" t="str">
         <v>Product Manager</v>
@@ -10184,7 +10184,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L163" t="str">
-        <v>https://jobs.ashbyhq.com/perplexity/f25e190e-0508-4707-b575-fcaed358dc13</v>
+        <v>https://jobs.ashbyhq.com/openai/05a8cae8-81bd-4f7b-bc48-41ef1bd67e5d</v>
       </c>
       <c r="M163">
         <v>200</v>
@@ -10193,7 +10193,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O163" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P163" t="str">
         <v>Today</v>
@@ -10205,30 +10205,30 @@
         <v>No</v>
       </c>
       <c r="S163">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>job-1fe57ea5</v>
+        <v>job-184a9e13</v>
       </c>
       <c r="B164" t="str">
-        <v>Member of Technical Staff (TPM, Inference)</v>
+        <v>Product Manager, API Infrastructure</v>
       </c>
       <c r="C164" t="str">
-        <v>Perplexity</v>
+        <v>OpenAI</v>
       </c>
       <c r="D164" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E164" t="str">
-        <v>Senior Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F164" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G164" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H164" t="str">
         <v>San Francisco</v>
@@ -10243,7 +10243,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L164" t="str">
-        <v>https://jobs.ashbyhq.com/perplexity/0c5d5a82-bfed-4786-b411-79073979af07</v>
+        <v>https://jobs.ashbyhq.com/openai/7ffa2a14-fa9c-46cb-a30a-1f7a35ae904a</v>
       </c>
       <c r="M164">
         <v>200</v>
@@ -10252,7 +10252,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O164" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P164" t="str">
         <v>Today</v>
@@ -10261,24 +10261,24 @@
         <v>Yes</v>
       </c>
       <c r="R164" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S164">
-        <v>116</v>
+        <v>91</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>job-12403072</v>
+        <v>job-61ec6778</v>
       </c>
       <c r="B165" t="str">
-        <v>Product Manager, Mobile Apps</v>
+        <v>Product Manager, Safety Measurement</v>
       </c>
       <c r="C165" t="str">
-        <v>Perplexity</v>
+        <v>OpenAI</v>
       </c>
       <c r="D165" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E165" t="str">
         <v>Product Manager</v>
@@ -10302,7 +10302,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L165" t="str">
-        <v>https://jobs.ashbyhq.com/perplexity/3c9c051f-e6ca-4a70-9abf-1f640e154ee1</v>
+        <v>https://jobs.ashbyhq.com/openai/fbc7ebaf-3a26-406d-9ff6-f166f3e246a2</v>
       </c>
       <c r="M165">
         <v>200</v>
@@ -10311,7 +10311,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O165" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P165" t="str">
         <v>Today</v>
@@ -10323,24 +10323,24 @@
         <v>No</v>
       </c>
       <c r="S165">
-        <v>43</v>
+        <v>107</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>job-10379173</v>
+        <v>job-32d0b9c4</v>
       </c>
       <c r="B166" t="str">
-        <v>Product Manager, Core Experience</v>
+        <v>Product Manager, Financial Engineering</v>
       </c>
       <c r="C166" t="str">
-        <v>Perplexity</v>
+        <v>OpenAI</v>
       </c>
       <c r="D166" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E166" t="str">
-        <v>Technical Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F166" t="str">
         <v>3-6 yrs</v>
@@ -10361,7 +10361,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L166" t="str">
-        <v>https://jobs.ashbyhq.com/perplexity/6f3c5131-2efa-400c-8248-44203a4dbfbb</v>
+        <v>https://jobs.ashbyhq.com/openai/0f4da2b4-df8a-4560-809d-d0a6ac1ad9bc</v>
       </c>
       <c r="M166">
         <v>200</v>
@@ -10370,7 +10370,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O166" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P166" t="str">
         <v>Today</v>
@@ -10382,24 +10382,24 @@
         <v>Yes</v>
       </c>
       <c r="S166">
-        <v>101</v>
+        <v>108</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>job-247da510</v>
+        <v>job-675130d5</v>
       </c>
       <c r="B167" t="str">
-        <v>Product Manager, AI Capabilities</v>
+        <v>Product Manager, Core Models</v>
       </c>
       <c r="C167" t="str">
-        <v>Perplexity</v>
+        <v>OpenAI</v>
       </c>
       <c r="D167" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E167" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F167" t="str">
         <v>3-6 yrs</v>
@@ -10420,7 +10420,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L167" t="str">
-        <v>https://jobs.ashbyhq.com/perplexity/7f880194-7276-4b46-8a50-58b48da8882e</v>
+        <v>https://jobs.ashbyhq.com/openai/33b8effb-b048-4934-a279-87fff192a330</v>
       </c>
       <c r="M167">
         <v>200</v>
@@ -10429,7 +10429,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O167" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P167" t="str">
         <v>Today</v>
@@ -10438,27 +10438,27 @@
         <v>Yes</v>
       </c>
       <c r="R167" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S167">
-        <v>53</v>
+        <v>40</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>job-757a314d</v>
+        <v>job-032480cd</v>
       </c>
       <c r="B168" t="str">
-        <v>Product Manager, Growth</v>
+        <v>Product Manager, Youth</v>
       </c>
       <c r="C168" t="str">
-        <v>Perplexity</v>
+        <v>OpenAI</v>
       </c>
       <c r="D168" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E168" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Product Manager</v>
       </c>
       <c r="F168" t="str">
         <v>3-6 yrs</v>
@@ -10467,10 +10467,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H168" t="str">
-        <v>New York City</v>
+        <v>San Francisco</v>
       </c>
       <c r="I168" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J168" t="str">
         <v>On-site</v>
@@ -10479,7 +10479,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L168" t="str">
-        <v>https://jobs.ashbyhq.com/perplexity/fa088d92-b08b-43f7-9232-275b0ae08827</v>
+        <v>https://jobs.ashbyhq.com/openai/cc0d0d86-eb9d-44a0-a6a4-42bbb6066b4b</v>
       </c>
       <c r="M168">
         <v>200</v>
@@ -10488,7 +10488,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O168" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P168" t="str">
         <v>Today</v>
@@ -10497,27 +10497,27 @@
         <v>Yes</v>
       </c>
       <c r="R168" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S168">
-        <v>81</v>
+        <v>112</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>job-376e5ff5</v>
+        <v>job-50e54898</v>
       </c>
       <c r="B169" t="str">
-        <v>Product Manager, SMB Growth</v>
+        <v>Product Manager, Learning</v>
       </c>
       <c r="C169" t="str">
-        <v>Perplexity</v>
+        <v>OpenAI</v>
       </c>
       <c r="D169" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E169" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Product Manager</v>
       </c>
       <c r="F169" t="str">
         <v>3-6 yrs</v>
@@ -10526,10 +10526,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H169" t="str">
-        <v>New York City</v>
+        <v>San Francisco</v>
       </c>
       <c r="I169" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J169" t="str">
         <v>On-site</v>
@@ -10538,7 +10538,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L169" t="str">
-        <v>https://jobs.ashbyhq.com/perplexity/182ab2ec-6fb1-409b-a2dc-63c7832b0a13</v>
+        <v>https://jobs.ashbyhq.com/openai/5953fed7-1466-4e90-94c9-43716a55e032</v>
       </c>
       <c r="M169">
         <v>200</v>
@@ -10547,7 +10547,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O169" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P169" t="str">
         <v>Today</v>
@@ -10556,24 +10556,24 @@
         <v>Yes</v>
       </c>
       <c r="R169" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S169">
-        <v>44</v>
+        <v>112</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>job-6fff938e</v>
+        <v>job-0df96522</v>
       </c>
       <c r="B170" t="str">
-        <v>Product Manager - Marketplace</v>
+        <v>Product Manager, Multimodal Safety</v>
       </c>
       <c r="C170" t="str">
-        <v>Supabase</v>
+        <v>OpenAI</v>
       </c>
       <c r="D170" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E170" t="str">
         <v>Product Manager</v>
@@ -10585,19 +10585,19 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H170" t="str">
-        <v>Remote, Global</v>
+        <v>San Francisco</v>
       </c>
       <c r="I170" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J170" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K170" t="str">
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L170" t="str">
-        <v>https://jobs.ashbyhq.com/supabase/23c9ce7e-6b7b-4316-8f00-8f318e902441</v>
+        <v>https://jobs.ashbyhq.com/openai/70d5259a-f18c-4595-bf52-ec03eeeeac4c</v>
       </c>
       <c r="M170">
         <v>200</v>
@@ -10606,7 +10606,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O170" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P170" t="str">
         <v>Today</v>
@@ -10615,24 +10615,24 @@
         <v>Yes</v>
       </c>
       <c r="R170" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S170">
-        <v>58</v>
+        <v>79</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>job-49f97312</v>
+        <v>job-47895783</v>
       </c>
       <c r="B171" t="str">
-        <v>Product Manager - Security &amp; Trust (EMEA/AMER)</v>
+        <v>Product Manager, Enterprise Identity</v>
       </c>
       <c r="C171" t="str">
-        <v>Supabase</v>
+        <v>OpenAI</v>
       </c>
       <c r="D171" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E171" t="str">
         <v>Product Manager</v>
@@ -10644,19 +10644,19 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H171" t="str">
-        <v>Remote, Global</v>
+        <v>San Francisco</v>
       </c>
       <c r="I171" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J171" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K171" t="str">
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L171" t="str">
-        <v>https://jobs.ashbyhq.com/supabase/b8010a28-109c-46a9-b8b7-c7f9b24077fa</v>
+        <v>https://jobs.ashbyhq.com/openai/83f6d415-9462-4afc-a539-ca8d996e011a</v>
       </c>
       <c r="M171">
         <v>200</v>
@@ -10665,7 +10665,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O171" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P171" t="str">
         <v>Today</v>
@@ -10674,24 +10674,24 @@
         <v>Yes</v>
       </c>
       <c r="R171" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S171">
-        <v>49</v>
+        <v>68</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>job-064fa6b5</v>
+        <v>job-3fd38143</v>
       </c>
       <c r="B172" t="str">
-        <v>Product Manager - Strategic Partner Integrations (Bay Area based)</v>
+        <v>Rosalind Life Sciences Product Manager</v>
       </c>
       <c r="C172" t="str">
-        <v>Supabase</v>
+        <v>OpenAI</v>
       </c>
       <c r="D172" t="str">
-        <v>Wellfound</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E172" t="str">
         <v>Product Manager</v>
@@ -10703,19 +10703,19 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H172" t="str">
-        <v>Remote, Bay Area, CA</v>
+        <v>San Francisco</v>
       </c>
       <c r="I172" t="str">
         <v>San Francisco</v>
       </c>
       <c r="J172" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K172" t="str">
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L172" t="str">
-        <v>https://jobs.ashbyhq.com/supabase/68a397e7-8a1a-4566-ae41-e8c61dd6ed93</v>
+        <v>https://jobs.ashbyhq.com/openai/2b5c3a30-8e8b-4845-be40-0617b0c9fd43</v>
       </c>
       <c r="M172">
         <v>200</v>
@@ -10724,7 +10724,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O172" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P172" t="str">
         <v>Today</v>
@@ -10733,27 +10733,27 @@
         <v>Yes</v>
       </c>
       <c r="R172" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S172">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>job-7da017c6</v>
+        <v>job-1fef334a</v>
       </c>
       <c r="B173" t="str">
-        <v>Product Manager | Vendor Intelligence &amp; Marketplace</v>
+        <v>Product Manager, Technology Vertical</v>
       </c>
       <c r="C173" t="str">
-        <v>Ramp</v>
+        <v>OpenAI</v>
       </c>
       <c r="D173" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E173" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Product Manager</v>
       </c>
       <c r="F173" t="str">
         <v>3-6 yrs</v>
@@ -10762,10 +10762,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H173" t="str">
-        <v>New York, NY (HQ)</v>
+        <v>San Francisco</v>
       </c>
       <c r="I173" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J173" t="str">
         <v>On-site</v>
@@ -10774,7 +10774,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L173" t="str">
-        <v>https://jobs.ashbyhq.com/ramp/cf3516f6-4d6b-4872-831f-c8ef4a3078ee</v>
+        <v>https://jobs.ashbyhq.com/openai/137e3df0-2bd4-4ad4-8edb-8455a7fdc912</v>
       </c>
       <c r="M173">
         <v>200</v>
@@ -10783,7 +10783,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O173" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P173" t="str">
         <v>Today</v>
@@ -10795,21 +10795,21 @@
         <v>No</v>
       </c>
       <c r="S173">
-        <v>86</v>
+        <v>41</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>job-338455bd</v>
+        <v>job-5db12f92</v>
       </c>
       <c r="B174" t="str">
-        <v>Product Manager | Tax</v>
+        <v>Product Manager (Builder)</v>
       </c>
       <c r="C174" t="str">
-        <v>Ramp</v>
+        <v>Perplexity</v>
       </c>
       <c r="D174" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E174" t="str">
         <v>Product Manager</v>
@@ -10821,10 +10821,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H174" t="str">
-        <v>New York, NY (HQ)</v>
+        <v>San Francisco</v>
       </c>
       <c r="I174" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J174" t="str">
         <v>On-site</v>
@@ -10833,7 +10833,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L174" t="str">
-        <v>https://jobs.ashbyhq.com/ramp/881f9f7d-9ec5-4b69-b50d-a67000264ca8</v>
+        <v>https://jobs.ashbyhq.com/perplexity/f25e190e-0508-4707-b575-fcaed358dc13</v>
       </c>
       <c r="M174">
         <v>200</v>
@@ -10842,7 +10842,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O174" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P174" t="str">
         <v>Today</v>
@@ -10854,36 +10854,36 @@
         <v>No</v>
       </c>
       <c r="S174">
-        <v>41</v>
+        <v>95</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>job-6744eb00</v>
+        <v>job-1fe57ea5</v>
       </c>
       <c r="B175" t="str">
-        <v>Product Manager | International</v>
+        <v>Member of Technical Staff (TPM, Inference)</v>
       </c>
       <c r="C175" t="str">
-        <v>Ramp</v>
+        <v>Perplexity</v>
       </c>
       <c r="D175" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E175" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F175" t="str">
-        <v>1-3 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G175" t="str">
-        <v>0-2 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H175" t="str">
-        <v>New York, NY (HQ)</v>
+        <v>San Francisco</v>
       </c>
       <c r="I175" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J175" t="str">
         <v>On-site</v>
@@ -10892,7 +10892,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L175" t="str">
-        <v>https://jobs.ashbyhq.com/ramp/8baec095-2235-41ab-ab64-9abc57823b4b</v>
+        <v>https://jobs.ashbyhq.com/perplexity/0c5d5a82-bfed-4786-b411-79073979af07</v>
       </c>
       <c r="M175">
         <v>200</v>
@@ -10901,7 +10901,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O175" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P175" t="str">
         <v>Today</v>
@@ -10910,39 +10910,39 @@
         <v>Yes</v>
       </c>
       <c r="R175" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S175">
-        <v>104</v>
+        <v>90</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>job-497b065e</v>
+        <v>job-12403072</v>
       </c>
       <c r="B176" t="str">
-        <v>Senior Product Manager, Mobile</v>
+        <v>Product Manager, Mobile Apps</v>
       </c>
       <c r="C176" t="str">
-        <v>Sentry</v>
+        <v>Perplexity</v>
       </c>
       <c r="D176" t="str">
-        <v>Indeed</v>
+        <v>Wellfound</v>
       </c>
       <c r="E176" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F176" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G176" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H176" t="str">
-        <v>Vienna, Austria</v>
+        <v>San Francisco</v>
       </c>
       <c r="I176" t="str">
-        <v>Vienna</v>
+        <v>San Francisco</v>
       </c>
       <c r="J176" t="str">
         <v>On-site</v>
@@ -10951,7 +10951,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L176" t="str">
-        <v>https://jobs.ashbyhq.com/sentry/6a973e19-6736-4973-8a87-043fcbcd553e</v>
+        <v>https://jobs.ashbyhq.com/perplexity/3c9c051f-e6ca-4a70-9abf-1f640e154ee1</v>
       </c>
       <c r="M176">
         <v>200</v>
@@ -10960,7 +10960,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O176" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P176" t="str">
         <v>Today</v>
@@ -10969,27 +10969,27 @@
         <v>Yes</v>
       </c>
       <c r="R176" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S176">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>job-33169045</v>
+        <v>job-10379173</v>
       </c>
       <c r="B177" t="str">
-        <v>Product Manager</v>
+        <v>Product Manager, Core Experience</v>
       </c>
       <c r="C177" t="str">
-        <v>Linear</v>
+        <v>Perplexity</v>
       </c>
       <c r="D177" t="str">
         <v>Wellfound</v>
       </c>
       <c r="E177" t="str">
-        <v>Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F177" t="str">
         <v>3-6 yrs</v>
@@ -10998,10 +10998,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H177" t="str">
-        <v>North America</v>
+        <v>San Francisco</v>
       </c>
       <c r="I177" t="str">
-        <v>North America</v>
+        <v>San Francisco</v>
       </c>
       <c r="J177" t="str">
         <v>On-site</v>
@@ -11010,7 +11010,7 @@
         <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L177" t="str">
-        <v>https://jobs.ashbyhq.com/linear/b7669c4b-eeca-421d-ba9a-d90203f6fcb2</v>
+        <v>https://jobs.ashbyhq.com/perplexity/6f3c5131-2efa-400c-8248-44203a4dbfbb</v>
       </c>
       <c r="M177">
         <v>200</v>
@@ -11019,7 +11019,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O177" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P177" t="str">
         <v>Today</v>
@@ -11031,45 +11031,45 @@
         <v>No</v>
       </c>
       <c r="S177">
-        <v>96</v>
+        <v>114</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>job-048a3bb1</v>
+        <v>job-247da510</v>
       </c>
       <c r="B178" t="str">
-        <v>Head of Product Management - Artist Products</v>
+        <v>Product Manager, AI Capabilities</v>
       </c>
       <c r="C178" t="str">
-        <v>Spotify</v>
+        <v>Perplexity</v>
       </c>
       <c r="D178" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E178" t="str">
-        <v>Product Lead / Director</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F178" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G178" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H178" t="str">
-        <v>New York, NY</v>
+        <v>San Francisco</v>
       </c>
       <c r="I178" t="str">
-        <v>New York</v>
+        <v>San Francisco</v>
       </c>
       <c r="J178" t="str">
         <v>On-site</v>
       </c>
       <c r="K178" t="str">
-        <v>$150k - $220k USD + RSUs</v>
+        <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L178" t="str">
-        <v>https://jobs.lever.co/spotify/e2c7bbb8-f873-42c7-811f-0bd45bf452ae</v>
+        <v>https://jobs.ashbyhq.com/perplexity/7f880194-7276-4b46-8a50-58b48da8882e</v>
       </c>
       <c r="M178">
         <v>200</v>
@@ -11078,7 +11078,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O178" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P178" t="str">
         <v>Today</v>
@@ -11087,48 +11087,48 @@
         <v>Yes</v>
       </c>
       <c r="R178" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S178">
-        <v>43</v>
+        <v>97</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>job-39d9f7fb</v>
+        <v>job-757a314d</v>
       </c>
       <c r="B179" t="str">
-        <v>Principal Product Manager - Audio and Media Playback</v>
+        <v>Product Manager, Growth</v>
       </c>
       <c r="C179" t="str">
-        <v>Spotify</v>
+        <v>Perplexity</v>
       </c>
       <c r="D179" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E179" t="str">
-        <v>Senior Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F179" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G179" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H179" t="str">
-        <v>Stockholm</v>
+        <v>New York City</v>
       </c>
       <c r="I179" t="str">
-        <v>Stockholm</v>
+        <v>New York</v>
       </c>
       <c r="J179" t="str">
         <v>On-site</v>
       </c>
       <c r="K179" t="str">
-        <v>$150k - $220k USD + RSUs</v>
+        <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L179" t="str">
-        <v>https://jobs.lever.co/spotify/080868dd-fc8c-4648-b6ab-6780d8ca3d63</v>
+        <v>https://jobs.ashbyhq.com/perplexity/fa088d92-b08b-43f7-9232-275b0ae08827</v>
       </c>
       <c r="M179">
         <v>200</v>
@@ -11137,7 +11137,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O179" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P179" t="str">
         <v>Today</v>
@@ -11146,48 +11146,48 @@
         <v>Yes</v>
       </c>
       <c r="R179" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S179">
-        <v>72</v>
+        <v>86</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>job-5b32c75d</v>
+        <v>job-376e5ff5</v>
       </c>
       <c r="B180" t="str">
-        <v>Principal Product Manager - Personalization</v>
+        <v>Product Manager, SMB Growth</v>
       </c>
       <c r="C180" t="str">
-        <v>Spotify</v>
+        <v>Perplexity</v>
       </c>
       <c r="D180" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E180" t="str">
-        <v>Senior Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F180" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G180" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H180" t="str">
-        <v>London</v>
+        <v>New York City</v>
       </c>
       <c r="I180" t="str">
-        <v>London</v>
+        <v>New York</v>
       </c>
       <c r="J180" t="str">
         <v>On-site</v>
       </c>
       <c r="K180" t="str">
-        <v>$150k - $220k USD + RSUs</v>
+        <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L180" t="str">
-        <v>https://jobs.lever.co/spotify/e74bfb24-55de-4d93-b228-ae38b8fdfbea</v>
+        <v>https://jobs.ashbyhq.com/perplexity/182ab2ec-6fb1-409b-a2dc-63c7832b0a13</v>
       </c>
       <c r="M180">
         <v>200</v>
@@ -11196,7 +11196,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O180" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P180" t="str">
         <v>Today</v>
@@ -11205,48 +11205,48 @@
         <v>Yes</v>
       </c>
       <c r="R180" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S180">
-        <v>34</v>
+        <v>56</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>job-61f86f2b</v>
+        <v>job-6fff938e</v>
       </c>
       <c r="B181" t="str">
-        <v>Product Manager - Customer Service Platform</v>
+        <v>Product Manager - Marketplace</v>
       </c>
       <c r="C181" t="str">
-        <v>Spotify</v>
+        <v>Supabase</v>
       </c>
       <c r="D181" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E181" t="str">
-        <v>Technical Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F181" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G181" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H181" t="str">
-        <v>London</v>
+        <v>Remote, Global</v>
       </c>
       <c r="I181" t="str">
-        <v>London</v>
+        <v>Remote</v>
       </c>
       <c r="J181" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K181" t="str">
-        <v>$150k - $220k USD + RSUs</v>
+        <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L181" t="str">
-        <v>https://jobs.lever.co/spotify/7f0a8faa-f4f5-4db9-9f51-4101d6a29b34</v>
+        <v>https://jobs.ashbyhq.com/supabase/23c9ce7e-6b7b-4316-8f00-8f318e902441</v>
       </c>
       <c r="M181">
         <v>200</v>
@@ -11255,7 +11255,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O181" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P181" t="str">
         <v>Today</v>
@@ -11264,48 +11264,48 @@
         <v>Yes</v>
       </c>
       <c r="R181" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S181">
-        <v>33</v>
+        <v>116</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>job-1a230b4c</v>
+        <v>job-49f97312</v>
       </c>
       <c r="B182" t="str">
-        <v>Product Manager - Data Platform</v>
+        <v>Product Manager - Security &amp; Trust (EMEA/AMER)</v>
       </c>
       <c r="C182" t="str">
-        <v>Spotify</v>
+        <v>Supabase</v>
       </c>
       <c r="D182" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E182" t="str">
-        <v>Technical Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F182" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G182" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H182" t="str">
-        <v>Toronto</v>
+        <v>Remote, Global</v>
       </c>
       <c r="I182" t="str">
-        <v>Toronto</v>
+        <v>Remote</v>
       </c>
       <c r="J182" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K182" t="str">
-        <v>$150k - $220k USD + RSUs</v>
+        <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L182" t="str">
-        <v>https://jobs.lever.co/spotify/03437e2a-2d5e-4593-9e97-11271014932e</v>
+        <v>https://jobs.ashbyhq.com/supabase/b8010a28-109c-46a9-b8b7-c7f9b24077fa</v>
       </c>
       <c r="M182">
         <v>200</v>
@@ -11314,7 +11314,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O182" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P182" t="str">
         <v>Today</v>
@@ -11323,48 +11323,48 @@
         <v>Yes</v>
       </c>
       <c r="R182" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S182">
-        <v>66</v>
+        <v>49</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>job-1ba340a4</v>
+        <v>job-064fa6b5</v>
       </c>
       <c r="B183" t="str">
-        <v>Senior Product Manager - Audiobooks Format Foundations</v>
+        <v>Product Manager - Strategic Partner Integrations (Bay Area based)</v>
       </c>
       <c r="C183" t="str">
-        <v>Spotify</v>
+        <v>Supabase</v>
       </c>
       <c r="D183" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E183" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F183" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G183" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H183" t="str">
-        <v>London</v>
+        <v>Remote, Bay Area, CA</v>
       </c>
       <c r="I183" t="str">
-        <v>London</v>
+        <v>San Francisco</v>
       </c>
       <c r="J183" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K183" t="str">
-        <v>$150k - $220k USD + RSUs</v>
+        <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L183" t="str">
-        <v>https://jobs.lever.co/spotify/e7b01c1e-4246-4f31-83ea-9219c8b22c83</v>
+        <v>https://jobs.ashbyhq.com/supabase/68a397e7-8a1a-4566-ae41-e8c61dd6ed93</v>
       </c>
       <c r="M183">
         <v>200</v>
@@ -11373,7 +11373,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O183" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P183" t="str">
         <v>Today</v>
@@ -11382,48 +11382,48 @@
         <v>Yes</v>
       </c>
       <c r="R183" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S183">
-        <v>50</v>
+        <v>102</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>job-3a0c9449</v>
+        <v>job-7da017c6</v>
       </c>
       <c r="B184" t="str">
-        <v>Senior Product Manager - Subscriptions</v>
+        <v>Product Manager | Vendor Intelligence &amp; Marketplace</v>
       </c>
       <c r="C184" t="str">
-        <v>Spotify</v>
+        <v>Ramp</v>
       </c>
       <c r="D184" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E184" t="str">
-        <v>Senior Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F184" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G184" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H184" t="str">
-        <v>London</v>
+        <v>New York, NY (HQ)</v>
       </c>
       <c r="I184" t="str">
-        <v>London</v>
+        <v>New York</v>
       </c>
       <c r="J184" t="str">
         <v>On-site</v>
       </c>
       <c r="K184" t="str">
-        <v>$150k - $220k USD + RSUs</v>
+        <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L184" t="str">
-        <v>https://jobs.lever.co/spotify/a57db22d-dc0d-4f36-9a2e-34acdf1ec046</v>
+        <v>https://jobs.ashbyhq.com/ramp/cf3516f6-4d6b-4872-831f-c8ef4a3078ee</v>
       </c>
       <c r="M184">
         <v>200</v>
@@ -11432,7 +11432,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O184" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P184" t="str">
         <v>Today</v>
@@ -11441,48 +11441,48 @@
         <v>Yes</v>
       </c>
       <c r="R184" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S184">
-        <v>84</v>
+        <v>46</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>job-32cac657</v>
+        <v>job-338455bd</v>
       </c>
       <c r="B185" t="str">
-        <v>Senior Product Manager - User Platform</v>
+        <v>Product Manager | Tax</v>
       </c>
       <c r="C185" t="str">
-        <v>Spotify</v>
+        <v>Ramp</v>
       </c>
       <c r="D185" t="str">
         <v>LinkedIn</v>
       </c>
       <c r="E185" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F185" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G185" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H185" t="str">
-        <v>London</v>
+        <v>New York, NY (HQ)</v>
       </c>
       <c r="I185" t="str">
-        <v>London</v>
+        <v>New York</v>
       </c>
       <c r="J185" t="str">
         <v>On-site</v>
       </c>
       <c r="K185" t="str">
-        <v>$150k - $220k USD + RSUs</v>
+        <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L185" t="str">
-        <v>https://jobs.lever.co/spotify/ee45924c-894c-4ea0-9c93-c5221894063f</v>
+        <v>https://jobs.ashbyhq.com/ramp/881f9f7d-9ec5-4b69-b50d-a67000264ca8</v>
       </c>
       <c r="M185">
         <v>200</v>
@@ -11491,7 +11491,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O185" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P185" t="str">
         <v>Today</v>
@@ -11500,36 +11500,36 @@
         <v>Yes</v>
       </c>
       <c r="R185" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S185">
-        <v>54</v>
+        <v>103</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>job-4d0308c8</v>
+        <v>job-6744eb00</v>
       </c>
       <c r="B186" t="str">
-        <v>Technical Program Manager (TPM)</v>
+        <v>Product Manager | International</v>
       </c>
       <c r="C186" t="str">
-        <v>Palantir</v>
+        <v>Ramp</v>
       </c>
       <c r="D186" t="str">
-        <v>Instahyre</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E186" t="str">
-        <v>Technical Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F186" t="str">
-        <v>5-8 yrs</v>
+        <v>1-3 yrs</v>
       </c>
       <c r="G186" t="str">
-        <v>5-8 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H186" t="str">
-        <v>New York, NY</v>
+        <v>New York, NY (HQ)</v>
       </c>
       <c r="I186" t="str">
         <v>New York</v>
@@ -11538,10 +11538,10 @@
         <v>On-site</v>
       </c>
       <c r="K186" t="str">
-        <v>$150k - $220k USD + RSUs</v>
+        <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L186" t="str">
-        <v>https://jobs.lever.co/palantir/7eb0dedb-37ee-4175-b29f-10a9e4340076</v>
+        <v>https://jobs.ashbyhq.com/ramp/8baec095-2235-41ab-ab64-9abc57823b4b</v>
       </c>
       <c r="M186">
         <v>200</v>
@@ -11550,7 +11550,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O186" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P186" t="str">
         <v>Today</v>
@@ -11559,27 +11559,27 @@
         <v>Yes</v>
       </c>
       <c r="R186" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S186">
-        <v>41</v>
+        <v>65</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>job-593275cb</v>
+        <v>job-497b065e</v>
       </c>
       <c r="B187" t="str">
-        <v>Technical Program Manager (TPM) - Defense</v>
+        <v>Senior Product Manager, Mobile</v>
       </c>
       <c r="C187" t="str">
-        <v>Palantir</v>
+        <v>Sentry</v>
       </c>
       <c r="D187" t="str">
-        <v>Instahyre</v>
+        <v>Indeed</v>
       </c>
       <c r="E187" t="str">
-        <v>Technical Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F187" t="str">
         <v>5-8 yrs</v>
@@ -11588,19 +11588,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H187" t="str">
-        <v>Washington, D.C.</v>
+        <v>Vienna, Austria</v>
       </c>
       <c r="I187" t="str">
-        <v>Washington</v>
+        <v>Vienna</v>
       </c>
       <c r="J187" t="str">
         <v>On-site</v>
       </c>
       <c r="K187" t="str">
-        <v>$150k - $220k USD + RSUs</v>
+        <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L187" t="str">
-        <v>https://jobs.lever.co/palantir/bd16f7ad-3bee-48fd-9902-b3ee9698b608</v>
+        <v>https://jobs.ashbyhq.com/sentry/6a973e19-6736-4973-8a87-043fcbcd553e</v>
       </c>
       <c r="M187">
         <v>200</v>
@@ -11609,7 +11609,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O187" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P187" t="str">
         <v>Today</v>
@@ -11618,48 +11618,48 @@
         <v>Yes</v>
       </c>
       <c r="R187" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S187">
-        <v>55</v>
+        <v>90</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>job-343d8912</v>
+        <v>job-33169045</v>
       </c>
       <c r="B188" t="str">
-        <v>Associate Product Manager (APM) - Growth &amp; Merchant Onboarding</v>
+        <v>Product Manager</v>
       </c>
       <c r="C188" t="str">
-        <v>Razorpay</v>
+        <v>Linear</v>
       </c>
       <c r="D188" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E188" t="str">
-        <v>Associate Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F188" t="str">
-        <v>1-3 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G188" t="str">
-        <v>0-2 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H188" t="str">
-        <v>Bengaluru, Karnataka</v>
+        <v>North America</v>
       </c>
       <c r="I188" t="str">
-        <v>Bengaluru</v>
+        <v>North America</v>
       </c>
       <c r="J188" t="str">
-        <v>Hybrid</v>
+        <v>On-site</v>
       </c>
       <c r="K188" t="str">
-        <v>₹18L - ₹26L PA + ESOPs</v>
+        <v>$160k - $240k USD + Equity</v>
       </c>
       <c r="L188" t="str">
-        <v>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited</v>
+        <v>https://jobs.ashbyhq.com/linear/b7669c4b-eeca-421d-ba9a-d90203f6fcb2</v>
       </c>
       <c r="M188">
         <v>200</v>
@@ -11668,7 +11668,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O188" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P188" t="str">
         <v>Today</v>
@@ -11677,27 +11677,27 @@
         <v>Yes</v>
       </c>
       <c r="R188" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S188">
-        <v>42</v>
+        <v>54</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>job-739e0b9f</v>
+        <v>job-048a3bb1</v>
       </c>
       <c r="B189" t="str">
-        <v>Senior Product Manager - Consumer Checkout &amp; Loyalty</v>
+        <v>Head of Product Management - Artist Products</v>
       </c>
       <c r="C189" t="str">
-        <v>Swiggy</v>
+        <v>Spotify</v>
       </c>
       <c r="D189" t="str">
-        <v>Naukri</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E189" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F189" t="str">
         <v>5-8 yrs</v>
@@ -11706,19 +11706,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H189" t="str">
-        <v>Bengaluru, Karnataka</v>
+        <v>New York, NY</v>
       </c>
       <c r="I189" t="str">
-        <v>Bengaluru</v>
+        <v>New York</v>
       </c>
       <c r="J189" t="str">
-        <v>Hybrid</v>
+        <v>On-site</v>
       </c>
       <c r="K189" t="str">
-        <v>₹45L - ₹65L PA + ESOPs</v>
+        <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L189" t="str">
-        <v>https://careers.swiggy.com/</v>
+        <v>https://jobs.lever.co/spotify/e2c7bbb8-f873-42c7-811f-0bd45bf452ae</v>
       </c>
       <c r="M189">
         <v>200</v>
@@ -11727,7 +11727,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O189" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P189" t="str">
         <v>Today</v>
@@ -11736,57 +11736,57 @@
         <v>Yes</v>
       </c>
       <c r="R189" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S189">
-        <v>115</v>
+        <v>50</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>job-66154b1b</v>
+        <v>job-39d9f7fb</v>
       </c>
       <c r="B190" t="str">
-        <v>Senior Product Manager - 10-Minute Dark Store &amp; Logistics Dispatch</v>
+        <v>Principal Product Manager - Audio and Media Playback</v>
       </c>
       <c r="C190" t="str">
-        <v>Zepto</v>
+        <v>Spotify</v>
       </c>
       <c r="D190" t="str">
-        <v>Naukri</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E190" t="str">
         <v>Senior Product Manager</v>
       </c>
       <c r="F190" t="str">
-        <v>4-7 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G190" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H190" t="str">
-        <v>Mumbai, Maharashtra</v>
+        <v>Stockholm</v>
       </c>
       <c r="I190" t="str">
-        <v>Mumbai</v>
+        <v>Stockholm</v>
       </c>
       <c r="J190" t="str">
         <v>On-site</v>
       </c>
       <c r="K190" t="str">
-        <v>₹42L - ₹60L PA + ESOPs</v>
+        <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L190" t="str">
-        <v>https://www.zeptonow.com/careers</v>
+        <v>https://jobs.lever.co/spotify/080868dd-fc8c-4648-b6ab-6780d8ca3d63</v>
       </c>
       <c r="M190">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="N190" t="str">
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O190" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P190" t="str">
         <v>Today</v>
@@ -11795,24 +11795,24 @@
         <v>Yes</v>
       </c>
       <c r="R190" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S190">
-        <v>94</v>
+        <v>82</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>job-169943b4</v>
+        <v>job-5b32c75d</v>
       </c>
       <c r="B191" t="str">
-        <v>Senior Product Manager - Customer Experience &amp; Live Support AI</v>
+        <v>Principal Product Manager - Personalization</v>
       </c>
       <c r="C191" t="str">
-        <v>Zomato</v>
+        <v>Spotify</v>
       </c>
       <c r="D191" t="str">
-        <v>Naukri</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E191" t="str">
         <v>Senior Product Manager</v>
@@ -11824,28 +11824,28 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H191" t="str">
-        <v>Gurgaon, Haryana</v>
+        <v>London</v>
       </c>
       <c r="I191" t="str">
-        <v>Gurgaon</v>
+        <v>London</v>
       </c>
       <c r="J191" t="str">
         <v>On-site</v>
       </c>
       <c r="K191" t="str">
-        <v>₹45L - ₹65L PA + ESOPs</v>
+        <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L191" t="str">
-        <v>https://www.zomato.com/careers</v>
+        <v>https://jobs.lever.co/spotify/e74bfb24-55de-4d93-b228-ae38b8fdfbea</v>
       </c>
       <c r="M191">
-        <v>503</v>
+        <v>200</v>
       </c>
       <c r="N191" t="str">
-        <v>BROKEN / 404</v>
+        <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O191" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P191" t="str">
         <v>Today</v>
@@ -11854,48 +11854,48 @@
         <v>Yes</v>
       </c>
       <c r="R191" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S191">
-        <v>95</v>
+        <v>51</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>job-23756e58</v>
+        <v>job-61f86f2b</v>
       </c>
       <c r="B192" t="str">
-        <v>Associate Product Manager (APM) - Social Commerce &amp; Creator Tools</v>
+        <v>Product Manager - Customer Service Platform</v>
       </c>
       <c r="C192" t="str">
-        <v>Meesho</v>
+        <v>Spotify</v>
       </c>
       <c r="D192" t="str">
-        <v>Naukri</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E192" t="str">
-        <v>Associate Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F192" t="str">
-        <v>0-2 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G192" t="str">
-        <v>0-2 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H192" t="str">
-        <v>Bengaluru, Karnataka</v>
+        <v>London</v>
       </c>
       <c r="I192" t="str">
-        <v>Bengaluru</v>
+        <v>London</v>
       </c>
       <c r="J192" t="str">
-        <v>Hybrid</v>
+        <v>On-site</v>
       </c>
       <c r="K192" t="str">
-        <v>₹18L - ₹25L PA + ESOPs</v>
+        <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L192" t="str">
-        <v>https://www.meesho.io/jobs</v>
+        <v>https://jobs.lever.co/spotify/7f0a8faa-f4f5-4db9-9f51-4101d6a29b34</v>
       </c>
       <c r="M192">
         <v>200</v>
@@ -11904,7 +11904,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O192" t="str">
-        <v>2026-09-27</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P192" t="str">
         <v>Today</v>
@@ -11913,48 +11913,48 @@
         <v>Yes</v>
       </c>
       <c r="R192" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S192">
-        <v>65</v>
+        <v>84</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>job-6900691e</v>
+        <v>job-1a230b4c</v>
       </c>
       <c r="B193" t="str">
-        <v>Product Owner - Core Banking &amp; Credit Line Engine</v>
+        <v>Product Manager - Data Platform</v>
       </c>
       <c r="C193" t="str">
-        <v>CRED</v>
+        <v>Spotify</v>
       </c>
       <c r="D193" t="str">
-        <v>Instahyre</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E193" t="str">
         <v>Technical Product Manager</v>
       </c>
       <c r="F193" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G193" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H193" t="str">
-        <v>Bengaluru, Karnataka</v>
+        <v>Toronto</v>
       </c>
       <c r="I193" t="str">
-        <v>Bengaluru</v>
+        <v>Toronto</v>
       </c>
       <c r="J193" t="str">
         <v>On-site</v>
       </c>
       <c r="K193" t="str">
-        <v>₹35L - ₹52L PA + ESOPs</v>
+        <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L193" t="str">
-        <v>https://careers.cred.club/</v>
+        <v>https://jobs.lever.co/spotify/03437e2a-2d5e-4593-9e97-11271014932e</v>
       </c>
       <c r="M193">
         <v>200</v>
@@ -11963,10 +11963,10 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O193" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P193" t="str">
-        <v>1d ago</v>
+        <v>Today</v>
       </c>
       <c r="Q193" t="str">
         <v>Yes</v>
@@ -11975,45 +11975,45 @@
         <v>No</v>
       </c>
       <c r="S193">
-        <v>76</v>
+        <v>31</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>job-1e98cdb6</v>
+        <v>job-1ba340a4</v>
       </c>
       <c r="B194" t="str">
-        <v>Product Lead - Merchant QR, Soundbox &amp; Offline Payments Rails</v>
+        <v>Senior Product Manager - Audiobooks Format Foundations</v>
       </c>
       <c r="C194" t="str">
-        <v>PhonePe</v>
+        <v>Spotify</v>
       </c>
       <c r="D194" t="str">
-        <v>Instahyre</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E194" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F194" t="str">
-        <v>7-11 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G194" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H194" t="str">
-        <v>Bengaluru, Karnataka</v>
+        <v>London</v>
       </c>
       <c r="I194" t="str">
-        <v>Bengaluru</v>
+        <v>London</v>
       </c>
       <c r="J194" t="str">
         <v>On-site</v>
       </c>
       <c r="K194" t="str">
-        <v>₹65L - ₹90L PA + ESOPs</v>
+        <v>$150k - $220k USD + RSUs</v>
       </c>
       <c r="L194" t="str">
-        <v>https://www.phonepe.com/careers/</v>
+        <v>https://jobs.lever.co/spotify/e7b01c1e-4246-4f31-83ea-9219c8b22c83</v>
       </c>
       <c r="M194">
         <v>200</v>
@@ -12022,83 +12022,732 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O194" t="str">
-        <v>2026-09-26</v>
+        <v>2026-09-28</v>
       </c>
       <c r="P194" t="str">
-        <v>1d ago</v>
+        <v>Today</v>
       </c>
       <c r="Q194" t="str">
         <v>Yes</v>
       </c>
       <c r="R194" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S194">
-        <v>125</v>
+        <v>80</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
+        <v>job-3a0c9449</v>
+      </c>
+      <c r="B195" t="str">
+        <v>Senior Product Manager - Subscriptions</v>
+      </c>
+      <c r="C195" t="str">
+        <v>Spotify</v>
+      </c>
+      <c r="D195" t="str">
+        <v>LinkedIn</v>
+      </c>
+      <c r="E195" t="str">
+        <v>Senior Product Manager</v>
+      </c>
+      <c r="F195" t="str">
+        <v>5-8 yrs</v>
+      </c>
+      <c r="G195" t="str">
+        <v>5-8 yrs</v>
+      </c>
+      <c r="H195" t="str">
+        <v>London</v>
+      </c>
+      <c r="I195" t="str">
+        <v>London</v>
+      </c>
+      <c r="J195" t="str">
+        <v>On-site</v>
+      </c>
+      <c r="K195" t="str">
+        <v>$150k - $220k USD + RSUs</v>
+      </c>
+      <c r="L195" t="str">
+        <v>https://jobs.lever.co/spotify/a57db22d-dc0d-4f36-9a2e-34acdf1ec046</v>
+      </c>
+      <c r="M195">
+        <v>200</v>
+      </c>
+      <c r="N195" t="str">
+        <v>ACTIVE / 100% VALID</v>
+      </c>
+      <c r="O195" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="P195" t="str">
+        <v>Today</v>
+      </c>
+      <c r="Q195" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="R195" t="str">
+        <v>No</v>
+      </c>
+      <c r="S195">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>job-32cac657</v>
+      </c>
+      <c r="B196" t="str">
+        <v>Senior Product Manager - User Platform</v>
+      </c>
+      <c r="C196" t="str">
+        <v>Spotify</v>
+      </c>
+      <c r="D196" t="str">
+        <v>LinkedIn</v>
+      </c>
+      <c r="E196" t="str">
+        <v>Senior Product Manager</v>
+      </c>
+      <c r="F196" t="str">
+        <v>5-8 yrs</v>
+      </c>
+      <c r="G196" t="str">
+        <v>5-8 yrs</v>
+      </c>
+      <c r="H196" t="str">
+        <v>London</v>
+      </c>
+      <c r="I196" t="str">
+        <v>London</v>
+      </c>
+      <c r="J196" t="str">
+        <v>On-site</v>
+      </c>
+      <c r="K196" t="str">
+        <v>$150k - $220k USD + RSUs</v>
+      </c>
+      <c r="L196" t="str">
+        <v>https://jobs.lever.co/spotify/ee45924c-894c-4ea0-9c93-c5221894063f</v>
+      </c>
+      <c r="M196">
+        <v>200</v>
+      </c>
+      <c r="N196" t="str">
+        <v>ACTIVE / 100% VALID</v>
+      </c>
+      <c r="O196" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="P196" t="str">
+        <v>Today</v>
+      </c>
+      <c r="Q196" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="R196" t="str">
+        <v>No</v>
+      </c>
+      <c r="S196">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>job-4d0308c8</v>
+      </c>
+      <c r="B197" t="str">
+        <v>Technical Program Manager (TPM)</v>
+      </c>
+      <c r="C197" t="str">
+        <v>Palantir</v>
+      </c>
+      <c r="D197" t="str">
+        <v>Instahyre</v>
+      </c>
+      <c r="E197" t="str">
+        <v>Technical Product Manager</v>
+      </c>
+      <c r="F197" t="str">
+        <v>5-8 yrs</v>
+      </c>
+      <c r="G197" t="str">
+        <v>5-8 yrs</v>
+      </c>
+      <c r="H197" t="str">
+        <v>New York, NY</v>
+      </c>
+      <c r="I197" t="str">
+        <v>New York</v>
+      </c>
+      <c r="J197" t="str">
+        <v>On-site</v>
+      </c>
+      <c r="K197" t="str">
+        <v>$150k - $220k USD + RSUs</v>
+      </c>
+      <c r="L197" t="str">
+        <v>https://jobs.lever.co/palantir/7eb0dedb-37ee-4175-b29f-10a9e4340076</v>
+      </c>
+      <c r="M197">
+        <v>200</v>
+      </c>
+      <c r="N197" t="str">
+        <v>ACTIVE / 100% VALID</v>
+      </c>
+      <c r="O197" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="P197" t="str">
+        <v>Today</v>
+      </c>
+      <c r="Q197" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="R197" t="str">
+        <v>No</v>
+      </c>
+      <c r="S197">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>job-593275cb</v>
+      </c>
+      <c r="B198" t="str">
+        <v>Technical Program Manager (TPM) - Defense</v>
+      </c>
+      <c r="C198" t="str">
+        <v>Palantir</v>
+      </c>
+      <c r="D198" t="str">
+        <v>Instahyre</v>
+      </c>
+      <c r="E198" t="str">
+        <v>Technical Product Manager</v>
+      </c>
+      <c r="F198" t="str">
+        <v>5-8 yrs</v>
+      </c>
+      <c r="G198" t="str">
+        <v>5-8 yrs</v>
+      </c>
+      <c r="H198" t="str">
+        <v>Washington, D.C.</v>
+      </c>
+      <c r="I198" t="str">
+        <v>Washington</v>
+      </c>
+      <c r="J198" t="str">
+        <v>On-site</v>
+      </c>
+      <c r="K198" t="str">
+        <v>$150k - $220k USD + RSUs</v>
+      </c>
+      <c r="L198" t="str">
+        <v>https://jobs.lever.co/palantir/bd16f7ad-3bee-48fd-9902-b3ee9698b608</v>
+      </c>
+      <c r="M198">
+        <v>200</v>
+      </c>
+      <c r="N198" t="str">
+        <v>ACTIVE / 100% VALID</v>
+      </c>
+      <c r="O198" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="P198" t="str">
+        <v>Today</v>
+      </c>
+      <c r="Q198" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="R198" t="str">
+        <v>No</v>
+      </c>
+      <c r="S198">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>job-343d8912</v>
+      </c>
+      <c r="B199" t="str">
+        <v>Associate Product Manager (APM) - Growth &amp; Merchant Onboarding</v>
+      </c>
+      <c r="C199" t="str">
+        <v>Razorpay</v>
+      </c>
+      <c r="D199" t="str">
+        <v>LinkedIn</v>
+      </c>
+      <c r="E199" t="str">
+        <v>Associate Product Manager</v>
+      </c>
+      <c r="F199" t="str">
+        <v>1-3 yrs</v>
+      </c>
+      <c r="G199" t="str">
+        <v>0-2 yrs</v>
+      </c>
+      <c r="H199" t="str">
+        <v>Bengaluru, Karnataka</v>
+      </c>
+      <c r="I199" t="str">
+        <v>Bengaluru</v>
+      </c>
+      <c r="J199" t="str">
+        <v>Hybrid</v>
+      </c>
+      <c r="K199" t="str">
+        <v>₹18L - ₹26L PA + ESOPs</v>
+      </c>
+      <c r="L199" t="str">
+        <v>https://job-boards.greenhouse.io/razorpaysoftwareprivatelimited</v>
+      </c>
+      <c r="M199">
+        <v>200</v>
+      </c>
+      <c r="N199" t="str">
+        <v>ACTIVE / 100% VALID</v>
+      </c>
+      <c r="O199" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="P199" t="str">
+        <v>Today</v>
+      </c>
+      <c r="Q199" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="R199" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="S199">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>job-739e0b9f</v>
+      </c>
+      <c r="B200" t="str">
+        <v>Senior Product Manager - Consumer Checkout &amp; Loyalty</v>
+      </c>
+      <c r="C200" t="str">
+        <v>Swiggy</v>
+      </c>
+      <c r="D200" t="str">
+        <v>Naukri</v>
+      </c>
+      <c r="E200" t="str">
+        <v>Senior Product Manager</v>
+      </c>
+      <c r="F200" t="str">
+        <v>5-8 yrs</v>
+      </c>
+      <c r="G200" t="str">
+        <v>5-8 yrs</v>
+      </c>
+      <c r="H200" t="str">
+        <v>Bengaluru, Karnataka</v>
+      </c>
+      <c r="I200" t="str">
+        <v>Bengaluru</v>
+      </c>
+      <c r="J200" t="str">
+        <v>Hybrid</v>
+      </c>
+      <c r="K200" t="str">
+        <v>₹45L - ₹65L PA + ESOPs</v>
+      </c>
+      <c r="L200" t="str">
+        <v>https://careers.swiggy.com/</v>
+      </c>
+      <c r="M200">
+        <v>200</v>
+      </c>
+      <c r="N200" t="str">
+        <v>ACTIVE / 100% VALID</v>
+      </c>
+      <c r="O200" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="P200" t="str">
+        <v>Today</v>
+      </c>
+      <c r="Q200" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="R200" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="S200">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>job-66154b1b</v>
+      </c>
+      <c r="B201" t="str">
+        <v>Senior Product Manager - 10-Minute Dark Store &amp; Logistics Dispatch</v>
+      </c>
+      <c r="C201" t="str">
+        <v>Zepto</v>
+      </c>
+      <c r="D201" t="str">
+        <v>Naukri</v>
+      </c>
+      <c r="E201" t="str">
+        <v>Senior Product Manager</v>
+      </c>
+      <c r="F201" t="str">
+        <v>4-7 yrs</v>
+      </c>
+      <c r="G201" t="str">
+        <v>2-5 yrs</v>
+      </c>
+      <c r="H201" t="str">
+        <v>Mumbai, Maharashtra</v>
+      </c>
+      <c r="I201" t="str">
+        <v>Mumbai</v>
+      </c>
+      <c r="J201" t="str">
+        <v>On-site</v>
+      </c>
+      <c r="K201" t="str">
+        <v>₹42L - ₹60L PA + ESOPs</v>
+      </c>
+      <c r="L201" t="str">
+        <v>https://www.zeptonow.com/careers</v>
+      </c>
+      <c r="M201">
+        <v>202</v>
+      </c>
+      <c r="N201" t="str">
+        <v>ACTIVE / 100% VALID</v>
+      </c>
+      <c r="O201" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="P201" t="str">
+        <v>Today</v>
+      </c>
+      <c r="Q201" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="R201" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="S201">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>job-169943b4</v>
+      </c>
+      <c r="B202" t="str">
+        <v>Senior Product Manager - Customer Experience &amp; Live Support AI</v>
+      </c>
+      <c r="C202" t="str">
+        <v>Zomato</v>
+      </c>
+      <c r="D202" t="str">
+        <v>Naukri</v>
+      </c>
+      <c r="E202" t="str">
+        <v>Senior Product Manager</v>
+      </c>
+      <c r="F202" t="str">
+        <v>5-8 yrs</v>
+      </c>
+      <c r="G202" t="str">
+        <v>5-8 yrs</v>
+      </c>
+      <c r="H202" t="str">
+        <v>Gurgaon, Haryana</v>
+      </c>
+      <c r="I202" t="str">
+        <v>Gurgaon</v>
+      </c>
+      <c r="J202" t="str">
+        <v>On-site</v>
+      </c>
+      <c r="K202" t="str">
+        <v>₹45L - ₹65L PA + ESOPs</v>
+      </c>
+      <c r="L202" t="str">
+        <v>https://www.zomato.com/careers</v>
+      </c>
+      <c r="M202">
+        <v>503</v>
+      </c>
+      <c r="N202" t="str">
+        <v>BROKEN / 404</v>
+      </c>
+      <c r="O202" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="P202" t="str">
+        <v>Today</v>
+      </c>
+      <c r="Q202" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="R202" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="S202">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>job-23756e58</v>
+      </c>
+      <c r="B203" t="str">
+        <v>Associate Product Manager (APM) - Social Commerce &amp; Creator Tools</v>
+      </c>
+      <c r="C203" t="str">
+        <v>Meesho</v>
+      </c>
+      <c r="D203" t="str">
+        <v>Naukri</v>
+      </c>
+      <c r="E203" t="str">
+        <v>Associate Product Manager</v>
+      </c>
+      <c r="F203" t="str">
+        <v>0-2 yrs</v>
+      </c>
+      <c r="G203" t="str">
+        <v>0-2 yrs</v>
+      </c>
+      <c r="H203" t="str">
+        <v>Bengaluru, Karnataka</v>
+      </c>
+      <c r="I203" t="str">
+        <v>Bengaluru</v>
+      </c>
+      <c r="J203" t="str">
+        <v>Hybrid</v>
+      </c>
+      <c r="K203" t="str">
+        <v>₹18L - ₹25L PA + ESOPs</v>
+      </c>
+      <c r="L203" t="str">
+        <v>https://www.meesho.io/jobs</v>
+      </c>
+      <c r="M203">
+        <v>200</v>
+      </c>
+      <c r="N203" t="str">
+        <v>ACTIVE / 100% VALID</v>
+      </c>
+      <c r="O203" t="str">
+        <v>2026-09-28</v>
+      </c>
+      <c r="P203" t="str">
+        <v>Today</v>
+      </c>
+      <c r="Q203" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="R203" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="S203">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>job-6900691e</v>
+      </c>
+      <c r="B204" t="str">
+        <v>Product Owner - Core Banking &amp; Credit Line Engine</v>
+      </c>
+      <c r="C204" t="str">
+        <v>CRED</v>
+      </c>
+      <c r="D204" t="str">
+        <v>Instahyre</v>
+      </c>
+      <c r="E204" t="str">
+        <v>Technical Product Manager</v>
+      </c>
+      <c r="F204" t="str">
+        <v>3-6 yrs</v>
+      </c>
+      <c r="G204" t="str">
+        <v>2-5 yrs</v>
+      </c>
+      <c r="H204" t="str">
+        <v>Bengaluru, Karnataka</v>
+      </c>
+      <c r="I204" t="str">
+        <v>Bengaluru</v>
+      </c>
+      <c r="J204" t="str">
+        <v>On-site</v>
+      </c>
+      <c r="K204" t="str">
+        <v>₹35L - ₹52L PA + ESOPs</v>
+      </c>
+      <c r="L204" t="str">
+        <v>https://careers.cred.club/</v>
+      </c>
+      <c r="M204">
+        <v>200</v>
+      </c>
+      <c r="N204" t="str">
+        <v>ACTIVE / 100% VALID</v>
+      </c>
+      <c r="O204" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="P204" t="str">
+        <v>1d ago</v>
+      </c>
+      <c r="Q204" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="R204" t="str">
+        <v>No</v>
+      </c>
+      <c r="S204">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>job-1e98cdb6</v>
+      </c>
+      <c r="B205" t="str">
+        <v>Product Lead - Merchant QR, Soundbox &amp; Offline Payments Rails</v>
+      </c>
+      <c r="C205" t="str">
+        <v>PhonePe</v>
+      </c>
+      <c r="D205" t="str">
+        <v>Instahyre</v>
+      </c>
+      <c r="E205" t="str">
+        <v>AI &amp; Growth PM</v>
+      </c>
+      <c r="F205" t="str">
+        <v>7-11 yrs</v>
+      </c>
+      <c r="G205" t="str">
+        <v>8+ yrs</v>
+      </c>
+      <c r="H205" t="str">
+        <v>Bengaluru, Karnataka</v>
+      </c>
+      <c r="I205" t="str">
+        <v>Bengaluru</v>
+      </c>
+      <c r="J205" t="str">
+        <v>On-site</v>
+      </c>
+      <c r="K205" t="str">
+        <v>₹65L - ₹90L PA + ESOPs</v>
+      </c>
+      <c r="L205" t="str">
+        <v>https://www.phonepe.com/careers/</v>
+      </c>
+      <c r="M205">
+        <v>200</v>
+      </c>
+      <c r="N205" t="str">
+        <v>ACTIVE / 100% VALID</v>
+      </c>
+      <c r="O205" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="P205" t="str">
+        <v>1d ago</v>
+      </c>
+      <c r="Q205" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="R205" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="S205">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
         <v>job-6ee4d4a9</v>
       </c>
-      <c r="B195" t="str">
+      <c r="B206" t="str">
         <v>Product Manager - Supply Chain Forecasting &amp; Dynamic Pricing</v>
       </c>
-      <c r="C195" t="str">
+      <c r="C206" t="str">
         <v>Flipkart</v>
       </c>
-      <c r="D195" t="str">
+      <c r="D206" t="str">
         <v>IIMJobs</v>
       </c>
-      <c r="E195" t="str">
+      <c r="E206" t="str">
         <v>AI &amp; Growth PM</v>
       </c>
-      <c r="F195" t="str">
+      <c r="F206" t="str">
         <v>3-6 yrs</v>
       </c>
-      <c r="G195" t="str">
+      <c r="G206" t="str">
         <v>2-5 yrs</v>
       </c>
-      <c r="H195" t="str">
+      <c r="H206" t="str">
         <v>Bengaluru, Karnataka</v>
       </c>
-      <c r="I195" t="str">
+      <c r="I206" t="str">
         <v>Bengaluru</v>
       </c>
-      <c r="J195" t="str">
+      <c r="J206" t="str">
         <v>Hybrid</v>
       </c>
-      <c r="K195" t="str">
+      <c r="K206" t="str">
         <v>₹32L - ₹48L PA + ESOPs</v>
       </c>
-      <c r="L195" t="str">
+      <c r="L206" t="str">
         <v>https://www.flipkartcareers.com/</v>
       </c>
-      <c r="M195">
-        <v>200</v>
-      </c>
-      <c r="N195" t="str">
-        <v>ACTIVE / 100% VALID</v>
-      </c>
-      <c r="O195" t="str">
-        <v>2026-09-26</v>
-      </c>
-      <c r="P195" t="str">
+      <c r="M206">
+        <v>200</v>
+      </c>
+      <c r="N206" t="str">
+        <v>ACTIVE / 100% VALID</v>
+      </c>
+      <c r="O206" t="str">
+        <v>2026-09-27</v>
+      </c>
+      <c r="P206" t="str">
         <v>1d ago</v>
       </c>
-      <c r="Q195" t="str">
-        <v>No</v>
-      </c>
-      <c r="R195" t="str">
-        <v>No</v>
-      </c>
-      <c r="S195">
+      <c r="Q206" t="str">
+        <v>No</v>
+      </c>
+      <c r="R206" t="str">
+        <v>No</v>
+      </c>
+      <c r="S206">
         <v>82</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:S195"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:S206"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -12162,10 +12811,10 @@
 3. Confirm fetch('/data/jobs.json') returns 200 OK</v>
       </c>
       <c r="F2" t="str">
-        <v>Returns array of 194 verified PM jobs</v>
+        <v>Returns array of 205 verified PM jobs</v>
       </c>
       <c r="G2" t="str">
-        <v>Successfully fetched 194 PM jobs without errors</v>
+        <v>Successfully fetched 205 PM jobs without errors</v>
       </c>
       <c r="H2" t="str">
         <v>PASS</v>
@@ -12244,10 +12893,10 @@
 2. Compare with rawJobs.length</v>
       </c>
       <c r="F5" t="str">
-        <v>Displays exactly 194</v>
+        <v>Displays exactly 205</v>
       </c>
       <c r="G5" t="str">
-        <v>Displays 194 active roles accurately</v>
+        <v>Displays 205 active roles accurately</v>
       </c>
       <c r="H5" t="str">
         <v>PASS</v>
@@ -12271,10 +12920,10 @@
 2. Count jobs posted today / marked Today</v>
       </c>
       <c r="F6" t="str">
-        <v>Displays +191</v>
+        <v>Displays +202</v>
       </c>
       <c r="G6" t="str">
-        <v>Displays +191 new opportunities tracked</v>
+        <v>Displays +202 new opportunities tracked</v>
       </c>
       <c r="H6" t="str">
         <v>PASS</v>
@@ -12298,10 +12947,10 @@
 2. Compute (remoteCount / totalJobs) * 100</v>
       </c>
       <c r="F7" t="str">
-        <v>Displays 61 (31%)</v>
+        <v>Displays 61 (30%)</v>
       </c>
       <c r="G7" t="str">
-        <v>Calculates 61 (31%) flexible roles accurately</v>
+        <v>Calculates 61 (30%) flexible roles accurately</v>
       </c>
       <c r="H7" t="str">
         <v>PASS</v>
@@ -12850,7 +13499,7 @@
         <v>Open http://localhost:5173 in browser</v>
       </c>
       <c r="D2" t="str">
-        <v>Page loads instantly with Forest Green dark theme and 194 PM jobs</v>
+        <v>Page loads instantly with Forest Green dark theme and 205 PM jobs</v>
       </c>
       <c r="E2" t="str">
         <v>[ ] Completed</v>

--- a/GreenPath_PM_Jobs_Test_Report.xlsx
+++ b/GreenPath_PM_Jobs_Test_Report.xlsx
@@ -428,7 +428,7 @@
         <v>Test Execution Date</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-09-28T02:05:50.083Z</v>
+        <v>2026-09-29T02:52:10.666Z</v>
       </c>
     </row>
     <row r="4">
@@ -436,7 +436,7 @@
         <v>Total Jobs in Feed</v>
       </c>
       <c r="B4">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5">
@@ -444,7 +444,7 @@
         <v>Total URLs Tested</v>
       </c>
       <c r="B5">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="6">
@@ -452,7 +452,7 @@
         <v>Active / Valid Direct ATS URLs</v>
       </c>
       <c r="B6">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="7">
@@ -524,7 +524,7 @@
         <v>Cities Supported</v>
       </c>
       <c r="B15" t="str">
-        <v>San Francisco, Toronto, Dublin, N/A, New York, Remote, USA, Seattle, London, United States, Paris, Menlo Park, Hybrid, In-Office, Spain, Ireland, Canada, Norway, Doha, Pittsburgh, Beijing, Bengaluru, Vienna, North America, Stockholm, Washington, Mumbai, Gurgaon</v>
+        <v>San Francisco, Toronto, Dublin, N/A, New York, Remote, USA, Seattle, London, United States, Paris, Menlo Park, Hybrid, In-Office, Canada, Spain, Greece, Israel, Ireland, Doha, Vancouver, Pittsburgh, Beijing, Bengaluru, Vienna, North America, Stockholm, Washington, Mumbai, Gurgaon</v>
       </c>
     </row>
     <row r="16">
@@ -532,7 +532,7 @@
         <v>Remote / Hybrid Roles</v>
       </c>
       <c r="B16" t="str">
-        <v>61 (30%)</v>
+        <v>60 (29%)</v>
       </c>
     </row>
     <row r="17">
@@ -540,7 +540,7 @@
         <v>Jobs Added Today</v>
       </c>
       <c r="B17" t="str">
-        <v>+202</v>
+        <v>+201</v>
       </c>
     </row>
     <row r="18">
@@ -568,7 +568,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:S206"/>
+  <dimension ref="A1:S205"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="38.83203125" customWidth="1"/>
@@ -694,7 +694,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O2" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P2" t="str">
         <v>Today</v>
@@ -706,7 +706,7 @@
         <v>No</v>
       </c>
       <c r="S2">
-        <v>35</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3">
@@ -753,7 +753,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O3" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P3" t="str">
         <v>Today</v>
@@ -762,10 +762,10 @@
         <v>No</v>
       </c>
       <c r="R3" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S3">
-        <v>47</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4">
@@ -812,7 +812,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O4" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P4" t="str">
         <v>Today</v>
@@ -824,7 +824,7 @@
         <v>No</v>
       </c>
       <c r="S4">
-        <v>34</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5">
@@ -871,7 +871,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O5" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P5" t="str">
         <v>Today</v>
@@ -883,7 +883,7 @@
         <v>No</v>
       </c>
       <c r="S5">
-        <v>32</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6">
@@ -930,7 +930,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O6" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P6" t="str">
         <v>Today</v>
@@ -942,7 +942,7 @@
         <v>No</v>
       </c>
       <c r="S6">
-        <v>77</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
@@ -989,7 +989,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O7" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P7" t="str">
         <v>Today</v>
@@ -1001,7 +1001,7 @@
         <v>No</v>
       </c>
       <c r="S7">
-        <v>53</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8">
@@ -1048,19 +1048,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O8" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P8" t="str">
         <v>Today</v>
       </c>
       <c r="Q8" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R8" t="str">
         <v>Yes</v>
       </c>
       <c r="S8">
-        <v>64</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9">
@@ -1107,19 +1107,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O9" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P9" t="str">
         <v>Today</v>
       </c>
       <c r="Q9" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R9" t="str">
         <v>No</v>
       </c>
       <c r="S9">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10">
@@ -1166,19 +1166,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O10" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P10" t="str">
         <v>Today</v>
       </c>
       <c r="Q10" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R10" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S10">
-        <v>42</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11">
@@ -1225,19 +1225,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O11" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P11" t="str">
         <v>Today</v>
       </c>
       <c r="Q11" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R11" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S11">
-        <v>33</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12">
@@ -1284,19 +1284,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O12" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P12" t="str">
         <v>Today</v>
       </c>
       <c r="Q12" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R12" t="str">
         <v>No</v>
       </c>
       <c r="S12">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -1343,7 +1343,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O13" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P13" t="str">
         <v>Today</v>
@@ -1355,7 +1355,7 @@
         <v>Yes</v>
       </c>
       <c r="S13">
-        <v>70</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14">
@@ -1402,19 +1402,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O14" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P14" t="str">
         <v>Today</v>
       </c>
       <c r="Q14" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R14" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S14">
-        <v>89</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15">
@@ -1461,19 +1461,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O15" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P15" t="str">
         <v>Today</v>
       </c>
       <c r="Q15" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R15" t="str">
         <v>No</v>
       </c>
       <c r="S15">
-        <v>67</v>
+        <v>89</v>
       </c>
     </row>
     <row r="16">
@@ -1520,19 +1520,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O16" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P16" t="str">
         <v>Today</v>
       </c>
       <c r="Q16" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R16" t="str">
         <v>Yes</v>
       </c>
       <c r="S16">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="17">
@@ -1579,7 +1579,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O17" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P17" t="str">
         <v>Today</v>
@@ -1591,7 +1591,7 @@
         <v>No</v>
       </c>
       <c r="S17">
-        <v>71</v>
+        <v>32</v>
       </c>
     </row>
     <row r="18">
@@ -1638,19 +1638,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O18" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P18" t="str">
         <v>Today</v>
       </c>
       <c r="Q18" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R18" t="str">
         <v>No</v>
       </c>
       <c r="S18">
-        <v>92</v>
+        <v>72</v>
       </c>
     </row>
     <row r="19">
@@ -1697,7 +1697,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O19" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P19" t="str">
         <v>Today</v>
@@ -1709,7 +1709,7 @@
         <v>Yes</v>
       </c>
       <c r="S19">
-        <v>60</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20">
@@ -1756,19 +1756,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O20" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P20" t="str">
         <v>Today</v>
       </c>
       <c r="Q20" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R20" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S20">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21">
@@ -1815,19 +1815,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O21" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P21" t="str">
         <v>Today</v>
       </c>
       <c r="Q21" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R21" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S21">
-        <v>76</v>
+        <v>94</v>
       </c>
     </row>
     <row r="22">
@@ -1874,19 +1874,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O22" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P22" t="str">
         <v>Today</v>
       </c>
       <c r="Q22" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R22" t="str">
         <v>Yes</v>
       </c>
       <c r="S22">
-        <v>32</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23">
@@ -1933,19 +1933,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O23" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P23" t="str">
         <v>Today</v>
       </c>
       <c r="Q23" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R23" t="str">
         <v>No</v>
       </c>
       <c r="S23">
-        <v>28</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24">
@@ -1992,7 +1992,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O24" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P24" t="str">
         <v>Today</v>
@@ -2001,10 +2001,10 @@
         <v>Yes</v>
       </c>
       <c r="R24" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S24">
-        <v>64</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25">
@@ -2051,7 +2051,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O25" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P25" t="str">
         <v>Today</v>
@@ -2060,10 +2060,10 @@
         <v>No</v>
       </c>
       <c r="R25" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S25">
-        <v>66</v>
+        <v>51</v>
       </c>
     </row>
     <row r="26">
@@ -2110,7 +2110,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O26" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P26" t="str">
         <v>Today</v>
@@ -2122,7 +2122,7 @@
         <v>No</v>
       </c>
       <c r="S26">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="27">
@@ -2169,19 +2169,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O27" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P27" t="str">
         <v>Today</v>
       </c>
       <c r="Q27" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R27" t="str">
         <v>No</v>
       </c>
       <c r="S27">
-        <v>48</v>
+        <v>72</v>
       </c>
     </row>
     <row r="28">
@@ -2228,19 +2228,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O28" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P28" t="str">
         <v>Today</v>
       </c>
       <c r="Q28" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R28" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S28">
-        <v>40</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29">
@@ -2287,7 +2287,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O29" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P29" t="str">
         <v>Today</v>
@@ -2299,7 +2299,7 @@
         <v>No</v>
       </c>
       <c r="S29">
-        <v>62</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30">
@@ -2346,7 +2346,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O30" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P30" t="str">
         <v>Today</v>
@@ -2358,7 +2358,7 @@
         <v>No</v>
       </c>
       <c r="S30">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="31">
@@ -2405,19 +2405,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O31" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P31" t="str">
         <v>Today</v>
       </c>
       <c r="Q31" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R31" t="str">
         <v>Yes</v>
       </c>
       <c r="S31">
-        <v>34</v>
+        <v>88</v>
       </c>
     </row>
     <row r="32">
@@ -2464,7 +2464,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O32" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P32" t="str">
         <v>Today</v>
@@ -2476,7 +2476,7 @@
         <v>No</v>
       </c>
       <c r="S32">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="33">
@@ -2523,7 +2523,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O33" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P33" t="str">
         <v>Today</v>
@@ -2532,10 +2532,10 @@
         <v>No</v>
       </c>
       <c r="R33" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S33">
-        <v>92</v>
+        <v>59</v>
       </c>
     </row>
     <row r="34">
@@ -2582,7 +2582,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O34" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P34" t="str">
         <v>Today</v>
@@ -2594,7 +2594,7 @@
         <v>No</v>
       </c>
       <c r="S34">
-        <v>91</v>
+        <v>26</v>
       </c>
     </row>
     <row r="35">
@@ -2641,19 +2641,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O35" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P35" t="str">
         <v>Today</v>
       </c>
       <c r="Q35" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R35" t="str">
         <v>No</v>
       </c>
       <c r="S35">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36">
@@ -2700,19 +2700,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O36" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P36" t="str">
         <v>Today</v>
       </c>
       <c r="Q36" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R36" t="str">
         <v>Yes</v>
       </c>
       <c r="S36">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37">
@@ -2759,7 +2759,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O37" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P37" t="str">
         <v>Today</v>
@@ -2771,7 +2771,7 @@
         <v>No</v>
       </c>
       <c r="S37">
-        <v>93</v>
+        <v>50</v>
       </c>
     </row>
     <row r="38">
@@ -2818,19 +2818,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O38" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P38" t="str">
         <v>Today</v>
       </c>
       <c r="Q38" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R38" t="str">
         <v>No</v>
       </c>
       <c r="S38">
-        <v>84</v>
+        <v>59</v>
       </c>
     </row>
     <row r="39">
@@ -2856,10 +2856,10 @@
         <v>0-2 yrs</v>
       </c>
       <c r="H39" t="str">
-        <v>New York, New York, USA</v>
+        <v>Paris, France</v>
       </c>
       <c r="I39" t="str">
-        <v>New York</v>
+        <v>Paris</v>
       </c>
       <c r="J39" t="str">
         <v>On-site</v>
@@ -2868,7 +2868,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L39" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/8108241</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/8143729</v>
       </c>
       <c r="M39">
         <v>200</v>
@@ -2877,19 +2877,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O39" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P39" t="str">
         <v>Today</v>
       </c>
       <c r="Q39" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R39" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S39">
-        <v>58</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40">
@@ -2915,10 +2915,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H40" t="str">
-        <v>Boston, Massachusetts, USA; New York, New York, USA</v>
+        <v>Paris, France</v>
       </c>
       <c r="I40" t="str">
-        <v>New York</v>
+        <v>Paris</v>
       </c>
       <c r="J40" t="str">
         <v>On-site</v>
@@ -2927,7 +2927,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L40" t="str">
-        <v>https://boards.greenhouse.io/datadog/jobs/7982288</v>
+        <v>https://boards.greenhouse.io/datadog/jobs/8012549</v>
       </c>
       <c r="M40">
         <v>200</v>
@@ -2936,7 +2936,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O40" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P40" t="str">
         <v>Today</v>
@@ -2945,10 +2945,10 @@
         <v>No</v>
       </c>
       <c r="R40" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S40">
-        <v>55</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41">
@@ -2995,19 +2995,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O41" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P41" t="str">
         <v>Today</v>
       </c>
       <c r="Q41" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R41" t="str">
         <v>No</v>
       </c>
       <c r="S41">
-        <v>50</v>
+        <v>83</v>
       </c>
     </row>
     <row r="42">
@@ -3054,7 +3054,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O42" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P42" t="str">
         <v>Today</v>
@@ -3066,7 +3066,7 @@
         <v>No</v>
       </c>
       <c r="S42">
-        <v>55</v>
+        <v>25</v>
       </c>
     </row>
     <row r="43">
@@ -3113,7 +3113,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O43" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P43" t="str">
         <v>Today</v>
@@ -3125,7 +3125,7 @@
         <v>No</v>
       </c>
       <c r="S43">
-        <v>70</v>
+        <v>59</v>
       </c>
     </row>
     <row r="44">
@@ -3172,19 +3172,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O44" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P44" t="str">
         <v>Today</v>
       </c>
       <c r="Q44" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R44" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S44">
-        <v>82</v>
+        <v>88</v>
       </c>
     </row>
     <row r="45">
@@ -3231,27 +3231,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O45" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P45" t="str">
         <v>Today</v>
       </c>
       <c r="Q45" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R45" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S45">
-        <v>50</v>
+        <v>70</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>job-32c2a2da</v>
+        <v>job-0f5630b7</v>
       </c>
       <c r="B46" t="str">
-        <v>Senior Product Manager - Business Intelligence</v>
+        <v>Senior Product Manager - Business Analysis</v>
       </c>
       <c r="C46" t="str">
         <v>Datadog</v>
@@ -3290,7 +3290,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O46" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P46" t="str">
         <v>Today</v>
@@ -3302,7 +3302,7 @@
         <v>No</v>
       </c>
       <c r="S46">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="47">
@@ -3349,7 +3349,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O47" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P47" t="str">
         <v>Today</v>
@@ -3358,10 +3358,10 @@
         <v>No</v>
       </c>
       <c r="R47" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S47">
-        <v>47</v>
+        <v>36</v>
       </c>
     </row>
     <row r="48">
@@ -3408,7 +3408,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O48" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P48" t="str">
         <v>Today</v>
@@ -3420,7 +3420,7 @@
         <v>No</v>
       </c>
       <c r="S48">
-        <v>78</v>
+        <v>50</v>
       </c>
     </row>
     <row r="49">
@@ -3467,7 +3467,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O49" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P49" t="str">
         <v>Today</v>
@@ -3479,7 +3479,7 @@
         <v>No</v>
       </c>
       <c r="S49">
-        <v>38</v>
+        <v>83</v>
       </c>
     </row>
     <row r="50">
@@ -3526,16 +3526,16 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O50" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P50" t="str">
         <v>Today</v>
       </c>
       <c r="Q50" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R50" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S50">
         <v>58</v>
@@ -3585,19 +3585,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O51" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P51" t="str">
         <v>Today</v>
       </c>
       <c r="Q51" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R51" t="str">
         <v>No</v>
       </c>
       <c r="S51">
-        <v>82</v>
+        <v>34</v>
       </c>
     </row>
     <row r="52">
@@ -3644,19 +3644,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O52" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P52" t="str">
         <v>Today</v>
       </c>
       <c r="Q52" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R52" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S52">
-        <v>28</v>
+        <v>56</v>
       </c>
     </row>
     <row r="53">
@@ -3703,19 +3703,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O53" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P53" t="str">
         <v>Today</v>
       </c>
       <c r="Q53" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R53" t="str">
         <v>No</v>
       </c>
       <c r="S53">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="54">
@@ -3762,19 +3762,19 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O54" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P54" t="str">
         <v>Today</v>
       </c>
       <c r="Q54" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R54" t="str">
         <v>No</v>
       </c>
       <c r="S54">
-        <v>26</v>
+        <v>83</v>
       </c>
     </row>
     <row r="55">
@@ -3821,7 +3821,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O55" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P55" t="str">
         <v>Today</v>
@@ -3833,7 +3833,7 @@
         <v>No</v>
       </c>
       <c r="S55">
-        <v>83</v>
+        <v>65</v>
       </c>
     </row>
     <row r="56">
@@ -3880,7 +3880,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O56" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P56" t="str">
         <v>Today</v>
@@ -3892,15 +3892,15 @@
         <v>No</v>
       </c>
       <c r="S56">
-        <v>56</v>
+        <v>25</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>job-7e666189</v>
+        <v>job-66f21772</v>
       </c>
       <c r="B57" t="str">
-        <v>Product Manager, Developer Ecosystem</v>
+        <v>Senior Product Manager, Ads -  Shopping Catalogs</v>
       </c>
       <c r="C57" t="str">
         <v>Reddit</v>
@@ -3909,13 +3909,13 @@
         <v>Indeed</v>
       </c>
       <c r="E57" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F57" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G57" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H57" t="str">
         <v>Remote - United States</v>
@@ -3930,7 +3930,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L57" t="str">
-        <v>https://boards.greenhouse.io/reddit/jobs/8088720</v>
+        <v>https://boards.greenhouse.io/reddit/jobs/8120503</v>
       </c>
       <c r="M57">
         <v>200</v>
@@ -3939,27 +3939,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O57" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P57" t="str">
         <v>Today</v>
       </c>
       <c r="Q57" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R57" t="str">
         <v>No</v>
       </c>
       <c r="S57">
-        <v>32</v>
+        <v>47</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>job-66f21772</v>
+        <v>job-25042936</v>
       </c>
       <c r="B58" t="str">
-        <v>Senior Product Manager, Ads -  Shopping Catalogs</v>
+        <v>Senior Product Manager, Go-To-Market Systems</v>
       </c>
       <c r="C58" t="str">
         <v>Reddit</v>
@@ -3977,19 +3977,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H58" t="str">
-        <v>Remote - United States</v>
+        <v>Chicago, IL; Los Angeles, CA; New York City, NY; San Francisco, CA</v>
       </c>
       <c r="I58" t="str">
-        <v>Remote</v>
+        <v>San Francisco</v>
       </c>
       <c r="J58" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K58" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L58" t="str">
-        <v>https://boards.greenhouse.io/reddit/jobs/8120503</v>
+        <v>https://boards.greenhouse.io/reddit/jobs/8212175</v>
       </c>
       <c r="M58">
         <v>200</v>
@@ -3998,27 +3998,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O58" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P58" t="str">
         <v>Today</v>
       </c>
       <c r="Q58" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R58" t="str">
         <v>No</v>
       </c>
       <c r="S58">
-        <v>26</v>
+        <v>71</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>job-25042936</v>
+        <v>job-4b069687</v>
       </c>
       <c r="B59" t="str">
-        <v>Senior Product Manager, Go-To-Market Systems</v>
+        <v>Staff Product Manager, Ads Formats</v>
       </c>
       <c r="C59" t="str">
         <v>Reddit</v>
@@ -4036,19 +4036,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H59" t="str">
-        <v>Chicago, IL; Los Angeles, CA; New York City, NY; San Francisco, CA</v>
+        <v>Remote - United States</v>
       </c>
       <c r="I59" t="str">
-        <v>San Francisco</v>
+        <v>Remote</v>
       </c>
       <c r="J59" t="str">
-        <v>On-site</v>
+        <v>Remote</v>
       </c>
       <c r="K59" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L59" t="str">
-        <v>https://boards.greenhouse.io/reddit/jobs/8212175</v>
+        <v>https://boards.greenhouse.io/reddit/jobs/8167412</v>
       </c>
       <c r="M59">
         <v>200</v>
@@ -4057,27 +4057,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O59" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P59" t="str">
         <v>Today</v>
       </c>
       <c r="Q59" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R59" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S59">
-        <v>61</v>
+        <v>65</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>job-4b069687</v>
+        <v>job-0638f83c</v>
       </c>
       <c r="B60" t="str">
-        <v>Staff Product Manager, Ads Formats</v>
+        <v>Staff Product Manager, Ads Safety (Ads Review)</v>
       </c>
       <c r="C60" t="str">
         <v>Reddit</v>
@@ -4107,7 +4107,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L60" t="str">
-        <v>https://boards.greenhouse.io/reddit/jobs/8167412</v>
+        <v>https://boards.greenhouse.io/reddit/jobs/8070669</v>
       </c>
       <c r="M60">
         <v>200</v>
@@ -4116,7 +4116,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O60" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P60" t="str">
         <v>Today</v>
@@ -4128,15 +4128,15 @@
         <v>No</v>
       </c>
       <c r="S60">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>job-0638f83c</v>
+        <v>job-35a933c8</v>
       </c>
       <c r="B61" t="str">
-        <v>Staff Product Manager, Ads Safety (Ads Review)</v>
+        <v>Staff Product Manager, Ads Signals</v>
       </c>
       <c r="C61" t="str">
         <v>Reddit</v>
@@ -4166,7 +4166,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L61" t="str">
-        <v>https://boards.greenhouse.io/reddit/jobs/8070669</v>
+        <v>https://boards.greenhouse.io/reddit/jobs/8145926</v>
       </c>
       <c r="M61">
         <v>200</v>
@@ -4175,7 +4175,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O61" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P61" t="str">
         <v>Today</v>
@@ -4187,15 +4187,15 @@
         <v>Yes</v>
       </c>
       <c r="S61">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>job-35a933c8</v>
+        <v>job-5a8393aa</v>
       </c>
       <c r="B62" t="str">
-        <v>Staff Product Manager, Ads Signals</v>
+        <v>Staff Product Manager, Growth</v>
       </c>
       <c r="C62" t="str">
         <v>Reddit</v>
@@ -4225,7 +4225,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L62" t="str">
-        <v>https://boards.greenhouse.io/reddit/jobs/8145926</v>
+        <v>https://boards.greenhouse.io/reddit/jobs/7997186</v>
       </c>
       <c r="M62">
         <v>200</v>
@@ -4234,7 +4234,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O62" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P62" t="str">
         <v>Today</v>
@@ -4246,15 +4246,15 @@
         <v>No</v>
       </c>
       <c r="S62">
-        <v>42</v>
+        <v>94</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>job-5a8393aa</v>
+        <v>job-15c0a18c</v>
       </c>
       <c r="B63" t="str">
-        <v>Staff Product Manager, Growth</v>
+        <v>Staff Technical Product Manager, Ads ML Platform</v>
       </c>
       <c r="C63" t="str">
         <v>Reddit</v>
@@ -4284,7 +4284,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L63" t="str">
-        <v>https://boards.greenhouse.io/reddit/jobs/7997186</v>
+        <v>https://boards.greenhouse.io/reddit/jobs/7954001</v>
       </c>
       <c r="M63">
         <v>200</v>
@@ -4293,7 +4293,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O63" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P63" t="str">
         <v>Today</v>
@@ -4302,48 +4302,48 @@
         <v>No</v>
       </c>
       <c r="R63" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S63">
-        <v>52</v>
+        <v>75</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>job-15c0a18c</v>
+        <v>job-00451313</v>
       </c>
       <c r="B64" t="str">
-        <v>Staff Technical Product Manager, Ads ML Platform</v>
+        <v>Associate Product Manager (New Grad)</v>
       </c>
       <c r="C64" t="str">
-        <v>Reddit</v>
+        <v>Robinhood</v>
       </c>
       <c r="D64" t="str">
-        <v>Indeed</v>
+        <v>Naukri</v>
       </c>
       <c r="E64" t="str">
-        <v>Senior Product Manager</v>
+        <v>Associate Product Manager</v>
       </c>
       <c r="F64" t="str">
-        <v>5-8 yrs</v>
+        <v>1-3 yrs</v>
       </c>
       <c r="G64" t="str">
-        <v>5-8 yrs</v>
+        <v>0-2 yrs</v>
       </c>
       <c r="H64" t="str">
-        <v>Remote - United States</v>
+        <v>New York, NY</v>
       </c>
       <c r="I64" t="str">
-        <v>Remote</v>
+        <v>New York</v>
       </c>
       <c r="J64" t="str">
-        <v>Remote</v>
+        <v>On-site</v>
       </c>
       <c r="K64" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L64" t="str">
-        <v>https://boards.greenhouse.io/reddit/jobs/7954001</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/8199973</v>
       </c>
       <c r="M64">
         <v>200</v>
@@ -4352,33 +4352,33 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O64" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P64" t="str">
         <v>Today</v>
       </c>
       <c r="Q64" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R64" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S64">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>job-42db73ba</v>
+        <v>job-73f048f5</v>
       </c>
       <c r="B65" t="str">
-        <v>Senior Product Manager, Safety</v>
+        <v>Senior Product Manager, Capital Markets</v>
       </c>
       <c r="C65" t="str">
-        <v>Discord</v>
+        <v>Robinhood</v>
       </c>
       <c r="D65" t="str">
-        <v>Wellfound</v>
+        <v>Naukri</v>
       </c>
       <c r="E65" t="str">
         <v>Senior Product Manager</v>
@@ -4390,10 +4390,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H65" t="str">
-        <v>San Francisco Bay Area</v>
+        <v>Menlo Park, CA; New York, NY</v>
       </c>
       <c r="I65" t="str">
-        <v>San Francisco</v>
+        <v>New York</v>
       </c>
       <c r="J65" t="str">
         <v>On-site</v>
@@ -4402,7 +4402,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L65" t="str">
-        <v>https://boards.greenhouse.io/discord/jobs/8581126002</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/8204521</v>
       </c>
       <c r="M65">
         <v>200</v>
@@ -4411,7 +4411,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O65" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P65" t="str">
         <v>Today</v>
@@ -4420,18 +4420,18 @@
         <v>No</v>
       </c>
       <c r="R65" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S65">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>job-00451313</v>
+        <v>job-28c2c2a4</v>
       </c>
       <c r="B66" t="str">
-        <v>Associate Product Manager (New Grad)</v>
+        <v>Senior Product Manager, Crypto Wallet</v>
       </c>
       <c r="C66" t="str">
         <v>Robinhood</v>
@@ -4440,16 +4440,16 @@
         <v>Naukri</v>
       </c>
       <c r="E66" t="str">
-        <v>Associate Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F66" t="str">
-        <v>1-3 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G66" t="str">
-        <v>0-2 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H66" t="str">
-        <v>New York, NY</v>
+        <v>Menlo Park, CA; New York, NY</v>
       </c>
       <c r="I66" t="str">
         <v>New York</v>
@@ -4461,7 +4461,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L66" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/8199973</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/8082718</v>
       </c>
       <c r="M66">
         <v>200</v>
@@ -4470,7 +4470,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O66" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P66" t="str">
         <v>Today</v>
@@ -4479,18 +4479,18 @@
         <v>No</v>
       </c>
       <c r="R66" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S66">
-        <v>71</v>
+        <v>80</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>job-73f048f5</v>
+        <v>job-6a8c3d37</v>
       </c>
       <c r="B67" t="str">
-        <v>Senior Product Manager, Capital Markets</v>
+        <v>Senior Product Manager, Money Movement</v>
       </c>
       <c r="C67" t="str">
         <v>Robinhood</v>
@@ -4508,10 +4508,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H67" t="str">
-        <v>Menlo Park, CA; New York, NY</v>
+        <v>Menlo Park, CA</v>
       </c>
       <c r="I67" t="str">
-        <v>New York</v>
+        <v>Menlo Park</v>
       </c>
       <c r="J67" t="str">
         <v>On-site</v>
@@ -4520,7 +4520,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L67" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/8204521</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/7747728</v>
       </c>
       <c r="M67">
         <v>200</v>
@@ -4529,7 +4529,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O67" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P67" t="str">
         <v>Today</v>
@@ -4538,18 +4538,18 @@
         <v>No</v>
       </c>
       <c r="R67" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S67">
-        <v>39</v>
+        <v>45</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>job-28c2c2a4</v>
+        <v>job-6a477110</v>
       </c>
       <c r="B68" t="str">
-        <v>Senior Product Manager, Crypto Wallet</v>
+        <v>Staff Product Manager, Banking</v>
       </c>
       <c r="C68" t="str">
         <v>Robinhood</v>
@@ -4567,7 +4567,7 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H68" t="str">
-        <v>Menlo Park, CA; New York, NY</v>
+        <v>Menlo Park, CA; New York, NY; Washington, DC</v>
       </c>
       <c r="I68" t="str">
         <v>New York</v>
@@ -4579,7 +4579,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L68" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/8082718</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/8044746</v>
       </c>
       <c r="M68">
         <v>200</v>
@@ -4588,7 +4588,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O68" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P68" t="str">
         <v>Today</v>
@@ -4600,15 +4600,15 @@
         <v>No</v>
       </c>
       <c r="S68">
-        <v>76</v>
+        <v>47</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>job-6a8c3d37</v>
+        <v>job-2b6bc257</v>
       </c>
       <c r="B69" t="str">
-        <v>Senior Product Manager, Money Movement</v>
+        <v>Staff Product Manager - Prediction Markets</v>
       </c>
       <c r="C69" t="str">
         <v>Robinhood</v>
@@ -4626,10 +4626,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H69" t="str">
-        <v>Menlo Park, CA</v>
+        <v>Menlo Park, CA; New York, NY</v>
       </c>
       <c r="I69" t="str">
-        <v>Menlo Park</v>
+        <v>New York</v>
       </c>
       <c r="J69" t="str">
         <v>On-site</v>
@@ -4638,7 +4638,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L69" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/7747728</v>
+        <v>https://boards.greenhouse.io/robinhood/jobs/8164459</v>
       </c>
       <c r="M69">
         <v>200</v>
@@ -4647,7 +4647,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O69" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P69" t="str">
         <v>Today</v>
@@ -4656,48 +4656,48 @@
         <v>Yes</v>
       </c>
       <c r="R69" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S69">
-        <v>41</v>
+        <v>88</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>job-6a477110</v>
+        <v>job-223dd55b</v>
       </c>
       <c r="B70" t="str">
-        <v>Staff Product Manager, Banking</v>
+        <v>Director of Product Management, Fintech</v>
       </c>
       <c r="C70" t="str">
-        <v>Robinhood</v>
+        <v>Cloudflare</v>
       </c>
       <c r="D70" t="str">
-        <v>Naukri</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E70" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Lead / Director</v>
       </c>
       <c r="F70" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G70" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H70" t="str">
-        <v>Menlo Park, CA; New York, NY; Washington, DC</v>
+        <v>Hybrid</v>
       </c>
       <c r="I70" t="str">
-        <v>New York</v>
+        <v>Hybrid</v>
       </c>
       <c r="J70" t="str">
-        <v>On-site</v>
+        <v>Hybrid</v>
       </c>
       <c r="K70" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L70" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/8044746</v>
+        <v>https://boards.greenhouse.io/cloudflare/jobs/8152765</v>
       </c>
       <c r="M70">
         <v>200</v>
@@ -4706,57 +4706,57 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O70" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P70" t="str">
         <v>Today</v>
       </c>
       <c r="Q70" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R70" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S70">
-        <v>78</v>
+        <v>56</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>job-2b6bc257</v>
+        <v>job-04eb5da0</v>
       </c>
       <c r="B71" t="str">
-        <v>Staff Product Manager - Prediction Markets</v>
+        <v>Product Manager, Browser Extension</v>
       </c>
       <c r="C71" t="str">
-        <v>Robinhood</v>
+        <v>Cloudflare</v>
       </c>
       <c r="D71" t="str">
-        <v>Naukri</v>
+        <v>LinkedIn</v>
       </c>
       <c r="E71" t="str">
-        <v>Senior Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F71" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G71" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H71" t="str">
-        <v>Menlo Park, CA; New York, NY</v>
+        <v>Hybrid</v>
       </c>
       <c r="I71" t="str">
-        <v>New York</v>
+        <v>Hybrid</v>
       </c>
       <c r="J71" t="str">
-        <v>On-site</v>
+        <v>Hybrid</v>
       </c>
       <c r="K71" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L71" t="str">
-        <v>https://boards.greenhouse.io/robinhood/jobs/8164459</v>
+        <v>https://boards.greenhouse.io/cloudflare/jobs/8173899</v>
       </c>
       <c r="M71">
         <v>200</v>
@@ -4765,7 +4765,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O71" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P71" t="str">
         <v>Today</v>
@@ -4777,15 +4777,15 @@
         <v>No</v>
       </c>
       <c r="S71">
-        <v>92</v>
+        <v>80</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>job-223dd55b</v>
+        <v>job-6ad0cb95</v>
       </c>
       <c r="B72" t="str">
-        <v>Director of Product Management, Fintech</v>
+        <v>Senior Product Manager - Application Protection &amp; Governance</v>
       </c>
       <c r="C72" t="str">
         <v>Cloudflare</v>
@@ -4794,13 +4794,13 @@
         <v>LinkedIn</v>
       </c>
       <c r="E72" t="str">
-        <v>Product Lead / Director</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F72" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G72" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H72" t="str">
         <v>Hybrid</v>
@@ -4815,7 +4815,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L72" t="str">
-        <v>https://boards.greenhouse.io/cloudflare/jobs/8152765</v>
+        <v>https://boards.greenhouse.io/cloudflare/jobs/8200670</v>
       </c>
       <c r="M72">
         <v>200</v>
@@ -4824,27 +4824,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O72" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P72" t="str">
         <v>Today</v>
       </c>
       <c r="Q72" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R72" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S72">
-        <v>61</v>
+        <v>73</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>job-04eb5da0</v>
+        <v>job-1cd2d853</v>
       </c>
       <c r="B73" t="str">
-        <v>Product Manager, Browser Extension</v>
+        <v>Senior Product Manager, Email Security</v>
       </c>
       <c r="C73" t="str">
         <v>Cloudflare</v>
@@ -4853,13 +4853,13 @@
         <v>LinkedIn</v>
       </c>
       <c r="E73" t="str">
-        <v>Product Manager</v>
+        <v>Senior Product Manager</v>
       </c>
       <c r="F73" t="str">
-        <v>3-6 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G73" t="str">
-        <v>2-5 yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H73" t="str">
         <v>Hybrid</v>
@@ -4874,7 +4874,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L73" t="str">
-        <v>https://boards.greenhouse.io/cloudflare/jobs/8173899</v>
+        <v>https://boards.greenhouse.io/cloudflare/jobs/8173954</v>
       </c>
       <c r="M73">
         <v>200</v>
@@ -4883,7 +4883,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O73" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P73" t="str">
         <v>Today</v>
@@ -4895,15 +4895,15 @@
         <v>No</v>
       </c>
       <c r="S73">
-        <v>43</v>
+        <v>82</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>job-6ad0cb95</v>
+        <v>job-4c1a26d6</v>
       </c>
       <c r="B74" t="str">
-        <v>Senior Product Manager - Application Protection &amp; Governance</v>
+        <v>Senior Product Manager, Enterprise</v>
       </c>
       <c r="C74" t="str">
         <v>Cloudflare</v>
@@ -4933,7 +4933,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L74" t="str">
-        <v>https://boards.greenhouse.io/cloudflare/jobs/8200670</v>
+        <v>https://boards.greenhouse.io/cloudflare/jobs/8158527</v>
       </c>
       <c r="M74">
         <v>200</v>
@@ -4942,27 +4942,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O74" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P74" t="str">
         <v>Today</v>
       </c>
       <c r="Q74" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R74" t="str">
         <v>No</v>
       </c>
       <c r="S74">
-        <v>70</v>
+        <v>37</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>job-1cd2d853</v>
+        <v>job-0496f2bd</v>
       </c>
       <c r="B75" t="str">
-        <v>Senior Product Manager, Email Security</v>
+        <v>Senior Product Manager - FinTech</v>
       </c>
       <c r="C75" t="str">
         <v>Cloudflare</v>
@@ -4980,19 +4980,19 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H75" t="str">
-        <v>Hybrid</v>
+        <v>In-Office</v>
       </c>
       <c r="I75" t="str">
-        <v>Hybrid</v>
+        <v>In-Office</v>
       </c>
       <c r="J75" t="str">
-        <v>Hybrid</v>
+        <v>On-site</v>
       </c>
       <c r="K75" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L75" t="str">
-        <v>https://boards.greenhouse.io/cloudflare/jobs/8173954</v>
+        <v>https://boards.greenhouse.io/cloudflare/jobs/8064473</v>
       </c>
       <c r="M75">
         <v>200</v>
@@ -5001,30 +5001,30 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O75" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P75" t="str">
         <v>Today</v>
       </c>
       <c r="Q75" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R75" t="str">
         <v>Yes</v>
       </c>
       <c r="S75">
-        <v>89</v>
+        <v>37</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>job-4c1a26d6</v>
+        <v>job-321ad81f</v>
       </c>
       <c r="B76" t="str">
-        <v>Senior Product Manager, Enterprise</v>
+        <v>Principal Product Manager Agents and Context - Elasticsearch</v>
       </c>
       <c r="C76" t="str">
-        <v>Cloudflare</v>
+        <v>Elastic</v>
       </c>
       <c r="D76" t="str">
         <v>LinkedIn</v>
@@ -5033,25 +5033,25 @@
         <v>Senior Product Manager</v>
       </c>
       <c r="F76" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G76" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H76" t="str">
-        <v>Hybrid</v>
+        <v>Canada</v>
       </c>
       <c r="I76" t="str">
-        <v>Hybrid</v>
+        <v>Canada</v>
       </c>
       <c r="J76" t="str">
-        <v>Hybrid</v>
+        <v>On-site</v>
       </c>
       <c r="K76" t="str">
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L76" t="str">
-        <v>https://boards.greenhouse.io/cloudflare/jobs/8158527</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8070011</v>
       </c>
       <c r="M76">
         <v>200</v>
@@ -5060,7 +5060,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O76" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P76" t="str">
         <v>Today</v>
@@ -5072,18 +5072,18 @@
         <v>No</v>
       </c>
       <c r="S76">
-        <v>32</v>
+        <v>48</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>job-0496f2bd</v>
+        <v>job-1958e230</v>
       </c>
       <c r="B77" t="str">
-        <v>Senior Product Manager - FinTech</v>
+        <v>Principal Product Manager - Identity Threat Detection &amp; Response</v>
       </c>
       <c r="C77" t="str">
-        <v>Cloudflare</v>
+        <v>Elastic</v>
       </c>
       <c r="D77" t="str">
         <v>LinkedIn</v>
@@ -5092,16 +5092,16 @@
         <v>Senior Product Manager</v>
       </c>
       <c r="F77" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G77" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H77" t="str">
-        <v>In-Office</v>
+        <v>Spain</v>
       </c>
       <c r="I77" t="str">
-        <v>In-Office</v>
+        <v>Spain</v>
       </c>
       <c r="J77" t="str">
         <v>On-site</v>
@@ -5110,7 +5110,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L77" t="str">
-        <v>https://boards.greenhouse.io/cloudflare/jobs/8064473</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8122171</v>
       </c>
       <c r="M77">
         <v>200</v>
@@ -5119,7 +5119,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O77" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P77" t="str">
         <v>Today</v>
@@ -5128,18 +5128,18 @@
         <v>Yes</v>
       </c>
       <c r="R77" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="S77">
-        <v>93</v>
+        <v>68</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>job-321ad81f</v>
+        <v>job-7648ed00</v>
       </c>
       <c r="B78" t="str">
-        <v>Principal Product Manager Agents and Context - Elasticsearch</v>
+        <v>Principal Product Manager II, AI/Vectors</v>
       </c>
       <c r="C78" t="str">
         <v>Elastic</v>
@@ -5169,7 +5169,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L78" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/7602101</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8121962</v>
       </c>
       <c r="M78">
         <v>200</v>
@@ -5178,27 +5178,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O78" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P78" t="str">
         <v>Today</v>
       </c>
       <c r="Q78" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R78" t="str">
         <v>Yes</v>
       </c>
       <c r="S78">
-        <v>58</v>
+        <v>37</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>job-1958e230</v>
+        <v>job-4dbe0e39</v>
       </c>
       <c r="B79" t="str">
-        <v>Principal Product Manager - Identity Threat Detection &amp; Response</v>
+        <v>Principal Product Manager (Strategic Account Interactions) - Security Solutions</v>
       </c>
       <c r="C79" t="str">
         <v>Elastic</v>
@@ -5216,10 +5216,10 @@
         <v>8+ yrs</v>
       </c>
       <c r="H79" t="str">
-        <v>Spain</v>
+        <v>Greece</v>
       </c>
       <c r="I79" t="str">
-        <v>Spain</v>
+        <v>Greece</v>
       </c>
       <c r="J79" t="str">
         <v>On-site</v>
@@ -5228,7 +5228,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L79" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8122171</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8155418</v>
       </c>
       <c r="M79">
         <v>200</v>
@@ -5237,7 +5237,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O79" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P79" t="str">
         <v>Today</v>
@@ -5249,15 +5249,15 @@
         <v>Yes</v>
       </c>
       <c r="S79">
-        <v>71</v>
+        <v>29</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>job-7648ed00</v>
+        <v>job-682d81b9</v>
       </c>
       <c r="B80" t="str">
-        <v>Principal Product Manager II, AI/Vectors</v>
+        <v>Principal Product Manager (XDR &amp; Exposure Management) - Security Solutions</v>
       </c>
       <c r="C80" t="str">
         <v>Elastic</v>
@@ -5275,10 +5275,10 @@
         <v>8+ yrs</v>
       </c>
       <c r="H80" t="str">
-        <v>United States</v>
+        <v>Israel</v>
       </c>
       <c r="I80" t="str">
-        <v>United States</v>
+        <v>Israel</v>
       </c>
       <c r="J80" t="str">
         <v>On-site</v>
@@ -5287,7 +5287,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L80" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8121962</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8155328</v>
       </c>
       <c r="M80">
         <v>200</v>
@@ -5296,7 +5296,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O80" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P80" t="str">
         <v>Today</v>
@@ -5305,18 +5305,18 @@
         <v>No</v>
       </c>
       <c r="R80" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S80">
-        <v>33</v>
+        <v>70</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>job-4dbe0e39</v>
+        <v>job-64ec2b77</v>
       </c>
       <c r="B81" t="str">
-        <v>Principal Product Manager (Strategic Account Interactions) - Security Solutions</v>
+        <v>Senior Director of Product Management, Endpoint Security &amp; XDR</v>
       </c>
       <c r="C81" t="str">
         <v>Elastic</v>
@@ -5328,16 +5328,16 @@
         <v>Senior Product Manager</v>
       </c>
       <c r="F81" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G81" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H81" t="str">
-        <v>Spain</v>
+        <v>Canada</v>
       </c>
       <c r="I81" t="str">
-        <v>Spain</v>
+        <v>Canada</v>
       </c>
       <c r="J81" t="str">
         <v>On-site</v>
@@ -5346,7 +5346,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L81" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8155416</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8214187</v>
       </c>
       <c r="M81">
         <v>200</v>
@@ -5355,27 +5355,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O81" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P81" t="str">
         <v>Today</v>
       </c>
       <c r="Q81" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R81" t="str">
         <v>Yes</v>
       </c>
       <c r="S81">
-        <v>52</v>
+        <v>84</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>job-682d81b9</v>
+        <v>job-2b6f27da</v>
       </c>
       <c r="B82" t="str">
-        <v>Principal Product Manager (XDR &amp; Exposure Management) - Security Solutions</v>
+        <v>Senior Product Manager, Control Plane - Platform</v>
       </c>
       <c r="C82" t="str">
         <v>Elastic</v>
@@ -5387,16 +5387,16 @@
         <v>Senior Product Manager</v>
       </c>
       <c r="F82" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="G82" t="str">
-        <v>8+ yrs</v>
+        <v>5-8 yrs</v>
       </c>
       <c r="H82" t="str">
-        <v>Ireland</v>
+        <v>Canada</v>
       </c>
       <c r="I82" t="str">
-        <v>Ireland</v>
+        <v>Canada</v>
       </c>
       <c r="J82" t="str">
         <v>On-site</v>
@@ -5405,7 +5405,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L82" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8155326</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8093933</v>
       </c>
       <c r="M82">
         <v>200</v>
@@ -5414,27 +5414,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O82" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P82" t="str">
         <v>Today</v>
       </c>
       <c r="Q82" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R82" t="str">
         <v>No</v>
       </c>
       <c r="S82">
-        <v>39</v>
+        <v>27</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>job-64ec2b77</v>
+        <v>job-03cee7aa</v>
       </c>
       <c r="B83" t="str">
-        <v>Senior Director of Product Management, Endpoint Security &amp; XDR</v>
+        <v>Senior Product Manager, Logs - Observability</v>
       </c>
       <c r="C83" t="str">
         <v>Elastic</v>
@@ -5452,10 +5452,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H83" t="str">
-        <v>Canada</v>
+        <v>United States</v>
       </c>
       <c r="I83" t="str">
-        <v>Canada</v>
+        <v>United States</v>
       </c>
       <c r="J83" t="str">
         <v>On-site</v>
@@ -5464,7 +5464,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L83" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8214187</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8053907</v>
       </c>
       <c r="M83">
         <v>200</v>
@@ -5473,7 +5473,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O83" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P83" t="str">
         <v>Today</v>
@@ -5485,15 +5485,15 @@
         <v>Yes</v>
       </c>
       <c r="S83">
-        <v>73</v>
+        <v>82</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>job-2b6f27da</v>
+        <v>job-264c8d5a</v>
       </c>
       <c r="B84" t="str">
-        <v>Senior Product Manager, Control Plane - Platform</v>
+        <v>Senior Product Manager - Self service cloud</v>
       </c>
       <c r="C84" t="str">
         <v>Elastic</v>
@@ -5511,10 +5511,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H84" t="str">
-        <v>Canada</v>
+        <v>Spain</v>
       </c>
       <c r="I84" t="str">
-        <v>Canada</v>
+        <v>Spain</v>
       </c>
       <c r="J84" t="str">
         <v>On-site</v>
@@ -5523,7 +5523,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L84" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8093933</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8028261</v>
       </c>
       <c r="M84">
         <v>200</v>
@@ -5532,7 +5532,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O84" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P84" t="str">
         <v>Today</v>
@@ -5544,15 +5544,15 @@
         <v>No</v>
       </c>
       <c r="S84">
-        <v>73</v>
+        <v>40</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>job-03cee7aa</v>
+        <v>job-5b8ec8c1</v>
       </c>
       <c r="B85" t="str">
-        <v>Senior Product Manager, Logs - Observability</v>
+        <v>Senior Product Manager - US Public Sector</v>
       </c>
       <c r="C85" t="str">
         <v>Elastic</v>
@@ -5570,10 +5570,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H85" t="str">
-        <v>Ireland</v>
+        <v>United States</v>
       </c>
       <c r="I85" t="str">
-        <v>Ireland</v>
+        <v>United States</v>
       </c>
       <c r="J85" t="str">
         <v>On-site</v>
@@ -5582,7 +5582,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L85" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8066516</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8188365</v>
       </c>
       <c r="M85">
         <v>200</v>
@@ -5591,27 +5591,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O85" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P85" t="str">
         <v>Today</v>
       </c>
       <c r="Q85" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R85" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S85">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>job-264c8d5a</v>
+        <v>job-7ab91933</v>
       </c>
       <c r="B86" t="str">
-        <v>Senior Product Manager - Self service cloud</v>
+        <v>Senior Product Manager (XDR) - Security Solutions</v>
       </c>
       <c r="C86" t="str">
         <v>Elastic</v>
@@ -5629,10 +5629,10 @@
         <v>5-8 yrs</v>
       </c>
       <c r="H86" t="str">
-        <v>Norway</v>
+        <v>Ireland</v>
       </c>
       <c r="I86" t="str">
-        <v>Norway</v>
+        <v>Ireland</v>
       </c>
       <c r="J86" t="str">
         <v>On-site</v>
@@ -5641,7 +5641,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L86" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8041211</v>
+        <v>https://boards.greenhouse.io/elastic/jobs/8194072</v>
       </c>
       <c r="M86">
         <v>200</v>
@@ -5650,48 +5650,48 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O86" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P86" t="str">
         <v>Today</v>
       </c>
       <c r="Q86" t="str">
-        <v>Yes</v>
+        <v>No</v>
       </c>
       <c r="R86" t="str">
         <v>No</v>
       </c>
       <c r="S86">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>job-5b8ec8c1</v>
+        <v>job-31af15ee</v>
       </c>
       <c r="B87" t="str">
-        <v>Senior Product Manager - US Public Sector</v>
+        <v>AI Product Manager (Coding/Multimodal)</v>
       </c>
       <c r="C87" t="str">
-        <v>Elastic</v>
+        <v>Scale AI</v>
       </c>
       <c r="D87" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E87" t="str">
-        <v>Senior Product Manager</v>
+        <v>AI &amp; Growth PM</v>
       </c>
       <c r="F87" t="str">
-        <v>5-8 yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G87" t="str">
-        <v>5-8 yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H87" t="str">
-        <v>United States</v>
+        <v>San Francisco, CA</v>
       </c>
       <c r="I87" t="str">
-        <v>United States</v>
+        <v>San Francisco</v>
       </c>
       <c r="J87" t="str">
         <v>On-site</v>
@@ -5700,7 +5700,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L87" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8188365</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4609736005</v>
       </c>
       <c r="M87">
         <v>200</v>
@@ -5709,7 +5709,7 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O87" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P87" t="str">
         <v>Today</v>
@@ -5718,39 +5718,39 @@
         <v>Yes</v>
       </c>
       <c r="R87" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S87">
-        <v>30</v>
+        <v>70</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>job-7ab91933</v>
+        <v>job-184e55c8</v>
       </c>
       <c r="B88" t="str">
-        <v>Senior Product Manager (XDR) - Security Solutions</v>
+        <v>Director of Product Management, Enterprise Core Platform</v>
       </c>
       <c r="C88" t="str">
-        <v>Elastic</v>
+        <v>Scale AI</v>
       </c>
       <c r="D88" t="str">
-        <v>LinkedIn</v>
+        <v>Wellfound</v>
       </c>
       <c r="E88" t="str">
-        <v>Senior Product Manager</v>
+        <v>Technical Product Manager</v>
       </c>
       <c r="F88" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="G88" t="str">
-        <v>5-8 yrs</v>
+        <v>8+ yrs</v>
       </c>
       <c r="H88" t="str">
-        <v>United States</v>
+        <v>San Francisco, CA; New York, NY</v>
       </c>
       <c r="I88" t="str">
-        <v>United States</v>
+        <v>San Francisco</v>
       </c>
       <c r="J88" t="str">
         <v>On-site</v>
@@ -5759,7 +5759,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L88" t="str">
-        <v>https://boards.greenhouse.io/elastic/jobs/8167771</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4714727005</v>
       </c>
       <c r="M88">
         <v>200</v>
@@ -5768,27 +5768,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O88" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P88" t="str">
         <v>Today</v>
       </c>
       <c r="Q88" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R88" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="S88">
-        <v>76</v>
+        <v>53</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>job-31af15ee</v>
+        <v>job-6681e5c8</v>
       </c>
       <c r="B89" t="str">
-        <v>AI Product Manager (Coding/Multimodal)</v>
+        <v>Forward Deployed Product Manager, Enterprise</v>
       </c>
       <c r="C89" t="str">
         <v>Scale AI</v>
@@ -5797,7 +5797,7 @@
         <v>Wellfound</v>
       </c>
       <c r="E89" t="str">
-        <v>AI &amp; Growth PM</v>
+        <v>Product Manager</v>
       </c>
       <c r="F89" t="str">
         <v>3-6 yrs</v>
@@ -5806,10 +5806,10 @@
         <v>2-5 yrs</v>
       </c>
       <c r="H89" t="str">
-        <v>San Francisco, CA</v>
+        <v>London, UK</v>
       </c>
       <c r="I89" t="str">
-        <v>San Francisco</v>
+        <v>London</v>
       </c>
       <c r="J89" t="str">
         <v>On-site</v>
@@ -5818,7 +5818,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L89" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4609736005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4644742005</v>
       </c>
       <c r="M89">
         <v>200</v>
@@ -5827,27 +5827,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O89" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P89" t="str">
         <v>Today</v>
       </c>
       <c r="Q89" t="str">
-        <v>No</v>
+        <v>Yes</v>
       </c>
       <c r="R89" t="str">
         <v>No</v>
       </c>
       <c r="S89">
-        <v>53</v>
+        <v>41</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>job-184e55c8</v>
+        <v>job-11245f1c</v>
       </c>
       <c r="B90" t="str">
-        <v>Director of Product Management, Enterprise Core Platform</v>
+        <v>Forward Deployed Product Manager, Public Sector</v>
       </c>
       <c r="C90" t="str">
         <v>Scale AI</v>
@@ -5856,19 +5856,19 @@
         <v>Wellfound</v>
       </c>
       <c r="E90" t="str">
-        <v>Technical Product Manager</v>
+        <v>Product Manager</v>
       </c>
       <c r="F90" t="str">
-        <v>8+ yrs</v>
+        <v>3-6 yrs</v>
       </c>
       <c r="G90" t="str">
-        <v>8+ yrs</v>
+        <v>2-5 yrs</v>
       </c>
       <c r="H90" t="str">
-        <v>San Francisco, CA; New York, NY</v>
+        <v>New York, NY; Washington, DC</v>
       </c>
       <c r="I90" t="str">
-        <v>San Francisco</v>
+        <v>New York</v>
       </c>
       <c r="J90" t="str">
         <v>On-site</v>
@@ -5877,7 +5877,7 @@
         <v>$140k - $220k USD + Equity</v>
       </c>
       <c r="L90" t="str">
-        <v>https://boards.greenhouse.io/scaleai/jobs/4714727005</v>
+        <v>https://boards.greenhouse.io/scaleai/jobs/4713648005</v>
       </c>
       <c r="M90">
         <v>200</v>
@@ -5886,27 +5886,27 @@
         <v>ACTIVE / 100% VALID</v>
       </c>
       <c r="O90" t="str">
-        <v>2026-09-28</v>
+        <v>2026-09-29</v>
       </c>
       <c r="P90" t="str">
         <v>Today</v>
       </c>
       <c r="Q90" t="str">
-        <v>Yes</v